--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="152">
   <si>
     <t>_id</t>
   </si>
@@ -284,7 +284,13 @@
     <t>180006,180008,180010,180018,180020,180021</t>
   </si>
   <si>
-    <t>180001,180005,180007,180008,180009,180019</t>
+    <t>18,18,18,18,18,18,18,18,18</t>
+  </si>
+  <si>
+    <t>180001,180002,180004,180005,180007,180008,180009,180018,180019</t>
+  </si>
+  <si>
+    <t>1,1,1,1,1,1,1,1,1</t>
   </si>
   <si>
     <t>神技自选</t>
@@ -333,9 +339,6 @@
   </si>
   <si>
     <t>99,100,101,102,103,104,105</t>
-  </si>
-  <si>
-    <t>1,1,1,1,1,1,1,1,1</t>
   </si>
   <si>
     <t>法力盾4件套</t>
@@ -2182,13 +2185,13 @@
         <v>0</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I30" s="7" t="s">
-        <v>45</v>
+        <v>87</v>
       </c>
       <c r="J30" s="1" t="s">
         <v>65</v>
@@ -2199,7 +2202,7 @@
         <v>26</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
@@ -2208,16 +2211,16 @@
         <v>0</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H31" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="I31" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="J31" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="I31" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:10">
@@ -2225,7 +2228,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E32" s="1">
         <v>1</v>
@@ -2237,13 +2240,13 @@
         <v>35</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="I32" s="7" t="s">
         <v>37</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:10">
@@ -2251,7 +2254,7 @@
         <v>28</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E33" s="1">
         <v>1</v>
@@ -2260,16 +2263,16 @@
         <v>0</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I33" s="7" t="s">
         <v>45</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:10">
@@ -2277,7 +2280,7 @@
         <v>29</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E34" s="1">
         <v>1</v>
@@ -2289,13 +2292,13 @@
         <v>35</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I34" s="7" t="s">
         <v>37</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:10">
@@ -2303,7 +2306,7 @@
         <v>98</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E37" s="1">
         <v>1</v>
@@ -2312,16 +2315,16 @@
         <v>0</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H37" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="I37" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="J37" s="1" t="s">
         <v>101</v>
-      </c>
-      <c r="I37" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="J37" s="1" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:10">
@@ -2329,7 +2332,7 @@
         <v>99</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E38" s="1">
         <v>0</v>
@@ -2338,16 +2341,16 @@
         <v>0</v>
       </c>
       <c r="G38" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="H38" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="I38" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="J38" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="H38" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="I38" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="J38" s="1" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:10">
@@ -2355,7 +2358,7 @@
         <v>100</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E39" s="1">
         <v>0</v>
@@ -2364,16 +2367,16 @@
         <v>0</v>
       </c>
       <c r="G39" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="H39" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="I39" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="J39" s="1" t="s">
         <v>108</v>
-      </c>
-      <c r="H39" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="I39" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="J39" s="1" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:10">
@@ -2381,7 +2384,7 @@
         <v>101</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E40" s="1">
         <v>0</v>
@@ -2390,16 +2393,16 @@
         <v>0</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H40" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="I40" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="J40" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="I40" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="J40" s="1" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:10">
@@ -2407,7 +2410,7 @@
         <v>102</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E41" s="1">
         <v>0</v>
@@ -2416,16 +2419,16 @@
         <v>0</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H41" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="I41" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="J41" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="I41" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="J41" s="1" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:10">
@@ -2433,7 +2436,7 @@
         <v>103</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E42" s="1">
         <v>0</v>
@@ -2442,16 +2445,16 @@
         <v>0</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H42" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="I42" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="J42" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="I42" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="J42" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:10">
@@ -2459,7 +2462,7 @@
         <v>104</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E43" s="1">
         <v>0</v>
@@ -2468,16 +2471,16 @@
         <v>0</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H43" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="I43" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="J43" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="I43" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="J43" s="1" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:10">
@@ -2485,7 +2488,7 @@
         <v>105</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E44" s="1">
         <v>0</v>
@@ -2494,16 +2497,16 @@
         <v>0</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H44" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="I44" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="J44" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="I44" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="J44" s="1" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="3:10">
@@ -2511,7 +2514,7 @@
         <v>106</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E46" s="1">
         <v>1</v>
@@ -2520,16 +2523,16 @@
         <v>0</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H46" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I46" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:10">
@@ -2537,7 +2540,7 @@
         <v>107</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E47" s="1">
         <v>1</v>
@@ -2549,7 +2552,7 @@
         <v>66</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I47" s="7" t="s">
         <v>45</v>
@@ -2563,7 +2566,7 @@
         <v>108</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E48" s="1">
         <v>1</v>
@@ -2575,13 +2578,13 @@
         <v>66</v>
       </c>
       <c r="H48" s="7" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I48" s="7" t="s">
         <v>45</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="3:10">
@@ -2589,7 +2592,7 @@
         <v>109</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E50" s="1">
         <v>1</v>
@@ -2598,16 +2601,16 @@
         <v>0</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H50" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I50" s="7" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="3:10">
@@ -2615,7 +2618,7 @@
         <v>110</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E51" s="1">
         <v>1</v>
@@ -2624,16 +2627,16 @@
         <v>0</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H51" s="7" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I51" s="7" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="3:10">
@@ -2641,7 +2644,7 @@
         <v>111</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E52" s="1">
         <v>1</v>
@@ -2650,16 +2653,16 @@
         <v>0</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H52" s="7" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I52" s="7" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:10">
@@ -2667,7 +2670,7 @@
         <v>112</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E53" s="1">
         <v>1</v>
@@ -2676,16 +2679,16 @@
         <v>0</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H53" s="7" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I53" s="7" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:10">
@@ -2693,7 +2696,7 @@
         <v>113</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E54" s="1">
         <v>1</v>
@@ -2702,16 +2705,16 @@
         <v>0</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H54" s="7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I54" s="7" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:10">
@@ -2719,7 +2722,7 @@
         <v>114</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E55" s="1">
         <v>1</v>
@@ -2728,16 +2731,16 @@
         <v>0</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H55" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I55" s="7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="156">
   <si>
     <t>_id</t>
   </si>
@@ -330,6 +330,18 @@
   </si>
   <si>
     <t>战魂，法魂，道魂 三选一</t>
+  </si>
+  <si>
+    <t>极法宝自选</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>180030</t>
+  </si>
+  <si>
+    <t>1</t>
   </si>
   <si>
     <t>专属自选</t>
@@ -2301,12 +2313,38 @@
         <v>100</v>
       </c>
     </row>
+    <row r="35" customHeight="1" spans="3:10">
+      <c r="C35" s="1">
+        <v>30</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="E35" s="1">
+        <v>1</v>
+      </c>
+      <c r="F35" s="2">
+        <v>0</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="H35" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="I35" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
     <row r="37" customHeight="1" spans="3:10">
       <c r="C37" s="1">
         <v>98</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E37" s="1">
         <v>1</v>
@@ -2315,16 +2353,16 @@
         <v>0</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="I37" s="7" t="s">
         <v>87</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:10">
@@ -2332,7 +2370,7 @@
         <v>99</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E38" s="1">
         <v>0</v>
@@ -2341,16 +2379,16 @@
         <v>0</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H38" s="7" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="I38" s="7" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:10">
@@ -2358,7 +2396,7 @@
         <v>100</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E39" s="1">
         <v>0</v>
@@ -2367,16 +2405,16 @@
         <v>0</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="I39" s="7" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:10">
@@ -2384,7 +2422,7 @@
         <v>101</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E40" s="1">
         <v>0</v>
@@ -2393,16 +2431,16 @@
         <v>0</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H40" s="7" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="I40" s="7" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:10">
@@ -2410,7 +2448,7 @@
         <v>102</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E41" s="1">
         <v>0</v>
@@ -2419,16 +2457,16 @@
         <v>0</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="I41" s="7" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:10">
@@ -2436,7 +2474,7 @@
         <v>103</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E42" s="1">
         <v>0</v>
@@ -2445,16 +2483,16 @@
         <v>0</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H42" s="7" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="I42" s="7" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:10">
@@ -2462,7 +2500,7 @@
         <v>104</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E43" s="1">
         <v>0</v>
@@ -2471,16 +2509,16 @@
         <v>0</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H43" s="7" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="I43" s="7" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:10">
@@ -2488,7 +2526,7 @@
         <v>105</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E44" s="1">
         <v>0</v>
@@ -2497,16 +2535,16 @@
         <v>0</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="I44" s="7" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="3:10">
@@ -2514,7 +2552,7 @@
         <v>106</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E46" s="1">
         <v>1</v>
@@ -2523,16 +2561,16 @@
         <v>0</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="H46" s="7" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="I46" s="7" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:10">
@@ -2540,7 +2578,7 @@
         <v>107</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="E47" s="1">
         <v>1</v>
@@ -2552,7 +2590,7 @@
         <v>66</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="I47" s="7" t="s">
         <v>45</v>
@@ -2566,7 +2604,7 @@
         <v>108</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E48" s="1">
         <v>1</v>
@@ -2578,13 +2616,13 @@
         <v>66</v>
       </c>
       <c r="H48" s="7" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="I48" s="7" t="s">
         <v>45</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="3:10">
@@ -2592,7 +2630,7 @@
         <v>109</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E50" s="1">
         <v>1</v>
@@ -2601,16 +2639,16 @@
         <v>0</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="H50" s="7" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="I50" s="7" t="s">
         <v>87</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="3:10">
@@ -2618,7 +2656,7 @@
         <v>110</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E51" s="1">
         <v>1</v>
@@ -2627,16 +2665,16 @@
         <v>0</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="H51" s="7" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="I51" s="7" t="s">
         <v>87</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="3:10">
@@ -2644,7 +2682,7 @@
         <v>111</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E52" s="1">
         <v>1</v>
@@ -2653,16 +2691,16 @@
         <v>0</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="H52" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="I52" s="7" t="s">
         <v>87</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:10">
@@ -2670,7 +2708,7 @@
         <v>112</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="E53" s="1">
         <v>1</v>
@@ -2679,16 +2717,16 @@
         <v>0</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="H53" s="7" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="I53" s="7" t="s">
         <v>87</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:10">
@@ -2696,7 +2734,7 @@
         <v>113</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E54" s="1">
         <v>1</v>
@@ -2705,16 +2743,16 @@
         <v>0</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="H54" s="7" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="I54" s="7" t="s">
         <v>87</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:10">
@@ -2722,7 +2760,7 @@
         <v>114</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E55" s="1">
         <v>1</v>
@@ -2731,16 +2769,16 @@
         <v>0</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="H55" s="7" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="I55" s="7" t="s">
         <v>91</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="158">
   <si>
     <t>_id</t>
   </si>
@@ -495,6 +495,12 @@
   </si>
   <si>
     <t>道士输出红装自选</t>
+  </si>
+  <si>
+    <t>红装自选</t>
+  </si>
+  <si>
+    <t>109,110,111,112,113,114,115</t>
   </si>
 </sst>
 </file>
@@ -1468,7 +1474,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:J55"/>
+  <dimension ref="C3:J56"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -2781,6 +2787,32 @@
         <v>155</v>
       </c>
     </row>
+    <row r="56" customHeight="1" spans="3:10">
+      <c r="C56" s="1">
+        <v>115</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E56" s="1">
+        <v>1</v>
+      </c>
+      <c r="F56" s="2">
+        <v>0</v>
+      </c>
+      <c r="G56" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="H56" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="I56" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="2">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="F3:F5" errorStyle="warning">

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="159">
   <si>
     <t>_id</t>
   </si>
@@ -500,7 +500,10 @@
     <t>红装自选</t>
   </si>
   <si>
-    <t>109,110,111,112,113,114,115</t>
+    <t>4,4,4,4,4,4</t>
+  </si>
+  <si>
+    <t>109,110,111,112,113,114</t>
   </si>
 </sst>
 </file>
@@ -2801,13 +2804,13 @@
         <v>0</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>106</v>
+        <v>157</v>
       </c>
       <c r="H56" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I56" s="7" t="s">
-        <v>87</v>
+        <v>45</v>
       </c>
       <c r="J56" s="1" t="s">
         <v>156</v>

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="176">
   <si>
     <t>_id</t>
   </si>
@@ -332,16 +332,25 @@
     <t>战魂，法魂，道魂 三选一</t>
   </si>
   <si>
+    <t>极矿工礼包</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>180030</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
     <t>极法宝自选</t>
   </si>
   <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>180030</t>
-  </si>
-  <si>
-    <t>1</t>
+    <t>18,18,18</t>
+  </si>
+  <si>
+    <t>180032,180033,180034</t>
   </si>
   <si>
     <t>专属自选</t>
@@ -504,6 +513,48 @@
   </si>
   <si>
     <t>109,110,111,112,113,114</t>
+  </si>
+  <si>
+    <t>战士平衡金装</t>
+  </si>
+  <si>
+    <t>101,102,103,104,105,106,107,108</t>
+  </si>
+  <si>
+    <t>法师平衡金装</t>
+  </si>
+  <si>
+    <t>109,110,111,112,113,114,115,116</t>
+  </si>
+  <si>
+    <t>道士平衡金装</t>
+  </si>
+  <si>
+    <t>117,118,119,120,121,122,123,124</t>
+  </si>
+  <si>
+    <t>战士防御金装</t>
+  </si>
+  <si>
+    <t>125,126,127,128,129,130,131,132</t>
+  </si>
+  <si>
+    <t>法师输出金装</t>
+  </si>
+  <si>
+    <t>133,134,135,136,137,138,139,140</t>
+  </si>
+  <si>
+    <t>道士输出金装</t>
+  </si>
+  <si>
+    <t>141,142,143,144,145,146,147,148</t>
+  </si>
+  <si>
+    <t>金装自选</t>
+  </si>
+  <si>
+    <t>121,122,123,124,125,126</t>
   </si>
 </sst>
 </file>
@@ -516,7 +567,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -529,17 +580,9 @@
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="9"/>
       <color theme="1"/>
       <name val="等线"/>
@@ -1014,150 +1057,149 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1477,7 +1519,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:J56"/>
+  <dimension ref="C3:J65"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -1581,16 +1623,16 @@
       <c r="F6" s="1">
         <v>0</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I6" s="7" t="s">
+      <c r="I6" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="J6" s="6" t="s">
+      <c r="J6" s="5" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1607,16 +1649,16 @@
       <c r="F7" s="1">
         <v>0</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="H7" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="I7" s="7" t="s">
+      <c r="I7" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="J7" s="6" t="s">
+      <c r="J7" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1633,16 +1675,16 @@
       <c r="F8" s="1">
         <v>0</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="I8" s="7" t="s">
+      <c r="I8" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="J8" s="6" t="s">
+      <c r="J8" s="5" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1659,16 +1701,16 @@
       <c r="F9" s="1">
         <v>0</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="G9" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="I9" s="7" t="s">
+      <c r="I9" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="J9" s="6" t="s">
+      <c r="J9" s="5" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1685,16 +1727,16 @@
       <c r="F10" s="1">
         <v>0</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="G10" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="H10" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="I10" s="7" t="s">
+      <c r="I10" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="J10" s="6" t="s">
+      <c r="J10" s="5" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1711,16 +1753,16 @@
       <c r="F11" s="1">
         <v>0</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="G11" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="H11" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="I11" s="7" t="s">
+      <c r="I11" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="J11" s="6" t="s">
+      <c r="J11" s="5" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1737,13 +1779,13 @@
       <c r="F12" s="1">
         <v>0</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="G12" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="H12" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="I12" s="7" t="s">
+      <c r="I12" s="6" t="s">
         <v>15</v>
       </c>
       <c r="J12" s="1" t="s">
@@ -1763,13 +1805,13 @@
       <c r="F13" s="2">
         <v>0</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="G13" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="H13" s="7" t="s">
+      <c r="H13" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="I13" s="7" t="s">
+      <c r="I13" s="6" t="s">
         <v>37</v>
       </c>
       <c r="J13" s="1" t="s">
@@ -1789,13 +1831,13 @@
       <c r="F14" s="2">
         <v>0</v>
       </c>
-      <c r="G14" s="7" t="s">
+      <c r="G14" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="H14" s="7" t="s">
+      <c r="H14" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="I14" s="7" t="s">
+      <c r="I14" s="6" t="s">
         <v>37</v>
       </c>
       <c r="J14" s="1" t="s">
@@ -1806,22 +1848,22 @@
       <c r="C15" s="1">
         <v>10</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E15" s="4">
+      <c r="E15" s="1">
         <v>0</v>
       </c>
       <c r="F15" s="2">
         <v>0</v>
       </c>
-      <c r="G15" s="7" t="s">
+      <c r="G15" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H15" s="7" t="s">
+      <c r="H15" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="I15" s="7" t="s">
+      <c r="I15" s="6" t="s">
         <v>45</v>
       </c>
       <c r="J15" s="1" t="s">
@@ -1832,25 +1874,25 @@
       <c r="C16" s="1">
         <v>11</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E16" s="4">
+      <c r="E16" s="1">
         <v>0</v>
       </c>
       <c r="F16" s="2">
         <v>0</v>
       </c>
-      <c r="G16" s="7" t="s">
+      <c r="G16" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H16" s="7" t="s">
+      <c r="H16" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="I16" s="7" t="s">
+      <c r="I16" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J16" s="4" t="s">
+      <c r="J16" s="1" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1858,25 +1900,25 @@
       <c r="C17" s="1">
         <v>12</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E17" s="4">
+      <c r="E17" s="1">
         <v>0</v>
       </c>
       <c r="F17" s="2">
         <v>0</v>
       </c>
-      <c r="G17" s="7" t="s">
+      <c r="G17" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H17" s="7" t="s">
+      <c r="H17" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="I17" s="7" t="s">
+      <c r="I17" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J17" s="4" t="s">
+      <c r="J17" s="1" t="s">
         <v>52</v>
       </c>
     </row>
@@ -1893,13 +1935,13 @@
       <c r="F18" s="1">
         <v>0</v>
       </c>
-      <c r="G18" s="7" t="s">
+      <c r="G18" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="H18" s="7" t="s">
+      <c r="H18" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="I18" s="7" t="s">
+      <c r="I18" s="6" t="s">
         <v>15</v>
       </c>
       <c r="J18" s="1" t="s">
@@ -1919,13 +1961,13 @@
       <c r="F19" s="2">
         <v>0</v>
       </c>
-      <c r="G19" s="7" t="s">
+      <c r="G19" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="H19" s="7" t="s">
+      <c r="H19" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="I19" s="7" t="s">
+      <c r="I19" s="6" t="s">
         <v>15</v>
       </c>
       <c r="J19" s="1" t="s">
@@ -1936,25 +1978,25 @@
       <c r="C20" s="1">
         <v>15</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="E20" s="4">
+      <c r="E20" s="1">
         <v>0</v>
       </c>
       <c r="F20" s="2">
         <v>0</v>
       </c>
-      <c r="G20" s="7" t="s">
+      <c r="G20" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H20" s="7" t="s">
+      <c r="H20" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="I20" s="7" t="s">
+      <c r="I20" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J20" s="4" t="s">
+      <c r="J20" s="1" t="s">
         <v>59</v>
       </c>
     </row>
@@ -1962,25 +2004,25 @@
       <c r="C21" s="1">
         <v>16</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="E21" s="4">
+      <c r="E21" s="1">
         <v>0</v>
       </c>
       <c r="F21" s="2">
         <v>0</v>
       </c>
-      <c r="G21" s="7" t="s">
+      <c r="G21" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H21" s="7" t="s">
+      <c r="H21" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="I21" s="7" t="s">
+      <c r="I21" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J21" s="4" t="s">
+      <c r="J21" s="1" t="s">
         <v>61</v>
       </c>
     </row>
@@ -1988,25 +2030,25 @@
       <c r="C22" s="1">
         <v>17</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="E22" s="4">
+      <c r="E22" s="1">
         <v>0</v>
       </c>
       <c r="F22" s="2">
         <v>0</v>
       </c>
-      <c r="G22" s="7" t="s">
+      <c r="G22" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H22" s="7" t="s">
+      <c r="H22" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="I22" s="7" t="s">
+      <c r="I22" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J22" s="4" t="s">
+      <c r="J22" s="1" t="s">
         <v>63</v>
       </c>
     </row>
@@ -2023,13 +2065,13 @@
       <c r="F23" s="2">
         <v>0</v>
       </c>
-      <c r="G23" s="7" t="s">
+      <c r="G23" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="H23" s="7" t="s">
+      <c r="H23" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="I23" s="7" t="s">
+      <c r="I23" s="6" t="s">
         <v>45</v>
       </c>
       <c r="J23" s="1" t="s">
@@ -2049,13 +2091,13 @@
       <c r="F24" s="2">
         <v>0</v>
       </c>
-      <c r="G24" s="7" t="s">
+      <c r="G24" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="H24" s="7" t="s">
+      <c r="H24" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="I24" s="7" t="s">
+      <c r="I24" s="6" t="s">
         <v>45</v>
       </c>
       <c r="J24" s="1" t="s">
@@ -2075,13 +2117,13 @@
       <c r="F25" s="2">
         <v>0</v>
       </c>
-      <c r="G25" s="7" t="s">
+      <c r="G25" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="H25" s="7" t="s">
+      <c r="H25" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="I25" s="7" t="s">
+      <c r="I25" s="6" t="s">
         <v>45</v>
       </c>
       <c r="J25" s="1" t="s">
@@ -2101,16 +2143,16 @@
       <c r="F26" s="1">
         <v>0</v>
       </c>
-      <c r="G26" s="7" t="s">
+      <c r="G26" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="H26" s="7" t="s">
+      <c r="H26" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="I26" s="7" t="s">
+      <c r="I26" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="J26" s="4" t="s">
+      <c r="J26" s="1" t="s">
         <v>77</v>
       </c>
     </row>
@@ -2127,16 +2169,16 @@
       <c r="F27" s="1">
         <v>0</v>
       </c>
-      <c r="G27" s="7" t="s">
+      <c r="G27" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="H27" s="7" t="s">
+      <c r="H27" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="I27" s="7" t="s">
+      <c r="I27" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J27" s="4" t="s">
+      <c r="J27" s="1" t="s">
         <v>78</v>
       </c>
     </row>
@@ -2153,13 +2195,13 @@
       <c r="F28" s="1">
         <v>0</v>
       </c>
-      <c r="G28" s="7" t="s">
+      <c r="G28" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="H28" s="7" t="s">
+      <c r="H28" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="I28" s="7" t="s">
+      <c r="I28" s="6" t="s">
         <v>45</v>
       </c>
       <c r="J28" s="1" t="s">
@@ -2179,13 +2221,13 @@
       <c r="F29" s="2">
         <v>0</v>
       </c>
-      <c r="G29" s="7" t="s">
+      <c r="G29" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="H29" s="7" t="s">
+      <c r="H29" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="I29" s="7" t="s">
+      <c r="I29" s="6" t="s">
         <v>45</v>
       </c>
       <c r="J29" s="1" t="s">
@@ -2205,13 +2247,13 @@
       <c r="F30" s="2">
         <v>0</v>
       </c>
-      <c r="G30" s="7" t="s">
+      <c r="G30" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="H30" s="7" t="s">
+      <c r="H30" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="I30" s="7" t="s">
+      <c r="I30" s="6" t="s">
         <v>87</v>
       </c>
       <c r="J30" s="1" t="s">
@@ -2231,13 +2273,13 @@
       <c r="F31" s="2">
         <v>0</v>
       </c>
-      <c r="G31" s="7" t="s">
+      <c r="G31" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="H31" s="7" t="s">
+      <c r="H31" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="I31" s="7" t="s">
+      <c r="I31" s="6" t="s">
         <v>91</v>
       </c>
       <c r="J31" s="1" t="s">
@@ -2257,13 +2299,13 @@
       <c r="F32" s="2">
         <v>0</v>
       </c>
-      <c r="G32" s="7" t="s">
+      <c r="G32" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="H32" s="7" t="s">
+      <c r="H32" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="I32" s="7" t="s">
+      <c r="I32" s="6" t="s">
         <v>37</v>
       </c>
       <c r="J32" s="1" t="s">
@@ -2283,13 +2325,13 @@
       <c r="F33" s="2">
         <v>0</v>
       </c>
-      <c r="G33" s="7" t="s">
+      <c r="G33" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="H33" s="8" t="s">
+      <c r="H33" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="I33" s="7" t="s">
+      <c r="I33" s="6" t="s">
         <v>45</v>
       </c>
       <c r="J33" s="1" t="s">
@@ -2309,13 +2351,13 @@
       <c r="F34" s="2">
         <v>0</v>
       </c>
-      <c r="G34" s="7" t="s">
+      <c r="G34" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="H34" s="7" t="s">
+      <c r="H34" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="I34" s="7" t="s">
+      <c r="I34" s="6" t="s">
         <v>37</v>
       </c>
       <c r="J34" s="1" t="s">
@@ -2326,7 +2368,7 @@
       <c r="C35" s="1">
         <v>30</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D35" s="1" t="s">
         <v>101</v>
       </c>
       <c r="E35" s="1">
@@ -2335,66 +2377,66 @@
       <c r="F35" s="2">
         <v>0</v>
       </c>
-      <c r="G35" s="7" t="s">
+      <c r="G35" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="H35" s="7" t="s">
+      <c r="H35" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="I35" s="7" t="s">
+      <c r="I35" s="6" t="s">
         <v>104</v>
       </c>
       <c r="J35" s="1" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="37" customHeight="1" spans="3:10">
-      <c r="C37" s="1">
-        <v>98</v>
-      </c>
-      <c r="D37" s="1" t="s">
+    <row r="36" customHeight="1" spans="3:10">
+      <c r="C36" s="1">
+        <v>31</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="E37" s="1">
-        <v>1</v>
-      </c>
-      <c r="F37" s="2">
-        <v>0</v>
-      </c>
-      <c r="G37" s="7" t="s">
+      <c r="E36" s="1">
+        <v>1</v>
+      </c>
+      <c r="F36" s="2">
+        <v>0</v>
+      </c>
+      <c r="G36" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="H37" s="7" t="s">
+      <c r="H36" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="I37" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="J37" s="1" t="s">
+      <c r="I36" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="J36" s="1" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:10">
       <c r="C38" s="1">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>108</v>
       </c>
       <c r="E38" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38" s="2">
         <v>0</v>
       </c>
-      <c r="G38" s="7" t="s">
+      <c r="G38" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="H38" s="7" t="s">
+      <c r="H38" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="I38" s="7" t="s">
-        <v>111</v>
+      <c r="I38" s="6" t="s">
+        <v>87</v>
       </c>
       <c r="J38" s="1" t="s">
         <v>108</v>
@@ -2402,62 +2444,62 @@
     </row>
     <row r="39" customHeight="1" spans="3:10">
       <c r="C39" s="1">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D39" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E39" s="1">
+        <v>0</v>
+      </c>
+      <c r="F39" s="2">
+        <v>0</v>
+      </c>
+      <c r="G39" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="E39" s="1">
-        <v>0</v>
-      </c>
-      <c r="F39" s="2">
-        <v>0</v>
-      </c>
-      <c r="G39" s="7" t="s">
+      <c r="H39" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="H39" s="7" t="s">
+      <c r="I39" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="I39" s="7" t="s">
-        <v>115</v>
-      </c>
       <c r="J39" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:10">
       <c r="C40" s="1">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D40" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E40" s="1">
+        <v>0</v>
+      </c>
+      <c r="F40" s="2">
+        <v>0</v>
+      </c>
+      <c r="G40" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E40" s="1">
-        <v>0</v>
-      </c>
-      <c r="F40" s="2">
-        <v>0</v>
-      </c>
-      <c r="G40" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="H40" s="7" t="s">
+      <c r="H40" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="I40" s="7" t="s">
-        <v>111</v>
+      <c r="I40" s="6" t="s">
+        <v>118</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:10">
       <c r="C41" s="1">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E41" s="1">
         <v>0</v>
@@ -2465,25 +2507,25 @@
       <c r="F41" s="2">
         <v>0</v>
       </c>
-      <c r="G41" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="H41" s="7" t="s">
+      <c r="G41" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="H41" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="I41" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="J41" s="1" t="s">
         <v>119</v>
-      </c>
-      <c r="I41" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="J41" s="1" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:10">
       <c r="C42" s="1">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E42" s="1">
         <v>0</v>
@@ -2491,25 +2533,25 @@
       <c r="F42" s="2">
         <v>0</v>
       </c>
-      <c r="G42" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="H42" s="7" t="s">
+      <c r="G42" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="H42" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="I42" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="J42" s="1" t="s">
         <v>121</v>
-      </c>
-      <c r="I42" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="J42" s="1" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:10">
       <c r="C43" s="1">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E43" s="1">
         <v>0</v>
@@ -2517,169 +2559,169 @@
       <c r="F43" s="2">
         <v>0</v>
       </c>
-      <c r="G43" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="H43" s="7" t="s">
+      <c r="G43" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="H43" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="I43" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="J43" s="1" t="s">
         <v>123</v>
-      </c>
-      <c r="I43" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="J43" s="1" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:10">
       <c r="C44" s="1">
+        <v>104</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E44" s="1">
+        <v>0</v>
+      </c>
+      <c r="F44" s="2">
+        <v>0</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="H44" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="I44" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="3:10">
+      <c r="C45" s="1">
         <v>105</v>
       </c>
-      <c r="D44" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="E44" s="1">
-        <v>0</v>
-      </c>
-      <c r="F44" s="2">
-        <v>0</v>
-      </c>
-      <c r="G44" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="H44" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="I44" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="J44" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="46" customHeight="1" spans="3:10">
-      <c r="C46" s="1">
-        <v>106</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="E46" s="1">
-        <v>1</v>
-      </c>
-      <c r="F46" s="2">
-        <v>0</v>
-      </c>
-      <c r="G46" s="7" t="s">
+      <c r="D45" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="H46" s="7" t="s">
+      <c r="E45" s="1">
+        <v>0</v>
+      </c>
+      <c r="F45" s="2">
+        <v>0</v>
+      </c>
+      <c r="G45" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="H45" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="I46" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="J46" s="1" t="s">
-        <v>130</v>
+      <c r="I45" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:10">
       <c r="C47" s="1">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D47" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E47" s="1">
+        <v>1</v>
+      </c>
+      <c r="F47" s="2">
+        <v>0</v>
+      </c>
+      <c r="G47" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="H47" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="E47" s="1">
-        <v>1</v>
-      </c>
-      <c r="F47" s="2">
-        <v>0</v>
-      </c>
-      <c r="G47" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="H47" s="7" t="s">
+      <c r="I47" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="I47" s="7" t="s">
-        <v>45</v>
-      </c>
       <c r="J47" s="1" t="s">
-        <v>83</v>
+        <v>133</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:10">
       <c r="C48" s="1">
+        <v>107</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E48" s="1">
+        <v>1</v>
+      </c>
+      <c r="F48" s="2">
+        <v>0</v>
+      </c>
+      <c r="G48" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="H48" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="I48" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="49" customHeight="1" spans="3:10">
+      <c r="C49" s="1">
         <v>108</v>
       </c>
-      <c r="D48" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="E48" s="1">
-        <v>1</v>
-      </c>
-      <c r="F48" s="2">
-        <v>0</v>
-      </c>
-      <c r="G48" s="7" t="s">
+      <c r="D49" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E49" s="1">
+        <v>1</v>
+      </c>
+      <c r="F49" s="2">
+        <v>0</v>
+      </c>
+      <c r="G49" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="H48" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="I48" s="7" t="s">
+      <c r="H49" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="I49" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J48" s="1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="50" customHeight="1" spans="3:10">
-      <c r="C50" s="1">
-        <v>109</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="E50" s="1">
-        <v>1</v>
-      </c>
-      <c r="F50" s="2">
-        <v>0</v>
-      </c>
-      <c r="G50" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="H50" s="7" t="s">
+      <c r="J49" s="1" t="s">
         <v>138</v>
-      </c>
-      <c r="I50" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="J50" s="1" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="3:10">
       <c r="C51" s="1">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D51" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E51" s="1">
+        <v>1</v>
+      </c>
+      <c r="F51" s="2">
+        <v>0</v>
+      </c>
+      <c r="G51" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="E51" s="1">
-        <v>1</v>
-      </c>
-      <c r="F51" s="2">
-        <v>0</v>
-      </c>
-      <c r="G51" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="H51" s="7" t="s">
+      <c r="H51" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="I51" s="7" t="s">
+      <c r="I51" s="6" t="s">
         <v>87</v>
       </c>
       <c r="J51" s="1" t="s">
@@ -2688,7 +2730,7 @@
     </row>
     <row r="52" customHeight="1" spans="3:10">
       <c r="C52" s="1">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>143</v>
@@ -2699,13 +2741,13 @@
       <c r="F52" s="2">
         <v>0</v>
       </c>
-      <c r="G52" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="H52" s="7" t="s">
+      <c r="G52" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="I52" s="7" t="s">
+      <c r="I52" s="6" t="s">
         <v>87</v>
       </c>
       <c r="J52" s="1" t="s">
@@ -2714,7 +2756,7 @@
     </row>
     <row r="53" customHeight="1" spans="3:10">
       <c r="C53" s="1">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>146</v>
@@ -2725,13 +2767,13 @@
       <c r="F53" s="2">
         <v>0</v>
       </c>
-      <c r="G53" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="H53" s="7" t="s">
+      <c r="G53" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="H53" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="I53" s="7" t="s">
+      <c r="I53" s="6" t="s">
         <v>87</v>
       </c>
       <c r="J53" s="1" t="s">
@@ -2740,7 +2782,7 @@
     </row>
     <row r="54" customHeight="1" spans="3:10">
       <c r="C54" s="1">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>149</v>
@@ -2751,13 +2793,13 @@
       <c r="F54" s="2">
         <v>0</v>
       </c>
-      <c r="G54" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="H54" s="7" t="s">
+      <c r="G54" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="I54" s="7" t="s">
+      <c r="I54" s="6" t="s">
         <v>87</v>
       </c>
       <c r="J54" s="1" t="s">
@@ -2766,7 +2808,7 @@
     </row>
     <row r="55" customHeight="1" spans="3:10">
       <c r="C55" s="1">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>152</v>
@@ -2777,43 +2819,251 @@
       <c r="F55" s="2">
         <v>0</v>
       </c>
-      <c r="G55" s="7" t="s">
+      <c r="G55" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="H55" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="H55" s="7" t="s">
+      <c r="I55" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="J55" s="1" t="s">
         <v>154</v>
-      </c>
-      <c r="I55" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="J55" s="1" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:10">
       <c r="C56" s="1">
+        <v>114</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E56" s="1">
+        <v>1</v>
+      </c>
+      <c r="F56" s="2">
+        <v>0</v>
+      </c>
+      <c r="G56" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="H56" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="I56" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="3:10">
+      <c r="C57" s="1">
         <v>115</v>
       </c>
-      <c r="D56" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="E56" s="1">
-        <v>1</v>
-      </c>
-      <c r="F56" s="2">
-        <v>0</v>
-      </c>
-      <c r="G56" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="H56" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="I56" s="7" t="s">
+      <c r="D57" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E57" s="1">
+        <v>1</v>
+      </c>
+      <c r="F57" s="2">
+        <v>0</v>
+      </c>
+      <c r="G57" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="H57" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="I57" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J56" s="1" t="s">
-        <v>156</v>
+      <c r="J57" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="59" customHeight="1" spans="3:10">
+      <c r="C59" s="1">
+        <v>121</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E59" s="1">
+        <v>1</v>
+      </c>
+      <c r="F59" s="2">
+        <v>0</v>
+      </c>
+      <c r="G59" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="H59" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="I59" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="J59" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="60" customHeight="1" spans="3:10">
+      <c r="C60" s="1">
+        <v>122</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="E60" s="1">
+        <v>1</v>
+      </c>
+      <c r="F60" s="2">
+        <v>0</v>
+      </c>
+      <c r="G60" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="H60" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="I60" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="J60" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="61" customHeight="1" spans="3:10">
+      <c r="C61" s="1">
+        <v>123</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E61" s="1">
+        <v>1</v>
+      </c>
+      <c r="F61" s="2">
+        <v>0</v>
+      </c>
+      <c r="G61" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="H61" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="I61" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="J61" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="62" customHeight="1" spans="3:10">
+      <c r="C62" s="1">
+        <v>124</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E62" s="1">
+        <v>1</v>
+      </c>
+      <c r="F62" s="2">
+        <v>0</v>
+      </c>
+      <c r="G62" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="H62" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="I62" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="J62" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="63" customHeight="1" spans="3:10">
+      <c r="C63" s="1">
+        <v>125</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="E63" s="1">
+        <v>1</v>
+      </c>
+      <c r="F63" s="2">
+        <v>0</v>
+      </c>
+      <c r="G63" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="H63" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="I63" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="J63" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="64" customHeight="1" spans="3:10">
+      <c r="C64" s="1">
+        <v>126</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E64" s="1">
+        <v>1</v>
+      </c>
+      <c r="F64" s="2">
+        <v>0</v>
+      </c>
+      <c r="G64" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="H64" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="I64" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="J64" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="65" customHeight="1" spans="3:10">
+      <c r="C65" s="1">
+        <v>127</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E65" s="1">
+        <v>1</v>
+      </c>
+      <c r="F65" s="2">
+        <v>0</v>
+      </c>
+      <c r="G65" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="H65" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="I65" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="J65" s="1" t="s">
+        <v>174</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="176">
   <si>
     <t>_id</t>
   </si>
@@ -545,16 +545,16 @@
     <t>133,134,135,136,137,138,139,140</t>
   </si>
   <si>
-    <t>道士输出金装</t>
-  </si>
-  <si>
-    <t>141,142,143,144,145,146,147,148</t>
-  </si>
-  <si>
     <t>金装自选</t>
   </si>
   <si>
-    <t>121,122,123,124,125,126</t>
+    <t>4,4,4,4,4</t>
+  </si>
+  <si>
+    <t>121,122,123,124,125</t>
+  </si>
+  <si>
+    <t>1,1,1,1,1,1,1</t>
   </si>
 </sst>
 </file>
@@ -3014,56 +3014,30 @@
         <v>170</v>
       </c>
     </row>
-    <row r="64" customHeight="1" spans="3:10">
-      <c r="C64" s="1">
-        <v>126</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="E64" s="1">
-        <v>1</v>
-      </c>
-      <c r="F64" s="2">
-        <v>0</v>
-      </c>
-      <c r="G64" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="I64" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="J64" s="1" t="s">
-        <v>172</v>
-      </c>
-    </row>
     <row r="65" customHeight="1" spans="3:10">
       <c r="C65" s="1">
         <v>127</v>
       </c>
       <c r="D65" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E65" s="1">
+        <v>1</v>
+      </c>
+      <c r="F65" s="2">
+        <v>0</v>
+      </c>
+      <c r="G65" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="H65" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="E65" s="1">
-        <v>1</v>
-      </c>
-      <c r="F65" s="2">
-        <v>0</v>
-      </c>
-      <c r="G65" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="H65" s="6" t="s">
+      <c r="I65" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="I65" s="6" t="s">
-        <v>37</v>
-      </c>
       <c r="J65" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="174">
   <si>
     <t>_id</t>
   </si>
@@ -548,13 +548,7 @@
     <t>金装自选</t>
   </si>
   <si>
-    <t>4,4,4,4,4</t>
-  </si>
-  <si>
     <t>121,122,123,124,125</t>
-  </si>
-  <si>
-    <t>1,1,1,1,1,1,1</t>
   </si>
 </sst>
 </file>
@@ -2410,7 +2404,7 @@
         <v>107</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>104</v>
+        <v>37</v>
       </c>
       <c r="J36" s="1" t="s">
         <v>105</v>
@@ -3028,13 +3022,13 @@
         <v>0</v>
       </c>
       <c r="G65" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="H65" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="H65" s="6" t="s">
-        <v>174</v>
-      </c>
       <c r="I65" s="6" t="s">
-        <v>175</v>
+        <v>45</v>
       </c>
       <c r="J65" s="1" t="s">
         <v>172</v>

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="175">
   <si>
     <t>_id</t>
   </si>
@@ -275,7 +275,13 @@
     <t>升级自选</t>
   </si>
   <si>
-    <t>807,808,809,810,811,812</t>
+    <t>12,12,12,12,12,12,12,12,12</t>
+  </si>
+  <si>
+    <t>807,808,809,810,811,812,813,814,815</t>
+  </si>
+  <si>
+    <t>1,1,1,1,1,1,1,1,1,1,1</t>
   </si>
   <si>
     <t>初级法宝自选</t>
@@ -300,9 +306,6 @@
   </si>
   <si>
     <t>8001,8002,8003,8004,8005,8006,8007,8008,8009,8010</t>
-  </si>
-  <si>
-    <t>1,1,1,1,1,1,1,1,1,1,1</t>
   </si>
   <si>
     <t>10阶级技能自选</t>
@@ -2190,13 +2193,13 @@
         <v>0</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>13</v>
+        <v>82</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="J28" s="1" t="s">
         <v>81</v>
@@ -2207,7 +2210,7 @@
         <v>24</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
@@ -2219,13 +2222,13 @@
         <v>66</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I29" s="6" t="s">
         <v>45</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:10">
@@ -2242,13 +2245,13 @@
         <v>0</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J30" s="1" t="s">
         <v>65</v>
@@ -2259,7 +2262,7 @@
         <v>26</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
@@ -2268,16 +2271,16 @@
         <v>0</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H31" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="J31" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="I31" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:10">
@@ -2285,7 +2288,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E32" s="1">
         <v>1</v>
@@ -2297,13 +2300,13 @@
         <v>35</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I32" s="6" t="s">
         <v>37</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:10">
@@ -2311,7 +2314,7 @@
         <v>28</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E33" s="1">
         <v>1</v>
@@ -2320,16 +2323,16 @@
         <v>0</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I33" s="6" t="s">
         <v>45</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:10">
@@ -2337,7 +2340,7 @@
         <v>29</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E34" s="1">
         <v>1</v>
@@ -2349,13 +2352,13 @@
         <v>35</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I34" s="6" t="s">
         <v>37</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:10">
@@ -2363,7 +2366,7 @@
         <v>30</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E35" s="1">
         <v>1</v>
@@ -2372,16 +2375,16 @@
         <v>0</v>
       </c>
       <c r="G35" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="J35" s="1" t="s">
         <v>102</v>
-      </c>
-      <c r="H35" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="I35" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="J35" s="1" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:10">
@@ -2389,7 +2392,7 @@
         <v>31</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E36" s="1">
         <v>1</v>
@@ -2398,16 +2401,16 @@
         <v>0</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I36" s="6" t="s">
         <v>37</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:10">
@@ -2415,7 +2418,7 @@
         <v>98</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E38" s="1">
         <v>1</v>
@@ -2424,16 +2427,16 @@
         <v>0</v>
       </c>
       <c r="G38" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="H38" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="I38" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="J38" s="1" t="s">
         <v>109</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="I38" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="J38" s="1" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:10">
@@ -2441,7 +2444,7 @@
         <v>99</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E39" s="1">
         <v>0</v>
@@ -2450,16 +2453,16 @@
         <v>0</v>
       </c>
       <c r="G39" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="H39" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="I39" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="J39" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="H39" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="I39" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="J39" s="1" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:10">
@@ -2467,7 +2470,7 @@
         <v>100</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E40" s="1">
         <v>0</v>
@@ -2476,16 +2479,16 @@
         <v>0</v>
       </c>
       <c r="G40" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="I40" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="J40" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="I40" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="J40" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:10">
@@ -2493,7 +2496,7 @@
         <v>101</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E41" s="1">
         <v>0</v>
@@ -2502,16 +2505,16 @@
         <v>0</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H41" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="I41" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="J41" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="I41" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="J41" s="1" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:10">
@@ -2519,7 +2522,7 @@
         <v>102</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E42" s="1">
         <v>0</v>
@@ -2528,16 +2531,16 @@
         <v>0</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H42" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="I42" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="J42" s="1" t="s">
         <v>122</v>
-      </c>
-      <c r="I42" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="J42" s="1" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:10">
@@ -2545,7 +2548,7 @@
         <v>103</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E43" s="1">
         <v>0</v>
@@ -2554,16 +2557,16 @@
         <v>0</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H43" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="I43" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="J43" s="1" t="s">
         <v>124</v>
-      </c>
-      <c r="I43" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="J43" s="1" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:10">
@@ -2571,7 +2574,7 @@
         <v>104</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E44" s="1">
         <v>0</v>
@@ -2580,16 +2583,16 @@
         <v>0</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H44" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="I44" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="J44" s="1" t="s">
         <v>126</v>
-      </c>
-      <c r="I44" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="J44" s="1" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:10">
@@ -2597,7 +2600,7 @@
         <v>105</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E45" s="1">
         <v>0</v>
@@ -2606,16 +2609,16 @@
         <v>0</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H45" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="I45" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="J45" s="1" t="s">
         <v>128</v>
-      </c>
-      <c r="I45" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="J45" s="1" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:10">
@@ -2623,7 +2626,7 @@
         <v>106</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E47" s="1">
         <v>1</v>
@@ -2632,16 +2635,16 @@
         <v>0</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:10">
@@ -2649,7 +2652,7 @@
         <v>107</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E48" s="1">
         <v>1</v>
@@ -2661,13 +2664,13 @@
         <v>66</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I48" s="6" t="s">
         <v>45</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="3:10">
@@ -2675,7 +2678,7 @@
         <v>108</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E49" s="1">
         <v>1</v>
@@ -2687,13 +2690,13 @@
         <v>66</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I49" s="6" t="s">
         <v>45</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="3:10">
@@ -2701,7 +2704,7 @@
         <v>109</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E51" s="1">
         <v>1</v>
@@ -2710,16 +2713,16 @@
         <v>0</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="3:10">
@@ -2727,7 +2730,7 @@
         <v>110</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E52" s="1">
         <v>1</v>
@@ -2736,16 +2739,16 @@
         <v>0</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I52" s="6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:10">
@@ -2753,7 +2756,7 @@
         <v>111</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E53" s="1">
         <v>1</v>
@@ -2762,16 +2765,16 @@
         <v>0</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I53" s="6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:10">
@@ -2779,7 +2782,7 @@
         <v>112</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E54" s="1">
         <v>1</v>
@@ -2788,16 +2791,16 @@
         <v>0</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:10">
@@ -2805,7 +2808,7 @@
         <v>113</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E55" s="1">
         <v>1</v>
@@ -2814,16 +2817,16 @@
         <v>0</v>
       </c>
       <c r="G55" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I55" s="6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:10">
@@ -2831,7 +2834,7 @@
         <v>114</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E56" s="1">
         <v>1</v>
@@ -2840,16 +2843,16 @@
         <v>0</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I56" s="6" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:10">
@@ -2857,7 +2860,7 @@
         <v>115</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E57" s="1">
         <v>1</v>
@@ -2866,16 +2869,16 @@
         <v>0</v>
       </c>
       <c r="G57" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I57" s="6" t="s">
         <v>45</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:10">
@@ -2883,7 +2886,7 @@
         <v>121</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E59" s="1">
         <v>1</v>
@@ -2892,16 +2895,16 @@
         <v>0</v>
       </c>
       <c r="G59" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H59" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="I59" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="J59" s="2" t="s">
         <v>163</v>
-      </c>
-      <c r="I59" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="J59" s="2" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="3:10">
@@ -2909,7 +2912,7 @@
         <v>122</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E60" s="1">
         <v>1</v>
@@ -2918,16 +2921,16 @@
         <v>0</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H60" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="I60" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="J60" s="2" t="s">
         <v>165</v>
-      </c>
-      <c r="I60" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="J60" s="2" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="3:10">
@@ -2935,7 +2938,7 @@
         <v>123</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E61" s="1">
         <v>1</v>
@@ -2944,16 +2947,16 @@
         <v>0</v>
       </c>
       <c r="G61" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H61" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="I61" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="J61" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="I61" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="J61" s="2" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="3:10">
@@ -2961,7 +2964,7 @@
         <v>124</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E62" s="1">
         <v>1</v>
@@ -2970,16 +2973,16 @@
         <v>0</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H62" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="I62" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="J62" s="1" t="s">
         <v>169</v>
-      </c>
-      <c r="I62" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="J62" s="1" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="3:10">
@@ -2987,7 +2990,7 @@
         <v>125</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E63" s="1">
         <v>1</v>
@@ -2996,16 +2999,16 @@
         <v>0</v>
       </c>
       <c r="G63" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H63" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="I63" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="J63" s="1" t="s">
         <v>171</v>
-      </c>
-      <c r="I63" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="J63" s="1" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:10">
@@ -3013,7 +3016,7 @@
         <v>127</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E65" s="1">
         <v>1</v>
@@ -3022,16 +3025,16 @@
         <v>0</v>
       </c>
       <c r="G65" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I65" s="6" t="s">
         <v>45</v>
       </c>
       <c r="J65" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="178">
   <si>
     <t>_id</t>
   </si>
@@ -354,6 +354,15 @@
   </si>
   <si>
     <t>180032,180033,180034</t>
+  </si>
+  <si>
+    <t>盾专属自选套</t>
+  </si>
+  <si>
+    <t>4,4,4,4</t>
+  </si>
+  <si>
+    <t>99,102,104</t>
   </si>
   <si>
     <t>专属自选</t>
@@ -1516,7 +1525,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:J65"/>
+  <dimension ref="C3:J66"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -2415,7 +2424,7 @@
     </row>
     <row r="38" customHeight="1" spans="3:10">
       <c r="C38" s="1">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>109</v>
@@ -2433,7 +2442,7 @@
         <v>111</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>89</v>
+        <v>37</v>
       </c>
       <c r="J38" s="1" t="s">
         <v>109</v>
@@ -2441,13 +2450,13 @@
     </row>
     <row r="39" customHeight="1" spans="3:10">
       <c r="C39" s="1">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>112</v>
       </c>
       <c r="E39" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39" s="2">
         <v>0</v>
@@ -2459,7 +2468,7 @@
         <v>114</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>115</v>
+        <v>89</v>
       </c>
       <c r="J39" s="1" t="s">
         <v>112</v>
@@ -2467,62 +2476,62 @@
     </row>
     <row r="40" customHeight="1" spans="3:10">
       <c r="C40" s="1">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D40" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E40" s="1">
+        <v>0</v>
+      </c>
+      <c r="F40" s="2">
+        <v>0</v>
+      </c>
+      <c r="G40" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E40" s="1">
-        <v>0</v>
-      </c>
-      <c r="F40" s="2">
-        <v>0</v>
-      </c>
-      <c r="G40" s="6" t="s">
+      <c r="H40" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="H40" s="6" t="s">
+      <c r="I40" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="I40" s="6" t="s">
-        <v>119</v>
-      </c>
       <c r="J40" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:10">
       <c r="C41" s="1">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D41" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E41" s="1">
+        <v>0</v>
+      </c>
+      <c r="F41" s="2">
+        <v>0</v>
+      </c>
+      <c r="G41" s="6" t="s">
         <v>120</v>
-      </c>
-      <c r="E41" s="1">
-        <v>0</v>
-      </c>
-      <c r="F41" s="2">
-        <v>0</v>
-      </c>
-      <c r="G41" s="6" t="s">
-        <v>113</v>
       </c>
       <c r="H41" s="6" t="s">
         <v>121</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:10">
       <c r="C42" s="1">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E42" s="1">
         <v>0</v>
@@ -2531,24 +2540,24 @@
         <v>0</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="H42" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="I42" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="J42" s="1" t="s">
         <v>123</v>
-      </c>
-      <c r="I42" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="J42" s="1" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:10">
       <c r="C43" s="1">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E43" s="1">
         <v>0</v>
@@ -2557,24 +2566,24 @@
         <v>0</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="H43" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="I43" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="J43" s="1" t="s">
         <v>125</v>
-      </c>
-      <c r="I43" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="J43" s="1" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:10">
       <c r="C44" s="1">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E44" s="1">
         <v>0</v>
@@ -2583,102 +2592,102 @@
         <v>0</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="H44" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="I44" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="J44" s="1" t="s">
         <v>127</v>
-      </c>
-      <c r="I44" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="J44" s="1" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:10">
       <c r="C45" s="1">
+        <v>104</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E45" s="1">
+        <v>0</v>
+      </c>
+      <c r="F45" s="2">
+        <v>0</v>
+      </c>
+      <c r="G45" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="H45" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="I45" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="3:10">
+      <c r="C46" s="1">
         <v>105</v>
       </c>
-      <c r="D45" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="E45" s="1">
-        <v>0</v>
-      </c>
-      <c r="F45" s="2">
-        <v>0</v>
-      </c>
-      <c r="G45" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="H45" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="I45" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="J45" s="1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="47" customHeight="1" spans="3:10">
-      <c r="C47" s="1">
-        <v>106</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E47" s="1">
-        <v>1</v>
-      </c>
-      <c r="F47" s="2">
-        <v>0</v>
-      </c>
-      <c r="G47" s="6" t="s">
+      <c r="D46" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="H47" s="6" t="s">
+      <c r="E46" s="1">
+        <v>0</v>
+      </c>
+      <c r="F46" s="2">
+        <v>0</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="H46" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="I47" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="J47" s="1" t="s">
-        <v>134</v>
+      <c r="I46" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:10">
       <c r="C48" s="1">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D48" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E48" s="1">
+        <v>1</v>
+      </c>
+      <c r="F48" s="2">
+        <v>0</v>
+      </c>
+      <c r="G48" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="E48" s="1">
-        <v>1</v>
-      </c>
-      <c r="F48" s="2">
-        <v>0</v>
-      </c>
-      <c r="G48" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="H48" s="6" t="s">
+      <c r="I48" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="I48" s="6" t="s">
-        <v>45</v>
-      </c>
       <c r="J48" s="1" t="s">
-        <v>85</v>
+        <v>137</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="3:10">
       <c r="C49" s="1">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E49" s="1">
         <v>1</v>
@@ -2690,56 +2699,56 @@
         <v>66</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I49" s="6" t="s">
         <v>45</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="51" customHeight="1" spans="3:10">
-      <c r="C51" s="1">
-        <v>109</v>
-      </c>
-      <c r="D51" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="50" customHeight="1" spans="3:10">
+      <c r="C50" s="1">
+        <v>108</v>
+      </c>
+      <c r="D50" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="E51" s="1">
-        <v>1</v>
-      </c>
-      <c r="F51" s="2">
-        <v>0</v>
-      </c>
-      <c r="G51" s="6" t="s">
+      <c r="E50" s="1">
+        <v>1</v>
+      </c>
+      <c r="F50" s="2">
+        <v>0</v>
+      </c>
+      <c r="G50" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="H50" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="H51" s="6" t="s">
+      <c r="I50" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="J50" s="1" t="s">
         <v>142</v>
-      </c>
-      <c r="I51" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="J51" s="1" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="3:10">
       <c r="C52" s="1">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D52" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E52" s="1">
+        <v>1</v>
+      </c>
+      <c r="F52" s="2">
+        <v>0</v>
+      </c>
+      <c r="G52" s="6" t="s">
         <v>144</v>
-      </c>
-      <c r="E52" s="1">
-        <v>1</v>
-      </c>
-      <c r="F52" s="2">
-        <v>0</v>
-      </c>
-      <c r="G52" s="6" t="s">
-        <v>141</v>
       </c>
       <c r="H52" s="6" t="s">
         <v>145</v>
@@ -2753,7 +2762,7 @@
     </row>
     <row r="53" customHeight="1" spans="3:10">
       <c r="C53" s="1">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>147</v>
@@ -2765,7 +2774,7 @@
         <v>0</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H53" s="6" t="s">
         <v>148</v>
@@ -2779,7 +2788,7 @@
     </row>
     <row r="54" customHeight="1" spans="3:10">
       <c r="C54" s="1">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>150</v>
@@ -2791,7 +2800,7 @@
         <v>0</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H54" s="6" t="s">
         <v>151</v>
@@ -2805,7 +2814,7 @@
     </row>
     <row r="55" customHeight="1" spans="3:10">
       <c r="C55" s="1">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>153</v>
@@ -2817,7 +2826,7 @@
         <v>0</v>
       </c>
       <c r="G55" s="6" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H55" s="6" t="s">
         <v>154</v>
@@ -2831,7 +2840,7 @@
     </row>
     <row r="56" customHeight="1" spans="3:10">
       <c r="C56" s="1">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>156</v>
@@ -2843,76 +2852,76 @@
         <v>0</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="H56" s="6" t="s">
+      <c r="I56" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="J56" s="1" t="s">
         <v>158</v>
-      </c>
-      <c r="I56" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="J56" s="1" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:10">
       <c r="C57" s="1">
+        <v>114</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E57" s="1">
+        <v>1</v>
+      </c>
+      <c r="F57" s="2">
+        <v>0</v>
+      </c>
+      <c r="G57" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="H57" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="I57" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="J57" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="3:10">
+      <c r="C58" s="1">
         <v>115</v>
       </c>
-      <c r="D57" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="E57" s="1">
-        <v>1</v>
-      </c>
-      <c r="F57" s="2">
-        <v>0</v>
-      </c>
-      <c r="G57" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="H57" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="I57" s="6" t="s">
+      <c r="D58" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E58" s="1">
+        <v>1</v>
+      </c>
+      <c r="F58" s="2">
+        <v>0</v>
+      </c>
+      <c r="G58" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="H58" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="I58" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J57" s="1" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="59" customHeight="1" spans="3:10">
-      <c r="C59" s="1">
-        <v>121</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="E59" s="1">
-        <v>1</v>
-      </c>
-      <c r="F59" s="2">
-        <v>0</v>
-      </c>
-      <c r="G59" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="H59" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="I59" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="J59" s="2" t="s">
+      <c r="J58" s="1" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="3:10">
       <c r="C60" s="1">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E60" s="1">
         <v>1</v>
@@ -2921,24 +2930,24 @@
         <v>0</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I60" s="6" t="s">
         <v>89</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="3:10">
       <c r="C61" s="1">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E61" s="1">
         <v>1</v>
@@ -2947,24 +2956,24 @@
         <v>0</v>
       </c>
       <c r="G61" s="6" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I61" s="6" t="s">
         <v>89</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="3:10">
       <c r="C62" s="1">
-        <v>124</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>169</v>
+        <v>123</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>170</v>
       </c>
       <c r="E62" s="1">
         <v>1</v>
@@ -2973,24 +2982,24 @@
         <v>0</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I62" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="J62" s="1" t="s">
-        <v>169</v>
+      <c r="J62" s="2" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="3:10">
       <c r="C63" s="1">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E63" s="1">
         <v>1</v>
@@ -2999,42 +3008,68 @@
         <v>0</v>
       </c>
       <c r="G63" s="6" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I63" s="6" t="s">
         <v>89</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="65" customHeight="1" spans="3:10">
-      <c r="C65" s="1">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="64" customHeight="1" spans="3:10">
+      <c r="C64" s="1">
+        <v>125</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E64" s="1">
+        <v>1</v>
+      </c>
+      <c r="F64" s="2">
+        <v>0</v>
+      </c>
+      <c r="G64" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="H64" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="I64" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="J64" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="66" customHeight="1" spans="3:10">
+      <c r="C66" s="1">
         <v>127</v>
       </c>
-      <c r="D65" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="E65" s="1">
-        <v>1</v>
-      </c>
-      <c r="F65" s="2">
-        <v>0</v>
-      </c>
-      <c r="G65" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="H65" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="I65" s="6" t="s">
+      <c r="D66" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="E66" s="1">
+        <v>1</v>
+      </c>
+      <c r="F66" s="2">
+        <v>0</v>
+      </c>
+      <c r="G66" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="H66" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="I66" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J65" s="1" t="s">
-        <v>173</v>
+      <c r="J66" s="1" t="s">
+        <v>176</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="180">
   <si>
     <t>_id</t>
   </si>
@@ -356,6 +356,18 @@
     <t>180032,180033,180034</t>
   </si>
   <si>
+    <t>火符距离4件套</t>
+  </si>
+  <si>
+    <t>12,12,12,12,5,5</t>
+  </si>
+  <si>
+    <t>36,37,38,39,4005,4010</t>
+  </si>
+  <si>
+    <t>1,1,1,1,300,60</t>
+  </si>
+  <si>
     <t>盾专属自选套</t>
   </si>
   <si>
@@ -368,22 +380,16 @@
     <t>专属自选</t>
   </si>
   <si>
-    <t>4,4,4,4,4,4,4</t>
-  </si>
-  <si>
-    <t>99,100,101,102,103,104,105</t>
+    <t>4,4,4,4,4,4,4,4,4</t>
+  </si>
+  <si>
+    <t>99,100,101,102,103,104,105,96</t>
   </si>
   <si>
     <t>法力盾4件套</t>
   </si>
   <si>
-    <t>12,12,12,12,5,5</t>
-  </si>
-  <si>
     <t>26,27,28,29,4005,4010</t>
-  </si>
-  <si>
-    <t>1,1,1,1,300,60</t>
   </si>
   <si>
     <t>雷电6件套</t>
@@ -1525,7 +1531,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:J66"/>
+  <dimension ref="C3:J67"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -2424,13 +2430,13 @@
     </row>
     <row r="38" customHeight="1" spans="3:10">
       <c r="C38" s="1">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>109</v>
       </c>
       <c r="E38" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F38" s="2">
         <v>0</v>
@@ -2442,7 +2448,7 @@
         <v>111</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>37</v>
+        <v>112</v>
       </c>
       <c r="J38" s="1" t="s">
         <v>109</v>
@@ -2450,10 +2456,10 @@
     </row>
     <row r="39" customHeight="1" spans="3:10">
       <c r="C39" s="1">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E39" s="1">
         <v>1</v>
@@ -2462,47 +2468,47 @@
         <v>0</v>
       </c>
       <c r="G39" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="H39" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="I39" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="J39" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="H39" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="I39" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="J39" s="1" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:10">
       <c r="C40" s="1">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E40" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F40" s="2">
         <v>0</v>
       </c>
       <c r="G40" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="I40" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="J40" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="I40" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="J40" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:10">
       <c r="C41" s="1">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>119</v>
@@ -2514,13 +2520,13 @@
         <v>0</v>
       </c>
       <c r="G41" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="H41" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="H41" s="6" t="s">
-        <v>121</v>
-      </c>
       <c r="I41" s="6" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="J41" s="1" t="s">
         <v>119</v>
@@ -2528,33 +2534,33 @@
     </row>
     <row r="42" customHeight="1" spans="3:10">
       <c r="C42" s="1">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D42" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E42" s="1">
+        <v>0</v>
+      </c>
+      <c r="F42" s="2">
+        <v>0</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="H42" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="E42" s="1">
-        <v>0</v>
-      </c>
-      <c r="F42" s="2">
-        <v>0</v>
-      </c>
-      <c r="G42" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="H42" s="6" t="s">
+      <c r="I42" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="I42" s="6" t="s">
-        <v>118</v>
-      </c>
       <c r="J42" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:10">
       <c r="C43" s="1">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>125</v>
@@ -2566,13 +2572,13 @@
         <v>0</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="H43" s="6" t="s">
         <v>126</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="J43" s="1" t="s">
         <v>125</v>
@@ -2580,7 +2586,7 @@
     </row>
     <row r="44" customHeight="1" spans="3:10">
       <c r="C44" s="1">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>127</v>
@@ -2592,13 +2598,13 @@
         <v>0</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="H44" s="6" t="s">
         <v>128</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="J44" s="1" t="s">
         <v>127</v>
@@ -2606,7 +2612,7 @@
     </row>
     <row r="45" customHeight="1" spans="3:10">
       <c r="C45" s="1">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>129</v>
@@ -2618,13 +2624,13 @@
         <v>0</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="H45" s="6" t="s">
         <v>130</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="J45" s="1" t="s">
         <v>129</v>
@@ -2632,7 +2638,7 @@
     </row>
     <row r="46" customHeight="1" spans="3:10">
       <c r="C46" s="1">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>131</v>
@@ -2644,73 +2650,73 @@
         <v>0</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="H46" s="6" t="s">
         <v>132</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="J46" s="1" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="48" customHeight="1" spans="3:10">
-      <c r="C48" s="1">
-        <v>106</v>
-      </c>
-      <c r="D48" s="1" t="s">
+    <row r="47" customHeight="1" spans="3:10">
+      <c r="C47" s="1">
+        <v>105</v>
+      </c>
+      <c r="D47" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="E48" s="1">
-        <v>1</v>
-      </c>
-      <c r="F48" s="2">
-        <v>0</v>
-      </c>
-      <c r="G48" s="6" t="s">
+      <c r="E47" s="1">
+        <v>0</v>
+      </c>
+      <c r="F47" s="2">
+        <v>0</v>
+      </c>
+      <c r="G47" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="H47" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="H48" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="I48" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="J48" s="1" t="s">
-        <v>137</v>
+      <c r="I47" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="3:10">
       <c r="C49" s="1">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D49" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E49" s="1">
+        <v>1</v>
+      </c>
+      <c r="F49" s="2">
+        <v>0</v>
+      </c>
+      <c r="G49" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="H49" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="I49" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="1">
-        <v>1</v>
-      </c>
-      <c r="F49" s="2">
-        <v>0</v>
-      </c>
-      <c r="G49" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="H49" s="6" t="s">
+      <c r="J49" s="1" t="s">
         <v>139</v>
-      </c>
-      <c r="I49" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="J49" s="1" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="3:10">
       <c r="C50" s="1">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>140</v>
@@ -2731,220 +2737,220 @@
         <v>45</v>
       </c>
       <c r="J50" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="51" customHeight="1" spans="3:10">
+      <c r="C51" s="1">
+        <v>108</v>
+      </c>
+      <c r="D51" s="1" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="52" customHeight="1" spans="3:10">
-      <c r="C52" s="1">
-        <v>109</v>
-      </c>
-      <c r="D52" s="1" t="s">
+      <c r="E51" s="1">
+        <v>1</v>
+      </c>
+      <c r="F51" s="2">
+        <v>0</v>
+      </c>
+      <c r="G51" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="H51" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="E52" s="1">
-        <v>1</v>
-      </c>
-      <c r="F52" s="2">
-        <v>0</v>
-      </c>
-      <c r="G52" s="6" t="s">
+      <c r="I51" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="J51" s="1" t="s">
         <v>144</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="I52" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="J52" s="1" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:10">
       <c r="C53" s="1">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D53" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E53" s="1">
+        <v>1</v>
+      </c>
+      <c r="F53" s="2">
+        <v>0</v>
+      </c>
+      <c r="G53" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="H53" s="6" t="s">
         <v>147</v>
-      </c>
-      <c r="E53" s="1">
-        <v>1</v>
-      </c>
-      <c r="F53" s="2">
-        <v>0</v>
-      </c>
-      <c r="G53" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="H53" s="6" t="s">
-        <v>148</v>
       </c>
       <c r="I53" s="6" t="s">
         <v>89</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:10">
       <c r="C54" s="1">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D54" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E54" s="1">
+        <v>1</v>
+      </c>
+      <c r="F54" s="2">
+        <v>0</v>
+      </c>
+      <c r="G54" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>150</v>
-      </c>
-      <c r="E54" s="1">
-        <v>1</v>
-      </c>
-      <c r="F54" s="2">
-        <v>0</v>
-      </c>
-      <c r="G54" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>151</v>
       </c>
       <c r="I54" s="6" t="s">
         <v>89</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:10">
       <c r="C55" s="1">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D55" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E55" s="1">
+        <v>1</v>
+      </c>
+      <c r="F55" s="2">
+        <v>0</v>
+      </c>
+      <c r="G55" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="H55" s="6" t="s">
         <v>153</v>
-      </c>
-      <c r="E55" s="1">
-        <v>1</v>
-      </c>
-      <c r="F55" s="2">
-        <v>0</v>
-      </c>
-      <c r="G55" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="H55" s="6" t="s">
-        <v>154</v>
       </c>
       <c r="I55" s="6" t="s">
         <v>89</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:10">
       <c r="C56" s="1">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D56" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E56" s="1">
+        <v>1</v>
+      </c>
+      <c r="F56" s="2">
+        <v>0</v>
+      </c>
+      <c r="G56" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>156</v>
-      </c>
-      <c r="E56" s="1">
-        <v>1</v>
-      </c>
-      <c r="F56" s="2">
-        <v>0</v>
-      </c>
-      <c r="G56" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>157</v>
       </c>
       <c r="I56" s="6" t="s">
         <v>89</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:10">
       <c r="C57" s="1">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D57" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E57" s="1">
+        <v>1</v>
+      </c>
+      <c r="F57" s="2">
+        <v>0</v>
+      </c>
+      <c r="G57" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="H57" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="E57" s="1">
-        <v>1</v>
-      </c>
-      <c r="F57" s="2">
-        <v>0</v>
-      </c>
-      <c r="G57" s="6" t="s">
+      <c r="I57" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="J57" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="H57" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="I57" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="J57" s="1" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:10">
       <c r="C58" s="1">
+        <v>114</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E58" s="1">
+        <v>1</v>
+      </c>
+      <c r="F58" s="2">
+        <v>0</v>
+      </c>
+      <c r="G58" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="H58" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="I58" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="J58" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="59" customHeight="1" spans="3:10">
+      <c r="C59" s="1">
         <v>115</v>
       </c>
-      <c r="D58" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="E58" s="1">
-        <v>1</v>
-      </c>
-      <c r="F58" s="2">
-        <v>0</v>
-      </c>
-      <c r="G58" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="H58" s="6" t="s">
+      <c r="D59" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="I58" s="6" t="s">
+      <c r="E59" s="1">
+        <v>1</v>
+      </c>
+      <c r="F59" s="2">
+        <v>0</v>
+      </c>
+      <c r="G59" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="H59" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="I59" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J58" s="1" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="60" customHeight="1" spans="3:10">
-      <c r="C60" s="1">
-        <v>121</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="E60" s="1">
-        <v>1</v>
-      </c>
-      <c r="F60" s="2">
-        <v>0</v>
-      </c>
-      <c r="G60" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="I60" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="J60" s="2" t="s">
-        <v>166</v>
+      <c r="J59" s="1" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="3:10">
       <c r="C61" s="1">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>168</v>
@@ -2956,7 +2962,7 @@
         <v>0</v>
       </c>
       <c r="G61" s="6" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H61" s="6" t="s">
         <v>169</v>
@@ -2970,7 +2976,7 @@
     </row>
     <row r="62" customHeight="1" spans="3:10">
       <c r="C62" s="1">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>170</v>
@@ -2982,7 +2988,7 @@
         <v>0</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H62" s="6" t="s">
         <v>171</v>
@@ -2996,9 +3002,9 @@
     </row>
     <row r="63" customHeight="1" spans="3:10">
       <c r="C63" s="1">
-        <v>124</v>
-      </c>
-      <c r="D63" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D63" s="2" t="s">
         <v>172</v>
       </c>
       <c r="E63" s="1">
@@ -3008,7 +3014,7 @@
         <v>0</v>
       </c>
       <c r="G63" s="6" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H63" s="6" t="s">
         <v>173</v>
@@ -3016,13 +3022,13 @@
       <c r="I63" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="J63" s="1" t="s">
+      <c r="J63" s="2" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:10">
       <c r="C64" s="1">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>174</v>
@@ -3034,7 +3040,7 @@
         <v>0</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H64" s="6" t="s">
         <v>175</v>
@@ -3046,30 +3052,56 @@
         <v>174</v>
       </c>
     </row>
-    <row r="66" customHeight="1" spans="3:10">
-      <c r="C66" s="1">
+    <row r="65" customHeight="1" spans="3:10">
+      <c r="C65" s="1">
+        <v>125</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="E65" s="1">
+        <v>1</v>
+      </c>
+      <c r="F65" s="2">
+        <v>0</v>
+      </c>
+      <c r="G65" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="H65" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="I65" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="J65" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="67" customHeight="1" spans="3:10">
+      <c r="C67" s="1">
         <v>127</v>
       </c>
-      <c r="D66" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="E66" s="1">
-        <v>1</v>
-      </c>
-      <c r="F66" s="2">
-        <v>0</v>
-      </c>
-      <c r="G66" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="I66" s="6" t="s">
+      <c r="D67" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="E67" s="1">
+        <v>1</v>
+      </c>
+      <c r="F67" s="2">
+        <v>0</v>
+      </c>
+      <c r="G67" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="H67" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="I67" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J66" s="1" t="s">
-        <v>176</v>
+      <c r="J67" s="1" t="s">
+        <v>178</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="177">
   <si>
     <t>_id</t>
   </si>
@@ -65,7 +65,7 @@
     <t>int[]</t>
   </si>
   <si>
-    <t>专属自选1</t>
+    <t>狂斩专属自选</t>
   </si>
   <si>
     <t>12,12,12,12,12,12</t>
@@ -77,54 +77,36 @@
     <t>1,1,1,1,1,1</t>
   </si>
   <si>
-    <t>专属1自选包</t>
-  </si>
-  <si>
-    <t>专属自选2</t>
+    <t>破魂专属自选</t>
   </si>
   <si>
     <t>201,202,203,204,205,206</t>
   </si>
   <si>
-    <t>专属2自选包</t>
-  </si>
-  <si>
-    <t>专属自选3</t>
+    <t>血刃专属自选</t>
   </si>
   <si>
     <t>301,302,303,304,305,306</t>
   </si>
   <si>
-    <t>专属3自选包</t>
-  </si>
-  <si>
-    <t>专属自选4</t>
+    <t>屠龙专属自选</t>
   </si>
   <si>
     <t>401,402,403,404,405,406</t>
   </si>
   <si>
-    <t>专属4自选包</t>
-  </si>
-  <si>
-    <t>专属自选5</t>
+    <t>倚天专属自选</t>
   </si>
   <si>
     <t>501,502,503,504,505,506</t>
   </si>
   <si>
-    <t>专属5自选包</t>
-  </si>
-  <si>
-    <t>专属自选6</t>
+    <t>天命专属自选</t>
   </si>
   <si>
     <t>601,602,603,604,605,606</t>
   </si>
   <si>
-    <t>专属6自选包</t>
-  </si>
-  <si>
     <t>攻略自选包</t>
   </si>
   <si>
@@ -155,7 +137,7 @@
     <t>开天，流星，月灵 三选一</t>
   </si>
   <si>
-    <t>战神时装包</t>
+    <t>斩仙时装包</t>
   </si>
   <si>
     <t>13,13,13,13,13,13,13,13</t>
@@ -167,25 +149,25 @@
     <t>1,1,1,1,1,1,1,1</t>
   </si>
   <si>
-    <t>战神时装一套</t>
-  </si>
-  <si>
-    <t>恶魔时装包</t>
+    <t>斩仙时装一套</t>
+  </si>
+  <si>
+    <t>魔尊时装包</t>
   </si>
   <si>
     <t>3000009,3000010,3000011,3000012,3000013,3000014,3000015,3000016</t>
   </si>
   <si>
-    <t>恶魔时装一套</t>
-  </si>
-  <si>
-    <t>幽灵时装包</t>
+    <t>魔尊时装一套</t>
+  </si>
+  <si>
+    <t>幽冥时装包</t>
   </si>
   <si>
     <t>3000017,3000018,3000019,3000020,3000021,3000022,3000023,3000024</t>
   </si>
   <si>
-    <t>幽灵时装一套</t>
+    <t>幽冥时装一套</t>
   </si>
   <si>
     <t>专属自选包7</t>
@@ -206,24 +188,33 @@
     <t>2024春节盖楼专属自选包</t>
   </si>
   <si>
-    <t>圣战时装包</t>
+    <t>战魂时装包</t>
   </si>
   <si>
     <t>3000025,3000026,3000027,3000028,3000029,3000030,3000031,3000032</t>
   </si>
   <si>
-    <t>法神时装包</t>
+    <t>战魂时装一套</t>
+  </si>
+  <si>
+    <t>法魂时装包</t>
   </si>
   <si>
     <t>3000033,3000034,3000035,3000036,3000037,3000038,3000039,3000040</t>
   </si>
   <si>
-    <t>天尊时装包</t>
+    <t>法魂时装一套</t>
+  </si>
+  <si>
+    <t>道魂时装包</t>
   </si>
   <si>
     <t>3000041,3000042,3000043,3000044,3000045,3000046,3000047,3000048</t>
   </si>
   <si>
+    <t>道魂时装一套</t>
+  </si>
+  <si>
     <t>法宝自选</t>
   </si>
   <si>
@@ -356,7 +347,7 @@
     <t>180032,180033,180034</t>
   </si>
   <si>
-    <t>火符距离4件套</t>
+    <t>驱魔符距离4件套</t>
   </si>
   <si>
     <t>12,12,12,12,5,5</t>
@@ -392,7 +383,7 @@
     <t>26,27,28,29,4005,4010</t>
   </si>
   <si>
-    <t>雷电6件套</t>
+    <t>神雷6件套</t>
   </si>
   <si>
     <t>12,12,12,12,12,12,5,5</t>
@@ -410,7 +401,7 @@
     <t>7,8,9,10,4005,4010</t>
   </si>
   <si>
-    <t>武力盾4件套</t>
+    <t>武神盾4件套</t>
   </si>
   <si>
     <t>11,12,13,14,4005,4010</t>
@@ -428,7 +419,7 @@
     <t>18,19,20,21,4005,4010</t>
   </si>
   <si>
-    <t>月灵4件套</t>
+    <t>月神4件套</t>
   </si>
   <si>
     <t>22,23,24,25,4005,4010</t>
@@ -1199,7 +1190,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1207,9 +1198,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1"/>
   </cellXfs>
@@ -1635,17 +1623,17 @@
       <c r="F6" s="1">
         <v>0</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="H6" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="I6" s="6" t="s">
+      <c r="I6" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J6" s="5" t="s">
-        <v>16</v>
+      <c r="J6" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -1653,25 +1641,25 @@
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="1">
+        <v>1</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="1">
-        <v>1</v>
-      </c>
-      <c r="F7" s="1">
-        <v>0</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I7" s="6" t="s">
+      <c r="I7" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J7" s="5" t="s">
-        <v>19</v>
+      <c r="J7" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -1679,7 +1667,7 @@
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -1687,17 +1675,17 @@
       <c r="F8" s="1">
         <v>0</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="H8" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="I8" s="6" t="s">
+      <c r="H8" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I8" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J8" s="5" t="s">
-        <v>22</v>
+      <c r="J8" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -1705,7 +1693,7 @@
         <v>4</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
@@ -1713,17 +1701,17 @@
       <c r="F9" s="1">
         <v>0</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="G9" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="H9" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="I9" s="6" t="s">
+      <c r="H9" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I9" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J9" s="5" t="s">
-        <v>25</v>
+      <c r="J9" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -1731,7 +1719,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -1739,17 +1727,17 @@
       <c r="F10" s="1">
         <v>0</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="H10" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="I10" s="6" t="s">
+      <c r="H10" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I10" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J10" s="5" t="s">
-        <v>28</v>
+      <c r="J10" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -1757,7 +1745,7 @@
         <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -1765,17 +1753,17 @@
       <c r="F11" s="1">
         <v>0</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="G11" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="H11" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="I11" s="6" t="s">
+      <c r="H11" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J11" s="5" t="s">
-        <v>31</v>
+      <c r="J11" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -1783,7 +1771,7 @@
         <v>7</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
@@ -1791,17 +1779,17 @@
       <c r="F12" s="1">
         <v>0</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="G12" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="H12" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I12" s="6" t="s">
+      <c r="H12" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I12" s="5" t="s">
         <v>15</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:10">
@@ -1809,7 +1797,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
@@ -1817,17 +1805,17 @@
       <c r="F13" s="2">
         <v>0</v>
       </c>
-      <c r="G13" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>37</v>
+      <c r="G13" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:10">
@@ -1835,7 +1823,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
@@ -1843,17 +1831,17 @@
       <c r="F14" s="2">
         <v>0</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="G14" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J14" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:10">
@@ -1861,7 +1849,7 @@
         <v>10</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E15" s="1">
         <v>0</v>
@@ -1869,17 +1857,17 @@
       <c r="F15" s="2">
         <v>0</v>
       </c>
-      <c r="G15" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I15" s="6" t="s">
-        <v>45</v>
+      <c r="G15" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>39</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:10">
@@ -1887,7 +1875,7 @@
         <v>11</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="E16" s="1">
         <v>0</v>
@@ -1895,17 +1883,17 @@
       <c r="F16" s="2">
         <v>0</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="G16" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="J16" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="I16" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:10">
@@ -1913,7 +1901,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E17" s="1">
         <v>0</v>
@@ -1921,17 +1909,17 @@
       <c r="F17" s="2">
         <v>0</v>
       </c>
-      <c r="G17" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="I17" s="6" t="s">
+      <c r="G17" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H17" s="5" t="s">
         <v>45</v>
       </c>
+      <c r="I17" s="5" t="s">
+        <v>39</v>
+      </c>
       <c r="J17" s="1" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -1939,7 +1927,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="E18" s="1">
         <v>1</v>
@@ -1947,17 +1935,17 @@
       <c r="F18" s="1">
         <v>0</v>
       </c>
-      <c r="G18" s="6" t="s">
+      <c r="G18" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="H18" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="I18" s="6" t="s">
+      <c r="H18" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="I18" s="5" t="s">
         <v>15</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:10">
@@ -1965,7 +1953,7 @@
         <v>14</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="E19" s="1">
         <v>1</v>
@@ -1973,17 +1961,17 @@
       <c r="F19" s="2">
         <v>0</v>
       </c>
-      <c r="G19" s="6" t="s">
+      <c r="G19" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="H19" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="I19" s="6" t="s">
+      <c r="H19" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="I19" s="5" t="s">
         <v>15</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:10">
@@ -1991,7 +1979,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E20" s="1">
         <v>0</v>
@@ -1999,17 +1987,17 @@
       <c r="F20" s="2">
         <v>0</v>
       </c>
-      <c r="G20" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I20" s="6" t="s">
-        <v>45</v>
+      <c r="G20" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>39</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:10">
@@ -2017,7 +2005,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E21" s="1">
         <v>0</v>
@@ -2025,17 +2013,17 @@
       <c r="F21" s="2">
         <v>0</v>
       </c>
-      <c r="G21" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="H21" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="I21" s="6" t="s">
-        <v>45</v>
+      <c r="G21" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>39</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:10">
@@ -2043,7 +2031,7 @@
         <v>17</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E22" s="1">
         <v>0</v>
@@ -2051,17 +2039,17 @@
       <c r="F22" s="2">
         <v>0</v>
       </c>
-      <c r="G22" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>45</v>
+      <c r="G22" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>39</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:10">
@@ -2069,25 +2057,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E23" s="1">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2">
+        <v>0</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="J23" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="E23" s="1">
-        <v>1</v>
-      </c>
-      <c r="F23" s="2">
-        <v>0</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="H23" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="I23" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="3:10">
@@ -2095,7 +2083,7 @@
         <v>19</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
@@ -2103,17 +2091,17 @@
       <c r="F24" s="2">
         <v>0</v>
       </c>
-      <c r="G24" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>45</v>
+      <c r="G24" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>39</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:10">
@@ -2121,7 +2109,7 @@
         <v>20</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E25" s="1">
         <v>1</v>
@@ -2129,17 +2117,17 @@
       <c r="F25" s="2">
         <v>0</v>
       </c>
-      <c r="G25" s="6" t="s">
+      <c r="G25" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="H25" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="H25" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="I25" s="6" t="s">
-        <v>45</v>
+      <c r="I25" s="5" t="s">
+        <v>39</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -2147,25 +2135,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E26" s="1">
+        <v>1</v>
+      </c>
+      <c r="F26" s="1">
+        <v>0</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J26" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="E26" s="1">
-        <v>1</v>
-      </c>
-      <c r="F26" s="1">
-        <v>0</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="I26" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -2173,7 +2161,7 @@
         <v>22</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E27" s="1">
         <v>1</v>
@@ -2181,17 +2169,17 @@
       <c r="F27" s="1">
         <v>0</v>
       </c>
-      <c r="G27" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="H27" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="I27" s="6" t="s">
-        <v>45</v>
+      <c r="G27" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>39</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:10">
@@ -2199,25 +2187,25 @@
         <v>23</v>
       </c>
       <c r="D28" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E28" s="1">
+        <v>1</v>
+      </c>
+      <c r="F28" s="1">
+        <v>0</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I28" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="E28" s="1">
-        <v>1</v>
-      </c>
-      <c r="F28" s="1">
-        <v>0</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="I28" s="6" t="s">
-        <v>84</v>
-      </c>
       <c r="J28" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:10">
@@ -2225,7 +2213,7 @@
         <v>24</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
@@ -2233,17 +2221,17 @@
       <c r="F29" s="2">
         <v>0</v>
       </c>
-      <c r="G29" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="H29" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="I29" s="6" t="s">
-        <v>45</v>
+      <c r="G29" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>39</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:10">
@@ -2251,7 +2239,7 @@
         <v>25</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
@@ -2259,17 +2247,17 @@
       <c r="F30" s="2">
         <v>0</v>
       </c>
-      <c r="G30" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="I30" s="6" t="s">
-        <v>89</v>
+      <c r="G30" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:10">
@@ -2277,7 +2265,7 @@
         <v>26</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
@@ -2285,17 +2273,17 @@
       <c r="F31" s="2">
         <v>0</v>
       </c>
-      <c r="G31" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="H31" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="I31" s="6" t="s">
-        <v>84</v>
+      <c r="G31" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>81</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:10">
@@ -2303,7 +2291,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E32" s="1">
         <v>1</v>
@@ -2311,17 +2299,17 @@
       <c r="F32" s="2">
         <v>0</v>
       </c>
-      <c r="G32" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="I32" s="6" t="s">
-        <v>37</v>
+      <c r="G32" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="I32" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:10">
@@ -2329,7 +2317,7 @@
         <v>28</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E33" s="1">
         <v>1</v>
@@ -2337,17 +2325,17 @@
       <c r="F33" s="2">
         <v>0</v>
       </c>
-      <c r="G33" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="H33" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="I33" s="6" t="s">
-        <v>45</v>
+      <c r="G33" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>39</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:10">
@@ -2355,7 +2343,7 @@
         <v>29</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E34" s="1">
         <v>1</v>
@@ -2363,17 +2351,17 @@
       <c r="F34" s="2">
         <v>0</v>
       </c>
-      <c r="G34" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="I34" s="6" t="s">
-        <v>37</v>
+      <c r="G34" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H34" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:10">
@@ -2381,25 +2369,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E35" s="1">
+        <v>1</v>
+      </c>
+      <c r="F35" s="2">
+        <v>0</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="H35" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="I35" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="E35" s="1">
-        <v>1</v>
-      </c>
-      <c r="F35" s="2">
-        <v>0</v>
-      </c>
-      <c r="G35" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="H35" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="I35" s="6" t="s">
-        <v>105</v>
-      </c>
       <c r="J35" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:10">
@@ -2407,7 +2395,7 @@
         <v>31</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E36" s="1">
         <v>1</v>
@@ -2415,17 +2403,17 @@
       <c r="F36" s="2">
         <v>0</v>
       </c>
-      <c r="G36" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="I36" s="6" t="s">
-        <v>37</v>
+      <c r="G36" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="H36" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="I36" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:10">
@@ -2433,25 +2421,25 @@
         <v>96</v>
       </c>
       <c r="D38" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E38" s="1">
+        <v>0</v>
+      </c>
+      <c r="F38" s="2">
+        <v>0</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="H38" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="I38" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="E38" s="1">
-        <v>0</v>
-      </c>
-      <c r="F38" s="2">
-        <v>0</v>
-      </c>
-      <c r="G38" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="I38" s="6" t="s">
-        <v>112</v>
-      </c>
       <c r="J38" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:10">
@@ -2459,7 +2447,7 @@
         <v>97</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E39" s="1">
         <v>1</v>
@@ -2467,17 +2455,17 @@
       <c r="F39" s="2">
         <v>0</v>
       </c>
-      <c r="G39" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="H39" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="I39" s="6" t="s">
-        <v>37</v>
+      <c r="G39" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="H39" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="I39" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:10">
@@ -2485,7 +2473,7 @@
         <v>98</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E40" s="1">
         <v>1</v>
@@ -2493,17 +2481,17 @@
       <c r="F40" s="2">
         <v>0</v>
       </c>
-      <c r="G40" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="I40" s="6" t="s">
-        <v>84</v>
+      <c r="G40" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="H40" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="I40" s="5" t="s">
+        <v>81</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:10">
@@ -2511,7 +2499,7 @@
         <v>99</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E41" s="1">
         <v>0</v>
@@ -2519,17 +2507,17 @@
       <c r="F41" s="2">
         <v>0</v>
       </c>
-      <c r="G41" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="H41" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="I41" s="6" t="s">
-        <v>112</v>
+      <c r="G41" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="H41" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="I41" s="5" t="s">
+        <v>109</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:10">
@@ -2537,25 +2525,25 @@
         <v>100</v>
       </c>
       <c r="D42" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E42" s="1">
+        <v>0</v>
+      </c>
+      <c r="F42" s="2">
+        <v>0</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="H42" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="I42" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="E42" s="1">
-        <v>0</v>
-      </c>
-      <c r="F42" s="2">
-        <v>0</v>
-      </c>
-      <c r="G42" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="I42" s="6" t="s">
-        <v>124</v>
-      </c>
       <c r="J42" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:10">
@@ -2563,7 +2551,7 @@
         <v>101</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E43" s="1">
         <v>0</v>
@@ -2571,17 +2559,17 @@
       <c r="F43" s="2">
         <v>0</v>
       </c>
-      <c r="G43" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="H43" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="I43" s="6" t="s">
-        <v>112</v>
+      <c r="G43" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="H43" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="I43" s="5" t="s">
+        <v>109</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:10">
@@ -2589,7 +2577,7 @@
         <v>102</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E44" s="1">
         <v>0</v>
@@ -2597,17 +2585,17 @@
       <c r="F44" s="2">
         <v>0</v>
       </c>
-      <c r="G44" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="I44" s="6" t="s">
-        <v>112</v>
+      <c r="G44" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="H44" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="I44" s="5" t="s">
+        <v>109</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:10">
@@ -2615,7 +2603,7 @@
         <v>103</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E45" s="1">
         <v>0</v>
@@ -2623,17 +2611,17 @@
       <c r="F45" s="2">
         <v>0</v>
       </c>
-      <c r="G45" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="H45" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="I45" s="6" t="s">
-        <v>112</v>
+      <c r="G45" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="H45" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="I45" s="5" t="s">
+        <v>109</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="3:10">
@@ -2641,7 +2629,7 @@
         <v>104</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E46" s="1">
         <v>0</v>
@@ -2649,17 +2637,17 @@
       <c r="F46" s="2">
         <v>0</v>
       </c>
-      <c r="G46" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="I46" s="6" t="s">
-        <v>112</v>
+      <c r="G46" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="H46" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="I46" s="5" t="s">
+        <v>109</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:10">
@@ -2667,7 +2655,7 @@
         <v>105</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E47" s="1">
         <v>0</v>
@@ -2675,17 +2663,17 @@
       <c r="F47" s="2">
         <v>0</v>
       </c>
-      <c r="G47" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="H47" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="I47" s="6" t="s">
-        <v>112</v>
+      <c r="G47" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="H47" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="I47" s="5" t="s">
+        <v>109</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="3:10">
@@ -2693,25 +2681,25 @@
         <v>106</v>
       </c>
       <c r="D49" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E49" s="1">
+        <v>1</v>
+      </c>
+      <c r="F49" s="2">
+        <v>0</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="H49" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="I49" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="E49" s="1">
-        <v>1</v>
-      </c>
-      <c r="F49" s="2">
-        <v>0</v>
-      </c>
-      <c r="G49" s="6" t="s">
+      <c r="J49" s="1" t="s">
         <v>136</v>
-      </c>
-      <c r="H49" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="I49" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="J49" s="1" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="3:10">
@@ -2719,7 +2707,7 @@
         <v>107</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E50" s="1">
         <v>1</v>
@@ -2727,17 +2715,17 @@
       <c r="F50" s="2">
         <v>0</v>
       </c>
-      <c r="G50" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="I50" s="6" t="s">
-        <v>45</v>
+      <c r="G50" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H50" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="I50" s="5" t="s">
+        <v>39</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="3:10">
@@ -2745,7 +2733,7 @@
         <v>108</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E51" s="1">
         <v>1</v>
@@ -2753,17 +2741,17 @@
       <c r="F51" s="2">
         <v>0</v>
       </c>
-      <c r="G51" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="H51" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="I51" s="6" t="s">
-        <v>45</v>
+      <c r="G51" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H51" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="I51" s="5" t="s">
+        <v>39</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:10">
@@ -2771,25 +2759,25 @@
         <v>109</v>
       </c>
       <c r="D53" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E53" s="1">
+        <v>1</v>
+      </c>
+      <c r="F53" s="2">
+        <v>0</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H53" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="I53" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="J53" s="1" t="s">
         <v>145</v>
-      </c>
-      <c r="E53" s="1">
-        <v>1</v>
-      </c>
-      <c r="F53" s="2">
-        <v>0</v>
-      </c>
-      <c r="G53" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="H53" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="I53" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="J53" s="1" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:10">
@@ -2797,7 +2785,7 @@
         <v>110</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E54" s="1">
         <v>1</v>
@@ -2805,17 +2793,17 @@
       <c r="F54" s="2">
         <v>0</v>
       </c>
-      <c r="G54" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="I54" s="6" t="s">
-        <v>89</v>
+      <c r="G54" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H54" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="I54" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:10">
@@ -2823,7 +2811,7 @@
         <v>111</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E55" s="1">
         <v>1</v>
@@ -2831,17 +2819,17 @@
       <c r="F55" s="2">
         <v>0</v>
       </c>
-      <c r="G55" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="H55" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="I55" s="6" t="s">
-        <v>89</v>
+      <c r="G55" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H55" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="I55" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:10">
@@ -2849,7 +2837,7 @@
         <v>112</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E56" s="1">
         <v>1</v>
@@ -2857,17 +2845,17 @@
       <c r="F56" s="2">
         <v>0</v>
       </c>
-      <c r="G56" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="I56" s="6" t="s">
-        <v>89</v>
+      <c r="G56" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H56" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="I56" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:10">
@@ -2875,7 +2863,7 @@
         <v>113</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E57" s="1">
         <v>1</v>
@@ -2883,17 +2871,17 @@
       <c r="F57" s="2">
         <v>0</v>
       </c>
-      <c r="G57" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="H57" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="I57" s="6" t="s">
-        <v>89</v>
+      <c r="G57" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H57" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="I57" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:10">
@@ -2901,25 +2889,25 @@
         <v>114</v>
       </c>
       <c r="D58" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E58" s="1">
+        <v>1</v>
+      </c>
+      <c r="F58" s="2">
+        <v>0</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="H58" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="I58" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="J58" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="E58" s="1">
-        <v>1</v>
-      </c>
-      <c r="F58" s="2">
-        <v>0</v>
-      </c>
-      <c r="G58" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="I58" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="J58" s="1" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:10">
@@ -2927,7 +2915,7 @@
         <v>115</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E59" s="1">
         <v>1</v>
@@ -2935,17 +2923,17 @@
       <c r="F59" s="2">
         <v>0</v>
       </c>
-      <c r="G59" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="H59" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="I59" s="6" t="s">
-        <v>45</v>
+      <c r="G59" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="H59" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="I59" s="5" t="s">
+        <v>39</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="3:10">
@@ -2953,7 +2941,7 @@
         <v>121</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E61" s="1">
         <v>1</v>
@@ -2961,17 +2949,17 @@
       <c r="F61" s="2">
         <v>0</v>
       </c>
-      <c r="G61" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="H61" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="I61" s="6" t="s">
-        <v>89</v>
+      <c r="G61" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H61" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="I61" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="3:10">
@@ -2979,7 +2967,7 @@
         <v>122</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="E62" s="1">
         <v>1</v>
@@ -2987,17 +2975,17 @@
       <c r="F62" s="2">
         <v>0</v>
       </c>
-      <c r="G62" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="I62" s="6" t="s">
-        <v>89</v>
+      <c r="G62" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H62" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="I62" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="3:10">
@@ -3005,7 +2993,7 @@
         <v>123</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E63" s="1">
         <v>1</v>
@@ -3013,17 +3001,17 @@
       <c r="F63" s="2">
         <v>0</v>
       </c>
-      <c r="G63" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="H63" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="I63" s="6" t="s">
-        <v>89</v>
+      <c r="G63" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H63" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="I63" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:10">
@@ -3031,7 +3019,7 @@
         <v>124</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E64" s="1">
         <v>1</v>
@@ -3039,17 +3027,17 @@
       <c r="F64" s="2">
         <v>0</v>
       </c>
-      <c r="G64" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="I64" s="6" t="s">
-        <v>89</v>
+      <c r="G64" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H64" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="I64" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="J64" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:10">
@@ -3057,7 +3045,7 @@
         <v>125</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E65" s="1">
         <v>1</v>
@@ -3065,17 +3053,17 @@
       <c r="F65" s="2">
         <v>0</v>
       </c>
-      <c r="G65" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="H65" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="I65" s="6" t="s">
-        <v>89</v>
+      <c r="G65" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H65" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="I65" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="J65" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:10">
@@ -3083,7 +3071,7 @@
         <v>127</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="E67" s="1">
         <v>1</v>
@@ -3091,17 +3079,17 @@
       <c r="F67" s="2">
         <v>0</v>
       </c>
-      <c r="G67" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="H67" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="I67" s="6" t="s">
-        <v>45</v>
+      <c r="G67" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="H67" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="I67" s="5" t="s">
+        <v>39</v>
       </c>
       <c r="J67" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="180">
   <si>
     <t>_id</t>
   </si>
@@ -558,6 +558,15 @@
   </si>
   <si>
     <t>121,122,123,124,125</t>
+  </si>
+  <si>
+    <t>橙宠自选</t>
+  </si>
+  <si>
+    <t>21,21,21</t>
+  </si>
+  <si>
+    <t>1,2,3</t>
   </si>
 </sst>
 </file>
@@ -1519,7 +1528,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:J67"/>
+  <dimension ref="C3:J69"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -3092,6 +3101,32 @@
         <v>175</v>
       </c>
     </row>
+    <row r="69" customHeight="1" spans="3:10">
+      <c r="C69" s="1">
+        <v>201</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E69" s="1">
+        <v>1</v>
+      </c>
+      <c r="F69" s="2">
+        <v>0</v>
+      </c>
+      <c r="G69" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="H69" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="I69" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J69" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="2">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="F3:F5" errorStyle="warning">

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="205">
   <si>
     <t>_id</t>
   </si>
@@ -560,13 +560,88 @@
     <t>121,122,123,124,125</t>
   </si>
   <si>
-    <t>橙宠自选</t>
+    <t>40橙宠自选</t>
   </si>
   <si>
     <t>21,21,21</t>
   </si>
   <si>
     <t>1,2,3</t>
+  </si>
+  <si>
+    <t>40资质橙宠自选</t>
+  </si>
+  <si>
+    <t>45橙宠自选</t>
+  </si>
+  <si>
+    <t>4,5,6</t>
+  </si>
+  <si>
+    <t>45资质橙宠自选</t>
+  </si>
+  <si>
+    <t>50橙宠自选</t>
+  </si>
+  <si>
+    <t>7,8,9</t>
+  </si>
+  <si>
+    <t>50资质橙宠自选</t>
+  </si>
+  <si>
+    <t>40红宠自选</t>
+  </si>
+  <si>
+    <t>10,11,12</t>
+  </si>
+  <si>
+    <t>40资质红宠自选</t>
+  </si>
+  <si>
+    <t>45红宠自选</t>
+  </si>
+  <si>
+    <t>13,14,15</t>
+  </si>
+  <si>
+    <t>45资质红宠自选</t>
+  </si>
+  <si>
+    <t>50红宠自选</t>
+  </si>
+  <si>
+    <t>16,17,18</t>
+  </si>
+  <si>
+    <t>50资质红宠自选</t>
+  </si>
+  <si>
+    <t>40金宠自选</t>
+  </si>
+  <si>
+    <t>18,20,21</t>
+  </si>
+  <si>
+    <t>40资质金宠自选</t>
+  </si>
+  <si>
+    <t>45金宠自选</t>
+  </si>
+  <si>
+    <t>22,23,24</t>
+  </si>
+  <si>
+    <t>45资质金宠自选</t>
+  </si>
+  <si>
+    <t>50金宠自选</t>
+  </si>
+  <si>
+    <t>25,26,27</t>
+  </si>
+  <si>
+    <t>50资质金宠自选</t>
   </si>
 </sst>
 </file>
@@ -1528,7 +1603,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:J69"/>
+  <dimension ref="C3:J77"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -3124,7 +3199,215 @@
         <v>31</v>
       </c>
       <c r="J69" s="1" t="s">
-        <v>177</v>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="70" customHeight="1" spans="3:10">
+      <c r="C70" s="1">
+        <v>202</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E70" s="1">
+        <v>1</v>
+      </c>
+      <c r="F70" s="2">
+        <v>0</v>
+      </c>
+      <c r="G70" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="H70" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="I70" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J70" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="71" customHeight="1" spans="3:10">
+      <c r="C71" s="1">
+        <v>203</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="E71" s="1">
+        <v>1</v>
+      </c>
+      <c r="F71" s="2">
+        <v>0</v>
+      </c>
+      <c r="G71" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="H71" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="I71" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J71" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="72" customHeight="1" spans="3:10">
+      <c r="C72" s="1">
+        <v>204</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E72" s="1">
+        <v>1</v>
+      </c>
+      <c r="F72" s="2">
+        <v>0</v>
+      </c>
+      <c r="G72" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="H72" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="I72" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J72" s="1" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="73" customHeight="1" spans="3:10">
+      <c r="C73" s="1">
+        <v>205</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E73" s="1">
+        <v>1</v>
+      </c>
+      <c r="F73" s="2">
+        <v>0</v>
+      </c>
+      <c r="G73" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="H73" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="I73" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J73" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="74" customHeight="1" spans="3:10">
+      <c r="C74" s="1">
+        <v>206</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="E74" s="1">
+        <v>1</v>
+      </c>
+      <c r="F74" s="2">
+        <v>0</v>
+      </c>
+      <c r="G74" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="H74" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="I74" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J74" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="75" customHeight="1" spans="3:10">
+      <c r="C75" s="1">
+        <v>207</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="E75" s="1">
+        <v>1</v>
+      </c>
+      <c r="F75" s="2">
+        <v>0</v>
+      </c>
+      <c r="G75" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="H75" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="I75" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J75" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="76" customHeight="1" spans="3:10">
+      <c r="C76" s="1">
+        <v>208</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="E76" s="1">
+        <v>1</v>
+      </c>
+      <c r="F76" s="2">
+        <v>0</v>
+      </c>
+      <c r="G76" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="H76" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I76" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J76" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="77" customHeight="1" spans="3:10">
+      <c r="C77" s="1">
+        <v>209</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="E77" s="1">
+        <v>1</v>
+      </c>
+      <c r="F77" s="2">
+        <v>0</v>
+      </c>
+      <c r="G77" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="H77" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="I77" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J77" s="1" t="s">
+        <v>204</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -620,7 +620,7 @@
     <t>40金宠自选</t>
   </si>
   <si>
-    <t>18,20,21</t>
+    <t>19,20,21</t>
   </si>
   <si>
     <t>40资质金宠自选</t>

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="214">
   <si>
     <t>_id</t>
   </si>
@@ -345,6 +345,33 @@
   </si>
   <si>
     <t>180032,180033,180034</t>
+  </si>
+  <si>
+    <t>普通金宠包</t>
+  </si>
+  <si>
+    <t>4,5</t>
+  </si>
+  <si>
+    <t>207,4022</t>
+  </si>
+  <si>
+    <t>2,10000</t>
+  </si>
+  <si>
+    <t>2个40资质金宠+1w口粮</t>
+  </si>
+  <si>
+    <t>满资质金宠包</t>
+  </si>
+  <si>
+    <t>209,4022</t>
+  </si>
+  <si>
+    <t>2,50000</t>
+  </si>
+  <si>
+    <t>2个50资质金宠+5w口粮</t>
   </si>
   <si>
     <t>驱魔符距离4件套</t>
@@ -1603,7 +1630,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:J77"/>
+  <dimension ref="C3:J79"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -2500,12 +2527,38 @@
         <v>103</v>
       </c>
     </row>
+    <row r="37" customHeight="1" spans="3:10">
+      <c r="C37" s="1">
+        <v>32</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E37" s="1">
+        <v>0</v>
+      </c>
+      <c r="F37" s="2">
+        <v>0</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="H37" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="I37" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
     <row r="38" customHeight="1" spans="3:10">
       <c r="C38" s="1">
-        <v>96</v>
+        <v>33</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E38" s="1">
         <v>0</v>
@@ -2517,125 +2570,99 @@
         <v>107</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="39" customHeight="1" spans="3:10">
-      <c r="C39" s="1">
-        <v>97</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="E39" s="1">
-        <v>1</v>
-      </c>
-      <c r="F39" s="2">
-        <v>0</v>
-      </c>
-      <c r="G39" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="H39" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="I39" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="J39" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:10">
       <c r="C40" s="1">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E40" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F40" s="2">
         <v>0</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H40" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="I40" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="J40" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="I40" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="J40" s="1" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:10">
       <c r="C41" s="1">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E41" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F41" s="2">
         <v>0</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="I41" s="5" t="s">
-        <v>109</v>
+        <v>31</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:10">
       <c r="C42" s="1">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E42" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42" s="2">
         <v>0</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="I42" s="5" t="s">
-        <v>121</v>
+        <v>81</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:10">
       <c r="C43" s="1">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E43" s="1">
         <v>0</v>
@@ -2644,24 +2671,24 @@
         <v>0</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="I43" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:10">
       <c r="C44" s="1">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E44" s="1">
         <v>0</v>
@@ -2670,24 +2697,24 @@
         <v>0</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="I44" s="5" t="s">
-        <v>109</v>
+        <v>130</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:10">
       <c r="C45" s="1">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="E45" s="1">
         <v>0</v>
@@ -2696,24 +2723,24 @@
         <v>0</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="I45" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="3:10">
       <c r="C46" s="1">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E46" s="1">
         <v>0</v>
@@ -2722,24 +2749,24 @@
         <v>0</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="I46" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:10">
       <c r="C47" s="1">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E47" s="1">
         <v>0</v>
@@ -2748,76 +2775,76 @@
         <v>0</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="I47" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>130</v>
+        <v>135</v>
+      </c>
+    </row>
+    <row r="48" customHeight="1" spans="3:10">
+      <c r="C48" s="1">
+        <v>104</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E48" s="1">
+        <v>0</v>
+      </c>
+      <c r="F48" s="2">
+        <v>0</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="H48" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="I48" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="3:10">
       <c r="C49" s="1">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="E49" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F49" s="2">
         <v>0</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="I49" s="5" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="50" customHeight="1" spans="3:10">
-      <c r="C50" s="1">
-        <v>107</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="E50" s="1">
-        <v>1</v>
-      </c>
-      <c r="F50" s="2">
-        <v>0</v>
-      </c>
-      <c r="G50" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="H50" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="I50" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="J50" s="1" t="s">
-        <v>82</v>
+        <v>139</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="3:10">
       <c r="C51" s="1">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E51" s="1">
         <v>1</v>
@@ -2826,24 +2853,50 @@
         <v>0</v>
       </c>
       <c r="G51" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="H51" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="I51" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="52" customHeight="1" spans="3:10">
+      <c r="C52" s="1">
+        <v>107</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E52" s="1">
+        <v>1</v>
+      </c>
+      <c r="F52" s="2">
+        <v>0</v>
+      </c>
+      <c r="G52" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="H51" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="I51" s="5" t="s">
+      <c r="H52" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="I52" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="J51" s="1" t="s">
-        <v>141</v>
+      <c r="J52" s="1" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:10">
       <c r="C53" s="1">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="E53" s="1">
         <v>1</v>
@@ -2852,50 +2905,24 @@
         <v>0</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>143</v>
+        <v>63</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I53" s="5" t="s">
-        <v>86</v>
+        <v>39</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="54" customHeight="1" spans="3:10">
-      <c r="C54" s="1">
-        <v>110</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="E54" s="1">
-        <v>1</v>
-      </c>
-      <c r="F54" s="2">
-        <v>0</v>
-      </c>
-      <c r="G54" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="H54" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="I54" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="J54" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:10">
       <c r="C55" s="1">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E55" s="1">
         <v>1</v>
@@ -2904,50 +2931,50 @@
         <v>0</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="I55" s="5" t="s">
         <v>86</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:10">
       <c r="C56" s="1">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D56" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E56" s="1">
+        <v>1</v>
+      </c>
+      <c r="F56" s="2">
+        <v>0</v>
+      </c>
+      <c r="G56" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="E56" s="1">
-        <v>1</v>
-      </c>
-      <c r="F56" s="2">
-        <v>0</v>
-      </c>
-      <c r="G56" s="5" t="s">
-        <v>143</v>
-      </c>
       <c r="H56" s="5" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="I56" s="5" t="s">
         <v>86</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:10">
       <c r="C57" s="1">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="E57" s="1">
         <v>1</v>
@@ -2956,24 +2983,24 @@
         <v>0</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="I57" s="5" t="s">
         <v>86</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:10">
       <c r="C58" s="1">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="E58" s="1">
         <v>1</v>
@@ -2982,24 +3009,24 @@
         <v>0</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="I58" s="5" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:10">
       <c r="C59" s="1">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E59" s="1">
         <v>1</v>
@@ -3008,24 +3035,50 @@
         <v>0</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I59" s="5" t="s">
-        <v>39</v>
+        <v>86</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>162</v>
+        <v>166</v>
+      </c>
+    </row>
+    <row r="60" customHeight="1" spans="3:10">
+      <c r="C60" s="1">
+        <v>114</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E60" s="1">
+        <v>1</v>
+      </c>
+      <c r="F60" s="2">
+        <v>0</v>
+      </c>
+      <c r="G60" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="H60" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="I60" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="J60" s="1" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="3:10">
       <c r="C61" s="1">
-        <v>121</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>165</v>
+        <v>115</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>171</v>
       </c>
       <c r="E61" s="1">
         <v>1</v>
@@ -3034,50 +3087,24 @@
         <v>0</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>143</v>
+        <v>172</v>
       </c>
       <c r="H61" s="5" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="I61" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="J61" s="2" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="62" customHeight="1" spans="3:10">
-      <c r="C62" s="1">
-        <v>122</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E62" s="1">
-        <v>1</v>
-      </c>
-      <c r="F62" s="2">
-        <v>0</v>
-      </c>
-      <c r="G62" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="H62" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="I62" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="J62" s="2" t="s">
-        <v>167</v>
+        <v>39</v>
+      </c>
+      <c r="J61" s="1" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="3:10">
       <c r="C63" s="1">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="E63" s="1">
         <v>1</v>
@@ -3086,24 +3113,24 @@
         <v>0</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="H63" s="5" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="I63" s="5" t="s">
         <v>86</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:10">
       <c r="C64" s="1">
-        <v>124</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>171</v>
+        <v>122</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>176</v>
       </c>
       <c r="E64" s="1">
         <v>1</v>
@@ -3112,24 +3139,24 @@
         <v>0</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="H64" s="5" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="I64" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="J64" s="1" t="s">
-        <v>171</v>
+      <c r="J64" s="2" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:10">
       <c r="C65" s="1">
-        <v>125</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>173</v>
+        <v>123</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>178</v>
       </c>
       <c r="E65" s="1">
         <v>1</v>
@@ -3138,24 +3165,50 @@
         <v>0</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="H65" s="5" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="I65" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="J65" s="1" t="s">
-        <v>173</v>
+      <c r="J65" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="66" customHeight="1" spans="3:10">
+      <c r="C66" s="1">
+        <v>124</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E66" s="1">
+        <v>1</v>
+      </c>
+      <c r="F66" s="2">
+        <v>0</v>
+      </c>
+      <c r="G66" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="H66" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="I66" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="J66" s="1" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:10">
       <c r="C67" s="1">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="E67" s="1">
         <v>1</v>
@@ -3164,24 +3217,24 @@
         <v>0</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="H67" s="5" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="I67" s="5" t="s">
-        <v>39</v>
+        <v>86</v>
       </c>
       <c r="J67" s="1" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:10">
       <c r="C69" s="1">
-        <v>201</v>
+        <v>127</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="E69" s="1">
         <v>1</v>
@@ -3190,50 +3243,24 @@
         <v>0</v>
       </c>
       <c r="G69" s="5" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="H69" s="5" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="I69" s="5" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="J69" s="1" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="70" customHeight="1" spans="3:10">
-      <c r="C70" s="1">
-        <v>202</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="E70" s="1">
-        <v>1</v>
-      </c>
-      <c r="F70" s="2">
-        <v>0</v>
-      </c>
-      <c r="G70" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="H70" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="I70" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="J70" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:10">
       <c r="C71" s="1">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E71" s="1">
         <v>1</v>
@@ -3242,50 +3269,50 @@
         <v>0</v>
       </c>
       <c r="G71" s="5" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="H71" s="5" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="I71" s="5" t="s">
         <v>31</v>
       </c>
       <c r="J71" s="1" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:10">
       <c r="C72" s="1">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D72" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E72" s="1">
+        <v>1</v>
+      </c>
+      <c r="F72" s="2">
+        <v>0</v>
+      </c>
+      <c r="G72" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="E72" s="1">
-        <v>1</v>
-      </c>
-      <c r="F72" s="2">
-        <v>0</v>
-      </c>
-      <c r="G72" s="5" t="s">
-        <v>178</v>
-      </c>
       <c r="H72" s="5" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="I72" s="5" t="s">
         <v>31</v>
       </c>
       <c r="J72" s="1" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:10">
       <c r="C73" s="1">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E73" s="1">
         <v>1</v>
@@ -3294,24 +3321,24 @@
         <v>0</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="H73" s="5" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="I73" s="5" t="s">
         <v>31</v>
       </c>
       <c r="J73" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:10">
       <c r="C74" s="1">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E74" s="1">
         <v>1</v>
@@ -3320,24 +3347,24 @@
         <v>0</v>
       </c>
       <c r="G74" s="5" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="H74" s="5" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="I74" s="5" t="s">
         <v>31</v>
       </c>
       <c r="J74" s="1" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:10">
       <c r="C75" s="1">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="E75" s="1">
         <v>1</v>
@@ -3346,24 +3373,24 @@
         <v>0</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="H75" s="5" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="I75" s="5" t="s">
         <v>31</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:10">
       <c r="C76" s="1">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="E76" s="1">
         <v>1</v>
@@ -3372,24 +3399,24 @@
         <v>0</v>
       </c>
       <c r="G76" s="5" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="H76" s="5" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="I76" s="5" t="s">
         <v>31</v>
       </c>
       <c r="J76" s="1" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:10">
       <c r="C77" s="1">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E77" s="1">
         <v>1</v>
@@ -3398,16 +3425,68 @@
         <v>0</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="H77" s="5" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="I77" s="5" t="s">
         <v>31</v>
       </c>
       <c r="J77" s="1" t="s">
-        <v>204</v>
+        <v>207</v>
+      </c>
+    </row>
+    <row r="78" customHeight="1" spans="3:10">
+      <c r="C78" s="1">
+        <v>208</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="E78" s="1">
+        <v>1</v>
+      </c>
+      <c r="F78" s="2">
+        <v>0</v>
+      </c>
+      <c r="G78" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="H78" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="I78" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J78" s="1" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="79" customHeight="1" spans="3:10">
+      <c r="C79" s="1">
+        <v>209</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E79" s="1">
+        <v>1</v>
+      </c>
+      <c r="F79" s="2">
+        <v>0</v>
+      </c>
+      <c r="G79" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="H79" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="I79" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J79" s="1" t="s">
+        <v>213</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="215">
   <si>
     <t>_id</t>
   </si>
@@ -647,7 +647,10 @@
     <t>40金宠自选</t>
   </si>
   <si>
-    <t>19,20,21</t>
+    <t>21,21,21,21,21,21</t>
+  </si>
+  <si>
+    <t>19,20,21,28,29,30</t>
   </si>
   <si>
     <t>40资质金宠自选</t>
@@ -656,7 +659,7 @@
     <t>45金宠自选</t>
   </si>
   <si>
-    <t>22,23,24</t>
+    <t>22,23,24,31,32,33</t>
   </si>
   <si>
     <t>45资质金宠自选</t>
@@ -665,7 +668,7 @@
     <t>50金宠自选</t>
   </si>
   <si>
-    <t>25,26,27</t>
+    <t>25,26,27,34,35,36</t>
   </si>
   <si>
     <t>50资质金宠自选</t>
@@ -3425,16 +3428,16 @@
         <v>0</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>187</v>
+        <v>206</v>
       </c>
       <c r="H77" s="5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I77" s="5" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="J77" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="3:10">
@@ -3442,7 +3445,7 @@
         <v>208</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E78" s="1">
         <v>1</v>
@@ -3451,16 +3454,16 @@
         <v>0</v>
       </c>
       <c r="G78" s="5" t="s">
-        <v>187</v>
+        <v>206</v>
       </c>
       <c r="H78" s="5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I78" s="5" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="J78" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="3:10">
@@ -3468,7 +3471,7 @@
         <v>209</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E79" s="1">
         <v>1</v>
@@ -3477,16 +3480,16 @@
         <v>0</v>
       </c>
       <c r="G79" s="5" t="s">
-        <v>187</v>
+        <v>206</v>
       </c>
       <c r="H79" s="5" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I79" s="5" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="J79" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -647,10 +647,10 @@
     <t>40金宠自选</t>
   </si>
   <si>
-    <t>21,21,21,21,21,21</t>
-  </si>
-  <si>
-    <t>19,20,21,28,29,30</t>
+    <t>21,21,21,21,21,21,21,21,21</t>
+  </si>
+  <si>
+    <t>19,20,21,28,29,30,37,38,39</t>
   </si>
   <si>
     <t>40资质金宠自选</t>
@@ -659,7 +659,7 @@
     <t>45金宠自选</t>
   </si>
   <si>
-    <t>22,23,24,31,32,33</t>
+    <t>22,23,24,31,32,33,40,41,42</t>
   </si>
   <si>
     <t>45资质金宠自选</t>
@@ -668,7 +668,7 @@
     <t>50金宠自选</t>
   </si>
   <si>
-    <t>25,26,27,34,35,36</t>
+    <t>25,26,27,34,35,36,43,44,45</t>
   </si>
   <si>
     <t>50资质金宠自选</t>
@@ -1639,7 +1639,7 @@
     <col min="1" max="3" width="9" style="1"/>
     <col min="4" max="5" width="16.625" style="1" customWidth="1"/>
     <col min="6" max="6" width="13.375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="19.75" style="1" customWidth="1"/>
+    <col min="7" max="7" width="31.25" style="1" customWidth="1"/>
     <col min="8" max="8" width="49.375" style="1" customWidth="1"/>
     <col min="9" max="9" width="26.875" style="1" customWidth="1"/>
     <col min="10" max="10" width="42.25" style="1" customWidth="1"/>
@@ -3434,7 +3434,7 @@
         <v>207</v>
       </c>
       <c r="I77" s="5" t="s">
-        <v>15</v>
+        <v>86</v>
       </c>
       <c r="J77" s="1" t="s">
         <v>208</v>
@@ -3460,7 +3460,7 @@
         <v>210</v>
       </c>
       <c r="I78" s="5" t="s">
-        <v>15</v>
+        <v>86</v>
       </c>
       <c r="J78" s="1" t="s">
         <v>211</v>
@@ -3486,7 +3486,7 @@
         <v>213</v>
       </c>
       <c r="I79" s="5" t="s">
-        <v>15</v>
+        <v>86</v>
       </c>
       <c r="J79" s="1" t="s">
         <v>214</v>

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="215">
   <si>
     <t>_id</t>
   </si>
@@ -647,10 +647,13 @@
     <t>40金宠自选</t>
   </si>
   <si>
-    <t>21,21,21,21,21,21,21,21,21</t>
-  </si>
-  <si>
-    <t>19,20,21,28,29,30,37,38,39</t>
+    <t>21,21,21,21,21,21,21,21,21,21,21,21</t>
+  </si>
+  <si>
+    <t>19,20,21,22,23,24,25,26,27,28,29,30</t>
+  </si>
+  <si>
+    <t>1,1,1,1,1,1,1,1,1,1,1,1</t>
   </si>
   <si>
     <t>40资质金宠自选</t>
@@ -659,16 +662,13 @@
     <t>45金宠自选</t>
   </si>
   <si>
-    <t>22,23,24,31,32,33,40,41,42</t>
-  </si>
-  <si>
     <t>45资质金宠自选</t>
   </si>
   <si>
     <t>50金宠自选</t>
   </si>
   <si>
-    <t>25,26,27,34,35,36,43,44,45</t>
+    <t>31,32,33,34,35,36,37,38,39,40,41,42</t>
   </si>
   <si>
     <t>50资质金宠自选</t>
@@ -3434,10 +3434,10 @@
         <v>207</v>
       </c>
       <c r="I77" s="5" t="s">
-        <v>86</v>
+        <v>208</v>
       </c>
       <c r="J77" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="3:10">
@@ -3445,7 +3445,7 @@
         <v>208</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E78" s="1">
         <v>1</v>
@@ -3453,15 +3453,9 @@
       <c r="F78" s="2">
         <v>0</v>
       </c>
-      <c r="G78" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="H78" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="I78" s="5" t="s">
-        <v>86</v>
-      </c>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
       <c r="J78" s="1" t="s">
         <v>211</v>
       </c>
@@ -3486,7 +3480,7 @@
         <v>213</v>
       </c>
       <c r="I79" s="5" t="s">
-        <v>86</v>
+        <v>208</v>
       </c>
       <c r="J79" s="1" t="s">
         <v>214</v>

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="216">
   <si>
     <t>_id</t>
   </si>
@@ -39,6 +39,9 @@
   </si>
   <si>
     <t>LevelRequired</t>
+  </si>
+  <si>
+    <t>OpenType</t>
   </si>
   <si>
     <t>ItemTypeList</t>
@@ -1633,20 +1636,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:J79"/>
+  <dimension ref="C3:K79"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
-    <col min="4" max="5" width="16.625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="31.25" style="1" customWidth="1"/>
-    <col min="8" max="8" width="49.375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="26.875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="42.25" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="1"/>
+    <col min="4" max="4" width="16.625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.1666666666667" style="1" customWidth="1"/>
+    <col min="6" max="7" width="13.0833333333333" style="2" customWidth="1"/>
+    <col min="8" max="8" width="31.25" style="1" customWidth="1"/>
+    <col min="9" max="9" width="49.375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="26.875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="42.25" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" customHeight="1" spans="3:10">
+    <row r="3" customHeight="1" spans="3:11">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1671,10 +1675,13 @@
       <c r="J3" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" customHeight="1" spans="3:10">
+      <c r="K3" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="3:11">
       <c r="C4" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>1</v>
@@ -1697,39 +1704,45 @@
       <c r="J4" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" customHeight="1" spans="3:10">
+      <c r="K4" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" customHeight="1" spans="3:11">
       <c r="C5" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>9</v>
-      </c>
       <c r="F5" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:10">
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C6" s="1">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -1737,8 +1750,8 @@
       <c r="F6" s="1">
         <v>0</v>
       </c>
-      <c r="G6" s="5" t="s">
-        <v>13</v>
+      <c r="G6" s="1">
+        <v>2</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>14</v>
@@ -1746,42 +1759,48 @@
       <c r="I6" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J6" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="J6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C7" s="1">
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="1">
+        <v>1</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0</v>
+      </c>
+      <c r="G7" s="1">
+        <v>2</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J7" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="1">
-        <v>1</v>
-      </c>
-      <c r="F7" s="1">
-        <v>0</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H7" s="5" t="s">
+      <c r="K7" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I7" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:10">
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -1789,25 +1808,28 @@
       <c r="F8" s="1">
         <v>0</v>
       </c>
-      <c r="G8" s="5" t="s">
-        <v>13</v>
+      <c r="G8" s="1">
+        <v>2</v>
       </c>
       <c r="H8" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I8" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:10">
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
@@ -1815,25 +1837,28 @@
       <c r="F9" s="1">
         <v>0</v>
       </c>
-      <c r="G9" s="5" t="s">
-        <v>13</v>
+      <c r="G9" s="1">
+        <v>2</v>
       </c>
       <c r="H9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K9" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I9" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:10">
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C10" s="1">
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -1841,25 +1866,28 @@
       <c r="F10" s="1">
         <v>0</v>
       </c>
-      <c r="G10" s="5" t="s">
-        <v>13</v>
+      <c r="G10" s="1">
+        <v>2</v>
       </c>
       <c r="H10" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K10" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="I10" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:10">
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C11" s="1">
         <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -1867,25 +1895,28 @@
       <c r="F11" s="1">
         <v>0</v>
       </c>
-      <c r="G11" s="5" t="s">
-        <v>13</v>
+      <c r="G11" s="1">
+        <v>2</v>
       </c>
       <c r="H11" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K11" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I11" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:10">
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C12" s="1">
         <v>7</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
@@ -1893,25 +1924,28 @@
       <c r="F12" s="1">
         <v>0</v>
       </c>
-      <c r="G12" s="5" t="s">
-        <v>13</v>
+      <c r="G12" s="1">
+        <v>2</v>
       </c>
       <c r="H12" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K12" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I12" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" customHeight="1" spans="3:10">
+    </row>
+    <row r="13" customHeight="1" spans="3:11">
       <c r="C13" s="1">
         <v>8</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
@@ -1919,8 +1953,8 @@
       <c r="F13" s="2">
         <v>0</v>
       </c>
-      <c r="G13" s="5" t="s">
-        <v>29</v>
+      <c r="G13" s="1">
+        <v>2</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>30</v>
@@ -1928,16 +1962,19 @@
       <c r="I13" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="J13" s="1" t="s">
+      <c r="J13" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="14" customHeight="1" spans="3:10">
+      <c r="K13" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="3:11">
       <c r="C14" s="1">
         <v>9</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
@@ -1945,25 +1982,28 @@
       <c r="F14" s="2">
         <v>0</v>
       </c>
-      <c r="G14" s="5" t="s">
-        <v>29</v>
+      <c r="G14" s="1">
+        <v>2</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="J14" s="1" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="15" customHeight="1" spans="3:10">
+      <c r="J14" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="3:11">
       <c r="C15" s="1">
         <v>10</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E15" s="1">
         <v>0</v>
@@ -1971,8 +2011,8 @@
       <c r="F15" s="2">
         <v>0</v>
       </c>
-      <c r="G15" s="5" t="s">
-        <v>37</v>
+      <c r="G15" s="1">
+        <v>1</v>
       </c>
       <c r="H15" s="5" t="s">
         <v>38</v>
@@ -1980,16 +2020,19 @@
       <c r="I15" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="J15" s="1" t="s">
+      <c r="J15" s="5" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="16" customHeight="1" spans="3:10">
+      <c r="K15" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="3:11">
       <c r="C16" s="1">
         <v>11</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E16" s="1">
         <v>0</v>
@@ -1997,25 +2040,28 @@
       <c r="F16" s="2">
         <v>0</v>
       </c>
-      <c r="G16" s="5" t="s">
-        <v>37</v>
+      <c r="G16" s="1">
+        <v>1</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="J16" s="1" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="17" customHeight="1" spans="3:10">
+      <c r="J16" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="3:11">
       <c r="C17" s="1">
         <v>12</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E17" s="1">
         <v>0</v>
@@ -2023,25 +2069,28 @@
       <c r="F17" s="2">
         <v>0</v>
       </c>
-      <c r="G17" s="5" t="s">
-        <v>37</v>
+      <c r="G17" s="1">
+        <v>1</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="J17" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="J17" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C18" s="1">
         <v>13</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E18" s="1">
         <v>1</v>
@@ -2049,25 +2098,28 @@
       <c r="F18" s="1">
         <v>0</v>
       </c>
-      <c r="G18" s="5" t="s">
-        <v>13</v>
+      <c r="G18" s="1">
+        <v>2</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="J18" s="1" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="19" customHeight="1" spans="3:10">
+      <c r="J18" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="3:11">
       <c r="C19" s="1">
         <v>14</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E19" s="1">
         <v>1</v>
@@ -2075,25 +2127,28 @@
       <c r="F19" s="2">
         <v>0</v>
       </c>
-      <c r="G19" s="5" t="s">
-        <v>13</v>
+      <c r="G19" s="1">
+        <v>2</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="J19" s="1" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="20" customHeight="1" spans="3:10">
+      <c r="J19" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="3:11">
       <c r="C20" s="1">
         <v>15</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E20" s="1">
         <v>0</v>
@@ -2101,25 +2156,28 @@
       <c r="F20" s="2">
         <v>0</v>
       </c>
-      <c r="G20" s="5" t="s">
-        <v>37</v>
+      <c r="G20" s="1">
+        <v>1</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="J20" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="21" customHeight="1" spans="3:10">
+      <c r="J20" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="3:11">
       <c r="C21" s="1">
         <v>16</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E21" s="1">
         <v>0</v>
@@ -2127,25 +2185,28 @@
       <c r="F21" s="2">
         <v>0</v>
       </c>
-      <c r="G21" s="5" t="s">
-        <v>37</v>
+      <c r="G21" s="1">
+        <v>1</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="J21" s="1" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="22" customHeight="1" spans="3:10">
+      <c r="J21" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="3:11">
       <c r="C22" s="1">
         <v>17</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E22" s="1">
         <v>0</v>
@@ -2153,25 +2214,28 @@
       <c r="F22" s="2">
         <v>0</v>
       </c>
-      <c r="G22" s="5" t="s">
-        <v>37</v>
+      <c r="G22" s="1">
+        <v>1</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="J22" s="1" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="23" customHeight="1" spans="3:10">
+      <c r="J22" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="3:11">
       <c r="C23" s="1">
         <v>18</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
@@ -2179,25 +2243,28 @@
       <c r="F23" s="2">
         <v>0</v>
       </c>
-      <c r="G23" s="5" t="s">
-        <v>63</v>
+      <c r="G23" s="1">
+        <v>2</v>
       </c>
       <c r="H23" s="5" t="s">
         <v>64</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="J23" s="1" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="24" customHeight="1" spans="3:10">
+      <c r="J23" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="3:11">
       <c r="C24" s="1">
         <v>19</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
@@ -2205,25 +2272,28 @@
       <c r="F24" s="2">
         <v>0</v>
       </c>
-      <c r="G24" s="5" t="s">
-        <v>67</v>
+      <c r="G24" s="1">
+        <v>2</v>
       </c>
       <c r="H24" s="5" t="s">
         <v>68</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="J24" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="25" customHeight="1" spans="3:10">
+        <v>69</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="3:11">
       <c r="C25" s="1">
         <v>20</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E25" s="1">
         <v>1</v>
@@ -2231,25 +2301,28 @@
       <c r="F25" s="2">
         <v>0</v>
       </c>
-      <c r="G25" s="5" t="s">
-        <v>67</v>
+      <c r="G25" s="1">
+        <v>2</v>
       </c>
       <c r="H25" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K25" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="I25" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:10">
+    </row>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C26" s="1">
         <v>21</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
@@ -2257,25 +2330,28 @@
       <c r="F26" s="1">
         <v>0</v>
       </c>
-      <c r="G26" s="5" t="s">
-        <v>72</v>
+      <c r="G26" s="1">
+        <v>2</v>
       </c>
       <c r="H26" s="5" t="s">
         <v>73</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="J26" s="1" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="J26" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C27" s="1">
         <v>22</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E27" s="1">
         <v>1</v>
@@ -2283,25 +2359,28 @@
       <c r="F27" s="1">
         <v>0</v>
       </c>
-      <c r="G27" s="5" t="s">
-        <v>76</v>
+      <c r="G27" s="1">
+        <v>2</v>
       </c>
       <c r="H27" s="5" t="s">
         <v>77</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="28" customHeight="1" spans="3:10">
+        <v>78</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="3:11">
       <c r="C28" s="1">
         <v>23</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E28" s="1">
         <v>1</v>
@@ -2309,8 +2388,8 @@
       <c r="F28" s="1">
         <v>0</v>
       </c>
-      <c r="G28" s="5" t="s">
-        <v>79</v>
+      <c r="G28" s="1">
+        <v>2</v>
       </c>
       <c r="H28" s="5" t="s">
         <v>80</v>
@@ -2318,16 +2397,19 @@
       <c r="I28" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="J28" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="29" customHeight="1" spans="3:10">
+      <c r="J28" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="3:11">
       <c r="C29" s="1">
         <v>24</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
@@ -2335,25 +2417,28 @@
       <c r="F29" s="2">
         <v>0</v>
       </c>
-      <c r="G29" s="5" t="s">
-        <v>63</v>
+      <c r="G29" s="1">
+        <v>2</v>
       </c>
       <c r="H29" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="J29" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K29" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="I29" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="J29" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="30" customHeight="1" spans="3:10">
+    </row>
+    <row r="30" customHeight="1" spans="3:11">
       <c r="C30" s="1">
         <v>25</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
@@ -2361,8 +2446,8 @@
       <c r="F30" s="2">
         <v>0</v>
       </c>
-      <c r="G30" s="5" t="s">
-        <v>84</v>
+      <c r="G30" s="1">
+        <v>2</v>
       </c>
       <c r="H30" s="5" t="s">
         <v>85</v>
@@ -2370,16 +2455,19 @@
       <c r="I30" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="J30" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="31" customHeight="1" spans="3:10">
+      <c r="J30" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="3:11">
       <c r="C31" s="1">
         <v>26</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
@@ -2387,25 +2475,28 @@
       <c r="F31" s="2">
         <v>0</v>
       </c>
-      <c r="G31" s="5" t="s">
-        <v>88</v>
+      <c r="G31" s="1">
+        <v>2</v>
       </c>
       <c r="H31" s="5" t="s">
         <v>89</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="32" customHeight="1" spans="3:10">
+        <v>90</v>
+      </c>
+      <c r="J31" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="3:11">
       <c r="C32" s="1">
         <v>27</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E32" s="1">
         <v>1</v>
@@ -2413,25 +2504,28 @@
       <c r="F32" s="2">
         <v>0</v>
       </c>
-      <c r="G32" s="5" t="s">
-        <v>29</v>
+      <c r="G32" s="1">
+        <v>2</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>91</v>
+        <v>30</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="J32" s="1" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="33" customHeight="1" spans="3:10">
+      <c r="J32" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="3:11">
       <c r="C33" s="1">
         <v>28</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E33" s="1">
         <v>1</v>
@@ -2439,25 +2533,28 @@
       <c r="F33" s="2">
         <v>0</v>
       </c>
-      <c r="G33" s="5" t="s">
+      <c r="G33" s="1">
+        <v>2</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="J33" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K33" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="H33" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="I33" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="J33" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="34" customHeight="1" spans="3:10">
+    </row>
+    <row r="34" customHeight="1" spans="3:11">
       <c r="C34" s="1">
         <v>29</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E34" s="1">
         <v>1</v>
@@ -2465,25 +2562,28 @@
       <c r="F34" s="2">
         <v>0</v>
       </c>
-      <c r="G34" s="5" t="s">
-        <v>29</v>
+      <c r="G34" s="1">
+        <v>2</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>97</v>
+        <v>30</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="J34" s="1" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="35" customHeight="1" spans="3:10">
+      <c r="J34" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="3:11">
       <c r="C35" s="1">
         <v>30</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E35" s="1">
         <v>1</v>
@@ -2491,8 +2591,8 @@
       <c r="F35" s="2">
         <v>0</v>
       </c>
-      <c r="G35" s="5" t="s">
-        <v>100</v>
+      <c r="G35" s="1">
+        <v>2</v>
       </c>
       <c r="H35" s="5" t="s">
         <v>101</v>
@@ -2500,16 +2600,19 @@
       <c r="I35" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="J35" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="36" customHeight="1" spans="3:10">
+      <c r="J35" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="3:11">
       <c r="C36" s="1">
         <v>31</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E36" s="1">
         <v>1</v>
@@ -2517,25 +2620,28 @@
       <c r="F36" s="2">
         <v>0</v>
       </c>
-      <c r="G36" s="5" t="s">
-        <v>104</v>
+      <c r="G36" s="1">
+        <v>2</v>
       </c>
       <c r="H36" s="5" t="s">
         <v>105</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="J36" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="37" customHeight="1" spans="3:10">
+        <v>106</v>
+      </c>
+      <c r="J36" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="3:11">
       <c r="C37" s="1">
         <v>32</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E37" s="1">
         <v>0</v>
@@ -2543,8 +2649,8 @@
       <c r="F37" s="2">
         <v>0</v>
       </c>
-      <c r="G37" s="5" t="s">
-        <v>107</v>
+      <c r="G37" s="1">
+        <v>2</v>
       </c>
       <c r="H37" s="5" t="s">
         <v>108</v>
@@ -2552,16 +2658,19 @@
       <c r="I37" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="J37" s="1" t="s">
+      <c r="J37" s="5" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="38" customHeight="1" spans="3:10">
+      <c r="K37" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="3:11">
       <c r="C38" s="1">
         <v>33</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E38" s="1">
         <v>0</v>
@@ -2569,25 +2678,28 @@
       <c r="F38" s="2">
         <v>0</v>
       </c>
-      <c r="G38" s="5" t="s">
-        <v>107</v>
+      <c r="G38" s="1">
+        <v>2</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="I38" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="J38" s="1" t="s">
+      <c r="J38" s="5" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="40" customHeight="1" spans="3:10">
+      <c r="K38" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="3:11">
       <c r="C40" s="1">
         <v>96</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E40" s="1">
         <v>0</v>
@@ -2595,8 +2707,8 @@
       <c r="F40" s="2">
         <v>0</v>
       </c>
-      <c r="G40" s="5" t="s">
-        <v>116</v>
+      <c r="G40" s="1">
+        <v>2</v>
       </c>
       <c r="H40" s="5" t="s">
         <v>117</v>
@@ -2604,16 +2716,19 @@
       <c r="I40" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="J40" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="41" customHeight="1" spans="3:10">
+      <c r="J40" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="3:11">
       <c r="C41" s="1">
         <v>97</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E41" s="1">
         <v>1</v>
@@ -2621,25 +2736,28 @@
       <c r="F41" s="2">
         <v>0</v>
       </c>
-      <c r="G41" s="5" t="s">
-        <v>120</v>
+      <c r="G41" s="1">
+        <v>2</v>
       </c>
       <c r="H41" s="5" t="s">
         <v>121</v>
       </c>
       <c r="I41" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="J41" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="42" customHeight="1" spans="3:10">
+        <v>122</v>
+      </c>
+      <c r="J41" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="3:11">
       <c r="C42" s="1">
         <v>98</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E42" s="1">
         <v>1</v>
@@ -2647,25 +2765,28 @@
       <c r="F42" s="2">
         <v>0</v>
       </c>
-      <c r="G42" s="5" t="s">
-        <v>123</v>
+      <c r="G42" s="1">
+        <v>2</v>
       </c>
       <c r="H42" s="5" t="s">
         <v>124</v>
       </c>
       <c r="I42" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="J42" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="43" customHeight="1" spans="3:10">
+        <v>125</v>
+      </c>
+      <c r="J42" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="3:11">
       <c r="C43" s="1">
         <v>99</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E43" s="1">
         <v>0</v>
@@ -2673,25 +2794,28 @@
       <c r="F43" s="2">
         <v>0</v>
       </c>
-      <c r="G43" s="5" t="s">
-        <v>116</v>
+      <c r="G43" s="1">
+        <v>2</v>
       </c>
       <c r="H43" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="I43" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="J43" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="K43" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="I43" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="J43" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="44" customHeight="1" spans="3:10">
+    </row>
+    <row r="44" customHeight="1" spans="3:11">
       <c r="C44" s="1">
         <v>100</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E44" s="1">
         <v>0</v>
@@ -2699,8 +2823,8 @@
       <c r="F44" s="2">
         <v>0</v>
       </c>
-      <c r="G44" s="5" t="s">
-        <v>128</v>
+      <c r="G44" s="1">
+        <v>2</v>
       </c>
       <c r="H44" s="5" t="s">
         <v>129</v>
@@ -2708,16 +2832,19 @@
       <c r="I44" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="J44" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="45" customHeight="1" spans="3:10">
+      <c r="J44" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="3:11">
       <c r="C45" s="1">
         <v>101</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E45" s="1">
         <v>0</v>
@@ -2725,25 +2852,28 @@
       <c r="F45" s="2">
         <v>0</v>
       </c>
-      <c r="G45" s="5" t="s">
-        <v>116</v>
+      <c r="G45" s="1">
+        <v>2</v>
       </c>
       <c r="H45" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="I45" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="J45" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="K45" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="I45" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="J45" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="46" customHeight="1" spans="3:10">
+    </row>
+    <row r="46" customHeight="1" spans="3:11">
       <c r="C46" s="1">
         <v>102</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E46" s="1">
         <v>0</v>
@@ -2751,25 +2881,28 @@
       <c r="F46" s="2">
         <v>0</v>
       </c>
-      <c r="G46" s="5" t="s">
-        <v>116</v>
+      <c r="G46" s="1">
+        <v>2</v>
       </c>
       <c r="H46" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="I46" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="J46" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="K46" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="I46" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="J46" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="47" customHeight="1" spans="3:10">
+    </row>
+    <row r="47" customHeight="1" spans="3:11">
       <c r="C47" s="1">
         <v>103</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E47" s="1">
         <v>0</v>
@@ -2777,25 +2910,28 @@
       <c r="F47" s="2">
         <v>0</v>
       </c>
-      <c r="G47" s="5" t="s">
-        <v>116</v>
+      <c r="G47" s="1">
+        <v>2</v>
       </c>
       <c r="H47" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="I47" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="J47" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="K47" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="I47" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="J47" s="1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="48" customHeight="1" spans="3:10">
+    </row>
+    <row r="48" customHeight="1" spans="3:11">
       <c r="C48" s="1">
         <v>104</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E48" s="1">
         <v>0</v>
@@ -2803,25 +2939,28 @@
       <c r="F48" s="2">
         <v>0</v>
       </c>
-      <c r="G48" s="5" t="s">
-        <v>116</v>
+      <c r="G48" s="1">
+        <v>2</v>
       </c>
       <c r="H48" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="I48" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="J48" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="K48" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="I48" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="J48" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="49" customHeight="1" spans="3:10">
+    </row>
+    <row r="49" customHeight="1" spans="3:11">
       <c r="C49" s="1">
         <v>105</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E49" s="1">
         <v>0</v>
@@ -2829,25 +2968,28 @@
       <c r="F49" s="2">
         <v>0</v>
       </c>
-      <c r="G49" s="5" t="s">
-        <v>116</v>
+      <c r="G49" s="1">
+        <v>2</v>
       </c>
       <c r="H49" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="I49" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="J49" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="K49" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="I49" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="J49" s="1" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="51" customHeight="1" spans="3:10">
+    </row>
+    <row r="51" customHeight="1" spans="3:11">
       <c r="C51" s="1">
         <v>106</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E51" s="1">
         <v>1</v>
@@ -2855,8 +2997,8 @@
       <c r="F51" s="2">
         <v>0</v>
       </c>
-      <c r="G51" s="5" t="s">
-        <v>142</v>
+      <c r="G51" s="1">
+        <v>1</v>
       </c>
       <c r="H51" s="5" t="s">
         <v>143</v>
@@ -2864,16 +3006,19 @@
       <c r="I51" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="J51" s="1" t="s">
+      <c r="J51" s="5" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="52" customHeight="1" spans="3:10">
+      <c r="K51" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="52" customHeight="1" spans="3:11">
       <c r="C52" s="1">
         <v>107</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E52" s="1">
         <v>1</v>
@@ -2881,25 +3026,28 @@
       <c r="F52" s="2">
         <v>0</v>
       </c>
-      <c r="G52" s="5" t="s">
-        <v>63</v>
+      <c r="G52" s="1">
+        <v>2</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>147</v>
+        <v>64</v>
       </c>
       <c r="I52" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="J52" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="53" customHeight="1" spans="3:10">
+        <v>148</v>
+      </c>
+      <c r="J52" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K52" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="53" customHeight="1" spans="3:11">
       <c r="C53" s="1">
         <v>108</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E53" s="1">
         <v>1</v>
@@ -2907,25 +3055,28 @@
       <c r="F53" s="2">
         <v>0</v>
       </c>
-      <c r="G53" s="5" t="s">
-        <v>63</v>
+      <c r="G53" s="1">
+        <v>2</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>149</v>
+        <v>64</v>
       </c>
       <c r="I53" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="J53" s="1" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="55" customHeight="1" spans="3:10">
+      <c r="J53" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K53" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="55" customHeight="1" spans="3:11">
       <c r="C55" s="1">
         <v>109</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E55" s="1">
         <v>1</v>
@@ -2933,25 +3084,28 @@
       <c r="F55" s="2">
         <v>0</v>
       </c>
-      <c r="G55" s="5" t="s">
-        <v>152</v>
+      <c r="G55" s="2">
+        <v>2</v>
       </c>
       <c r="H55" s="5" t="s">
         <v>153</v>
       </c>
       <c r="I55" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="J55" s="1" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="56" customHeight="1" spans="3:10">
+      <c r="J55" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K55" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="56" customHeight="1" spans="3:11">
       <c r="C56" s="1">
         <v>110</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E56" s="1">
         <v>1</v>
@@ -2959,25 +3113,28 @@
       <c r="F56" s="2">
         <v>0</v>
       </c>
-      <c r="G56" s="5" t="s">
-        <v>152</v>
+      <c r="G56" s="2">
+        <v>2</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="I56" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="J56" s="1" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="57" customHeight="1" spans="3:10">
+      <c r="J56" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="3:11">
       <c r="C57" s="1">
         <v>111</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E57" s="1">
         <v>1</v>
@@ -2985,25 +3142,28 @@
       <c r="F57" s="2">
         <v>0</v>
       </c>
-      <c r="G57" s="5" t="s">
-        <v>152</v>
+      <c r="G57" s="2">
+        <v>2</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="I57" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="J57" s="1" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="58" customHeight="1" spans="3:10">
+      <c r="J57" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K57" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="3:11">
       <c r="C58" s="1">
         <v>112</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E58" s="1">
         <v>1</v>
@@ -3011,25 +3171,28 @@
       <c r="F58" s="2">
         <v>0</v>
       </c>
-      <c r="G58" s="5" t="s">
-        <v>152</v>
+      <c r="G58" s="2">
+        <v>2</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="I58" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="J58" s="1" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="59" customHeight="1" spans="3:10">
+      <c r="J58" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K58" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="59" customHeight="1" spans="3:11">
       <c r="C59" s="1">
         <v>113</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E59" s="1">
         <v>1</v>
@@ -3037,25 +3200,28 @@
       <c r="F59" s="2">
         <v>0</v>
       </c>
-      <c r="G59" s="5" t="s">
-        <v>152</v>
+      <c r="G59" s="2">
+        <v>2</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="I59" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="J59" s="1" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="60" customHeight="1" spans="3:10">
+      <c r="J59" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K59" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="60" customHeight="1" spans="3:11">
       <c r="C60" s="1">
         <v>114</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E60" s="1">
         <v>1</v>
@@ -3063,25 +3229,28 @@
       <c r="F60" s="2">
         <v>0</v>
       </c>
-      <c r="G60" s="5" t="s">
-        <v>168</v>
+      <c r="G60" s="2">
+        <v>2</v>
       </c>
       <c r="H60" s="5" t="s">
         <v>169</v>
       </c>
       <c r="I60" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="J60" s="1" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="61" customHeight="1" spans="3:10">
+      <c r="J60" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="K60" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="61" customHeight="1" spans="3:11">
       <c r="C61" s="1">
         <v>115</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E61" s="1">
         <v>1</v>
@@ -3089,25 +3258,28 @@
       <c r="F61" s="2">
         <v>0</v>
       </c>
-      <c r="G61" s="5" t="s">
-        <v>172</v>
+      <c r="G61" s="2">
+        <v>2</v>
       </c>
       <c r="H61" s="5" t="s">
         <v>173</v>
       </c>
       <c r="I61" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="J61" s="1" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="63" customHeight="1" spans="3:10">
+        <v>174</v>
+      </c>
+      <c r="J61" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K61" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="63" customHeight="1" spans="3:11">
       <c r="C63" s="1">
         <v>121</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E63" s="1">
         <v>1</v>
@@ -3115,25 +3287,28 @@
       <c r="F63" s="2">
         <v>0</v>
       </c>
-      <c r="G63" s="5" t="s">
-        <v>152</v>
+      <c r="G63" s="2">
+        <v>2</v>
       </c>
       <c r="H63" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="I63" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="J63" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K63" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="I63" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="J63" s="2" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="64" customHeight="1" spans="3:10">
+    </row>
+    <row r="64" customHeight="1" spans="3:11">
       <c r="C64" s="1">
         <v>122</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E64" s="1">
         <v>1</v>
@@ -3141,25 +3316,28 @@
       <c r="F64" s="2">
         <v>0</v>
       </c>
-      <c r="G64" s="5" t="s">
-        <v>152</v>
+      <c r="G64" s="2">
+        <v>2</v>
       </c>
       <c r="H64" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="I64" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="J64" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K64" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="I64" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="J64" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="65" customHeight="1" spans="3:10">
+    </row>
+    <row r="65" customHeight="1" spans="3:11">
       <c r="C65" s="1">
         <v>123</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E65" s="1">
         <v>1</v>
@@ -3167,25 +3345,28 @@
       <c r="F65" s="2">
         <v>0</v>
       </c>
-      <c r="G65" s="5" t="s">
-        <v>152</v>
+      <c r="G65" s="2">
+        <v>2</v>
       </c>
       <c r="H65" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="I65" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="J65" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K65" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="I65" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="J65" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="66" customHeight="1" spans="3:10">
+    </row>
+    <row r="66" customHeight="1" spans="3:11">
       <c r="C66" s="1">
         <v>124</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E66" s="1">
         <v>1</v>
@@ -3193,25 +3374,28 @@
       <c r="F66" s="2">
         <v>0</v>
       </c>
-      <c r="G66" s="5" t="s">
-        <v>152</v>
+      <c r="G66" s="2">
+        <v>2</v>
       </c>
       <c r="H66" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="I66" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="J66" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K66" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="I66" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="J66" s="1" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="67" customHeight="1" spans="3:10">
+    </row>
+    <row r="67" customHeight="1" spans="3:11">
       <c r="C67" s="1">
         <v>125</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E67" s="1">
         <v>1</v>
@@ -3219,25 +3403,28 @@
       <c r="F67" s="2">
         <v>0</v>
       </c>
-      <c r="G67" s="5" t="s">
-        <v>152</v>
+      <c r="G67" s="2">
+        <v>2</v>
       </c>
       <c r="H67" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="I67" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="J67" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K67" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="I67" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="J67" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="69" customHeight="1" spans="3:10">
+    </row>
+    <row r="69" customHeight="1" spans="3:11">
       <c r="C69" s="1">
         <v>127</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E69" s="1">
         <v>1</v>
@@ -3245,25 +3432,28 @@
       <c r="F69" s="2">
         <v>0</v>
       </c>
-      <c r="G69" s="5" t="s">
-        <v>172</v>
+      <c r="G69" s="2">
+        <v>2</v>
       </c>
       <c r="H69" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="I69" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="J69" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K69" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="I69" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="J69" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="71" customHeight="1" spans="3:10">
+    </row>
+    <row r="71" customHeight="1" spans="3:11">
       <c r="C71" s="1">
         <v>201</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E71" s="1">
         <v>1</v>
@@ -3271,25 +3461,28 @@
       <c r="F71" s="2">
         <v>0</v>
       </c>
-      <c r="G71" s="5" t="s">
-        <v>187</v>
+      <c r="G71" s="2">
+        <v>2</v>
       </c>
       <c r="H71" s="5" t="s">
         <v>188</v>
       </c>
       <c r="I71" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="J71" s="1" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="72" customHeight="1" spans="3:10">
+      <c r="J71" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K71" s="1" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="72" customHeight="1" spans="3:11">
       <c r="C72" s="1">
         <v>202</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E72" s="1">
         <v>1</v>
@@ -3297,25 +3490,28 @@
       <c r="F72" s="2">
         <v>0</v>
       </c>
-      <c r="G72" s="5" t="s">
-        <v>187</v>
+      <c r="G72" s="2">
+        <v>2</v>
       </c>
       <c r="H72" s="5" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="I72" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="J72" s="1" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="73" customHeight="1" spans="3:10">
+      <c r="J72" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K72" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="73" customHeight="1" spans="3:11">
       <c r="C73" s="1">
         <v>203</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E73" s="1">
         <v>1</v>
@@ -3323,25 +3519,28 @@
       <c r="F73" s="2">
         <v>0</v>
       </c>
-      <c r="G73" s="5" t="s">
-        <v>187</v>
+      <c r="G73" s="2">
+        <v>2</v>
       </c>
       <c r="H73" s="5" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="I73" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="J73" s="1" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="74" customHeight="1" spans="3:10">
+      <c r="J73" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K73" s="1" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="74" customHeight="1" spans="3:11">
       <c r="C74" s="1">
         <v>204</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E74" s="1">
         <v>1</v>
@@ -3349,25 +3548,28 @@
       <c r="F74" s="2">
         <v>0</v>
       </c>
-      <c r="G74" s="5" t="s">
-        <v>187</v>
+      <c r="G74" s="2">
+        <v>2</v>
       </c>
       <c r="H74" s="5" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="I74" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="J74" s="1" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="75" customHeight="1" spans="3:10">
+      <c r="J74" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K74" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="75" customHeight="1" spans="3:11">
       <c r="C75" s="1">
         <v>205</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E75" s="1">
         <v>1</v>
@@ -3375,25 +3577,28 @@
       <c r="F75" s="2">
         <v>0</v>
       </c>
-      <c r="G75" s="5" t="s">
-        <v>187</v>
+      <c r="G75" s="2">
+        <v>2</v>
       </c>
       <c r="H75" s="5" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="I75" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="J75" s="1" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="76" customHeight="1" spans="3:10">
+      <c r="J75" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K75" s="1" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="76" customHeight="1" spans="3:11">
       <c r="C76" s="1">
         <v>206</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E76" s="1">
         <v>1</v>
@@ -3401,25 +3606,28 @@
       <c r="F76" s="2">
         <v>0</v>
       </c>
-      <c r="G76" s="5" t="s">
-        <v>187</v>
+      <c r="G76" s="2">
+        <v>2</v>
       </c>
       <c r="H76" s="5" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="I76" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="J76" s="1" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="77" customHeight="1" spans="3:10">
+      <c r="J76" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K76" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="77" customHeight="1" spans="3:11">
       <c r="C77" s="1">
         <v>207</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E77" s="1">
         <v>1</v>
@@ -3427,8 +3635,8 @@
       <c r="F77" s="2">
         <v>0</v>
       </c>
-      <c r="G77" s="5" t="s">
-        <v>206</v>
+      <c r="G77" s="2">
+        <v>2</v>
       </c>
       <c r="H77" s="5" t="s">
         <v>207</v>
@@ -3436,16 +3644,19 @@
       <c r="I77" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="J77" s="1" t="s">
+      <c r="J77" s="5" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="78" customHeight="1" spans="3:10">
+      <c r="K77" s="1" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="78" customHeight="1" spans="3:11">
       <c r="C78" s="1">
         <v>208</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E78" s="1">
         <v>1</v>
@@ -3453,19 +3664,22 @@
       <c r="F78" s="2">
         <v>0</v>
       </c>
-      <c r="G78" s="1"/>
+      <c r="G78" s="2">
+        <v>2</v>
+      </c>
       <c r="H78" s="1"/>
       <c r="I78" s="1"/>
-      <c r="J78" s="1" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="79" customHeight="1" spans="3:10">
+      <c r="J78" s="1"/>
+      <c r="K78" s="1" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="79" customHeight="1" spans="3:11">
       <c r="C79" s="1">
         <v>209</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E79" s="1">
         <v>1</v>
@@ -3473,25 +3687,28 @@
       <c r="F79" s="2">
         <v>0</v>
       </c>
-      <c r="G79" s="5" t="s">
-        <v>206</v>
+      <c r="G79" s="2">
+        <v>2</v>
       </c>
       <c r="H79" s="5" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="I79" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="J79" s="1" t="s">
         <v>214</v>
+      </c>
+      <c r="J79" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="K79" s="1" t="s">
+        <v>215</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="F3:F5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="F3:G5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,F3)&lt;2</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:E5 G3:J5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:E5 H3:K5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -281,7 +281,7 @@
     <t>初级法宝自选</t>
   </si>
   <si>
-    <t>180006,180008,180010,180018,180020,180021</t>
+    <t>180006,180011,180012,180013,180020,180021</t>
   </si>
   <si>
     <t>18,18,18,18,18,18,18,18,18</t>
@@ -1636,7 +1636,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:K79"/>
+  <dimension ref="C3:K80"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -2694,44 +2694,18 @@
         <v>115</v>
       </c>
     </row>
-    <row r="40" customHeight="1" spans="3:11">
-      <c r="C40" s="1">
-        <v>96</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="E40" s="1">
-        <v>0</v>
-      </c>
-      <c r="F40" s="2">
-        <v>0</v>
-      </c>
-      <c r="G40" s="1">
-        <v>2</v>
-      </c>
-      <c r="H40" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="I40" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="J40" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="K40" s="1" t="s">
-        <v>116</v>
-      </c>
+    <row r="39" customHeight="1" spans="7:7">
+      <c r="G39" s="1"/>
     </row>
     <row r="41" customHeight="1" spans="3:11">
       <c r="C41" s="1">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E41" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F41" s="2">
         <v>0</v>
@@ -2740,24 +2714,24 @@
         <v>2</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="I41" s="5" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J41" s="5" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:11">
       <c r="C42" s="1">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E42" s="1">
         <v>1</v>
@@ -2769,27 +2743,27 @@
         <v>2</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="I42" s="5" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="J42" s="5" t="s">
-        <v>82</v>
+        <v>32</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:11">
       <c r="C43" s="1">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E43" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" s="2">
         <v>0</v>
@@ -2798,24 +2772,24 @@
         <v>2</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="I43" s="5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="J43" s="5" t="s">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:11">
       <c r="C44" s="1">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E44" s="1">
         <v>0</v>
@@ -2827,24 +2801,24 @@
         <v>2</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="I44" s="5" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="J44" s="5" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:11">
       <c r="C45" s="1">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E45" s="1">
         <v>0</v>
@@ -2856,24 +2830,24 @@
         <v>2</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="I45" s="5" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="J45" s="5" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="3:11">
       <c r="C46" s="1">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E46" s="1">
         <v>0</v>
@@ -2888,21 +2862,21 @@
         <v>117</v>
       </c>
       <c r="I46" s="5" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="J46" s="5" t="s">
         <v>119</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:11">
       <c r="C47" s="1">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E47" s="1">
         <v>0</v>
@@ -2917,21 +2891,21 @@
         <v>117</v>
       </c>
       <c r="I47" s="5" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="J47" s="5" t="s">
         <v>119</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:11">
       <c r="C48" s="1">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E48" s="1">
         <v>0</v>
@@ -2946,21 +2920,21 @@
         <v>117</v>
       </c>
       <c r="I48" s="5" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="J48" s="5" t="s">
         <v>119</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="3:11">
       <c r="C49" s="1">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E49" s="1">
         <v>0</v>
@@ -2975,50 +2949,50 @@
         <v>117</v>
       </c>
       <c r="I49" s="5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J49" s="5" t="s">
         <v>119</v>
       </c>
       <c r="K49" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="50" customHeight="1" spans="3:11">
+      <c r="C50" s="1">
+        <v>105</v>
+      </c>
+      <c r="D50" s="1" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="51" customHeight="1" spans="3:11">
-      <c r="C51" s="1">
-        <v>106</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="E51" s="1">
-        <v>1</v>
-      </c>
-      <c r="F51" s="2">
-        <v>0</v>
-      </c>
-      <c r="G51" s="1">
-        <v>1</v>
-      </c>
-      <c r="H51" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="I51" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="J51" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="K51" s="1" t="s">
-        <v>146</v>
+      <c r="E50" s="1">
+        <v>0</v>
+      </c>
+      <c r="F50" s="2">
+        <v>0</v>
+      </c>
+      <c r="G50" s="1">
+        <v>2</v>
+      </c>
+      <c r="H50" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="I50" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="J50" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="K50" s="1" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="3:11">
       <c r="C52" s="1">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="E52" s="1">
         <v>1</v>
@@ -3027,27 +3001,27 @@
         <v>0</v>
       </c>
       <c r="G52" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>64</v>
+        <v>143</v>
       </c>
       <c r="I52" s="5" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="J52" s="5" t="s">
-        <v>40</v>
+        <v>145</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>83</v>
+        <v>146</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:11">
       <c r="C53" s="1">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E53" s="1">
         <v>1</v>
@@ -3062,50 +3036,50 @@
         <v>64</v>
       </c>
       <c r="I53" s="5" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="J53" s="5" t="s">
         <v>40</v>
       </c>
       <c r="K53" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="54" customHeight="1" spans="3:11">
+      <c r="C54" s="1">
+        <v>108</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E54" s="1">
+        <v>1</v>
+      </c>
+      <c r="F54" s="2">
+        <v>0</v>
+      </c>
+      <c r="G54" s="1">
+        <v>2</v>
+      </c>
+      <c r="H54" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="I54" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="J54" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K54" s="1" t="s">
         <v>151</v>
-      </c>
-    </row>
-    <row r="55" customHeight="1" spans="3:11">
-      <c r="C55" s="1">
-        <v>109</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="E55" s="1">
-        <v>1</v>
-      </c>
-      <c r="F55" s="2">
-        <v>0</v>
-      </c>
-      <c r="G55" s="2">
-        <v>2</v>
-      </c>
-      <c r="H55" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="I55" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="J55" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="K55" s="1" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:11">
       <c r="C56" s="1">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E56" s="1">
         <v>1</v>
@@ -3120,21 +3094,21 @@
         <v>153</v>
       </c>
       <c r="I56" s="5" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="J56" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:11">
       <c r="C57" s="1">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E57" s="1">
         <v>1</v>
@@ -3149,21 +3123,21 @@
         <v>153</v>
       </c>
       <c r="I57" s="5" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="J57" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:11">
       <c r="C58" s="1">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E58" s="1">
         <v>1</v>
@@ -3178,21 +3152,21 @@
         <v>153</v>
       </c>
       <c r="I58" s="5" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="J58" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:11">
       <c r="C59" s="1">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E59" s="1">
         <v>1</v>
@@ -3207,21 +3181,21 @@
         <v>153</v>
       </c>
       <c r="I59" s="5" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="J59" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="3:11">
       <c r="C60" s="1">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E60" s="1">
         <v>1</v>
@@ -3233,82 +3207,82 @@
         <v>2</v>
       </c>
       <c r="H60" s="5" t="s">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="I60" s="5" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="J60" s="5" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="3:11">
       <c r="C61" s="1">
+        <v>114</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E61" s="1">
+        <v>1</v>
+      </c>
+      <c r="F61" s="2">
+        <v>0</v>
+      </c>
+      <c r="G61" s="2">
+        <v>2</v>
+      </c>
+      <c r="H61" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="I61" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="J61" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="K61" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="62" customHeight="1" spans="3:11">
+      <c r="C62" s="1">
         <v>115</v>
       </c>
-      <c r="D61" s="1" t="s">
+      <c r="D62" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="E61" s="1">
-        <v>1</v>
-      </c>
-      <c r="F61" s="2">
-        <v>0</v>
-      </c>
-      <c r="G61" s="2">
-        <v>2</v>
-      </c>
-      <c r="H61" s="5" t="s">
+      <c r="E62" s="1">
+        <v>1</v>
+      </c>
+      <c r="F62" s="2">
+        <v>0</v>
+      </c>
+      <c r="G62" s="2">
+        <v>2</v>
+      </c>
+      <c r="H62" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="I61" s="5" t="s">
+      <c r="I62" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="J61" s="5" t="s">
+      <c r="J62" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="K61" s="1" t="s">
+      <c r="K62" s="1" t="s">
         <v>172</v>
-      </c>
-    </row>
-    <row r="63" customHeight="1" spans="3:11">
-      <c r="C63" s="1">
-        <v>121</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="E63" s="1">
-        <v>1</v>
-      </c>
-      <c r="F63" s="2">
-        <v>0</v>
-      </c>
-      <c r="G63" s="2">
-        <v>2</v>
-      </c>
-      <c r="H63" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="I63" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="J63" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="K63" s="2" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:11">
       <c r="C64" s="1">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E64" s="1">
         <v>1</v>
@@ -3323,21 +3297,21 @@
         <v>153</v>
       </c>
       <c r="I64" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="J64" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:11">
       <c r="C65" s="1">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E65" s="1">
         <v>1</v>
@@ -3352,21 +3326,21 @@
         <v>153</v>
       </c>
       <c r="I65" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="J65" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="3:11">
       <c r="C66" s="1">
-        <v>124</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>181</v>
+        <v>123</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>179</v>
       </c>
       <c r="E66" s="1">
         <v>1</v>
@@ -3381,21 +3355,21 @@
         <v>153</v>
       </c>
       <c r="I66" s="5" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="J66" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="K66" s="1" t="s">
-        <v>181</v>
+      <c r="K66" s="2" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:11">
       <c r="C67" s="1">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E67" s="1">
         <v>1</v>
@@ -3410,79 +3384,79 @@
         <v>153</v>
       </c>
       <c r="I67" s="5" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="J67" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K67" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="68" customHeight="1" spans="3:11">
+      <c r="C68" s="1">
+        <v>125</v>
+      </c>
+      <c r="D68" s="1" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="69" customHeight="1" spans="3:11">
-      <c r="C69" s="1">
+      <c r="E68" s="1">
+        <v>1</v>
+      </c>
+      <c r="F68" s="2">
+        <v>0</v>
+      </c>
+      <c r="G68" s="2">
+        <v>2</v>
+      </c>
+      <c r="H68" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="I68" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="J68" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K68" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="70" customHeight="1" spans="3:11">
+      <c r="C70" s="1">
         <v>127</v>
       </c>
-      <c r="D69" s="1" t="s">
+      <c r="D70" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="E69" s="1">
-        <v>1</v>
-      </c>
-      <c r="F69" s="2">
-        <v>0</v>
-      </c>
-      <c r="G69" s="2">
-        <v>2</v>
-      </c>
-      <c r="H69" s="5" t="s">
+      <c r="E70" s="1">
+        <v>1</v>
+      </c>
+      <c r="F70" s="2">
+        <v>0</v>
+      </c>
+      <c r="G70" s="2">
+        <v>2</v>
+      </c>
+      <c r="H70" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="I69" s="5" t="s">
+      <c r="I70" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="J69" s="5" t="s">
+      <c r="J70" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="K69" s="1" t="s">
+      <c r="K70" s="1" t="s">
         <v>185</v>
-      </c>
-    </row>
-    <row r="71" customHeight="1" spans="3:11">
-      <c r="C71" s="1">
-        <v>201</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E71" s="1">
-        <v>1</v>
-      </c>
-      <c r="F71" s="2">
-        <v>0</v>
-      </c>
-      <c r="G71" s="2">
-        <v>2</v>
-      </c>
-      <c r="H71" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="I71" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="J71" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K71" s="1" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:11">
       <c r="C72" s="1">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="E72" s="1">
         <v>1</v>
@@ -3497,21 +3471,21 @@
         <v>188</v>
       </c>
       <c r="I72" s="5" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="J72" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:11">
       <c r="C73" s="1">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E73" s="1">
         <v>1</v>
@@ -3526,21 +3500,21 @@
         <v>188</v>
       </c>
       <c r="I73" s="5" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="J73" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:11">
       <c r="C74" s="1">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E74" s="1">
         <v>1</v>
@@ -3555,21 +3529,21 @@
         <v>188</v>
       </c>
       <c r="I74" s="5" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="J74" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:11">
       <c r="C75" s="1">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="E75" s="1">
         <v>1</v>
@@ -3584,21 +3558,21 @@
         <v>188</v>
       </c>
       <c r="I75" s="5" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="J75" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K75" s="1" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:11">
       <c r="C76" s="1">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E76" s="1">
         <v>1</v>
@@ -3613,21 +3587,21 @@
         <v>188</v>
       </c>
       <c r="I76" s="5" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="J76" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K76" s="1" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:11">
       <c r="C77" s="1">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E77" s="1">
         <v>1</v>
@@ -3639,67 +3613,93 @@
         <v>2</v>
       </c>
       <c r="H77" s="5" t="s">
-        <v>207</v>
+        <v>188</v>
       </c>
       <c r="I77" s="5" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="J77" s="5" t="s">
-        <v>209</v>
+        <v>32</v>
       </c>
       <c r="K77" s="1" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="3:11">
       <c r="C78" s="1">
+        <v>207</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="E78" s="1">
+        <v>1</v>
+      </c>
+      <c r="F78" s="2">
+        <v>0</v>
+      </c>
+      <c r="G78" s="2">
+        <v>2</v>
+      </c>
+      <c r="H78" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="I78" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="D78" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="E78" s="1">
-        <v>1</v>
-      </c>
-      <c r="F78" s="2">
-        <v>0</v>
-      </c>
-      <c r="G78" s="2">
-        <v>2</v>
-      </c>
-      <c r="H78" s="1"/>
-      <c r="I78" s="1"/>
-      <c r="J78" s="1"/>
+      <c r="J78" s="5" t="s">
+        <v>209</v>
+      </c>
       <c r="K78" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="3:11">
       <c r="C79" s="1">
+        <v>208</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E79" s="1">
+        <v>1</v>
+      </c>
+      <c r="F79" s="2">
+        <v>0</v>
+      </c>
+      <c r="G79" s="2">
+        <v>2</v>
+      </c>
+      <c r="K79" s="1" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="80" customHeight="1" spans="3:11">
+      <c r="C80" s="1">
         <v>209</v>
       </c>
-      <c r="D79" s="1" t="s">
+      <c r="D80" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="E79" s="1">
-        <v>1</v>
-      </c>
-      <c r="F79" s="2">
-        <v>0</v>
-      </c>
-      <c r="G79" s="2">
-        <v>2</v>
-      </c>
-      <c r="H79" s="5" t="s">
+      <c r="E80" s="1">
+        <v>1</v>
+      </c>
+      <c r="F80" s="2">
+        <v>0</v>
+      </c>
+      <c r="G80" s="2">
+        <v>2</v>
+      </c>
+      <c r="H80" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="I79" s="5" t="s">
+      <c r="I80" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="J79" s="5" t="s">
+      <c r="J80" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="K79" s="1" t="s">
+      <c r="K80" s="1" t="s">
         <v>215</v>
       </c>
     </row>

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="218">
   <si>
     <t>_id</t>
   </si>
@@ -375,6 +375,12 @@
   </si>
   <si>
     <t>2个50资质金宠+5w口粮</t>
+  </si>
+  <si>
+    <t>新手法宝自选</t>
+  </si>
+  <si>
+    <t>180006,180008,180010,180018,180020,180021</t>
   </si>
   <si>
     <t>驱魔符距离4件套</t>
@@ -1636,7 +1642,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:K80"/>
+  <dimension ref="A3:K80"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -2694,15 +2700,43 @@
         <v>115</v>
       </c>
     </row>
-    <row r="39" customHeight="1" spans="7:7">
-      <c r="G39" s="1"/>
+    <row r="39" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A39" s="1"/>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1">
+        <v>34</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E39" s="1">
+        <v>1</v>
+      </c>
+      <c r="F39" s="2">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>2</v>
+      </c>
+      <c r="H39" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="I39" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="J39" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="41" customHeight="1" spans="3:11">
       <c r="C41" s="1">
         <v>96</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E41" s="1">
         <v>0</v>
@@ -2714,16 +2748,16 @@
         <v>2</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I41" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="J41" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="K41" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="J41" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="K41" s="1" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:11">
@@ -2731,7 +2765,7 @@
         <v>97</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E42" s="1">
         <v>1</v>
@@ -2743,16 +2777,16 @@
         <v>2</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="I42" s="5" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J42" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:11">
@@ -2760,7 +2794,7 @@
         <v>98</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E43" s="1">
         <v>1</v>
@@ -2772,16 +2806,16 @@
         <v>2</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I43" s="5" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="J43" s="5" t="s">
         <v>82</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:11">
@@ -2789,7 +2823,7 @@
         <v>99</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E44" s="1">
         <v>0</v>
@@ -2801,16 +2835,16 @@
         <v>2</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I44" s="5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J44" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:11">
@@ -2818,7 +2852,7 @@
         <v>100</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E45" s="1">
         <v>0</v>
@@ -2830,16 +2864,16 @@
         <v>2</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="I45" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="J45" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="K45" s="1" t="s">
         <v>130</v>
-      </c>
-      <c r="J45" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="K45" s="1" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="3:11">
@@ -2847,7 +2881,7 @@
         <v>101</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E46" s="1">
         <v>0</v>
@@ -2859,16 +2893,16 @@
         <v>2</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I46" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J46" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:11">
@@ -2876,7 +2910,7 @@
         <v>102</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E47" s="1">
         <v>0</v>
@@ -2888,16 +2922,16 @@
         <v>2</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I47" s="5" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="J47" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:11">
@@ -2905,7 +2939,7 @@
         <v>103</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E48" s="1">
         <v>0</v>
@@ -2917,16 +2951,16 @@
         <v>2</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I48" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="J48" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="3:11">
@@ -2934,7 +2968,7 @@
         <v>104</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E49" s="1">
         <v>0</v>
@@ -2946,16 +2980,16 @@
         <v>2</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I49" s="5" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J49" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="3:11">
@@ -2963,7 +2997,7 @@
         <v>105</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E50" s="1">
         <v>0</v>
@@ -2975,16 +3009,16 @@
         <v>2</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I50" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="J50" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="3:11">
@@ -2992,7 +3026,7 @@
         <v>106</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E52" s="1">
         <v>1</v>
@@ -3004,16 +3038,16 @@
         <v>1</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="I52" s="5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="J52" s="5" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:11">
@@ -3021,7 +3055,7 @@
         <v>107</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E53" s="1">
         <v>1</v>
@@ -3036,7 +3070,7 @@
         <v>64</v>
       </c>
       <c r="I53" s="5" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J53" s="5" t="s">
         <v>40</v>
@@ -3050,7 +3084,7 @@
         <v>108</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E54" s="1">
         <v>1</v>
@@ -3065,13 +3099,13 @@
         <v>64</v>
       </c>
       <c r="I54" s="5" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J54" s="5" t="s">
         <v>40</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:11">
@@ -3079,7 +3113,7 @@
         <v>109</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E56" s="1">
         <v>1</v>
@@ -3091,16 +3125,16 @@
         <v>2</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I56" s="5" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="J56" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:11">
@@ -3108,7 +3142,7 @@
         <v>110</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E57" s="1">
         <v>1</v>
@@ -3120,16 +3154,16 @@
         <v>2</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I57" s="5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="J57" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:11">
@@ -3137,7 +3171,7 @@
         <v>111</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E58" s="1">
         <v>1</v>
@@ -3149,16 +3183,16 @@
         <v>2</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I58" s="5" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="J58" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:11">
@@ -3166,7 +3200,7 @@
         <v>112</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E59" s="1">
         <v>1</v>
@@ -3178,16 +3212,16 @@
         <v>2</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I59" s="5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J59" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="3:11">
@@ -3195,7 +3229,7 @@
         <v>113</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E60" s="1">
         <v>1</v>
@@ -3207,16 +3241,16 @@
         <v>2</v>
       </c>
       <c r="H60" s="5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I60" s="5" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="J60" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="3:11">
@@ -3224,7 +3258,7 @@
         <v>114</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E61" s="1">
         <v>1</v>
@@ -3236,16 +3270,16 @@
         <v>2</v>
       </c>
       <c r="H61" s="5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="I61" s="5" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="J61" s="5" t="s">
         <v>82</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="3:11">
@@ -3253,7 +3287,7 @@
         <v>115</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E62" s="1">
         <v>1</v>
@@ -3265,16 +3299,16 @@
         <v>2</v>
       </c>
       <c r="H62" s="5" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="I62" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J62" s="5" t="s">
         <v>40</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:11">
@@ -3282,7 +3316,7 @@
         <v>121</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E64" s="1">
         <v>1</v>
@@ -3294,16 +3328,16 @@
         <v>2</v>
       </c>
       <c r="H64" s="5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I64" s="5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="J64" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:11">
@@ -3311,7 +3345,7 @@
         <v>122</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E65" s="1">
         <v>1</v>
@@ -3323,16 +3357,16 @@
         <v>2</v>
       </c>
       <c r="H65" s="5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I65" s="5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J65" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="3:11">
@@ -3340,7 +3374,7 @@
         <v>123</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E66" s="1">
         <v>1</v>
@@ -3352,16 +3386,16 @@
         <v>2</v>
       </c>
       <c r="H66" s="5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I66" s="5" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="J66" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:11">
@@ -3369,7 +3403,7 @@
         <v>124</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E67" s="1">
         <v>1</v>
@@ -3381,16 +3415,16 @@
         <v>2</v>
       </c>
       <c r="H67" s="5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I67" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="J67" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:11">
@@ -3398,7 +3432,7 @@
         <v>125</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E68" s="1">
         <v>1</v>
@@ -3410,16 +3444,16 @@
         <v>2</v>
       </c>
       <c r="H68" s="5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I68" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="J68" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:11">
@@ -3427,7 +3461,7 @@
         <v>127</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E70" s="1">
         <v>1</v>
@@ -3439,16 +3473,16 @@
         <v>2</v>
       </c>
       <c r="H70" s="5" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="I70" s="5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="J70" s="5" t="s">
         <v>40</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:11">
@@ -3456,7 +3490,7 @@
         <v>201</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E72" s="1">
         <v>1</v>
@@ -3468,16 +3502,16 @@
         <v>2</v>
       </c>
       <c r="H72" s="5" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="I72" s="5" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="J72" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:11">
@@ -3485,7 +3519,7 @@
         <v>202</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E73" s="1">
         <v>1</v>
@@ -3497,16 +3531,16 @@
         <v>2</v>
       </c>
       <c r="H73" s="5" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="I73" s="5" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="J73" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:11">
@@ -3514,7 +3548,7 @@
         <v>203</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E74" s="1">
         <v>1</v>
@@ -3526,16 +3560,16 @@
         <v>2</v>
       </c>
       <c r="H74" s="5" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="I74" s="5" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="J74" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:11">
@@ -3543,7 +3577,7 @@
         <v>204</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E75" s="1">
         <v>1</v>
@@ -3555,16 +3589,16 @@
         <v>2</v>
       </c>
       <c r="H75" s="5" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="I75" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="J75" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K75" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:11">
@@ -3572,7 +3606,7 @@
         <v>205</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E76" s="1">
         <v>1</v>
@@ -3584,16 +3618,16 @@
         <v>2</v>
       </c>
       <c r="H76" s="5" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="I76" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="J76" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K76" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:11">
@@ -3601,7 +3635,7 @@
         <v>206</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E77" s="1">
         <v>1</v>
@@ -3613,16 +3647,16 @@
         <v>2</v>
       </c>
       <c r="H77" s="5" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="I77" s="5" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="J77" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K77" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="3:11">
@@ -3630,7 +3664,7 @@
         <v>207</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E78" s="1">
         <v>1</v>
@@ -3642,16 +3676,16 @@
         <v>2</v>
       </c>
       <c r="H78" s="5" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I78" s="5" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="J78" s="5" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="K78" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="3:11">
@@ -3659,7 +3693,7 @@
         <v>208</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E79" s="1">
         <v>1</v>
@@ -3671,7 +3705,7 @@
         <v>2</v>
       </c>
       <c r="K79" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="3:11">
@@ -3679,7 +3713,7 @@
         <v>209</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E80" s="1">
         <v>1</v>
@@ -3691,25 +3725,25 @@
         <v>2</v>
       </c>
       <c r="H80" s="5" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I80" s="5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="J80" s="5" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="K80" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:E5 H3:K5" errorStyle="warning">
+      <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
+    </dataValidation>
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="F3:G5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,F3)&lt;2</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:E5 H3:K5" errorStyle="warning">
-      <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="224">
   <si>
     <t>_id</t>
   </si>
@@ -381,6 +381,24 @@
   </si>
   <si>
     <t>180006,180008,180010,180018,180020,180021</t>
+  </si>
+  <si>
+    <t>青龙神器自选</t>
+  </si>
+  <si>
+    <t>61000001,61000002,61000003,61000004,61000005,61000006,61000007,61000008</t>
+  </si>
+  <si>
+    <t>宝石自选</t>
+  </si>
+  <si>
+    <t>5,5,5,5,5,5,5,5,5,5,5,5</t>
+  </si>
+  <si>
+    <t>60000001,60000002,60000003,60000004,60000005,60000006,60000007,60000008,60000009,60000010</t>
+  </si>
+  <si>
+    <t>1,1,1,1,1,1,1,1,1,1,1,1,1</t>
   </si>
   <si>
     <t>驱魔符距离4件套</t>
@@ -1642,7 +1660,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:K80"/>
+  <dimension ref="A3:K82"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -1650,7 +1668,7 @@
     <col min="5" max="5" width="14.1666666666667" style="1" customWidth="1"/>
     <col min="6" max="7" width="13.0833333333333" style="2" customWidth="1"/>
     <col min="8" max="8" width="31.25" style="1" customWidth="1"/>
-    <col min="9" max="9" width="49.375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="60.3333333333333" style="1" customWidth="1"/>
     <col min="10" max="10" width="26.875" style="1" customWidth="1"/>
     <col min="11" max="11" width="42.25" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
@@ -2731,102 +2749,102 @@
         <v>116</v>
       </c>
     </row>
+    <row r="40" customHeight="1" spans="3:11">
+      <c r="C40" s="1">
+        <v>35</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E40" s="1">
+        <v>1</v>
+      </c>
+      <c r="F40" s="2">
+        <v>0</v>
+      </c>
+      <c r="G40" s="1">
+        <v>1</v>
+      </c>
+      <c r="H40" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="I40" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="J40" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
     <row r="41" customHeight="1" spans="3:11">
       <c r="C41" s="1">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E41" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F41" s="2">
         <v>0</v>
       </c>
-      <c r="G41" s="1">
-        <v>2</v>
+      <c r="G41" s="2">
+        <v>1</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="I41" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="J41" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="K41" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="J41" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="K41" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="42" customHeight="1" spans="3:11">
-      <c r="C42" s="1">
-        <v>97</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="E42" s="1">
-        <v>1</v>
-      </c>
-      <c r="F42" s="2">
-        <v>0</v>
-      </c>
-      <c r="G42" s="1">
-        <v>2</v>
-      </c>
-      <c r="H42" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="I42" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="J42" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K42" s="1" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:11">
       <c r="C43" s="1">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D43" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E43" s="1">
+        <v>0</v>
+      </c>
+      <c r="F43" s="2">
+        <v>0</v>
+      </c>
+      <c r="G43" s="1">
+        <v>2</v>
+      </c>
+      <c r="H43" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="E43" s="1">
-        <v>1</v>
-      </c>
-      <c r="F43" s="2">
-        <v>0</v>
-      </c>
-      <c r="G43" s="1">
-        <v>2</v>
-      </c>
-      <c r="H43" s="5" t="s">
+      <c r="I43" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="I43" s="5" t="s">
+      <c r="J43" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="J43" s="5" t="s">
-        <v>82</v>
-      </c>
       <c r="K43" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:11">
       <c r="C44" s="1">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>128</v>
       </c>
       <c r="E44" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F44" s="2">
         <v>0</v>
@@ -2835,13 +2853,13 @@
         <v>2</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="I44" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J44" s="5" t="s">
-        <v>121</v>
+        <v>32</v>
       </c>
       <c r="K44" s="1" t="s">
         <v>128</v>
@@ -2849,13 +2867,13 @@
     </row>
     <row r="45" customHeight="1" spans="3:11">
       <c r="C45" s="1">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E45" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45" s="2">
         <v>0</v>
@@ -2864,21 +2882,21 @@
         <v>2</v>
       </c>
       <c r="H45" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="I45" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="J45" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="K45" s="1" t="s">
         <v>131</v>
-      </c>
-      <c r="I45" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="J45" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="K45" s="1" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="3:11">
       <c r="C46" s="1">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>134</v>
@@ -2893,13 +2911,13 @@
         <v>2</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="I46" s="5" t="s">
         <v>135</v>
       </c>
       <c r="J46" s="5" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="K46" s="1" t="s">
         <v>134</v>
@@ -2907,7 +2925,7 @@
     </row>
     <row r="47" customHeight="1" spans="3:11">
       <c r="C47" s="1">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>136</v>
@@ -2922,13 +2940,13 @@
         <v>2</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="I47" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J47" s="5" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="K47" s="1" t="s">
         <v>136</v>
@@ -2936,10 +2954,10 @@
     </row>
     <row r="48" customHeight="1" spans="3:11">
       <c r="C48" s="1">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E48" s="1">
         <v>0</v>
@@ -2951,24 +2969,24 @@
         <v>2</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="I48" s="5" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J48" s="5" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="3:11">
       <c r="C49" s="1">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E49" s="1">
         <v>0</v>
@@ -2980,24 +2998,24 @@
         <v>2</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="I49" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="J49" s="5" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="3:11">
       <c r="C50" s="1">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E50" s="1">
         <v>0</v>
@@ -3009,111 +3027,140 @@
         <v>2</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="I50" s="5" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="J50" s="5" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
+      </c>
+    </row>
+    <row r="51" customHeight="1" spans="3:11">
+      <c r="C51" s="1">
+        <v>104</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E51" s="1">
+        <v>0</v>
+      </c>
+      <c r="F51" s="2">
+        <v>0</v>
+      </c>
+      <c r="G51" s="1">
+        <v>2</v>
+      </c>
+      <c r="H51" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="I51" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="J51" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="K51" s="1" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="3:11">
       <c r="C52" s="1">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="E52" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F52" s="2">
         <v>0</v>
       </c>
       <c r="G52" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="I52" s="5" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="J52" s="5" t="s">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="K52" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="53" customHeight="1" spans="3:11">
-      <c r="C53" s="1">
-        <v>107</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="E53" s="1">
-        <v>1</v>
-      </c>
-      <c r="F53" s="2">
-        <v>0</v>
-      </c>
-      <c r="G53" s="1">
-        <v>2</v>
-      </c>
-      <c r="H53" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="I53" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="J53" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="K53" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
     <row r="54" customHeight="1" spans="3:11">
       <c r="C54" s="1">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D54" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E54" s="1">
+        <v>1</v>
+      </c>
+      <c r="F54" s="2">
+        <v>0</v>
+      </c>
+      <c r="G54" s="1">
+        <v>1</v>
+      </c>
+      <c r="H54" s="5" t="s">
         <v>151</v>
-      </c>
-      <c r="E54" s="1">
-        <v>1</v>
-      </c>
-      <c r="F54" s="2">
-        <v>0</v>
-      </c>
-      <c r="G54" s="1">
-        <v>2</v>
-      </c>
-      <c r="H54" s="5" t="s">
-        <v>64</v>
       </c>
       <c r="I54" s="5" t="s">
         <v>152</v>
       </c>
       <c r="J54" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="55" customHeight="1" spans="3:11">
+      <c r="C55" s="1">
+        <v>107</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E55" s="1">
+        <v>1</v>
+      </c>
+      <c r="F55" s="2">
+        <v>0</v>
+      </c>
+      <c r="G55" s="1">
+        <v>2</v>
+      </c>
+      <c r="H55" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="I55" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="J55" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="K54" s="1" t="s">
-        <v>153</v>
+      <c r="K55" s="1" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:11">
       <c r="C56" s="1">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E56" s="1">
         <v>1</v>
@@ -3121,69 +3168,40 @@
       <c r="F56" s="2">
         <v>0</v>
       </c>
-      <c r="G56" s="2">
+      <c r="G56" s="1">
         <v>2</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>155</v>
+        <v>64</v>
       </c>
       <c r="I56" s="5" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="J56" s="5" t="s">
-        <v>87</v>
+        <v>40</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="57" customHeight="1" spans="3:11">
-      <c r="C57" s="1">
-        <v>110</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="E57" s="1">
-        <v>1</v>
-      </c>
-      <c r="F57" s="2">
-        <v>0</v>
-      </c>
-      <c r="G57" s="2">
-        <v>2</v>
-      </c>
-      <c r="H57" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="I57" s="5" t="s">
         <v>159</v>
-      </c>
-      <c r="J57" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="K57" s="1" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:11">
       <c r="C58" s="1">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D58" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E58" s="1">
+        <v>1</v>
+      </c>
+      <c r="F58" s="2">
+        <v>0</v>
+      </c>
+      <c r="G58" s="2">
+        <v>2</v>
+      </c>
+      <c r="H58" s="5" t="s">
         <v>161</v>
-      </c>
-      <c r="E58" s="1">
-        <v>1</v>
-      </c>
-      <c r="F58" s="2">
-        <v>0</v>
-      </c>
-      <c r="G58" s="2">
-        <v>2</v>
-      </c>
-      <c r="H58" s="5" t="s">
-        <v>155</v>
       </c>
       <c r="I58" s="5" t="s">
         <v>162</v>
@@ -3197,7 +3215,7 @@
     </row>
     <row r="59" customHeight="1" spans="3:11">
       <c r="C59" s="1">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>164</v>
@@ -3212,7 +3230,7 @@
         <v>2</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="I59" s="5" t="s">
         <v>165</v>
@@ -3226,7 +3244,7 @@
     </row>
     <row r="60" customHeight="1" spans="3:11">
       <c r="C60" s="1">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>167</v>
@@ -3241,7 +3259,7 @@
         <v>2</v>
       </c>
       <c r="H60" s="5" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="I60" s="5" t="s">
         <v>168</v>
@@ -3255,7 +3273,7 @@
     </row>
     <row r="61" customHeight="1" spans="3:11">
       <c r="C61" s="1">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>170</v>
@@ -3270,53 +3288,82 @@
         <v>2</v>
       </c>
       <c r="H61" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="I61" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="I61" s="5" t="s">
+      <c r="J61" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K61" s="1" t="s">
         <v>172</v>
-      </c>
-      <c r="J61" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="K61" s="1" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="3:11">
       <c r="C62" s="1">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D62" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="E62" s="1">
+        <v>1</v>
+      </c>
+      <c r="F62" s="2">
+        <v>0</v>
+      </c>
+      <c r="G62" s="2">
+        <v>2</v>
+      </c>
+      <c r="H62" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="I62" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="E62" s="1">
-        <v>1</v>
-      </c>
-      <c r="F62" s="2">
-        <v>0</v>
-      </c>
-      <c r="G62" s="2">
-        <v>2</v>
-      </c>
-      <c r="H62" s="5" t="s">
+      <c r="J62" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K62" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="I62" s="5" t="s">
+    </row>
+    <row r="63" customHeight="1" spans="3:11">
+      <c r="C63" s="1">
+        <v>114</v>
+      </c>
+      <c r="D63" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="J62" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="K62" s="1" t="s">
-        <v>174</v>
+      <c r="E63" s="1">
+        <v>1</v>
+      </c>
+      <c r="F63" s="2">
+        <v>0</v>
+      </c>
+      <c r="G63" s="2">
+        <v>2</v>
+      </c>
+      <c r="H63" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="I63" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="J63" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="K63" s="1" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:11">
       <c r="C64" s="1">
-        <v>121</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>177</v>
+        <v>115</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>180</v>
       </c>
       <c r="E64" s="1">
         <v>1</v>
@@ -3328,53 +3375,24 @@
         <v>2</v>
       </c>
       <c r="H64" s="5" t="s">
-        <v>155</v>
+        <v>181</v>
       </c>
       <c r="I64" s="5" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="J64" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="K64" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="65" customHeight="1" spans="3:11">
-      <c r="C65" s="1">
-        <v>122</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="E65" s="1">
-        <v>1</v>
-      </c>
-      <c r="F65" s="2">
-        <v>0</v>
-      </c>
-      <c r="G65" s="2">
-        <v>2</v>
-      </c>
-      <c r="H65" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="I65" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K64" s="1" t="s">
         <v>180</v>
-      </c>
-      <c r="J65" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="K65" s="2" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="3:11">
       <c r="C66" s="1">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E66" s="1">
         <v>1</v>
@@ -3386,24 +3404,24 @@
         <v>2</v>
       </c>
       <c r="H66" s="5" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="I66" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="J66" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:11">
       <c r="C67" s="1">
-        <v>124</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>183</v>
+        <v>122</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>185</v>
       </c>
       <c r="E67" s="1">
         <v>1</v>
@@ -3415,24 +3433,24 @@
         <v>2</v>
       </c>
       <c r="H67" s="5" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="I67" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="J67" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="K67" s="1" t="s">
-        <v>183</v>
+      <c r="K67" s="2" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:11">
       <c r="C68" s="1">
-        <v>125</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>185</v>
+        <v>123</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>187</v>
       </c>
       <c r="E68" s="1">
         <v>1</v>
@@ -3444,24 +3462,53 @@
         <v>2</v>
       </c>
       <c r="H68" s="5" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="I68" s="5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="J68" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="K68" s="1" t="s">
-        <v>185</v>
+      <c r="K68" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="69" customHeight="1" spans="3:11">
+      <c r="C69" s="1">
+        <v>124</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="E69" s="1">
+        <v>1</v>
+      </c>
+      <c r="F69" s="2">
+        <v>0</v>
+      </c>
+      <c r="G69" s="2">
+        <v>2</v>
+      </c>
+      <c r="H69" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="I69" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="J69" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K69" s="1" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:11">
       <c r="C70" s="1">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="E70" s="1">
         <v>1</v>
@@ -3473,24 +3520,24 @@
         <v>2</v>
       </c>
       <c r="H70" s="5" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="I70" s="5" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="J70" s="5" t="s">
-        <v>40</v>
+        <v>87</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:11">
       <c r="C72" s="1">
-        <v>201</v>
+        <v>127</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="E72" s="1">
         <v>1</v>
@@ -3502,65 +3549,36 @@
         <v>2</v>
       </c>
       <c r="H72" s="5" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="I72" s="5" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="J72" s="5" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="73" customHeight="1" spans="3:11">
-      <c r="C73" s="1">
-        <v>202</v>
-      </c>
-      <c r="D73" s="1" t="s">
         <v>193</v>
-      </c>
-      <c r="E73" s="1">
-        <v>1</v>
-      </c>
-      <c r="F73" s="2">
-        <v>0</v>
-      </c>
-      <c r="G73" s="2">
-        <v>2</v>
-      </c>
-      <c r="H73" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="I73" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="J73" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K73" s="1" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:11">
       <c r="C74" s="1">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D74" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="E74" s="1">
+        <v>1</v>
+      </c>
+      <c r="F74" s="2">
+        <v>0</v>
+      </c>
+      <c r="G74" s="2">
+        <v>2</v>
+      </c>
+      <c r="H74" s="5" t="s">
         <v>196</v>
-      </c>
-      <c r="E74" s="1">
-        <v>1</v>
-      </c>
-      <c r="F74" s="2">
-        <v>0</v>
-      </c>
-      <c r="G74" s="2">
-        <v>2</v>
-      </c>
-      <c r="H74" s="5" t="s">
-        <v>190</v>
       </c>
       <c r="I74" s="5" t="s">
         <v>197</v>
@@ -3574,7 +3592,7 @@
     </row>
     <row r="75" customHeight="1" spans="3:11">
       <c r="C75" s="1">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>199</v>
@@ -3589,7 +3607,7 @@
         <v>2</v>
       </c>
       <c r="H75" s="5" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="I75" s="5" t="s">
         <v>200</v>
@@ -3603,7 +3621,7 @@
     </row>
     <row r="76" customHeight="1" spans="3:11">
       <c r="C76" s="1">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>202</v>
@@ -3618,7 +3636,7 @@
         <v>2</v>
       </c>
       <c r="H76" s="5" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="I76" s="5" t="s">
         <v>203</v>
@@ -3632,7 +3650,7 @@
     </row>
     <row r="77" customHeight="1" spans="3:11">
       <c r="C77" s="1">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>205</v>
@@ -3647,7 +3665,7 @@
         <v>2</v>
       </c>
       <c r="H77" s="5" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="I77" s="5" t="s">
         <v>206</v>
@@ -3661,7 +3679,7 @@
     </row>
     <row r="78" customHeight="1" spans="3:11">
       <c r="C78" s="1">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>208</v>
@@ -3676,65 +3694,123 @@
         <v>2</v>
       </c>
       <c r="H78" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="I78" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="I78" s="5" t="s">
+      <c r="J78" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K78" s="1" t="s">
         <v>210</v>
-      </c>
-      <c r="J78" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="K78" s="1" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="3:11">
       <c r="C79" s="1">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D79" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E79" s="1">
+        <v>1</v>
+      </c>
+      <c r="F79" s="2">
+        <v>0</v>
+      </c>
+      <c r="G79" s="2">
+        <v>2</v>
+      </c>
+      <c r="H79" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="I79" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="J79" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K79" s="1" t="s">
         <v>213</v>
-      </c>
-      <c r="E79" s="1">
-        <v>1</v>
-      </c>
-      <c r="F79" s="2">
-        <v>0</v>
-      </c>
-      <c r="G79" s="2">
-        <v>2</v>
-      </c>
-      <c r="K79" s="1" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="3:11">
       <c r="C80" s="1">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D80" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="E80" s="1">
+        <v>1</v>
+      </c>
+      <c r="F80" s="2">
+        <v>0</v>
+      </c>
+      <c r="G80" s="2">
+        <v>2</v>
+      </c>
+      <c r="H80" s="5" t="s">
         <v>215</v>
-      </c>
-      <c r="E80" s="1">
-        <v>1</v>
-      </c>
-      <c r="F80" s="2">
-        <v>0</v>
-      </c>
-      <c r="G80" s="2">
-        <v>2</v>
-      </c>
-      <c r="H80" s="5" t="s">
-        <v>209</v>
       </c>
       <c r="I80" s="5" t="s">
         <v>216</v>
       </c>
       <c r="J80" s="5" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="K80" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="81" customHeight="1" spans="3:11">
+      <c r="C81" s="1">
+        <v>208</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="E81" s="1">
+        <v>1</v>
+      </c>
+      <c r="F81" s="2">
+        <v>0</v>
+      </c>
+      <c r="G81" s="2">
+        <v>2</v>
+      </c>
+      <c r="K81" s="1" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="82" customHeight="1" spans="3:11">
+      <c r="C82" s="1">
+        <v>209</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="E82" s="1">
+        <v>1</v>
+      </c>
+      <c r="F82" s="2">
+        <v>0</v>
+      </c>
+      <c r="G82" s="2">
+        <v>2</v>
+      </c>
+      <c r="H82" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="I82" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="J82" s="5" t="s">
         <v>217</v>
+      </c>
+      <c r="K82" s="1" t="s">
+        <v>223</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="234">
   <si>
     <t>_id</t>
   </si>
@@ -578,6 +578,24 @@
     <t>109,110,111,112,113,114</t>
   </si>
   <si>
+    <t>战士暗金</t>
+  </si>
+  <si>
+    <t>151,152,153,154,155,156,157,158</t>
+  </si>
+  <si>
+    <t>法师暗金</t>
+  </si>
+  <si>
+    <t>161,162,163,164,165,166,167,168</t>
+  </si>
+  <si>
+    <t>道士暗金</t>
+  </si>
+  <si>
+    <t>171,172,173,174,175,176,177,178</t>
+  </si>
+  <si>
     <t>战士平衡金装</t>
   </si>
   <si>
@@ -612,6 +630,18 @@
   </si>
   <si>
     <t>121,122,123,124,125</t>
+  </si>
+  <si>
+    <t>暗金自选</t>
+  </si>
+  <si>
+    <t>4,4,4</t>
+  </si>
+  <si>
+    <t>118,119,120</t>
+  </si>
+  <si>
+    <t>1,1,1,</t>
   </si>
   <si>
     <t>40橙宠自选</t>
@@ -1660,7 +1690,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:K82"/>
+  <dimension ref="A3:K95"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -3389,7 +3419,7 @@
     </row>
     <row r="66" customHeight="1" spans="3:11">
       <c r="C66" s="1">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>183</v>
@@ -3418,7 +3448,7 @@
     </row>
     <row r="67" customHeight="1" spans="3:11">
       <c r="C67" s="1">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>185</v>
@@ -3447,7 +3477,7 @@
     </row>
     <row r="68" customHeight="1" spans="3:11">
       <c r="C68" s="1">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>187</v>
@@ -3476,9 +3506,9 @@
     </row>
     <row r="69" customHeight="1" spans="3:11">
       <c r="C69" s="1">
-        <v>124</v>
-      </c>
-      <c r="D69" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="D69" s="2" t="s">
         <v>189</v>
       </c>
       <c r="E69" s="1">
@@ -3499,15 +3529,15 @@
       <c r="J69" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="K69" s="1" t="s">
+      <c r="K69" s="2" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:11">
       <c r="C70" s="1">
-        <v>125</v>
-      </c>
-      <c r="D70" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D70" s="2" t="s">
         <v>191</v>
       </c>
       <c r="E70" s="1">
@@ -3528,16 +3558,45 @@
       <c r="J70" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="K70" s="1" t="s">
+      <c r="K70" s="2" t="s">
         <v>191</v>
+      </c>
+    </row>
+    <row r="71" customHeight="1" spans="3:11">
+      <c r="C71" s="1">
+        <v>123</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="E71" s="1">
+        <v>1</v>
+      </c>
+      <c r="F71" s="2">
+        <v>0</v>
+      </c>
+      <c r="G71" s="2">
+        <v>2</v>
+      </c>
+      <c r="H71" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="I71" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="J71" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K71" s="2" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:11">
       <c r="C72" s="1">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E72" s="1">
         <v>1</v>
@@ -3549,50 +3608,50 @@
         <v>2</v>
       </c>
       <c r="H72" s="5" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="I72" s="5" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="J72" s="5" t="s">
-        <v>40</v>
+        <v>87</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="74" customHeight="1" spans="3:11">
-      <c r="C74" s="1">
-        <v>201</v>
-      </c>
-      <c r="D74" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="E74" s="1">
-        <v>1</v>
-      </c>
-      <c r="F74" s="2">
-        <v>0</v>
-      </c>
-      <c r="G74" s="2">
-        <v>2</v>
-      </c>
-      <c r="H74" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="I74" s="5" t="s">
+    </row>
+    <row r="73" customHeight="1" spans="3:11">
+      <c r="C73" s="1">
+        <v>125</v>
+      </c>
+      <c r="D73" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="J74" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K74" s="1" t="s">
+      <c r="E73" s="1">
+        <v>1</v>
+      </c>
+      <c r="F73" s="2">
+        <v>0</v>
+      </c>
+      <c r="G73" s="2">
+        <v>2</v>
+      </c>
+      <c r="H73" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="I73" s="5" t="s">
         <v>198</v>
+      </c>
+      <c r="J73" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K73" s="1" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:11">
       <c r="C75" s="1">
-        <v>202</v>
+        <v>127</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>199</v>
@@ -3607,210 +3666,297 @@
         <v>2</v>
       </c>
       <c r="H75" s="5" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="I75" s="5" t="s">
         <v>200</v>
       </c>
       <c r="J75" s="5" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="K75" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:11">
       <c r="C76" s="1">
-        <v>203</v>
+        <v>128</v>
       </c>
       <c r="D76" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="E76" s="1">
+        <v>1</v>
+      </c>
+      <c r="F76" s="2">
+        <v>0</v>
+      </c>
+      <c r="G76" s="2">
+        <v>2</v>
+      </c>
+      <c r="H76" s="5" t="s">
         <v>202</v>
-      </c>
-      <c r="E76" s="1">
-        <v>1</v>
-      </c>
-      <c r="F76" s="2">
-        <v>0</v>
-      </c>
-      <c r="G76" s="2">
-        <v>2</v>
-      </c>
-      <c r="H76" s="5" t="s">
-        <v>196</v>
       </c>
       <c r="I76" s="5" t="s">
         <v>203</v>
       </c>
       <c r="J76" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="K76" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="87" customHeight="1" spans="3:11">
+      <c r="C87" s="1">
+        <v>201</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="E87" s="1">
+        <v>1</v>
+      </c>
+      <c r="F87" s="2">
+        <v>0</v>
+      </c>
+      <c r="G87" s="2">
+        <v>2</v>
+      </c>
+      <c r="H87" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="I87" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="J87" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="K76" s="1" t="s">
+      <c r="K87" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="88" customHeight="1" spans="3:11">
+      <c r="C88" s="1">
+        <v>202</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="E88" s="1">
+        <v>1</v>
+      </c>
+      <c r="F88" s="2">
+        <v>0</v>
+      </c>
+      <c r="G88" s="2">
+        <v>2</v>
+      </c>
+      <c r="H88" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="I88" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="J88" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K88" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="89" customHeight="1" spans="3:11">
+      <c r="C89" s="1">
+        <v>203</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="E89" s="1">
+        <v>1</v>
+      </c>
+      <c r="F89" s="2">
+        <v>0</v>
+      </c>
+      <c r="G89" s="2">
+        <v>2</v>
+      </c>
+      <c r="H89" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="I89" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J89" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K89" s="1" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="90" customHeight="1" spans="3:11">
+      <c r="C90" s="1">
         <v>204</v>
       </c>
-    </row>
-    <row r="77" customHeight="1" spans="3:11">
-      <c r="C77" s="1">
-        <v>204</v>
-      </c>
-      <c r="D77" s="1" t="s">
+      <c r="D90" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E90" s="1">
+        <v>1</v>
+      </c>
+      <c r="F90" s="2">
+        <v>0</v>
+      </c>
+      <c r="G90" s="2">
+        <v>2</v>
+      </c>
+      <c r="H90" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="I90" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="J90" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K90" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="91" customHeight="1" spans="3:11">
+      <c r="C91" s="1">
         <v>205</v>
       </c>
-      <c r="E77" s="1">
-        <v>1</v>
-      </c>
-      <c r="F77" s="2">
-        <v>0</v>
-      </c>
-      <c r="G77" s="2">
-        <v>2</v>
-      </c>
-      <c r="H77" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="I77" s="5" t="s">
+      <c r="D91" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="E91" s="1">
+        <v>1</v>
+      </c>
+      <c r="F91" s="2">
+        <v>0</v>
+      </c>
+      <c r="G91" s="2">
+        <v>2</v>
+      </c>
+      <c r="H91" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="J77" s="5" t="s">
+      <c r="I91" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="J91" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="K77" s="1" t="s">
+      <c r="K91" s="1" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="92" customHeight="1" spans="3:11">
+      <c r="C92" s="1">
+        <v>206</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="E92" s="1">
+        <v>1</v>
+      </c>
+      <c r="F92" s="2">
+        <v>0</v>
+      </c>
+      <c r="G92" s="2">
+        <v>2</v>
+      </c>
+      <c r="H92" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="I92" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="J92" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K92" s="1" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="93" customHeight="1" spans="3:11">
+      <c r="C93" s="1">
         <v>207</v>
       </c>
-    </row>
-    <row r="78" customHeight="1" spans="3:11">
-      <c r="C78" s="1">
-        <v>205</v>
-      </c>
-      <c r="D78" s="1" t="s">
+      <c r="D93" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="E93" s="1">
+        <v>1</v>
+      </c>
+      <c r="F93" s="2">
+        <v>0</v>
+      </c>
+      <c r="G93" s="2">
+        <v>2</v>
+      </c>
+      <c r="H93" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="I93" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="J93" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="K93" s="1" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="94" customHeight="1" spans="3:11">
+      <c r="C94" s="1">
         <v>208</v>
       </c>
-      <c r="E78" s="1">
-        <v>1</v>
-      </c>
-      <c r="F78" s="2">
-        <v>0</v>
-      </c>
-      <c r="G78" s="2">
-        <v>2</v>
-      </c>
-      <c r="H78" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="I78" s="5" t="s">
+      <c r="D94" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E94" s="1">
+        <v>1</v>
+      </c>
+      <c r="F94" s="2">
+        <v>0</v>
+      </c>
+      <c r="G94" s="2">
+        <v>2</v>
+      </c>
+      <c r="K94" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="95" customHeight="1" spans="3:11">
+      <c r="C95" s="1">
         <v>209</v>
       </c>
-      <c r="J78" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K78" s="1" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="79" customHeight="1" spans="3:11">
-      <c r="C79" s="1">
-        <v>206</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="E79" s="1">
-        <v>1</v>
-      </c>
-      <c r="F79" s="2">
-        <v>0</v>
-      </c>
-      <c r="G79" s="2">
-        <v>2</v>
-      </c>
-      <c r="H79" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="I79" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="J79" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K79" s="1" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="80" customHeight="1" spans="3:11">
-      <c r="C80" s="1">
-        <v>207</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="E80" s="1">
-        <v>1</v>
-      </c>
-      <c r="F80" s="2">
-        <v>0</v>
-      </c>
-      <c r="G80" s="2">
-        <v>2</v>
-      </c>
-      <c r="H80" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="I80" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="J80" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="K80" s="1" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="81" customHeight="1" spans="3:11">
-      <c r="C81" s="1">
-        <v>208</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="E81" s="1">
-        <v>1</v>
-      </c>
-      <c r="F81" s="2">
-        <v>0</v>
-      </c>
-      <c r="G81" s="2">
-        <v>2</v>
-      </c>
-      <c r="K81" s="1" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="82" customHeight="1" spans="3:11">
-      <c r="C82" s="1">
-        <v>209</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="E82" s="1">
-        <v>1</v>
-      </c>
-      <c r="F82" s="2">
-        <v>0</v>
-      </c>
-      <c r="G82" s="2">
-        <v>2</v>
-      </c>
-      <c r="H82" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="I82" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="J82" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="K82" s="1" t="s">
-        <v>223</v>
+      <c r="D95" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="E95" s="1">
+        <v>1</v>
+      </c>
+      <c r="F95" s="2">
+        <v>0</v>
+      </c>
+      <c r="G95" s="2">
+        <v>2</v>
+      </c>
+      <c r="H95" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="I95" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="J95" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="K95" s="1" t="s">
+        <v>233</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -347,7 +347,7 @@
     <t>18,18,18</t>
   </si>
   <si>
-    <t>180032,180033,180034</t>
+    <t>180032,180034,180035,180036,180038,180039</t>
   </si>
   <si>
     <t>普通金宠包</t>
@@ -2684,7 +2684,7 @@
         <v>106</v>
       </c>
       <c r="J36" s="5" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="K36" s="1" t="s">
         <v>104</v>

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -173,7 +173,7 @@
     <t>幽冥时装一套</t>
   </si>
   <si>
-    <t>专属自选包7</t>
+    <t>冰咆哮专属</t>
   </si>
   <si>
     <t>701,702,703,704,705,706</t>
@@ -401,58 +401,58 @@
     <t>1,1,1,1,1,1,1,1,1,1,1,1,1</t>
   </si>
   <si>
-    <t>驱魔符距离4件套</t>
+    <t>驱魔6件套</t>
+  </si>
+  <si>
+    <t>12,12,12,12,12,12,5,5</t>
+  </si>
+  <si>
+    <t>36,37,38,39,40,41,4005,4010</t>
+  </si>
+  <si>
+    <t>1,1,1,1,1,1,300,60</t>
+  </si>
+  <si>
+    <t>盾专属自选套</t>
+  </si>
+  <si>
+    <t>4,4,4,4</t>
+  </si>
+  <si>
+    <t>99,102,104</t>
+  </si>
+  <si>
+    <t>专属自选</t>
+  </si>
+  <si>
+    <t>4,4,4,4,4,4,4,4,4</t>
+  </si>
+  <si>
+    <t>99,100,101,102,103,104,105,96</t>
+  </si>
+  <si>
+    <t>法力盾4件套</t>
   </si>
   <si>
     <t>12,12,12,12,5,5</t>
   </si>
   <si>
-    <t>36,37,38,39,4005,4010</t>
+    <t>26,27,28,29,4005,4010</t>
   </si>
   <si>
     <t>1,1,1,1,300,60</t>
   </si>
   <si>
-    <t>盾专属自选套</t>
-  </si>
-  <si>
-    <t>4,4,4,4</t>
-  </si>
-  <si>
-    <t>99,102,104</t>
-  </si>
-  <si>
-    <t>专属自选</t>
-  </si>
-  <si>
-    <t>4,4,4,4,4,4,4,4,4</t>
-  </si>
-  <si>
-    <t>99,100,101,102,103,104,105,96</t>
-  </si>
-  <si>
-    <t>法力盾4件套</t>
-  </si>
-  <si>
-    <t>26,27,28,29,4005,4010</t>
-  </si>
-  <si>
     <t>神雷6件套</t>
   </si>
   <si>
-    <t>12,12,12,12,12,12,5,5</t>
-  </si>
-  <si>
     <t>30,31,32,33,34,35,4005,4010</t>
   </si>
   <si>
-    <t>1,1,1,1,1,1,300,60</t>
-  </si>
-  <si>
-    <t>刺杀吸血4件套</t>
-  </si>
-  <si>
-    <t>7,8,9,10,4005,4010</t>
+    <t>流光6件套</t>
+  </si>
+  <si>
+    <t>5,6,7,8,9,10,4005,4010</t>
   </si>
   <si>
     <t>武神盾4件套</t>
@@ -2941,13 +2941,13 @@
         <v>2</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="I46" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J46" s="5" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="K46" s="1" t="s">
         <v>134</v>
@@ -2958,7 +2958,7 @@
         <v>100</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E47" s="1">
         <v>0</v>
@@ -2970,16 +2970,16 @@
         <v>2</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="I47" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="J47" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="K47" s="1" t="s">
         <v>138</v>
-      </c>
-      <c r="J47" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="K47" s="1" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:11">
@@ -3028,13 +3028,13 @@
         <v>2</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="I49" s="5" t="s">
         <v>143</v>
       </c>
       <c r="J49" s="5" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="K49" s="1" t="s">
         <v>142</v>
@@ -3057,13 +3057,13 @@
         <v>2</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="I50" s="5" t="s">
         <v>145</v>
       </c>
       <c r="J50" s="5" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="K50" s="1" t="s">
         <v>144</v>
@@ -3086,13 +3086,13 @@
         <v>2</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="I51" s="5" t="s">
         <v>147</v>
       </c>
       <c r="J51" s="5" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="K51" s="1" t="s">
         <v>146</v>
@@ -3115,13 +3115,13 @@
         <v>2</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="I52" s="5" t="s">
         <v>149</v>
       </c>
       <c r="J52" s="5" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="K52" s="1" t="s">
         <v>148</v>

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="233">
   <si>
     <t>_id</t>
   </si>
@@ -342,9 +342,6 @@
   </si>
   <si>
     <t>极法宝自选</t>
-  </si>
-  <si>
-    <t>18,18,18</t>
   </si>
   <si>
     <t>180032,180034,180035,180036,180038,180039</t>
@@ -2678,10 +2675,10 @@
         <v>2</v>
       </c>
       <c r="H36" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="I36" s="5" t="s">
         <v>105</v>
-      </c>
-      <c r="I36" s="5" t="s">
-        <v>106</v>
       </c>
       <c r="J36" s="5" t="s">
         <v>40</v>
@@ -2695,28 +2692,28 @@
         <v>32</v>
       </c>
       <c r="D37" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E37" s="1">
+        <v>0</v>
+      </c>
+      <c r="F37" s="2">
+        <v>0</v>
+      </c>
+      <c r="G37" s="1">
+        <v>2</v>
+      </c>
+      <c r="H37" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="E37" s="1">
-        <v>0</v>
-      </c>
-      <c r="F37" s="2">
-        <v>0</v>
-      </c>
-      <c r="G37" s="1">
-        <v>2</v>
-      </c>
-      <c r="H37" s="5" t="s">
+      <c r="I37" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="I37" s="5" t="s">
+      <c r="J37" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="J37" s="5" t="s">
+      <c r="K37" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="K37" s="1" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:11">
@@ -2724,28 +2721,28 @@
         <v>33</v>
       </c>
       <c r="D38" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E38" s="1">
+        <v>0</v>
+      </c>
+      <c r="F38" s="2">
+        <v>0</v>
+      </c>
+      <c r="G38" s="1">
+        <v>2</v>
+      </c>
+      <c r="H38" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="I38" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="E38" s="1">
-        <v>0</v>
-      </c>
-      <c r="F38" s="2">
-        <v>0</v>
-      </c>
-      <c r="G38" s="1">
-        <v>2</v>
-      </c>
-      <c r="H38" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="I38" s="5" t="s">
+      <c r="J38" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="J38" s="5" t="s">
+      <c r="K38" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="K38" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="39" customFormat="1" customHeight="1" spans="1:11">
@@ -2755,7 +2752,7 @@
         <v>34</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E39" s="1">
         <v>1</v>
@@ -2770,13 +2767,13 @@
         <v>64</v>
       </c>
       <c r="I39" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J39" s="5" t="s">
         <v>40</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:11">
@@ -2784,7 +2781,7 @@
         <v>35</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E40" s="1">
         <v>1</v>
@@ -2799,13 +2796,13 @@
         <v>89</v>
       </c>
       <c r="I40" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J40" s="5" t="s">
         <v>82</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:11">
@@ -2813,28 +2810,28 @@
         <v>36</v>
       </c>
       <c r="D41" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E41" s="1">
+        <v>1</v>
+      </c>
+      <c r="F41" s="2">
+        <v>0</v>
+      </c>
+      <c r="G41" s="2">
+        <v>1</v>
+      </c>
+      <c r="H41" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="E41" s="1">
-        <v>1</v>
-      </c>
-      <c r="F41" s="2">
-        <v>0</v>
-      </c>
-      <c r="G41" s="2">
-        <v>1</v>
-      </c>
-      <c r="H41" s="5" t="s">
+      <c r="I41" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="I41" s="5" t="s">
+      <c r="J41" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="J41" s="5" t="s">
-        <v>123</v>
-      </c>
       <c r="K41" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:11">
@@ -2842,28 +2839,28 @@
         <v>96</v>
       </c>
       <c r="D43" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E43" s="1">
+        <v>0</v>
+      </c>
+      <c r="F43" s="2">
+        <v>0</v>
+      </c>
+      <c r="G43" s="1">
+        <v>2</v>
+      </c>
+      <c r="H43" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="E43" s="1">
-        <v>0</v>
-      </c>
-      <c r="F43" s="2">
-        <v>0</v>
-      </c>
-      <c r="G43" s="1">
-        <v>2</v>
-      </c>
-      <c r="H43" s="5" t="s">
+      <c r="I43" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="I43" s="5" t="s">
+      <c r="J43" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="J43" s="5" t="s">
-        <v>127</v>
-      </c>
       <c r="K43" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:11">
@@ -2871,28 +2868,28 @@
         <v>97</v>
       </c>
       <c r="D44" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E44" s="1">
+        <v>1</v>
+      </c>
+      <c r="F44" s="2">
+        <v>0</v>
+      </c>
+      <c r="G44" s="1">
+        <v>2</v>
+      </c>
+      <c r="H44" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="E44" s="1">
-        <v>1</v>
-      </c>
-      <c r="F44" s="2">
-        <v>0</v>
-      </c>
-      <c r="G44" s="1">
-        <v>2</v>
-      </c>
-      <c r="H44" s="5" t="s">
+      <c r="I44" s="5" t="s">
         <v>129</v>
-      </c>
-      <c r="I44" s="5" t="s">
-        <v>130</v>
       </c>
       <c r="J44" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:11">
@@ -2900,28 +2897,28 @@
         <v>98</v>
       </c>
       <c r="D45" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E45" s="1">
+        <v>1</v>
+      </c>
+      <c r="F45" s="2">
+        <v>0</v>
+      </c>
+      <c r="G45" s="1">
+        <v>2</v>
+      </c>
+      <c r="H45" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="E45" s="1">
-        <v>1</v>
-      </c>
-      <c r="F45" s="2">
-        <v>0</v>
-      </c>
-      <c r="G45" s="1">
-        <v>2</v>
-      </c>
-      <c r="H45" s="5" t="s">
+      <c r="I45" s="5" t="s">
         <v>132</v>
-      </c>
-      <c r="I45" s="5" t="s">
-        <v>133</v>
       </c>
       <c r="J45" s="5" t="s">
         <v>82</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="3:11">
@@ -2929,28 +2926,28 @@
         <v>99</v>
       </c>
       <c r="D46" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E46" s="1">
+        <v>0</v>
+      </c>
+      <c r="F46" s="2">
+        <v>0</v>
+      </c>
+      <c r="G46" s="1">
+        <v>2</v>
+      </c>
+      <c r="H46" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="E46" s="1">
-        <v>0</v>
-      </c>
-      <c r="F46" s="2">
-        <v>0</v>
-      </c>
-      <c r="G46" s="1">
-        <v>2</v>
-      </c>
-      <c r="H46" s="5" t="s">
+      <c r="I46" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="I46" s="5" t="s">
+      <c r="J46" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="J46" s="5" t="s">
-        <v>137</v>
-      </c>
       <c r="K46" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:11">
@@ -2958,28 +2955,28 @@
         <v>100</v>
       </c>
       <c r="D47" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E47" s="1">
+        <v>0</v>
+      </c>
+      <c r="F47" s="2">
+        <v>0</v>
+      </c>
+      <c r="G47" s="1">
+        <v>2</v>
+      </c>
+      <c r="H47" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="I47" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="E47" s="1">
-        <v>0</v>
-      </c>
-      <c r="F47" s="2">
-        <v>0</v>
-      </c>
-      <c r="G47" s="1">
-        <v>2</v>
-      </c>
-      <c r="H47" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="I47" s="5" t="s">
-        <v>139</v>
-      </c>
       <c r="J47" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:11">
@@ -2987,28 +2984,28 @@
         <v>101</v>
       </c>
       <c r="D48" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E48" s="1">
+        <v>0</v>
+      </c>
+      <c r="F48" s="2">
+        <v>0</v>
+      </c>
+      <c r="G48" s="1">
+        <v>2</v>
+      </c>
+      <c r="H48" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="I48" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="E48" s="1">
-        <v>0</v>
-      </c>
-      <c r="F48" s="2">
-        <v>0</v>
-      </c>
-      <c r="G48" s="1">
-        <v>2</v>
-      </c>
-      <c r="H48" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="I48" s="5" t="s">
-        <v>141</v>
-      </c>
       <c r="J48" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="3:11">
@@ -3016,28 +3013,28 @@
         <v>102</v>
       </c>
       <c r="D49" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E49" s="1">
+        <v>0</v>
+      </c>
+      <c r="F49" s="2">
+        <v>0</v>
+      </c>
+      <c r="G49" s="1">
+        <v>2</v>
+      </c>
+      <c r="H49" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="I49" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="E49" s="1">
-        <v>0</v>
-      </c>
-      <c r="F49" s="2">
-        <v>0</v>
-      </c>
-      <c r="G49" s="1">
-        <v>2</v>
-      </c>
-      <c r="H49" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="I49" s="5" t="s">
-        <v>143</v>
-      </c>
       <c r="J49" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="3:11">
@@ -3045,28 +3042,28 @@
         <v>103</v>
       </c>
       <c r="D50" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E50" s="1">
+        <v>0</v>
+      </c>
+      <c r="F50" s="2">
+        <v>0</v>
+      </c>
+      <c r="G50" s="1">
+        <v>2</v>
+      </c>
+      <c r="H50" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="I50" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="E50" s="1">
-        <v>0</v>
-      </c>
-      <c r="F50" s="2">
-        <v>0</v>
-      </c>
-      <c r="G50" s="1">
-        <v>2</v>
-      </c>
-      <c r="H50" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="I50" s="5" t="s">
-        <v>145</v>
-      </c>
       <c r="J50" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="3:11">
@@ -3074,28 +3071,28 @@
         <v>104</v>
       </c>
       <c r="D51" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E51" s="1">
+        <v>0</v>
+      </c>
+      <c r="F51" s="2">
+        <v>0</v>
+      </c>
+      <c r="G51" s="1">
+        <v>2</v>
+      </c>
+      <c r="H51" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="I51" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="E51" s="1">
-        <v>0</v>
-      </c>
-      <c r="F51" s="2">
-        <v>0</v>
-      </c>
-      <c r="G51" s="1">
-        <v>2</v>
-      </c>
-      <c r="H51" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="I51" s="5" t="s">
-        <v>147</v>
-      </c>
       <c r="J51" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="3:11">
@@ -3103,28 +3100,28 @@
         <v>105</v>
       </c>
       <c r="D52" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="E52" s="1">
+        <v>0</v>
+      </c>
+      <c r="F52" s="2">
+        <v>0</v>
+      </c>
+      <c r="G52" s="1">
+        <v>2</v>
+      </c>
+      <c r="H52" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="I52" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="E52" s="1">
-        <v>0</v>
-      </c>
-      <c r="F52" s="2">
-        <v>0</v>
-      </c>
-      <c r="G52" s="1">
-        <v>2</v>
-      </c>
-      <c r="H52" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="I52" s="5" t="s">
-        <v>149</v>
-      </c>
       <c r="J52" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:11">
@@ -3132,28 +3129,28 @@
         <v>106</v>
       </c>
       <c r="D54" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E54" s="1">
+        <v>1</v>
+      </c>
+      <c r="F54" s="2">
+        <v>0</v>
+      </c>
+      <c r="G54" s="1">
+        <v>1</v>
+      </c>
+      <c r="H54" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="E54" s="1">
-        <v>1</v>
-      </c>
-      <c r="F54" s="2">
-        <v>0</v>
-      </c>
-      <c r="G54" s="1">
-        <v>1</v>
-      </c>
-      <c r="H54" s="5" t="s">
+      <c r="I54" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="I54" s="5" t="s">
+      <c r="J54" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="J54" s="5" t="s">
+      <c r="K54" s="1" t="s">
         <v>153</v>
-      </c>
-      <c r="K54" s="1" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:11">
@@ -3161,7 +3158,7 @@
         <v>107</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E55" s="1">
         <v>1</v>
@@ -3176,7 +3173,7 @@
         <v>64</v>
       </c>
       <c r="I55" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J55" s="5" t="s">
         <v>40</v>
@@ -3190,7 +3187,7 @@
         <v>108</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E56" s="1">
         <v>1</v>
@@ -3205,13 +3202,13 @@
         <v>64</v>
       </c>
       <c r="I56" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J56" s="5" t="s">
         <v>40</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:11">
@@ -3219,28 +3216,28 @@
         <v>109</v>
       </c>
       <c r="D58" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E58" s="1">
+        <v>1</v>
+      </c>
+      <c r="F58" s="2">
+        <v>0</v>
+      </c>
+      <c r="G58" s="2">
+        <v>2</v>
+      </c>
+      <c r="H58" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="E58" s="1">
-        <v>1</v>
-      </c>
-      <c r="F58" s="2">
-        <v>0</v>
-      </c>
-      <c r="G58" s="2">
-        <v>2</v>
-      </c>
-      <c r="H58" s="5" t="s">
+      <c r="I58" s="5" t="s">
         <v>161</v>
-      </c>
-      <c r="I58" s="5" t="s">
-        <v>162</v>
       </c>
       <c r="J58" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:11">
@@ -3248,28 +3245,28 @@
         <v>110</v>
       </c>
       <c r="D59" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E59" s="1">
+        <v>1</v>
+      </c>
+      <c r="F59" s="2">
+        <v>0</v>
+      </c>
+      <c r="G59" s="2">
+        <v>2</v>
+      </c>
+      <c r="H59" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="I59" s="5" t="s">
         <v>164</v>
-      </c>
-      <c r="E59" s="1">
-        <v>1</v>
-      </c>
-      <c r="F59" s="2">
-        <v>0</v>
-      </c>
-      <c r="G59" s="2">
-        <v>2</v>
-      </c>
-      <c r="H59" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="I59" s="5" t="s">
-        <v>165</v>
       </c>
       <c r="J59" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="3:11">
@@ -3277,28 +3274,28 @@
         <v>111</v>
       </c>
       <c r="D60" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E60" s="1">
+        <v>1</v>
+      </c>
+      <c r="F60" s="2">
+        <v>0</v>
+      </c>
+      <c r="G60" s="2">
+        <v>2</v>
+      </c>
+      <c r="H60" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="I60" s="5" t="s">
         <v>167</v>
-      </c>
-      <c r="E60" s="1">
-        <v>1</v>
-      </c>
-      <c r="F60" s="2">
-        <v>0</v>
-      </c>
-      <c r="G60" s="2">
-        <v>2</v>
-      </c>
-      <c r="H60" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="I60" s="5" t="s">
-        <v>168</v>
       </c>
       <c r="J60" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="3:11">
@@ -3306,28 +3303,28 @@
         <v>112</v>
       </c>
       <c r="D61" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="E61" s="1">
+        <v>1</v>
+      </c>
+      <c r="F61" s="2">
+        <v>0</v>
+      </c>
+      <c r="G61" s="2">
+        <v>2</v>
+      </c>
+      <c r="H61" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="I61" s="5" t="s">
         <v>170</v>
-      </c>
-      <c r="E61" s="1">
-        <v>1</v>
-      </c>
-      <c r="F61" s="2">
-        <v>0</v>
-      </c>
-      <c r="G61" s="2">
-        <v>2</v>
-      </c>
-      <c r="H61" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="I61" s="5" t="s">
-        <v>171</v>
       </c>
       <c r="J61" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="3:11">
@@ -3335,28 +3332,28 @@
         <v>113</v>
       </c>
       <c r="D62" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E62" s="1">
+        <v>1</v>
+      </c>
+      <c r="F62" s="2">
+        <v>0</v>
+      </c>
+      <c r="G62" s="2">
+        <v>2</v>
+      </c>
+      <c r="H62" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="I62" s="5" t="s">
         <v>173</v>
-      </c>
-      <c r="E62" s="1">
-        <v>1</v>
-      </c>
-      <c r="F62" s="2">
-        <v>0</v>
-      </c>
-      <c r="G62" s="2">
-        <v>2</v>
-      </c>
-      <c r="H62" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="I62" s="5" t="s">
-        <v>174</v>
       </c>
       <c r="J62" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="3:11">
@@ -3364,28 +3361,28 @@
         <v>114</v>
       </c>
       <c r="D63" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E63" s="1">
+        <v>1</v>
+      </c>
+      <c r="F63" s="2">
+        <v>0</v>
+      </c>
+      <c r="G63" s="2">
+        <v>2</v>
+      </c>
+      <c r="H63" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="E63" s="1">
-        <v>1</v>
-      </c>
-      <c r="F63" s="2">
-        <v>0</v>
-      </c>
-      <c r="G63" s="2">
-        <v>2</v>
-      </c>
-      <c r="H63" s="5" t="s">
+      <c r="I63" s="5" t="s">
         <v>177</v>
-      </c>
-      <c r="I63" s="5" t="s">
-        <v>178</v>
       </c>
       <c r="J63" s="5" t="s">
         <v>82</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:11">
@@ -3393,28 +3390,28 @@
         <v>115</v>
       </c>
       <c r="D64" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="E64" s="1">
+        <v>1</v>
+      </c>
+      <c r="F64" s="2">
+        <v>0</v>
+      </c>
+      <c r="G64" s="2">
+        <v>2</v>
+      </c>
+      <c r="H64" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="E64" s="1">
-        <v>1</v>
-      </c>
-      <c r="F64" s="2">
-        <v>0</v>
-      </c>
-      <c r="G64" s="2">
-        <v>2</v>
-      </c>
-      <c r="H64" s="5" t="s">
+      <c r="I64" s="5" t="s">
         <v>181</v>
-      </c>
-      <c r="I64" s="5" t="s">
-        <v>182</v>
       </c>
       <c r="J64" s="5" t="s">
         <v>40</v>
       </c>
       <c r="K64" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="3:11">
@@ -3422,28 +3419,28 @@
         <v>118</v>
       </c>
       <c r="D66" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="E66" s="1">
+        <v>1</v>
+      </c>
+      <c r="F66" s="2">
+        <v>0</v>
+      </c>
+      <c r="G66" s="2">
+        <v>2</v>
+      </c>
+      <c r="H66" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="I66" s="5" t="s">
         <v>183</v>
-      </c>
-      <c r="E66" s="1">
-        <v>1</v>
-      </c>
-      <c r="F66" s="2">
-        <v>0</v>
-      </c>
-      <c r="G66" s="2">
-        <v>2</v>
-      </c>
-      <c r="H66" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="I66" s="5" t="s">
-        <v>184</v>
       </c>
       <c r="J66" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:11">
@@ -3451,28 +3448,28 @@
         <v>119</v>
       </c>
       <c r="D67" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="E67" s="1">
+        <v>1</v>
+      </c>
+      <c r="F67" s="2">
+        <v>0</v>
+      </c>
+      <c r="G67" s="2">
+        <v>2</v>
+      </c>
+      <c r="H67" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="I67" s="5" t="s">
         <v>185</v>
-      </c>
-      <c r="E67" s="1">
-        <v>1</v>
-      </c>
-      <c r="F67" s="2">
-        <v>0</v>
-      </c>
-      <c r="G67" s="2">
-        <v>2</v>
-      </c>
-      <c r="H67" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="I67" s="5" t="s">
-        <v>186</v>
       </c>
       <c r="J67" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:11">
@@ -3480,28 +3477,28 @@
         <v>120</v>
       </c>
       <c r="D68" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="E68" s="1">
+        <v>1</v>
+      </c>
+      <c r="F68" s="2">
+        <v>0</v>
+      </c>
+      <c r="G68" s="2">
+        <v>2</v>
+      </c>
+      <c r="H68" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="I68" s="5" t="s">
         <v>187</v>
-      </c>
-      <c r="E68" s="1">
-        <v>1</v>
-      </c>
-      <c r="F68" s="2">
-        <v>0</v>
-      </c>
-      <c r="G68" s="2">
-        <v>2</v>
-      </c>
-      <c r="H68" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="I68" s="5" t="s">
-        <v>188</v>
       </c>
       <c r="J68" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:11">
@@ -3509,28 +3506,28 @@
         <v>121</v>
       </c>
       <c r="D69" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E69" s="1">
+        <v>1</v>
+      </c>
+      <c r="F69" s="2">
+        <v>0</v>
+      </c>
+      <c r="G69" s="2">
+        <v>2</v>
+      </c>
+      <c r="H69" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="I69" s="5" t="s">
         <v>189</v>
-      </c>
-      <c r="E69" s="1">
-        <v>1</v>
-      </c>
-      <c r="F69" s="2">
-        <v>0</v>
-      </c>
-      <c r="G69" s="2">
-        <v>2</v>
-      </c>
-      <c r="H69" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="I69" s="5" t="s">
-        <v>190</v>
       </c>
       <c r="J69" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:11">
@@ -3538,28 +3535,28 @@
         <v>122</v>
       </c>
       <c r="D70" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E70" s="1">
+        <v>1</v>
+      </c>
+      <c r="F70" s="2">
+        <v>0</v>
+      </c>
+      <c r="G70" s="2">
+        <v>2</v>
+      </c>
+      <c r="H70" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="I70" s="5" t="s">
         <v>191</v>
-      </c>
-      <c r="E70" s="1">
-        <v>1</v>
-      </c>
-      <c r="F70" s="2">
-        <v>0</v>
-      </c>
-      <c r="G70" s="2">
-        <v>2</v>
-      </c>
-      <c r="H70" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="I70" s="5" t="s">
-        <v>192</v>
       </c>
       <c r="J70" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:11">
@@ -3567,28 +3564,28 @@
         <v>123</v>
       </c>
       <c r="D71" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="E71" s="1">
+        <v>1</v>
+      </c>
+      <c r="F71" s="2">
+        <v>0</v>
+      </c>
+      <c r="G71" s="2">
+        <v>2</v>
+      </c>
+      <c r="H71" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="I71" s="5" t="s">
         <v>193</v>
-      </c>
-      <c r="E71" s="1">
-        <v>1</v>
-      </c>
-      <c r="F71" s="2">
-        <v>0</v>
-      </c>
-      <c r="G71" s="2">
-        <v>2</v>
-      </c>
-      <c r="H71" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="I71" s="5" t="s">
-        <v>194</v>
       </c>
       <c r="J71" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:11">
@@ -3596,28 +3593,28 @@
         <v>124</v>
       </c>
       <c r="D72" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E72" s="1">
+        <v>1</v>
+      </c>
+      <c r="F72" s="2">
+        <v>0</v>
+      </c>
+      <c r="G72" s="2">
+        <v>2</v>
+      </c>
+      <c r="H72" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="I72" s="5" t="s">
         <v>195</v>
-      </c>
-      <c r="E72" s="1">
-        <v>1</v>
-      </c>
-      <c r="F72" s="2">
-        <v>0</v>
-      </c>
-      <c r="G72" s="2">
-        <v>2</v>
-      </c>
-      <c r="H72" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="I72" s="5" t="s">
-        <v>196</v>
       </c>
       <c r="J72" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:11">
@@ -3625,28 +3622,28 @@
         <v>125</v>
       </c>
       <c r="D73" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="E73" s="1">
+        <v>1</v>
+      </c>
+      <c r="F73" s="2">
+        <v>0</v>
+      </c>
+      <c r="G73" s="2">
+        <v>2</v>
+      </c>
+      <c r="H73" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="I73" s="5" t="s">
         <v>197</v>
-      </c>
-      <c r="E73" s="1">
-        <v>1</v>
-      </c>
-      <c r="F73" s="2">
-        <v>0</v>
-      </c>
-      <c r="G73" s="2">
-        <v>2</v>
-      </c>
-      <c r="H73" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="I73" s="5" t="s">
-        <v>198</v>
       </c>
       <c r="J73" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:11">
@@ -3654,28 +3651,28 @@
         <v>127</v>
       </c>
       <c r="D75" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E75" s="1">
+        <v>1</v>
+      </c>
+      <c r="F75" s="2">
+        <v>0</v>
+      </c>
+      <c r="G75" s="2">
+        <v>2</v>
+      </c>
+      <c r="H75" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="I75" s="5" t="s">
         <v>199</v>
-      </c>
-      <c r="E75" s="1">
-        <v>1</v>
-      </c>
-      <c r="F75" s="2">
-        <v>0</v>
-      </c>
-      <c r="G75" s="2">
-        <v>2</v>
-      </c>
-      <c r="H75" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="I75" s="5" t="s">
-        <v>200</v>
       </c>
       <c r="J75" s="5" t="s">
         <v>40</v>
       </c>
       <c r="K75" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:11">
@@ -3683,28 +3680,28 @@
         <v>128</v>
       </c>
       <c r="D76" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="E76" s="1">
+        <v>1</v>
+      </c>
+      <c r="F76" s="2">
+        <v>0</v>
+      </c>
+      <c r="G76" s="2">
+        <v>2</v>
+      </c>
+      <c r="H76" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="E76" s="1">
-        <v>1</v>
-      </c>
-      <c r="F76" s="2">
-        <v>0</v>
-      </c>
-      <c r="G76" s="2">
-        <v>2</v>
-      </c>
-      <c r="H76" s="5" t="s">
+      <c r="I76" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="I76" s="5" t="s">
+      <c r="J76" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="J76" s="5" t="s">
-        <v>204</v>
-      </c>
       <c r="K76" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="87" customHeight="1" spans="3:11">
@@ -3712,28 +3709,28 @@
         <v>201</v>
       </c>
       <c r="D87" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="E87" s="1">
+        <v>1</v>
+      </c>
+      <c r="F87" s="2">
+        <v>0</v>
+      </c>
+      <c r="G87" s="2">
+        <v>2</v>
+      </c>
+      <c r="H87" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="E87" s="1">
-        <v>1</v>
-      </c>
-      <c r="F87" s="2">
-        <v>0</v>
-      </c>
-      <c r="G87" s="2">
-        <v>2</v>
-      </c>
-      <c r="H87" s="5" t="s">
+      <c r="I87" s="5" t="s">
         <v>206</v>
-      </c>
-      <c r="I87" s="5" t="s">
-        <v>207</v>
       </c>
       <c r="J87" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K87" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="88" customHeight="1" spans="3:11">
@@ -3741,28 +3738,28 @@
         <v>202</v>
       </c>
       <c r="D88" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="E88" s="1">
+        <v>1</v>
+      </c>
+      <c r="F88" s="2">
+        <v>0</v>
+      </c>
+      <c r="G88" s="2">
+        <v>2</v>
+      </c>
+      <c r="H88" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="I88" s="5" t="s">
         <v>209</v>
-      </c>
-      <c r="E88" s="1">
-        <v>1</v>
-      </c>
-      <c r="F88" s="2">
-        <v>0</v>
-      </c>
-      <c r="G88" s="2">
-        <v>2</v>
-      </c>
-      <c r="H88" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="I88" s="5" t="s">
-        <v>210</v>
       </c>
       <c r="J88" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K88" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="89" customHeight="1" spans="3:11">
@@ -3770,28 +3767,28 @@
         <v>203</v>
       </c>
       <c r="D89" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E89" s="1">
+        <v>1</v>
+      </c>
+      <c r="F89" s="2">
+        <v>0</v>
+      </c>
+      <c r="G89" s="2">
+        <v>2</v>
+      </c>
+      <c r="H89" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="I89" s="5" t="s">
         <v>212</v>
-      </c>
-      <c r="E89" s="1">
-        <v>1</v>
-      </c>
-      <c r="F89" s="2">
-        <v>0</v>
-      </c>
-      <c r="G89" s="2">
-        <v>2</v>
-      </c>
-      <c r="H89" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="I89" s="5" t="s">
-        <v>213</v>
       </c>
       <c r="J89" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K89" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="90" customHeight="1" spans="3:11">
@@ -3799,28 +3796,28 @@
         <v>204</v>
       </c>
       <c r="D90" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="E90" s="1">
+        <v>1</v>
+      </c>
+      <c r="F90" s="2">
+        <v>0</v>
+      </c>
+      <c r="G90" s="2">
+        <v>2</v>
+      </c>
+      <c r="H90" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="I90" s="5" t="s">
         <v>215</v>
-      </c>
-      <c r="E90" s="1">
-        <v>1</v>
-      </c>
-      <c r="F90" s="2">
-        <v>0</v>
-      </c>
-      <c r="G90" s="2">
-        <v>2</v>
-      </c>
-      <c r="H90" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="I90" s="5" t="s">
-        <v>216</v>
       </c>
       <c r="J90" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K90" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="3:11">
@@ -3828,28 +3825,28 @@
         <v>205</v>
       </c>
       <c r="D91" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="E91" s="1">
+        <v>1</v>
+      </c>
+      <c r="F91" s="2">
+        <v>0</v>
+      </c>
+      <c r="G91" s="2">
+        <v>2</v>
+      </c>
+      <c r="H91" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="I91" s="5" t="s">
         <v>218</v>
-      </c>
-      <c r="E91" s="1">
-        <v>1</v>
-      </c>
-      <c r="F91" s="2">
-        <v>0</v>
-      </c>
-      <c r="G91" s="2">
-        <v>2</v>
-      </c>
-      <c r="H91" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="I91" s="5" t="s">
-        <v>219</v>
       </c>
       <c r="J91" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K91" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="92" customHeight="1" spans="3:11">
@@ -3857,28 +3854,28 @@
         <v>206</v>
       </c>
       <c r="D92" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="E92" s="1">
+        <v>1</v>
+      </c>
+      <c r="F92" s="2">
+        <v>0</v>
+      </c>
+      <c r="G92" s="2">
+        <v>2</v>
+      </c>
+      <c r="H92" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="I92" s="5" t="s">
         <v>221</v>
-      </c>
-      <c r="E92" s="1">
-        <v>1</v>
-      </c>
-      <c r="F92" s="2">
-        <v>0</v>
-      </c>
-      <c r="G92" s="2">
-        <v>2</v>
-      </c>
-      <c r="H92" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="I92" s="5" t="s">
-        <v>222</v>
       </c>
       <c r="J92" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K92" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="93" customHeight="1" spans="3:11">
@@ -3886,28 +3883,28 @@
         <v>207</v>
       </c>
       <c r="D93" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="E93" s="1">
+        <v>1</v>
+      </c>
+      <c r="F93" s="2">
+        <v>0</v>
+      </c>
+      <c r="G93" s="2">
+        <v>2</v>
+      </c>
+      <c r="H93" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="E93" s="1">
-        <v>1</v>
-      </c>
-      <c r="F93" s="2">
-        <v>0</v>
-      </c>
-      <c r="G93" s="2">
-        <v>2</v>
-      </c>
-      <c r="H93" s="5" t="s">
+      <c r="I93" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="I93" s="5" t="s">
+      <c r="J93" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="J93" s="5" t="s">
+      <c r="K93" s="1" t="s">
         <v>227</v>
-      </c>
-      <c r="K93" s="1" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="94" customHeight="1" spans="3:11">
@@ -3915,19 +3912,19 @@
         <v>208</v>
       </c>
       <c r="D94" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E94" s="1">
+        <v>1</v>
+      </c>
+      <c r="F94" s="2">
+        <v>0</v>
+      </c>
+      <c r="G94" s="2">
+        <v>2</v>
+      </c>
+      <c r="K94" s="1" t="s">
         <v>229</v>
-      </c>
-      <c r="E94" s="1">
-        <v>1</v>
-      </c>
-      <c r="F94" s="2">
-        <v>0</v>
-      </c>
-      <c r="G94" s="2">
-        <v>2</v>
-      </c>
-      <c r="K94" s="1" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="95" customHeight="1" spans="3:11">
@@ -3935,28 +3932,28 @@
         <v>209</v>
       </c>
       <c r="D95" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="E95" s="1">
+        <v>1</v>
+      </c>
+      <c r="F95" s="2">
+        <v>0</v>
+      </c>
+      <c r="G95" s="2">
+        <v>2</v>
+      </c>
+      <c r="H95" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="I95" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="E95" s="1">
-        <v>1</v>
-      </c>
-      <c r="F95" s="2">
-        <v>0</v>
-      </c>
-      <c r="G95" s="2">
-        <v>2</v>
-      </c>
-      <c r="H95" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="I95" s="5" t="s">
+      <c r="J95" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="K95" s="1" t="s">
         <v>232</v>
-      </c>
-      <c r="J95" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="K95" s="1" t="s">
-        <v>233</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="27952" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="239">
   <si>
     <t>_id</t>
   </si>
@@ -396,6 +396,24 @@
   </si>
   <si>
     <t>1,1,1,1,1,1,1,1,1,1,1,1,1</t>
+  </si>
+  <si>
+    <t>白虎神器自选</t>
+  </si>
+  <si>
+    <t>61000009,61000010,61000011,61000012,61000013,61000014,61000015,61000016</t>
+  </si>
+  <si>
+    <t>朱雀神器自选</t>
+  </si>
+  <si>
+    <t>61000017,61000018,61000019,61000020,61000021,61000022,61000023,61000024</t>
+  </si>
+  <si>
+    <t>玄武神器自选</t>
+  </si>
+  <si>
+    <t>61000025,61000026,61000027,61000028,61000029,61000030,61000031,61000032</t>
   </si>
   <si>
     <t>驱魔6件套</t>
@@ -1687,17 +1705,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:K95"/>
+  <dimension ref="A3:K99"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
-    <col min="4" max="4" width="16.625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.1666666666667" style="1" customWidth="1"/>
-    <col min="6" max="7" width="13.0833333333333" style="2" customWidth="1"/>
-    <col min="8" max="8" width="31.25" style="1" customWidth="1"/>
-    <col min="9" max="9" width="60.3333333333333" style="1" customWidth="1"/>
-    <col min="10" max="10" width="26.875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="42.25" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.6283185840708" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.1681415929204" style="1" customWidth="1"/>
+    <col min="6" max="7" width="13.0796460176991" style="2" customWidth="1"/>
+    <col min="8" max="8" width="31.2477876106195" style="1" customWidth="1"/>
+    <col min="9" max="9" width="72.0176991150443" style="1" customWidth="1"/>
+    <col min="10" max="10" width="26.8761061946903" style="1" customWidth="1"/>
+    <col min="11" max="11" width="42.2477876106195" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -2834,38 +2852,67 @@
         <v>119</v>
       </c>
     </row>
+    <row r="42" customHeight="1" spans="3:11">
+      <c r="C42" s="1">
+        <v>37</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E42" s="1">
+        <v>1</v>
+      </c>
+      <c r="F42" s="2">
+        <v>0</v>
+      </c>
+      <c r="G42" s="1">
+        <v>1</v>
+      </c>
+      <c r="H42" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="I42" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="J42" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
     <row r="43" customHeight="1" spans="3:11">
       <c r="C43" s="1">
-        <v>96</v>
+        <v>38</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E43" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" s="2">
         <v>0</v>
       </c>
       <c r="G43" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>124</v>
+        <v>89</v>
       </c>
       <c r="I43" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="J43" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="K43" s="1" t="s">
         <v>125</v>
-      </c>
-      <c r="J43" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="K43" s="1" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:11">
       <c r="C44" s="1">
-        <v>97</v>
+        <v>39</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>127</v>
@@ -2877,85 +2924,27 @@
         <v>0</v>
       </c>
       <c r="G44" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H44" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="I44" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="I44" s="5" t="s">
-        <v>129</v>
-      </c>
       <c r="J44" s="5" t="s">
-        <v>32</v>
+        <v>82</v>
       </c>
       <c r="K44" s="1" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="45" customHeight="1" spans="3:11">
-      <c r="C45" s="1">
-        <v>98</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E45" s="1">
-        <v>1</v>
-      </c>
-      <c r="F45" s="2">
-        <v>0</v>
-      </c>
-      <c r="G45" s="1">
-        <v>2</v>
-      </c>
-      <c r="H45" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="I45" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="J45" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="K45" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="46" customHeight="1" spans="3:11">
-      <c r="C46" s="1">
-        <v>99</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="E46" s="1">
-        <v>0</v>
-      </c>
-      <c r="F46" s="2">
-        <v>0</v>
-      </c>
-      <c r="G46" s="1">
-        <v>2</v>
-      </c>
-      <c r="H46" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="I46" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="J46" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="K46" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
     <row r="47" customHeight="1" spans="3:11">
       <c r="C47" s="1">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="E47" s="1">
         <v>0</v>
@@ -2967,27 +2956,27 @@
         <v>2</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="I47" s="5" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="J47" s="5" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:11">
       <c r="C48" s="1">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="E48" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F48" s="2">
         <v>0</v>
@@ -2996,27 +2985,27 @@
         <v>2</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="I48" s="5" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="J48" s="5" t="s">
-        <v>126</v>
+        <v>32</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="3:11">
       <c r="C49" s="1">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="E49" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" s="2">
         <v>0</v>
@@ -3025,24 +3014,24 @@
         <v>2</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="I49" s="5" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="J49" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="K49" s="1" t="s">
         <v>136</v>
-      </c>
-      <c r="K49" s="1" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="3:11">
       <c r="C50" s="1">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E50" s="1">
         <v>0</v>
@@ -3054,24 +3043,24 @@
         <v>2</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="I50" s="5" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="J50" s="5" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="3:11">
       <c r="C51" s="1">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E51" s="1">
         <v>0</v>
@@ -3083,85 +3072,114 @@
         <v>2</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="I51" s="5" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="J51" s="5" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="3:11">
       <c r="C52" s="1">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D52" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E52" s="1">
+        <v>0</v>
+      </c>
+      <c r="F52" s="2">
+        <v>0</v>
+      </c>
+      <c r="G52" s="1">
+        <v>2</v>
+      </c>
+      <c r="H52" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="I52" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="J52" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="K52" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="53" customHeight="1" spans="3:11">
+      <c r="C53" s="1">
+        <v>102</v>
+      </c>
+      <c r="D53" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="E52" s="1">
-        <v>0</v>
-      </c>
-      <c r="F52" s="2">
-        <v>0</v>
-      </c>
-      <c r="G52" s="1">
-        <v>2</v>
-      </c>
-      <c r="H52" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="I52" s="5" t="s">
+      <c r="E53" s="1">
+        <v>0</v>
+      </c>
+      <c r="F53" s="2">
+        <v>0</v>
+      </c>
+      <c r="G53" s="1">
+        <v>2</v>
+      </c>
+      <c r="H53" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="I53" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="J52" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="K52" s="1" t="s">
+      <c r="J53" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="K53" s="1" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:11">
       <c r="C54" s="1">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>149</v>
       </c>
       <c r="E54" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F54" s="2">
         <v>0</v>
       </c>
       <c r="G54" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H54" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="I54" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="I54" s="5" t="s">
-        <v>151</v>
-      </c>
       <c r="J54" s="5" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:11">
       <c r="C55" s="1">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E55" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F55" s="2">
         <v>0</v>
@@ -3170,27 +3188,27 @@
         <v>2</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>64</v>
+        <v>140</v>
       </c>
       <c r="I55" s="5" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="J55" s="5" t="s">
-        <v>40</v>
+        <v>142</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>83</v>
+        <v>151</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:11">
       <c r="C56" s="1">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E56" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F56" s="2">
         <v>0</v>
@@ -3199,53 +3217,53 @@
         <v>2</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>64</v>
+        <v>140</v>
       </c>
       <c r="I56" s="5" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="J56" s="5" t="s">
-        <v>40</v>
+        <v>142</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:11">
       <c r="C58" s="1">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D58" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E58" s="1">
+        <v>1</v>
+      </c>
+      <c r="F58" s="2">
+        <v>0</v>
+      </c>
+      <c r="G58" s="1">
+        <v>1</v>
+      </c>
+      <c r="H58" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="I58" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="J58" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="K58" s="1" t="s">
         <v>159</v>
-      </c>
-      <c r="E58" s="1">
-        <v>1</v>
-      </c>
-      <c r="F58" s="2">
-        <v>0</v>
-      </c>
-      <c r="G58" s="2">
-        <v>2</v>
-      </c>
-      <c r="H58" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="I58" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="J58" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="K58" s="1" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:11">
       <c r="C59" s="1">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E59" s="1">
         <v>1</v>
@@ -3253,28 +3271,28 @@
       <c r="F59" s="2">
         <v>0</v>
       </c>
-      <c r="G59" s="2">
+      <c r="G59" s="1">
         <v>2</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>160</v>
+        <v>64</v>
       </c>
       <c r="I59" s="5" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="J59" s="5" t="s">
-        <v>87</v>
+        <v>40</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>165</v>
+        <v>83</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="3:11">
       <c r="C60" s="1">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="E60" s="1">
         <v>1</v>
@@ -3282,57 +3300,28 @@
       <c r="F60" s="2">
         <v>0</v>
       </c>
-      <c r="G60" s="2">
+      <c r="G60" s="1">
         <v>2</v>
       </c>
       <c r="H60" s="5" t="s">
-        <v>160</v>
+        <v>64</v>
       </c>
       <c r="I60" s="5" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="J60" s="5" t="s">
-        <v>87</v>
+        <v>40</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="61" customHeight="1" spans="3:11">
-      <c r="C61" s="1">
-        <v>112</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="E61" s="1">
-        <v>1</v>
-      </c>
-      <c r="F61" s="2">
-        <v>0</v>
-      </c>
-      <c r="G61" s="2">
-        <v>2</v>
-      </c>
-      <c r="H61" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="I61" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="J61" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="K61" s="1" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="3:11">
       <c r="C62" s="1">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="E62" s="1">
         <v>1</v>
@@ -3344,24 +3333,24 @@
         <v>2</v>
       </c>
       <c r="H62" s="5" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="I62" s="5" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="J62" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="3:11">
       <c r="C63" s="1">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="E63" s="1">
         <v>1</v>
@@ -3373,24 +3362,24 @@
         <v>2</v>
       </c>
       <c r="H63" s="5" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="I63" s="5" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="J63" s="5" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:11">
       <c r="C64" s="1">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="E64" s="1">
         <v>1</v>
@@ -3402,24 +3391,53 @@
         <v>2</v>
       </c>
       <c r="H64" s="5" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="I64" s="5" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="J64" s="5" t="s">
-        <v>40</v>
+        <v>87</v>
       </c>
       <c r="K64" s="1" t="s">
-        <v>179</v>
+        <v>174</v>
+      </c>
+    </row>
+    <row r="65" customHeight="1" spans="3:11">
+      <c r="C65" s="1">
+        <v>112</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E65" s="1">
+        <v>1</v>
+      </c>
+      <c r="F65" s="2">
+        <v>0</v>
+      </c>
+      <c r="G65" s="2">
+        <v>2</v>
+      </c>
+      <c r="H65" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="I65" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="J65" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K65" s="1" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="3:11">
       <c r="C66" s="1">
-        <v>118</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>182</v>
+        <v>113</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>178</v>
       </c>
       <c r="E66" s="1">
         <v>1</v>
@@ -3431,24 +3449,24 @@
         <v>2</v>
       </c>
       <c r="H66" s="5" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="I66" s="5" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="J66" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="K66" s="2" t="s">
-        <v>182</v>
+      <c r="K66" s="1" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:11">
       <c r="C67" s="1">
-        <v>119</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>184</v>
+        <v>114</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>181</v>
       </c>
       <c r="E67" s="1">
         <v>1</v>
@@ -3460,82 +3478,53 @@
         <v>2</v>
       </c>
       <c r="H67" s="5" t="s">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="I67" s="5" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J67" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="K67" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="K67" s="1" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:11">
       <c r="C68" s="1">
-        <v>120</v>
-      </c>
-      <c r="D68" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E68" s="1">
+        <v>1</v>
+      </c>
+      <c r="F68" s="2">
+        <v>0</v>
+      </c>
+      <c r="G68" s="2">
+        <v>2</v>
+      </c>
+      <c r="H68" s="5" t="s">
         <v>186</v>
-      </c>
-      <c r="E68" s="1">
-        <v>1</v>
-      </c>
-      <c r="F68" s="2">
-        <v>0</v>
-      </c>
-      <c r="G68" s="2">
-        <v>2</v>
-      </c>
-      <c r="H68" s="5" t="s">
-        <v>160</v>
       </c>
       <c r="I68" s="5" t="s">
         <v>187</v>
       </c>
       <c r="J68" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="K68" s="2" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="69" customHeight="1" spans="3:11">
-      <c r="C69" s="1">
-        <v>121</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="E69" s="1">
-        <v>1</v>
-      </c>
-      <c r="F69" s="2">
-        <v>0</v>
-      </c>
-      <c r="G69" s="2">
-        <v>2</v>
-      </c>
-      <c r="H69" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="I69" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="J69" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="K69" s="2" t="s">
-        <v>188</v>
+        <v>40</v>
+      </c>
+      <c r="K68" s="1" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:11">
       <c r="C70" s="1">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E70" s="1">
         <v>1</v>
@@ -3547,24 +3536,24 @@
         <v>2</v>
       </c>
       <c r="H70" s="5" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="I70" s="5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="J70" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:11">
       <c r="C71" s="1">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E71" s="1">
         <v>1</v>
@@ -3576,24 +3565,24 @@
         <v>2</v>
       </c>
       <c r="H71" s="5" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="I71" s="5" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="J71" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:11">
       <c r="C72" s="1">
-        <v>124</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>194</v>
+        <v>120</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>192</v>
       </c>
       <c r="E72" s="1">
         <v>1</v>
@@ -3605,24 +3594,24 @@
         <v>2</v>
       </c>
       <c r="H72" s="5" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="I72" s="5" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="J72" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="K72" s="1" t="s">
-        <v>194</v>
+      <c r="K72" s="2" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:11">
       <c r="C73" s="1">
-        <v>125</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>196</v>
+        <v>121</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>194</v>
       </c>
       <c r="E73" s="1">
         <v>1</v>
@@ -3634,23 +3623,52 @@
         <v>2</v>
       </c>
       <c r="H73" s="5" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="I73" s="5" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="J73" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="K73" s="1" t="s">
+      <c r="K73" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="74" customHeight="1" spans="3:11">
+      <c r="C74" s="1">
+        <v>122</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E74" s="1">
+        <v>1</v>
+      </c>
+      <c r="F74" s="2">
+        <v>0</v>
+      </c>
+      <c r="G74" s="2">
+        <v>2</v>
+      </c>
+      <c r="H74" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="I74" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="J74" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K74" s="2" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:11">
       <c r="C75" s="1">
-        <v>127</v>
-      </c>
-      <c r="D75" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D75" s="2" t="s">
         <v>198</v>
       </c>
       <c r="E75" s="1">
@@ -3663,21 +3681,21 @@
         <v>2</v>
       </c>
       <c r="H75" s="5" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="I75" s="5" t="s">
         <v>199</v>
       </c>
       <c r="J75" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="K75" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="K75" s="2" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:11">
       <c r="C76" s="1">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>200</v>
@@ -3692,140 +3710,111 @@
         <v>2</v>
       </c>
       <c r="H76" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="I76" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="I76" s="5" t="s">
-        <v>202</v>
-      </c>
       <c r="J76" s="5" t="s">
-        <v>203</v>
+        <v>87</v>
       </c>
       <c r="K76" s="1" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="87" customHeight="1" spans="3:11">
-      <c r="C87" s="1">
-        <v>201</v>
-      </c>
-      <c r="D87" s="1" t="s">
+    <row r="77" customHeight="1" spans="3:11">
+      <c r="C77" s="1">
+        <v>125</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="E77" s="1">
+        <v>1</v>
+      </c>
+      <c r="F77" s="2">
+        <v>0</v>
+      </c>
+      <c r="G77" s="2">
+        <v>2</v>
+      </c>
+      <c r="H77" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="I77" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="J77" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K77" s="1" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="79" customHeight="1" spans="3:11">
+      <c r="C79" s="1">
+        <v>127</v>
+      </c>
+      <c r="D79" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="E87" s="1">
-        <v>1</v>
-      </c>
-      <c r="F87" s="2">
-        <v>0</v>
-      </c>
-      <c r="G87" s="2">
-        <v>2</v>
-      </c>
-      <c r="H87" s="5" t="s">
+      <c r="E79" s="1">
+        <v>1</v>
+      </c>
+      <c r="F79" s="2">
+        <v>0</v>
+      </c>
+      <c r="G79" s="2">
+        <v>2</v>
+      </c>
+      <c r="H79" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="I79" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="I87" s="5" t="s">
+      <c r="J79" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K79" s="1" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="80" customHeight="1" spans="3:11">
+      <c r="C80" s="1">
+        <v>128</v>
+      </c>
+      <c r="D80" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="J87" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K87" s="1" t="s">
+      <c r="E80" s="1">
+        <v>1</v>
+      </c>
+      <c r="F80" s="2">
+        <v>0</v>
+      </c>
+      <c r="G80" s="2">
+        <v>2</v>
+      </c>
+      <c r="H80" s="5" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="88" customHeight="1" spans="3:11">
-      <c r="C88" s="1">
-        <v>202</v>
-      </c>
-      <c r="D88" s="1" t="s">
+      <c r="I80" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="E88" s="1">
-        <v>1</v>
-      </c>
-      <c r="F88" s="2">
-        <v>0</v>
-      </c>
-      <c r="G88" s="2">
-        <v>2</v>
-      </c>
-      <c r="H88" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="I88" s="5" t="s">
+      <c r="J80" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="J88" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K88" s="1" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="89" customHeight="1" spans="3:11">
-      <c r="C89" s="1">
-        <v>203</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="E89" s="1">
-        <v>1</v>
-      </c>
-      <c r="F89" s="2">
-        <v>0</v>
-      </c>
-      <c r="G89" s="2">
-        <v>2</v>
-      </c>
-      <c r="H89" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="I89" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="J89" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K89" s="1" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="90" customHeight="1" spans="3:11">
-      <c r="C90" s="1">
-        <v>204</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="E90" s="1">
-        <v>1</v>
-      </c>
-      <c r="F90" s="2">
-        <v>0</v>
-      </c>
-      <c r="G90" s="2">
-        <v>2</v>
-      </c>
-      <c r="H90" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="I90" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="J90" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K90" s="1" t="s">
-        <v>216</v>
+      <c r="K80" s="1" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="3:11">
       <c r="C91" s="1">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="E91" s="1">
         <v>1</v>
@@ -3837,24 +3826,24 @@
         <v>2</v>
       </c>
       <c r="H91" s="5" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="I91" s="5" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="J91" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K91" s="1" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
     </row>
     <row r="92" customHeight="1" spans="3:11">
       <c r="C92" s="1">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="E92" s="1">
         <v>1</v>
@@ -3866,24 +3855,24 @@
         <v>2</v>
       </c>
       <c r="H92" s="5" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="I92" s="5" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="J92" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K92" s="1" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
     </row>
     <row r="93" customHeight="1" spans="3:11">
       <c r="C93" s="1">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="E93" s="1">
         <v>1</v>
@@ -3895,24 +3884,24 @@
         <v>2</v>
       </c>
       <c r="H93" s="5" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="I93" s="5" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="J93" s="5" t="s">
-        <v>226</v>
+        <v>32</v>
       </c>
       <c r="K93" s="1" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
     </row>
     <row r="94" customHeight="1" spans="3:11">
       <c r="C94" s="1">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="E94" s="1">
         <v>1</v>
@@ -3923,37 +3912,153 @@
       <c r="G94" s="2">
         <v>2</v>
       </c>
+      <c r="H94" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="I94" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="J94" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="K94" s="1" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
     </row>
     <row r="95" customHeight="1" spans="3:11">
       <c r="C95" s="1">
+        <v>205</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="E95" s="1">
+        <v>1</v>
+      </c>
+      <c r="F95" s="2">
+        <v>0</v>
+      </c>
+      <c r="G95" s="2">
+        <v>2</v>
+      </c>
+      <c r="H95" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="I95" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="J95" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K95" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="96" customHeight="1" spans="3:11">
+      <c r="C96" s="1">
+        <v>206</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="E96" s="1">
+        <v>1</v>
+      </c>
+      <c r="F96" s="2">
+        <v>0</v>
+      </c>
+      <c r="G96" s="2">
+        <v>2</v>
+      </c>
+      <c r="H96" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="I96" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="J96" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K96" s="1" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="97" customHeight="1" spans="3:11">
+      <c r="C97" s="1">
+        <v>207</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E97" s="1">
+        <v>1</v>
+      </c>
+      <c r="F97" s="2">
+        <v>0</v>
+      </c>
+      <c r="G97" s="2">
+        <v>2</v>
+      </c>
+      <c r="H97" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="I97" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="J97" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="K97" s="1" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="98" customHeight="1" spans="3:11">
+      <c r="C98" s="1">
+        <v>208</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="E98" s="1">
+        <v>1</v>
+      </c>
+      <c r="F98" s="2">
+        <v>0</v>
+      </c>
+      <c r="G98" s="2">
+        <v>2</v>
+      </c>
+      <c r="K98" s="1" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="99" customHeight="1" spans="3:11">
+      <c r="C99" s="1">
         <v>209</v>
       </c>
-      <c r="D95" s="1" t="s">
+      <c r="D99" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="E99" s="1">
+        <v>1</v>
+      </c>
+      <c r="F99" s="2">
+        <v>0</v>
+      </c>
+      <c r="G99" s="2">
+        <v>2</v>
+      </c>
+      <c r="H99" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="E95" s="1">
-        <v>1</v>
-      </c>
-      <c r="F95" s="2">
-        <v>0</v>
-      </c>
-      <c r="G95" s="2">
-        <v>2</v>
-      </c>
-      <c r="H95" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="I95" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="J95" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="K95" s="1" t="s">
+      <c r="I99" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="J99" s="5" t="s">
         <v>232</v>
+      </c>
+      <c r="K99" s="1" t="s">
+        <v>238</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="242">
   <si>
     <t>_id</t>
   </si>
@@ -414,6 +414,15 @@
   </si>
   <si>
     <t>61000025,61000026,61000027,61000028,61000029,61000030,61000031,61000032</t>
+  </si>
+  <si>
+    <t>神器自选</t>
+  </si>
+  <si>
+    <t>4,4</t>
+  </si>
+  <si>
+    <t>35,37</t>
   </si>
   <si>
     <t>驱魔6件套</t>
@@ -1705,7 +1714,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:K99"/>
+  <dimension ref="A3:K100"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -2939,67 +2948,96 @@
         <v>127</v>
       </c>
     </row>
-    <row r="47" customHeight="1" spans="3:11">
-      <c r="C47" s="1">
-        <v>96</v>
-      </c>
-      <c r="D47" s="1" t="s">
+    <row r="45" customHeight="1" spans="3:11">
+      <c r="C45" s="1">
+        <v>40</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E45" s="1">
+        <v>1</v>
+      </c>
+      <c r="F45" s="2">
+        <v>0</v>
+      </c>
+      <c r="G45" s="1">
+        <v>1</v>
+      </c>
+      <c r="H45" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="I45" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="J45" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="K45" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="3:11">
+      <c r="C46" s="1">
+        <v>41</v>
+      </c>
+      <c r="D46" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E47" s="1">
-        <v>0</v>
-      </c>
-      <c r="F47" s="2">
-        <v>0</v>
-      </c>
-      <c r="G47" s="1">
-        <v>2</v>
-      </c>
-      <c r="H47" s="5" t="s">
+      <c r="E46" s="1">
+        <v>1</v>
+      </c>
+      <c r="F46" s="2">
+        <v>0</v>
+      </c>
+      <c r="G46" s="1">
+        <v>1</v>
+      </c>
+      <c r="H46" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="I47" s="5" t="s">
+      <c r="I46" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="J47" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="K47" s="1" t="s">
-        <v>129</v>
+      <c r="J46" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="K46" s="1" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:11">
       <c r="C48" s="1">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D48" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E48" s="1">
+        <v>0</v>
+      </c>
+      <c r="F48" s="2">
+        <v>0</v>
+      </c>
+      <c r="G48" s="1">
+        <v>2</v>
+      </c>
+      <c r="H48" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="E48" s="1">
-        <v>1</v>
-      </c>
-      <c r="F48" s="2">
-        <v>0</v>
-      </c>
-      <c r="G48" s="1">
-        <v>2</v>
-      </c>
-      <c r="H48" s="5" t="s">
+      <c r="I48" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="I48" s="5" t="s">
+      <c r="J48" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="J48" s="5" t="s">
-        <v>32</v>
-      </c>
       <c r="K48" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="3:11">
       <c r="C49" s="1">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>136</v>
@@ -3020,7 +3058,7 @@
         <v>138</v>
       </c>
       <c r="J49" s="5" t="s">
-        <v>82</v>
+        <v>32</v>
       </c>
       <c r="K49" s="1" t="s">
         <v>136</v>
@@ -3028,13 +3066,13 @@
     </row>
     <row r="50" customHeight="1" spans="3:11">
       <c r="C50" s="1">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>139</v>
       </c>
       <c r="E50" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50" s="2">
         <v>0</v>
@@ -3049,7 +3087,7 @@
         <v>141</v>
       </c>
       <c r="J50" s="5" t="s">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="K50" s="1" t="s">
         <v>139</v>
@@ -3057,39 +3095,39 @@
     </row>
     <row r="51" customHeight="1" spans="3:11">
       <c r="C51" s="1">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D51" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E51" s="1">
+        <v>0</v>
+      </c>
+      <c r="F51" s="2">
+        <v>0</v>
+      </c>
+      <c r="G51" s="1">
+        <v>2</v>
+      </c>
+      <c r="H51" s="5" t="s">
         <v>143</v>
-      </c>
-      <c r="E51" s="1">
-        <v>0</v>
-      </c>
-      <c r="F51" s="2">
-        <v>0</v>
-      </c>
-      <c r="G51" s="1">
-        <v>2</v>
-      </c>
-      <c r="H51" s="5" t="s">
-        <v>130</v>
       </c>
       <c r="I51" s="5" t="s">
         <v>144</v>
       </c>
       <c r="J51" s="5" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="3:11">
       <c r="C52" s="1">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E52" s="1">
         <v>0</v>
@@ -3101,24 +3139,24 @@
         <v>2</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="I52" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="J52" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="K52" s="1" t="s">
         <v>146</v>
-      </c>
-      <c r="J52" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="K52" s="1" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:11">
       <c r="C53" s="1">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E53" s="1">
         <v>0</v>
@@ -3130,24 +3168,24 @@
         <v>2</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="I53" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="J53" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="K53" s="1" t="s">
         <v>148</v>
-      </c>
-      <c r="J53" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="K53" s="1" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:11">
       <c r="C54" s="1">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E54" s="1">
         <v>0</v>
@@ -3159,24 +3197,24 @@
         <v>2</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="I54" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="J54" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="K54" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="J54" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="K54" s="1" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:11">
       <c r="C55" s="1">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E55" s="1">
         <v>0</v>
@@ -3188,111 +3226,111 @@
         <v>2</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="I55" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="J55" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="K55" s="1" t="s">
         <v>152</v>
-      </c>
-      <c r="J55" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="K55" s="1" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:11">
       <c r="C56" s="1">
+        <v>104</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E56" s="1">
+        <v>0</v>
+      </c>
+      <c r="F56" s="2">
+        <v>0</v>
+      </c>
+      <c r="G56" s="1">
+        <v>2</v>
+      </c>
+      <c r="H56" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="I56" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="J56" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="3:11">
+      <c r="C57" s="1">
         <v>105</v>
       </c>
-      <c r="D56" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E56" s="1">
-        <v>0</v>
-      </c>
-      <c r="F56" s="2">
-        <v>0</v>
-      </c>
-      <c r="G56" s="1">
-        <v>2</v>
-      </c>
-      <c r="H56" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="I56" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="J56" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="K56" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="58" customHeight="1" spans="3:11">
-      <c r="C58" s="1">
-        <v>106</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="E58" s="1">
-        <v>1</v>
-      </c>
-      <c r="F58" s="2">
-        <v>0</v>
-      </c>
-      <c r="G58" s="1">
-        <v>1</v>
-      </c>
-      <c r="H58" s="5" t="s">
+      <c r="D57" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="I58" s="5" t="s">
+      <c r="E57" s="1">
+        <v>0</v>
+      </c>
+      <c r="F57" s="2">
+        <v>0</v>
+      </c>
+      <c r="G57" s="1">
+        <v>2</v>
+      </c>
+      <c r="H57" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="I57" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="J58" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="K58" s="1" t="s">
-        <v>159</v>
+      <c r="J57" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="K57" s="1" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:11">
       <c r="C59" s="1">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D59" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E59" s="1">
+        <v>1</v>
+      </c>
+      <c r="F59" s="2">
+        <v>0</v>
+      </c>
+      <c r="G59" s="1">
+        <v>1</v>
+      </c>
+      <c r="H59" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="I59" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="E59" s="1">
-        <v>1</v>
-      </c>
-      <c r="F59" s="2">
-        <v>0</v>
-      </c>
-      <c r="G59" s="1">
-        <v>2</v>
-      </c>
-      <c r="H59" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="I59" s="5" t="s">
+      <c r="J59" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="J59" s="5" t="s">
-        <v>40</v>
-      </c>
       <c r="K59" s="1" t="s">
-        <v>83</v>
+        <v>162</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="3:11">
       <c r="C60" s="1">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E60" s="1">
         <v>1</v>
@@ -3307,62 +3345,62 @@
         <v>64</v>
       </c>
       <c r="I60" s="5" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J60" s="5" t="s">
         <v>40</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="62" customHeight="1" spans="3:11">
-      <c r="C62" s="1">
-        <v>109</v>
-      </c>
-      <c r="D62" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="61" customHeight="1" spans="3:11">
+      <c r="C61" s="1">
+        <v>108</v>
+      </c>
+      <c r="D61" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="E62" s="1">
-        <v>1</v>
-      </c>
-      <c r="F62" s="2">
-        <v>0</v>
-      </c>
-      <c r="G62" s="2">
-        <v>2</v>
-      </c>
-      <c r="H62" s="5" t="s">
+      <c r="E61" s="1">
+        <v>1</v>
+      </c>
+      <c r="F61" s="2">
+        <v>0</v>
+      </c>
+      <c r="G61" s="1">
+        <v>2</v>
+      </c>
+      <c r="H61" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="I61" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="I62" s="5" t="s">
+      <c r="J61" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K61" s="1" t="s">
         <v>167</v>
-      </c>
-      <c r="J62" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="K62" s="1" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="3:11">
       <c r="C63" s="1">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D63" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E63" s="1">
+        <v>1</v>
+      </c>
+      <c r="F63" s="2">
+        <v>0</v>
+      </c>
+      <c r="G63" s="2">
+        <v>2</v>
+      </c>
+      <c r="H63" s="5" t="s">
         <v>169</v>
-      </c>
-      <c r="E63" s="1">
-        <v>1</v>
-      </c>
-      <c r="F63" s="2">
-        <v>0</v>
-      </c>
-      <c r="G63" s="2">
-        <v>2</v>
-      </c>
-      <c r="H63" s="5" t="s">
-        <v>166</v>
       </c>
       <c r="I63" s="5" t="s">
         <v>170</v>
@@ -3376,7 +3414,7 @@
     </row>
     <row r="64" customHeight="1" spans="3:11">
       <c r="C64" s="1">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>172</v>
@@ -3391,7 +3429,7 @@
         <v>2</v>
       </c>
       <c r="H64" s="5" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="I64" s="5" t="s">
         <v>173</v>
@@ -3405,7 +3443,7 @@
     </row>
     <row r="65" customHeight="1" spans="3:11">
       <c r="C65" s="1">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>175</v>
@@ -3420,7 +3458,7 @@
         <v>2</v>
       </c>
       <c r="H65" s="5" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="I65" s="5" t="s">
         <v>176</v>
@@ -3434,7 +3472,7 @@
     </row>
     <row r="66" customHeight="1" spans="3:11">
       <c r="C66" s="1">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>178</v>
@@ -3449,7 +3487,7 @@
         <v>2</v>
       </c>
       <c r="H66" s="5" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="I66" s="5" t="s">
         <v>179</v>
@@ -3463,7 +3501,7 @@
     </row>
     <row r="67" customHeight="1" spans="3:11">
       <c r="C67" s="1">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>181</v>
@@ -3478,82 +3516,82 @@
         <v>2</v>
       </c>
       <c r="H67" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="I67" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="I67" s="5" t="s">
+      <c r="J67" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K67" s="1" t="s">
         <v>183</v>
-      </c>
-      <c r="J67" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="K67" s="1" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:11">
       <c r="C68" s="1">
+        <v>114</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="E68" s="1">
+        <v>1</v>
+      </c>
+      <c r="F68" s="2">
+        <v>0</v>
+      </c>
+      <c r="G68" s="2">
+        <v>2</v>
+      </c>
+      <c r="H68" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="I68" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="J68" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="K68" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="69" customHeight="1" spans="3:11">
+      <c r="C69" s="1">
         <v>115</v>
       </c>
-      <c r="D68" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="E68" s="1">
-        <v>1</v>
-      </c>
-      <c r="F68" s="2">
-        <v>0</v>
-      </c>
-      <c r="G68" s="2">
-        <v>2</v>
-      </c>
-      <c r="H68" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="I68" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="J68" s="5" t="s">
+      <c r="D69" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="E69" s="1">
+        <v>1</v>
+      </c>
+      <c r="F69" s="2">
+        <v>0</v>
+      </c>
+      <c r="G69" s="2">
+        <v>2</v>
+      </c>
+      <c r="H69" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="I69" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="J69" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="K68" s="1" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="70" customHeight="1" spans="3:11">
-      <c r="C70" s="1">
-        <v>118</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="E70" s="1">
-        <v>1</v>
-      </c>
-      <c r="F70" s="2">
-        <v>0</v>
-      </c>
-      <c r="G70" s="2">
-        <v>2</v>
-      </c>
-      <c r="H70" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="I70" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="J70" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="K70" s="2" t="s">
+      <c r="K69" s="1" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:11">
       <c r="C71" s="1">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E71" s="1">
         <v>1</v>
@@ -3565,24 +3603,24 @@
         <v>2</v>
       </c>
       <c r="H71" s="5" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="I71" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J71" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:11">
       <c r="C72" s="1">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E72" s="1">
         <v>1</v>
@@ -3594,24 +3632,24 @@
         <v>2</v>
       </c>
       <c r="H72" s="5" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="I72" s="5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="J72" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:11">
       <c r="C73" s="1">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E73" s="1">
         <v>1</v>
@@ -3623,24 +3661,24 @@
         <v>2</v>
       </c>
       <c r="H73" s="5" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="I73" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="J73" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:11">
       <c r="C74" s="1">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E74" s="1">
         <v>1</v>
@@ -3652,24 +3690,24 @@
         <v>2</v>
       </c>
       <c r="H74" s="5" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="I74" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J74" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:11">
       <c r="C75" s="1">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E75" s="1">
         <v>1</v>
@@ -3681,24 +3719,24 @@
         <v>2</v>
       </c>
       <c r="H75" s="5" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="I75" s="5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="J75" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:11">
       <c r="C76" s="1">
-        <v>124</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>200</v>
+        <v>123</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>201</v>
       </c>
       <c r="E76" s="1">
         <v>1</v>
@@ -3710,24 +3748,24 @@
         <v>2</v>
       </c>
       <c r="H76" s="5" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="I76" s="5" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="J76" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="K76" s="1" t="s">
-        <v>200</v>
+      <c r="K76" s="2" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:11">
       <c r="C77" s="1">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E77" s="1">
         <v>1</v>
@@ -3739,53 +3777,53 @@
         <v>2</v>
       </c>
       <c r="H77" s="5" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="I77" s="5" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="J77" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K77" s="1" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="79" customHeight="1" spans="3:11">
-      <c r="C79" s="1">
-        <v>127</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="E79" s="1">
-        <v>1</v>
-      </c>
-      <c r="F79" s="2">
-        <v>0</v>
-      </c>
-      <c r="G79" s="2">
-        <v>2</v>
-      </c>
-      <c r="H79" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="I79" s="5" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="78" customHeight="1" spans="3:11">
+      <c r="C78" s="1">
+        <v>125</v>
+      </c>
+      <c r="D78" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="J79" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="K79" s="1" t="s">
-        <v>204</v>
+      <c r="E78" s="1">
+        <v>1</v>
+      </c>
+      <c r="F78" s="2">
+        <v>0</v>
+      </c>
+      <c r="G78" s="2">
+        <v>2</v>
+      </c>
+      <c r="H78" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="I78" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="J78" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K78" s="1" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="3:11">
       <c r="C80" s="1">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E80" s="1">
         <v>1</v>
@@ -3797,65 +3835,65 @@
         <v>2</v>
       </c>
       <c r="H80" s="5" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="I80" s="5" t="s">
         <v>208</v>
       </c>
       <c r="J80" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K80" s="1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="81" customHeight="1" spans="3:11">
+      <c r="C81" s="1">
+        <v>128</v>
+      </c>
+      <c r="D81" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="K80" s="1" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="91" customHeight="1" spans="3:11">
-      <c r="C91" s="1">
-        <v>201</v>
-      </c>
-      <c r="D91" s="1" t="s">
+      <c r="E81" s="1">
+        <v>1</v>
+      </c>
+      <c r="F81" s="2">
+        <v>0</v>
+      </c>
+      <c r="G81" s="2">
+        <v>2</v>
+      </c>
+      <c r="H81" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="E91" s="1">
-        <v>1</v>
-      </c>
-      <c r="F91" s="2">
-        <v>0</v>
-      </c>
-      <c r="G91" s="2">
-        <v>2</v>
-      </c>
-      <c r="H91" s="5" t="s">
+      <c r="I81" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="I91" s="5" t="s">
+      <c r="J81" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="J91" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K91" s="1" t="s">
-        <v>213</v>
+      <c r="K81" s="1" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="92" customHeight="1" spans="3:11">
       <c r="C92" s="1">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D92" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="E92" s="1">
+        <v>1</v>
+      </c>
+      <c r="F92" s="2">
+        <v>0</v>
+      </c>
+      <c r="G92" s="2">
+        <v>2</v>
+      </c>
+      <c r="H92" s="5" t="s">
         <v>214</v>
-      </c>
-      <c r="E92" s="1">
-        <v>1</v>
-      </c>
-      <c r="F92" s="2">
-        <v>0</v>
-      </c>
-      <c r="G92" s="2">
-        <v>2</v>
-      </c>
-      <c r="H92" s="5" t="s">
-        <v>211</v>
       </c>
       <c r="I92" s="5" t="s">
         <v>215</v>
@@ -3869,7 +3907,7 @@
     </row>
     <row r="93" customHeight="1" spans="3:11">
       <c r="C93" s="1">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>217</v>
@@ -3884,7 +3922,7 @@
         <v>2</v>
       </c>
       <c r="H93" s="5" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="I93" s="5" t="s">
         <v>218</v>
@@ -3898,7 +3936,7 @@
     </row>
     <row r="94" customHeight="1" spans="3:11">
       <c r="C94" s="1">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>220</v>
@@ -3913,7 +3951,7 @@
         <v>2</v>
       </c>
       <c r="H94" s="5" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="I94" s="5" t="s">
         <v>221</v>
@@ -3927,7 +3965,7 @@
     </row>
     <row r="95" customHeight="1" spans="3:11">
       <c r="C95" s="1">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>223</v>
@@ -3942,7 +3980,7 @@
         <v>2</v>
       </c>
       <c r="H95" s="5" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="I95" s="5" t="s">
         <v>224</v>
@@ -3956,7 +3994,7 @@
     </row>
     <row r="96" customHeight="1" spans="3:11">
       <c r="C96" s="1">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>226</v>
@@ -3971,7 +4009,7 @@
         <v>2</v>
       </c>
       <c r="H96" s="5" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="I96" s="5" t="s">
         <v>227</v>
@@ -3985,7 +4023,7 @@
     </row>
     <row r="97" customHeight="1" spans="3:11">
       <c r="C97" s="1">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>229</v>
@@ -4000,44 +4038,53 @@
         <v>2</v>
       </c>
       <c r="H97" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="I97" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="I97" s="5" t="s">
+      <c r="J97" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K97" s="1" t="s">
         <v>231</v>
-      </c>
-      <c r="J97" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="K97" s="1" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="98" customHeight="1" spans="3:11">
       <c r="C98" s="1">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D98" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="E98" s="1">
+        <v>1</v>
+      </c>
+      <c r="F98" s="2">
+        <v>0</v>
+      </c>
+      <c r="G98" s="2">
+        <v>2</v>
+      </c>
+      <c r="H98" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="I98" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="E98" s="1">
-        <v>1</v>
-      </c>
-      <c r="F98" s="2">
-        <v>0</v>
-      </c>
-      <c r="G98" s="2">
-        <v>2</v>
+      <c r="J98" s="5" t="s">
+        <v>235</v>
       </c>
       <c r="K98" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="99" customHeight="1" spans="3:11">
       <c r="C99" s="1">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E99" s="1">
         <v>1</v>
@@ -4047,18 +4094,38 @@
       </c>
       <c r="G99" s="2">
         <v>2</v>
-      </c>
-      <c r="H99" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="I99" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="J99" s="5" t="s">
-        <v>232</v>
       </c>
       <c r="K99" s="1" t="s">
         <v>238</v>
+      </c>
+    </row>
+    <row r="100" customHeight="1" spans="3:11">
+      <c r="C100" s="1">
+        <v>209</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="E100" s="1">
+        <v>1</v>
+      </c>
+      <c r="F100" s="2">
+        <v>0</v>
+      </c>
+      <c r="G100" s="2">
+        <v>2</v>
+      </c>
+      <c r="H100" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="I100" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="J100" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="K100" s="1" t="s">
+        <v>241</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="241">
   <si>
     <t>_id</t>
   </si>
@@ -419,10 +419,10 @@
     <t>神器自选</t>
   </si>
   <si>
-    <t>4,4</t>
-  </si>
-  <si>
-    <t>35,37</t>
+    <t>4,4,4</t>
+  </si>
+  <si>
+    <t>35,37,38</t>
   </si>
   <si>
     <t>驱魔6件套</t>
@@ -657,9 +657,6 @@
   </si>
   <si>
     <t>暗金自选</t>
-  </si>
-  <si>
-    <t>4,4,4</t>
   </si>
   <si>
     <t>118,119,120</t>
@@ -3864,13 +3861,13 @@
         <v>2</v>
       </c>
       <c r="H81" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="I81" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="I81" s="5" t="s">
+      <c r="J81" s="5" t="s">
         <v>211</v>
-      </c>
-      <c r="J81" s="5" t="s">
-        <v>212</v>
       </c>
       <c r="K81" s="1" t="s">
         <v>209</v>
@@ -3881,28 +3878,28 @@
         <v>201</v>
       </c>
       <c r="D92" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="E92" s="1">
+        <v>1</v>
+      </c>
+      <c r="F92" s="2">
+        <v>0</v>
+      </c>
+      <c r="G92" s="2">
+        <v>2</v>
+      </c>
+      <c r="H92" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="E92" s="1">
-        <v>1</v>
-      </c>
-      <c r="F92" s="2">
-        <v>0</v>
-      </c>
-      <c r="G92" s="2">
-        <v>2</v>
-      </c>
-      <c r="H92" s="5" t="s">
+      <c r="I92" s="5" t="s">
         <v>214</v>
-      </c>
-      <c r="I92" s="5" t="s">
-        <v>215</v>
       </c>
       <c r="J92" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K92" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="93" customHeight="1" spans="3:11">
@@ -3910,28 +3907,28 @@
         <v>202</v>
       </c>
       <c r="D93" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="E93" s="1">
+        <v>1</v>
+      </c>
+      <c r="F93" s="2">
+        <v>0</v>
+      </c>
+      <c r="G93" s="2">
+        <v>2</v>
+      </c>
+      <c r="H93" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="I93" s="5" t="s">
         <v>217</v>
-      </c>
-      <c r="E93" s="1">
-        <v>1</v>
-      </c>
-      <c r="F93" s="2">
-        <v>0</v>
-      </c>
-      <c r="G93" s="2">
-        <v>2</v>
-      </c>
-      <c r="H93" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="I93" s="5" t="s">
-        <v>218</v>
       </c>
       <c r="J93" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K93" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="94" customHeight="1" spans="3:11">
@@ -3939,28 +3936,28 @@
         <v>203</v>
       </c>
       <c r="D94" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="E94" s="1">
+        <v>1</v>
+      </c>
+      <c r="F94" s="2">
+        <v>0</v>
+      </c>
+      <c r="G94" s="2">
+        <v>2</v>
+      </c>
+      <c r="H94" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="I94" s="5" t="s">
         <v>220</v>
-      </c>
-      <c r="E94" s="1">
-        <v>1</v>
-      </c>
-      <c r="F94" s="2">
-        <v>0</v>
-      </c>
-      <c r="G94" s="2">
-        <v>2</v>
-      </c>
-      <c r="H94" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="I94" s="5" t="s">
-        <v>221</v>
       </c>
       <c r="J94" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K94" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="95" customHeight="1" spans="3:11">
@@ -3968,28 +3965,28 @@
         <v>204</v>
       </c>
       <c r="D95" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E95" s="1">
+        <v>1</v>
+      </c>
+      <c r="F95" s="2">
+        <v>0</v>
+      </c>
+      <c r="G95" s="2">
+        <v>2</v>
+      </c>
+      <c r="H95" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="I95" s="5" t="s">
         <v>223</v>
-      </c>
-      <c r="E95" s="1">
-        <v>1</v>
-      </c>
-      <c r="F95" s="2">
-        <v>0</v>
-      </c>
-      <c r="G95" s="2">
-        <v>2</v>
-      </c>
-      <c r="H95" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="I95" s="5" t="s">
-        <v>224</v>
       </c>
       <c r="J95" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K95" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="96" customHeight="1" spans="3:11">
@@ -3997,28 +3994,28 @@
         <v>205</v>
       </c>
       <c r="D96" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="E96" s="1">
+        <v>1</v>
+      </c>
+      <c r="F96" s="2">
+        <v>0</v>
+      </c>
+      <c r="G96" s="2">
+        <v>2</v>
+      </c>
+      <c r="H96" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="I96" s="5" t="s">
         <v>226</v>
-      </c>
-      <c r="E96" s="1">
-        <v>1</v>
-      </c>
-      <c r="F96" s="2">
-        <v>0</v>
-      </c>
-      <c r="G96" s="2">
-        <v>2</v>
-      </c>
-      <c r="H96" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="I96" s="5" t="s">
-        <v>227</v>
       </c>
       <c r="J96" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K96" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="97" customHeight="1" spans="3:11">
@@ -4026,28 +4023,28 @@
         <v>206</v>
       </c>
       <c r="D97" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E97" s="1">
+        <v>1</v>
+      </c>
+      <c r="F97" s="2">
+        <v>0</v>
+      </c>
+      <c r="G97" s="2">
+        <v>2</v>
+      </c>
+      <c r="H97" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="I97" s="5" t="s">
         <v>229</v>
-      </c>
-      <c r="E97" s="1">
-        <v>1</v>
-      </c>
-      <c r="F97" s="2">
-        <v>0</v>
-      </c>
-      <c r="G97" s="2">
-        <v>2</v>
-      </c>
-      <c r="H97" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="I97" s="5" t="s">
-        <v>230</v>
       </c>
       <c r="J97" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K97" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="98" customHeight="1" spans="3:11">
@@ -4055,28 +4052,28 @@
         <v>207</v>
       </c>
       <c r="D98" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="E98" s="1">
+        <v>1</v>
+      </c>
+      <c r="F98" s="2">
+        <v>0</v>
+      </c>
+      <c r="G98" s="2">
+        <v>2</v>
+      </c>
+      <c r="H98" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="E98" s="1">
-        <v>1</v>
-      </c>
-      <c r="F98" s="2">
-        <v>0</v>
-      </c>
-      <c r="G98" s="2">
-        <v>2</v>
-      </c>
-      <c r="H98" s="5" t="s">
+      <c r="I98" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="I98" s="5" t="s">
+      <c r="J98" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="J98" s="5" t="s">
+      <c r="K98" s="1" t="s">
         <v>235</v>
-      </c>
-      <c r="K98" s="1" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="99" customHeight="1" spans="3:11">
@@ -4084,19 +4081,19 @@
         <v>208</v>
       </c>
       <c r="D99" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="E99" s="1">
+        <v>1</v>
+      </c>
+      <c r="F99" s="2">
+        <v>0</v>
+      </c>
+      <c r="G99" s="2">
+        <v>2</v>
+      </c>
+      <c r="K99" s="1" t="s">
         <v>237</v>
-      </c>
-      <c r="E99" s="1">
-        <v>1</v>
-      </c>
-      <c r="F99" s="2">
-        <v>0</v>
-      </c>
-      <c r="G99" s="2">
-        <v>2</v>
-      </c>
-      <c r="K99" s="1" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="100" customHeight="1" spans="3:11">
@@ -4104,28 +4101,28 @@
         <v>209</v>
       </c>
       <c r="D100" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="E100" s="1">
+        <v>1</v>
+      </c>
+      <c r="F100" s="2">
+        <v>0</v>
+      </c>
+      <c r="G100" s="2">
+        <v>2</v>
+      </c>
+      <c r="H100" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="I100" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="E100" s="1">
-        <v>1</v>
-      </c>
-      <c r="F100" s="2">
-        <v>0</v>
-      </c>
-      <c r="G100" s="2">
-        <v>2</v>
-      </c>
-      <c r="H100" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="I100" s="5" t="s">
+      <c r="J100" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="K100" s="1" t="s">
         <v>240</v>
-      </c>
-      <c r="J100" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="K100" s="1" t="s">
-        <v>241</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -1,13 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27952" windowHeight="12255"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="专属礼包" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="286">
   <si>
     <t>_id</t>
   </si>
@@ -269,39 +270,42 @@
     <t>升级自选</t>
   </si>
   <si>
-    <t>12,12,12,12,12,12,12,12,12</t>
-  </si>
-  <si>
-    <t>807,808,809,810,811,812,813,814,815</t>
+    <t>12,12,12,12,12,12,12,12,12,12,12,12</t>
+  </si>
+  <si>
+    <t>807,808,813,816,809,810,814,817,811,812,815,818</t>
+  </si>
+  <si>
+    <t>1,1,1,1,1,1,1,1,1,1,1,1,1,1</t>
+  </si>
+  <si>
+    <t>初级法宝自选</t>
+  </si>
+  <si>
+    <t>180006,180011,180012,180013,180020,180021</t>
+  </si>
+  <si>
+    <t>18,18,18,18,18,18,18,18,18</t>
+  </si>
+  <si>
+    <t>180001,180002,180004,180005,180007,180008,180009,180018,180019</t>
+  </si>
+  <si>
+    <t>1,1,1,1,1,1,1,1,1</t>
+  </si>
+  <si>
+    <t>神技自选</t>
+  </si>
+  <si>
+    <t>5,5,5,5,5,5,5,5,5,5</t>
+  </si>
+  <si>
+    <t>8001,8002,8003,8004,8005,8006,8007,8008,8009,8010</t>
   </si>
   <si>
     <t>1,1,1,1,1,1,1,1,1,1,1</t>
   </si>
   <si>
-    <t>初级法宝自选</t>
-  </si>
-  <si>
-    <t>180006,180011,180012,180013,180020,180021</t>
-  </si>
-  <si>
-    <t>18,18,18,18,18,18,18,18,18</t>
-  </si>
-  <si>
-    <t>180001,180002,180004,180005,180007,180008,180009,180018,180019</t>
-  </si>
-  <si>
-    <t>1,1,1,1,1,1,1,1,1</t>
-  </si>
-  <si>
-    <t>神技自选</t>
-  </si>
-  <si>
-    <t>5,5,5,5,5,5,5,5,5,5</t>
-  </si>
-  <si>
-    <t>8001,8002,8003,8004,8005,8006,8007,8008,8009,8010</t>
-  </si>
-  <si>
     <t>10阶级技能自选</t>
   </si>
   <si>
@@ -425,6 +429,21 @@
     <t>35,37,38</t>
   </si>
   <si>
+    <t>暗金专属自选</t>
+  </si>
+  <si>
+    <t>4,4,4,4,4,4</t>
+  </si>
+  <si>
+    <t>1101,1102,1103,1104,1105,1106</t>
+  </si>
+  <si>
+    <t>金色专属自选</t>
+  </si>
+  <si>
+    <t>1001,1002,1003,1004,1005,1006</t>
+  </si>
+  <si>
     <t>驱魔6件套</t>
   </si>
   <si>
@@ -596,9 +615,6 @@
     <t>红装自选</t>
   </si>
   <si>
-    <t>4,4,4,4,4,4</t>
-  </si>
-  <si>
     <t>109,110,111,112,113,114</t>
   </si>
   <si>
@@ -750,6 +766,126 @@
   </si>
   <si>
     <t>50资质金宠自选</t>
+  </si>
+  <si>
+    <t>金色刺杀专属包</t>
+  </si>
+  <si>
+    <t>金色雷电专属包</t>
+  </si>
+  <si>
+    <t>1007,1008,1009,1010,1011,1012</t>
+  </si>
+  <si>
+    <t>金色火符专属包</t>
+  </si>
+  <si>
+    <t>1013,1014,1015,1016,1017,1018</t>
+  </si>
+  <si>
+    <t>金色战吼专属包</t>
+  </si>
+  <si>
+    <t>1019,1020,1021,1022,1023,1024</t>
+  </si>
+  <si>
+    <t>金色瞬移专属包</t>
+  </si>
+  <si>
+    <t>1025,1026,1027,1028,1029,1030</t>
+  </si>
+  <si>
+    <t>金色隐身专属包</t>
+  </si>
+  <si>
+    <t>1031,1032,1033,1034,1035,1036</t>
+  </si>
+  <si>
+    <t>金色裂地专属包</t>
+  </si>
+  <si>
+    <t>1037,1038,1039,1040,1041,1042</t>
+  </si>
+  <si>
+    <t>金色分身专属包</t>
+  </si>
+  <si>
+    <t>1043,1044,1045,1046,1047,1048</t>
+  </si>
+  <si>
+    <t>金色无极专属包</t>
+  </si>
+  <si>
+    <t>1049,1050,1051,1052,1053,1054</t>
+  </si>
+  <si>
+    <t>暗金1阶技能专属</t>
+  </si>
+  <si>
+    <t>暗金2阶技能专属</t>
+  </si>
+  <si>
+    <t>1107,1108,1109,1110,1111,1112</t>
+  </si>
+  <si>
+    <t>暗金3阶技能专属</t>
+  </si>
+  <si>
+    <t>1113,1114,1115,1116,1117,1118</t>
+  </si>
+  <si>
+    <t>暗金4阶技能专属</t>
+  </si>
+  <si>
+    <t>1119,1120,1121,1122,1123,1124</t>
+  </si>
+  <si>
+    <t>暗金5阶技能专属</t>
+  </si>
+  <si>
+    <t>1125,1126,1127,1128,1129,1130</t>
+  </si>
+  <si>
+    <t>暗金6阶技能专属</t>
+  </si>
+  <si>
+    <t>1131,1132,1133,1134,1135,1136</t>
+  </si>
+  <si>
+    <t>暗金7阶技能专属</t>
+  </si>
+  <si>
+    <t>1137,1138,1139,1140,1141,1142</t>
+  </si>
+  <si>
+    <t>暗金8阶技能专属</t>
+  </si>
+  <si>
+    <t>1143,1144,1145,1146,1147,1148</t>
+  </si>
+  <si>
+    <t>暗金9阶技能专属</t>
+  </si>
+  <si>
+    <t>1149,1150,1151,1152,1153,1154</t>
+  </si>
+  <si>
+    <t>暗金10阶技能专属</t>
+  </si>
+  <si>
+    <t>1155,1156,1157,1158,1159,1160</t>
+  </si>
+  <si>
+    <t>暗金11阶技能专属</t>
+  </si>
+  <si>
+    <t>1161,1162,1163,1164,1165,1166</t>
+  </si>
+  <si>
+    <t>暗金12阶技能专属</t>
+  </si>
+  <si>
+    <t>1167,1168,1169,1170,1171,1172</t>
   </si>
 </sst>
 </file>
@@ -1385,10 +1521,10 @@
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1"/>
@@ -1711,104 +1847,104 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:K100"/>
+  <dimension ref="A3:K102"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
-    <col min="4" max="4" width="16.6283185840708" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.1681415929204" style="1" customWidth="1"/>
-    <col min="6" max="7" width="13.0796460176991" style="2" customWidth="1"/>
-    <col min="8" max="8" width="31.2477876106195" style="1" customWidth="1"/>
-    <col min="9" max="9" width="72.0176991150443" style="1" customWidth="1"/>
-    <col min="10" max="10" width="26.8761061946903" style="1" customWidth="1"/>
-    <col min="11" max="11" width="42.2477876106195" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.1666666666667" style="1" customWidth="1"/>
+    <col min="6" max="7" width="13.0833333333333" style="3" customWidth="1"/>
+    <col min="8" max="8" width="31.25" style="1" customWidth="1"/>
+    <col min="9" max="9" width="72.0166666666667" style="1" customWidth="1"/>
+    <col min="10" max="10" width="26.875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="42.25" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="3" customHeight="1" spans="3:11">
-      <c r="C3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="3:11">
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="3" t="s">
+      <c r="D4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="K4" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="3:11">
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="I5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="J5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="K5" s="2" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2025,7 +2161,7 @@
       <c r="E13" s="1">
         <v>1</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="3">
         <v>0</v>
       </c>
       <c r="G13" s="1">
@@ -2054,7 +2190,7 @@
       <c r="E14" s="1">
         <v>1</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="3">
         <v>0</v>
       </c>
       <c r="G14" s="1">
@@ -2083,7 +2219,7 @@
       <c r="E15" s="1">
         <v>0</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="3">
         <v>0</v>
       </c>
       <c r="G15" s="1">
@@ -2112,7 +2248,7 @@
       <c r="E16" s="1">
         <v>0</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16" s="3">
         <v>0</v>
       </c>
       <c r="G16" s="1">
@@ -2141,7 +2277,7 @@
       <c r="E17" s="1">
         <v>0</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17" s="3">
         <v>0</v>
       </c>
       <c r="G17" s="1">
@@ -2199,7 +2335,7 @@
       <c r="E19" s="1">
         <v>1</v>
       </c>
-      <c r="F19" s="2">
+      <c r="F19" s="3">
         <v>0</v>
       </c>
       <c r="G19" s="1">
@@ -2228,7 +2364,7 @@
       <c r="E20" s="1">
         <v>0</v>
       </c>
-      <c r="F20" s="2">
+      <c r="F20" s="3">
         <v>0</v>
       </c>
       <c r="G20" s="1">
@@ -2257,7 +2393,7 @@
       <c r="E21" s="1">
         <v>0</v>
       </c>
-      <c r="F21" s="2">
+      <c r="F21" s="3">
         <v>0</v>
       </c>
       <c r="G21" s="1">
@@ -2286,7 +2422,7 @@
       <c r="E22" s="1">
         <v>0</v>
       </c>
-      <c r="F22" s="2">
+      <c r="F22" s="3">
         <v>0</v>
       </c>
       <c r="G22" s="1">
@@ -2315,7 +2451,7 @@
       <c r="E23" s="1">
         <v>1</v>
       </c>
-      <c r="F23" s="2">
+      <c r="F23" s="3">
         <v>0</v>
       </c>
       <c r="G23" s="1">
@@ -2344,7 +2480,7 @@
       <c r="E24" s="1">
         <v>1</v>
       </c>
-      <c r="F24" s="2">
+      <c r="F24" s="3">
         <v>0</v>
       </c>
       <c r="G24" s="1">
@@ -2373,7 +2509,7 @@
       <c r="E25" s="1">
         <v>1</v>
       </c>
-      <c r="F25" s="2">
+      <c r="F25" s="3">
         <v>0</v>
       </c>
       <c r="G25" s="1">
@@ -2489,7 +2625,7 @@
       <c r="E29" s="1">
         <v>1</v>
       </c>
-      <c r="F29" s="2">
+      <c r="F29" s="3">
         <v>0</v>
       </c>
       <c r="G29" s="1">
@@ -2518,7 +2654,7 @@
       <c r="E30" s="1">
         <v>1</v>
       </c>
-      <c r="F30" s="2">
+      <c r="F30" s="3">
         <v>0</v>
       </c>
       <c r="G30" s="1">
@@ -2547,7 +2683,7 @@
       <c r="E31" s="1">
         <v>1</v>
       </c>
-      <c r="F31" s="2">
+      <c r="F31" s="3">
         <v>0</v>
       </c>
       <c r="G31" s="1">
@@ -2560,7 +2696,7 @@
         <v>90</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K31" s="1" t="s">
         <v>88</v>
@@ -2571,12 +2707,12 @@
         <v>27</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E32" s="1">
         <v>1</v>
       </c>
-      <c r="F32" s="2">
+      <c r="F32" s="3">
         <v>0</v>
       </c>
       <c r="G32" s="1">
@@ -2586,13 +2722,13 @@
         <v>30</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J32" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:11">
@@ -2600,28 +2736,28 @@
         <v>28</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E33" s="1">
         <v>1</v>
       </c>
-      <c r="F33" s="2">
+      <c r="F33" s="3">
         <v>0</v>
       </c>
       <c r="G33" s="1">
         <v>2</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J33" s="5" t="s">
         <v>40</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:11">
@@ -2629,12 +2765,12 @@
         <v>29</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E34" s="1">
         <v>1</v>
       </c>
-      <c r="F34" s="2">
+      <c r="F34" s="3">
         <v>0</v>
       </c>
       <c r="G34" s="1">
@@ -2644,13 +2780,13 @@
         <v>30</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J34" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:11">
@@ -2658,28 +2794,28 @@
         <v>30</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E35" s="1">
         <v>1</v>
       </c>
-      <c r="F35" s="2">
+      <c r="F35" s="3">
         <v>0</v>
       </c>
       <c r="G35" s="1">
         <v>2</v>
       </c>
       <c r="H35" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="I35" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="J35" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="K35" s="1" t="s">
         <v>101</v>
-      </c>
-      <c r="I35" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="J35" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="K35" s="1" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:11">
@@ -2687,12 +2823,12 @@
         <v>31</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E36" s="1">
         <v>1</v>
       </c>
-      <c r="F36" s="2">
+      <c r="F36" s="3">
         <v>0</v>
       </c>
       <c r="G36" s="1">
@@ -2702,13 +2838,13 @@
         <v>64</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="J36" s="5" t="s">
         <v>40</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:11">
@@ -2716,28 +2852,28 @@
         <v>32</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E37" s="1">
         <v>0</v>
       </c>
-      <c r="F37" s="2">
+      <c r="F37" s="3">
         <v>0</v>
       </c>
       <c r="G37" s="1">
         <v>2</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I37" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J37" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:11">
@@ -2745,28 +2881,28 @@
         <v>33</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E38" s="1">
         <v>0</v>
       </c>
-      <c r="F38" s="2">
+      <c r="F38" s="3">
         <v>0</v>
       </c>
       <c r="G38" s="1">
         <v>2</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J38" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="39" customFormat="1" customHeight="1" spans="1:11">
@@ -2776,12 +2912,12 @@
         <v>34</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E39" s="1">
         <v>1</v>
       </c>
-      <c r="F39" s="2">
+      <c r="F39" s="3">
         <v>0</v>
       </c>
       <c r="G39">
@@ -2791,13 +2927,13 @@
         <v>64</v>
       </c>
       <c r="I39" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J39" s="5" t="s">
         <v>40</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:11">
@@ -2805,12 +2941,12 @@
         <v>35</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E40" s="1">
         <v>1</v>
       </c>
-      <c r="F40" s="2">
+      <c r="F40" s="3">
         <v>0</v>
       </c>
       <c r="G40" s="1">
@@ -2820,13 +2956,13 @@
         <v>89</v>
       </c>
       <c r="I40" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="J40" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="K40" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="J40" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="K40" s="1" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:11">
@@ -2834,28 +2970,28 @@
         <v>36</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E41" s="1">
         <v>1</v>
       </c>
-      <c r="F41" s="2">
-        <v>0</v>
-      </c>
-      <c r="G41" s="2">
+      <c r="F41" s="3">
+        <v>0</v>
+      </c>
+      <c r="G41" s="3">
         <v>1</v>
       </c>
       <c r="H41" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="I41" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="J41" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="K41" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="I41" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="J41" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="K41" s="1" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:11">
@@ -2863,12 +2999,12 @@
         <v>37</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E42" s="1">
         <v>1</v>
       </c>
-      <c r="F42" s="2">
+      <c r="F42" s="3">
         <v>0</v>
       </c>
       <c r="G42" s="1">
@@ -2878,13 +3014,13 @@
         <v>89</v>
       </c>
       <c r="I42" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="J42" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="K42" s="1" t="s">
         <v>124</v>
-      </c>
-      <c r="J42" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="K42" s="1" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:11">
@@ -2892,12 +3028,12 @@
         <v>38</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E43" s="1">
         <v>1</v>
       </c>
-      <c r="F43" s="2">
+      <c r="F43" s="3">
         <v>0</v>
       </c>
       <c r="G43" s="1">
@@ -2907,13 +3043,13 @@
         <v>89</v>
       </c>
       <c r="I43" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="J43" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="K43" s="1" t="s">
         <v>126</v>
-      </c>
-      <c r="J43" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="K43" s="1" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:11">
@@ -2921,12 +3057,12 @@
         <v>39</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E44" s="1">
         <v>1</v>
       </c>
-      <c r="F44" s="2">
+      <c r="F44" s="3">
         <v>0</v>
       </c>
       <c r="G44" s="1">
@@ -2936,13 +3072,13 @@
         <v>89</v>
       </c>
       <c r="I44" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="J44" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="K44" s="1" t="s">
         <v>128</v>
-      </c>
-      <c r="J44" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="K44" s="1" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:11">
@@ -2950,12 +3086,12 @@
         <v>40</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E45" s="1">
         <v>1</v>
       </c>
-      <c r="F45" s="2">
+      <c r="F45" s="3">
         <v>0</v>
       </c>
       <c r="G45" s="1">
@@ -2965,13 +3101,13 @@
         <v>89</v>
       </c>
       <c r="I45" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="J45" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="K45" s="1" t="s">
         <v>128</v>
-      </c>
-      <c r="J45" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="K45" s="1" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="3:11">
@@ -2979,62 +3115,66 @@
         <v>41</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E46" s="1">
         <v>1</v>
       </c>
-      <c r="F46" s="2">
+      <c r="F46" s="3">
         <v>0</v>
       </c>
       <c r="G46" s="1">
         <v>1</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I46" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J46" s="5" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="48" customHeight="1" spans="3:11">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="48" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A48" s="1"/>
+      <c r="B48" s="1"/>
       <c r="C48" s="1">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E48" s="1">
-        <v>0</v>
-      </c>
-      <c r="F48" s="2">
+        <v>1</v>
+      </c>
+      <c r="F48" s="3">
         <v>0</v>
       </c>
       <c r="G48" s="1">
         <v>2</v>
       </c>
       <c r="H48" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="I48" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="J48" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K48" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="I48" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="J48" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="K48" s="1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="49" customHeight="1" spans="3:11">
+    </row>
+    <row r="49" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A49" s="1"/>
+      <c r="B49" s="1"/>
       <c r="C49" s="1">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>136</v>
@@ -3042,20 +3182,20 @@
       <c r="E49" s="1">
         <v>1</v>
       </c>
-      <c r="F49" s="2">
+      <c r="F49" s="3">
         <v>0</v>
       </c>
       <c r="G49" s="1">
         <v>2</v>
       </c>
       <c r="H49" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="I49" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="I49" s="5" t="s">
-        <v>138</v>
-      </c>
       <c r="J49" s="5" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="K49" s="1" t="s">
         <v>136</v>
@@ -3063,44 +3203,44 @@
     </row>
     <row r="50" customHeight="1" spans="3:11">
       <c r="C50" s="1">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D50" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E50" s="1">
+        <v>0</v>
+      </c>
+      <c r="F50" s="3">
+        <v>0</v>
+      </c>
+      <c r="G50" s="1">
+        <v>2</v>
+      </c>
+      <c r="H50" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="E50" s="1">
-        <v>1</v>
-      </c>
-      <c r="F50" s="2">
-        <v>0</v>
-      </c>
-      <c r="G50" s="1">
-        <v>2</v>
-      </c>
-      <c r="H50" s="5" t="s">
+      <c r="I50" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="I50" s="5" t="s">
+      <c r="J50" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="J50" s="5" t="s">
-        <v>82</v>
-      </c>
       <c r="K50" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="3:11">
       <c r="C51" s="1">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>142</v>
       </c>
       <c r="E51" s="1">
-        <v>0</v>
-      </c>
-      <c r="F51" s="2">
+        <v>1</v>
+      </c>
+      <c r="F51" s="3">
         <v>0</v>
       </c>
       <c r="G51" s="1">
@@ -3113,7 +3253,7 @@
         <v>144</v>
       </c>
       <c r="J51" s="5" t="s">
-        <v>145</v>
+        <v>32</v>
       </c>
       <c r="K51" s="1" t="s">
         <v>142</v>
@@ -3121,36 +3261,36 @@
     </row>
     <row r="52" customHeight="1" spans="3:11">
       <c r="C52" s="1">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D52" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E52" s="1">
+        <v>1</v>
+      </c>
+      <c r="F52" s="3">
+        <v>0</v>
+      </c>
+      <c r="G52" s="1">
+        <v>2</v>
+      </c>
+      <c r="H52" s="5" t="s">
         <v>146</v>
-      </c>
-      <c r="E52" s="1">
-        <v>0</v>
-      </c>
-      <c r="F52" s="2">
-        <v>0</v>
-      </c>
-      <c r="G52" s="1">
-        <v>2</v>
-      </c>
-      <c r="H52" s="5" t="s">
-        <v>133</v>
       </c>
       <c r="I52" s="5" t="s">
         <v>147</v>
       </c>
       <c r="J52" s="5" t="s">
-        <v>135</v>
+        <v>91</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:11">
       <c r="C53" s="1">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>148</v>
@@ -3158,20 +3298,20 @@
       <c r="E53" s="1">
         <v>0</v>
       </c>
-      <c r="F53" s="2">
+      <c r="F53" s="3">
         <v>0</v>
       </c>
       <c r="G53" s="1">
         <v>2</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="I53" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J53" s="5" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="K53" s="1" t="s">
         <v>148</v>
@@ -3179,283 +3319,283 @@
     </row>
     <row r="54" customHeight="1" spans="3:11">
       <c r="C54" s="1">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E54" s="1">
         <v>0</v>
       </c>
-      <c r="F54" s="2">
+      <c r="F54" s="3">
         <v>0</v>
       </c>
       <c r="G54" s="1">
         <v>2</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="I54" s="5" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="J54" s="5" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:11">
       <c r="C55" s="1">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E55" s="1">
         <v>0</v>
       </c>
-      <c r="F55" s="2">
+      <c r="F55" s="3">
         <v>0</v>
       </c>
       <c r="G55" s="1">
         <v>2</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="I55" s="5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="J55" s="5" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:11">
       <c r="C56" s="1">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E56" s="1">
         <v>0</v>
       </c>
-      <c r="F56" s="2">
+      <c r="F56" s="3">
         <v>0</v>
       </c>
       <c r="G56" s="1">
         <v>2</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="I56" s="5" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="J56" s="5" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:11">
       <c r="C57" s="1">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E57" s="1">
         <v>0</v>
       </c>
-      <c r="F57" s="2">
+      <c r="F57" s="3">
         <v>0</v>
       </c>
       <c r="G57" s="1">
         <v>2</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="I57" s="5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="J57" s="5" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="3:11">
+      <c r="C58" s="1">
+        <v>104</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E58" s="1">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="1">
+        <v>2</v>
+      </c>
+      <c r="H58" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="I58" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="J58" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="K58" s="1" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:11">
       <c r="C59" s="1">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="E59" s="1">
-        <v>1</v>
-      </c>
-      <c r="F59" s="2">
+        <v>0</v>
+      </c>
+      <c r="F59" s="3">
         <v>0</v>
       </c>
       <c r="G59" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="I59" s="5" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="J59" s="5" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="K59" s="1" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="60" customHeight="1" spans="3:11">
-      <c r="C60" s="1">
-        <v>107</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="E60" s="1">
-        <v>1</v>
-      </c>
-      <c r="F60" s="2">
-        <v>0</v>
-      </c>
-      <c r="G60" s="1">
-        <v>2</v>
-      </c>
-      <c r="H60" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="I60" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="J60" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="K60" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
     <row r="61" customHeight="1" spans="3:11">
       <c r="C61" s="1">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D61" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E61" s="1">
+        <v>1</v>
+      </c>
+      <c r="F61" s="3">
+        <v>0</v>
+      </c>
+      <c r="G61" s="1">
+        <v>1</v>
+      </c>
+      <c r="H61" s="5" t="s">
         <v>165</v>
-      </c>
-      <c r="E61" s="1">
-        <v>1</v>
-      </c>
-      <c r="F61" s="2">
-        <v>0</v>
-      </c>
-      <c r="G61" s="1">
-        <v>2</v>
-      </c>
-      <c r="H61" s="5" t="s">
-        <v>64</v>
       </c>
       <c r="I61" s="5" t="s">
         <v>166</v>
       </c>
       <c r="J61" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="K61" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="62" customHeight="1" spans="3:11">
+      <c r="C62" s="1">
+        <v>107</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="E62" s="1">
+        <v>1</v>
+      </c>
+      <c r="F62" s="3">
+        <v>0</v>
+      </c>
+      <c r="G62" s="1">
+        <v>2</v>
+      </c>
+      <c r="H62" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="I62" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="J62" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="K61" s="1" t="s">
-        <v>167</v>
+      <c r="K62" s="1" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="3:11">
       <c r="C63" s="1">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="E63" s="1">
         <v>1</v>
       </c>
-      <c r="F63" s="2">
-        <v>0</v>
-      </c>
-      <c r="G63" s="2">
+      <c r="F63" s="3">
+        <v>0</v>
+      </c>
+      <c r="G63" s="1">
         <v>2</v>
       </c>
       <c r="H63" s="5" t="s">
-        <v>169</v>
+        <v>64</v>
       </c>
       <c r="I63" s="5" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="J63" s="5" t="s">
-        <v>87</v>
+        <v>40</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="64" customHeight="1" spans="3:11">
-      <c r="C64" s="1">
-        <v>110</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="E64" s="1">
-        <v>1</v>
-      </c>
-      <c r="F64" s="2">
-        <v>0</v>
-      </c>
-      <c r="G64" s="2">
-        <v>2</v>
-      </c>
-      <c r="H64" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="I64" s="5" t="s">
         <v>173</v>
-      </c>
-      <c r="J64" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="K64" s="1" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:11">
       <c r="C65" s="1">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D65" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E65" s="1">
+        <v>1</v>
+      </c>
+      <c r="F65" s="3">
+        <v>0</v>
+      </c>
+      <c r="G65" s="3">
+        <v>2</v>
+      </c>
+      <c r="H65" s="5" t="s">
         <v>175</v>
-      </c>
-      <c r="E65" s="1">
-        <v>1</v>
-      </c>
-      <c r="F65" s="2">
-        <v>0</v>
-      </c>
-      <c r="G65" s="2">
-        <v>2</v>
-      </c>
-      <c r="H65" s="5" t="s">
-        <v>169</v>
       </c>
       <c r="I65" s="5" t="s">
         <v>176</v>
@@ -3469,7 +3609,7 @@
     </row>
     <row r="66" customHeight="1" spans="3:11">
       <c r="C66" s="1">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>178</v>
@@ -3477,14 +3617,14 @@
       <c r="E66" s="1">
         <v>1</v>
       </c>
-      <c r="F66" s="2">
-        <v>0</v>
-      </c>
-      <c r="G66" s="2">
+      <c r="F66" s="3">
+        <v>0</v>
+      </c>
+      <c r="G66" s="3">
         <v>2</v>
       </c>
       <c r="H66" s="5" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="I66" s="5" t="s">
         <v>179</v>
@@ -3498,7 +3638,7 @@
     </row>
     <row r="67" customHeight="1" spans="3:11">
       <c r="C67" s="1">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>181</v>
@@ -3506,14 +3646,14 @@
       <c r="E67" s="1">
         <v>1</v>
       </c>
-      <c r="F67" s="2">
-        <v>0</v>
-      </c>
-      <c r="G67" s="2">
+      <c r="F67" s="3">
+        <v>0</v>
+      </c>
+      <c r="G67" s="3">
         <v>2</v>
       </c>
       <c r="H67" s="5" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="I67" s="5" t="s">
         <v>182</v>
@@ -3527,7 +3667,7 @@
     </row>
     <row r="68" customHeight="1" spans="3:11">
       <c r="C68" s="1">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>184</v>
@@ -3535,594 +3675,652 @@
       <c r="E68" s="1">
         <v>1</v>
       </c>
-      <c r="F68" s="2">
-        <v>0</v>
-      </c>
-      <c r="G68" s="2">
+      <c r="F68" s="3">
+        <v>0</v>
+      </c>
+      <c r="G68" s="3">
         <v>2</v>
       </c>
       <c r="H68" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="I68" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="I68" s="5" t="s">
+      <c r="J68" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K68" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="J68" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="K68" s="1" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:11">
       <c r="C69" s="1">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D69" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E69" s="1">
+        <v>1</v>
+      </c>
+      <c r="F69" s="3">
+        <v>0</v>
+      </c>
+      <c r="G69" s="3">
+        <v>2</v>
+      </c>
+      <c r="H69" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="I69" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="E69" s="1">
-        <v>1</v>
-      </c>
-      <c r="F69" s="2">
-        <v>0</v>
-      </c>
-      <c r="G69" s="2">
-        <v>2</v>
-      </c>
-      <c r="H69" s="5" t="s">
+      <c r="J69" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K69" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="I69" s="5" t="s">
+    </row>
+    <row r="70" customHeight="1" spans="3:11">
+      <c r="C70" s="1">
+        <v>114</v>
+      </c>
+      <c r="D70" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="J69" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="K69" s="1" t="s">
-        <v>188</v>
+      <c r="E70" s="1">
+        <v>1</v>
+      </c>
+      <c r="F70" s="3">
+        <v>0</v>
+      </c>
+      <c r="G70" s="3">
+        <v>2</v>
+      </c>
+      <c r="H70" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="I70" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="J70" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="K70" s="1" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:11">
       <c r="C71" s="1">
-        <v>118</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>191</v>
+        <v>115</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>194</v>
       </c>
       <c r="E71" s="1">
         <v>1</v>
       </c>
-      <c r="F71" s="2">
-        <v>0</v>
-      </c>
-      <c r="G71" s="2">
+      <c r="F71" s="3">
+        <v>0</v>
+      </c>
+      <c r="G71" s="3">
         <v>2</v>
       </c>
       <c r="H71" s="5" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="I71" s="5" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="J71" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="K71" s="2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="72" customHeight="1" spans="3:11">
-      <c r="C72" s="1">
-        <v>119</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="E72" s="1">
-        <v>1</v>
-      </c>
-      <c r="F72" s="2">
-        <v>0</v>
-      </c>
-      <c r="G72" s="2">
-        <v>2</v>
-      </c>
-      <c r="H72" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="I72" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K71" s="1" t="s">
         <v>194</v>
-      </c>
-      <c r="J72" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="K72" s="2" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:11">
       <c r="C73" s="1">
-        <v>120</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>195</v>
+        <v>118</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>196</v>
       </c>
       <c r="E73" s="1">
         <v>1</v>
       </c>
-      <c r="F73" s="2">
-        <v>0</v>
-      </c>
-      <c r="G73" s="2">
+      <c r="F73" s="3">
+        <v>0</v>
+      </c>
+      <c r="G73" s="3">
         <v>2</v>
       </c>
       <c r="H73" s="5" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="I73" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J73" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="K73" s="2" t="s">
-        <v>195</v>
+      <c r="K73" s="3" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:11">
       <c r="C74" s="1">
-        <v>121</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>197</v>
+        <v>119</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>198</v>
       </c>
       <c r="E74" s="1">
         <v>1</v>
       </c>
-      <c r="F74" s="2">
-        <v>0</v>
-      </c>
-      <c r="G74" s="2">
+      <c r="F74" s="3">
+        <v>0</v>
+      </c>
+      <c r="G74" s="3">
         <v>2</v>
       </c>
       <c r="H74" s="5" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="I74" s="5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J74" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="K74" s="2" t="s">
-        <v>197</v>
+      <c r="K74" s="3" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:11">
       <c r="C75" s="1">
-        <v>122</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>199</v>
+        <v>120</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>200</v>
       </c>
       <c r="E75" s="1">
         <v>1</v>
       </c>
-      <c r="F75" s="2">
-        <v>0</v>
-      </c>
-      <c r="G75" s="2">
+      <c r="F75" s="3">
+        <v>0</v>
+      </c>
+      <c r="G75" s="3">
         <v>2</v>
       </c>
       <c r="H75" s="5" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="I75" s="5" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="J75" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="K75" s="2" t="s">
-        <v>199</v>
+      <c r="K75" s="3" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:11">
       <c r="C76" s="1">
-        <v>123</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>201</v>
+        <v>121</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="E76" s="1">
         <v>1</v>
       </c>
-      <c r="F76" s="2">
-        <v>0</v>
-      </c>
-      <c r="G76" s="2">
+      <c r="F76" s="3">
+        <v>0</v>
+      </c>
+      <c r="G76" s="3">
         <v>2</v>
       </c>
       <c r="H76" s="5" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="I76" s="5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="J76" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="K76" s="2" t="s">
-        <v>201</v>
+      <c r="K76" s="3" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:11">
       <c r="C77" s="1">
-        <v>124</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>203</v>
+        <v>122</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>204</v>
       </c>
       <c r="E77" s="1">
         <v>1</v>
       </c>
-      <c r="F77" s="2">
-        <v>0</v>
-      </c>
-      <c r="G77" s="2">
+      <c r="F77" s="3">
+        <v>0</v>
+      </c>
+      <c r="G77" s="3">
         <v>2</v>
       </c>
       <c r="H77" s="5" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="I77" s="5" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J77" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="K77" s="1" t="s">
-        <v>203</v>
+      <c r="K77" s="3" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="3:11">
       <c r="C78" s="1">
-        <v>125</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>205</v>
+        <v>123</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>206</v>
       </c>
       <c r="E78" s="1">
         <v>1</v>
       </c>
-      <c r="F78" s="2">
-        <v>0</v>
-      </c>
-      <c r="G78" s="2">
+      <c r="F78" s="3">
+        <v>0</v>
+      </c>
+      <c r="G78" s="3">
         <v>2</v>
       </c>
       <c r="H78" s="5" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="I78" s="5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J78" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="K78" s="1" t="s">
-        <v>205</v>
+      <c r="K78" s="3" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="79" customHeight="1" spans="3:11">
+      <c r="C79" s="1">
+        <v>124</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="E79" s="1">
+        <v>1</v>
+      </c>
+      <c r="F79" s="3">
+        <v>0</v>
+      </c>
+      <c r="G79" s="3">
+        <v>2</v>
+      </c>
+      <c r="H79" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="I79" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="J79" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K79" s="1" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="3:11">
       <c r="C80" s="1">
+        <v>125</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E80" s="1">
+        <v>1</v>
+      </c>
+      <c r="F80" s="3">
+        <v>0</v>
+      </c>
+      <c r="G80" s="3">
+        <v>2</v>
+      </c>
+      <c r="H80" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="I80" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="J80" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K80" s="1" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="82" customHeight="1" spans="3:11">
+      <c r="C82" s="1">
         <v>127</v>
       </c>
-      <c r="D80" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="E80" s="1">
-        <v>1</v>
-      </c>
-      <c r="F80" s="2">
-        <v>0</v>
-      </c>
-      <c r="G80" s="2">
-        <v>2</v>
-      </c>
-      <c r="H80" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="I80" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="J80" s="5" t="s">
+      <c r="D82" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="E82" s="1">
+        <v>1</v>
+      </c>
+      <c r="F82" s="3">
+        <v>0</v>
+      </c>
+      <c r="G82" s="3">
+        <v>2</v>
+      </c>
+      <c r="H82" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="I82" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J82" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="K80" s="1" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="81" customHeight="1" spans="3:11">
-      <c r="C81" s="1">
+      <c r="K82" s="1" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="83" customHeight="1" spans="3:11">
+      <c r="C83" s="1">
         <v>128</v>
       </c>
-      <c r="D81" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="E81" s="1">
-        <v>1</v>
-      </c>
-      <c r="F81" s="2">
-        <v>0</v>
-      </c>
-      <c r="G81" s="2">
-        <v>2</v>
-      </c>
-      <c r="H81" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="I81" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="J81" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="K81" s="1" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="92" customHeight="1" spans="3:11">
-      <c r="C92" s="1">
-        <v>201</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="E92" s="1">
-        <v>1</v>
-      </c>
-      <c r="F92" s="2">
-        <v>0</v>
-      </c>
-      <c r="G92" s="2">
-        <v>2</v>
-      </c>
-      <c r="H92" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="I92" s="5" t="s">
+      <c r="D83" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="J92" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K92" s="1" t="s">
+      <c r="E83" s="1">
+        <v>1</v>
+      </c>
+      <c r="F83" s="3">
+        <v>0</v>
+      </c>
+      <c r="G83" s="3">
+        <v>2</v>
+      </c>
+      <c r="H83" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="I83" s="5" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="93" customHeight="1" spans="3:11">
-      <c r="C93" s="1">
-        <v>202</v>
-      </c>
-      <c r="D93" s="1" t="s">
+      <c r="J83" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="E93" s="1">
-        <v>1</v>
-      </c>
-      <c r="F93" s="2">
-        <v>0</v>
-      </c>
-      <c r="G93" s="2">
-        <v>2</v>
-      </c>
-      <c r="H93" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="I93" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="J93" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K93" s="1" t="s">
-        <v>218</v>
+      <c r="K83" s="1" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="94" customHeight="1" spans="3:11">
       <c r="C94" s="1">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D94" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="E94" s="1">
+        <v>1</v>
+      </c>
+      <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
+        <v>2</v>
+      </c>
+      <c r="H94" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="I94" s="5" t="s">
         <v>219</v>
-      </c>
-      <c r="E94" s="1">
-        <v>1</v>
-      </c>
-      <c r="F94" s="2">
-        <v>0</v>
-      </c>
-      <c r="G94" s="2">
-        <v>2</v>
-      </c>
-      <c r="H94" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="I94" s="5" t="s">
-        <v>220</v>
       </c>
       <c r="J94" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K94" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="95" customHeight="1" spans="3:11">
       <c r="C95" s="1">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D95" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="E95" s="1">
+        <v>1</v>
+      </c>
+      <c r="F95" s="3">
+        <v>0</v>
+      </c>
+      <c r="G95" s="3">
+        <v>2</v>
+      </c>
+      <c r="H95" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="I95" s="5" t="s">
         <v>222</v>
-      </c>
-      <c r="E95" s="1">
-        <v>1</v>
-      </c>
-      <c r="F95" s="2">
-        <v>0</v>
-      </c>
-      <c r="G95" s="2">
-        <v>2</v>
-      </c>
-      <c r="H95" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="I95" s="5" t="s">
-        <v>223</v>
       </c>
       <c r="J95" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K95" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="96" customHeight="1" spans="3:11">
       <c r="C96" s="1">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D96" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="E96" s="1">
+        <v>1</v>
+      </c>
+      <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
+        <v>2</v>
+      </c>
+      <c r="H96" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="I96" s="5" t="s">
         <v>225</v>
-      </c>
-      <c r="E96" s="1">
-        <v>1</v>
-      </c>
-      <c r="F96" s="2">
-        <v>0</v>
-      </c>
-      <c r="G96" s="2">
-        <v>2</v>
-      </c>
-      <c r="H96" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="I96" s="5" t="s">
-        <v>226</v>
       </c>
       <c r="J96" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K96" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="97" customHeight="1" spans="3:11">
       <c r="C97" s="1">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D97" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="E97" s="1">
+        <v>1</v>
+      </c>
+      <c r="F97" s="3">
+        <v>0</v>
+      </c>
+      <c r="G97" s="3">
+        <v>2</v>
+      </c>
+      <c r="H97" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="I97" s="5" t="s">
         <v>228</v>
-      </c>
-      <c r="E97" s="1">
-        <v>1</v>
-      </c>
-      <c r="F97" s="2">
-        <v>0</v>
-      </c>
-      <c r="G97" s="2">
-        <v>2</v>
-      </c>
-      <c r="H97" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="I97" s="5" t="s">
-        <v>229</v>
       </c>
       <c r="J97" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K97" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="98" customHeight="1" spans="3:11">
       <c r="C98" s="1">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D98" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="E98" s="1">
+        <v>1</v>
+      </c>
+      <c r="F98" s="3">
+        <v>0</v>
+      </c>
+      <c r="G98" s="3">
+        <v>2</v>
+      </c>
+      <c r="H98" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="I98" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="E98" s="1">
-        <v>1</v>
-      </c>
-      <c r="F98" s="2">
-        <v>0</v>
-      </c>
-      <c r="G98" s="2">
-        <v>2</v>
-      </c>
-      <c r="H98" s="5" t="s">
+      <c r="J98" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K98" s="1" t="s">
         <v>232</v>
-      </c>
-      <c r="I98" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="J98" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="K98" s="1" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="99" customHeight="1" spans="3:11">
       <c r="C99" s="1">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="E99" s="1">
         <v>1</v>
       </c>
-      <c r="F99" s="2">
-        <v>0</v>
-      </c>
-      <c r="G99" s="2">
-        <v>2</v>
+      <c r="F99" s="3">
+        <v>0</v>
+      </c>
+      <c r="G99" s="3">
+        <v>2</v>
+      </c>
+      <c r="H99" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="I99" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="J99" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="K99" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="100" customHeight="1" spans="3:11">
       <c r="C100" s="1">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D100" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="E100" s="1">
+        <v>1</v>
+      </c>
+      <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
+        <v>2</v>
+      </c>
+      <c r="H100" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="I100" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="E100" s="1">
-        <v>1</v>
-      </c>
-      <c r="F100" s="2">
-        <v>0</v>
-      </c>
-      <c r="G100" s="2">
-        <v>2</v>
-      </c>
-      <c r="H100" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="I100" s="5" t="s">
+      <c r="J100" s="5" t="s">
         <v>239</v>
-      </c>
-      <c r="J100" s="5" t="s">
-        <v>234</v>
       </c>
       <c r="K100" s="1" t="s">
         <v>240</v>
+      </c>
+    </row>
+    <row r="101" customHeight="1" spans="3:11">
+      <c r="C101" s="1">
+        <v>208</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="E101" s="1">
+        <v>1</v>
+      </c>
+      <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
+        <v>2</v>
+      </c>
+      <c r="K101" s="1" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="102" customHeight="1" spans="3:11">
+      <c r="C102" s="1">
+        <v>209</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="E102" s="1">
+        <v>1</v>
+      </c>
+      <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
+        <v>2</v>
+      </c>
+      <c r="H102" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="I102" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="J102" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="K102" s="1" t="s">
+        <v>245</v>
       </c>
     </row>
   </sheetData>
@@ -4137,4 +4335,881 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="B3:L50"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="3" width="9"/>
+    <col min="4" max="4" width="16.625" customWidth="1"/>
+    <col min="5" max="5" width="12.1666666666667" customWidth="1"/>
+    <col min="6" max="6" width="10.5" customWidth="1"/>
+    <col min="7" max="7" width="10.25" customWidth="1"/>
+    <col min="8" max="8" width="30.4166666666667" customWidth="1"/>
+    <col min="9" max="9" width="72.0166666666667" customWidth="1"/>
+    <col min="10" max="10" width="26.875" customWidth="1"/>
+    <col min="11" max="11" width="42.25" customWidth="1"/>
+    <col min="12" max="16384" width="9"/>
+  </cols>
+  <sheetData>
+    <row r="3" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+      <c r="C3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+      <c r="C5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+      <c r="C6" s="1">
+        <v>1001</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1">
+        <v>2</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+      <c r="C7" s="1">
+        <v>1002</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0</v>
+      </c>
+      <c r="G7" s="1">
+        <v>2</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+      <c r="C8" s="1">
+        <v>1003</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1">
+        <v>2</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+      <c r="C9" s="1">
+        <v>1004</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1">
+        <v>2</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+      <c r="C10" s="1">
+        <v>1005</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="1">
+        <v>2</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+      <c r="C11" s="1">
+        <v>1006</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0</v>
+      </c>
+      <c r="G11" s="1">
+        <v>2</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+      <c r="C12" s="1">
+        <v>1007</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1">
+        <v>2</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+      <c r="C13" s="1">
+        <v>1008</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="E13" s="1">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0</v>
+      </c>
+      <c r="G13" s="1">
+        <v>2</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+      <c r="C14" s="1">
+        <v>1009</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="E14" s="1">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="1">
+        <v>2</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" ht="18" customHeight="1"/>
+    <row r="16" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+      <c r="C16" s="1">
+        <v>1101</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="E16" s="1">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0</v>
+      </c>
+      <c r="G16" s="1">
+        <v>2</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+      <c r="C17" s="1">
+        <v>1102</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="E17" s="1">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0</v>
+      </c>
+      <c r="G17" s="1">
+        <v>2</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+      <c r="C18" s="1">
+        <v>1103</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="E18" s="1">
+        <v>0</v>
+      </c>
+      <c r="F18" s="3">
+        <v>0</v>
+      </c>
+      <c r="G18" s="1">
+        <v>2</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+      <c r="C19" s="1">
+        <v>1104</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="E19" s="1">
+        <v>0</v>
+      </c>
+      <c r="F19" s="3">
+        <v>0</v>
+      </c>
+      <c r="G19" s="1">
+        <v>2</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+      <c r="C20" s="1">
+        <v>1105</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="E20" s="1">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="1">
+        <v>2</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="J20" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+      <c r="C21" s="1">
+        <v>1106</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="E21" s="1">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3">
+        <v>0</v>
+      </c>
+      <c r="G21" s="1">
+        <v>2</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+      <c r="C22" s="1">
+        <v>1107</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="E22" s="1">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="1">
+        <v>2</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+      <c r="C23" s="1">
+        <v>1108</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="E23" s="1">
+        <v>0</v>
+      </c>
+      <c r="F23" s="3">
+        <v>0</v>
+      </c>
+      <c r="G23" s="1">
+        <v>2</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+      <c r="C24" s="1">
+        <v>1109</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E24" s="1">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="1">
+        <v>2</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+      <c r="C25" s="1">
+        <v>1110</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="E25" s="1">
+        <v>0</v>
+      </c>
+      <c r="F25" s="3">
+        <v>0</v>
+      </c>
+      <c r="G25" s="1">
+        <v>2</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+      <c r="C26" s="1">
+        <v>1111</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="E26" s="1">
+        <v>0</v>
+      </c>
+      <c r="F26" s="3">
+        <v>0</v>
+      </c>
+      <c r="G26" s="1">
+        <v>2</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+      <c r="C27" s="1">
+        <v>1112</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="E27" s="1">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3">
+        <v>0</v>
+      </c>
+      <c r="G27" s="1">
+        <v>2</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
+      <c r="B28"/>
+      <c r="C28"/>
+      <c r="D28"/>
+      <c r="E28"/>
+      <c r="F28"/>
+      <c r="G28"/>
+      <c r="H28"/>
+      <c r="I28"/>
+      <c r="J28"/>
+      <c r="K28"/>
+      <c r="L28"/>
+    </row>
+    <row r="30" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
+      <c r="B30"/>
+      <c r="C30"/>
+      <c r="D30"/>
+      <c r="E30"/>
+      <c r="F30"/>
+      <c r="G30"/>
+      <c r="H30"/>
+      <c r="I30"/>
+      <c r="J30"/>
+      <c r="K30"/>
+      <c r="L30"/>
+    </row>
+    <row r="31" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
+      <c r="B31"/>
+      <c r="C31"/>
+      <c r="D31"/>
+      <c r="E31"/>
+      <c r="F31"/>
+      <c r="G31"/>
+      <c r="H31"/>
+      <c r="I31"/>
+      <c r="J31"/>
+      <c r="K31"/>
+      <c r="L31"/>
+    </row>
+    <row r="42" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
+      <c r="B42"/>
+      <c r="C42"/>
+      <c r="D42"/>
+      <c r="E42"/>
+      <c r="F42"/>
+      <c r="G42"/>
+      <c r="H42"/>
+      <c r="I42"/>
+      <c r="J42"/>
+      <c r="K42"/>
+      <c r="L42"/>
+    </row>
+    <row r="43" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
+      <c r="B43"/>
+      <c r="C43"/>
+      <c r="D43"/>
+      <c r="E43"/>
+      <c r="F43"/>
+      <c r="G43"/>
+      <c r="H43"/>
+      <c r="I43"/>
+      <c r="J43"/>
+      <c r="K43"/>
+      <c r="L43"/>
+    </row>
+    <row r="44" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
+      <c r="B44"/>
+      <c r="C44"/>
+      <c r="D44"/>
+      <c r="E44"/>
+      <c r="F44"/>
+      <c r="G44"/>
+      <c r="H44"/>
+      <c r="I44"/>
+      <c r="J44"/>
+      <c r="K44"/>
+      <c r="L44"/>
+    </row>
+    <row r="45" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
+      <c r="B45"/>
+      <c r="C45"/>
+      <c r="D45"/>
+      <c r="E45"/>
+      <c r="F45"/>
+      <c r="G45"/>
+      <c r="H45"/>
+      <c r="I45"/>
+      <c r="J45"/>
+      <c r="K45"/>
+      <c r="L45"/>
+    </row>
+    <row r="46" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
+      <c r="B46"/>
+      <c r="C46"/>
+      <c r="D46"/>
+      <c r="E46"/>
+      <c r="F46"/>
+      <c r="G46"/>
+      <c r="H46"/>
+      <c r="I46"/>
+      <c r="J46"/>
+      <c r="K46"/>
+      <c r="L46"/>
+    </row>
+    <row r="47" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
+      <c r="B47"/>
+      <c r="C47"/>
+      <c r="D47"/>
+      <c r="E47"/>
+      <c r="F47"/>
+      <c r="G47"/>
+      <c r="H47"/>
+      <c r="I47"/>
+      <c r="J47"/>
+      <c r="K47"/>
+      <c r="L47"/>
+    </row>
+    <row r="48" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
+      <c r="B48"/>
+      <c r="C48"/>
+      <c r="D48"/>
+      <c r="E48"/>
+      <c r="F48"/>
+      <c r="G48"/>
+      <c r="H48"/>
+      <c r="I48"/>
+      <c r="J48"/>
+      <c r="K48"/>
+      <c r="L48"/>
+    </row>
+    <row r="49" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
+      <c r="B49"/>
+      <c r="C49"/>
+      <c r="D49"/>
+      <c r="E49"/>
+      <c r="F49"/>
+      <c r="G49"/>
+      <c r="H49"/>
+      <c r="I49"/>
+      <c r="J49"/>
+      <c r="K49"/>
+      <c r="L49"/>
+    </row>
+    <row r="50" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
+      <c r="B50"/>
+      <c r="C50"/>
+      <c r="D50"/>
+      <c r="E50"/>
+      <c r="F50"/>
+      <c r="G50"/>
+      <c r="H50"/>
+      <c r="I50"/>
+      <c r="J50"/>
+      <c r="K50"/>
+      <c r="L50"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="291">
   <si>
     <t>_id</t>
   </si>
@@ -429,6 +429,12 @@
     <t>35,37,38</t>
   </si>
   <si>
+    <t>1012,2012,3012</t>
+  </si>
+  <si>
+    <t>12技能三选一</t>
+  </si>
+  <si>
     <t>暗金专属自选</t>
   </si>
   <si>
@@ -438,12 +444,24 @@
     <t>1101,1102,1103,1104,1105,1106</t>
   </si>
   <si>
+    <t>高级暗金专属</t>
+  </si>
+  <si>
+    <t>1107,1108,1109,1110,1111,1112</t>
+  </si>
+  <si>
     <t>金色专属自选</t>
   </si>
   <si>
     <t>1001,1002,1003,1004,1005,1006</t>
   </si>
   <si>
+    <t>高级金色专属</t>
+  </si>
+  <si>
+    <t>1007,1008,1009</t>
+  </si>
+  <si>
     <t>驱魔6件套</t>
   </si>
   <si>
@@ -823,9 +841,6 @@
   </si>
   <si>
     <t>暗金2阶技能专属</t>
-  </si>
-  <si>
-    <t>1107,1108,1109,1110,1111,1112</t>
   </si>
   <si>
     <t>暗金3阶技能专属</t>
@@ -1847,7 +1862,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:K102"/>
+  <dimension ref="A3:K105"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -3139,57 +3154,68 @@
         <v>128</v>
       </c>
     </row>
+    <row r="47" customHeight="1" spans="3:11">
+      <c r="C47" s="1">
+        <v>42</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E47" s="1">
+        <v>1</v>
+      </c>
+      <c r="F47" s="3">
+        <v>0</v>
+      </c>
+      <c r="G47" s="1">
+        <v>2</v>
+      </c>
+      <c r="H47" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I47" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="J47" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
     <row r="48" customFormat="1" customHeight="1" spans="1:11">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
-      <c r="C48" s="1">
-        <v>94</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="E48" s="1">
-        <v>1</v>
-      </c>
-      <c r="F48" s="3">
-        <v>0</v>
-      </c>
-      <c r="G48" s="1">
-        <v>2</v>
-      </c>
-      <c r="H48" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="I48" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="J48" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="K48" s="1" t="s">
-        <v>133</v>
-      </c>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1"/>
+      <c r="J48" s="1"/>
+      <c r="K48" s="1"/>
     </row>
     <row r="49" customFormat="1" customHeight="1" spans="1:11">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D49" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E49" s="1">
+        <v>1</v>
+      </c>
+      <c r="F49" s="3">
+        <v>0</v>
+      </c>
+      <c r="G49" s="1">
+        <v>2</v>
+      </c>
+      <c r="H49" s="5" t="s">
         <v>136</v>
-      </c>
-      <c r="E49" s="1">
-        <v>1</v>
-      </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
-      <c r="G49" s="1">
-        <v>2</v>
-      </c>
-      <c r="H49" s="5" t="s">
-        <v>134</v>
       </c>
       <c r="I49" s="5" t="s">
         <v>137</v>
@@ -3198,18 +3224,20 @@
         <v>16</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="50" customHeight="1" spans="3:11">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="50" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A50" s="1"/>
+      <c r="B50" s="1"/>
       <c r="C50" s="1">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>138</v>
       </c>
       <c r="E50" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50" s="3">
         <v>0</v>
@@ -3218,82 +3246,86 @@
         <v>2</v>
       </c>
       <c r="H50" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="I50" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="I50" s="5" t="s">
+      <c r="J50" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K50" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="51" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A51" s="1"/>
+      <c r="B51" s="1"/>
+      <c r="C51" s="1">
+        <v>94</v>
+      </c>
+      <c r="D51" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="J50" s="5" t="s">
+      <c r="E51" s="1">
+        <v>1</v>
+      </c>
+      <c r="F51" s="3">
+        <v>0</v>
+      </c>
+      <c r="G51" s="1">
+        <v>2</v>
+      </c>
+      <c r="H51" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="I51" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="K50" s="1" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="51" customHeight="1" spans="3:11">
-      <c r="C51" s="1">
-        <v>97</v>
-      </c>
-      <c r="D51" s="1" t="s">
+      <c r="J51" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K51" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="52" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A52" s="1"/>
+      <c r="B52" s="1"/>
+      <c r="C52" s="1">
+        <v>95</v>
+      </c>
+      <c r="D52" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="E51" s="1">
-        <v>1</v>
-      </c>
-      <c r="F51" s="3">
-        <v>0</v>
-      </c>
-      <c r="G51" s="1">
-        <v>2</v>
-      </c>
-      <c r="H51" s="5" t="s">
+      <c r="E52" s="1">
+        <v>1</v>
+      </c>
+      <c r="F52" s="3">
+        <v>0</v>
+      </c>
+      <c r="G52" s="1">
+        <v>2</v>
+      </c>
+      <c r="H52" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="I52" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="I51" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="J51" s="5" t="s">
+      <c r="J52" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="K51" s="1" t="s">
+      <c r="K52" s="1" t="s">
         <v>142</v>
-      </c>
-    </row>
-    <row r="52" customHeight="1" spans="3:11">
-      <c r="C52" s="1">
-        <v>98</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="E52" s="1">
-        <v>1</v>
-      </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="1">
-        <v>2</v>
-      </c>
-      <c r="H52" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="I52" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="J52" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="K52" s="1" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:11">
       <c r="C53" s="1">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="E53" s="1">
         <v>0</v>
@@ -3305,27 +3337,27 @@
         <v>2</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="I53" s="5" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="J53" s="5" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:11">
       <c r="C54" s="1">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E54" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F54" s="3">
         <v>0</v>
@@ -3334,27 +3366,27 @@
         <v>2</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="I54" s="5" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="J54" s="5" t="s">
-        <v>141</v>
+        <v>32</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:11">
       <c r="C55" s="1">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E55" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55" s="3">
         <v>0</v>
@@ -3363,50 +3395,50 @@
         <v>2</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="I55" s="5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="J55" s="5" t="s">
-        <v>141</v>
+        <v>91</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:11">
       <c r="C56" s="1">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D56" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E56" s="1">
+        <v>0</v>
+      </c>
+      <c r="F56" s="3">
+        <v>0</v>
+      </c>
+      <c r="G56" s="1">
+        <v>2</v>
+      </c>
+      <c r="H56" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="I56" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="E56" s="1">
-        <v>0</v>
-      </c>
-      <c r="F56" s="3">
-        <v>0</v>
-      </c>
-      <c r="G56" s="1">
-        <v>2</v>
-      </c>
-      <c r="H56" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="I56" s="5" t="s">
+      <c r="J56" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="J56" s="5" t="s">
-        <v>151</v>
-      </c>
       <c r="K56" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:11">
       <c r="C57" s="1">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>158</v>
@@ -3421,13 +3453,13 @@
         <v>2</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="I57" s="5" t="s">
         <v>159</v>
       </c>
       <c r="J57" s="5" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="K57" s="1" t="s">
         <v>158</v>
@@ -3435,7 +3467,7 @@
     </row>
     <row r="58" customHeight="1" spans="3:11">
       <c r="C58" s="1">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>160</v>
@@ -3450,13 +3482,13 @@
         <v>2</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="I58" s="5" t="s">
         <v>161</v>
       </c>
       <c r="J58" s="5" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="K58" s="1" t="s">
         <v>160</v>
@@ -3464,7 +3496,7 @@
     </row>
     <row r="59" customHeight="1" spans="3:11">
       <c r="C59" s="1">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>162</v>
@@ -3479,111 +3511,140 @@
         <v>2</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="I59" s="5" t="s">
         <v>163</v>
       </c>
       <c r="J59" s="5" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="K59" s="1" t="s">
         <v>162</v>
       </c>
     </row>
+    <row r="60" customHeight="1" spans="3:11">
+      <c r="C60" s="1">
+        <v>103</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E60" s="1">
+        <v>0</v>
+      </c>
+      <c r="F60" s="3">
+        <v>0</v>
+      </c>
+      <c r="G60" s="1">
+        <v>2</v>
+      </c>
+      <c r="H60" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="I60" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="J60" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="K60" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
     <row r="61" customHeight="1" spans="3:11">
       <c r="C61" s="1">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E61" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F61" s="3">
         <v>0</v>
       </c>
       <c r="G61" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H61" s="5" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="I61" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="J61" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="K61" s="1" t="s">
         <v>166</v>
-      </c>
-      <c r="J61" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="K61" s="1" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="3:11">
       <c r="C62" s="1">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D62" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E62" s="1">
+        <v>0</v>
+      </c>
+      <c r="F62" s="3">
+        <v>0</v>
+      </c>
+      <c r="G62" s="1">
+        <v>2</v>
+      </c>
+      <c r="H62" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="I62" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="E62" s="1">
-        <v>1</v>
-      </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
-      <c r="G62" s="1">
-        <v>2</v>
-      </c>
-      <c r="H62" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="I62" s="5" t="s">
+      <c r="J62" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="K62" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="64" customHeight="1" spans="3:11">
+      <c r="C64" s="1">
+        <v>106</v>
+      </c>
+      <c r="D64" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="J62" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="K62" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="63" customHeight="1" spans="3:11">
-      <c r="C63" s="1">
-        <v>108</v>
-      </c>
-      <c r="D63" s="1" t="s">
+      <c r="E64" s="1">
+        <v>1</v>
+      </c>
+      <c r="F64" s="3">
+        <v>0</v>
+      </c>
+      <c r="G64" s="1">
+        <v>1</v>
+      </c>
+      <c r="H64" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="E63" s="1">
-        <v>1</v>
-      </c>
-      <c r="F63" s="3">
-        <v>0</v>
-      </c>
-      <c r="G63" s="1">
-        <v>2</v>
-      </c>
-      <c r="H63" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="I63" s="5" t="s">
+      <c r="I64" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="J63" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="K63" s="1" t="s">
+      <c r="J64" s="5" t="s">
         <v>173</v>
+      </c>
+      <c r="K64" s="1" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:11">
       <c r="C65" s="1">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E65" s="1">
         <v>1</v>
@@ -3591,86 +3652,57 @@
       <c r="F65" s="3">
         <v>0</v>
       </c>
-      <c r="G65" s="3">
+      <c r="G65" s="1">
         <v>2</v>
       </c>
       <c r="H65" s="5" t="s">
-        <v>175</v>
+        <v>64</v>
       </c>
       <c r="I65" s="5" t="s">
         <v>176</v>
       </c>
       <c r="J65" s="5" t="s">
-        <v>87</v>
+        <v>40</v>
       </c>
       <c r="K65" s="1" t="s">
-        <v>177</v>
+        <v>83</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="3:11">
       <c r="C66" s="1">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D66" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E66" s="1">
+        <v>1</v>
+      </c>
+      <c r="F66" s="3">
+        <v>0</v>
+      </c>
+      <c r="G66" s="1">
+        <v>2</v>
+      </c>
+      <c r="H66" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="I66" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="E66" s="1">
-        <v>1</v>
-      </c>
-      <c r="F66" s="3">
-        <v>0</v>
-      </c>
-      <c r="G66" s="3">
-        <v>2</v>
-      </c>
-      <c r="H66" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="I66" s="5" t="s">
+      <c r="J66" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K66" s="1" t="s">
         <v>179</v>
-      </c>
-      <c r="J66" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="K66" s="1" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="67" customHeight="1" spans="3:11">
-      <c r="C67" s="1">
-        <v>111</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="E67" s="1">
-        <v>1</v>
-      </c>
-      <c r="F67" s="3">
-        <v>0</v>
-      </c>
-      <c r="G67" s="3">
-        <v>2</v>
-      </c>
-      <c r="H67" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="I67" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="J67" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="K67" s="1" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:11">
       <c r="C68" s="1">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="E68" s="1">
         <v>1</v>
@@ -3682,24 +3714,24 @@
         <v>2</v>
       </c>
       <c r="H68" s="5" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="I68" s="5" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="J68" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:11">
       <c r="C69" s="1">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="E69" s="1">
         <v>1</v>
@@ -3711,24 +3743,24 @@
         <v>2</v>
       </c>
       <c r="H69" s="5" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="I69" s="5" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="J69" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:11">
       <c r="C70" s="1">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E70" s="1">
         <v>1</v>
@@ -3740,52 +3772,81 @@
         <v>2</v>
       </c>
       <c r="H70" s="5" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="I70" s="5" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="J70" s="5" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:11">
       <c r="C71" s="1">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D71" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E71" s="1">
+        <v>1</v>
+      </c>
+      <c r="F71" s="3">
+        <v>0</v>
+      </c>
+      <c r="G71" s="3">
+        <v>2</v>
+      </c>
+      <c r="H71" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="I71" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="J71" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K71" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="72" customHeight="1" spans="3:11">
+      <c r="C72" s="1">
+        <v>113</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="E72" s="1">
+        <v>1</v>
+      </c>
+      <c r="F72" s="3">
+        <v>0</v>
+      </c>
+      <c r="G72" s="3">
+        <v>2</v>
+      </c>
+      <c r="H72" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="I72" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="E71" s="1">
-        <v>1</v>
-      </c>
-      <c r="F71" s="3">
-        <v>0</v>
-      </c>
-      <c r="G71" s="3">
-        <v>2</v>
-      </c>
-      <c r="H71" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="I71" s="5" t="s">
+      <c r="J72" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K72" s="1" t="s">
         <v>195</v>
-      </c>
-      <c r="J71" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="K71" s="1" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:11">
       <c r="C73" s="1">
-        <v>118</v>
-      </c>
-      <c r="D73" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D73" s="1" t="s">
         <v>196</v>
       </c>
       <c r="E73" s="1">
@@ -3798,24 +3859,24 @@
         <v>2</v>
       </c>
       <c r="H73" s="5" t="s">
-        <v>175</v>
+        <v>197</v>
       </c>
       <c r="I73" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J73" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="K73" s="3" t="s">
-        <v>196</v>
+        <v>91</v>
+      </c>
+      <c r="K73" s="1" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:11">
       <c r="C74" s="1">
-        <v>119</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>198</v>
+        <v>115</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>200</v>
       </c>
       <c r="E74" s="1">
         <v>1</v>
@@ -3827,50 +3888,21 @@
         <v>2</v>
       </c>
       <c r="H74" s="5" t="s">
-        <v>175</v>
+        <v>136</v>
       </c>
       <c r="I74" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="J74" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="K74" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="75" customHeight="1" spans="3:11">
-      <c r="C75" s="1">
-        <v>120</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="E75" s="1">
-        <v>1</v>
-      </c>
-      <c r="F75" s="3">
-        <v>0</v>
-      </c>
-      <c r="G75" s="3">
-        <v>2</v>
-      </c>
-      <c r="H75" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="I75" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="J75" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="K75" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="K74" s="1" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:11">
       <c r="C76" s="1">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>202</v>
@@ -3885,7 +3917,7 @@
         <v>2</v>
       </c>
       <c r="H76" s="5" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="I76" s="5" t="s">
         <v>203</v>
@@ -3899,7 +3931,7 @@
     </row>
     <row r="77" customHeight="1" spans="3:11">
       <c r="C77" s="1">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>204</v>
@@ -3914,7 +3946,7 @@
         <v>2</v>
       </c>
       <c r="H77" s="5" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="I77" s="5" t="s">
         <v>205</v>
@@ -3928,7 +3960,7 @@
     </row>
     <row r="78" customHeight="1" spans="3:11">
       <c r="C78" s="1">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>206</v>
@@ -3943,7 +3975,7 @@
         <v>2</v>
       </c>
       <c r="H78" s="5" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="I78" s="5" t="s">
         <v>207</v>
@@ -3957,9 +3989,9 @@
     </row>
     <row r="79" customHeight="1" spans="3:11">
       <c r="C79" s="1">
-        <v>124</v>
-      </c>
-      <c r="D79" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="D79" s="3" t="s">
         <v>208</v>
       </c>
       <c r="E79" s="1">
@@ -3972,7 +4004,7 @@
         <v>2</v>
       </c>
       <c r="H79" s="5" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="I79" s="5" t="s">
         <v>209</v>
@@ -3980,15 +4012,15 @@
       <c r="J79" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="K79" s="1" t="s">
+      <c r="K79" s="3" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="3:11">
       <c r="C80" s="1">
-        <v>125</v>
-      </c>
-      <c r="D80" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D80" s="3" t="s">
         <v>210</v>
       </c>
       <c r="E80" s="1">
@@ -4001,7 +4033,7 @@
         <v>2</v>
       </c>
       <c r="H80" s="5" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="I80" s="5" t="s">
         <v>211</v>
@@ -4009,16 +4041,45 @@
       <c r="J80" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="K80" s="1" t="s">
+      <c r="K80" s="3" t="s">
         <v>210</v>
+      </c>
+    </row>
+    <row r="81" customHeight="1" spans="3:11">
+      <c r="C81" s="1">
+        <v>123</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="E81" s="1">
+        <v>1</v>
+      </c>
+      <c r="F81" s="3">
+        <v>0</v>
+      </c>
+      <c r="G81" s="3">
+        <v>2</v>
+      </c>
+      <c r="H81" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="I81" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J81" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K81" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="3:11">
       <c r="C82" s="1">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E82" s="1">
         <v>1</v>
@@ -4030,140 +4091,111 @@
         <v>2</v>
       </c>
       <c r="H82" s="5" t="s">
-        <v>134</v>
+        <v>181</v>
       </c>
       <c r="I82" s="5" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="J82" s="5" t="s">
-        <v>40</v>
+        <v>87</v>
       </c>
       <c r="K82" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="3:11">
       <c r="C83" s="1">
+        <v>125</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="E83" s="1">
+        <v>1</v>
+      </c>
+      <c r="F83" s="3">
+        <v>0</v>
+      </c>
+      <c r="G83" s="3">
+        <v>2</v>
+      </c>
+      <c r="H83" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="I83" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="J83" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K83" s="1" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="85" customHeight="1" spans="3:11">
+      <c r="C85" s="1">
+        <v>127</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="E85" s="1">
+        <v>1</v>
+      </c>
+      <c r="F85" s="3">
+        <v>0</v>
+      </c>
+      <c r="G85" s="3">
+        <v>2</v>
+      </c>
+      <c r="H85" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="I85" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="J85" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K85" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="86" customHeight="1" spans="3:11">
+      <c r="C86" s="1">
         <v>128</v>
       </c>
-      <c r="D83" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="E83" s="1">
-        <v>1</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>2</v>
-      </c>
-      <c r="H83" s="5" t="s">
+      <c r="D86" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="E86" s="1">
+        <v>1</v>
+      </c>
+      <c r="F86" s="3">
+        <v>0</v>
+      </c>
+      <c r="G86" s="3">
+        <v>2</v>
+      </c>
+      <c r="H86" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="I83" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="J83" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="K83" s="1" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="94" customHeight="1" spans="3:11">
-      <c r="C94" s="1">
-        <v>201</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="E94" s="1">
-        <v>1</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>2</v>
-      </c>
-      <c r="H94" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="I94" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="J94" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K94" s="1" t="s">
+      <c r="I86" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="J86" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="K86" s="1" t="s">
         <v>220</v>
-      </c>
-    </row>
-    <row r="95" customHeight="1" spans="3:11">
-      <c r="C95" s="1">
-        <v>202</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="E95" s="1">
-        <v>1</v>
-      </c>
-      <c r="F95" s="3">
-        <v>0</v>
-      </c>
-      <c r="G95" s="3">
-        <v>2</v>
-      </c>
-      <c r="H95" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="I95" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="J95" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K95" s="1" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="96" customHeight="1" spans="3:11">
-      <c r="C96" s="1">
-        <v>203</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="E96" s="1">
-        <v>1</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>2</v>
-      </c>
-      <c r="H96" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="I96" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="J96" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K96" s="1" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="97" customHeight="1" spans="3:11">
       <c r="C97" s="1">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="E97" s="1">
         <v>1</v>
@@ -4175,24 +4207,24 @@
         <v>2</v>
       </c>
       <c r="H97" s="5" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I97" s="5" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="J97" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K97" s="1" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="98" customHeight="1" spans="3:11">
       <c r="C98" s="1">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E98" s="1">
         <v>1</v>
@@ -4204,24 +4236,24 @@
         <v>2</v>
       </c>
       <c r="H98" s="5" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I98" s="5" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="J98" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K98" s="1" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="99" customHeight="1" spans="3:11">
       <c r="C99" s="1">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="E99" s="1">
         <v>1</v>
@@ -4233,24 +4265,24 @@
         <v>2</v>
       </c>
       <c r="H99" s="5" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I99" s="5" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="J99" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K99" s="1" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="100" customHeight="1" spans="3:11">
       <c r="C100" s="1">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="E100" s="1">
         <v>1</v>
@@ -4262,24 +4294,24 @@
         <v>2</v>
       </c>
       <c r="H100" s="5" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="I100" s="5" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="J100" s="5" t="s">
-        <v>239</v>
+        <v>32</v>
       </c>
       <c r="K100" s="1" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
     </row>
     <row r="101" customHeight="1" spans="3:11">
       <c r="C101" s="1">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="E101" s="1">
         <v>1</v>
@@ -4290,37 +4322,124 @@
       <c r="G101" s="3">
         <v>2</v>
       </c>
+      <c r="H101" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="I101" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="J101" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="K101" s="1" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
     </row>
     <row r="102" customHeight="1" spans="3:11">
       <c r="C102" s="1">
+        <v>206</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="E102" s="1">
+        <v>1</v>
+      </c>
+      <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
+        <v>2</v>
+      </c>
+      <c r="H102" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="I102" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="J102" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K102" s="1" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="103" customHeight="1" spans="3:11">
+      <c r="C103" s="1">
+        <v>207</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="E103" s="1">
+        <v>1</v>
+      </c>
+      <c r="F103" s="3">
+        <v>0</v>
+      </c>
+      <c r="G103" s="3">
+        <v>2</v>
+      </c>
+      <c r="H103" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="I103" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="J103" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="K103" s="1" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="104" customHeight="1" spans="3:11">
+      <c r="C104" s="1">
+        <v>208</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="E104" s="1">
+        <v>1</v>
+      </c>
+      <c r="F104" s="3">
+        <v>0</v>
+      </c>
+      <c r="G104" s="3">
+        <v>2</v>
+      </c>
+      <c r="K104" s="1" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="105" customHeight="1" spans="3:11">
+      <c r="C105" s="1">
         <v>209</v>
       </c>
-      <c r="D102" s="1" t="s">
+      <c r="D105" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="E105" s="1">
+        <v>1</v>
+      </c>
+      <c r="F105" s="3">
+        <v>0</v>
+      </c>
+      <c r="G105" s="3">
+        <v>2</v>
+      </c>
+      <c r="H105" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="E102" s="1">
-        <v>1</v>
-      </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
-      <c r="G102" s="3">
-        <v>2</v>
-      </c>
-      <c r="H102" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="I102" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="J102" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="K102" s="1" t="s">
+      <c r="I105" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="J105" s="5" t="s">
         <v>245</v>
+      </c>
+      <c r="K105" s="1" t="s">
+        <v>251</v>
       </c>
     </row>
   </sheetData>
@@ -4447,7 +4566,7 @@
         <v>1001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="E6" s="1">
         <v>0</v>
@@ -4462,13 +4581,13 @@
         <v>14</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="J6" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4476,7 +4595,7 @@
         <v>1002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="E7" s="1">
         <v>0</v>
@@ -4491,13 +4610,13 @@
         <v>14</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="J7" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4505,7 +4624,7 @@
         <v>1003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="E8" s="1">
         <v>0</v>
@@ -4520,13 +4639,13 @@
         <v>14</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="J8" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4534,7 +4653,7 @@
         <v>1004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="E9" s="1">
         <v>0</v>
@@ -4549,13 +4668,13 @@
         <v>14</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="J9" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4563,7 +4682,7 @@
         <v>1005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E10" s="1">
         <v>0</v>
@@ -4578,13 +4697,13 @@
         <v>14</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="J10" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4592,7 +4711,7 @@
         <v>1006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E11" s="1">
         <v>0</v>
@@ -4607,13 +4726,13 @@
         <v>14</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="J11" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4621,7 +4740,7 @@
         <v>1007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="E12" s="1">
         <v>0</v>
@@ -4636,13 +4755,13 @@
         <v>14</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="J12" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4650,7 +4769,7 @@
         <v>1008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="E13" s="1">
         <v>0</v>
@@ -4665,13 +4784,13 @@
         <v>14</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="J13" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4679,7 +4798,7 @@
         <v>1009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="E14" s="1">
         <v>0</v>
@@ -4694,13 +4813,13 @@
         <v>14</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="J14" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="18" customHeight="1"/>
@@ -4709,7 +4828,7 @@
         <v>1101</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="E16" s="1">
         <v>0</v>
@@ -4724,13 +4843,13 @@
         <v>14</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="J16" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4738,7 +4857,7 @@
         <v>1102</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="E17" s="1">
         <v>0</v>
@@ -4753,13 +4872,13 @@
         <v>14</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>265</v>
+        <v>139</v>
       </c>
       <c r="J17" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4767,7 +4886,7 @@
         <v>1103</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="E18" s="1">
         <v>0</v>
@@ -4782,13 +4901,13 @@
         <v>14</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="J18" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4796,7 +4915,7 @@
         <v>1104</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="E19" s="1">
         <v>0</v>
@@ -4811,13 +4930,13 @@
         <v>14</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="J19" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4825,7 +4944,7 @@
         <v>1105</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="E20" s="1">
         <v>0</v>
@@ -4840,13 +4959,13 @@
         <v>14</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="J20" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4854,7 +4973,7 @@
         <v>1106</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="E21" s="1">
         <v>0</v>
@@ -4869,13 +4988,13 @@
         <v>14</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="J21" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4883,7 +5002,7 @@
         <v>1107</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="E22" s="1">
         <v>0</v>
@@ -4898,13 +5017,13 @@
         <v>14</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="J22" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4912,7 +5031,7 @@
         <v>1108</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="E23" s="1">
         <v>0</v>
@@ -4927,13 +5046,13 @@
         <v>14</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="J23" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4941,7 +5060,7 @@
         <v>1109</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="E24" s="1">
         <v>0</v>
@@ -4956,13 +5075,13 @@
         <v>14</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="J24" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4970,7 +5089,7 @@
         <v>1110</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="E25" s="1">
         <v>0</v>
@@ -4985,13 +5104,13 @@
         <v>14</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="J25" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4999,7 +5118,7 @@
         <v>1111</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="E26" s="1">
         <v>0</v>
@@ -5014,13 +5133,13 @@
         <v>14</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="J26" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5028,7 +5147,7 @@
         <v>1112</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="E27" s="1">
         <v>0</v>
@@ -5043,13 +5162,13 @@
         <v>14</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="J27" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="312">
   <si>
     <t>_id</t>
   </si>
@@ -459,7 +459,10 @@
     <t>高级金色专属</t>
   </si>
   <si>
-    <t>1007,1008,1009</t>
+    <t>4,4,4,4,4,4,4,4,4</t>
+  </si>
+  <si>
+    <t>1007,1008,1009,1001,1002,1003,1004,1005,1006</t>
   </si>
   <si>
     <t>驱魔6件套</t>
@@ -486,9 +489,6 @@
     <t>专属自选</t>
   </si>
   <si>
-    <t>4,4,4,4,4,4,4,4,4</t>
-  </si>
-  <si>
     <t>99,100,101,102,103,104,105,96</t>
   </si>
   <si>
@@ -786,121 +786,184 @@
     <t>50资质金宠自选</t>
   </si>
   <si>
+    <t>金色刺杀自选</t>
+  </si>
+  <si>
     <t>金色刺杀专属包</t>
   </si>
   <si>
+    <t>金色雷电自选</t>
+  </si>
+  <si>
+    <t>1007,1008,1009,1010,1011,1012</t>
+  </si>
+  <si>
     <t>金色雷电专属包</t>
   </si>
   <si>
-    <t>1007,1008,1009,1010,1011,1012</t>
+    <t>金色火符自选</t>
+  </si>
+  <si>
+    <t>1013,1014,1015,1016,1017,1018</t>
   </si>
   <si>
     <t>金色火符专属包</t>
   </si>
   <si>
-    <t>1013,1014,1015,1016,1017,1018</t>
+    <t>金色战吼自选</t>
+  </si>
+  <si>
+    <t>1019,1020,1021,1022,1023,1024</t>
   </si>
   <si>
     <t>金色战吼专属包</t>
   </si>
   <si>
-    <t>1019,1020,1021,1022,1023,1024</t>
+    <t>金色瞬移自选</t>
+  </si>
+  <si>
+    <t>1025,1026,1027,1028,1029,1030</t>
   </si>
   <si>
     <t>金色瞬移专属包</t>
   </si>
   <si>
-    <t>1025,1026,1027,1028,1029,1030</t>
+    <t>金色隐身自选</t>
+  </si>
+  <si>
+    <t>1031,1032,1033,1034,1035,1036</t>
   </si>
   <si>
     <t>金色隐身专属包</t>
   </si>
   <si>
-    <t>1031,1032,1033,1034,1035,1036</t>
+    <t>金色裂地自选</t>
+  </si>
+  <si>
+    <t>1037,1038,1039,1040,1041,1042</t>
   </si>
   <si>
     <t>金色裂地专属包</t>
   </si>
   <si>
-    <t>1037,1038,1039,1040,1041,1042</t>
+    <t>金色分身自选</t>
+  </si>
+  <si>
+    <t>1043,1044,1045,1046,1047,1048</t>
   </si>
   <si>
     <t>金色分身专属包</t>
   </si>
   <si>
-    <t>1043,1044,1045,1046,1047,1048</t>
+    <t>金色无极自选</t>
+  </si>
+  <si>
+    <t>1049,1050,1051,1052,1053,1054</t>
   </si>
   <si>
     <t>金色无极专属包</t>
   </si>
   <si>
-    <t>1049,1050,1051,1052,1053,1054</t>
+    <t>暗金1阶自选</t>
   </si>
   <si>
     <t>暗金1阶技能专属</t>
   </si>
   <si>
+    <t>暗金2阶自选</t>
+  </si>
+  <si>
     <t>暗金2阶技能专属</t>
   </si>
   <si>
+    <t>暗金3阶自选</t>
+  </si>
+  <si>
+    <t>1113,1114,1115,1116,1117,1118</t>
+  </si>
+  <si>
     <t>暗金3阶技能专属</t>
   </si>
   <si>
-    <t>1113,1114,1115,1116,1117,1118</t>
+    <t>暗金4阶自选</t>
+  </si>
+  <si>
+    <t>1119,1120,1121,1122,1123,1124</t>
   </si>
   <si>
     <t>暗金4阶技能专属</t>
   </si>
   <si>
-    <t>1119,1120,1121,1122,1123,1124</t>
+    <t>暗金5阶自选</t>
+  </si>
+  <si>
+    <t>1125,1126,1127,1128,1129,1130</t>
   </si>
   <si>
     <t>暗金5阶技能专属</t>
   </si>
   <si>
-    <t>1125,1126,1127,1128,1129,1130</t>
+    <t>暗金6阶自选</t>
+  </si>
+  <si>
+    <t>1131,1132,1133,1134,1135,1136</t>
   </si>
   <si>
     <t>暗金6阶技能专属</t>
   </si>
   <si>
-    <t>1131,1132,1133,1134,1135,1136</t>
+    <t>暗金7阶自选</t>
+  </si>
+  <si>
+    <t>1137,1138,1139,1140,1141,1142</t>
   </si>
   <si>
     <t>暗金7阶技能专属</t>
   </si>
   <si>
-    <t>1137,1138,1139,1140,1141,1142</t>
+    <t>暗金8阶自选</t>
+  </si>
+  <si>
+    <t>1143,1144,1145,1146,1147,1148</t>
   </si>
   <si>
     <t>暗金8阶技能专属</t>
   </si>
   <si>
-    <t>1143,1144,1145,1146,1147,1148</t>
+    <t>暗金9阶自选</t>
+  </si>
+  <si>
+    <t>1149,1150,1151,1152,1153,1154</t>
   </si>
   <si>
     <t>暗金9阶技能专属</t>
   </si>
   <si>
-    <t>1149,1150,1151,1152,1153,1154</t>
+    <t>暗金10阶自选</t>
+  </si>
+  <si>
+    <t>1155,1156,1157,1158,1159,1160</t>
   </si>
   <si>
     <t>暗金10阶技能专属</t>
   </si>
   <si>
-    <t>1155,1156,1157,1158,1159,1160</t>
+    <t>暗金11阶自选</t>
+  </si>
+  <si>
+    <t>1161,1162,1163,1164,1165,1166</t>
   </si>
   <si>
     <t>暗金11阶技能专属</t>
   </si>
   <si>
-    <t>1161,1162,1163,1164,1165,1166</t>
+    <t>暗金12阶自选</t>
+  </si>
+  <si>
+    <t>1167,1168,1169,1170,1171,1172</t>
   </si>
   <si>
     <t>暗金12阶技能专属</t>
-  </si>
-  <si>
-    <t>1167,1168,1169,1170,1171,1172</t>
   </si>
 </sst>
 </file>
@@ -3308,13 +3371,13 @@
         <v>2</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="I52" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J52" s="5" t="s">
-        <v>32</v>
+        <v>87</v>
       </c>
       <c r="K52" s="1" t="s">
         <v>142</v>
@@ -3325,7 +3388,7 @@
         <v>96</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E53" s="1">
         <v>0</v>
@@ -3337,16 +3400,16 @@
         <v>2</v>
       </c>
       <c r="H53" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="I53" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="J53" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="K53" s="1" t="s">
         <v>145</v>
-      </c>
-      <c r="I53" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="J53" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="K53" s="1" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:11">
@@ -3354,7 +3417,7 @@
         <v>97</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E54" s="1">
         <v>1</v>
@@ -3366,16 +3429,16 @@
         <v>2</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I54" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J54" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:11">
@@ -3383,7 +3446,7 @@
         <v>98</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E55" s="1">
         <v>1</v>
@@ -3395,7 +3458,7 @@
         <v>2</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="I55" s="5" t="s">
         <v>153</v>
@@ -3404,7 +3467,7 @@
         <v>91</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:11">
@@ -3453,13 +3516,13 @@
         <v>2</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I57" s="5" t="s">
         <v>159</v>
       </c>
       <c r="J57" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K57" s="1" t="s">
         <v>158</v>
@@ -3482,13 +3545,13 @@
         <v>2</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I58" s="5" t="s">
         <v>161</v>
       </c>
       <c r="J58" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K58" s="1" t="s">
         <v>160</v>
@@ -4569,7 +4632,7 @@
         <v>252</v>
       </c>
       <c r="E6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="3">
         <v>0</v>
@@ -4587,7 +4650,7 @@
         <v>16</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4595,10 +4658,10 @@
         <v>1002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="3">
         <v>0</v>
@@ -4610,13 +4673,13 @@
         <v>14</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J7" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4624,10 +4687,10 @@
         <v>1003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="3">
         <v>0</v>
@@ -4639,13 +4702,13 @@
         <v>14</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="J8" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4653,10 +4716,10 @@
         <v>1004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="E9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="3">
         <v>0</v>
@@ -4668,13 +4731,13 @@
         <v>14</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="J9" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4682,10 +4745,10 @@
         <v>1005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="E10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="3">
         <v>0</v>
@@ -4697,13 +4760,13 @@
         <v>14</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="J10" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4711,10 +4774,10 @@
         <v>1006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="E11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="3">
         <v>0</v>
@@ -4726,13 +4789,13 @@
         <v>14</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="J11" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4740,10 +4803,10 @@
         <v>1007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="E12" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" s="3">
         <v>0</v>
@@ -4755,13 +4818,13 @@
         <v>14</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="J12" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4769,10 +4832,10 @@
         <v>1008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="E13" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="3">
         <v>0</v>
@@ -4784,13 +4847,13 @@
         <v>14</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="J13" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4798,10 +4861,10 @@
         <v>1009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="E14" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="3">
         <v>0</v>
@@ -4813,13 +4876,13 @@
         <v>14</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="J14" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="18" customHeight="1"/>
@@ -4828,10 +4891,10 @@
         <v>1101</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="E16" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" s="3">
         <v>0</v>
@@ -4849,7 +4912,7 @@
         <v>16</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4857,10 +4920,10 @@
         <v>1102</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="E17" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" s="3">
         <v>0</v>
@@ -4878,7 +4941,7 @@
         <v>16</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4886,10 +4949,10 @@
         <v>1103</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="E18" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" s="3">
         <v>0</v>
@@ -4901,13 +4964,13 @@
         <v>14</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="J18" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>271</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4915,10 +4978,10 @@
         <v>1104</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="E19" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" s="3">
         <v>0</v>
@@ -4930,13 +4993,13 @@
         <v>14</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="J19" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>273</v>
+        <v>287</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4944,10 +5007,10 @@
         <v>1105</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="E20" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" s="3">
         <v>0</v>
@@ -4959,13 +5022,13 @@
         <v>14</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="J20" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>275</v>
+        <v>290</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4973,10 +5036,10 @@
         <v>1106</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="E21" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" s="3">
         <v>0</v>
@@ -4988,13 +5051,13 @@
         <v>14</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="J21" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>277</v>
+        <v>293</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5002,10 +5065,10 @@
         <v>1107</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>279</v>
+        <v>294</v>
       </c>
       <c r="E22" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" s="3">
         <v>0</v>
@@ -5017,13 +5080,13 @@
         <v>14</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>280</v>
+        <v>295</v>
       </c>
       <c r="J22" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>279</v>
+        <v>296</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5031,10 +5094,10 @@
         <v>1108</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>281</v>
+        <v>297</v>
       </c>
       <c r="E23" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" s="3">
         <v>0</v>
@@ -5046,13 +5109,13 @@
         <v>14</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>282</v>
+        <v>298</v>
       </c>
       <c r="J23" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>281</v>
+        <v>299</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5060,10 +5123,10 @@
         <v>1109</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>283</v>
+        <v>300</v>
       </c>
       <c r="E24" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" s="3">
         <v>0</v>
@@ -5075,13 +5138,13 @@
         <v>14</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>284</v>
+        <v>301</v>
       </c>
       <c r="J24" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>283</v>
+        <v>302</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5089,10 +5152,10 @@
         <v>1110</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>285</v>
+        <v>303</v>
       </c>
       <c r="E25" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" s="3">
         <v>0</v>
@@ -5104,13 +5167,13 @@
         <v>14</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>286</v>
+        <v>304</v>
       </c>
       <c r="J25" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>285</v>
+        <v>305</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5118,10 +5181,10 @@
         <v>1111</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>287</v>
+        <v>306</v>
       </c>
       <c r="E26" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" s="3">
         <v>0</v>
@@ -5133,13 +5196,13 @@
         <v>14</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>288</v>
+        <v>307</v>
       </c>
       <c r="J26" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>287</v>
+        <v>308</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5147,10 +5210,10 @@
         <v>1112</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>289</v>
+        <v>309</v>
       </c>
       <c r="E27" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" s="3">
         <v>0</v>
@@ -5162,13 +5225,13 @@
         <v>14</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="J27" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>289</v>
+        <v>311</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="313">
   <si>
     <t>_id</t>
   </si>
@@ -427,6 +427,9 @@
   </si>
   <si>
     <t>35,37,38</t>
+  </si>
+  <si>
+    <t>12阶技能自选</t>
   </si>
   <si>
     <t>1012,2012,3012</t>
@@ -3222,7 +3225,7 @@
         <v>42</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>98</v>
+        <v>133</v>
       </c>
       <c r="E47" s="1">
         <v>1</v>
@@ -3237,13 +3240,13 @@
         <v>30</v>
       </c>
       <c r="I47" s="5" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J47" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="48" customFormat="1" customHeight="1" spans="1:11">
@@ -3266,7 +3269,7 @@
         <v>90</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E49" s="1">
         <v>1</v>
@@ -3278,16 +3281,16 @@
         <v>2</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I49" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J49" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="50" customFormat="1" customHeight="1" spans="1:11">
@@ -3297,7 +3300,7 @@
         <v>91</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E50" s="1">
         <v>1</v>
@@ -3309,16 +3312,16 @@
         <v>2</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I50" s="5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J50" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="51" customFormat="1" customHeight="1" spans="1:11">
@@ -3328,7 +3331,7 @@
         <v>94</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E51" s="1">
         <v>1</v>
@@ -3340,16 +3343,16 @@
         <v>2</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I51" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J51" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="52" customFormat="1" customHeight="1" spans="1:11">
@@ -3359,7 +3362,7 @@
         <v>95</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E52" s="1">
         <v>1</v>
@@ -3371,16 +3374,16 @@
         <v>2</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I52" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J52" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:11">
@@ -3388,7 +3391,7 @@
         <v>96</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E53" s="1">
         <v>0</v>
@@ -3400,16 +3403,16 @@
         <v>2</v>
       </c>
       <c r="H53" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="I53" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="J53" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="K53" s="1" t="s">
         <v>146</v>
-      </c>
-      <c r="I53" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="J53" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="K53" s="1" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:11">
@@ -3417,7 +3420,7 @@
         <v>97</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E54" s="1">
         <v>1</v>
@@ -3429,16 +3432,16 @@
         <v>2</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I54" s="5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J54" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:11">
@@ -3446,7 +3449,7 @@
         <v>98</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E55" s="1">
         <v>1</v>
@@ -3458,16 +3461,16 @@
         <v>2</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I55" s="5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J55" s="5" t="s">
         <v>91</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:11">
@@ -3475,7 +3478,7 @@
         <v>99</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E56" s="1">
         <v>0</v>
@@ -3487,16 +3490,16 @@
         <v>2</v>
       </c>
       <c r="H56" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="I56" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="J56" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="K56" s="1" t="s">
         <v>155</v>
-      </c>
-      <c r="I56" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="J56" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="K56" s="1" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:11">
@@ -3504,7 +3507,7 @@
         <v>100</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E57" s="1">
         <v>0</v>
@@ -3516,16 +3519,16 @@
         <v>2</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I57" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="J57" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="K57" s="1" t="s">
         <v>159</v>
-      </c>
-      <c r="J57" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="K57" s="1" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:11">
@@ -3533,7 +3536,7 @@
         <v>101</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E58" s="1">
         <v>0</v>
@@ -3545,16 +3548,16 @@
         <v>2</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I58" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="J58" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="K58" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="J58" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="K58" s="1" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:11">
@@ -3562,7 +3565,7 @@
         <v>102</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E59" s="1">
         <v>0</v>
@@ -3574,16 +3577,16 @@
         <v>2</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I59" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="J59" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="K59" s="1" t="s">
         <v>163</v>
-      </c>
-      <c r="J59" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="K59" s="1" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="3:11">
@@ -3591,7 +3594,7 @@
         <v>103</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E60" s="1">
         <v>0</v>
@@ -3603,16 +3606,16 @@
         <v>2</v>
       </c>
       <c r="H60" s="5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I60" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="J60" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="K60" s="1" t="s">
         <v>165</v>
-      </c>
-      <c r="J60" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="K60" s="1" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="3:11">
@@ -3620,7 +3623,7 @@
         <v>104</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E61" s="1">
         <v>0</v>
@@ -3632,16 +3635,16 @@
         <v>2</v>
       </c>
       <c r="H61" s="5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I61" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="J61" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="K61" s="1" t="s">
         <v>167</v>
-      </c>
-      <c r="J61" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="K61" s="1" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="3:11">
@@ -3649,7 +3652,7 @@
         <v>105</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E62" s="1">
         <v>0</v>
@@ -3661,16 +3664,16 @@
         <v>2</v>
       </c>
       <c r="H62" s="5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I62" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="J62" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="K62" s="1" t="s">
         <v>169</v>
-      </c>
-      <c r="J62" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="K62" s="1" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:11">
@@ -3678,7 +3681,7 @@
         <v>106</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E64" s="1">
         <v>1</v>
@@ -3690,16 +3693,16 @@
         <v>1</v>
       </c>
       <c r="H64" s="5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I64" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J64" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K64" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:11">
@@ -3707,7 +3710,7 @@
         <v>107</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E65" s="1">
         <v>1</v>
@@ -3722,7 +3725,7 @@
         <v>64</v>
       </c>
       <c r="I65" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J65" s="5" t="s">
         <v>40</v>
@@ -3736,7 +3739,7 @@
         <v>108</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E66" s="1">
         <v>1</v>
@@ -3751,13 +3754,13 @@
         <v>64</v>
       </c>
       <c r="I66" s="5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="J66" s="5" t="s">
         <v>40</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:11">
@@ -3765,7 +3768,7 @@
         <v>109</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E68" s="1">
         <v>1</v>
@@ -3777,16 +3780,16 @@
         <v>2</v>
       </c>
       <c r="H68" s="5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I68" s="5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J68" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:11">
@@ -3794,7 +3797,7 @@
         <v>110</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E69" s="1">
         <v>1</v>
@@ -3806,16 +3809,16 @@
         <v>2</v>
       </c>
       <c r="H69" s="5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I69" s="5" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J69" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:11">
@@ -3823,7 +3826,7 @@
         <v>111</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E70" s="1">
         <v>1</v>
@@ -3835,16 +3838,16 @@
         <v>2</v>
       </c>
       <c r="H70" s="5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I70" s="5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J70" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:11">
@@ -3852,7 +3855,7 @@
         <v>112</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E71" s="1">
         <v>1</v>
@@ -3864,16 +3867,16 @@
         <v>2</v>
       </c>
       <c r="H71" s="5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I71" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J71" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:11">
@@ -3881,7 +3884,7 @@
         <v>113</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E72" s="1">
         <v>1</v>
@@ -3893,16 +3896,16 @@
         <v>2</v>
       </c>
       <c r="H72" s="5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I72" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J72" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:11">
@@ -3910,7 +3913,7 @@
         <v>114</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E73" s="1">
         <v>1</v>
@@ -3922,16 +3925,16 @@
         <v>2</v>
       </c>
       <c r="H73" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I73" s="5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J73" s="5" t="s">
         <v>91</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:11">
@@ -3939,7 +3942,7 @@
         <v>115</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E74" s="1">
         <v>1</v>
@@ -3951,16 +3954,16 @@
         <v>2</v>
       </c>
       <c r="H74" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I74" s="5" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="J74" s="5" t="s">
         <v>40</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:11">
@@ -3968,7 +3971,7 @@
         <v>118</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E76" s="1">
         <v>1</v>
@@ -3980,16 +3983,16 @@
         <v>2</v>
       </c>
       <c r="H76" s="5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I76" s="5" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="J76" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K76" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:11">
@@ -3997,7 +4000,7 @@
         <v>119</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E77" s="1">
         <v>1</v>
@@ -4009,16 +4012,16 @@
         <v>2</v>
       </c>
       <c r="H77" s="5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I77" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="J77" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K77" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="3:11">
@@ -4026,7 +4029,7 @@
         <v>120</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E78" s="1">
         <v>1</v>
@@ -4038,16 +4041,16 @@
         <v>2</v>
       </c>
       <c r="H78" s="5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I78" s="5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="J78" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K78" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="3:11">
@@ -4055,7 +4058,7 @@
         <v>121</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E79" s="1">
         <v>1</v>
@@ -4067,16 +4070,16 @@
         <v>2</v>
       </c>
       <c r="H79" s="5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I79" s="5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="J79" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="3:11">
@@ -4084,7 +4087,7 @@
         <v>122</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E80" s="1">
         <v>1</v>
@@ -4096,16 +4099,16 @@
         <v>2</v>
       </c>
       <c r="H80" s="5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I80" s="5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J80" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K80" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="3:11">
@@ -4113,7 +4116,7 @@
         <v>123</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E81" s="1">
         <v>1</v>
@@ -4125,16 +4128,16 @@
         <v>2</v>
       </c>
       <c r="H81" s="5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I81" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J81" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K81" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="3:11">
@@ -4142,7 +4145,7 @@
         <v>124</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E82" s="1">
         <v>1</v>
@@ -4154,16 +4157,16 @@
         <v>2</v>
       </c>
       <c r="H82" s="5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I82" s="5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J82" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K82" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="3:11">
@@ -4171,7 +4174,7 @@
         <v>125</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E83" s="1">
         <v>1</v>
@@ -4183,16 +4186,16 @@
         <v>2</v>
       </c>
       <c r="H83" s="5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I83" s="5" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="J83" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="85" customHeight="1" spans="3:11">
@@ -4200,7 +4203,7 @@
         <v>127</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E85" s="1">
         <v>1</v>
@@ -4212,16 +4215,16 @@
         <v>2</v>
       </c>
       <c r="H85" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I85" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J85" s="5" t="s">
         <v>40</v>
       </c>
       <c r="K85" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="3:11">
@@ -4229,7 +4232,7 @@
         <v>128</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E86" s="1">
         <v>1</v>
@@ -4244,13 +4247,13 @@
         <v>131</v>
       </c>
       <c r="I86" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="J86" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="K86" s="1" t="s">
         <v>221</v>
-      </c>
-      <c r="J86" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="K86" s="1" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="97" customHeight="1" spans="3:11">
@@ -4258,7 +4261,7 @@
         <v>201</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E97" s="1">
         <v>1</v>
@@ -4270,16 +4273,16 @@
         <v>2</v>
       </c>
       <c r="H97" s="5" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I97" s="5" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="J97" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K97" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="98" customHeight="1" spans="3:11">
@@ -4287,7 +4290,7 @@
         <v>202</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E98" s="1">
         <v>1</v>
@@ -4299,16 +4302,16 @@
         <v>2</v>
       </c>
       <c r="H98" s="5" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I98" s="5" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="J98" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K98" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="99" customHeight="1" spans="3:11">
@@ -4316,7 +4319,7 @@
         <v>203</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E99" s="1">
         <v>1</v>
@@ -4328,16 +4331,16 @@
         <v>2</v>
       </c>
       <c r="H99" s="5" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I99" s="5" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="J99" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K99" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="100" customHeight="1" spans="3:11">
@@ -4345,7 +4348,7 @@
         <v>204</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E100" s="1">
         <v>1</v>
@@ -4357,16 +4360,16 @@
         <v>2</v>
       </c>
       <c r="H100" s="5" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I100" s="5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="J100" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K100" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="101" customHeight="1" spans="3:11">
@@ -4374,7 +4377,7 @@
         <v>205</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E101" s="1">
         <v>1</v>
@@ -4386,16 +4389,16 @@
         <v>2</v>
       </c>
       <c r="H101" s="5" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I101" s="5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J101" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K101" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="102" customHeight="1" spans="3:11">
@@ -4403,7 +4406,7 @@
         <v>206</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E102" s="1">
         <v>1</v>
@@ -4415,16 +4418,16 @@
         <v>2</v>
       </c>
       <c r="H102" s="5" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I102" s="5" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="J102" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K102" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="103" customHeight="1" spans="3:11">
@@ -4432,7 +4435,7 @@
         <v>207</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E103" s="1">
         <v>1</v>
@@ -4444,16 +4447,16 @@
         <v>2</v>
       </c>
       <c r="H103" s="5" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I103" s="5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="J103" s="5" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K103" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="104" customHeight="1" spans="3:11">
@@ -4461,7 +4464,7 @@
         <v>208</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E104" s="1">
         <v>1</v>
@@ -4473,7 +4476,7 @@
         <v>2</v>
       </c>
       <c r="K104" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="105" customHeight="1" spans="3:11">
@@ -4481,7 +4484,7 @@
         <v>209</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E105" s="1">
         <v>1</v>
@@ -4493,16 +4496,16 @@
         <v>2</v>
       </c>
       <c r="H105" s="5" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I105" s="5" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="J105" s="5" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K105" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
   </sheetData>
@@ -4629,7 +4632,7 @@
         <v>1001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -4644,13 +4647,13 @@
         <v>14</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J6" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4658,7 +4661,7 @@
         <v>1002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -4673,13 +4676,13 @@
         <v>14</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="J7" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4687,7 +4690,7 @@
         <v>1003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -4702,13 +4705,13 @@
         <v>14</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="J8" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4716,7 +4719,7 @@
         <v>1004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
@@ -4731,13 +4734,13 @@
         <v>14</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="J9" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4745,7 +4748,7 @@
         <v>1005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -4760,13 +4763,13 @@
         <v>14</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="J10" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4774,7 +4777,7 @@
         <v>1006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -4789,13 +4792,13 @@
         <v>14</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J11" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4803,7 +4806,7 @@
         <v>1007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
@@ -4818,13 +4821,13 @@
         <v>14</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="J12" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4832,7 +4835,7 @@
         <v>1008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
@@ -4847,13 +4850,13 @@
         <v>14</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J13" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4861,7 +4864,7 @@
         <v>1009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
@@ -4876,13 +4879,13 @@
         <v>14</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="J14" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="18" customHeight="1"/>
@@ -4891,7 +4894,7 @@
         <v>1101</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E16" s="1">
         <v>1</v>
@@ -4906,13 +4909,13 @@
         <v>14</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J16" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4920,7 +4923,7 @@
         <v>1102</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E17" s="1">
         <v>1</v>
@@ -4935,13 +4938,13 @@
         <v>14</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J17" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4949,7 +4952,7 @@
         <v>1103</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E18" s="1">
         <v>1</v>
@@ -4964,13 +4967,13 @@
         <v>14</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J18" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4978,7 +4981,7 @@
         <v>1104</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E19" s="1">
         <v>1</v>
@@ -4993,13 +4996,13 @@
         <v>14</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="J19" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5007,7 +5010,7 @@
         <v>1105</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E20" s="1">
         <v>1</v>
@@ -5022,13 +5025,13 @@
         <v>14</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J20" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5036,7 +5039,7 @@
         <v>1106</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
@@ -5051,13 +5054,13 @@
         <v>14</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="J21" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5065,7 +5068,7 @@
         <v>1107</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
@@ -5080,13 +5083,13 @@
         <v>14</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="J22" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5094,7 +5097,7 @@
         <v>1108</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
@@ -5109,13 +5112,13 @@
         <v>14</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="J23" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5123,7 +5126,7 @@
         <v>1109</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
@@ -5138,13 +5141,13 @@
         <v>14</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J24" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5152,7 +5155,7 @@
         <v>1110</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E25" s="1">
         <v>1</v>
@@ -5167,13 +5170,13 @@
         <v>14</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="J25" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5181,7 +5184,7 @@
         <v>1111</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
@@ -5196,13 +5199,13 @@
         <v>14</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="J26" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5210,7 +5213,7 @@
         <v>1112</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E27" s="1">
         <v>1</v>
@@ -5225,13 +5228,13 @@
         <v>14</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J27" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="320">
   <si>
     <t>_id</t>
   </si>
@@ -456,342 +456,345 @@
     <t>金色专属自选</t>
   </si>
   <si>
+    <t>1001,1002,1003,1010,1011,1012</t>
+  </si>
+  <si>
+    <t>高级金色专属</t>
+  </si>
+  <si>
+    <t>4,4,4,4,4,4,4,4,4</t>
+  </si>
+  <si>
+    <t>1007,1008,1009,1001,1002,1003,1004,1005,1006</t>
+  </si>
+  <si>
+    <t>驱魔6件套</t>
+  </si>
+  <si>
+    <t>12,12,12,12,12,12,5,5</t>
+  </si>
+  <si>
+    <t>36,37,38,39,40,41,4005,4010</t>
+  </si>
+  <si>
+    <t>1,1,1,1,1,1,300,60</t>
+  </si>
+  <si>
+    <t>盾专属自选套</t>
+  </si>
+  <si>
+    <t>4,4,4,4</t>
+  </si>
+  <si>
+    <t>99,102,104</t>
+  </si>
+  <si>
+    <t>专属自选</t>
+  </si>
+  <si>
+    <t>99,100,101,102,103,104,105,96</t>
+  </si>
+  <si>
+    <t>法力盾4件套</t>
+  </si>
+  <si>
+    <t>12,12,12,12,5,5</t>
+  </si>
+  <si>
+    <t>26,27,28,29,4005,4010</t>
+  </si>
+  <si>
+    <t>1,1,1,1,300,60</t>
+  </si>
+  <si>
+    <t>神雷6件套</t>
+  </si>
+  <si>
+    <t>30,31,32,33,34,35,4005,4010</t>
+  </si>
+  <si>
+    <t>流光6件套</t>
+  </si>
+  <si>
+    <t>5,6,7,8,9,10,4005,4010</t>
+  </si>
+  <si>
+    <t>武神盾4件套</t>
+  </si>
+  <si>
+    <t>11,12,13,14,4005,4010</t>
+  </si>
+  <si>
+    <t>冰咆哮4件套</t>
+  </si>
+  <si>
+    <t>803,804,705,706,4005,4010</t>
+  </si>
+  <si>
+    <t>道力盾4件套</t>
+  </si>
+  <si>
+    <t>18,19,20,21,4005,4010</t>
+  </si>
+  <si>
+    <t>月神4件套</t>
+  </si>
+  <si>
+    <t>22,23,24,25,4005,4010</t>
+  </si>
+  <si>
+    <t>白银礼包</t>
+  </si>
+  <si>
+    <t>15,5,5,5,5,5</t>
+  </si>
+  <si>
+    <t>4014,4012,4001,4011,4102,4010</t>
+  </si>
+  <si>
+    <t>500,2000,10000000,20,200,50</t>
+  </si>
+  <si>
+    <t>经验丹0.5K,传世精华2k,魂环碎片1KW,红装精华3,高级书页200个,专属之心50个</t>
+  </si>
+  <si>
+    <t>黄金礼包</t>
+  </si>
+  <si>
+    <t>180005,180006,180018,180002,180004,180008</t>
+  </si>
+  <si>
+    <t>钻石礼包</t>
+  </si>
+  <si>
+    <t>180007,180009,180001,180002,180004,180019</t>
+  </si>
+  <si>
+    <t>高级法宝自选</t>
+  </si>
+  <si>
+    <t>战士经验红装</t>
+  </si>
+  <si>
+    <t>20,20,20,20,20,20,20,20</t>
+  </si>
+  <si>
+    <t>1,2,3,4,5,6,7,8</t>
+  </si>
+  <si>
+    <t>战士满经验红装自选</t>
+  </si>
+  <si>
+    <t>法师经验红装</t>
+  </si>
+  <si>
+    <t>9,10,11,12,13,14,15,16</t>
+  </si>
+  <si>
+    <t>法师满经验红装自选</t>
+  </si>
+  <si>
+    <t>道士经验红装</t>
+  </si>
+  <si>
+    <t>17,18,19,20,21,22,23,24</t>
+  </si>
+  <si>
+    <t>道士满经验红装自选</t>
+  </si>
+  <si>
+    <t>战士输出红装</t>
+  </si>
+  <si>
+    <t>25,26,27,28,29,30,31,32</t>
+  </si>
+  <si>
+    <t>战士输出红装自选</t>
+  </si>
+  <si>
+    <t>法师输出红装</t>
+  </si>
+  <si>
+    <t>33,34,35,36,37,38,39,40</t>
+  </si>
+  <si>
+    <t>法师输出红装自选</t>
+  </si>
+  <si>
+    <t>道士输出红装</t>
+  </si>
+  <si>
+    <t>20,20,20,20,20,20,20,20,20,20</t>
+  </si>
+  <si>
+    <t>41,42,43,44,45,46,47,48,49,50</t>
+  </si>
+  <si>
+    <t>道士输出红装自选</t>
+  </si>
+  <si>
+    <t>红装自选</t>
+  </si>
+  <si>
+    <t>109,110,111,112,113,114</t>
+  </si>
+  <si>
+    <t>战士暗金</t>
+  </si>
+  <si>
+    <t>151,152,153,154,155,156,157,158</t>
+  </si>
+  <si>
+    <t>法师暗金</t>
+  </si>
+  <si>
+    <t>161,162,163,164,165,166,167,168</t>
+  </si>
+  <si>
+    <t>道士暗金</t>
+  </si>
+  <si>
+    <t>171,172,173,174,175,176,177,178</t>
+  </si>
+  <si>
+    <t>战士平衡金装</t>
+  </si>
+  <si>
+    <t>101,102,103,104,105,106,107,108</t>
+  </si>
+  <si>
+    <t>法师平衡金装</t>
+  </si>
+  <si>
+    <t>109,110,111,112,113,114,115,116</t>
+  </si>
+  <si>
+    <t>道士平衡金装</t>
+  </si>
+  <si>
+    <t>117,118,119,120,121,122,123,124</t>
+  </si>
+  <si>
+    <t>战士防御金装</t>
+  </si>
+  <si>
+    <t>125,126,127,128,129,130,131,132</t>
+  </si>
+  <si>
+    <t>法师输出金装</t>
+  </si>
+  <si>
+    <t>133,134,135,136,137,138,139,140</t>
+  </si>
+  <si>
+    <t>金装自选</t>
+  </si>
+  <si>
+    <t>121,122,123,124,125</t>
+  </si>
+  <si>
+    <t>暗金自选</t>
+  </si>
+  <si>
+    <t>118,119,120</t>
+  </si>
+  <si>
+    <t>1,1,1,</t>
+  </si>
+  <si>
+    <t>40橙宠自选</t>
+  </si>
+  <si>
+    <t>21,21,21</t>
+  </si>
+  <si>
+    <t>1,2,3</t>
+  </si>
+  <si>
+    <t>40资质橙宠自选</t>
+  </si>
+  <si>
+    <t>45橙宠自选</t>
+  </si>
+  <si>
+    <t>4,5,6</t>
+  </si>
+  <si>
+    <t>45资质橙宠自选</t>
+  </si>
+  <si>
+    <t>50橙宠自选</t>
+  </si>
+  <si>
+    <t>7,8,9</t>
+  </si>
+  <si>
+    <t>50资质橙宠自选</t>
+  </si>
+  <si>
+    <t>40红宠自选</t>
+  </si>
+  <si>
+    <t>10,11,12</t>
+  </si>
+  <si>
+    <t>40资质红宠自选</t>
+  </si>
+  <si>
+    <t>45红宠自选</t>
+  </si>
+  <si>
+    <t>13,14,15</t>
+  </si>
+  <si>
+    <t>45资质红宠自选</t>
+  </si>
+  <si>
+    <t>50红宠自选</t>
+  </si>
+  <si>
+    <t>16,17,18</t>
+  </si>
+  <si>
+    <t>50资质红宠自选</t>
+  </si>
+  <si>
+    <t>40金宠自选</t>
+  </si>
+  <si>
+    <t>21,21,21,21,21,21,21,21,21,21,21,21</t>
+  </si>
+  <si>
+    <t>19,20,21,22,23,24,25,26,27,28,29,30</t>
+  </si>
+  <si>
+    <t>1,1,1,1,1,1,1,1,1,1,1,1</t>
+  </si>
+  <si>
+    <t>40资质金宠自选</t>
+  </si>
+  <si>
+    <t>45金宠自选</t>
+  </si>
+  <si>
+    <t>45资质金宠自选</t>
+  </si>
+  <si>
+    <t>50金宠自选</t>
+  </si>
+  <si>
+    <t>31,32,33,34,35,36,37,38,39,40,41,42</t>
+  </si>
+  <si>
+    <t>50资质金宠自选</t>
+  </si>
+  <si>
+    <t>金色刺杀自选</t>
+  </si>
+  <si>
     <t>1001,1002,1003,1004,1005,1006</t>
   </si>
   <si>
-    <t>高级金色专属</t>
-  </si>
-  <si>
-    <t>4,4,4,4,4,4,4,4,4</t>
-  </si>
-  <si>
-    <t>1007,1008,1009,1001,1002,1003,1004,1005,1006</t>
-  </si>
-  <si>
-    <t>驱魔6件套</t>
-  </si>
-  <si>
-    <t>12,12,12,12,12,12,5,5</t>
-  </si>
-  <si>
-    <t>36,37,38,39,40,41,4005,4010</t>
-  </si>
-  <si>
-    <t>1,1,1,1,1,1,300,60</t>
-  </si>
-  <si>
-    <t>盾专属自选套</t>
-  </si>
-  <si>
-    <t>4,4,4,4</t>
-  </si>
-  <si>
-    <t>99,102,104</t>
-  </si>
-  <si>
-    <t>专属自选</t>
-  </si>
-  <si>
-    <t>99,100,101,102,103,104,105,96</t>
-  </si>
-  <si>
-    <t>法力盾4件套</t>
-  </si>
-  <si>
-    <t>12,12,12,12,5,5</t>
-  </si>
-  <si>
-    <t>26,27,28,29,4005,4010</t>
-  </si>
-  <si>
-    <t>1,1,1,1,300,60</t>
-  </si>
-  <si>
-    <t>神雷6件套</t>
-  </si>
-  <si>
-    <t>30,31,32,33,34,35,4005,4010</t>
-  </si>
-  <si>
-    <t>流光6件套</t>
-  </si>
-  <si>
-    <t>5,6,7,8,9,10,4005,4010</t>
-  </si>
-  <si>
-    <t>武神盾4件套</t>
-  </si>
-  <si>
-    <t>11,12,13,14,4005,4010</t>
-  </si>
-  <si>
-    <t>冰咆哮4件套</t>
-  </si>
-  <si>
-    <t>803,804,705,706,4005,4010</t>
-  </si>
-  <si>
-    <t>道力盾4件套</t>
-  </si>
-  <si>
-    <t>18,19,20,21,4005,4010</t>
-  </si>
-  <si>
-    <t>月神4件套</t>
-  </si>
-  <si>
-    <t>22,23,24,25,4005,4010</t>
-  </si>
-  <si>
-    <t>白银礼包</t>
-  </si>
-  <si>
-    <t>15,5,5,5,5,5</t>
-  </si>
-  <si>
-    <t>4014,4012,4001,4011,4102,4010</t>
-  </si>
-  <si>
-    <t>500,2000,10000000,20,200,50</t>
-  </si>
-  <si>
-    <t>经验丹0.5K,传世精华2k,魂环碎片1KW,红装精华3,高级书页200个,专属之心50个</t>
-  </si>
-  <si>
-    <t>黄金礼包</t>
-  </si>
-  <si>
-    <t>180005,180006,180018,180002,180004,180008</t>
-  </si>
-  <si>
-    <t>钻石礼包</t>
-  </si>
-  <si>
-    <t>180007,180009,180001,180002,180004,180019</t>
-  </si>
-  <si>
-    <t>高级法宝自选</t>
-  </si>
-  <si>
-    <t>战士经验红装</t>
-  </si>
-  <si>
-    <t>20,20,20,20,20,20,20,20</t>
-  </si>
-  <si>
-    <t>1,2,3,4,5,6,7,8</t>
-  </si>
-  <si>
-    <t>战士满经验红装自选</t>
-  </si>
-  <si>
-    <t>法师经验红装</t>
-  </si>
-  <si>
-    <t>9,10,11,12,13,14,15,16</t>
-  </si>
-  <si>
-    <t>法师满经验红装自选</t>
-  </si>
-  <si>
-    <t>道士经验红装</t>
-  </si>
-  <si>
-    <t>17,18,19,20,21,22,23,24</t>
-  </si>
-  <si>
-    <t>道士满经验红装自选</t>
-  </si>
-  <si>
-    <t>战士输出红装</t>
-  </si>
-  <si>
-    <t>25,26,27,28,29,30,31,32</t>
-  </si>
-  <si>
-    <t>战士输出红装自选</t>
-  </si>
-  <si>
-    <t>法师输出红装</t>
-  </si>
-  <si>
-    <t>33,34,35,36,37,38,39,40</t>
-  </si>
-  <si>
-    <t>法师输出红装自选</t>
-  </si>
-  <si>
-    <t>道士输出红装</t>
-  </si>
-  <si>
-    <t>20,20,20,20,20,20,20,20,20,20</t>
-  </si>
-  <si>
-    <t>41,42,43,44,45,46,47,48,49,50</t>
-  </si>
-  <si>
-    <t>道士输出红装自选</t>
-  </si>
-  <si>
-    <t>红装自选</t>
-  </si>
-  <si>
-    <t>109,110,111,112,113,114</t>
-  </si>
-  <si>
-    <t>战士暗金</t>
-  </si>
-  <si>
-    <t>151,152,153,154,155,156,157,158</t>
-  </si>
-  <si>
-    <t>法师暗金</t>
-  </si>
-  <si>
-    <t>161,162,163,164,165,166,167,168</t>
-  </si>
-  <si>
-    <t>道士暗金</t>
-  </si>
-  <si>
-    <t>171,172,173,174,175,176,177,178</t>
-  </si>
-  <si>
-    <t>战士平衡金装</t>
-  </si>
-  <si>
-    <t>101,102,103,104,105,106,107,108</t>
-  </si>
-  <si>
-    <t>法师平衡金装</t>
-  </si>
-  <si>
-    <t>109,110,111,112,113,114,115,116</t>
-  </si>
-  <si>
-    <t>道士平衡金装</t>
-  </si>
-  <si>
-    <t>117,118,119,120,121,122,123,124</t>
-  </si>
-  <si>
-    <t>战士防御金装</t>
-  </si>
-  <si>
-    <t>125,126,127,128,129,130,131,132</t>
-  </si>
-  <si>
-    <t>法师输出金装</t>
-  </si>
-  <si>
-    <t>133,134,135,136,137,138,139,140</t>
-  </si>
-  <si>
-    <t>金装自选</t>
-  </si>
-  <si>
-    <t>121,122,123,124,125</t>
-  </si>
-  <si>
-    <t>暗金自选</t>
-  </si>
-  <si>
-    <t>118,119,120</t>
-  </si>
-  <si>
-    <t>1,1,1,</t>
-  </si>
-  <si>
-    <t>40橙宠自选</t>
-  </si>
-  <si>
-    <t>21,21,21</t>
-  </si>
-  <si>
-    <t>1,2,3</t>
-  </si>
-  <si>
-    <t>40资质橙宠自选</t>
-  </si>
-  <si>
-    <t>45橙宠自选</t>
-  </si>
-  <si>
-    <t>4,5,6</t>
-  </si>
-  <si>
-    <t>45资质橙宠自选</t>
-  </si>
-  <si>
-    <t>50橙宠自选</t>
-  </si>
-  <si>
-    <t>7,8,9</t>
-  </si>
-  <si>
-    <t>50资质橙宠自选</t>
-  </si>
-  <si>
-    <t>40红宠自选</t>
-  </si>
-  <si>
-    <t>10,11,12</t>
-  </si>
-  <si>
-    <t>40资质红宠自选</t>
-  </si>
-  <si>
-    <t>45红宠自选</t>
-  </si>
-  <si>
-    <t>13,14,15</t>
-  </si>
-  <si>
-    <t>45资质红宠自选</t>
-  </si>
-  <si>
-    <t>50红宠自选</t>
-  </si>
-  <si>
-    <t>16,17,18</t>
-  </si>
-  <si>
-    <t>50资质红宠自选</t>
-  </si>
-  <si>
-    <t>40金宠自选</t>
-  </si>
-  <si>
-    <t>21,21,21,21,21,21,21,21,21,21,21,21</t>
-  </si>
-  <si>
-    <t>19,20,21,22,23,24,25,26,27,28,29,30</t>
-  </si>
-  <si>
-    <t>1,1,1,1,1,1,1,1,1,1,1,1</t>
-  </si>
-  <si>
-    <t>40资质金宠自选</t>
-  </si>
-  <si>
-    <t>45金宠自选</t>
-  </si>
-  <si>
-    <t>45资质金宠自选</t>
-  </si>
-  <si>
-    <t>50金宠自选</t>
-  </si>
-  <si>
-    <t>31,32,33,34,35,36,37,38,39,40,41,42</t>
-  </si>
-  <si>
-    <t>50资质金宠自选</t>
-  </si>
-  <si>
-    <t>金色刺杀自选</t>
-  </si>
-  <si>
     <t>金色刺杀专属包</t>
   </si>
   <si>
@@ -865,6 +868,24 @@
   </si>
   <si>
     <t>金色无极专属包</t>
+  </si>
+  <si>
+    <t>金色武盾自选</t>
+  </si>
+  <si>
+    <t>1055,1056,1057,1058,1059,1060</t>
+  </si>
+  <si>
+    <t>金色法盾自选</t>
+  </si>
+  <si>
+    <t>1061,1062,1063,1064,1065,1066</t>
+  </si>
+  <si>
+    <t>金色道盾自选</t>
+  </si>
+  <si>
+    <t>1067,1068,1069,1070,1071,1072</t>
   </si>
   <si>
     <t>暗金1阶自选</t>
@@ -4525,7 +4546,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B3:L50"/>
+  <dimension ref="B3:L53"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="3" width="9"/>
@@ -4647,13 +4668,13 @@
         <v>14</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>142</v>
+        <v>254</v>
       </c>
       <c r="J6" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4661,7 +4682,7 @@
         <v>1002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -4676,13 +4697,13 @@
         <v>14</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J7" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4690,7 +4711,7 @@
         <v>1003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -4705,13 +4726,13 @@
         <v>14</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="J8" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4719,7 +4740,7 @@
         <v>1004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
@@ -4734,13 +4755,13 @@
         <v>14</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J9" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4748,7 +4769,7 @@
         <v>1005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -4763,13 +4784,13 @@
         <v>14</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="J10" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4777,7 +4798,7 @@
         <v>1006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -4792,13 +4813,13 @@
         <v>14</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="J11" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4806,7 +4827,7 @@
         <v>1007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
@@ -4821,13 +4842,13 @@
         <v>14</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="J12" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4835,7 +4856,7 @@
         <v>1008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
@@ -4850,13 +4871,13 @@
         <v>14</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="J13" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4864,7 +4885,7 @@
         <v>1009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
@@ -4879,22 +4900,50 @@
         <v>14</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J14" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" ht="18" customHeight="1"/>
+        <v>279</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+      <c r="C15" s="1">
+        <v>1010</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="E15" s="1">
+        <v>1</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="1">
+        <v>2</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>280</v>
+      </c>
+    </row>
     <row r="16" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
       <c r="C16" s="1">
-        <v>1101</v>
+        <v>1011</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="E16" s="1">
         <v>1</v>
@@ -4909,21 +4958,21 @@
         <v>14</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>138</v>
+        <v>283</v>
       </c>
       <c r="J16" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
       <c r="C17" s="1">
-        <v>1102</v>
+        <v>1012</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E17" s="1">
         <v>1</v>
@@ -4938,47 +4987,19 @@
         <v>14</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>140</v>
+        <v>285</v>
       </c>
       <c r="J17" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
-      <c r="C18" s="1">
-        <v>1103</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="E18" s="1">
-        <v>1</v>
-      </c>
-      <c r="F18" s="3">
-        <v>0</v>
-      </c>
-      <c r="G18" s="1">
-        <v>2</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I18" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="J18" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>285</v>
-      </c>
-    </row>
+    </row>
+    <row r="18" s="1" customFormat="1" ht="18" customHeight="1"/>
     <row r="19" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
       <c r="C19" s="1">
-        <v>1104</v>
+        <v>1101</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>286</v>
@@ -4996,21 +5017,21 @@
         <v>14</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>287</v>
+        <v>138</v>
       </c>
       <c r="J19" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
       <c r="C20" s="1">
-        <v>1105</v>
+        <v>1102</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E20" s="1">
         <v>1</v>
@@ -5025,21 +5046,21 @@
         <v>14</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>290</v>
+        <v>140</v>
       </c>
       <c r="J20" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
       <c r="C21" s="1">
-        <v>1106</v>
+        <v>1103</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
@@ -5054,21 +5075,21 @@
         <v>14</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="J21" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
       <c r="C22" s="1">
-        <v>1107</v>
+        <v>1104</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
@@ -5083,21 +5104,21 @@
         <v>14</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="J22" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
       <c r="C23" s="1">
-        <v>1108</v>
+        <v>1105</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
@@ -5112,21 +5133,21 @@
         <v>14</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="J23" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
       <c r="C24" s="1">
-        <v>1109</v>
+        <v>1106</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
@@ -5141,21 +5162,21 @@
         <v>14</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="J24" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
       <c r="C25" s="1">
-        <v>1110</v>
+        <v>1107</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E25" s="1">
         <v>1</v>
@@ -5170,21 +5191,21 @@
         <v>14</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="J25" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
       <c r="C26" s="1">
-        <v>1111</v>
+        <v>1108</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
@@ -5199,21 +5220,21 @@
         <v>14</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="J26" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
       <c r="C27" s="1">
-        <v>1112</v>
+        <v>1109</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="E27" s="1">
         <v>1</v>
@@ -5228,40 +5249,101 @@
         <v>14</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="J27" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K27" s="1" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+      <c r="C28" s="1">
+        <v>1110</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="E28" s="1">
+        <v>1</v>
+      </c>
+      <c r="F28" s="3">
+        <v>0</v>
+      </c>
+      <c r="G28" s="1">
+        <v>2</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I28" s="5" t="s">
         <v>312</v>
       </c>
-    </row>
-    <row r="28" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
-      <c r="B28"/>
-      <c r="C28"/>
-      <c r="D28"/>
-      <c r="E28"/>
-      <c r="F28"/>
-      <c r="G28"/>
-      <c r="H28"/>
-      <c r="I28"/>
-      <c r="J28"/>
-      <c r="K28"/>
-      <c r="L28"/>
-    </row>
-    <row r="30" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
-      <c r="B30"/>
-      <c r="C30"/>
-      <c r="D30"/>
-      <c r="E30"/>
-      <c r="F30"/>
-      <c r="G30"/>
-      <c r="H30"/>
-      <c r="I30"/>
-      <c r="J30"/>
-      <c r="K30"/>
-      <c r="L30"/>
+      <c r="J28" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+      <c r="C29" s="1">
+        <v>1111</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="E29" s="1">
+        <v>1</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="1">
+        <v>2</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="J29" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="30" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+      <c r="C30" s="1">
+        <v>1112</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="E30" s="1">
+        <v>1</v>
+      </c>
+      <c r="F30" s="3">
+        <v>0</v>
+      </c>
+      <c r="G30" s="1">
+        <v>2</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="J30" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>319</v>
+      </c>
     </row>
     <row r="31" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
       <c r="B31"/>
@@ -5276,44 +5358,31 @@
       <c r="K31"/>
       <c r="L31"/>
     </row>
-    <row r="42" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
-      <c r="B42"/>
-      <c r="C42"/>
-      <c r="D42"/>
-      <c r="E42"/>
-      <c r="F42"/>
-      <c r="G42"/>
-      <c r="H42"/>
-      <c r="I42"/>
-      <c r="J42"/>
-      <c r="K42"/>
-      <c r="L42"/>
-    </row>
-    <row r="43" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
-      <c r="B43"/>
-      <c r="C43"/>
-      <c r="D43"/>
-      <c r="E43"/>
-      <c r="F43"/>
-      <c r="G43"/>
-      <c r="H43"/>
-      <c r="I43"/>
-      <c r="J43"/>
-      <c r="K43"/>
-      <c r="L43"/>
-    </row>
-    <row r="44" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
-      <c r="B44"/>
-      <c r="C44"/>
-      <c r="D44"/>
-      <c r="E44"/>
-      <c r="F44"/>
-      <c r="G44"/>
-      <c r="H44"/>
-      <c r="I44"/>
-      <c r="J44"/>
-      <c r="K44"/>
-      <c r="L44"/>
+    <row r="33" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
+      <c r="B33"/>
+      <c r="C33"/>
+      <c r="D33"/>
+      <c r="E33"/>
+      <c r="F33"/>
+      <c r="G33"/>
+      <c r="H33"/>
+      <c r="I33"/>
+      <c r="J33"/>
+      <c r="K33"/>
+      <c r="L33"/>
+    </row>
+    <row r="34" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
+      <c r="B34"/>
+      <c r="C34"/>
+      <c r="D34"/>
+      <c r="E34"/>
+      <c r="F34"/>
+      <c r="G34"/>
+      <c r="H34"/>
+      <c r="I34"/>
+      <c r="J34"/>
+      <c r="K34"/>
+      <c r="L34"/>
     </row>
     <row r="45" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
       <c r="B45"/>
@@ -5393,6 +5462,45 @@
       <c r="K50"/>
       <c r="L50"/>
     </row>
+    <row r="51" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
+      <c r="B51"/>
+      <c r="C51"/>
+      <c r="D51"/>
+      <c r="E51"/>
+      <c r="F51"/>
+      <c r="G51"/>
+      <c r="H51"/>
+      <c r="I51"/>
+      <c r="J51"/>
+      <c r="K51"/>
+      <c r="L51"/>
+    </row>
+    <row r="52" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
+      <c r="B52"/>
+      <c r="C52"/>
+      <c r="D52"/>
+      <c r="E52"/>
+      <c r="F52"/>
+      <c r="G52"/>
+      <c r="H52"/>
+      <c r="I52"/>
+      <c r="J52"/>
+      <c r="K52"/>
+      <c r="L52"/>
+    </row>
+    <row r="53" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
+      <c r="B53"/>
+      <c r="C53"/>
+      <c r="D53"/>
+      <c r="E53"/>
+      <c r="F53"/>
+      <c r="G53"/>
+      <c r="H53"/>
+      <c r="I53"/>
+      <c r="J53"/>
+      <c r="K53"/>
+      <c r="L53"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="324">
   <si>
     <t>_id</t>
   </si>
@@ -462,36 +462,42 @@
     <t>高级金色专属</t>
   </si>
   <si>
+    <t>4,4,4,4,4,4,4,4,4,4</t>
+  </si>
+  <si>
+    <t>1007,1008,1009,1001,1002,1003,1004,1005,1006,1013</t>
+  </si>
+  <si>
+    <t>1,1,1,1,1,1,1,1,1,1</t>
+  </si>
+  <si>
+    <t>驱魔6件套</t>
+  </si>
+  <si>
+    <t>12,12,12,12,12,12,5,5</t>
+  </si>
+  <si>
+    <t>36,37,38,39,40,41,4005,4010</t>
+  </si>
+  <si>
+    <t>1,1,1,1,1,1,300,60</t>
+  </si>
+  <si>
+    <t>盾专属自选套</t>
+  </si>
+  <si>
+    <t>4,4,4,4</t>
+  </si>
+  <si>
+    <t>99,102,104</t>
+  </si>
+  <si>
+    <t>专属自选</t>
+  </si>
+  <si>
     <t>4,4,4,4,4,4,4,4,4</t>
   </si>
   <si>
-    <t>1007,1008,1009,1001,1002,1003,1004,1005,1006</t>
-  </si>
-  <si>
-    <t>驱魔6件套</t>
-  </si>
-  <si>
-    <t>12,12,12,12,12,12,5,5</t>
-  </si>
-  <si>
-    <t>36,37,38,39,40,41,4005,4010</t>
-  </si>
-  <si>
-    <t>1,1,1,1,1,1,300,60</t>
-  </si>
-  <si>
-    <t>盾专属自选套</t>
-  </si>
-  <si>
-    <t>4,4,4,4</t>
-  </si>
-  <si>
-    <t>99,102,104</t>
-  </si>
-  <si>
-    <t>专属自选</t>
-  </si>
-  <si>
     <t>99,100,101,102,103,104,105,96</t>
   </si>
   <si>
@@ -886,6 +892,12 @@
   </si>
   <si>
     <t>1067,1068,1069,1070,1071,1072</t>
+  </si>
+  <si>
+    <t>金色专精自选</t>
+  </si>
+  <si>
+    <t>1073,1074,1075</t>
   </si>
   <si>
     <t>暗金1阶自选</t>
@@ -3401,7 +3413,7 @@
         <v>145</v>
       </c>
       <c r="J52" s="5" t="s">
-        <v>87</v>
+        <v>146</v>
       </c>
       <c r="K52" s="1" t="s">
         <v>143</v>
@@ -3412,7 +3424,7 @@
         <v>96</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E53" s="1">
         <v>0</v>
@@ -3424,16 +3436,16 @@
         <v>2</v>
       </c>
       <c r="H53" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="I53" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="J53" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="K53" s="1" t="s">
         <v>147</v>
-      </c>
-      <c r="I53" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="J53" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="K53" s="1" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:11">
@@ -3441,7 +3453,7 @@
         <v>97</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E54" s="1">
         <v>1</v>
@@ -3453,16 +3465,16 @@
         <v>2</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I54" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J54" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:11">
@@ -3470,7 +3482,7 @@
         <v>98</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E55" s="1">
         <v>1</v>
@@ -3482,16 +3494,16 @@
         <v>2</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="I55" s="5" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="J55" s="5" t="s">
         <v>91</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:11">
@@ -3499,7 +3511,7 @@
         <v>99</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E56" s="1">
         <v>0</v>
@@ -3511,16 +3523,16 @@
         <v>2</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="I56" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="J56" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="K56" s="1" t="s">
         <v>157</v>
-      </c>
-      <c r="J56" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="K56" s="1" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:11">
@@ -3528,7 +3540,7 @@
         <v>100</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E57" s="1">
         <v>0</v>
@@ -3540,16 +3552,16 @@
         <v>2</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I57" s="5" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="J57" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:11">
@@ -3557,7 +3569,7 @@
         <v>101</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E58" s="1">
         <v>0</v>
@@ -3569,16 +3581,16 @@
         <v>2</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I58" s="5" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="J58" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:11">
@@ -3586,7 +3598,7 @@
         <v>102</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E59" s="1">
         <v>0</v>
@@ -3598,16 +3610,16 @@
         <v>2</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="I59" s="5" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J59" s="5" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="3:11">
@@ -3615,7 +3627,7 @@
         <v>103</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E60" s="1">
         <v>0</v>
@@ -3627,16 +3639,16 @@
         <v>2</v>
       </c>
       <c r="H60" s="5" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="I60" s="5" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="J60" s="5" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="3:11">
@@ -3644,7 +3656,7 @@
         <v>104</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E61" s="1">
         <v>0</v>
@@ -3656,16 +3668,16 @@
         <v>2</v>
       </c>
       <c r="H61" s="5" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="I61" s="5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="J61" s="5" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="3:11">
@@ -3673,7 +3685,7 @@
         <v>105</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E62" s="1">
         <v>0</v>
@@ -3685,16 +3697,16 @@
         <v>2</v>
       </c>
       <c r="H62" s="5" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="I62" s="5" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="J62" s="5" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:11">
@@ -3702,7 +3714,7 @@
         <v>106</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E64" s="1">
         <v>1</v>
@@ -3714,16 +3726,16 @@
         <v>1</v>
       </c>
       <c r="H64" s="5" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I64" s="5" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="J64" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="K64" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:11">
@@ -3731,7 +3743,7 @@
         <v>107</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E65" s="1">
         <v>1</v>
@@ -3746,7 +3758,7 @@
         <v>64</v>
       </c>
       <c r="I65" s="5" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="J65" s="5" t="s">
         <v>40</v>
@@ -3760,7 +3772,7 @@
         <v>108</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E66" s="1">
         <v>1</v>
@@ -3775,13 +3787,13 @@
         <v>64</v>
       </c>
       <c r="I66" s="5" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="J66" s="5" t="s">
         <v>40</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:11">
@@ -3789,7 +3801,7 @@
         <v>109</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E68" s="1">
         <v>1</v>
@@ -3801,16 +3813,16 @@
         <v>2</v>
       </c>
       <c r="H68" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="I68" s="5" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="J68" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:11">
@@ -3818,7 +3830,7 @@
         <v>110</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E69" s="1">
         <v>1</v>
@@ -3830,16 +3842,16 @@
         <v>2</v>
       </c>
       <c r="H69" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="I69" s="5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="J69" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:11">
@@ -3847,7 +3859,7 @@
         <v>111</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E70" s="1">
         <v>1</v>
@@ -3859,16 +3871,16 @@
         <v>2</v>
       </c>
       <c r="H70" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="I70" s="5" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="J70" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:11">
@@ -3876,7 +3888,7 @@
         <v>112</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E71" s="1">
         <v>1</v>
@@ -3888,16 +3900,16 @@
         <v>2</v>
       </c>
       <c r="H71" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="I71" s="5" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="J71" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:11">
@@ -3905,7 +3917,7 @@
         <v>113</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E72" s="1">
         <v>1</v>
@@ -3917,16 +3929,16 @@
         <v>2</v>
       </c>
       <c r="H72" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="I72" s="5" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="J72" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:11">
@@ -3934,7 +3946,7 @@
         <v>114</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E73" s="1">
         <v>1</v>
@@ -3946,16 +3958,16 @@
         <v>2</v>
       </c>
       <c r="H73" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="I73" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="J73" s="5" t="s">
         <v>91</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:11">
@@ -3963,7 +3975,7 @@
         <v>115</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E74" s="1">
         <v>1</v>
@@ -3978,13 +3990,13 @@
         <v>137</v>
       </c>
       <c r="I74" s="5" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="J74" s="5" t="s">
         <v>40</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:11">
@@ -3992,7 +4004,7 @@
         <v>118</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E76" s="1">
         <v>1</v>
@@ -4004,16 +4016,16 @@
         <v>2</v>
       </c>
       <c r="H76" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="I76" s="5" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="J76" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K76" s="3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:11">
@@ -4021,7 +4033,7 @@
         <v>119</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E77" s="1">
         <v>1</v>
@@ -4033,16 +4045,16 @@
         <v>2</v>
       </c>
       <c r="H77" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="I77" s="5" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="J77" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K77" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="3:11">
@@ -4050,7 +4062,7 @@
         <v>120</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E78" s="1">
         <v>1</v>
@@ -4062,16 +4074,16 @@
         <v>2</v>
       </c>
       <c r="H78" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="I78" s="5" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="J78" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K78" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="3:11">
@@ -4079,7 +4091,7 @@
         <v>121</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E79" s="1">
         <v>1</v>
@@ -4091,16 +4103,16 @@
         <v>2</v>
       </c>
       <c r="H79" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="I79" s="5" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="J79" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="3:11">
@@ -4108,7 +4120,7 @@
         <v>122</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E80" s="1">
         <v>1</v>
@@ -4120,16 +4132,16 @@
         <v>2</v>
       </c>
       <c r="H80" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="I80" s="5" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J80" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K80" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="3:11">
@@ -4137,7 +4149,7 @@
         <v>123</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E81" s="1">
         <v>1</v>
@@ -4149,16 +4161,16 @@
         <v>2</v>
       </c>
       <c r="H81" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="I81" s="5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="J81" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K81" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="3:11">
@@ -4166,7 +4178,7 @@
         <v>124</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E82" s="1">
         <v>1</v>
@@ -4178,16 +4190,16 @@
         <v>2</v>
       </c>
       <c r="H82" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="I82" s="5" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="J82" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K82" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="3:11">
@@ -4195,7 +4207,7 @@
         <v>125</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E83" s="1">
         <v>1</v>
@@ -4207,16 +4219,16 @@
         <v>2</v>
       </c>
       <c r="H83" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="I83" s="5" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="J83" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="85" customHeight="1" spans="3:11">
@@ -4224,7 +4236,7 @@
         <v>127</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E85" s="1">
         <v>1</v>
@@ -4239,13 +4251,13 @@
         <v>137</v>
       </c>
       <c r="I85" s="5" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="J85" s="5" t="s">
         <v>40</v>
       </c>
       <c r="K85" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="3:11">
@@ -4253,7 +4265,7 @@
         <v>128</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E86" s="1">
         <v>1</v>
@@ -4268,13 +4280,13 @@
         <v>131</v>
       </c>
       <c r="I86" s="5" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="J86" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="K86" s="1" t="s">
         <v>223</v>
-      </c>
-      <c r="K86" s="1" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="97" customHeight="1" spans="3:11">
@@ -4282,7 +4294,7 @@
         <v>201</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E97" s="1">
         <v>1</v>
@@ -4294,16 +4306,16 @@
         <v>2</v>
       </c>
       <c r="H97" s="5" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I97" s="5" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="J97" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K97" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="98" customHeight="1" spans="3:11">
@@ -4311,7 +4323,7 @@
         <v>202</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E98" s="1">
         <v>1</v>
@@ -4323,16 +4335,16 @@
         <v>2</v>
       </c>
       <c r="H98" s="5" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I98" s="5" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="J98" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K98" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="99" customHeight="1" spans="3:11">
@@ -4340,7 +4352,7 @@
         <v>203</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E99" s="1">
         <v>1</v>
@@ -4352,16 +4364,16 @@
         <v>2</v>
       </c>
       <c r="H99" s="5" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I99" s="5" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="J99" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K99" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="100" customHeight="1" spans="3:11">
@@ -4369,7 +4381,7 @@
         <v>204</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="E100" s="1">
         <v>1</v>
@@ -4381,16 +4393,16 @@
         <v>2</v>
       </c>
       <c r="H100" s="5" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I100" s="5" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="J100" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K100" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="101" customHeight="1" spans="3:11">
@@ -4398,7 +4410,7 @@
         <v>205</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E101" s="1">
         <v>1</v>
@@ -4410,16 +4422,16 @@
         <v>2</v>
       </c>
       <c r="H101" s="5" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I101" s="5" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="J101" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K101" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="102" customHeight="1" spans="3:11">
@@ -4427,7 +4439,7 @@
         <v>206</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E102" s="1">
         <v>1</v>
@@ -4439,16 +4451,16 @@
         <v>2</v>
       </c>
       <c r="H102" s="5" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I102" s="5" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="J102" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K102" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="103" customHeight="1" spans="3:11">
@@ -4456,7 +4468,7 @@
         <v>207</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E103" s="1">
         <v>1</v>
@@ -4468,16 +4480,16 @@
         <v>2</v>
       </c>
       <c r="H103" s="5" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="I103" s="5" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="J103" s="5" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K103" s="1" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="104" customHeight="1" spans="3:11">
@@ -4485,7 +4497,7 @@
         <v>208</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E104" s="1">
         <v>1</v>
@@ -4497,7 +4509,7 @@
         <v>2</v>
       </c>
       <c r="K104" s="1" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="105" customHeight="1" spans="3:11">
@@ -4505,7 +4517,7 @@
         <v>209</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E105" s="1">
         <v>1</v>
@@ -4517,21 +4529,21 @@
         <v>2</v>
       </c>
       <c r="H105" s="5" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="I105" s="5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="J105" s="5" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K105" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:E5 H3:K5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="H3:K5 C3:E5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="F3:G5" errorStyle="warning">
@@ -4546,7 +4558,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B3:L53"/>
+  <dimension ref="B3:L54"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="3" width="9"/>
@@ -4653,7 +4665,7 @@
         <v>1001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -4668,13 +4680,13 @@
         <v>14</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="J6" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4682,7 +4694,7 @@
         <v>1002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -4697,13 +4709,13 @@
         <v>14</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="J7" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4711,7 +4723,7 @@
         <v>1003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -4726,13 +4738,13 @@
         <v>14</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="J8" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4740,7 +4752,7 @@
         <v>1004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
@@ -4755,13 +4767,13 @@
         <v>14</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="J9" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4769,7 +4781,7 @@
         <v>1005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -4784,13 +4796,13 @@
         <v>14</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="J10" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4798,7 +4810,7 @@
         <v>1006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -4813,13 +4825,13 @@
         <v>14</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="J11" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4827,7 +4839,7 @@
         <v>1007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
@@ -4842,13 +4854,13 @@
         <v>14</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="J12" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4856,7 +4868,7 @@
         <v>1008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
@@ -4871,13 +4883,13 @@
         <v>14</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="J13" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4885,7 +4897,7 @@
         <v>1009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
@@ -4900,13 +4912,13 @@
         <v>14</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J14" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4914,7 +4926,7 @@
         <v>1010</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
@@ -4929,13 +4941,13 @@
         <v>14</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="J15" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4943,7 +4955,7 @@
         <v>1011</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E16" s="1">
         <v>1</v>
@@ -4958,13 +4970,13 @@
         <v>14</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="J16" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4972,7 +4984,7 @@
         <v>1012</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E17" s="1">
         <v>1</v>
@@ -4987,51 +4999,51 @@
         <v>14</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="J17" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" ht="18" customHeight="1"/>
-    <row r="19" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
-      <c r="C19" s="1">
-        <v>1101</v>
-      </c>
-      <c r="D19" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="E19" s="1">
-        <v>1</v>
-      </c>
-      <c r="F19" s="3">
-        <v>0</v>
-      </c>
-      <c r="G19" s="1">
-        <v>2</v>
-      </c>
-      <c r="H19" s="5" t="s">
+    </row>
+    <row r="18" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+      <c r="C18" s="1">
+        <v>1013</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="E18" s="1">
+        <v>1</v>
+      </c>
+      <c r="F18" s="3">
+        <v>0</v>
+      </c>
+      <c r="G18" s="1">
+        <v>2</v>
+      </c>
+      <c r="H18" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="I19" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="J19" s="5" t="s">
+      <c r="I18" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="J18" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="K19" s="1" t="s">
-        <v>287</v>
-      </c>
-    </row>
+      <c r="K18" s="1" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" ht="18" customHeight="1"/>
     <row r="20" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
       <c r="C20" s="1">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E20" s="1">
         <v>1</v>
@@ -5046,21 +5058,21 @@
         <v>14</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="J20" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
       <c r="C21" s="1">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
@@ -5075,21 +5087,21 @@
         <v>14</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>291</v>
+        <v>140</v>
       </c>
       <c r="J21" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
       <c r="C22" s="1">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
@@ -5104,21 +5116,21 @@
         <v>14</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="J22" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
       <c r="C23" s="1">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
@@ -5133,21 +5145,21 @@
         <v>14</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="J23" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
       <c r="C24" s="1">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
@@ -5162,21 +5174,21 @@
         <v>14</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J24" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
       <c r="C25" s="1">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E25" s="1">
         <v>1</v>
@@ -5191,21 +5203,21 @@
         <v>14</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="J25" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
       <c r="C26" s="1">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
@@ -5220,21 +5232,21 @@
         <v>14</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="J26" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
       <c r="C27" s="1">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E27" s="1">
         <v>1</v>
@@ -5249,21 +5261,21 @@
         <v>14</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="J27" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
       <c r="C28" s="1">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E28" s="1">
         <v>1</v>
@@ -5278,21 +5290,21 @@
         <v>14</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="J28" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
       <c r="C29" s="1">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
@@ -5307,21 +5319,21 @@
         <v>14</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="J29" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
       <c r="C30" s="1">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
@@ -5336,40 +5348,56 @@
         <v>14</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="J30" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="31" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
-      <c r="B31"/>
-      <c r="C31"/>
-      <c r="D31"/>
-      <c r="E31"/>
-      <c r="F31"/>
-      <c r="G31"/>
-      <c r="H31"/>
-      <c r="I31"/>
-      <c r="J31"/>
-      <c r="K31"/>
-      <c r="L31"/>
-    </row>
-    <row r="33" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
-      <c r="B33"/>
-      <c r="C33"/>
-      <c r="D33"/>
-      <c r="E33"/>
-      <c r="F33"/>
-      <c r="G33"/>
-      <c r="H33"/>
-      <c r="I33"/>
-      <c r="J33"/>
-      <c r="K33"/>
-      <c r="L33"/>
+        <v>320</v>
+      </c>
+    </row>
+    <row r="31" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+      <c r="C31" s="1">
+        <v>1112</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="E31" s="1">
+        <v>1</v>
+      </c>
+      <c r="F31" s="3">
+        <v>0</v>
+      </c>
+      <c r="G31" s="1">
+        <v>2</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="J31" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="32" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
+      <c r="B32"/>
+      <c r="C32"/>
+      <c r="D32"/>
+      <c r="E32"/>
+      <c r="F32"/>
+      <c r="G32"/>
+      <c r="H32"/>
+      <c r="I32"/>
+      <c r="J32"/>
+      <c r="K32"/>
+      <c r="L32"/>
     </row>
     <row r="34" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
       <c r="B34"/>
@@ -5384,18 +5412,18 @@
       <c r="K34"/>
       <c r="L34"/>
     </row>
-    <row r="45" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
-      <c r="B45"/>
-      <c r="C45"/>
-      <c r="D45"/>
-      <c r="E45"/>
-      <c r="F45"/>
-      <c r="G45"/>
-      <c r="H45"/>
-      <c r="I45"/>
-      <c r="J45"/>
-      <c r="K45"/>
-      <c r="L45"/>
+    <row r="35" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
+      <c r="B35"/>
+      <c r="C35"/>
+      <c r="D35"/>
+      <c r="E35"/>
+      <c r="F35"/>
+      <c r="G35"/>
+      <c r="H35"/>
+      <c r="I35"/>
+      <c r="J35"/>
+      <c r="K35"/>
+      <c r="L35"/>
     </row>
     <row r="46" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
       <c r="B46"/>
@@ -5501,6 +5529,19 @@
       <c r="K53"/>
       <c r="L53"/>
     </row>
+    <row r="54" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
+      <c r="B54"/>
+      <c r="C54"/>
+      <c r="D54"/>
+      <c r="E54"/>
+      <c r="F54"/>
+      <c r="G54"/>
+      <c r="H54"/>
+      <c r="I54"/>
+      <c r="J54"/>
+      <c r="K54"/>
+      <c r="L54"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="325">
   <si>
     <t>_id</t>
   </si>
@@ -420,286 +420,289 @@
     <t>61000025,61000026,61000027,61000028,61000029,61000030,61000031,61000032</t>
   </si>
   <si>
+    <t>麒麟神器自选</t>
+  </si>
+  <si>
     <t>神器自选</t>
   </si>
   <si>
+    <t>4,4,4,4</t>
+  </si>
+  <si>
+    <t>35,37,38,39</t>
+  </si>
+  <si>
+    <t>12阶技能自选</t>
+  </si>
+  <si>
+    <t>1012,2012,3012</t>
+  </si>
+  <si>
+    <t>12技能三选一</t>
+  </si>
+  <si>
+    <t>暗金专属自选</t>
+  </si>
+  <si>
+    <t>4,4,4,4,4,4</t>
+  </si>
+  <si>
+    <t>1101,1102,1103,1104,1105,1106</t>
+  </si>
+  <si>
+    <t>高级暗金专属</t>
+  </si>
+  <si>
+    <t>1107,1108,1109,1110,1111,1112</t>
+  </si>
+  <si>
+    <t>金色专属自选</t>
+  </si>
+  <si>
+    <t>1001,1002,1003,1010,1011,1012</t>
+  </si>
+  <si>
+    <t>高级金色专属</t>
+  </si>
+  <si>
+    <t>4,4,4,4,4,4,4,4,4,4</t>
+  </si>
+  <si>
+    <t>1007,1008,1009,1001,1002,1003,1004,1005,1006,1013</t>
+  </si>
+  <si>
+    <t>1,1,1,1,1,1,1,1,1,1</t>
+  </si>
+  <si>
+    <t>驱魔6件套</t>
+  </si>
+  <si>
+    <t>12,12,12,12,12,12,5,5</t>
+  </si>
+  <si>
+    <t>36,37,38,39,40,41,4005,4010</t>
+  </si>
+  <si>
+    <t>1,1,1,1,1,1,300,60</t>
+  </si>
+  <si>
+    <t>盾专属自选套</t>
+  </si>
+  <si>
+    <t>99,102,104</t>
+  </si>
+  <si>
+    <t>专属自选</t>
+  </si>
+  <si>
+    <t>4,4,4,4,4,4,4,4,4</t>
+  </si>
+  <si>
+    <t>99,100,101,102,103,104,105,96</t>
+  </si>
+  <si>
+    <t>法力盾4件套</t>
+  </si>
+  <si>
+    <t>12,12,12,12,5,5</t>
+  </si>
+  <si>
+    <t>26,27,28,29,4005,4010</t>
+  </si>
+  <si>
+    <t>1,1,1,1,300,60</t>
+  </si>
+  <si>
+    <t>神雷6件套</t>
+  </si>
+  <si>
+    <t>30,31,32,33,34,35,4005,4010</t>
+  </si>
+  <si>
+    <t>流光6件套</t>
+  </si>
+  <si>
+    <t>5,6,7,8,9,10,4005,4010</t>
+  </si>
+  <si>
+    <t>武神盾4件套</t>
+  </si>
+  <si>
+    <t>11,12,13,14,4005,4010</t>
+  </si>
+  <si>
+    <t>冰咆哮4件套</t>
+  </si>
+  <si>
+    <t>803,804,705,706,4005,4010</t>
+  </si>
+  <si>
+    <t>道力盾4件套</t>
+  </si>
+  <si>
+    <t>18,19,20,21,4005,4010</t>
+  </si>
+  <si>
+    <t>月神4件套</t>
+  </si>
+  <si>
+    <t>22,23,24,25,4005,4010</t>
+  </si>
+  <si>
+    <t>白银礼包</t>
+  </si>
+  <si>
+    <t>15,5,5,5,5,5</t>
+  </si>
+  <si>
+    <t>4014,4012,4001,4011,4102,4010</t>
+  </si>
+  <si>
+    <t>500,2000,10000000,20,200,50</t>
+  </si>
+  <si>
+    <t>经验丹0.5K,传世精华2k,魂环碎片1KW,红装精华3,高级书页200个,专属之心50个</t>
+  </si>
+  <si>
+    <t>黄金礼包</t>
+  </si>
+  <si>
+    <t>180005,180006,180018,180002,180004,180008</t>
+  </si>
+  <si>
+    <t>钻石礼包</t>
+  </si>
+  <si>
+    <t>180007,180009,180001,180002,180004,180019</t>
+  </si>
+  <si>
+    <t>高级法宝自选</t>
+  </si>
+  <si>
+    <t>战士经验红装</t>
+  </si>
+  <si>
+    <t>20,20,20,20,20,20,20,20</t>
+  </si>
+  <si>
+    <t>1,2,3,4,5,6,7,8</t>
+  </si>
+  <si>
+    <t>战士满经验红装自选</t>
+  </si>
+  <si>
+    <t>法师经验红装</t>
+  </si>
+  <si>
+    <t>9,10,11,12,13,14,15,16</t>
+  </si>
+  <si>
+    <t>法师满经验红装自选</t>
+  </si>
+  <si>
+    <t>道士经验红装</t>
+  </si>
+  <si>
+    <t>17,18,19,20,21,22,23,24</t>
+  </si>
+  <si>
+    <t>道士满经验红装自选</t>
+  </si>
+  <si>
+    <t>战士输出红装</t>
+  </si>
+  <si>
+    <t>25,26,27,28,29,30,31,32</t>
+  </si>
+  <si>
+    <t>战士输出红装自选</t>
+  </si>
+  <si>
+    <t>法师输出红装</t>
+  </si>
+  <si>
+    <t>33,34,35,36,37,38,39,40</t>
+  </si>
+  <si>
+    <t>法师输出红装自选</t>
+  </si>
+  <si>
+    <t>道士输出红装</t>
+  </si>
+  <si>
+    <t>20,20,20,20,20,20,20,20,20,20</t>
+  </si>
+  <si>
+    <t>41,42,43,44,45,46,47,48,49,50</t>
+  </si>
+  <si>
+    <t>道士输出红装自选</t>
+  </si>
+  <si>
+    <t>红装自选</t>
+  </si>
+  <si>
+    <t>109,110,111,112,113,114</t>
+  </si>
+  <si>
+    <t>战士暗金</t>
+  </si>
+  <si>
+    <t>151,152,153,154,155,156,157,158</t>
+  </si>
+  <si>
+    <t>法师暗金</t>
+  </si>
+  <si>
+    <t>161,162,163,164,165,166,167,168</t>
+  </si>
+  <si>
+    <t>道士暗金</t>
+  </si>
+  <si>
+    <t>171,172,173,174,175,176,177,178</t>
+  </si>
+  <si>
+    <t>战士平衡金装</t>
+  </si>
+  <si>
+    <t>101,102,103,104,105,106,107,108</t>
+  </si>
+  <si>
+    <t>法师平衡金装</t>
+  </si>
+  <si>
+    <t>109,110,111,112,113,114,115,116</t>
+  </si>
+  <si>
+    <t>道士平衡金装</t>
+  </si>
+  <si>
+    <t>117,118,119,120,121,122,123,124</t>
+  </si>
+  <si>
+    <t>战士防御金装</t>
+  </si>
+  <si>
+    <t>125,126,127,128,129,130,131,132</t>
+  </si>
+  <si>
+    <t>法师输出金装</t>
+  </si>
+  <si>
+    <t>133,134,135,136,137,138,139,140</t>
+  </si>
+  <si>
+    <t>金装自选</t>
+  </si>
+  <si>
+    <t>121,122,123,124,125</t>
+  </si>
+  <si>
+    <t>暗金自选</t>
+  </si>
+  <si>
     <t>4,4,4</t>
-  </si>
-  <si>
-    <t>35,37,38</t>
-  </si>
-  <si>
-    <t>12阶技能自选</t>
-  </si>
-  <si>
-    <t>1012,2012,3012</t>
-  </si>
-  <si>
-    <t>12技能三选一</t>
-  </si>
-  <si>
-    <t>暗金专属自选</t>
-  </si>
-  <si>
-    <t>4,4,4,4,4,4</t>
-  </si>
-  <si>
-    <t>1101,1102,1103,1104,1105,1106</t>
-  </si>
-  <si>
-    <t>高级暗金专属</t>
-  </si>
-  <si>
-    <t>1107,1108,1109,1110,1111,1112</t>
-  </si>
-  <si>
-    <t>金色专属自选</t>
-  </si>
-  <si>
-    <t>1001,1002,1003,1010,1011,1012</t>
-  </si>
-  <si>
-    <t>高级金色专属</t>
-  </si>
-  <si>
-    <t>4,4,4,4,4,4,4,4,4,4</t>
-  </si>
-  <si>
-    <t>1007,1008,1009,1001,1002,1003,1004,1005,1006,1013</t>
-  </si>
-  <si>
-    <t>1,1,1,1,1,1,1,1,1,1</t>
-  </si>
-  <si>
-    <t>驱魔6件套</t>
-  </si>
-  <si>
-    <t>12,12,12,12,12,12,5,5</t>
-  </si>
-  <si>
-    <t>36,37,38,39,40,41,4005,4010</t>
-  </si>
-  <si>
-    <t>1,1,1,1,1,1,300,60</t>
-  </si>
-  <si>
-    <t>盾专属自选套</t>
-  </si>
-  <si>
-    <t>4,4,4,4</t>
-  </si>
-  <si>
-    <t>99,102,104</t>
-  </si>
-  <si>
-    <t>专属自选</t>
-  </si>
-  <si>
-    <t>4,4,4,4,4,4,4,4,4</t>
-  </si>
-  <si>
-    <t>99,100,101,102,103,104,105,96</t>
-  </si>
-  <si>
-    <t>法力盾4件套</t>
-  </si>
-  <si>
-    <t>12,12,12,12,5,5</t>
-  </si>
-  <si>
-    <t>26,27,28,29,4005,4010</t>
-  </si>
-  <si>
-    <t>1,1,1,1,300,60</t>
-  </si>
-  <si>
-    <t>神雷6件套</t>
-  </si>
-  <si>
-    <t>30,31,32,33,34,35,4005,4010</t>
-  </si>
-  <si>
-    <t>流光6件套</t>
-  </si>
-  <si>
-    <t>5,6,7,8,9,10,4005,4010</t>
-  </si>
-  <si>
-    <t>武神盾4件套</t>
-  </si>
-  <si>
-    <t>11,12,13,14,4005,4010</t>
-  </si>
-  <si>
-    <t>冰咆哮4件套</t>
-  </si>
-  <si>
-    <t>803,804,705,706,4005,4010</t>
-  </si>
-  <si>
-    <t>道力盾4件套</t>
-  </si>
-  <si>
-    <t>18,19,20,21,4005,4010</t>
-  </si>
-  <si>
-    <t>月神4件套</t>
-  </si>
-  <si>
-    <t>22,23,24,25,4005,4010</t>
-  </si>
-  <si>
-    <t>白银礼包</t>
-  </si>
-  <si>
-    <t>15,5,5,5,5,5</t>
-  </si>
-  <si>
-    <t>4014,4012,4001,4011,4102,4010</t>
-  </si>
-  <si>
-    <t>500,2000,10000000,20,200,50</t>
-  </si>
-  <si>
-    <t>经验丹0.5K,传世精华2k,魂环碎片1KW,红装精华3,高级书页200个,专属之心50个</t>
-  </si>
-  <si>
-    <t>黄金礼包</t>
-  </si>
-  <si>
-    <t>180005,180006,180018,180002,180004,180008</t>
-  </si>
-  <si>
-    <t>钻石礼包</t>
-  </si>
-  <si>
-    <t>180007,180009,180001,180002,180004,180019</t>
-  </si>
-  <si>
-    <t>高级法宝自选</t>
-  </si>
-  <si>
-    <t>战士经验红装</t>
-  </si>
-  <si>
-    <t>20,20,20,20,20,20,20,20</t>
-  </si>
-  <si>
-    <t>1,2,3,4,5,6,7,8</t>
-  </si>
-  <si>
-    <t>战士满经验红装自选</t>
-  </si>
-  <si>
-    <t>法师经验红装</t>
-  </si>
-  <si>
-    <t>9,10,11,12,13,14,15,16</t>
-  </si>
-  <si>
-    <t>法师满经验红装自选</t>
-  </si>
-  <si>
-    <t>道士经验红装</t>
-  </si>
-  <si>
-    <t>17,18,19,20,21,22,23,24</t>
-  </si>
-  <si>
-    <t>道士满经验红装自选</t>
-  </si>
-  <si>
-    <t>战士输出红装</t>
-  </si>
-  <si>
-    <t>25,26,27,28,29,30,31,32</t>
-  </si>
-  <si>
-    <t>战士输出红装自选</t>
-  </si>
-  <si>
-    <t>法师输出红装</t>
-  </si>
-  <si>
-    <t>33,34,35,36,37,38,39,40</t>
-  </si>
-  <si>
-    <t>法师输出红装自选</t>
-  </si>
-  <si>
-    <t>道士输出红装</t>
-  </si>
-  <si>
-    <t>20,20,20,20,20,20,20,20,20,20</t>
-  </si>
-  <si>
-    <t>41,42,43,44,45,46,47,48,49,50</t>
-  </si>
-  <si>
-    <t>道士输出红装自选</t>
-  </si>
-  <si>
-    <t>红装自选</t>
-  </si>
-  <si>
-    <t>109,110,111,112,113,114</t>
-  </si>
-  <si>
-    <t>战士暗金</t>
-  </si>
-  <si>
-    <t>151,152,153,154,155,156,157,158</t>
-  </si>
-  <si>
-    <t>法师暗金</t>
-  </si>
-  <si>
-    <t>161,162,163,164,165,166,167,168</t>
-  </si>
-  <si>
-    <t>道士暗金</t>
-  </si>
-  <si>
-    <t>171,172,173,174,175,176,177,178</t>
-  </si>
-  <si>
-    <t>战士平衡金装</t>
-  </si>
-  <si>
-    <t>101,102,103,104,105,106,107,108</t>
-  </si>
-  <si>
-    <t>法师平衡金装</t>
-  </si>
-  <si>
-    <t>109,110,111,112,113,114,115,116</t>
-  </si>
-  <si>
-    <t>道士平衡金装</t>
-  </si>
-  <si>
-    <t>117,118,119,120,121,122,123,124</t>
-  </si>
-  <si>
-    <t>战士防御金装</t>
-  </si>
-  <si>
-    <t>125,126,127,128,129,130,131,132</t>
-  </si>
-  <si>
-    <t>法师输出金装</t>
-  </si>
-  <si>
-    <t>133,134,135,136,137,138,139,140</t>
-  </si>
-  <si>
-    <t>金装自选</t>
-  </si>
-  <si>
-    <t>121,122,123,124,125</t>
-  </si>
-  <si>
-    <t>暗金自选</t>
   </si>
   <si>
     <t>118,119,120</t>
@@ -3200,7 +3203,7 @@
         <v>40</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E45" s="1">
         <v>1</v>
@@ -3229,7 +3232,7 @@
         <v>41</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E46" s="1">
         <v>1</v>
@@ -3241,10 +3244,10 @@
         <v>1</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I46" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J46" s="5" t="s">
         <v>91</v>
@@ -3258,7 +3261,7 @@
         <v>42</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E47" s="1">
         <v>1</v>
@@ -3273,13 +3276,13 @@
         <v>30</v>
       </c>
       <c r="I47" s="5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J47" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="48" customFormat="1" customHeight="1" spans="1:11">
@@ -3302,7 +3305,7 @@
         <v>90</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E49" s="1">
         <v>1</v>
@@ -3314,16 +3317,16 @@
         <v>2</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I49" s="5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J49" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="50" customFormat="1" customHeight="1" spans="1:11">
@@ -3333,7 +3336,7 @@
         <v>91</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E50" s="1">
         <v>1</v>
@@ -3345,16 +3348,16 @@
         <v>2</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I50" s="5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J50" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="51" customFormat="1" customHeight="1" spans="1:11">
@@ -3364,7 +3367,7 @@
         <v>94</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E51" s="1">
         <v>1</v>
@@ -3376,16 +3379,16 @@
         <v>2</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I51" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J51" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="52" customFormat="1" customHeight="1" spans="1:11">
@@ -3395,7 +3398,7 @@
         <v>95</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E52" s="1">
         <v>1</v>
@@ -3407,16 +3410,16 @@
         <v>2</v>
       </c>
       <c r="H52" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="I52" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="J52" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="K52" s="1" t="s">
         <v>144</v>
-      </c>
-      <c r="I52" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="J52" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="K52" s="1" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:11">
@@ -3424,7 +3427,7 @@
         <v>96</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E53" s="1">
         <v>0</v>
@@ -3436,16 +3439,16 @@
         <v>2</v>
       </c>
       <c r="H53" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="I53" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="J53" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="K53" s="1" t="s">
         <v>148</v>
-      </c>
-      <c r="I53" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="J53" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="K53" s="1" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:11">
@@ -3453,7 +3456,7 @@
         <v>97</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E54" s="1">
         <v>1</v>
@@ -3465,7 +3468,7 @@
         <v>2</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="I54" s="5" t="s">
         <v>153</v>
@@ -3474,7 +3477,7 @@
         <v>32</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:11">
@@ -3552,13 +3555,13 @@
         <v>2</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I57" s="5" t="s">
         <v>162</v>
       </c>
       <c r="J57" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K57" s="1" t="s">
         <v>161</v>
@@ -3581,13 +3584,13 @@
         <v>2</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I58" s="5" t="s">
         <v>164</v>
       </c>
       <c r="J58" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K58" s="1" t="s">
         <v>163</v>
@@ -3987,7 +3990,7 @@
         <v>2</v>
       </c>
       <c r="H74" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I74" s="5" t="s">
         <v>204</v>
@@ -4248,7 +4251,7 @@
         <v>2</v>
       </c>
       <c r="H85" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I85" s="5" t="s">
         <v>222</v>
@@ -4277,13 +4280,13 @@
         <v>2</v>
       </c>
       <c r="H86" s="5" t="s">
-        <v>131</v>
+        <v>224</v>
       </c>
       <c r="I86" s="5" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="J86" s="5" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="K86" s="1" t="s">
         <v>223</v>
@@ -4294,7 +4297,7 @@
         <v>201</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E97" s="1">
         <v>1</v>
@@ -4306,16 +4309,16 @@
         <v>2</v>
       </c>
       <c r="H97" s="5" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I97" s="5" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="J97" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K97" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="98" customHeight="1" spans="3:11">
@@ -4323,7 +4326,7 @@
         <v>202</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E98" s="1">
         <v>1</v>
@@ -4335,16 +4338,16 @@
         <v>2</v>
       </c>
       <c r="H98" s="5" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I98" s="5" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="J98" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K98" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="99" customHeight="1" spans="3:11">
@@ -4352,7 +4355,7 @@
         <v>203</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E99" s="1">
         <v>1</v>
@@ -4364,16 +4367,16 @@
         <v>2</v>
       </c>
       <c r="H99" s="5" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I99" s="5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="J99" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K99" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="100" customHeight="1" spans="3:11">
@@ -4381,7 +4384,7 @@
         <v>204</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E100" s="1">
         <v>1</v>
@@ -4393,16 +4396,16 @@
         <v>2</v>
       </c>
       <c r="H100" s="5" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I100" s="5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J100" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K100" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="101" customHeight="1" spans="3:11">
@@ -4410,7 +4413,7 @@
         <v>205</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E101" s="1">
         <v>1</v>
@@ -4422,16 +4425,16 @@
         <v>2</v>
       </c>
       <c r="H101" s="5" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I101" s="5" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="J101" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K101" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="102" customHeight="1" spans="3:11">
@@ -4439,7 +4442,7 @@
         <v>206</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E102" s="1">
         <v>1</v>
@@ -4451,16 +4454,16 @@
         <v>2</v>
       </c>
       <c r="H102" s="5" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I102" s="5" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="J102" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K102" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="103" customHeight="1" spans="3:11">
@@ -4468,7 +4471,7 @@
         <v>207</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E103" s="1">
         <v>1</v>
@@ -4480,16 +4483,16 @@
         <v>2</v>
       </c>
       <c r="H103" s="5" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I103" s="5" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="J103" s="5" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K103" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="104" customHeight="1" spans="3:11">
@@ -4497,7 +4500,7 @@
         <v>208</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E104" s="1">
         <v>1</v>
@@ -4509,7 +4512,7 @@
         <v>2</v>
       </c>
       <c r="K104" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="105" customHeight="1" spans="3:11">
@@ -4517,7 +4520,7 @@
         <v>209</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E105" s="1">
         <v>1</v>
@@ -4529,21 +4532,21 @@
         <v>2</v>
       </c>
       <c r="H105" s="5" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I105" s="5" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J105" s="5" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K105" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="H3:K5 C3:E5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:E5 H3:K5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="F3:G5" errorStyle="warning">
@@ -4665,7 +4668,7 @@
         <v>1001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -4680,13 +4683,13 @@
         <v>14</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J6" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4694,7 +4697,7 @@
         <v>1002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -4709,13 +4712,13 @@
         <v>14</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="J7" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4723,7 +4726,7 @@
         <v>1003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -4738,13 +4741,13 @@
         <v>14</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J8" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4752,7 +4755,7 @@
         <v>1004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
@@ -4767,13 +4770,13 @@
         <v>14</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="J9" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4781,7 +4784,7 @@
         <v>1005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -4796,13 +4799,13 @@
         <v>14</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="J10" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4810,7 +4813,7 @@
         <v>1006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -4825,13 +4828,13 @@
         <v>14</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="J11" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4839,7 +4842,7 @@
         <v>1007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
@@ -4854,13 +4857,13 @@
         <v>14</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="J12" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4868,7 +4871,7 @@
         <v>1008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
@@ -4883,13 +4886,13 @@
         <v>14</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J13" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4897,7 +4900,7 @@
         <v>1009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
@@ -4912,13 +4915,13 @@
         <v>14</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J14" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4926,7 +4929,7 @@
         <v>1010</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
@@ -4941,13 +4944,13 @@
         <v>14</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J15" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4955,7 +4958,7 @@
         <v>1011</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E16" s="1">
         <v>1</v>
@@ -4970,13 +4973,13 @@
         <v>14</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="J16" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4984,7 +4987,7 @@
         <v>1012</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E17" s="1">
         <v>1</v>
@@ -4999,13 +5002,13 @@
         <v>14</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="J17" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5013,7 +5016,7 @@
         <v>1013</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E18" s="1">
         <v>1</v>
@@ -5028,13 +5031,13 @@
         <v>14</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J18" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" ht="18" customHeight="1"/>
@@ -5043,7 +5046,7 @@
         <v>1101</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E20" s="1">
         <v>1</v>
@@ -5058,13 +5061,13 @@
         <v>14</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J20" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5072,7 +5075,7 @@
         <v>1102</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
@@ -5087,13 +5090,13 @@
         <v>14</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J21" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5101,7 +5104,7 @@
         <v>1103</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
@@ -5116,13 +5119,13 @@
         <v>14</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="J22" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5130,7 +5133,7 @@
         <v>1104</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
@@ -5145,13 +5148,13 @@
         <v>14</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="J23" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5159,7 +5162,7 @@
         <v>1105</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
@@ -5174,13 +5177,13 @@
         <v>14</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J24" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5188,7 +5191,7 @@
         <v>1106</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E25" s="1">
         <v>1</v>
@@ -5203,13 +5206,13 @@
         <v>14</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="J25" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5217,7 +5220,7 @@
         <v>1107</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
@@ -5232,13 +5235,13 @@
         <v>14</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="J26" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5246,7 +5249,7 @@
         <v>1108</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E27" s="1">
         <v>1</v>
@@ -5261,13 +5264,13 @@
         <v>14</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J27" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5275,7 +5278,7 @@
         <v>1109</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E28" s="1">
         <v>1</v>
@@ -5290,13 +5293,13 @@
         <v>14</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J28" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5304,7 +5307,7 @@
         <v>1110</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
@@ -5319,13 +5322,13 @@
         <v>14</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="J29" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5333,7 +5336,7 @@
         <v>1111</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
@@ -5348,13 +5351,13 @@
         <v>14</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J30" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5362,7 +5365,7 @@
         <v>1112</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
@@ -5377,13 +5380,13 @@
         <v>14</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="J31" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="325">
   <si>
     <t>_id</t>
   </si>
@@ -783,7 +783,7 @@
     <t>40资质金宠自选</t>
   </si>
   <si>
-    <t>45金宠自选</t>
+    <t>40金宠自选1</t>
   </si>
   <si>
     <t>45资质金宠自选</t>
@@ -4511,6 +4511,15 @@
       <c r="G104" s="3">
         <v>2</v>
       </c>
+      <c r="H104" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="I104" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="J104" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="K104" s="1" t="s">
         <v>252</v>
       </c>

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -27,6 +27,62 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Administrator</author>
+  </authors>
+  <commentList>
+    <comment ref="E3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1 自选包
+2 自动开启包</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1 可以一键开启
+2 不可以一键</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="325">
   <si>
@@ -390,7 +446,7 @@
     <t>61000001,61000002,61000003,61000004,61000005,61000006,61000007,61000008</t>
   </si>
   <si>
-    <t>宝石自选</t>
+    <t>宝石集合包</t>
   </si>
   <si>
     <t>5,5,5,5,5,5,5,5,5,5,5,5</t>
@@ -1015,7 +1071,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1179,6 +1235,17 @@
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="34">
@@ -3090,7 +3157,7 @@
         <v>120</v>
       </c>
       <c r="E41" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F41" s="3">
         <v>0</v>
@@ -4564,6 +4631,7 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -362,7 +362,7 @@
     <t>1,1,1,1,1,1,1,1,1,1,1</t>
   </si>
   <si>
-    <t>10阶级技能自选</t>
+    <t>10阶技能自选</t>
   </si>
   <si>
     <t>1010,2010,3010</t>
@@ -380,7 +380,7 @@
     <t>8101,8102,8103,8104,8105,8106,8107,8108</t>
   </si>
   <si>
-    <t>11阶级技能自选</t>
+    <t>11阶技能自选</t>
   </si>
   <si>
     <t>1011,2011,3011</t>

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="329">
   <si>
     <t>_id</t>
   </si>
@@ -500,472 +500,484 @@
     <t>暗金专属自选</t>
   </si>
   <si>
+    <t>4,4,4,4,4,4,4,4,4,4,4</t>
+  </si>
+  <si>
+    <t>1101,1102,1103,1104,1105,1106,1107,1108,1109,1110,1111</t>
+  </si>
+  <si>
+    <t>高级暗金专属</t>
+  </si>
+  <si>
+    <t>4,4,4,4,4</t>
+  </si>
+  <si>
+    <t>1107,1108,1109,1110,1111</t>
+  </si>
+  <si>
+    <t>金色专属自选</t>
+  </si>
+  <si>
     <t>4,4,4,4,4,4</t>
   </si>
   <si>
+    <t>1001,1002,1003,1010,1011,1012</t>
+  </si>
+  <si>
+    <t>高级金色专属</t>
+  </si>
+  <si>
+    <t>4,4,4,4,4,4,4,4,4,4</t>
+  </si>
+  <si>
+    <t>1007,1008,1009,1001,1002,1003,1004,1005,1006,1013</t>
+  </si>
+  <si>
+    <t>1,1,1,1,1,1,1,1,1,1</t>
+  </si>
+  <si>
+    <t>驱魔6件套</t>
+  </si>
+  <si>
+    <t>12,12,12,12,12,12,5,5</t>
+  </si>
+  <si>
+    <t>36,37,38,39,40,41,4005,4010</t>
+  </si>
+  <si>
+    <t>1,1,1,1,1,1,300,60</t>
+  </si>
+  <si>
+    <t>盾专属自选套</t>
+  </si>
+  <si>
+    <t>99,102,104</t>
+  </si>
+  <si>
+    <t>专属自选</t>
+  </si>
+  <si>
+    <t>4,4,4,4,4,4,4,4,4</t>
+  </si>
+  <si>
+    <t>99,100,101,102,103,104,105,96</t>
+  </si>
+  <si>
+    <t>法力盾4件套</t>
+  </si>
+  <si>
+    <t>12,12,12,12,5,5</t>
+  </si>
+  <si>
+    <t>26,27,28,29,4005,4010</t>
+  </si>
+  <si>
+    <t>1,1,1,1,300,60</t>
+  </si>
+  <si>
+    <t>神雷6件套</t>
+  </si>
+  <si>
+    <t>30,31,32,33,34,35,4005,4010</t>
+  </si>
+  <si>
+    <t>流光6件套</t>
+  </si>
+  <si>
+    <t>5,6,7,8,9,10,4005,4010</t>
+  </si>
+  <si>
+    <t>武神盾4件套</t>
+  </si>
+  <si>
+    <t>11,12,13,14,4005,4010</t>
+  </si>
+  <si>
+    <t>冰咆哮4件套</t>
+  </si>
+  <si>
+    <t>803,804,705,706,4005,4010</t>
+  </si>
+  <si>
+    <t>道力盾4件套</t>
+  </si>
+  <si>
+    <t>18,19,20,21,4005,4010</t>
+  </si>
+  <si>
+    <t>月神4件套</t>
+  </si>
+  <si>
+    <t>22,23,24,25,4005,4010</t>
+  </si>
+  <si>
+    <t>白银礼包</t>
+  </si>
+  <si>
+    <t>15,5,5,5,5,5</t>
+  </si>
+  <si>
+    <t>4014,4012,4001,4011,4102,4010</t>
+  </si>
+  <si>
+    <t>500,2000,10000000,20,200,50</t>
+  </si>
+  <si>
+    <t>经验丹0.5K,传世精华2k,魂环碎片1KW,红装精华3,高级书页200个,专属之心50个</t>
+  </si>
+  <si>
+    <t>黄金礼包</t>
+  </si>
+  <si>
+    <t>180005,180006,180018,180002,180004,180008</t>
+  </si>
+  <si>
+    <t>钻石礼包</t>
+  </si>
+  <si>
+    <t>180007,180009,180001,180002,180004,180019</t>
+  </si>
+  <si>
+    <t>高级法宝自选</t>
+  </si>
+  <si>
+    <t>战士经验红装</t>
+  </si>
+  <si>
+    <t>20,20,20,20,20,20,20,20</t>
+  </si>
+  <si>
+    <t>1,2,3,4,5,6,7,8</t>
+  </si>
+  <si>
+    <t>战士满经验红装自选</t>
+  </si>
+  <si>
+    <t>法师经验红装</t>
+  </si>
+  <si>
+    <t>9,10,11,12,13,14,15,16</t>
+  </si>
+  <si>
+    <t>法师满经验红装自选</t>
+  </si>
+  <si>
+    <t>道士经验红装</t>
+  </si>
+  <si>
+    <t>17,18,19,20,21,22,23,24</t>
+  </si>
+  <si>
+    <t>道士满经验红装自选</t>
+  </si>
+  <si>
+    <t>战士输出红装</t>
+  </si>
+  <si>
+    <t>25,26,27,28,29,30,31,32</t>
+  </si>
+  <si>
+    <t>战士输出红装自选</t>
+  </si>
+  <si>
+    <t>法师输出红装</t>
+  </si>
+  <si>
+    <t>33,34,35,36,37,38,39,40</t>
+  </si>
+  <si>
+    <t>法师输出红装自选</t>
+  </si>
+  <si>
+    <t>道士输出红装</t>
+  </si>
+  <si>
+    <t>20,20,20,20,20,20,20,20,20,20</t>
+  </si>
+  <si>
+    <t>41,42,43,44,45,46,47,48,49,50</t>
+  </si>
+  <si>
+    <t>道士输出红装自选</t>
+  </si>
+  <si>
+    <t>红装自选</t>
+  </si>
+  <si>
+    <t>109,110,111,112,113,114</t>
+  </si>
+  <si>
+    <t>战士暗金</t>
+  </si>
+  <si>
+    <t>151,152,153,154,155,156,157,158</t>
+  </si>
+  <si>
+    <t>法师暗金</t>
+  </si>
+  <si>
+    <t>161,162,163,164,165,166,167,168</t>
+  </si>
+  <si>
+    <t>道士暗金</t>
+  </si>
+  <si>
+    <t>171,172,173,174,175,176,177,178</t>
+  </si>
+  <si>
+    <t>战士平衡金装</t>
+  </si>
+  <si>
+    <t>101,102,103,104,105,106,107,108</t>
+  </si>
+  <si>
+    <t>法师平衡金装</t>
+  </si>
+  <si>
+    <t>109,110,111,112,113,114,115,116</t>
+  </si>
+  <si>
+    <t>道士平衡金装</t>
+  </si>
+  <si>
+    <t>117,118,119,120,121,122,123,124</t>
+  </si>
+  <si>
+    <t>战士防御金装</t>
+  </si>
+  <si>
+    <t>125,126,127,128,129,130,131,132</t>
+  </si>
+  <si>
+    <t>法师输出金装</t>
+  </si>
+  <si>
+    <t>133,134,135,136,137,138,139,140</t>
+  </si>
+  <si>
+    <t>金装自选</t>
+  </si>
+  <si>
+    <t>121,122,123,124,125</t>
+  </si>
+  <si>
+    <t>暗金自选</t>
+  </si>
+  <si>
+    <t>4,4,4</t>
+  </si>
+  <si>
+    <t>118,119,120</t>
+  </si>
+  <si>
+    <t>1,1,1,</t>
+  </si>
+  <si>
+    <t>40橙宠自选</t>
+  </si>
+  <si>
+    <t>21,21,21</t>
+  </si>
+  <si>
+    <t>1,2,3</t>
+  </si>
+  <si>
+    <t>40资质橙宠自选</t>
+  </si>
+  <si>
+    <t>45橙宠自选</t>
+  </si>
+  <si>
+    <t>4,5,6</t>
+  </si>
+  <si>
+    <t>45资质橙宠自选</t>
+  </si>
+  <si>
+    <t>50橙宠自选</t>
+  </si>
+  <si>
+    <t>7,8,9</t>
+  </si>
+  <si>
+    <t>50资质橙宠自选</t>
+  </si>
+  <si>
+    <t>40红宠自选</t>
+  </si>
+  <si>
+    <t>10,11,12</t>
+  </si>
+  <si>
+    <t>40资质红宠自选</t>
+  </si>
+  <si>
+    <t>45红宠自选</t>
+  </si>
+  <si>
+    <t>13,14,15</t>
+  </si>
+  <si>
+    <t>45资质红宠自选</t>
+  </si>
+  <si>
+    <t>50红宠自选</t>
+  </si>
+  <si>
+    <t>16,17,18</t>
+  </si>
+  <si>
+    <t>50资质红宠自选</t>
+  </si>
+  <si>
+    <t>40金宠自选</t>
+  </si>
+  <si>
+    <t>21,21,21,21,21,21,21,21,21,21,21,21</t>
+  </si>
+  <si>
+    <t>19,20,21,22,23,24,25,26,27,28,29,30</t>
+  </si>
+  <si>
+    <t>1,1,1,1,1,1,1,1,1,1,1,1</t>
+  </si>
+  <si>
+    <t>40资质金宠自选</t>
+  </si>
+  <si>
+    <t>40金宠自选1</t>
+  </si>
+  <si>
+    <t>45资质金宠自选</t>
+  </si>
+  <si>
+    <t>50金宠自选</t>
+  </si>
+  <si>
+    <t>31,32,33,34,35,36,37,38,39,40,41,42</t>
+  </si>
+  <si>
+    <t>50资质金宠自选</t>
+  </si>
+  <si>
+    <t>金色刺杀自选</t>
+  </si>
+  <si>
+    <t>1001,1002,1003,1004,1005,1006</t>
+  </si>
+  <si>
+    <t>金色刺杀专属包</t>
+  </si>
+  <si>
+    <t>金色雷电自选</t>
+  </si>
+  <si>
+    <t>1007,1008,1009,1010,1011,1012</t>
+  </si>
+  <si>
+    <t>金色雷电专属包</t>
+  </si>
+  <si>
+    <t>金色火符自选</t>
+  </si>
+  <si>
+    <t>1013,1014,1015,1016,1017,1018</t>
+  </si>
+  <si>
+    <t>金色火符专属包</t>
+  </si>
+  <si>
+    <t>金色战吼自选</t>
+  </si>
+  <si>
+    <t>1019,1020,1021,1022,1023,1024</t>
+  </si>
+  <si>
+    <t>金色战吼专属包</t>
+  </si>
+  <si>
+    <t>金色瞬移自选</t>
+  </si>
+  <si>
+    <t>1025,1026,1027,1028,1029,1030</t>
+  </si>
+  <si>
+    <t>金色瞬移专属包</t>
+  </si>
+  <si>
+    <t>金色隐身自选</t>
+  </si>
+  <si>
+    <t>1031,1032,1033,1034,1035,1036</t>
+  </si>
+  <si>
+    <t>金色隐身专属包</t>
+  </si>
+  <si>
+    <t>金色裂地自选</t>
+  </si>
+  <si>
+    <t>1037,1038,1039,1040,1041,1042</t>
+  </si>
+  <si>
+    <t>金色裂地专属包</t>
+  </si>
+  <si>
+    <t>金色分身自选</t>
+  </si>
+  <si>
+    <t>1043,1044,1045,1046,1047,1048</t>
+  </si>
+  <si>
+    <t>金色分身专属包</t>
+  </si>
+  <si>
+    <t>金色无极自选</t>
+  </si>
+  <si>
+    <t>1049,1050,1051,1052,1053,1054</t>
+  </si>
+  <si>
+    <t>金色无极专属包</t>
+  </si>
+  <si>
+    <t>金色武盾自选</t>
+  </si>
+  <si>
+    <t>1055,1056,1057,1058,1059,1060</t>
+  </si>
+  <si>
+    <t>金色法盾自选</t>
+  </si>
+  <si>
+    <t>1061,1062,1063,1064,1065,1066</t>
+  </si>
+  <si>
+    <t>金色道盾自选</t>
+  </si>
+  <si>
+    <t>1067,1068,1069,1070,1071,1072</t>
+  </si>
+  <si>
+    <t>金色专精自选</t>
+  </si>
+  <si>
+    <t>1073,1074,1075</t>
+  </si>
+  <si>
+    <t>暗金1阶自选</t>
+  </si>
+  <si>
     <t>1101,1102,1103,1104,1105,1106</t>
   </si>
   <si>
-    <t>高级暗金专属</t>
+    <t>暗金1阶技能专属</t>
+  </si>
+  <si>
+    <t>暗金2阶自选</t>
   </si>
   <si>
     <t>1107,1108,1109,1110,1111,1112</t>
-  </si>
-  <si>
-    <t>金色专属自选</t>
-  </si>
-  <si>
-    <t>1001,1002,1003,1010,1011,1012</t>
-  </si>
-  <si>
-    <t>高级金色专属</t>
-  </si>
-  <si>
-    <t>4,4,4,4,4,4,4,4,4,4</t>
-  </si>
-  <si>
-    <t>1007,1008,1009,1001,1002,1003,1004,1005,1006,1013</t>
-  </si>
-  <si>
-    <t>1,1,1,1,1,1,1,1,1,1</t>
-  </si>
-  <si>
-    <t>驱魔6件套</t>
-  </si>
-  <si>
-    <t>12,12,12,12,12,12,5,5</t>
-  </si>
-  <si>
-    <t>36,37,38,39,40,41,4005,4010</t>
-  </si>
-  <si>
-    <t>1,1,1,1,1,1,300,60</t>
-  </si>
-  <si>
-    <t>盾专属自选套</t>
-  </si>
-  <si>
-    <t>99,102,104</t>
-  </si>
-  <si>
-    <t>专属自选</t>
-  </si>
-  <si>
-    <t>4,4,4,4,4,4,4,4,4</t>
-  </si>
-  <si>
-    <t>99,100,101,102,103,104,105,96</t>
-  </si>
-  <si>
-    <t>法力盾4件套</t>
-  </si>
-  <si>
-    <t>12,12,12,12,5,5</t>
-  </si>
-  <si>
-    <t>26,27,28,29,4005,4010</t>
-  </si>
-  <si>
-    <t>1,1,1,1,300,60</t>
-  </si>
-  <si>
-    <t>神雷6件套</t>
-  </si>
-  <si>
-    <t>30,31,32,33,34,35,4005,4010</t>
-  </si>
-  <si>
-    <t>流光6件套</t>
-  </si>
-  <si>
-    <t>5,6,7,8,9,10,4005,4010</t>
-  </si>
-  <si>
-    <t>武神盾4件套</t>
-  </si>
-  <si>
-    <t>11,12,13,14,4005,4010</t>
-  </si>
-  <si>
-    <t>冰咆哮4件套</t>
-  </si>
-  <si>
-    <t>803,804,705,706,4005,4010</t>
-  </si>
-  <si>
-    <t>道力盾4件套</t>
-  </si>
-  <si>
-    <t>18,19,20,21,4005,4010</t>
-  </si>
-  <si>
-    <t>月神4件套</t>
-  </si>
-  <si>
-    <t>22,23,24,25,4005,4010</t>
-  </si>
-  <si>
-    <t>白银礼包</t>
-  </si>
-  <si>
-    <t>15,5,5,5,5,5</t>
-  </si>
-  <si>
-    <t>4014,4012,4001,4011,4102,4010</t>
-  </si>
-  <si>
-    <t>500,2000,10000000,20,200,50</t>
-  </si>
-  <si>
-    <t>经验丹0.5K,传世精华2k,魂环碎片1KW,红装精华3,高级书页200个,专属之心50个</t>
-  </si>
-  <si>
-    <t>黄金礼包</t>
-  </si>
-  <si>
-    <t>180005,180006,180018,180002,180004,180008</t>
-  </si>
-  <si>
-    <t>钻石礼包</t>
-  </si>
-  <si>
-    <t>180007,180009,180001,180002,180004,180019</t>
-  </si>
-  <si>
-    <t>高级法宝自选</t>
-  </si>
-  <si>
-    <t>战士经验红装</t>
-  </si>
-  <si>
-    <t>20,20,20,20,20,20,20,20</t>
-  </si>
-  <si>
-    <t>1,2,3,4,5,6,7,8</t>
-  </si>
-  <si>
-    <t>战士满经验红装自选</t>
-  </si>
-  <si>
-    <t>法师经验红装</t>
-  </si>
-  <si>
-    <t>9,10,11,12,13,14,15,16</t>
-  </si>
-  <si>
-    <t>法师满经验红装自选</t>
-  </si>
-  <si>
-    <t>道士经验红装</t>
-  </si>
-  <si>
-    <t>17,18,19,20,21,22,23,24</t>
-  </si>
-  <si>
-    <t>道士满经验红装自选</t>
-  </si>
-  <si>
-    <t>战士输出红装</t>
-  </si>
-  <si>
-    <t>25,26,27,28,29,30,31,32</t>
-  </si>
-  <si>
-    <t>战士输出红装自选</t>
-  </si>
-  <si>
-    <t>法师输出红装</t>
-  </si>
-  <si>
-    <t>33,34,35,36,37,38,39,40</t>
-  </si>
-  <si>
-    <t>法师输出红装自选</t>
-  </si>
-  <si>
-    <t>道士输出红装</t>
-  </si>
-  <si>
-    <t>20,20,20,20,20,20,20,20,20,20</t>
-  </si>
-  <si>
-    <t>41,42,43,44,45,46,47,48,49,50</t>
-  </si>
-  <si>
-    <t>道士输出红装自选</t>
-  </si>
-  <si>
-    <t>红装自选</t>
-  </si>
-  <si>
-    <t>109,110,111,112,113,114</t>
-  </si>
-  <si>
-    <t>战士暗金</t>
-  </si>
-  <si>
-    <t>151,152,153,154,155,156,157,158</t>
-  </si>
-  <si>
-    <t>法师暗金</t>
-  </si>
-  <si>
-    <t>161,162,163,164,165,166,167,168</t>
-  </si>
-  <si>
-    <t>道士暗金</t>
-  </si>
-  <si>
-    <t>171,172,173,174,175,176,177,178</t>
-  </si>
-  <si>
-    <t>战士平衡金装</t>
-  </si>
-  <si>
-    <t>101,102,103,104,105,106,107,108</t>
-  </si>
-  <si>
-    <t>法师平衡金装</t>
-  </si>
-  <si>
-    <t>109,110,111,112,113,114,115,116</t>
-  </si>
-  <si>
-    <t>道士平衡金装</t>
-  </si>
-  <si>
-    <t>117,118,119,120,121,122,123,124</t>
-  </si>
-  <si>
-    <t>战士防御金装</t>
-  </si>
-  <si>
-    <t>125,126,127,128,129,130,131,132</t>
-  </si>
-  <si>
-    <t>法师输出金装</t>
-  </si>
-  <si>
-    <t>133,134,135,136,137,138,139,140</t>
-  </si>
-  <si>
-    <t>金装自选</t>
-  </si>
-  <si>
-    <t>121,122,123,124,125</t>
-  </si>
-  <si>
-    <t>暗金自选</t>
-  </si>
-  <si>
-    <t>4,4,4</t>
-  </si>
-  <si>
-    <t>118,119,120</t>
-  </si>
-  <si>
-    <t>1,1,1,</t>
-  </si>
-  <si>
-    <t>40橙宠自选</t>
-  </si>
-  <si>
-    <t>21,21,21</t>
-  </si>
-  <si>
-    <t>1,2,3</t>
-  </si>
-  <si>
-    <t>40资质橙宠自选</t>
-  </si>
-  <si>
-    <t>45橙宠自选</t>
-  </si>
-  <si>
-    <t>4,5,6</t>
-  </si>
-  <si>
-    <t>45资质橙宠自选</t>
-  </si>
-  <si>
-    <t>50橙宠自选</t>
-  </si>
-  <si>
-    <t>7,8,9</t>
-  </si>
-  <si>
-    <t>50资质橙宠自选</t>
-  </si>
-  <si>
-    <t>40红宠自选</t>
-  </si>
-  <si>
-    <t>10,11,12</t>
-  </si>
-  <si>
-    <t>40资质红宠自选</t>
-  </si>
-  <si>
-    <t>45红宠自选</t>
-  </si>
-  <si>
-    <t>13,14,15</t>
-  </si>
-  <si>
-    <t>45资质红宠自选</t>
-  </si>
-  <si>
-    <t>50红宠自选</t>
-  </si>
-  <si>
-    <t>16,17,18</t>
-  </si>
-  <si>
-    <t>50资质红宠自选</t>
-  </si>
-  <si>
-    <t>40金宠自选</t>
-  </si>
-  <si>
-    <t>21,21,21,21,21,21,21,21,21,21,21,21</t>
-  </si>
-  <si>
-    <t>19,20,21,22,23,24,25,26,27,28,29,30</t>
-  </si>
-  <si>
-    <t>1,1,1,1,1,1,1,1,1,1,1,1</t>
-  </si>
-  <si>
-    <t>40资质金宠自选</t>
-  </si>
-  <si>
-    <t>40金宠自选1</t>
-  </si>
-  <si>
-    <t>45资质金宠自选</t>
-  </si>
-  <si>
-    <t>50金宠自选</t>
-  </si>
-  <si>
-    <t>31,32,33,34,35,36,37,38,39,40,41,42</t>
-  </si>
-  <si>
-    <t>50资质金宠自选</t>
-  </si>
-  <si>
-    <t>金色刺杀自选</t>
-  </si>
-  <si>
-    <t>1001,1002,1003,1004,1005,1006</t>
-  </si>
-  <si>
-    <t>金色刺杀专属包</t>
-  </si>
-  <si>
-    <t>金色雷电自选</t>
-  </si>
-  <si>
-    <t>1007,1008,1009,1010,1011,1012</t>
-  </si>
-  <si>
-    <t>金色雷电专属包</t>
-  </si>
-  <si>
-    <t>金色火符自选</t>
-  </si>
-  <si>
-    <t>1013,1014,1015,1016,1017,1018</t>
-  </si>
-  <si>
-    <t>金色火符专属包</t>
-  </si>
-  <si>
-    <t>金色战吼自选</t>
-  </si>
-  <si>
-    <t>1019,1020,1021,1022,1023,1024</t>
-  </si>
-  <si>
-    <t>金色战吼专属包</t>
-  </si>
-  <si>
-    <t>金色瞬移自选</t>
-  </si>
-  <si>
-    <t>1025,1026,1027,1028,1029,1030</t>
-  </si>
-  <si>
-    <t>金色瞬移专属包</t>
-  </si>
-  <si>
-    <t>金色隐身自选</t>
-  </si>
-  <si>
-    <t>1031,1032,1033,1034,1035,1036</t>
-  </si>
-  <si>
-    <t>金色隐身专属包</t>
-  </si>
-  <si>
-    <t>金色裂地自选</t>
-  </si>
-  <si>
-    <t>1037,1038,1039,1040,1041,1042</t>
-  </si>
-  <si>
-    <t>金色裂地专属包</t>
-  </si>
-  <si>
-    <t>金色分身自选</t>
-  </si>
-  <si>
-    <t>1043,1044,1045,1046,1047,1048</t>
-  </si>
-  <si>
-    <t>金色分身专属包</t>
-  </si>
-  <si>
-    <t>金色无极自选</t>
-  </si>
-  <si>
-    <t>1049,1050,1051,1052,1053,1054</t>
-  </si>
-  <si>
-    <t>金色无极专属包</t>
-  </si>
-  <si>
-    <t>金色武盾自选</t>
-  </si>
-  <si>
-    <t>1055,1056,1057,1058,1059,1060</t>
-  </si>
-  <si>
-    <t>金色法盾自选</t>
-  </si>
-  <si>
-    <t>1061,1062,1063,1064,1065,1066</t>
-  </si>
-  <si>
-    <t>金色道盾自选</t>
-  </si>
-  <si>
-    <t>1067,1068,1069,1070,1071,1072</t>
-  </si>
-  <si>
-    <t>金色专精自选</t>
-  </si>
-  <si>
-    <t>1073,1074,1075</t>
-  </si>
-  <si>
-    <t>暗金1阶自选</t>
-  </si>
-  <si>
-    <t>暗金1阶技能专属</t>
-  </si>
-  <si>
-    <t>暗金2阶自选</t>
   </si>
   <si>
     <t>暗金2阶技能专属</t>
@@ -1237,12 +1249,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -3415,10 +3427,10 @@
         <v>2</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="I50" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J50" s="5" t="s">
         <v>16</v>
@@ -3434,7 +3446,7 @@
         <v>94</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E51" s="1">
         <v>1</v>
@@ -3446,16 +3458,16 @@
         <v>2</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="I51" s="5" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="J51" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="52" customFormat="1" customHeight="1" spans="1:11">
@@ -3465,7 +3477,7 @@
         <v>95</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E52" s="1">
         <v>1</v>
@@ -3477,16 +3489,16 @@
         <v>2</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I52" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="J52" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="K52" s="1" t="s">
         <v>146</v>
-      </c>
-      <c r="J52" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="K52" s="1" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:11">
@@ -3494,7 +3506,7 @@
         <v>96</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E53" s="1">
         <v>0</v>
@@ -3506,16 +3518,16 @@
         <v>2</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I53" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="J53" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="K53" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="J53" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="K53" s="1" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:11">
@@ -3523,7 +3535,7 @@
         <v>97</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E54" s="1">
         <v>1</v>
@@ -3538,13 +3550,13 @@
         <v>132</v>
       </c>
       <c r="I54" s="5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="J54" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:11">
@@ -3552,7 +3564,7 @@
         <v>98</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E55" s="1">
         <v>1</v>
@@ -3564,16 +3576,16 @@
         <v>2</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="I55" s="5" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="J55" s="5" t="s">
         <v>91</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:11">
@@ -3581,7 +3593,7 @@
         <v>99</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E56" s="1">
         <v>0</v>
@@ -3593,16 +3605,16 @@
         <v>2</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I56" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="J56" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="K56" s="1" t="s">
         <v>159</v>
-      </c>
-      <c r="J56" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="K56" s="1" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:11">
@@ -3610,7 +3622,7 @@
         <v>100</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E57" s="1">
         <v>0</v>
@@ -3622,16 +3634,16 @@
         <v>2</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I57" s="5" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="J57" s="5" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:11">
@@ -3639,7 +3651,7 @@
         <v>101</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E58" s="1">
         <v>0</v>
@@ -3651,16 +3663,16 @@
         <v>2</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I58" s="5" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J58" s="5" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:11">
@@ -3668,7 +3680,7 @@
         <v>102</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E59" s="1">
         <v>0</v>
@@ -3680,16 +3692,16 @@
         <v>2</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I59" s="5" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="J59" s="5" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="3:11">
@@ -3697,7 +3709,7 @@
         <v>103</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E60" s="1">
         <v>0</v>
@@ -3709,16 +3721,16 @@
         <v>2</v>
       </c>
       <c r="H60" s="5" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I60" s="5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="J60" s="5" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="3:11">
@@ -3726,7 +3738,7 @@
         <v>104</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E61" s="1">
         <v>0</v>
@@ -3738,16 +3750,16 @@
         <v>2</v>
       </c>
       <c r="H61" s="5" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I61" s="5" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="J61" s="5" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="3:11">
@@ -3755,7 +3767,7 @@
         <v>105</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E62" s="1">
         <v>0</v>
@@ -3767,16 +3779,16 @@
         <v>2</v>
       </c>
       <c r="H62" s="5" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I62" s="5" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J62" s="5" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:11">
@@ -3784,7 +3796,7 @@
         <v>106</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E64" s="1">
         <v>1</v>
@@ -3796,16 +3808,16 @@
         <v>1</v>
       </c>
       <c r="H64" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="I64" s="5" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="J64" s="5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="K64" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:11">
@@ -3813,7 +3825,7 @@
         <v>107</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E65" s="1">
         <v>1</v>
@@ -3828,7 +3840,7 @@
         <v>64</v>
       </c>
       <c r="I65" s="5" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="J65" s="5" t="s">
         <v>40</v>
@@ -3842,7 +3854,7 @@
         <v>108</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E66" s="1">
         <v>1</v>
@@ -3857,13 +3869,13 @@
         <v>64</v>
       </c>
       <c r="I66" s="5" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="J66" s="5" t="s">
         <v>40</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:11">
@@ -3871,7 +3883,7 @@
         <v>109</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E68" s="1">
         <v>1</v>
@@ -3883,16 +3895,16 @@
         <v>2</v>
       </c>
       <c r="H68" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="I68" s="5" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="J68" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:11">
@@ -3900,7 +3912,7 @@
         <v>110</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E69" s="1">
         <v>1</v>
@@ -3912,16 +3924,16 @@
         <v>2</v>
       </c>
       <c r="H69" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="I69" s="5" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="J69" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:11">
@@ -3929,7 +3941,7 @@
         <v>111</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E70" s="1">
         <v>1</v>
@@ -3941,16 +3953,16 @@
         <v>2</v>
       </c>
       <c r="H70" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="I70" s="5" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="J70" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:11">
@@ -3958,7 +3970,7 @@
         <v>112</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E71" s="1">
         <v>1</v>
@@ -3970,16 +3982,16 @@
         <v>2</v>
       </c>
       <c r="H71" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="I71" s="5" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="J71" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:11">
@@ -3987,7 +3999,7 @@
         <v>113</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E72" s="1">
         <v>1</v>
@@ -3999,16 +4011,16 @@
         <v>2</v>
       </c>
       <c r="H72" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="I72" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="J72" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:11">
@@ -4016,7 +4028,7 @@
         <v>114</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E73" s="1">
         <v>1</v>
@@ -4028,16 +4040,16 @@
         <v>2</v>
       </c>
       <c r="H73" s="5" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="I73" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="J73" s="5" t="s">
         <v>91</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:11">
@@ -4045,7 +4057,7 @@
         <v>115</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E74" s="1">
         <v>1</v>
@@ -4057,16 +4069,16 @@
         <v>2</v>
       </c>
       <c r="H74" s="5" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="I74" s="5" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="J74" s="5" t="s">
         <v>40</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:11">
@@ -4074,7 +4086,7 @@
         <v>118</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E76" s="1">
         <v>1</v>
@@ -4086,16 +4098,16 @@
         <v>2</v>
       </c>
       <c r="H76" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="I76" s="5" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="J76" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K76" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:11">
@@ -4103,7 +4115,7 @@
         <v>119</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E77" s="1">
         <v>1</v>
@@ -4115,16 +4127,16 @@
         <v>2</v>
       </c>
       <c r="H77" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="I77" s="5" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="J77" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K77" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="3:11">
@@ -4132,7 +4144,7 @@
         <v>120</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E78" s="1">
         <v>1</v>
@@ -4144,16 +4156,16 @@
         <v>2</v>
       </c>
       <c r="H78" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="I78" s="5" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="J78" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K78" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="3:11">
@@ -4161,7 +4173,7 @@
         <v>121</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E79" s="1">
         <v>1</v>
@@ -4173,16 +4185,16 @@
         <v>2</v>
       </c>
       <c r="H79" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="I79" s="5" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J79" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="3:11">
@@ -4190,7 +4202,7 @@
         <v>122</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E80" s="1">
         <v>1</v>
@@ -4202,16 +4214,16 @@
         <v>2</v>
       </c>
       <c r="H80" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="I80" s="5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="J80" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K80" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="3:11">
@@ -4219,7 +4231,7 @@
         <v>123</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E81" s="1">
         <v>1</v>
@@ -4231,16 +4243,16 @@
         <v>2</v>
       </c>
       <c r="H81" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="I81" s="5" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="J81" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K81" s="3" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="3:11">
@@ -4248,7 +4260,7 @@
         <v>124</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E82" s="1">
         <v>1</v>
@@ -4260,16 +4272,16 @@
         <v>2</v>
       </c>
       <c r="H82" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="I82" s="5" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="J82" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K82" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="3:11">
@@ -4277,7 +4289,7 @@
         <v>125</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E83" s="1">
         <v>1</v>
@@ -4289,16 +4301,16 @@
         <v>2</v>
       </c>
       <c r="H83" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="I83" s="5" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="J83" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="85" customHeight="1" spans="3:11">
@@ -4306,7 +4318,7 @@
         <v>127</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E85" s="1">
         <v>1</v>
@@ -4318,16 +4330,16 @@
         <v>2</v>
       </c>
       <c r="H85" s="5" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="I85" s="5" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="J85" s="5" t="s">
         <v>40</v>
       </c>
       <c r="K85" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="3:11">
@@ -4335,7 +4347,7 @@
         <v>128</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E86" s="1">
         <v>1</v>
@@ -4347,16 +4359,16 @@
         <v>2</v>
       </c>
       <c r="H86" s="5" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I86" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="J86" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="K86" s="1" t="s">
         <v>225</v>
-      </c>
-      <c r="J86" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="K86" s="1" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="97" customHeight="1" spans="3:11">
@@ -4364,7 +4376,7 @@
         <v>201</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E97" s="1">
         <v>1</v>
@@ -4376,16 +4388,16 @@
         <v>2</v>
       </c>
       <c r="H97" s="5" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I97" s="5" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="J97" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K97" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="98" customHeight="1" spans="3:11">
@@ -4393,7 +4405,7 @@
         <v>202</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E98" s="1">
         <v>1</v>
@@ -4405,16 +4417,16 @@
         <v>2</v>
       </c>
       <c r="H98" s="5" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I98" s="5" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="J98" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K98" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="99" customHeight="1" spans="3:11">
@@ -4422,7 +4434,7 @@
         <v>203</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="E99" s="1">
         <v>1</v>
@@ -4434,16 +4446,16 @@
         <v>2</v>
       </c>
       <c r="H99" s="5" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I99" s="5" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="J99" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K99" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="100" customHeight="1" spans="3:11">
@@ -4451,7 +4463,7 @@
         <v>204</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E100" s="1">
         <v>1</v>
@@ -4463,16 +4475,16 @@
         <v>2</v>
       </c>
       <c r="H100" s="5" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I100" s="5" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="J100" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K100" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="101" customHeight="1" spans="3:11">
@@ -4480,7 +4492,7 @@
         <v>205</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E101" s="1">
         <v>1</v>
@@ -4492,16 +4504,16 @@
         <v>2</v>
       </c>
       <c r="H101" s="5" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I101" s="5" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="J101" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K101" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="102" customHeight="1" spans="3:11">
@@ -4509,7 +4521,7 @@
         <v>206</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E102" s="1">
         <v>1</v>
@@ -4521,16 +4533,16 @@
         <v>2</v>
       </c>
       <c r="H102" s="5" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I102" s="5" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="J102" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K102" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="103" customHeight="1" spans="3:11">
@@ -4538,7 +4550,7 @@
         <v>207</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E103" s="1">
         <v>1</v>
@@ -4550,16 +4562,16 @@
         <v>2</v>
       </c>
       <c r="H103" s="5" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="I103" s="5" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="J103" s="5" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="K103" s="1" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="104" customHeight="1" spans="3:11">
@@ -4567,7 +4579,7 @@
         <v>208</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E104" s="1">
         <v>1</v>
@@ -4579,16 +4591,16 @@
         <v>2</v>
       </c>
       <c r="H104" s="5" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I104" s="5" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="J104" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K104" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="105" customHeight="1" spans="3:11">
@@ -4596,7 +4608,7 @@
         <v>209</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E105" s="1">
         <v>1</v>
@@ -4608,16 +4620,16 @@
         <v>2</v>
       </c>
       <c r="H105" s="5" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="I105" s="5" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="J105" s="5" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="K105" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
   </sheetData>
@@ -4745,7 +4757,7 @@
         <v>1001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -4760,13 +4772,13 @@
         <v>14</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="J6" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4774,7 +4786,7 @@
         <v>1002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -4789,13 +4801,13 @@
         <v>14</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="J7" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4803,7 +4815,7 @@
         <v>1003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -4818,13 +4830,13 @@
         <v>14</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="J8" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4832,7 +4844,7 @@
         <v>1004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
@@ -4847,13 +4859,13 @@
         <v>14</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="J9" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4861,7 +4873,7 @@
         <v>1005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -4876,13 +4888,13 @@
         <v>14</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="J10" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4890,7 +4902,7 @@
         <v>1006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -4905,13 +4917,13 @@
         <v>14</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="J11" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4919,7 +4931,7 @@
         <v>1007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
@@ -4934,13 +4946,13 @@
         <v>14</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="J12" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4948,7 +4960,7 @@
         <v>1008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
@@ -4963,13 +4975,13 @@
         <v>14</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J13" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4977,7 +4989,7 @@
         <v>1009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
@@ -4992,13 +5004,13 @@
         <v>14</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="J14" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5006,7 +5018,7 @@
         <v>1010</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
@@ -5021,13 +5033,13 @@
         <v>14</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="J15" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5035,7 +5047,7 @@
         <v>1011</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E16" s="1">
         <v>1</v>
@@ -5050,13 +5062,13 @@
         <v>14</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="J16" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5064,7 +5076,7 @@
         <v>1012</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E17" s="1">
         <v>1</v>
@@ -5079,13 +5091,13 @@
         <v>14</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="J17" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5093,7 +5105,7 @@
         <v>1013</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E18" s="1">
         <v>1</v>
@@ -5108,13 +5120,13 @@
         <v>14</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="J18" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" ht="18" customHeight="1"/>
@@ -5123,7 +5135,7 @@
         <v>1101</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E20" s="1">
         <v>1</v>
@@ -5138,13 +5150,13 @@
         <v>14</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>139</v>
+        <v>294</v>
       </c>
       <c r="J20" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5152,7 +5164,7 @@
         <v>1102</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
@@ -5167,13 +5179,13 @@
         <v>14</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>141</v>
+        <v>297</v>
       </c>
       <c r="J21" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5181,7 +5193,7 @@
         <v>1103</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
@@ -5196,13 +5208,13 @@
         <v>14</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="J22" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5210,7 +5222,7 @@
         <v>1104</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
@@ -5225,13 +5237,13 @@
         <v>14</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="J23" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5239,7 +5251,7 @@
         <v>1105</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
@@ -5254,13 +5266,13 @@
         <v>14</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="J24" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5268,7 +5280,7 @@
         <v>1106</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="E25" s="1">
         <v>1</v>
@@ -5283,13 +5295,13 @@
         <v>14</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="J25" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5297,7 +5309,7 @@
         <v>1107</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
@@ -5312,13 +5324,13 @@
         <v>14</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="J26" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5326,7 +5338,7 @@
         <v>1108</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="E27" s="1">
         <v>1</v>
@@ -5341,13 +5353,13 @@
         <v>14</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="J27" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5355,7 +5367,7 @@
         <v>1109</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="E28" s="1">
         <v>1</v>
@@ -5370,13 +5382,13 @@
         <v>14</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="J28" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5384,7 +5396,7 @@
         <v>1110</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
@@ -5399,13 +5411,13 @@
         <v>14</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="J29" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5413,7 +5425,7 @@
         <v>1111</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
@@ -5428,13 +5440,13 @@
         <v>14</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="J30" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5442,7 +5454,7 @@
         <v>1112</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
@@ -5457,13 +5469,13 @@
         <v>14</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="J31" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="330">
   <si>
     <t>_id</t>
   </si>
@@ -504,6 +504,9 @@
   </si>
   <si>
     <t>1101,1102,1103,1104,1105,1106,1107,1108,1109,1110,1111</t>
+  </si>
+  <si>
+    <t>1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1</t>
   </si>
   <si>
     <t>高级暗金专属</t>
@@ -1249,12 +1252,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -3402,7 +3405,7 @@
         <v>139</v>
       </c>
       <c r="J49" s="5" t="s">
-        <v>16</v>
+        <v>140</v>
       </c>
       <c r="K49" s="1" t="s">
         <v>137</v>
@@ -3415,7 +3418,7 @@
         <v>91</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E50" s="1">
         <v>1</v>
@@ -3427,10 +3430,10 @@
         <v>2</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I50" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J50" s="5" t="s">
         <v>16</v>
@@ -3446,7 +3449,7 @@
         <v>94</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E51" s="1">
         <v>1</v>
@@ -3458,16 +3461,16 @@
         <v>2</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I51" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J51" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="52" customFormat="1" customHeight="1" spans="1:11">
@@ -3477,7 +3480,7 @@
         <v>95</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E52" s="1">
         <v>1</v>
@@ -3489,16 +3492,16 @@
         <v>2</v>
       </c>
       <c r="H52" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="I52" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="J52" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="K52" s="1" t="s">
         <v>147</v>
-      </c>
-      <c r="I52" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="J52" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="K52" s="1" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:11">
@@ -3506,7 +3509,7 @@
         <v>96</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E53" s="1">
         <v>0</v>
@@ -3518,16 +3521,16 @@
         <v>2</v>
       </c>
       <c r="H53" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="I53" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="J53" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="K53" s="1" t="s">
         <v>151</v>
-      </c>
-      <c r="I53" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="J53" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="K53" s="1" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:11">
@@ -3535,7 +3538,7 @@
         <v>97</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E54" s="1">
         <v>1</v>
@@ -3550,13 +3553,13 @@
         <v>132</v>
       </c>
       <c r="I54" s="5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J54" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:11">
@@ -3564,7 +3567,7 @@
         <v>98</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E55" s="1">
         <v>1</v>
@@ -3576,16 +3579,16 @@
         <v>2</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I55" s="5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J55" s="5" t="s">
         <v>91</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:11">
@@ -3593,7 +3596,7 @@
         <v>99</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E56" s="1">
         <v>0</v>
@@ -3605,16 +3608,16 @@
         <v>2</v>
       </c>
       <c r="H56" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="I56" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="J56" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="K56" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="I56" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="J56" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="K56" s="1" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:11">
@@ -3622,7 +3625,7 @@
         <v>100</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E57" s="1">
         <v>0</v>
@@ -3634,16 +3637,16 @@
         <v>2</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I57" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="J57" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="K57" s="1" t="s">
         <v>164</v>
-      </c>
-      <c r="J57" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="K57" s="1" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:11">
@@ -3651,7 +3654,7 @@
         <v>101</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E58" s="1">
         <v>0</v>
@@ -3663,16 +3666,16 @@
         <v>2</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I58" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="J58" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="K58" s="1" t="s">
         <v>166</v>
-      </c>
-      <c r="J58" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="K58" s="1" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:11">
@@ -3680,7 +3683,7 @@
         <v>102</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E59" s="1">
         <v>0</v>
@@ -3692,16 +3695,16 @@
         <v>2</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I59" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="J59" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="K59" s="1" t="s">
         <v>168</v>
-      </c>
-      <c r="J59" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="K59" s="1" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="3:11">
@@ -3709,7 +3712,7 @@
         <v>103</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E60" s="1">
         <v>0</v>
@@ -3721,16 +3724,16 @@
         <v>2</v>
       </c>
       <c r="H60" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I60" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="J60" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="K60" s="1" t="s">
         <v>170</v>
-      </c>
-      <c r="J60" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="K60" s="1" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="3:11">
@@ -3738,7 +3741,7 @@
         <v>104</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E61" s="1">
         <v>0</v>
@@ -3750,16 +3753,16 @@
         <v>2</v>
       </c>
       <c r="H61" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I61" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="J61" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="K61" s="1" t="s">
         <v>172</v>
-      </c>
-      <c r="J61" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="K61" s="1" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="3:11">
@@ -3767,7 +3770,7 @@
         <v>105</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E62" s="1">
         <v>0</v>
@@ -3779,16 +3782,16 @@
         <v>2</v>
       </c>
       <c r="H62" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I62" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="J62" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="K62" s="1" t="s">
         <v>174</v>
-      </c>
-      <c r="J62" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="K62" s="1" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:11">
@@ -3796,7 +3799,7 @@
         <v>106</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E64" s="1">
         <v>1</v>
@@ -3808,16 +3811,16 @@
         <v>1</v>
       </c>
       <c r="H64" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I64" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J64" s="5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K64" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:11">
@@ -3825,7 +3828,7 @@
         <v>107</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E65" s="1">
         <v>1</v>
@@ -3840,7 +3843,7 @@
         <v>64</v>
       </c>
       <c r="I65" s="5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J65" s="5" t="s">
         <v>40</v>
@@ -3854,7 +3857,7 @@
         <v>108</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E66" s="1">
         <v>1</v>
@@ -3869,13 +3872,13 @@
         <v>64</v>
       </c>
       <c r="I66" s="5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J66" s="5" t="s">
         <v>40</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:11">
@@ -3883,7 +3886,7 @@
         <v>109</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E68" s="1">
         <v>1</v>
@@ -3895,16 +3898,16 @@
         <v>2</v>
       </c>
       <c r="H68" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I68" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J68" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:11">
@@ -3912,7 +3915,7 @@
         <v>110</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E69" s="1">
         <v>1</v>
@@ -3924,16 +3927,16 @@
         <v>2</v>
       </c>
       <c r="H69" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I69" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J69" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:11">
@@ -3941,7 +3944,7 @@
         <v>111</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E70" s="1">
         <v>1</v>
@@ -3953,16 +3956,16 @@
         <v>2</v>
       </c>
       <c r="H70" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I70" s="5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="J70" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:11">
@@ -3970,7 +3973,7 @@
         <v>112</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E71" s="1">
         <v>1</v>
@@ -3982,16 +3985,16 @@
         <v>2</v>
       </c>
       <c r="H71" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I71" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J71" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:11">
@@ -3999,7 +4002,7 @@
         <v>113</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E72" s="1">
         <v>1</v>
@@ -4011,16 +4014,16 @@
         <v>2</v>
       </c>
       <c r="H72" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I72" s="5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="J72" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:11">
@@ -4028,7 +4031,7 @@
         <v>114</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E73" s="1">
         <v>1</v>
@@ -4040,16 +4043,16 @@
         <v>2</v>
       </c>
       <c r="H73" s="5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I73" s="5" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="J73" s="5" t="s">
         <v>91</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:11">
@@ -4057,7 +4060,7 @@
         <v>115</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E74" s="1">
         <v>1</v>
@@ -4069,16 +4072,16 @@
         <v>2</v>
       </c>
       <c r="H74" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I74" s="5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J74" s="5" t="s">
         <v>40</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:11">
@@ -4086,7 +4089,7 @@
         <v>118</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E76" s="1">
         <v>1</v>
@@ -4098,16 +4101,16 @@
         <v>2</v>
       </c>
       <c r="H76" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I76" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J76" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K76" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:11">
@@ -4115,7 +4118,7 @@
         <v>119</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E77" s="1">
         <v>1</v>
@@ -4127,16 +4130,16 @@
         <v>2</v>
       </c>
       <c r="H77" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I77" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J77" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K77" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="3:11">
@@ -4144,7 +4147,7 @@
         <v>120</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E78" s="1">
         <v>1</v>
@@ -4156,16 +4159,16 @@
         <v>2</v>
       </c>
       <c r="H78" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I78" s="5" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="J78" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K78" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="3:11">
@@ -4173,7 +4176,7 @@
         <v>121</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E79" s="1">
         <v>1</v>
@@ -4185,16 +4188,16 @@
         <v>2</v>
       </c>
       <c r="H79" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I79" s="5" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="J79" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="3:11">
@@ -4202,7 +4205,7 @@
         <v>122</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E80" s="1">
         <v>1</v>
@@ -4214,16 +4217,16 @@
         <v>2</v>
       </c>
       <c r="H80" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I80" s="5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J80" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K80" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="3:11">
@@ -4231,7 +4234,7 @@
         <v>123</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E81" s="1">
         <v>1</v>
@@ -4243,16 +4246,16 @@
         <v>2</v>
       </c>
       <c r="H81" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I81" s="5" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="J81" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K81" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="3:11">
@@ -4260,7 +4263,7 @@
         <v>124</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E82" s="1">
         <v>1</v>
@@ -4272,16 +4275,16 @@
         <v>2</v>
       </c>
       <c r="H82" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I82" s="5" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="J82" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K82" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="3:11">
@@ -4289,7 +4292,7 @@
         <v>125</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E83" s="1">
         <v>1</v>
@@ -4301,16 +4304,16 @@
         <v>2</v>
       </c>
       <c r="H83" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I83" s="5" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="J83" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="85" customHeight="1" spans="3:11">
@@ -4318,7 +4321,7 @@
         <v>127</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E85" s="1">
         <v>1</v>
@@ -4330,16 +4333,16 @@
         <v>2</v>
       </c>
       <c r="H85" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I85" s="5" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="J85" s="5" t="s">
         <v>40</v>
       </c>
       <c r="K85" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="3:11">
@@ -4347,7 +4350,7 @@
         <v>128</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E86" s="1">
         <v>1</v>
@@ -4359,16 +4362,16 @@
         <v>2</v>
       </c>
       <c r="H86" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="I86" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="J86" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="K86" s="1" t="s">
         <v>226</v>
-      </c>
-      <c r="I86" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="J86" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="K86" s="1" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="97" customHeight="1" spans="3:11">
@@ -4376,7 +4379,7 @@
         <v>201</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E97" s="1">
         <v>1</v>
@@ -4388,16 +4391,16 @@
         <v>2</v>
       </c>
       <c r="H97" s="5" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I97" s="5" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="J97" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K97" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="98" customHeight="1" spans="3:11">
@@ -4405,7 +4408,7 @@
         <v>202</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E98" s="1">
         <v>1</v>
@@ -4417,16 +4420,16 @@
         <v>2</v>
       </c>
       <c r="H98" s="5" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I98" s="5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="J98" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K98" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="99" customHeight="1" spans="3:11">
@@ -4434,7 +4437,7 @@
         <v>203</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E99" s="1">
         <v>1</v>
@@ -4446,16 +4449,16 @@
         <v>2</v>
       </c>
       <c r="H99" s="5" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I99" s="5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J99" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K99" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="100" customHeight="1" spans="3:11">
@@ -4463,7 +4466,7 @@
         <v>204</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E100" s="1">
         <v>1</v>
@@ -4475,16 +4478,16 @@
         <v>2</v>
       </c>
       <c r="H100" s="5" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I100" s="5" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="J100" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K100" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="101" customHeight="1" spans="3:11">
@@ -4492,7 +4495,7 @@
         <v>205</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E101" s="1">
         <v>1</v>
@@ -4504,16 +4507,16 @@
         <v>2</v>
       </c>
       <c r="H101" s="5" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I101" s="5" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="J101" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K101" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="102" customHeight="1" spans="3:11">
@@ -4521,7 +4524,7 @@
         <v>206</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E102" s="1">
         <v>1</v>
@@ -4533,16 +4536,16 @@
         <v>2</v>
       </c>
       <c r="H102" s="5" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I102" s="5" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="J102" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K102" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="103" customHeight="1" spans="3:11">
@@ -4550,7 +4553,7 @@
         <v>207</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E103" s="1">
         <v>1</v>
@@ -4562,16 +4565,16 @@
         <v>2</v>
       </c>
       <c r="H103" s="5" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I103" s="5" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="J103" s="5" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K103" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="104" customHeight="1" spans="3:11">
@@ -4579,7 +4582,7 @@
         <v>208</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E104" s="1">
         <v>1</v>
@@ -4591,16 +4594,16 @@
         <v>2</v>
       </c>
       <c r="H104" s="5" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I104" s="5" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="J104" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K104" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="105" customHeight="1" spans="3:11">
@@ -4608,7 +4611,7 @@
         <v>209</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E105" s="1">
         <v>1</v>
@@ -4620,16 +4623,16 @@
         <v>2</v>
       </c>
       <c r="H105" s="5" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I105" s="5" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J105" s="5" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K105" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
   </sheetData>
@@ -4757,7 +4760,7 @@
         <v>1001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -4772,13 +4775,13 @@
         <v>14</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="J6" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4786,7 +4789,7 @@
         <v>1002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -4801,13 +4804,13 @@
         <v>14</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J7" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4815,7 +4818,7 @@
         <v>1003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -4830,13 +4833,13 @@
         <v>14</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="J8" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4844,7 +4847,7 @@
         <v>1004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
@@ -4859,13 +4862,13 @@
         <v>14</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="J9" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4873,7 +4876,7 @@
         <v>1005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -4888,13 +4891,13 @@
         <v>14</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="J10" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4902,7 +4905,7 @@
         <v>1006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -4917,13 +4920,13 @@
         <v>14</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="J11" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4931,7 +4934,7 @@
         <v>1007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
@@ -4946,13 +4949,13 @@
         <v>14</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J12" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4960,7 +4963,7 @@
         <v>1008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
@@ -4975,13 +4978,13 @@
         <v>14</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J13" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4989,7 +4992,7 @@
         <v>1009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
@@ -5004,13 +5007,13 @@
         <v>14</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J14" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5018,7 +5021,7 @@
         <v>1010</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
@@ -5033,13 +5036,13 @@
         <v>14</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="J15" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5047,7 +5050,7 @@
         <v>1011</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E16" s="1">
         <v>1</v>
@@ -5062,13 +5065,13 @@
         <v>14</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="J16" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5076,7 +5079,7 @@
         <v>1012</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E17" s="1">
         <v>1</v>
@@ -5091,13 +5094,13 @@
         <v>14</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="J17" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5105,7 +5108,7 @@
         <v>1013</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E18" s="1">
         <v>1</v>
@@ -5120,13 +5123,13 @@
         <v>14</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="J18" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" ht="18" customHeight="1"/>
@@ -5135,7 +5138,7 @@
         <v>1101</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E20" s="1">
         <v>1</v>
@@ -5150,13 +5153,13 @@
         <v>14</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="J20" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5164,7 +5167,7 @@
         <v>1102</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
@@ -5179,13 +5182,13 @@
         <v>14</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="J21" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5193,7 +5196,7 @@
         <v>1103</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
@@ -5208,13 +5211,13 @@
         <v>14</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J22" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5222,7 +5225,7 @@
         <v>1104</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
@@ -5237,13 +5240,13 @@
         <v>14</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="J23" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5251,7 +5254,7 @@
         <v>1105</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
@@ -5266,13 +5269,13 @@
         <v>14</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="J24" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5280,7 +5283,7 @@
         <v>1106</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E25" s="1">
         <v>1</v>
@@ -5295,13 +5298,13 @@
         <v>14</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="J25" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5309,7 +5312,7 @@
         <v>1107</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
@@ -5324,13 +5327,13 @@
         <v>14</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="J26" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5338,7 +5341,7 @@
         <v>1108</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E27" s="1">
         <v>1</v>
@@ -5353,13 +5356,13 @@
         <v>14</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="J27" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5367,7 +5370,7 @@
         <v>1109</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E28" s="1">
         <v>1</v>
@@ -5382,13 +5385,13 @@
         <v>14</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="J28" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5396,7 +5399,7 @@
         <v>1110</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
@@ -5411,13 +5414,13 @@
         <v>14</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="J29" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5425,7 +5428,7 @@
         <v>1111</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
@@ -5440,13 +5443,13 @@
         <v>14</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="J30" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5454,7 +5457,7 @@
         <v>1112</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
@@ -5469,13 +5472,13 @@
         <v>14</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="J31" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="332">
   <si>
     <t>_id</t>
   </si>
@@ -861,6 +861,12 @@
   </si>
   <si>
     <t>50资质金宠自选</t>
+  </si>
+  <si>
+    <t>50金宠自选1</t>
+  </si>
+  <si>
+    <t>43,44,45</t>
   </si>
   <si>
     <t>金色刺杀自选</t>
@@ -2046,7 +2052,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:K105"/>
+  <dimension ref="A3:K106"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -4632,6 +4638,35 @@
         <v>252</v>
       </c>
       <c r="K105" s="1" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="106" customHeight="1" spans="3:11">
+      <c r="C106" s="1">
+        <v>210</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="E106" s="1">
+        <v>1</v>
+      </c>
+      <c r="F106" s="3">
+        <v>0</v>
+      </c>
+      <c r="G106" s="3">
+        <v>2</v>
+      </c>
+      <c r="H106" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="I106" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="J106" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K106" s="1" t="s">
         <v>258</v>
       </c>
     </row>
@@ -4760,7 +4795,7 @@
         <v>1001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -4775,13 +4810,13 @@
         <v>14</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="J6" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4789,7 +4824,7 @@
         <v>1002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -4804,13 +4839,13 @@
         <v>14</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="J7" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4818,7 +4853,7 @@
         <v>1003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -4833,13 +4868,13 @@
         <v>14</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="J8" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4847,7 +4882,7 @@
         <v>1004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
@@ -4862,13 +4897,13 @@
         <v>14</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="J9" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4876,7 +4911,7 @@
         <v>1005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -4891,13 +4926,13 @@
         <v>14</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="J10" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4905,7 +4940,7 @@
         <v>1006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -4920,13 +4955,13 @@
         <v>14</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="J11" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4934,7 +4969,7 @@
         <v>1007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
@@ -4949,13 +4984,13 @@
         <v>14</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J12" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4963,7 +4998,7 @@
         <v>1008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
@@ -4978,13 +5013,13 @@
         <v>14</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="J13" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4992,7 +5027,7 @@
         <v>1009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
@@ -5007,13 +5042,13 @@
         <v>14</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="J14" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5021,7 +5056,7 @@
         <v>1010</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
@@ -5036,13 +5071,13 @@
         <v>14</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="J15" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5050,7 +5085,7 @@
         <v>1011</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E16" s="1">
         <v>1</v>
@@ -5065,13 +5100,13 @@
         <v>14</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="J16" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5079,7 +5114,7 @@
         <v>1012</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="E17" s="1">
         <v>1</v>
@@ -5094,13 +5129,13 @@
         <v>14</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="J17" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5108,7 +5143,7 @@
         <v>1013</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="E18" s="1">
         <v>1</v>
@@ -5123,13 +5158,13 @@
         <v>14</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="J18" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" ht="18" customHeight="1"/>
@@ -5138,7 +5173,7 @@
         <v>1101</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E20" s="1">
         <v>1</v>
@@ -5153,13 +5188,13 @@
         <v>14</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="J20" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5167,7 +5202,7 @@
         <v>1102</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
@@ -5182,13 +5217,13 @@
         <v>14</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J21" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5196,7 +5231,7 @@
         <v>1103</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
@@ -5211,13 +5246,13 @@
         <v>14</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="J22" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5225,7 +5260,7 @@
         <v>1104</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
@@ -5240,13 +5275,13 @@
         <v>14</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="J23" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5254,7 +5289,7 @@
         <v>1105</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
@@ -5269,13 +5304,13 @@
         <v>14</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="J24" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5283,7 +5318,7 @@
         <v>1106</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="E25" s="1">
         <v>1</v>
@@ -5298,13 +5333,13 @@
         <v>14</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="J25" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5312,7 +5347,7 @@
         <v>1107</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
@@ -5327,13 +5362,13 @@
         <v>14</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="J26" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5341,7 +5376,7 @@
         <v>1108</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E27" s="1">
         <v>1</v>
@@ -5356,13 +5391,13 @@
         <v>14</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="J27" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5370,7 +5405,7 @@
         <v>1109</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E28" s="1">
         <v>1</v>
@@ -5385,13 +5420,13 @@
         <v>14</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="J28" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5399,7 +5434,7 @@
         <v>1110</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
@@ -5414,13 +5449,13 @@
         <v>14</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="J29" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5428,7 +5463,7 @@
         <v>1111</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
@@ -5443,13 +5478,13 @@
         <v>14</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="J30" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5457,7 +5492,7 @@
         <v>1112</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
@@ -5472,13 +5507,13 @@
         <v>14</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="J31" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="334">
   <si>
     <t>_id</t>
   </si>
@@ -851,7 +851,10 @@
     <t>40金宠自选1</t>
   </si>
   <si>
-    <t>45资质金宠自选</t>
+    <t>16,17,18,101,102,103,104,105,106</t>
+  </si>
+  <si>
+    <t>40资质金宠自选1</t>
   </si>
   <si>
     <t>50金宠自选</t>
@@ -866,7 +869,10 @@
     <t>50金宠自选1</t>
   </si>
   <si>
-    <t>43,44,45</t>
+    <t>21,21,21,21,21,21</t>
+  </si>
+  <si>
+    <t>43,44,45,46,47,48</t>
   </si>
   <si>
     <t>金色刺杀自选</t>
@@ -1258,12 +1264,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -4600,16 +4606,16 @@
         <v>2</v>
       </c>
       <c r="H104" s="5" t="s">
-        <v>231</v>
+        <v>250</v>
       </c>
       <c r="I104" s="5" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="J104" s="5" t="s">
-        <v>32</v>
+        <v>252</v>
       </c>
       <c r="K104" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="105" customHeight="1" spans="3:11">
@@ -4617,7 +4623,7 @@
         <v>209</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E105" s="1">
         <v>1</v>
@@ -4632,13 +4638,13 @@
         <v>250</v>
       </c>
       <c r="I105" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="J105" s="5" t="s">
         <v>252</v>
       </c>
       <c r="K105" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="106" customHeight="1" spans="3:11">
@@ -4646,28 +4652,28 @@
         <v>210</v>
       </c>
       <c r="D106" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="E106" s="1">
+        <v>1</v>
+      </c>
+      <c r="F106" s="3">
+        <v>0</v>
+      </c>
+      <c r="G106" s="3">
+        <v>2</v>
+      </c>
+      <c r="H106" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="I106" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="J106" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="K106" s="1" t="s">
         <v>259</v>
-      </c>
-      <c r="E106" s="1">
-        <v>1</v>
-      </c>
-      <c r="F106" s="3">
-        <v>0</v>
-      </c>
-      <c r="G106" s="3">
-        <v>2</v>
-      </c>
-      <c r="H106" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="I106" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="J106" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K106" s="1" t="s">
-        <v>258</v>
       </c>
     </row>
   </sheetData>
@@ -4795,7 +4801,7 @@
         <v>1001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -4810,13 +4816,13 @@
         <v>14</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="J6" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4824,7 +4830,7 @@
         <v>1002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -4839,13 +4845,13 @@
         <v>14</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="J7" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4853,7 +4859,7 @@
         <v>1003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -4868,13 +4874,13 @@
         <v>14</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="J8" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4882,7 +4888,7 @@
         <v>1004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
@@ -4897,13 +4903,13 @@
         <v>14</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="J9" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4911,7 +4917,7 @@
         <v>1005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -4926,13 +4932,13 @@
         <v>14</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="J10" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4940,7 +4946,7 @@
         <v>1006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -4955,13 +4961,13 @@
         <v>14</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="J11" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4969,7 +4975,7 @@
         <v>1007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
@@ -4984,13 +4990,13 @@
         <v>14</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J12" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4998,7 +5004,7 @@
         <v>1008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
@@ -5013,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="J13" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5027,7 +5033,7 @@
         <v>1009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
@@ -5042,13 +5048,13 @@
         <v>14</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="J14" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5056,7 +5062,7 @@
         <v>1010</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
@@ -5071,13 +5077,13 @@
         <v>14</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="J15" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5085,7 +5091,7 @@
         <v>1011</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="E16" s="1">
         <v>1</v>
@@ -5100,13 +5106,13 @@
         <v>14</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="J16" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5114,7 +5120,7 @@
         <v>1012</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="E17" s="1">
         <v>1</v>
@@ -5129,13 +5135,13 @@
         <v>14</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="J17" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5143,7 +5149,7 @@
         <v>1013</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E18" s="1">
         <v>1</v>
@@ -5158,13 +5164,13 @@
         <v>14</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="J18" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" ht="18" customHeight="1"/>
@@ -5173,7 +5179,7 @@
         <v>1101</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="E20" s="1">
         <v>1</v>
@@ -5188,13 +5194,13 @@
         <v>14</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="J20" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5202,7 +5208,7 @@
         <v>1102</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
@@ -5217,13 +5223,13 @@
         <v>14</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="J21" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5231,7 +5237,7 @@
         <v>1103</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
@@ -5246,13 +5252,13 @@
         <v>14</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="J22" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5260,7 +5266,7 @@
         <v>1104</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
@@ -5275,13 +5281,13 @@
         <v>14</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="J23" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5289,7 +5295,7 @@
         <v>1105</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
@@ -5304,13 +5310,13 @@
         <v>14</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="J24" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5318,7 +5324,7 @@
         <v>1106</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E25" s="1">
         <v>1</v>
@@ -5333,13 +5339,13 @@
         <v>14</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="J25" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5347,7 +5353,7 @@
         <v>1107</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
@@ -5362,13 +5368,13 @@
         <v>14</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="J26" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5376,7 +5382,7 @@
         <v>1108</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="E27" s="1">
         <v>1</v>
@@ -5391,13 +5397,13 @@
         <v>14</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="J27" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5405,7 +5411,7 @@
         <v>1109</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E28" s="1">
         <v>1</v>
@@ -5420,13 +5426,13 @@
         <v>14</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="J28" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5434,7 +5440,7 @@
         <v>1110</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
@@ -5449,13 +5455,13 @@
         <v>14</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="J29" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5463,7 +5469,7 @@
         <v>1111</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
@@ -5478,13 +5484,13 @@
         <v>14</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="J30" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5492,7 +5498,7 @@
         <v>1112</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
@@ -5507,13 +5513,13 @@
         <v>14</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="J31" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -416,7 +416,7 @@
     <t>207,4022</t>
   </si>
   <si>
-    <t>2,10000</t>
+    <t>2,100000</t>
   </si>
   <si>
     <t>2个40资质金宠+1w口粮</t>
@@ -428,7 +428,7 @@
     <t>209,4022</t>
   </si>
   <si>
-    <t>2,50000</t>
+    <t>2,200000</t>
   </si>
   <si>
     <t>2个50资质金宠+5w口粮</t>
@@ -1264,12 +1264,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="337">
   <si>
     <t>_id</t>
   </si>
@@ -497,6 +497,18 @@
     <t>12技能三选一</t>
   </si>
   <si>
+    <t>生肖自选</t>
+  </si>
+  <si>
+    <t>22,22,22,22,22,22,22,22,22,22,22,22</t>
+  </si>
+  <si>
+    <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
+  </si>
+  <si>
+    <t>1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1</t>
+  </si>
+  <si>
     <t>暗金专属自选</t>
   </si>
   <si>
@@ -504,9 +516,6 @@
   </si>
   <si>
     <t>1101,1102,1103,1104,1105,1106,1107,1108,1109,1110,1111</t>
-  </si>
-  <si>
-    <t>1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1</t>
   </si>
   <si>
     <t>高级暗金专属</t>
@@ -2058,7 +2067,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:K106"/>
+  <dimension ref="A3:K107"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -3382,52 +3391,52 @@
     <row r="48" customFormat="1" customHeight="1" spans="1:11">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
-      <c r="C48" s="1"/>
-      <c r="D48" s="1"/>
-      <c r="E48" s="1"/>
-      <c r="F48" s="3"/>
-      <c r="G48" s="3"/>
-      <c r="H48" s="1"/>
-      <c r="I48" s="1"/>
-      <c r="J48" s="1"/>
-      <c r="K48" s="1"/>
+      <c r="C48" s="1">
+        <v>43</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E48" s="1">
+        <v>1</v>
+      </c>
+      <c r="F48" s="3">
+        <v>0</v>
+      </c>
+      <c r="G48" s="3">
+        <v>1</v>
+      </c>
+      <c r="H48" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="I48" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="J48" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="K48" s="1" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="49" customFormat="1" customHeight="1" spans="1:11">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
-      <c r="C49" s="1">
-        <v>90</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="E49" s="1">
-        <v>1</v>
-      </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
-      <c r="G49" s="1">
-        <v>2</v>
-      </c>
-      <c r="H49" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="I49" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="J49" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="K49" s="1" t="s">
-        <v>137</v>
-      </c>
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
+      <c r="E49" s="1"/>
+      <c r="F49" s="3"/>
+      <c r="G49" s="3"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1"/>
+      <c r="J49" s="1"/>
+      <c r="K49" s="1"/>
     </row>
     <row r="50" customFormat="1" customHeight="1" spans="1:11">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>141</v>
@@ -3448,17 +3457,17 @@
         <v>143</v>
       </c>
       <c r="J50" s="5" t="s">
-        <v>16</v>
+        <v>140</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="51" customFormat="1" customHeight="1" spans="1:11">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>144</v>
@@ -3482,14 +3491,14 @@
         <v>16</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="52" customFormat="1" customHeight="1" spans="1:11">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>147</v>
@@ -3510,76 +3519,78 @@
         <v>149</v>
       </c>
       <c r="J52" s="5" t="s">
-        <v>150</v>
+        <v>16</v>
       </c>
       <c r="K52" s="1" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="53" customHeight="1" spans="3:11">
+    <row r="53" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A53" s="1"/>
+      <c r="B53" s="1"/>
       <c r="C53" s="1">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D53" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E53" s="1">
+        <v>1</v>
+      </c>
+      <c r="F53" s="3">
+        <v>0</v>
+      </c>
+      <c r="G53" s="1">
+        <v>2</v>
+      </c>
+      <c r="H53" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="E53" s="1">
-        <v>0</v>
-      </c>
-      <c r="F53" s="3">
-        <v>0</v>
-      </c>
-      <c r="G53" s="1">
-        <v>2</v>
-      </c>
-      <c r="H53" s="5" t="s">
+      <c r="I53" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="I53" s="5" t="s">
+      <c r="J53" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="J53" s="5" t="s">
-        <v>154</v>
-      </c>
       <c r="K53" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:11">
       <c r="C54" s="1">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D54" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E54" s="1">
+        <v>0</v>
+      </c>
+      <c r="F54" s="3">
+        <v>0</v>
+      </c>
+      <c r="G54" s="1">
+        <v>2</v>
+      </c>
+      <c r="H54" s="5" t="s">
         <v>155</v>
-      </c>
-      <c r="E54" s="1">
-        <v>1</v>
-      </c>
-      <c r="F54" s="3">
-        <v>0</v>
-      </c>
-      <c r="G54" s="1">
-        <v>2</v>
-      </c>
-      <c r="H54" s="5" t="s">
-        <v>132</v>
       </c>
       <c r="I54" s="5" t="s">
         <v>156</v>
       </c>
       <c r="J54" s="5" t="s">
-        <v>32</v>
+        <v>157</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:11">
       <c r="C55" s="1">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E55" s="1">
         <v>1</v>
@@ -3591,27 +3602,27 @@
         <v>2</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>158</v>
+        <v>132</v>
       </c>
       <c r="I55" s="5" t="s">
         <v>159</v>
       </c>
       <c r="J55" s="5" t="s">
-        <v>91</v>
+        <v>32</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:11">
       <c r="C56" s="1">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>160</v>
       </c>
       <c r="E56" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" s="3">
         <v>0</v>
@@ -3626,7 +3637,7 @@
         <v>162</v>
       </c>
       <c r="J56" s="5" t="s">
-        <v>163</v>
+        <v>91</v>
       </c>
       <c r="K56" s="1" t="s">
         <v>160</v>
@@ -3634,39 +3645,39 @@
     </row>
     <row r="57" customHeight="1" spans="3:11">
       <c r="C57" s="1">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D57" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E57" s="1">
+        <v>0</v>
+      </c>
+      <c r="F57" s="3">
+        <v>0</v>
+      </c>
+      <c r="G57" s="1">
+        <v>2</v>
+      </c>
+      <c r="H57" s="5" t="s">
         <v>164</v>
-      </c>
-      <c r="E57" s="1">
-        <v>0</v>
-      </c>
-      <c r="F57" s="3">
-        <v>0</v>
-      </c>
-      <c r="G57" s="1">
-        <v>2</v>
-      </c>
-      <c r="H57" s="5" t="s">
-        <v>152</v>
       </c>
       <c r="I57" s="5" t="s">
         <v>165</v>
       </c>
       <c r="J57" s="5" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:11">
       <c r="C58" s="1">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E58" s="1">
         <v>0</v>
@@ -3678,24 +3689,24 @@
         <v>2</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="I58" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="J58" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="K58" s="1" t="s">
         <v>167</v>
-      </c>
-      <c r="J58" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="K58" s="1" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:11">
       <c r="C59" s="1">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E59" s="1">
         <v>0</v>
@@ -3707,24 +3718,24 @@
         <v>2</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="I59" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="J59" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="K59" s="1" t="s">
         <v>169</v>
-      </c>
-      <c r="J59" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="K59" s="1" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="3:11">
       <c r="C60" s="1">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E60" s="1">
         <v>0</v>
@@ -3736,24 +3747,24 @@
         <v>2</v>
       </c>
       <c r="H60" s="5" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="I60" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="J60" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="K60" s="1" t="s">
         <v>171</v>
-      </c>
-      <c r="J60" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="K60" s="1" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="3:11">
       <c r="C61" s="1">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E61" s="1">
         <v>0</v>
@@ -3765,111 +3776,111 @@
         <v>2</v>
       </c>
       <c r="H61" s="5" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="I61" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="J61" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="K61" s="1" t="s">
         <v>173</v>
-      </c>
-      <c r="J61" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="K61" s="1" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="3:11">
       <c r="C62" s="1">
+        <v>104</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E62" s="1">
+        <v>0</v>
+      </c>
+      <c r="F62" s="3">
+        <v>0</v>
+      </c>
+      <c r="G62" s="1">
+        <v>2</v>
+      </c>
+      <c r="H62" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="I62" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="J62" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="K62" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="63" customHeight="1" spans="3:11">
+      <c r="C63" s="1">
         <v>105</v>
       </c>
-      <c r="D62" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="E62" s="1">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
-      <c r="G62" s="1">
-        <v>2</v>
-      </c>
-      <c r="H62" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="I62" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="J62" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="K62" s="1" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="64" customHeight="1" spans="3:11">
-      <c r="C64" s="1">
-        <v>106</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="E64" s="1">
-        <v>1</v>
-      </c>
-      <c r="F64" s="3">
-        <v>0</v>
-      </c>
-      <c r="G64" s="1">
-        <v>1</v>
-      </c>
-      <c r="H64" s="5" t="s">
+      <c r="D63" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="I64" s="5" t="s">
+      <c r="E63" s="1">
+        <v>0</v>
+      </c>
+      <c r="F63" s="3">
+        <v>0</v>
+      </c>
+      <c r="G63" s="1">
+        <v>2</v>
+      </c>
+      <c r="H63" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="I63" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="J64" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="K64" s="1" t="s">
-        <v>180</v>
+      <c r="J63" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="K63" s="1" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:11">
       <c r="C65" s="1">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D65" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="E65" s="1">
+        <v>1</v>
+      </c>
+      <c r="F65" s="3">
+        <v>0</v>
+      </c>
+      <c r="G65" s="1">
+        <v>1</v>
+      </c>
+      <c r="H65" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="I65" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="E65" s="1">
-        <v>1</v>
-      </c>
-      <c r="F65" s="3">
-        <v>0</v>
-      </c>
-      <c r="G65" s="1">
-        <v>2</v>
-      </c>
-      <c r="H65" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="I65" s="5" t="s">
+      <c r="J65" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="J65" s="5" t="s">
-        <v>40</v>
-      </c>
       <c r="K65" s="1" t="s">
-        <v>83</v>
+        <v>183</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="3:11">
       <c r="C66" s="1">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E66" s="1">
         <v>1</v>
@@ -3884,62 +3895,62 @@
         <v>64</v>
       </c>
       <c r="I66" s="5" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="J66" s="5" t="s">
         <v>40</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="68" customHeight="1" spans="3:11">
-      <c r="C68" s="1">
-        <v>109</v>
-      </c>
-      <c r="D68" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="67" customHeight="1" spans="3:11">
+      <c r="C67" s="1">
+        <v>108</v>
+      </c>
+      <c r="D67" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="E68" s="1">
-        <v>1</v>
-      </c>
-      <c r="F68" s="3">
-        <v>0</v>
-      </c>
-      <c r="G68" s="3">
-        <v>2</v>
-      </c>
-      <c r="H68" s="5" t="s">
+      <c r="E67" s="1">
+        <v>1</v>
+      </c>
+      <c r="F67" s="3">
+        <v>0</v>
+      </c>
+      <c r="G67" s="1">
+        <v>2</v>
+      </c>
+      <c r="H67" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="I67" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="I68" s="5" t="s">
+      <c r="J67" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K67" s="1" t="s">
         <v>188</v>
-      </c>
-      <c r="J68" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="K68" s="1" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:11">
       <c r="C69" s="1">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D69" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="E69" s="1">
+        <v>1</v>
+      </c>
+      <c r="F69" s="3">
+        <v>0</v>
+      </c>
+      <c r="G69" s="3">
+        <v>2</v>
+      </c>
+      <c r="H69" s="5" t="s">
         <v>190</v>
-      </c>
-      <c r="E69" s="1">
-        <v>1</v>
-      </c>
-      <c r="F69" s="3">
-        <v>0</v>
-      </c>
-      <c r="G69" s="3">
-        <v>2</v>
-      </c>
-      <c r="H69" s="5" t="s">
-        <v>187</v>
       </c>
       <c r="I69" s="5" t="s">
         <v>191</v>
@@ -3953,7 +3964,7 @@
     </row>
     <row r="70" customHeight="1" spans="3:11">
       <c r="C70" s="1">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>193</v>
@@ -3968,7 +3979,7 @@
         <v>2</v>
       </c>
       <c r="H70" s="5" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I70" s="5" t="s">
         <v>194</v>
@@ -3982,7 +3993,7 @@
     </row>
     <row r="71" customHeight="1" spans="3:11">
       <c r="C71" s="1">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>196</v>
@@ -3997,7 +4008,7 @@
         <v>2</v>
       </c>
       <c r="H71" s="5" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I71" s="5" t="s">
         <v>197</v>
@@ -4011,7 +4022,7 @@
     </row>
     <row r="72" customHeight="1" spans="3:11">
       <c r="C72" s="1">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>199</v>
@@ -4026,7 +4037,7 @@
         <v>2</v>
       </c>
       <c r="H72" s="5" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I72" s="5" t="s">
         <v>200</v>
@@ -4040,7 +4051,7 @@
     </row>
     <row r="73" customHeight="1" spans="3:11">
       <c r="C73" s="1">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>202</v>
@@ -4055,82 +4066,82 @@
         <v>2</v>
       </c>
       <c r="H73" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="I73" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="I73" s="5" t="s">
+      <c r="J73" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K73" s="1" t="s">
         <v>204</v>
-      </c>
-      <c r="J73" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="K73" s="1" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:11">
       <c r="C74" s="1">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D74" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="E74" s="1">
+        <v>1</v>
+      </c>
+      <c r="F74" s="3">
+        <v>0</v>
+      </c>
+      <c r="G74" s="3">
+        <v>2</v>
+      </c>
+      <c r="H74" s="5" t="s">
         <v>206</v>
-      </c>
-      <c r="E74" s="1">
-        <v>1</v>
-      </c>
-      <c r="F74" s="3">
-        <v>0</v>
-      </c>
-      <c r="G74" s="3">
-        <v>2</v>
-      </c>
-      <c r="H74" s="5" t="s">
-        <v>145</v>
       </c>
       <c r="I74" s="5" t="s">
         <v>207</v>
       </c>
       <c r="J74" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="K74" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="75" customHeight="1" spans="3:11">
+      <c r="C75" s="1">
+        <v>115</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="E75" s="1">
+        <v>1</v>
+      </c>
+      <c r="F75" s="3">
+        <v>0</v>
+      </c>
+      <c r="G75" s="3">
+        <v>2</v>
+      </c>
+      <c r="H75" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="I75" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="J75" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="K74" s="1" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="76" customHeight="1" spans="3:11">
-      <c r="C76" s="1">
-        <v>118</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="E76" s="1">
-        <v>1</v>
-      </c>
-      <c r="F76" s="3">
-        <v>0</v>
-      </c>
-      <c r="G76" s="3">
-        <v>2</v>
-      </c>
-      <c r="H76" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="I76" s="5" t="s">
+      <c r="K75" s="1" t="s">
         <v>209</v>
-      </c>
-      <c r="J76" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="K76" s="3" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:11">
       <c r="C77" s="1">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E77" s="1">
         <v>1</v>
@@ -4142,24 +4153,24 @@
         <v>2</v>
       </c>
       <c r="H77" s="5" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I77" s="5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J77" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K77" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="3:11">
       <c r="C78" s="1">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E78" s="1">
         <v>1</v>
@@ -4171,24 +4182,24 @@
         <v>2</v>
       </c>
       <c r="H78" s="5" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I78" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J78" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K78" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="3:11">
       <c r="C79" s="1">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E79" s="1">
         <v>1</v>
@@ -4200,24 +4211,24 @@
         <v>2</v>
       </c>
       <c r="H79" s="5" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I79" s="5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J79" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="3:11">
       <c r="C80" s="1">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E80" s="1">
         <v>1</v>
@@ -4229,24 +4240,24 @@
         <v>2</v>
       </c>
       <c r="H80" s="5" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I80" s="5" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="J80" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K80" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="3:11">
       <c r="C81" s="1">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E81" s="1">
         <v>1</v>
@@ -4258,24 +4269,24 @@
         <v>2</v>
       </c>
       <c r="H81" s="5" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I81" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J81" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K81" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="3:11">
       <c r="C82" s="1">
-        <v>124</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>220</v>
+        <v>123</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>221</v>
       </c>
       <c r="E82" s="1">
         <v>1</v>
@@ -4287,24 +4298,24 @@
         <v>2</v>
       </c>
       <c r="H82" s="5" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I82" s="5" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="J82" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="K82" s="1" t="s">
-        <v>220</v>
+      <c r="K82" s="3" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="3:11">
       <c r="C83" s="1">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E83" s="1">
         <v>1</v>
@@ -4316,53 +4327,53 @@
         <v>2</v>
       </c>
       <c r="H83" s="5" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I83" s="5" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J83" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="85" customHeight="1" spans="3:11">
-      <c r="C85" s="1">
-        <v>127</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="E85" s="1">
-        <v>1</v>
-      </c>
-      <c r="F85" s="3">
-        <v>0</v>
-      </c>
-      <c r="G85" s="3">
-        <v>2</v>
-      </c>
-      <c r="H85" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="I85" s="5" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="84" customHeight="1" spans="3:11">
+      <c r="C84" s="1">
+        <v>125</v>
+      </c>
+      <c r="D84" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="J85" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="K85" s="1" t="s">
-        <v>224</v>
+      <c r="E84" s="1">
+        <v>1</v>
+      </c>
+      <c r="F84" s="3">
+        <v>0</v>
+      </c>
+      <c r="G84" s="3">
+        <v>2</v>
+      </c>
+      <c r="H84" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="I84" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="J84" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K84" s="1" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="3:11">
       <c r="C86" s="1">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E86" s="1">
         <v>1</v>
@@ -4374,65 +4385,65 @@
         <v>2</v>
       </c>
       <c r="H86" s="5" t="s">
-        <v>227</v>
+        <v>148</v>
       </c>
       <c r="I86" s="5" t="s">
         <v>228</v>
       </c>
       <c r="J86" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K86" s="1" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="87" customHeight="1" spans="3:11">
+      <c r="C87" s="1">
+        <v>128</v>
+      </c>
+      <c r="D87" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="K86" s="1" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="97" customHeight="1" spans="3:11">
-      <c r="C97" s="1">
-        <v>201</v>
-      </c>
-      <c r="D97" s="1" t="s">
+      <c r="E87" s="1">
+        <v>1</v>
+      </c>
+      <c r="F87" s="3">
+        <v>0</v>
+      </c>
+      <c r="G87" s="3">
+        <v>2</v>
+      </c>
+      <c r="H87" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="E97" s="1">
-        <v>1</v>
-      </c>
-      <c r="F97" s="3">
-        <v>0</v>
-      </c>
-      <c r="G97" s="3">
-        <v>2</v>
-      </c>
-      <c r="H97" s="5" t="s">
+      <c r="I87" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="I97" s="5" t="s">
+      <c r="J87" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="J97" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K97" s="1" t="s">
-        <v>233</v>
+      <c r="K87" s="1" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="98" customHeight="1" spans="3:11">
       <c r="C98" s="1">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D98" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E98" s="1">
+        <v>1</v>
+      </c>
+      <c r="F98" s="3">
+        <v>0</v>
+      </c>
+      <c r="G98" s="3">
+        <v>2</v>
+      </c>
+      <c r="H98" s="5" t="s">
         <v>234</v>
-      </c>
-      <c r="E98" s="1">
-        <v>1</v>
-      </c>
-      <c r="F98" s="3">
-        <v>0</v>
-      </c>
-      <c r="G98" s="3">
-        <v>2</v>
-      </c>
-      <c r="H98" s="5" t="s">
-        <v>231</v>
       </c>
       <c r="I98" s="5" t="s">
         <v>235</v>
@@ -4446,7 +4457,7 @@
     </row>
     <row r="99" customHeight="1" spans="3:11">
       <c r="C99" s="1">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D99" s="1" t="s">
         <v>237</v>
@@ -4461,7 +4472,7 @@
         <v>2</v>
       </c>
       <c r="H99" s="5" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="I99" s="5" t="s">
         <v>238</v>
@@ -4475,7 +4486,7 @@
     </row>
     <row r="100" customHeight="1" spans="3:11">
       <c r="C100" s="1">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D100" s="1" t="s">
         <v>240</v>
@@ -4490,7 +4501,7 @@
         <v>2</v>
       </c>
       <c r="H100" s="5" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="I100" s="5" t="s">
         <v>241</v>
@@ -4504,7 +4515,7 @@
     </row>
     <row r="101" customHeight="1" spans="3:11">
       <c r="C101" s="1">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D101" s="1" t="s">
         <v>243</v>
@@ -4519,7 +4530,7 @@
         <v>2</v>
       </c>
       <c r="H101" s="5" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="I101" s="5" t="s">
         <v>244</v>
@@ -4533,7 +4544,7 @@
     </row>
     <row r="102" customHeight="1" spans="3:11">
       <c r="C102" s="1">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D102" s="1" t="s">
         <v>246</v>
@@ -4548,7 +4559,7 @@
         <v>2</v>
       </c>
       <c r="H102" s="5" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="I102" s="5" t="s">
         <v>247</v>
@@ -4562,7 +4573,7 @@
     </row>
     <row r="103" customHeight="1" spans="3:11">
       <c r="C103" s="1">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D103" s="1" t="s">
         <v>249</v>
@@ -4577,42 +4588,42 @@
         <v>2</v>
       </c>
       <c r="H103" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="I103" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="I103" s="5" t="s">
+      <c r="J103" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K103" s="1" t="s">
         <v>251</v>
-      </c>
-      <c r="J103" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="K103" s="1" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="104" customHeight="1" spans="3:11">
       <c r="C104" s="1">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D104" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="E104" s="1">
+        <v>1</v>
+      </c>
+      <c r="F104" s="3">
+        <v>0</v>
+      </c>
+      <c r="G104" s="3">
+        <v>2</v>
+      </c>
+      <c r="H104" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="I104" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="E104" s="1">
-        <v>1</v>
-      </c>
-      <c r="F104" s="3">
-        <v>0</v>
-      </c>
-      <c r="G104" s="3">
-        <v>2</v>
-      </c>
-      <c r="H104" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="I104" s="5" t="s">
+      <c r="J104" s="5" t="s">
         <v>255</v>
-      </c>
-      <c r="J104" s="5" t="s">
-        <v>252</v>
       </c>
       <c r="K104" s="1" t="s">
         <v>256</v>
@@ -4620,7 +4631,7 @@
     </row>
     <row r="105" customHeight="1" spans="3:11">
       <c r="C105" s="1">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D105" s="1" t="s">
         <v>257</v>
@@ -4635,13 +4646,13 @@
         <v>2</v>
       </c>
       <c r="H105" s="5" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="I105" s="5" t="s">
         <v>258</v>
       </c>
       <c r="J105" s="5" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="K105" s="1" t="s">
         <v>259</v>
@@ -4649,7 +4660,7 @@
     </row>
     <row r="106" customHeight="1" spans="3:11">
       <c r="C106" s="1">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D106" s="1" t="s">
         <v>260</v>
@@ -4664,16 +4675,45 @@
         <v>2</v>
       </c>
       <c r="H106" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="I106" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="I106" s="5" t="s">
+      <c r="J106" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="K106" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="J106" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="K106" s="1" t="s">
-        <v>259</v>
+    </row>
+    <row r="107" customHeight="1" spans="3:11">
+      <c r="C107" s="1">
+        <v>210</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="E107" s="1">
+        <v>1</v>
+      </c>
+      <c r="F107" s="3">
+        <v>0</v>
+      </c>
+      <c r="G107" s="3">
+        <v>2</v>
+      </c>
+      <c r="H107" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="I107" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="J107" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="K107" s="1" t="s">
+        <v>262</v>
       </c>
     </row>
   </sheetData>
@@ -4801,7 +4841,7 @@
         <v>1001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -4816,13 +4856,13 @@
         <v>14</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="J6" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4830,7 +4870,7 @@
         <v>1002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -4845,13 +4885,13 @@
         <v>14</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="J7" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4859,7 +4899,7 @@
         <v>1003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -4874,13 +4914,13 @@
         <v>14</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="J8" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4888,7 +4928,7 @@
         <v>1004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
@@ -4903,13 +4943,13 @@
         <v>14</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="J9" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4917,7 +4957,7 @@
         <v>1005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -4932,13 +4972,13 @@
         <v>14</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="J10" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4946,7 +4986,7 @@
         <v>1006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -4961,13 +5001,13 @@
         <v>14</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="J11" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4975,7 +5015,7 @@
         <v>1007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
@@ -4990,13 +5030,13 @@
         <v>14</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="J12" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5004,7 +5044,7 @@
         <v>1008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
@@ -5019,13 +5059,13 @@
         <v>14</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="J13" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5033,7 +5073,7 @@
         <v>1009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
@@ -5048,13 +5088,13 @@
         <v>14</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="J14" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5062,7 +5102,7 @@
         <v>1010</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
@@ -5077,13 +5117,13 @@
         <v>14</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="J15" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5091,7 +5131,7 @@
         <v>1011</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="E16" s="1">
         <v>1</v>
@@ -5106,13 +5146,13 @@
         <v>14</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="J16" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5120,7 +5160,7 @@
         <v>1012</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E17" s="1">
         <v>1</v>
@@ -5135,13 +5175,13 @@
         <v>14</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="J17" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5149,7 +5189,7 @@
         <v>1013</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="E18" s="1">
         <v>1</v>
@@ -5164,13 +5204,13 @@
         <v>14</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="J18" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" ht="18" customHeight="1"/>
@@ -5179,7 +5219,7 @@
         <v>1101</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="E20" s="1">
         <v>1</v>
@@ -5194,13 +5234,13 @@
         <v>14</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="J20" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5208,7 +5248,7 @@
         <v>1102</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
@@ -5223,13 +5263,13 @@
         <v>14</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="J21" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5237,7 +5277,7 @@
         <v>1103</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
@@ -5252,13 +5292,13 @@
         <v>14</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="J22" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5266,7 +5306,7 @@
         <v>1104</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
@@ -5281,13 +5321,13 @@
         <v>14</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="J23" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5295,7 +5335,7 @@
         <v>1105</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
@@ -5310,13 +5350,13 @@
         <v>14</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="J24" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5324,7 +5364,7 @@
         <v>1106</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E25" s="1">
         <v>1</v>
@@ -5339,13 +5379,13 @@
         <v>14</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="J25" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5353,7 +5393,7 @@
         <v>1107</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
@@ -5368,13 +5408,13 @@
         <v>14</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="J26" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5382,7 +5422,7 @@
         <v>1108</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E27" s="1">
         <v>1</v>
@@ -5397,13 +5437,13 @@
         <v>14</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="J27" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5411,7 +5451,7 @@
         <v>1109</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E28" s="1">
         <v>1</v>
@@ -5426,13 +5466,13 @@
         <v>14</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="J28" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5440,7 +5480,7 @@
         <v>1110</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
@@ -5455,13 +5495,13 @@
         <v>14</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="J29" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5469,7 +5509,7 @@
         <v>1111</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
@@ -5484,13 +5524,13 @@
         <v>14</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="J30" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5498,7 +5538,7 @@
         <v>1112</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
@@ -5513,13 +5553,13 @@
         <v>14</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J31" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -3404,7 +3404,7 @@
         <v>0</v>
       </c>
       <c r="G48" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H48" s="5" t="s">
         <v>138</v>

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="338">
   <si>
     <t>_id</t>
   </si>
@@ -860,7 +860,10 @@
     <t>40金宠自选1</t>
   </si>
   <si>
-    <t>16,17,18,101,102,103,104,105,106</t>
+    <t>21,21,21,21,21,21,21,21,21,21,21,21,21,21,21</t>
+  </si>
+  <si>
+    <t>16,17,18,101,102,103,104,105,106,107,108,109</t>
   </si>
   <si>
     <t>40资质金宠自选1</t>
@@ -4646,16 +4649,16 @@
         <v>2</v>
       </c>
       <c r="H105" s="5" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="I105" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="J105" s="5" t="s">
-        <v>255</v>
+        <v>140</v>
       </c>
       <c r="K105" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="106" customHeight="1" spans="3:11">
@@ -4663,7 +4666,7 @@
         <v>209</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E106" s="1">
         <v>1</v>
@@ -4678,13 +4681,13 @@
         <v>253</v>
       </c>
       <c r="I106" s="5" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="J106" s="5" t="s">
         <v>255</v>
       </c>
       <c r="K106" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="107" customHeight="1" spans="3:11">
@@ -4692,7 +4695,7 @@
         <v>210</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E107" s="1">
         <v>1</v>
@@ -4704,16 +4707,16 @@
         <v>2</v>
       </c>
       <c r="H107" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I107" s="5" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="J107" s="5" t="s">
         <v>255</v>
       </c>
       <c r="K107" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -4841,7 +4844,7 @@
         <v>1001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -4856,13 +4859,13 @@
         <v>14</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J6" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4870,7 +4873,7 @@
         <v>1002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -4885,13 +4888,13 @@
         <v>14</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="J7" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4899,7 +4902,7 @@
         <v>1003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -4914,13 +4917,13 @@
         <v>14</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J8" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4928,7 +4931,7 @@
         <v>1004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
@@ -4943,13 +4946,13 @@
         <v>14</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="J9" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4957,7 +4960,7 @@
         <v>1005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -4972,13 +4975,13 @@
         <v>14</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="J10" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4986,7 +4989,7 @@
         <v>1006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -5001,13 +5004,13 @@
         <v>14</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="J11" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5015,7 +5018,7 @@
         <v>1007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
@@ -5030,13 +5033,13 @@
         <v>14</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="J12" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5044,7 +5047,7 @@
         <v>1008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
@@ -5059,13 +5062,13 @@
         <v>14</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="J13" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5073,7 +5076,7 @@
         <v>1009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
@@ -5088,13 +5091,13 @@
         <v>14</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="J14" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5102,7 +5105,7 @@
         <v>1010</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
@@ -5117,13 +5120,13 @@
         <v>14</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="J15" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5131,7 +5134,7 @@
         <v>1011</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E16" s="1">
         <v>1</v>
@@ -5146,13 +5149,13 @@
         <v>14</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J16" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5160,7 +5163,7 @@
         <v>1012</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E17" s="1">
         <v>1</v>
@@ -5175,13 +5178,13 @@
         <v>14</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="J17" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5189,7 +5192,7 @@
         <v>1013</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E18" s="1">
         <v>1</v>
@@ -5204,13 +5207,13 @@
         <v>14</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J18" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" ht="18" customHeight="1"/>
@@ -5219,7 +5222,7 @@
         <v>1101</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E20" s="1">
         <v>1</v>
@@ -5234,13 +5237,13 @@
         <v>14</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="J20" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5248,7 +5251,7 @@
         <v>1102</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
@@ -5263,13 +5266,13 @@
         <v>14</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J21" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5277,7 +5280,7 @@
         <v>1103</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
@@ -5292,13 +5295,13 @@
         <v>14</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="J22" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5306,7 +5309,7 @@
         <v>1104</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
@@ -5321,13 +5324,13 @@
         <v>14</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="J23" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5335,7 +5338,7 @@
         <v>1105</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
@@ -5350,13 +5353,13 @@
         <v>14</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J24" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5364,7 +5367,7 @@
         <v>1106</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E25" s="1">
         <v>1</v>
@@ -5379,13 +5382,13 @@
         <v>14</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="J25" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5393,7 +5396,7 @@
         <v>1107</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
@@ -5408,13 +5411,13 @@
         <v>14</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J26" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5422,7 +5425,7 @@
         <v>1108</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E27" s="1">
         <v>1</v>
@@ -5437,13 +5440,13 @@
         <v>14</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="J27" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5451,7 +5454,7 @@
         <v>1109</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E28" s="1">
         <v>1</v>
@@ -5466,13 +5469,13 @@
         <v>14</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="J28" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5480,7 +5483,7 @@
         <v>1110</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
@@ -5495,13 +5498,13 @@
         <v>14</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="J29" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5509,7 +5512,7 @@
         <v>1111</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
@@ -5524,13 +5527,13 @@
         <v>14</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="J30" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5538,7 +5541,7 @@
         <v>1112</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
@@ -5553,13 +5556,13 @@
         <v>14</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="J31" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="347">
   <si>
     <t>_id</t>
   </si>
@@ -719,6 +719,9 @@
     <t>109,110,111,112,113,114</t>
   </si>
   <si>
+    <t>#</t>
+  </si>
+  <si>
     <t>战士暗金</t>
   </si>
   <si>
@@ -767,6 +770,24 @@
     <t>133,134,135,136,137,138,139,140</t>
   </si>
   <si>
+    <t>粉色战士</t>
+  </si>
+  <si>
+    <t>181,182,183,184,185,186,187,188</t>
+  </si>
+  <si>
+    <t>粉色法师</t>
+  </si>
+  <si>
+    <t>191,192,193,194,195,196,197,198</t>
+  </si>
+  <si>
+    <t>粉色道士</t>
+  </si>
+  <si>
+    <t>201,202,203,204,205,206,207,208</t>
+  </si>
+  <si>
     <t>金装自选</t>
   </si>
   <si>
@@ -783,6 +804,12 @@
   </si>
   <si>
     <t>1,1,1,</t>
+  </si>
+  <si>
+    <t>粉色自选</t>
+  </si>
+  <si>
+    <t>126,127,128</t>
   </si>
   <si>
     <t>40橙宠自选</t>
@@ -2070,7 +2097,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:K107"/>
+  <dimension ref="A3:K110"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -4139,12 +4166,18 @@
         <v>209</v>
       </c>
     </row>
-    <row r="77" customHeight="1" spans="3:11">
+    <row r="77" customHeight="1" spans="1:11">
+      <c r="A77" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="C77" s="1">
         <v>118</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E77" s="1">
         <v>1</v>
@@ -4159,21 +4192,27 @@
         <v>190</v>
       </c>
       <c r="I77" s="5" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="J77" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K77" s="3" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="78" customHeight="1" spans="1:11">
+      <c r="A78" s="1" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="78" customHeight="1" spans="3:11">
+      <c r="B78" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="C78" s="1">
         <v>119</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E78" s="1">
         <v>1</v>
@@ -4188,21 +4227,27 @@
         <v>190</v>
       </c>
       <c r="I78" s="5" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="J78" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K78" s="3" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="79" customHeight="1" spans="3:11">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="79" customHeight="1" spans="1:11">
+      <c r="A79" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="C79" s="1">
         <v>120</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E79" s="1">
         <v>1</v>
@@ -4217,21 +4262,27 @@
         <v>190</v>
       </c>
       <c r="I79" s="5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J79" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="80" customHeight="1" spans="3:11">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="80" customHeight="1" spans="1:11">
+      <c r="A80" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="C80" s="1">
         <v>121</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E80" s="1">
         <v>1</v>
@@ -4246,21 +4297,27 @@
         <v>190</v>
       </c>
       <c r="I80" s="5" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="J80" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K80" s="3" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="81" customHeight="1" spans="3:11">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="81" customHeight="1" spans="1:11">
+      <c r="A81" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="C81" s="1">
         <v>122</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E81" s="1">
         <v>1</v>
@@ -4275,21 +4332,27 @@
         <v>190</v>
       </c>
       <c r="I81" s="5" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="J81" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K81" s="3" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="82" customHeight="1" spans="3:11">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="82" customHeight="1" spans="1:11">
+      <c r="A82" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="C82" s="1">
         <v>123</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E82" s="1">
         <v>1</v>
@@ -4304,21 +4367,27 @@
         <v>190</v>
       </c>
       <c r="I82" s="5" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="J82" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K82" s="3" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="83" customHeight="1" spans="3:11">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="83" customHeight="1" spans="1:11">
+      <c r="A83" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="C83" s="1">
         <v>124</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E83" s="1">
         <v>1</v>
@@ -4333,21 +4402,27 @@
         <v>190</v>
       </c>
       <c r="I83" s="5" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="J83" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="84" customHeight="1" spans="3:11">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="84" customHeight="1" spans="1:11">
+      <c r="A84" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="C84" s="1">
         <v>125</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E84" s="1">
         <v>1</v>
@@ -4362,21 +4437,62 @@
         <v>190</v>
       </c>
       <c r="I84" s="5" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="J84" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K84" s="1" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="86" customHeight="1" spans="3:11">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="85" customHeight="1" spans="1:11">
+      <c r="A85" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C85" s="1">
+        <v>126</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E85" s="1">
+        <v>1</v>
+      </c>
+      <c r="F85" s="3">
+        <v>0</v>
+      </c>
+      <c r="G85" s="3">
+        <v>2</v>
+      </c>
+      <c r="H85" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="I85" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="J85" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K85" s="1" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="86" customHeight="1" spans="1:11">
+      <c r="A86" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="C86" s="1">
         <v>127</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E86" s="1">
         <v>1</v>
@@ -4388,24 +4504,30 @@
         <v>2</v>
       </c>
       <c r="H86" s="5" t="s">
-        <v>148</v>
+        <v>190</v>
       </c>
       <c r="I86" s="5" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="J86" s="5" t="s">
-        <v>40</v>
+        <v>87</v>
       </c>
       <c r="K86" s="1" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="87" customHeight="1" spans="3:11">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="87" customHeight="1" spans="1:11">
+      <c r="A87" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="C87" s="1">
         <v>128</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E87" s="1">
         <v>1</v>
@@ -4417,123 +4539,141 @@
         <v>2</v>
       </c>
       <c r="H87" s="5" t="s">
-        <v>230</v>
+        <v>190</v>
       </c>
       <c r="I87" s="5" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="J87" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K87" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="K87" s="1" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="98" customHeight="1" spans="3:11">
-      <c r="C98" s="1">
-        <v>201</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="E98" s="1">
-        <v>1</v>
-      </c>
-      <c r="F98" s="3">
-        <v>0</v>
-      </c>
-      <c r="G98" s="3">
-        <v>2</v>
-      </c>
-      <c r="H98" s="5" t="s">
+    </row>
+    <row r="89" customHeight="1" spans="1:11">
+      <c r="A89" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C89" s="1">
+        <v>137</v>
+      </c>
+      <c r="D89" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="I98" s="5" t="s">
+      <c r="E89" s="1">
+        <v>1</v>
+      </c>
+      <c r="F89" s="3">
+        <v>0</v>
+      </c>
+      <c r="G89" s="3">
+        <v>2</v>
+      </c>
+      <c r="H89" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="I89" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="J98" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K98" s="1" t="s">
+      <c r="J89" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K89" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="90" customHeight="1" spans="1:11">
+      <c r="A90" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C90" s="1">
+        <v>138</v>
+      </c>
+      <c r="D90" s="1" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="99" customHeight="1" spans="3:11">
-      <c r="C99" s="1">
-        <v>202</v>
-      </c>
-      <c r="D99" s="1" t="s">
+      <c r="E90" s="1">
+        <v>1</v>
+      </c>
+      <c r="F90" s="3">
+        <v>0</v>
+      </c>
+      <c r="G90" s="3">
+        <v>2</v>
+      </c>
+      <c r="H90" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="E99" s="1">
-        <v>1</v>
-      </c>
-      <c r="F99" s="3">
-        <v>0</v>
-      </c>
-      <c r="G99" s="3">
-        <v>2</v>
-      </c>
-      <c r="H99" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="I99" s="5" t="s">
+      <c r="I90" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="J99" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K99" s="1" t="s">
+      <c r="J90" s="5" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="100" customHeight="1" spans="3:11">
-      <c r="C100" s="1">
-        <v>203</v>
-      </c>
-      <c r="D100" s="1" t="s">
+      <c r="K90" s="1" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="91" customHeight="1" spans="1:11">
+      <c r="A91" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C91" s="1">
+        <v>139</v>
+      </c>
+      <c r="D91" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="E100" s="1">
-        <v>1</v>
-      </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
-        <v>2</v>
-      </c>
-      <c r="H100" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="I100" s="5" t="s">
+      <c r="E91" s="1">
+        <v>1</v>
+      </c>
+      <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
+        <v>2</v>
+      </c>
+      <c r="H91" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="I91" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="J100" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K100" s="1" t="s">
-        <v>242</v>
+      <c r="J91" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="K91" s="1" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="101" customHeight="1" spans="3:11">
       <c r="C101" s="1">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D101" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="E101" s="1">
+        <v>1</v>
+      </c>
+      <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
+        <v>2</v>
+      </c>
+      <c r="H101" s="5" t="s">
         <v>243</v>
-      </c>
-      <c r="E101" s="1">
-        <v>1</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>2</v>
-      </c>
-      <c r="H101" s="5" t="s">
-        <v>234</v>
       </c>
       <c r="I101" s="5" t="s">
         <v>244</v>
@@ -4547,7 +4687,7 @@
     </row>
     <row r="102" customHeight="1" spans="3:11">
       <c r="C102" s="1">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D102" s="1" t="s">
         <v>246</v>
@@ -4562,7 +4702,7 @@
         <v>2</v>
       </c>
       <c r="H102" s="5" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="I102" s="5" t="s">
         <v>247</v>
@@ -4576,7 +4716,7 @@
     </row>
     <row r="103" customHeight="1" spans="3:11">
       <c r="C103" s="1">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="D103" s="1" t="s">
         <v>249</v>
@@ -4591,7 +4731,7 @@
         <v>2</v>
       </c>
       <c r="H103" s="5" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="I103" s="5" t="s">
         <v>250</v>
@@ -4605,7 +4745,7 @@
     </row>
     <row r="104" customHeight="1" spans="3:11">
       <c r="C104" s="1">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D104" s="1" t="s">
         <v>252</v>
@@ -4620,53 +4760,53 @@
         <v>2</v>
       </c>
       <c r="H104" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="I104" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="I104" s="5" t="s">
+      <c r="J104" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K104" s="1" t="s">
         <v>254</v>
-      </c>
-      <c r="J104" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="K104" s="1" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="105" customHeight="1" spans="3:11">
       <c r="C105" s="1">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D105" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="E105" s="1">
+        <v>1</v>
+      </c>
+      <c r="F105" s="3">
+        <v>0</v>
+      </c>
+      <c r="G105" s="3">
+        <v>2</v>
+      </c>
+      <c r="H105" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="I105" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="J105" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K105" s="1" t="s">
         <v>257</v>
-      </c>
-      <c r="E105" s="1">
-        <v>1</v>
-      </c>
-      <c r="F105" s="3">
-        <v>0</v>
-      </c>
-      <c r="G105" s="3">
-        <v>2</v>
-      </c>
-      <c r="H105" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="I105" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="J105" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="K105" s="1" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="106" customHeight="1" spans="3:11">
       <c r="C106" s="1">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="E106" s="1">
         <v>1</v>
@@ -4678,45 +4818,132 @@
         <v>2</v>
       </c>
       <c r="H106" s="5" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="I106" s="5" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="J106" s="5" t="s">
-        <v>255</v>
+        <v>32</v>
       </c>
       <c r="K106" s="1" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
     </row>
     <row r="107" customHeight="1" spans="3:11">
       <c r="C107" s="1">
+        <v>207</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="E107" s="1">
+        <v>1</v>
+      </c>
+      <c r="F107" s="3">
+        <v>0</v>
+      </c>
+      <c r="G107" s="3">
+        <v>2</v>
+      </c>
+      <c r="H107" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="I107" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="J107" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="K107" s="1" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="108" customHeight="1" spans="3:11">
+      <c r="C108" s="1">
+        <v>208</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="E108" s="1">
+        <v>1</v>
+      </c>
+      <c r="F108" s="3">
+        <v>0</v>
+      </c>
+      <c r="G108" s="3">
+        <v>2</v>
+      </c>
+      <c r="H108" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="I108" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="J108" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="K108" s="1" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="109" customHeight="1" spans="3:11">
+      <c r="C109" s="1">
+        <v>209</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="E109" s="1">
+        <v>1</v>
+      </c>
+      <c r="F109" s="3">
+        <v>0</v>
+      </c>
+      <c r="G109" s="3">
+        <v>2</v>
+      </c>
+      <c r="H109" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="I109" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="J109" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="K109" s="1" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="110" customHeight="1" spans="3:11">
+      <c r="C110" s="1">
         <v>210</v>
       </c>
-      <c r="D107" s="1" t="s">
+      <c r="D110" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="E110" s="1">
+        <v>1</v>
+      </c>
+      <c r="F110" s="3">
+        <v>0</v>
+      </c>
+      <c r="G110" s="3">
+        <v>2</v>
+      </c>
+      <c r="H110" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="I110" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="J110" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="E107" s="1">
-        <v>1</v>
-      </c>
-      <c r="F107" s="3">
-        <v>0</v>
-      </c>
-      <c r="G107" s="3">
-        <v>2</v>
-      </c>
-      <c r="H107" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="I107" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="J107" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="K107" s="1" t="s">
-        <v>263</v>
+      <c r="K110" s="1" t="s">
+        <v>272</v>
       </c>
     </row>
   </sheetData>
@@ -4844,7 +5071,7 @@
         <v>1001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -4859,13 +5086,13 @@
         <v>14</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="J6" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4873,7 +5100,7 @@
         <v>1002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -4888,13 +5115,13 @@
         <v>14</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="J7" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4902,7 +5129,7 @@
         <v>1003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -4917,13 +5144,13 @@
         <v>14</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="J8" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4931,7 +5158,7 @@
         <v>1004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
@@ -4946,13 +5173,13 @@
         <v>14</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="J9" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4960,7 +5187,7 @@
         <v>1005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -4975,13 +5202,13 @@
         <v>14</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="J10" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -4989,7 +5216,7 @@
         <v>1006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -5004,13 +5231,13 @@
         <v>14</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="J11" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5018,7 +5245,7 @@
         <v>1007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
@@ -5033,13 +5260,13 @@
         <v>14</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="J12" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5047,7 +5274,7 @@
         <v>1008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
@@ -5062,13 +5289,13 @@
         <v>14</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="J13" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5076,7 +5303,7 @@
         <v>1009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
@@ -5091,13 +5318,13 @@
         <v>14</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="J14" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5105,7 +5332,7 @@
         <v>1010</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
@@ -5120,13 +5347,13 @@
         <v>14</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="J15" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5134,7 +5361,7 @@
         <v>1011</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="E16" s="1">
         <v>1</v>
@@ -5149,13 +5376,13 @@
         <v>14</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="J16" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5163,7 +5390,7 @@
         <v>1012</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="E17" s="1">
         <v>1</v>
@@ -5178,13 +5405,13 @@
         <v>14</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="J17" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5192,7 +5419,7 @@
         <v>1013</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="E18" s="1">
         <v>1</v>
@@ -5207,13 +5434,13 @@
         <v>14</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="J18" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" ht="18" customHeight="1"/>
@@ -5222,7 +5449,7 @@
         <v>1101</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="E20" s="1">
         <v>1</v>
@@ -5237,13 +5464,13 @@
         <v>14</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="J20" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5251,7 +5478,7 @@
         <v>1102</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
@@ -5266,13 +5493,13 @@
         <v>14</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="J21" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5280,7 +5507,7 @@
         <v>1103</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
@@ -5295,13 +5522,13 @@
         <v>14</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="J22" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5309,7 +5536,7 @@
         <v>1104</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
@@ -5324,13 +5551,13 @@
         <v>14</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="J23" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5338,7 +5565,7 @@
         <v>1105</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
@@ -5353,13 +5580,13 @@
         <v>14</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="J24" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5367,7 +5594,7 @@
         <v>1106</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="E25" s="1">
         <v>1</v>
@@ -5382,13 +5609,13 @@
         <v>14</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="J25" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5396,7 +5623,7 @@
         <v>1107</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
@@ -5411,13 +5638,13 @@
         <v>14</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="J26" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5425,7 +5652,7 @@
         <v>1108</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="E27" s="1">
         <v>1</v>
@@ -5440,13 +5667,13 @@
         <v>14</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="J27" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5454,7 +5681,7 @@
         <v>1109</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="E28" s="1">
         <v>1</v>
@@ -5469,13 +5696,13 @@
         <v>14</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="J28" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5483,7 +5710,7 @@
         <v>1110</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
@@ -5498,13 +5725,13 @@
         <v>14</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="J29" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5512,7 +5739,7 @@
         <v>1111</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
@@ -5527,13 +5754,13 @@
         <v>14</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="J30" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5541,7 +5768,7 @@
         <v>1112</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
@@ -5556,13 +5783,13 @@
         <v>14</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="J31" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="349">
   <si>
     <t>_id</t>
   </si>
@@ -507,6 +507,12 @@
   </si>
   <si>
     <t>1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1</t>
+  </si>
+  <si>
+    <t>极戒自选</t>
+  </si>
+  <si>
+    <t>190007,190008,190009,190010,190011,190012</t>
   </si>
   <si>
     <t>暗金专属自选</t>
@@ -2097,7 +2103,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:K110"/>
+  <dimension ref="A3:K111"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -2981,7 +2987,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="33" customHeight="1" spans="3:11">
+    <row r="33" customHeight="1" spans="1:11">
       <c r="C33" s="1">
         <v>28</v>
       </c>
@@ -3010,7 +3016,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="34" customHeight="1" spans="3:11">
+    <row r="34" customHeight="1" spans="1:11">
       <c r="C34" s="1">
         <v>29</v>
       </c>
@@ -3039,7 +3045,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="35" customHeight="1" spans="3:11">
+    <row r="35" customHeight="1" spans="1:11">
       <c r="C35" s="1">
         <v>30</v>
       </c>
@@ -3068,7 +3074,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="36" customHeight="1" spans="3:11">
+    <row r="36" customHeight="1" spans="1:11">
       <c r="C36" s="1">
         <v>31</v>
       </c>
@@ -3097,7 +3103,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="37" customHeight="1" spans="3:11">
+    <row r="37" customHeight="1" spans="1:11">
       <c r="C37" s="1">
         <v>32</v>
       </c>
@@ -3126,7 +3132,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="38" customHeight="1" spans="3:11">
+    <row r="38" customHeight="1" spans="1:11">
       <c r="C38" s="1">
         <v>33</v>
       </c>
@@ -3186,7 +3192,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="40" customHeight="1" spans="3:11">
+    <row r="40" customHeight="1" spans="1:11">
       <c r="C40" s="1">
         <v>35</v>
       </c>
@@ -3215,7 +3221,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="41" customHeight="1" spans="3:11">
+    <row r="41" customHeight="1" spans="1:11">
       <c r="C41" s="1">
         <v>36</v>
       </c>
@@ -3244,7 +3250,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="42" customHeight="1" spans="3:11">
+    <row r="42" customHeight="1" spans="1:11">
       <c r="C42" s="1">
         <v>37</v>
       </c>
@@ -3273,7 +3279,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="43" customHeight="1" spans="3:11">
+    <row r="43" customHeight="1" spans="1:11">
       <c r="C43" s="1">
         <v>38</v>
       </c>
@@ -3302,7 +3308,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="44" customHeight="1" spans="3:11">
+    <row r="44" customHeight="1" spans="1:11">
       <c r="C44" s="1">
         <v>39</v>
       </c>
@@ -3331,7 +3337,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="45" customHeight="1" spans="3:11">
+    <row r="45" customHeight="1" spans="1:11">
       <c r="C45" s="1">
         <v>40</v>
       </c>
@@ -3360,7 +3366,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="46" customHeight="1" spans="3:11">
+    <row r="46" customHeight="1" spans="1:11">
       <c r="C46" s="1">
         <v>41</v>
       </c>
@@ -3389,7 +3395,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="47" customHeight="1" spans="3:11">
+    <row r="47" customHeight="1" spans="1:11">
       <c r="C47" s="1">
         <v>42</v>
       </c>
@@ -3449,204 +3455,204 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A49" s="1"/>
-      <c r="B49" s="1"/>
-      <c r="C49" s="1"/>
-      <c r="D49" s="1"/>
-      <c r="E49" s="1"/>
-      <c r="F49" s="3"/>
-      <c r="G49" s="3"/>
-      <c r="H49" s="1"/>
-      <c r="I49" s="1"/>
-      <c r="J49" s="1"/>
-      <c r="K49" s="1"/>
+    <row r="49" s="1" customFormat="1" customHeight="1" spans="1:11">
+      <c r="C49" s="1">
+        <v>44</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E49" s="1">
+        <v>1</v>
+      </c>
+      <c r="F49" s="1">
+        <v>0</v>
+      </c>
+      <c r="G49" s="1">
+        <v>2</v>
+      </c>
+      <c r="H49" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="I49" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="J49" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K49" s="1" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="50" customFormat="1" customHeight="1" spans="1:11">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
-      <c r="C50" s="1">
-        <v>90</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="E50" s="1">
-        <v>1</v>
-      </c>
-      <c r="F50" s="3">
-        <v>0</v>
-      </c>
-      <c r="G50" s="1">
-        <v>2</v>
-      </c>
-      <c r="H50" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="I50" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="J50" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="K50" s="1" t="s">
-        <v>141</v>
-      </c>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1"/>
+      <c r="J50" s="1"/>
+      <c r="K50" s="1"/>
     </row>
     <row r="51" customFormat="1" customHeight="1" spans="1:11">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D51" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E51" s="1">
+        <v>1</v>
+      </c>
+      <c r="F51" s="3">
+        <v>0</v>
+      </c>
+      <c r="G51" s="1">
+        <v>2</v>
+      </c>
+      <c r="H51" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="E51" s="1">
-        <v>1</v>
-      </c>
-      <c r="F51" s="3">
-        <v>0</v>
-      </c>
-      <c r="G51" s="1">
-        <v>2</v>
-      </c>
-      <c r="H51" s="5" t="s">
+      <c r="I51" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="I51" s="5" t="s">
-        <v>146</v>
-      </c>
       <c r="J51" s="5" t="s">
-        <v>16</v>
+        <v>140</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="52" customFormat="1" customHeight="1" spans="1:11">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D52" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E52" s="1">
+        <v>1</v>
+      </c>
+      <c r="F52" s="3">
+        <v>0</v>
+      </c>
+      <c r="G52" s="1">
+        <v>2</v>
+      </c>
+      <c r="H52" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="E52" s="1">
-        <v>1</v>
-      </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="1">
-        <v>2</v>
-      </c>
-      <c r="H52" s="5" t="s">
+      <c r="I52" s="5" t="s">
         <v>148</v>
-      </c>
-      <c r="I52" s="5" t="s">
-        <v>149</v>
       </c>
       <c r="J52" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="53" customFormat="1" customHeight="1" spans="1:11">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1">
+        <v>94</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E53" s="1">
+        <v>1</v>
+      </c>
+      <c r="F53" s="3">
+        <v>0</v>
+      </c>
+      <c r="G53" s="1">
+        <v>2</v>
+      </c>
+      <c r="H53" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="I53" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="J53" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K53" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="54" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A54" s="1"/>
+      <c r="B54" s="1"/>
+      <c r="C54" s="1">
         <v>95</v>
       </c>
-      <c r="D53" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="E53" s="1">
-        <v>1</v>
-      </c>
-      <c r="F53" s="3">
-        <v>0</v>
-      </c>
-      <c r="G53" s="1">
-        <v>2</v>
-      </c>
-      <c r="H53" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="I53" s="5" t="s">
+      <c r="D54" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="J53" s="5" t="s">
+      <c r="E54" s="1">
+        <v>1</v>
+      </c>
+      <c r="F54" s="3">
+        <v>0</v>
+      </c>
+      <c r="G54" s="1">
+        <v>2</v>
+      </c>
+      <c r="H54" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="K53" s="1" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="54" customHeight="1" spans="3:11">
-      <c r="C54" s="1">
+      <c r="I54" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="J54" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="55" customHeight="1" spans="1:11">
+      <c r="C55" s="1">
         <v>96</v>
       </c>
-      <c r="D54" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="E54" s="1">
-        <v>0</v>
-      </c>
-      <c r="F54" s="3">
-        <v>0</v>
-      </c>
-      <c r="G54" s="1">
-        <v>2</v>
-      </c>
-      <c r="H54" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="I54" s="5" t="s">
+      <c r="D55" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="J54" s="5" t="s">
+      <c r="E55" s="1">
+        <v>0</v>
+      </c>
+      <c r="F55" s="3">
+        <v>0</v>
+      </c>
+      <c r="G55" s="1">
+        <v>2</v>
+      </c>
+      <c r="H55" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="K54" s="1" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="55" customHeight="1" spans="3:11">
-      <c r="C55" s="1">
+      <c r="I55" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="J55" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="K55" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="56" customHeight="1" spans="1:11">
+      <c r="C56" s="1">
         <v>97</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="E55" s="1">
-        <v>1</v>
-      </c>
-      <c r="F55" s="3">
-        <v>0</v>
-      </c>
-      <c r="G55" s="1">
-        <v>2</v>
-      </c>
-      <c r="H55" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="I55" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="J55" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K55" s="1" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="56" customHeight="1" spans="3:11">
-      <c r="C56" s="1">
-        <v>98</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>160</v>
@@ -3661,79 +3667,79 @@
         <v>2</v>
       </c>
       <c r="H56" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="I56" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="I56" s="5" t="s">
-        <v>162</v>
-      </c>
       <c r="J56" s="5" t="s">
-        <v>91</v>
+        <v>32</v>
       </c>
       <c r="K56" s="1" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="57" customHeight="1" spans="3:11">
+    <row r="57" customHeight="1" spans="1:11">
       <c r="C57" s="1">
+        <v>98</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E57" s="1">
+        <v>1</v>
+      </c>
+      <c r="F57" s="3">
+        <v>0</v>
+      </c>
+      <c r="G57" s="1">
+        <v>2</v>
+      </c>
+      <c r="H57" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="I57" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="J57" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="K57" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="1:11">
+      <c r="C58" s="1">
         <v>99</v>
       </c>
-      <c r="D57" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="E57" s="1">
-        <v>0</v>
-      </c>
-      <c r="F57" s="3">
-        <v>0</v>
-      </c>
-      <c r="G57" s="1">
-        <v>2</v>
-      </c>
-      <c r="H57" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="I57" s="5" t="s">
+      <c r="D58" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="J57" s="5" t="s">
+      <c r="E58" s="1">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="1">
+        <v>2</v>
+      </c>
+      <c r="H58" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="K57" s="1" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="58" customHeight="1" spans="3:11">
-      <c r="C58" s="1">
+      <c r="I58" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="J58" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="K58" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="59" customHeight="1" spans="1:11">
+      <c r="C59" s="1">
         <v>100</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="E58" s="1">
-        <v>0</v>
-      </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
-      <c r="G58" s="1">
-        <v>2</v>
-      </c>
-      <c r="H58" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="I58" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="J58" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="K58" s="1" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="59" customHeight="1" spans="3:11">
-      <c r="C59" s="1">
-        <v>101</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>169</v>
@@ -3748,21 +3754,21 @@
         <v>2</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="I59" s="5" t="s">
         <v>170</v>
       </c>
       <c r="J59" s="5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="K59" s="1" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="60" customHeight="1" spans="3:11">
+    <row r="60" customHeight="1" spans="1:11">
       <c r="C60" s="1">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>171</v>
@@ -3777,21 +3783,21 @@
         <v>2</v>
       </c>
       <c r="H60" s="5" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="I60" s="5" t="s">
         <v>172</v>
       </c>
       <c r="J60" s="5" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="K60" s="1" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="61" customHeight="1" spans="3:11">
+    <row r="61" customHeight="1" spans="1:11">
       <c r="C61" s="1">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>173</v>
@@ -3806,21 +3812,21 @@
         <v>2</v>
       </c>
       <c r="H61" s="5" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="I61" s="5" t="s">
         <v>174</v>
       </c>
       <c r="J61" s="5" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="K61" s="1" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="62" customHeight="1" spans="3:11">
+    <row r="62" customHeight="1" spans="1:11">
       <c r="C62" s="1">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>175</v>
@@ -3835,21 +3841,21 @@
         <v>2</v>
       </c>
       <c r="H62" s="5" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="I62" s="5" t="s">
         <v>176</v>
       </c>
       <c r="J62" s="5" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="K62" s="1" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="63" customHeight="1" spans="3:11">
+    <row r="63" customHeight="1" spans="1:11">
       <c r="C63" s="1">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>177</v>
@@ -3864,79 +3870,79 @@
         <v>2</v>
       </c>
       <c r="H63" s="5" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="I63" s="5" t="s">
         <v>178</v>
       </c>
       <c r="J63" s="5" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="K63" s="1" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="65" customHeight="1" spans="3:11">
-      <c r="C65" s="1">
+    <row r="64" customHeight="1" spans="1:11">
+      <c r="C64" s="1">
+        <v>105</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="E64" s="1">
+        <v>0</v>
+      </c>
+      <c r="F64" s="3">
+        <v>0</v>
+      </c>
+      <c r="G64" s="1">
+        <v>2</v>
+      </c>
+      <c r="H64" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="I64" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="J64" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="K64" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="66" customHeight="1" spans="1:11">
+      <c r="C66" s="1">
         <v>106</v>
       </c>
-      <c r="D65" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="E65" s="1">
-        <v>1</v>
-      </c>
-      <c r="F65" s="3">
-        <v>0</v>
-      </c>
-      <c r="G65" s="1">
-        <v>1</v>
-      </c>
-      <c r="H65" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="I65" s="5" t="s">
+      <c r="D66" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="J65" s="5" t="s">
+      <c r="E66" s="1">
+        <v>1</v>
+      </c>
+      <c r="F66" s="3">
+        <v>0</v>
+      </c>
+      <c r="G66" s="1">
+        <v>1</v>
+      </c>
+      <c r="H66" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="K65" s="1" t="s">
+      <c r="I66" s="5" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="66" customHeight="1" spans="3:11">
-      <c r="C66" s="1">
+      <c r="J66" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="K66" s="1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="67" customHeight="1" spans="1:11">
+      <c r="C67" s="1">
         <v>107</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="E66" s="1">
-        <v>1</v>
-      </c>
-      <c r="F66" s="3">
-        <v>0</v>
-      </c>
-      <c r="G66" s="1">
-        <v>2</v>
-      </c>
-      <c r="H66" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="I66" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="J66" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="K66" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="67" customHeight="1" spans="3:11">
-      <c r="C67" s="1">
-        <v>108</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>186</v>
@@ -3960,256 +3966,250 @@
         <v>40</v>
       </c>
       <c r="K67" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="68" customHeight="1" spans="1:11">
+      <c r="C68" s="1">
+        <v>108</v>
+      </c>
+      <c r="D68" s="1" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="69" customHeight="1" spans="3:11">
-      <c r="C69" s="1">
+      <c r="E68" s="1">
+        <v>1</v>
+      </c>
+      <c r="F68" s="3">
+        <v>0</v>
+      </c>
+      <c r="G68" s="1">
+        <v>2</v>
+      </c>
+      <c r="H68" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="I68" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="J68" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K68" s="1" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="70" customHeight="1" spans="1:11">
+      <c r="C70" s="1">
         <v>109</v>
       </c>
-      <c r="D69" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="E69" s="1">
-        <v>1</v>
-      </c>
-      <c r="F69" s="3">
-        <v>0</v>
-      </c>
-      <c r="G69" s="3">
-        <v>2</v>
-      </c>
-      <c r="H69" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="I69" s="5" t="s">
+      <c r="D70" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="J69" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="K69" s="1" t="s">
+      <c r="E70" s="1">
+        <v>1</v>
+      </c>
+      <c r="F70" s="3">
+        <v>0</v>
+      </c>
+      <c r="G70" s="3">
+        <v>2</v>
+      </c>
+      <c r="H70" s="5" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="70" customHeight="1" spans="3:11">
-      <c r="C70" s="1">
-        <v>110</v>
-      </c>
-      <c r="D70" s="1" t="s">
+      <c r="I70" s="5" t="s">
         <v>193</v>
-      </c>
-      <c r="E70" s="1">
-        <v>1</v>
-      </c>
-      <c r="F70" s="3">
-        <v>0</v>
-      </c>
-      <c r="G70" s="3">
-        <v>2</v>
-      </c>
-      <c r="H70" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="I70" s="5" t="s">
-        <v>194</v>
       </c>
       <c r="J70" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K70" s="1" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="71" customHeight="1" spans="1:11">
+      <c r="C71" s="1">
+        <v>110</v>
+      </c>
+      <c r="D71" s="1" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="71" customHeight="1" spans="3:11">
-      <c r="C71" s="1">
-        <v>111</v>
-      </c>
-      <c r="D71" s="1" t="s">
+      <c r="E71" s="1">
+        <v>1</v>
+      </c>
+      <c r="F71" s="3">
+        <v>0</v>
+      </c>
+      <c r="G71" s="3">
+        <v>2</v>
+      </c>
+      <c r="H71" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="I71" s="5" t="s">
         <v>196</v>
-      </c>
-      <c r="E71" s="1">
-        <v>1</v>
-      </c>
-      <c r="F71" s="3">
-        <v>0</v>
-      </c>
-      <c r="G71" s="3">
-        <v>2</v>
-      </c>
-      <c r="H71" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="I71" s="5" t="s">
-        <v>197</v>
       </c>
       <c r="J71" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K71" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="72" customHeight="1" spans="1:11">
+      <c r="C72" s="1">
+        <v>111</v>
+      </c>
+      <c r="D72" s="1" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="72" customHeight="1" spans="3:11">
-      <c r="C72" s="1">
-        <v>112</v>
-      </c>
-      <c r="D72" s="1" t="s">
+      <c r="E72" s="1">
+        <v>1</v>
+      </c>
+      <c r="F72" s="3">
+        <v>0</v>
+      </c>
+      <c r="G72" s="3">
+        <v>2</v>
+      </c>
+      <c r="H72" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="I72" s="5" t="s">
         <v>199</v>
-      </c>
-      <c r="E72" s="1">
-        <v>1</v>
-      </c>
-      <c r="F72" s="3">
-        <v>0</v>
-      </c>
-      <c r="G72" s="3">
-        <v>2</v>
-      </c>
-      <c r="H72" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="I72" s="5" t="s">
-        <v>200</v>
       </c>
       <c r="J72" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K72" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="73" customHeight="1" spans="1:11">
+      <c r="C73" s="1">
+        <v>112</v>
+      </c>
+      <c r="D73" s="1" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="73" customHeight="1" spans="3:11">
-      <c r="C73" s="1">
-        <v>113</v>
-      </c>
-      <c r="D73" s="1" t="s">
+      <c r="E73" s="1">
+        <v>1</v>
+      </c>
+      <c r="F73" s="3">
+        <v>0</v>
+      </c>
+      <c r="G73" s="3">
+        <v>2</v>
+      </c>
+      <c r="H73" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="I73" s="5" t="s">
         <v>202</v>
-      </c>
-      <c r="E73" s="1">
-        <v>1</v>
-      </c>
-      <c r="F73" s="3">
-        <v>0</v>
-      </c>
-      <c r="G73" s="3">
-        <v>2</v>
-      </c>
-      <c r="H73" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="I73" s="5" t="s">
-        <v>203</v>
       </c>
       <c r="J73" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K73" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="74" customHeight="1" spans="1:11">
+      <c r="C74" s="1">
+        <v>113</v>
+      </c>
+      <c r="D74" s="1" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="74" customHeight="1" spans="3:11">
-      <c r="C74" s="1">
+      <c r="E74" s="1">
+        <v>1</v>
+      </c>
+      <c r="F74" s="3">
+        <v>0</v>
+      </c>
+      <c r="G74" s="3">
+        <v>2</v>
+      </c>
+      <c r="H74" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="I74" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="J74" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K74" s="1" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="75" customHeight="1" spans="1:11">
+      <c r="C75" s="1">
         <v>114</v>
       </c>
-      <c r="D74" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="E74" s="1">
-        <v>1</v>
-      </c>
-      <c r="F74" s="3">
-        <v>0</v>
-      </c>
-      <c r="G74" s="3">
-        <v>2</v>
-      </c>
-      <c r="H74" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="I74" s="5" t="s">
+      <c r="D75" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="J74" s="5" t="s">
+      <c r="E75" s="1">
+        <v>1</v>
+      </c>
+      <c r="F75" s="3">
+        <v>0</v>
+      </c>
+      <c r="G75" s="3">
+        <v>2</v>
+      </c>
+      <c r="H75" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="I75" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="J75" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="K74" s="1" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="75" customHeight="1" spans="3:11">
-      <c r="C75" s="1">
+      <c r="K75" s="1" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="76" customHeight="1" spans="1:11">
+      <c r="C76" s="1">
         <v>115</v>
       </c>
-      <c r="D75" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="E75" s="1">
-        <v>1</v>
-      </c>
-      <c r="F75" s="3">
-        <v>0</v>
-      </c>
-      <c r="G75" s="3">
-        <v>2</v>
-      </c>
-      <c r="H75" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="I75" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="J75" s="5" t="s">
+      <c r="D76" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E76" s="1">
+        <v>1</v>
+      </c>
+      <c r="F76" s="3">
+        <v>0</v>
+      </c>
+      <c r="G76" s="3">
+        <v>2</v>
+      </c>
+      <c r="H76" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="I76" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="J76" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="K75" s="1" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="77" customHeight="1" spans="1:11">
-      <c r="A77" s="1" t="s">
+      <c r="K76" s="1" t="s">
         <v>211</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="C77" s="1">
-        <v>118</v>
-      </c>
-      <c r="D77" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="E77" s="1">
-        <v>1</v>
-      </c>
-      <c r="F77" s="3">
-        <v>0</v>
-      </c>
-      <c r="G77" s="3">
-        <v>2</v>
-      </c>
-      <c r="H77" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="I77" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="J77" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="K77" s="3" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="1:11">
       <c r="A78" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C78" s="1">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>214</v>
@@ -4224,7 +4224,7 @@
         <v>2</v>
       </c>
       <c r="H78" s="5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="I78" s="5" t="s">
         <v>215</v>
@@ -4238,13 +4238,13 @@
     </row>
     <row r="79" customHeight="1" spans="1:11">
       <c r="A79" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C79" s="1">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>216</v>
@@ -4259,7 +4259,7 @@
         <v>2</v>
       </c>
       <c r="H79" s="5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="I79" s="5" t="s">
         <v>217</v>
@@ -4273,13 +4273,13 @@
     </row>
     <row r="80" customHeight="1" spans="1:11">
       <c r="A80" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C80" s="1">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>218</v>
@@ -4294,7 +4294,7 @@
         <v>2</v>
       </c>
       <c r="H80" s="5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="I80" s="5" t="s">
         <v>219</v>
@@ -4308,13 +4308,13 @@
     </row>
     <row r="81" customHeight="1" spans="1:11">
       <c r="A81" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C81" s="1">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>220</v>
@@ -4329,7 +4329,7 @@
         <v>2</v>
       </c>
       <c r="H81" s="5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="I81" s="5" t="s">
         <v>221</v>
@@ -4343,13 +4343,13 @@
     </row>
     <row r="82" customHeight="1" spans="1:11">
       <c r="A82" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C82" s="1">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>222</v>
@@ -4364,7 +4364,7 @@
         <v>2</v>
       </c>
       <c r="H82" s="5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="I82" s="5" t="s">
         <v>223</v>
@@ -4378,15 +4378,15 @@
     </row>
     <row r="83" customHeight="1" spans="1:11">
       <c r="A83" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C83" s="1">
-        <v>124</v>
-      </c>
-      <c r="D83" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D83" s="3" t="s">
         <v>224</v>
       </c>
       <c r="E83" s="1">
@@ -4399,7 +4399,7 @@
         <v>2</v>
       </c>
       <c r="H83" s="5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="I83" s="5" t="s">
         <v>225</v>
@@ -4407,19 +4407,19 @@
       <c r="J83" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="K83" s="1" t="s">
+      <c r="K83" s="3" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="84" customHeight="1" spans="1:11">
       <c r="A84" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C84" s="1">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>226</v>
@@ -4434,7 +4434,7 @@
         <v>2</v>
       </c>
       <c r="H84" s="5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="I84" s="5" t="s">
         <v>227</v>
@@ -4448,13 +4448,13 @@
     </row>
     <row r="85" customHeight="1" spans="1:11">
       <c r="A85" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C85" s="1">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>228</v>
@@ -4469,7 +4469,7 @@
         <v>2</v>
       </c>
       <c r="H85" s="5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="I85" s="5" t="s">
         <v>229</v>
@@ -4483,13 +4483,13 @@
     </row>
     <row r="86" customHeight="1" spans="1:11">
       <c r="A86" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C86" s="1">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>230</v>
@@ -4504,7 +4504,7 @@
         <v>2</v>
       </c>
       <c r="H86" s="5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="I86" s="5" t="s">
         <v>231</v>
@@ -4518,13 +4518,13 @@
     </row>
     <row r="87" customHeight="1" spans="1:11">
       <c r="A87" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C87" s="1">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>232</v>
@@ -4539,7 +4539,7 @@
         <v>2</v>
       </c>
       <c r="H87" s="5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="I87" s="5" t="s">
         <v>233</v>
@@ -4551,50 +4551,50 @@
         <v>232</v>
       </c>
     </row>
-    <row r="89" customHeight="1" spans="1:11">
-      <c r="A89" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="C89" s="1">
-        <v>137</v>
-      </c>
-      <c r="D89" s="1" t="s">
+    <row r="88" customHeight="1" spans="1:11">
+      <c r="A88" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C88" s="1">
+        <v>128</v>
+      </c>
+      <c r="D88" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="E89" s="1">
-        <v>1</v>
-      </c>
-      <c r="F89" s="3">
-        <v>0</v>
-      </c>
-      <c r="G89" s="3">
-        <v>2</v>
-      </c>
-      <c r="H89" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="I89" s="5" t="s">
+      <c r="E88" s="1">
+        <v>1</v>
+      </c>
+      <c r="F88" s="3">
+        <v>0</v>
+      </c>
+      <c r="G88" s="3">
+        <v>2</v>
+      </c>
+      <c r="H88" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="I88" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="J89" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="K89" s="1" t="s">
+      <c r="J88" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K88" s="1" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="90" customHeight="1" spans="1:11">
       <c r="A90" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C90" s="1">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>236</v>
@@ -4609,13 +4609,13 @@
         <v>2</v>
       </c>
       <c r="H90" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="I90" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="I90" s="5" t="s">
-        <v>238</v>
-      </c>
       <c r="J90" s="5" t="s">
-        <v>239</v>
+        <v>40</v>
       </c>
       <c r="K90" s="1" t="s">
         <v>236</v>
@@ -4623,327 +4623,362 @@
     </row>
     <row r="91" customHeight="1" spans="1:11">
       <c r="A91" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C91" s="1">
+        <v>138</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="E91" s="1">
+        <v>1</v>
+      </c>
+      <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
+        <v>2</v>
+      </c>
+      <c r="H91" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="I91" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="J91" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="K91" s="1" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="92" customHeight="1" spans="1:11">
+      <c r="A92" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C92" s="1">
         <v>139</v>
       </c>
-      <c r="D91" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="E91" s="1">
-        <v>1</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>2</v>
-      </c>
-      <c r="H91" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="I91" s="5" t="s">
+      <c r="D92" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="E92" s="1">
+        <v>1</v>
+      </c>
+      <c r="F92" s="3">
+        <v>0</v>
+      </c>
+      <c r="G92" s="3">
+        <v>2</v>
+      </c>
+      <c r="H92" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="I92" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="J92" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="J91" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="K91" s="1" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="101" customHeight="1" spans="3:11">
-      <c r="C101" s="1">
-        <v>201</v>
-      </c>
-      <c r="D101" s="1" t="s">
+      <c r="K92" s="1" t="s">
         <v>242</v>
-      </c>
-      <c r="E101" s="1">
-        <v>1</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>2</v>
-      </c>
-      <c r="H101" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="I101" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="J101" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K101" s="1" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="102" customHeight="1" spans="3:11">
       <c r="C102" s="1">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D102" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="E102" s="1">
+        <v>1</v>
+      </c>
+      <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
+        <v>2</v>
+      </c>
+      <c r="H102" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="I102" s="5" t="s">
         <v>246</v>
-      </c>
-      <c r="E102" s="1">
-        <v>1</v>
-      </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
-      <c r="G102" s="3">
-        <v>2</v>
-      </c>
-      <c r="H102" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="I102" s="5" t="s">
-        <v>247</v>
       </c>
       <c r="J102" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K102" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="103" customHeight="1" spans="3:11">
       <c r="C103" s="1">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D103" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="E103" s="1">
+        <v>1</v>
+      </c>
+      <c r="F103" s="3">
+        <v>0</v>
+      </c>
+      <c r="G103" s="3">
+        <v>2</v>
+      </c>
+      <c r="H103" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="I103" s="5" t="s">
         <v>249</v>
-      </c>
-      <c r="E103" s="1">
-        <v>1</v>
-      </c>
-      <c r="F103" s="3">
-        <v>0</v>
-      </c>
-      <c r="G103" s="3">
-        <v>2</v>
-      </c>
-      <c r="H103" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="I103" s="5" t="s">
-        <v>250</v>
       </c>
       <c r="J103" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K103" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="104" customHeight="1" spans="3:11">
       <c r="C104" s="1">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D104" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="E104" s="1">
+        <v>1</v>
+      </c>
+      <c r="F104" s="3">
+        <v>0</v>
+      </c>
+      <c r="G104" s="3">
+        <v>2</v>
+      </c>
+      <c r="H104" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="I104" s="5" t="s">
         <v>252</v>
-      </c>
-      <c r="E104" s="1">
-        <v>1</v>
-      </c>
-      <c r="F104" s="3">
-        <v>0</v>
-      </c>
-      <c r="G104" s="3">
-        <v>2</v>
-      </c>
-      <c r="H104" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="I104" s="5" t="s">
-        <v>253</v>
       </c>
       <c r="J104" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K104" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="105" customHeight="1" spans="3:11">
       <c r="C105" s="1">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D105" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="E105" s="1">
+        <v>1</v>
+      </c>
+      <c r="F105" s="3">
+        <v>0</v>
+      </c>
+      <c r="G105" s="3">
+        <v>2</v>
+      </c>
+      <c r="H105" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="I105" s="5" t="s">
         <v>255</v>
-      </c>
-      <c r="E105" s="1">
-        <v>1</v>
-      </c>
-      <c r="F105" s="3">
-        <v>0</v>
-      </c>
-      <c r="G105" s="3">
-        <v>2</v>
-      </c>
-      <c r="H105" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="I105" s="5" t="s">
-        <v>256</v>
       </c>
       <c r="J105" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K105" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="106" customHeight="1" spans="3:11">
       <c r="C106" s="1">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D106" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="E106" s="1">
+        <v>1</v>
+      </c>
+      <c r="F106" s="3">
+        <v>0</v>
+      </c>
+      <c r="G106" s="3">
+        <v>2</v>
+      </c>
+      <c r="H106" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="I106" s="5" t="s">
         <v>258</v>
-      </c>
-      <c r="E106" s="1">
-        <v>1</v>
-      </c>
-      <c r="F106" s="3">
-        <v>0</v>
-      </c>
-      <c r="G106" s="3">
-        <v>2</v>
-      </c>
-      <c r="H106" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="I106" s="5" t="s">
-        <v>259</v>
       </c>
       <c r="J106" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K106" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="107" customHeight="1" spans="3:11">
       <c r="C107" s="1">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D107" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="E107" s="1">
+        <v>1</v>
+      </c>
+      <c r="F107" s="3">
+        <v>0</v>
+      </c>
+      <c r="G107" s="3">
+        <v>2</v>
+      </c>
+      <c r="H107" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="I107" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="E107" s="1">
-        <v>1</v>
-      </c>
-      <c r="F107" s="3">
-        <v>0</v>
-      </c>
-      <c r="G107" s="3">
-        <v>2</v>
-      </c>
-      <c r="H107" s="5" t="s">
+      <c r="J107" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K107" s="1" t="s">
         <v>262</v>
-      </c>
-      <c r="I107" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="J107" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="K107" s="1" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="108" customHeight="1" spans="3:11">
       <c r="C108" s="1">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D108" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="E108" s="1">
+        <v>1</v>
+      </c>
+      <c r="F108" s="3">
+        <v>0</v>
+      </c>
+      <c r="G108" s="3">
+        <v>2</v>
+      </c>
+      <c r="H108" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="I108" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="J108" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="E108" s="1">
-        <v>1</v>
-      </c>
-      <c r="F108" s="3">
-        <v>0</v>
-      </c>
-      <c r="G108" s="3">
-        <v>2</v>
-      </c>
-      <c r="H108" s="5" t="s">
+      <c r="K108" s="1" t="s">
         <v>267</v>
-      </c>
-      <c r="I108" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="J108" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="K108" s="1" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="109" customHeight="1" spans="3:11">
       <c r="C109" s="1">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D109" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="E109" s="1">
+        <v>1</v>
+      </c>
+      <c r="F109" s="3">
+        <v>0</v>
+      </c>
+      <c r="G109" s="3">
+        <v>2</v>
+      </c>
+      <c r="H109" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="I109" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="E109" s="1">
-        <v>1</v>
-      </c>
-      <c r="F109" s="3">
-        <v>0</v>
-      </c>
-      <c r="G109" s="3">
-        <v>2</v>
-      </c>
-      <c r="H109" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="I109" s="5" t="s">
+      <c r="J109" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="K109" s="1" t="s">
         <v>271</v>
-      </c>
-      <c r="J109" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="K109" s="1" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="110" customHeight="1" spans="3:11">
       <c r="C110" s="1">
+        <v>209</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="E110" s="1">
+        <v>1</v>
+      </c>
+      <c r="F110" s="3">
+        <v>0</v>
+      </c>
+      <c r="G110" s="3">
+        <v>2</v>
+      </c>
+      <c r="H110" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="I110" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="J110" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="K110" s="1" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="111" customHeight="1" spans="3:11">
+      <c r="C111" s="1">
         <v>210</v>
       </c>
-      <c r="D110" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="E110" s="1">
-        <v>1</v>
-      </c>
-      <c r="F110" s="3">
-        <v>0</v>
-      </c>
-      <c r="G110" s="3">
-        <v>2</v>
-      </c>
-      <c r="H110" s="5" t="s">
+      <c r="D111" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="E111" s="1">
+        <v>1</v>
+      </c>
+      <c r="F111" s="3">
+        <v>0</v>
+      </c>
+      <c r="G111" s="3">
+        <v>2</v>
+      </c>
+      <c r="H111" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="I111" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="J111" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="K111" s="1" t="s">
         <v>274</v>
-      </c>
-      <c r="I110" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="J110" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="K110" s="1" t="s">
-        <v>272</v>
       </c>
     </row>
   </sheetData>
@@ -5071,7 +5106,7 @@
         <v>1001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -5086,13 +5121,13 @@
         <v>14</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="J6" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5100,7 +5135,7 @@
         <v>1002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -5115,13 +5150,13 @@
         <v>14</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J7" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5129,7 +5164,7 @@
         <v>1003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -5144,13 +5179,13 @@
         <v>14</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="J8" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5158,7 +5193,7 @@
         <v>1004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
@@ -5173,13 +5208,13 @@
         <v>14</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="J9" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5187,7 +5222,7 @@
         <v>1005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -5202,13 +5237,13 @@
         <v>14</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="J10" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5216,7 +5251,7 @@
         <v>1006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -5231,13 +5266,13 @@
         <v>14</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="J11" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5245,7 +5280,7 @@
         <v>1007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
@@ -5260,13 +5295,13 @@
         <v>14</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="J12" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5274,7 +5309,7 @@
         <v>1008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
@@ -5289,13 +5324,13 @@
         <v>14</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J13" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5303,7 +5338,7 @@
         <v>1009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
@@ -5318,13 +5353,13 @@
         <v>14</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="J14" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5332,7 +5367,7 @@
         <v>1010</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
@@ -5347,13 +5382,13 @@
         <v>14</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="J15" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5361,7 +5396,7 @@
         <v>1011</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E16" s="1">
         <v>1</v>
@@ -5376,21 +5411,21 @@
         <v>14</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="J16" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
       <c r="C17" s="1">
         <v>1012</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="E17" s="1">
         <v>1</v>
@@ -5405,21 +5440,21 @@
         <v>14</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="J17" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
       <c r="C18" s="1">
         <v>1013</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="E18" s="1">
         <v>1</v>
@@ -5434,22 +5469,22 @@
         <v>14</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="J18" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" ht="18" customHeight="1"/>
-    <row r="20" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+    <row r="20" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
       <c r="C20" s="1">
         <v>1101</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E20" s="1">
         <v>1</v>
@@ -5464,21 +5499,21 @@
         <v>14</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="J20" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
       <c r="C21" s="1">
         <v>1102</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
@@ -5493,21 +5528,21 @@
         <v>14</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="J21" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="22" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
       <c r="C22" s="1">
         <v>1103</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
@@ -5522,21 +5557,21 @@
         <v>14</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="J22" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="23" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
       <c r="C23" s="1">
         <v>1104</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
@@ -5551,21 +5586,21 @@
         <v>14</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="J23" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="24" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
       <c r="C24" s="1">
         <v>1105</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
@@ -5580,21 +5615,21 @@
         <v>14</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="J24" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="25" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
       <c r="C25" s="1">
         <v>1106</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E25" s="1">
         <v>1</v>
@@ -5609,21 +5644,21 @@
         <v>14</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="J25" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="26" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
       <c r="C26" s="1">
         <v>1107</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
@@ -5638,21 +5673,21 @@
         <v>14</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="J26" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="27" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
       <c r="C27" s="1">
         <v>1108</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="E27" s="1">
         <v>1</v>
@@ -5667,21 +5702,21 @@
         <v>14</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="J27" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="28" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
       <c r="C28" s="1">
         <v>1109</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E28" s="1">
         <v>1</v>
@@ -5696,21 +5731,21 @@
         <v>14</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="J28" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="29" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
       <c r="C29" s="1">
         <v>1110</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
@@ -5725,21 +5760,21 @@
         <v>14</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="J29" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="30" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="30" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
       <c r="C30" s="1">
         <v>1111</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
@@ -5754,21 +5789,21 @@
         <v>14</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="J30" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="31" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="31" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
       <c r="C31" s="1">
         <v>1112</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
@@ -5783,13 +5818,13 @@
         <v>14</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="J31" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="349">
   <si>
     <t>_id</t>
   </si>
@@ -545,13 +545,7 @@
     <t>高级金色专属</t>
   </si>
   <si>
-    <t>4,4,4,4,4,4,4,4,4,4</t>
-  </si>
-  <si>
-    <t>1007,1008,1009,1001,1002,1003,1004,1005,1006,1013</t>
-  </si>
-  <si>
-    <t>1,1,1,1,1,1,1,1,1,1</t>
+    <t>1007,1008,1009,1001,1002,1003,1004,1005,1006,1013,1014</t>
   </si>
   <si>
     <t>驱魔6件套</t>
@@ -1023,6 +1017,12 @@
   </si>
   <si>
     <t>1073,1074,1075</t>
+  </si>
+  <si>
+    <t>金色盾自选</t>
+  </si>
+  <si>
+    <t>1076,1077,1078</t>
   </si>
   <si>
     <t>暗金1阶自选</t>
@@ -3609,13 +3609,13 @@
         <v>2</v>
       </c>
       <c r="H54" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="I54" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="I54" s="5" t="s">
-        <v>154</v>
-      </c>
       <c r="J54" s="5" t="s">
-        <v>155</v>
+        <v>91</v>
       </c>
       <c r="K54" s="1" t="s">
         <v>152</v>
@@ -3626,28 +3626,28 @@
         <v>96</v>
       </c>
       <c r="D55" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E55" s="1">
+        <v>0</v>
+      </c>
+      <c r="F55" s="3">
+        <v>0</v>
+      </c>
+      <c r="G55" s="1">
+        <v>2</v>
+      </c>
+      <c r="H55" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="I55" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="E55" s="1">
-        <v>0</v>
-      </c>
-      <c r="F55" s="3">
-        <v>0</v>
-      </c>
-      <c r="G55" s="1">
-        <v>2</v>
-      </c>
-      <c r="H55" s="5" t="s">
+      <c r="J55" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="I55" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="J55" s="5" t="s">
-        <v>159</v>
-      </c>
       <c r="K55" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="1:11">
@@ -3655,7 +3655,7 @@
         <v>97</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E56" s="1">
         <v>1</v>
@@ -3670,13 +3670,13 @@
         <v>132</v>
       </c>
       <c r="I56" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="J56" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="1:11">
@@ -3684,28 +3684,28 @@
         <v>98</v>
       </c>
       <c r="D57" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E57" s="1">
+        <v>1</v>
+      </c>
+      <c r="F57" s="3">
+        <v>0</v>
+      </c>
+      <c r="G57" s="1">
+        <v>2</v>
+      </c>
+      <c r="H57" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="I57" s="5" t="s">
         <v>162</v>
-      </c>
-      <c r="E57" s="1">
-        <v>1</v>
-      </c>
-      <c r="F57" s="3">
-        <v>0</v>
-      </c>
-      <c r="G57" s="1">
-        <v>2</v>
-      </c>
-      <c r="H57" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="I57" s="5" t="s">
-        <v>164</v>
       </c>
       <c r="J57" s="5" t="s">
         <v>91</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="1:11">
@@ -3713,28 +3713,28 @@
         <v>99</v>
       </c>
       <c r="D58" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E58" s="1">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="1">
+        <v>2</v>
+      </c>
+      <c r="H58" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="I58" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="E58" s="1">
-        <v>0</v>
-      </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
-      <c r="G58" s="1">
-        <v>2</v>
-      </c>
-      <c r="H58" s="5" t="s">
+      <c r="J58" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="I58" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="J58" s="5" t="s">
-        <v>168</v>
-      </c>
       <c r="K58" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="1:11">
@@ -3742,7 +3742,7 @@
         <v>100</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E59" s="1">
         <v>0</v>
@@ -3754,16 +3754,16 @@
         <v>2</v>
       </c>
       <c r="H59" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="I59" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="J59" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="I59" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="J59" s="5" t="s">
-        <v>159</v>
-      </c>
       <c r="K59" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="1:11">
@@ -3771,7 +3771,7 @@
         <v>101</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E60" s="1">
         <v>0</v>
@@ -3783,16 +3783,16 @@
         <v>2</v>
       </c>
       <c r="H60" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="I60" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="J60" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="I60" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="J60" s="5" t="s">
-        <v>159</v>
-      </c>
       <c r="K60" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="1:11">
@@ -3800,7 +3800,7 @@
         <v>102</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E61" s="1">
         <v>0</v>
@@ -3812,16 +3812,16 @@
         <v>2</v>
       </c>
       <c r="H61" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="I61" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="J61" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="I61" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="J61" s="5" t="s">
-        <v>168</v>
-      </c>
       <c r="K61" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="1:11">
@@ -3829,7 +3829,7 @@
         <v>103</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E62" s="1">
         <v>0</v>
@@ -3841,16 +3841,16 @@
         <v>2</v>
       </c>
       <c r="H62" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="I62" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="J62" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="I62" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="J62" s="5" t="s">
-        <v>168</v>
-      </c>
       <c r="K62" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="1:11">
@@ -3858,7 +3858,7 @@
         <v>104</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E63" s="1">
         <v>0</v>
@@ -3870,16 +3870,16 @@
         <v>2</v>
       </c>
       <c r="H63" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="I63" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="J63" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="I63" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="J63" s="5" t="s">
-        <v>168</v>
-      </c>
       <c r="K63" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="1:11">
@@ -3887,7 +3887,7 @@
         <v>105</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E64" s="1">
         <v>0</v>
@@ -3899,16 +3899,16 @@
         <v>2</v>
       </c>
       <c r="H64" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="I64" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="J64" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="I64" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="J64" s="5" t="s">
-        <v>168</v>
-      </c>
       <c r="K64" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="1:11">
@@ -3916,28 +3916,28 @@
         <v>106</v>
       </c>
       <c r="D66" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="E66" s="1">
+        <v>1</v>
+      </c>
+      <c r="F66" s="3">
+        <v>0</v>
+      </c>
+      <c r="G66" s="1">
+        <v>1</v>
+      </c>
+      <c r="H66" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="I66" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="E66" s="1">
-        <v>1</v>
-      </c>
-      <c r="F66" s="3">
-        <v>0</v>
-      </c>
-      <c r="G66" s="1">
-        <v>1</v>
-      </c>
-      <c r="H66" s="5" t="s">
+      <c r="J66" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="I66" s="5" t="s">
+      <c r="K66" s="1" t="s">
         <v>183</v>
-      </c>
-      <c r="J66" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="K66" s="1" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="1:11">
@@ -3945,7 +3945,7 @@
         <v>107</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E67" s="1">
         <v>1</v>
@@ -3960,7 +3960,7 @@
         <v>64</v>
       </c>
       <c r="I67" s="5" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="J67" s="5" t="s">
         <v>40</v>
@@ -3974,7 +3974,7 @@
         <v>108</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E68" s="1">
         <v>1</v>
@@ -3989,13 +3989,13 @@
         <v>64</v>
       </c>
       <c r="I68" s="5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="J68" s="5" t="s">
         <v>40</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="1:11">
@@ -4003,28 +4003,28 @@
         <v>109</v>
       </c>
       <c r="D70" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="E70" s="1">
+        <v>1</v>
+      </c>
+      <c r="F70" s="3">
+        <v>0</v>
+      </c>
+      <c r="G70" s="3">
+        <v>2</v>
+      </c>
+      <c r="H70" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="I70" s="5" t="s">
         <v>191</v>
-      </c>
-      <c r="E70" s="1">
-        <v>1</v>
-      </c>
-      <c r="F70" s="3">
-        <v>0</v>
-      </c>
-      <c r="G70" s="3">
-        <v>2</v>
-      </c>
-      <c r="H70" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="I70" s="5" t="s">
-        <v>193</v>
       </c>
       <c r="J70" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="1:11">
@@ -4032,7 +4032,7 @@
         <v>110</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E71" s="1">
         <v>1</v>
@@ -4044,16 +4044,16 @@
         <v>2</v>
       </c>
       <c r="H71" s="5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I71" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="J71" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="1:11">
@@ -4061,7 +4061,7 @@
         <v>111</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E72" s="1">
         <v>1</v>
@@ -4073,16 +4073,16 @@
         <v>2</v>
       </c>
       <c r="H72" s="5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I72" s="5" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="J72" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="1:11">
@@ -4090,7 +4090,7 @@
         <v>112</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E73" s="1">
         <v>1</v>
@@ -4102,16 +4102,16 @@
         <v>2</v>
       </c>
       <c r="H73" s="5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I73" s="5" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="J73" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="1:11">
@@ -4119,7 +4119,7 @@
         <v>113</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E74" s="1">
         <v>1</v>
@@ -4131,16 +4131,16 @@
         <v>2</v>
       </c>
       <c r="H74" s="5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I74" s="5" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="J74" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="1:11">
@@ -4148,28 +4148,28 @@
         <v>114</v>
       </c>
       <c r="D75" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="E75" s="1">
+        <v>1</v>
+      </c>
+      <c r="F75" s="3">
+        <v>0</v>
+      </c>
+      <c r="G75" s="3">
+        <v>2</v>
+      </c>
+      <c r="H75" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="I75" s="5" t="s">
         <v>207</v>
-      </c>
-      <c r="E75" s="1">
-        <v>1</v>
-      </c>
-      <c r="F75" s="3">
-        <v>0</v>
-      </c>
-      <c r="G75" s="3">
-        <v>2</v>
-      </c>
-      <c r="H75" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="I75" s="5" t="s">
-        <v>209</v>
       </c>
       <c r="J75" s="5" t="s">
         <v>91</v>
       </c>
       <c r="K75" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="1:11">
@@ -4177,7 +4177,7 @@
         <v>115</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E76" s="1">
         <v>1</v>
@@ -4192,27 +4192,27 @@
         <v>150</v>
       </c>
       <c r="I76" s="5" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="J76" s="5" t="s">
         <v>40</v>
       </c>
       <c r="K76" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="1:11">
       <c r="A78" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C78" s="1">
         <v>118</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E78" s="1">
         <v>1</v>
@@ -4224,30 +4224,30 @@
         <v>2</v>
       </c>
       <c r="H78" s="5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I78" s="5" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="J78" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K78" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="1:11">
       <c r="A79" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C79" s="1">
         <v>119</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E79" s="1">
         <v>1</v>
@@ -4259,30 +4259,30 @@
         <v>2</v>
       </c>
       <c r="H79" s="5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I79" s="5" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="J79" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="1:11">
       <c r="A80" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C80" s="1">
         <v>120</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E80" s="1">
         <v>1</v>
@@ -4294,30 +4294,30 @@
         <v>2</v>
       </c>
       <c r="H80" s="5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I80" s="5" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="J80" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K80" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="1:11">
       <c r="A81" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C81" s="1">
         <v>121</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E81" s="1">
         <v>1</v>
@@ -4329,30 +4329,30 @@
         <v>2</v>
       </c>
       <c r="H81" s="5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I81" s="5" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="J81" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K81" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="1:11">
       <c r="A82" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C82" s="1">
         <v>122</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E82" s="1">
         <v>1</v>
@@ -4364,30 +4364,30 @@
         <v>2</v>
       </c>
       <c r="H82" s="5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I82" s="5" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="J82" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K82" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="1:11">
       <c r="A83" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C83" s="1">
         <v>123</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E83" s="1">
         <v>1</v>
@@ -4399,30 +4399,30 @@
         <v>2</v>
       </c>
       <c r="H83" s="5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I83" s="5" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="J83" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K83" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="84" customHeight="1" spans="1:11">
       <c r="A84" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C84" s="1">
         <v>124</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E84" s="1">
         <v>1</v>
@@ -4434,30 +4434,30 @@
         <v>2</v>
       </c>
       <c r="H84" s="5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I84" s="5" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="J84" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K84" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="85" customHeight="1" spans="1:11">
       <c r="A85" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C85" s="1">
         <v>125</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E85" s="1">
         <v>1</v>
@@ -4469,30 +4469,30 @@
         <v>2</v>
       </c>
       <c r="H85" s="5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I85" s="5" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="J85" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K85" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="1:11">
       <c r="A86" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C86" s="1">
         <v>126</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E86" s="1">
         <v>1</v>
@@ -4504,30 +4504,30 @@
         <v>2</v>
       </c>
       <c r="H86" s="5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I86" s="5" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="J86" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K86" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="87" customHeight="1" spans="1:11">
       <c r="A87" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C87" s="1">
         <v>127</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E87" s="1">
         <v>1</v>
@@ -4539,30 +4539,30 @@
         <v>2</v>
       </c>
       <c r="H87" s="5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I87" s="5" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="J87" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K87" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="88" customHeight="1" spans="1:11">
       <c r="A88" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C88" s="1">
         <v>128</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E88" s="1">
         <v>1</v>
@@ -4574,30 +4574,30 @@
         <v>2</v>
       </c>
       <c r="H88" s="5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I88" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="J88" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K88" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="90" customHeight="1" spans="1:11">
       <c r="A90" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C90" s="1">
         <v>137</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E90" s="1">
         <v>1</v>
@@ -4612,62 +4612,62 @@
         <v>150</v>
       </c>
       <c r="I90" s="5" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="J90" s="5" t="s">
         <v>40</v>
       </c>
       <c r="K90" s="1" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="1:11">
       <c r="A91" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C91" s="1">
         <v>138</v>
       </c>
       <c r="D91" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="E91" s="1">
+        <v>1</v>
+      </c>
+      <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
+        <v>2</v>
+      </c>
+      <c r="H91" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="I91" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="E91" s="1">
-        <v>1</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>2</v>
-      </c>
-      <c r="H91" s="5" t="s">
+      <c r="J91" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="I91" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="J91" s="5" t="s">
-        <v>241</v>
-      </c>
       <c r="K91" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="92" customHeight="1" spans="1:11">
       <c r="A92" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C92" s="1">
         <v>139</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E92" s="1">
         <v>1</v>
@@ -4679,16 +4679,16 @@
         <v>2</v>
       </c>
       <c r="H92" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="I92" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="J92" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="I92" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="J92" s="5" t="s">
-        <v>241</v>
-      </c>
       <c r="K92" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="102" customHeight="1" spans="3:11">
@@ -4696,28 +4696,28 @@
         <v>201</v>
       </c>
       <c r="D102" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="E102" s="1">
+        <v>1</v>
+      </c>
+      <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
+        <v>2</v>
+      </c>
+      <c r="H102" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="I102" s="5" t="s">
         <v>244</v>
-      </c>
-      <c r="E102" s="1">
-        <v>1</v>
-      </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
-      <c r="G102" s="3">
-        <v>2</v>
-      </c>
-      <c r="H102" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="I102" s="5" t="s">
-        <v>246</v>
       </c>
       <c r="J102" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K102" s="1" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="103" customHeight="1" spans="3:11">
@@ -4725,7 +4725,7 @@
         <v>202</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E103" s="1">
         <v>1</v>
@@ -4737,16 +4737,16 @@
         <v>2</v>
       </c>
       <c r="H103" s="5" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I103" s="5" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="J103" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K103" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="104" customHeight="1" spans="3:11">
@@ -4754,7 +4754,7 @@
         <v>203</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E104" s="1">
         <v>1</v>
@@ -4766,16 +4766,16 @@
         <v>2</v>
       </c>
       <c r="H104" s="5" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I104" s="5" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J104" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K104" s="1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="105" customHeight="1" spans="3:11">
@@ -4783,7 +4783,7 @@
         <v>204</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E105" s="1">
         <v>1</v>
@@ -4795,16 +4795,16 @@
         <v>2</v>
       </c>
       <c r="H105" s="5" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I105" s="5" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="J105" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K105" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="106" customHeight="1" spans="3:11">
@@ -4812,7 +4812,7 @@
         <v>205</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E106" s="1">
         <v>1</v>
@@ -4824,16 +4824,16 @@
         <v>2</v>
       </c>
       <c r="H106" s="5" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I106" s="5" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="J106" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K106" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="107" customHeight="1" spans="3:11">
@@ -4841,7 +4841,7 @@
         <v>206</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E107" s="1">
         <v>1</v>
@@ -4853,16 +4853,16 @@
         <v>2</v>
       </c>
       <c r="H107" s="5" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I107" s="5" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="J107" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K107" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="108" customHeight="1" spans="3:11">
@@ -4870,28 +4870,28 @@
         <v>207</v>
       </c>
       <c r="D108" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="E108" s="1">
+        <v>1</v>
+      </c>
+      <c r="F108" s="3">
+        <v>0</v>
+      </c>
+      <c r="G108" s="3">
+        <v>2</v>
+      </c>
+      <c r="H108" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="I108" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="E108" s="1">
-        <v>1</v>
-      </c>
-      <c r="F108" s="3">
-        <v>0</v>
-      </c>
-      <c r="G108" s="3">
-        <v>2</v>
-      </c>
-      <c r="H108" s="5" t="s">
+      <c r="J108" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="I108" s="5" t="s">
+      <c r="K108" s="1" t="s">
         <v>265</v>
-      </c>
-      <c r="J108" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="K108" s="1" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="109" customHeight="1" spans="3:11">
@@ -4899,28 +4899,28 @@
         <v>208</v>
       </c>
       <c r="D109" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="E109" s="1">
+        <v>1</v>
+      </c>
+      <c r="F109" s="3">
+        <v>0</v>
+      </c>
+      <c r="G109" s="3">
+        <v>2</v>
+      </c>
+      <c r="H109" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="I109" s="5" t="s">
         <v>268</v>
-      </c>
-      <c r="E109" s="1">
-        <v>1</v>
-      </c>
-      <c r="F109" s="3">
-        <v>0</v>
-      </c>
-      <c r="G109" s="3">
-        <v>2</v>
-      </c>
-      <c r="H109" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="I109" s="5" t="s">
-        <v>270</v>
       </c>
       <c r="J109" s="5" t="s">
         <v>140</v>
       </c>
       <c r="K109" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="110" customHeight="1" spans="3:11">
@@ -4928,28 +4928,28 @@
         <v>209</v>
       </c>
       <c r="D110" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="E110" s="1">
+        <v>1</v>
+      </c>
+      <c r="F110" s="3">
+        <v>0</v>
+      </c>
+      <c r="G110" s="3">
+        <v>2</v>
+      </c>
+      <c r="H110" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="I110" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="J110" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="K110" s="1" t="s">
         <v>272</v>
-      </c>
-      <c r="E110" s="1">
-        <v>1</v>
-      </c>
-      <c r="F110" s="3">
-        <v>0</v>
-      </c>
-      <c r="G110" s="3">
-        <v>2</v>
-      </c>
-      <c r="H110" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="I110" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="J110" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="K110" s="1" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="111" customHeight="1" spans="3:11">
@@ -4957,33 +4957,33 @@
         <v>210</v>
       </c>
       <c r="D111" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="E111" s="1">
+        <v>1</v>
+      </c>
+      <c r="F111" s="3">
+        <v>0</v>
+      </c>
+      <c r="G111" s="3">
+        <v>2</v>
+      </c>
+      <c r="H111" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="I111" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="E111" s="1">
-        <v>1</v>
-      </c>
-      <c r="F111" s="3">
-        <v>0</v>
-      </c>
-      <c r="G111" s="3">
-        <v>2</v>
-      </c>
-      <c r="H111" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="I111" s="5" t="s">
-        <v>277</v>
-      </c>
       <c r="J111" s="5" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="K111" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:E5 H3:K5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="H3:K5 C3:E5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="F3:G5" errorStyle="warning">
@@ -4999,7 +4999,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B3:L54"/>
+  <dimension ref="B3:L55"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="3" width="9"/>
@@ -5106,7 +5106,7 @@
         <v>1001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -5121,13 +5121,13 @@
         <v>14</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="J6" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5135,7 +5135,7 @@
         <v>1002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -5150,13 +5150,13 @@
         <v>14</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="J7" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5164,7 +5164,7 @@
         <v>1003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -5179,13 +5179,13 @@
         <v>14</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="J8" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5193,7 +5193,7 @@
         <v>1004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
@@ -5208,13 +5208,13 @@
         <v>14</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="J9" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5222,7 +5222,7 @@
         <v>1005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -5237,13 +5237,13 @@
         <v>14</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="J10" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5251,7 +5251,7 @@
         <v>1006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -5266,13 +5266,13 @@
         <v>14</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="J11" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5280,7 +5280,7 @@
         <v>1007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
@@ -5295,13 +5295,13 @@
         <v>14</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="J12" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5309,7 +5309,7 @@
         <v>1008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
@@ -5324,13 +5324,13 @@
         <v>14</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="J13" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5338,7 +5338,7 @@
         <v>1009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
@@ -5353,13 +5353,13 @@
         <v>14</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="J14" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5367,7 +5367,7 @@
         <v>1010</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
@@ -5382,13 +5382,13 @@
         <v>14</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J15" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5396,7 +5396,7 @@
         <v>1011</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="E16" s="1">
         <v>1</v>
@@ -5411,21 +5411,21 @@
         <v>14</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="J16" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
       <c r="C17" s="1">
         <v>1012</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E17" s="1">
         <v>1</v>
@@ -5440,21 +5440,21 @@
         <v>14</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J17" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
       <c r="C18" s="1">
         <v>1013</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E18" s="1">
         <v>1</v>
@@ -5469,51 +5469,51 @@
         <v>14</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="J18" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K18" s="1" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+      <c r="C19" s="1">
+        <v>1014</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="19" s="1" customFormat="1" ht="18" customHeight="1"/>
-    <row r="20" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
-      <c r="C20" s="1">
+      <c r="E19" s="1">
+        <v>1</v>
+      </c>
+      <c r="F19" s="3">
+        <v>0</v>
+      </c>
+      <c r="G19" s="1">
+        <v>2</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" ht="18" customHeight="1"/>
+    <row r="21" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+      <c r="C21" s="1">
         <v>1101</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D21" s="1" t="s">
         <v>313</v>
-      </c>
-      <c r="E20" s="1">
-        <v>1</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="1">
-        <v>2</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I20" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="J20" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
-      <c r="C21" s="1">
-        <v>1102</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>316</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
@@ -5528,21 +5528,21 @@
         <v>14</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="J21" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="22" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
       <c r="C22" s="1">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
@@ -5557,21 +5557,21 @@
         <v>14</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="J22" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="23" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
       <c r="C23" s="1">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
@@ -5586,21 +5586,21 @@
         <v>14</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="J23" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="24" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
       <c r="C24" s="1">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
@@ -5615,21 +5615,21 @@
         <v>14</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="J24" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="25" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
       <c r="C25" s="1">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="E25" s="1">
         <v>1</v>
@@ -5644,21 +5644,21 @@
         <v>14</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="J25" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="26" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
       <c r="C26" s="1">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
@@ -5673,21 +5673,21 @@
         <v>14</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="J26" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="27" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
       <c r="C27" s="1">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="E27" s="1">
         <v>1</v>
@@ -5702,21 +5702,21 @@
         <v>14</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="J27" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="28" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
       <c r="C28" s="1">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="E28" s="1">
         <v>1</v>
@@ -5731,21 +5731,21 @@
         <v>14</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="J28" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="29" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
       <c r="C29" s="1">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
@@ -5760,21 +5760,21 @@
         <v>14</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="J29" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="30" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="30" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
       <c r="C30" s="1">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
@@ -5789,21 +5789,21 @@
         <v>14</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="J30" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="31" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="31" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
       <c r="C31" s="1">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
@@ -5818,40 +5818,56 @@
         <v>14</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="J31" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K31" s="1" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="32" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+      <c r="C32" s="1">
+        <v>1112</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="E32" s="1">
+        <v>1</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="1">
+        <v>2</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I32" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="J32" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K32" s="1" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="32" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
-      <c r="B32"/>
-      <c r="C32"/>
-      <c r="D32"/>
-      <c r="E32"/>
-      <c r="F32"/>
-      <c r="G32"/>
-      <c r="H32"/>
-      <c r="I32"/>
-      <c r="J32"/>
-      <c r="K32"/>
-      <c r="L32"/>
-    </row>
-    <row r="34" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
-      <c r="B34"/>
-      <c r="C34"/>
-      <c r="D34"/>
-      <c r="E34"/>
-      <c r="F34"/>
-      <c r="G34"/>
-      <c r="H34"/>
-      <c r="I34"/>
-      <c r="J34"/>
-      <c r="K34"/>
-      <c r="L34"/>
+    <row r="33" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
+      <c r="B33"/>
+      <c r="C33"/>
+      <c r="D33"/>
+      <c r="E33"/>
+      <c r="F33"/>
+      <c r="G33"/>
+      <c r="H33"/>
+      <c r="I33"/>
+      <c r="J33"/>
+      <c r="K33"/>
+      <c r="L33"/>
     </row>
     <row r="35" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
       <c r="B35"/>
@@ -5866,18 +5882,18 @@
       <c r="K35"/>
       <c r="L35"/>
     </row>
-    <row r="46" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
-      <c r="B46"/>
-      <c r="C46"/>
-      <c r="D46"/>
-      <c r="E46"/>
-      <c r="F46"/>
-      <c r="G46"/>
-      <c r="H46"/>
-      <c r="I46"/>
-      <c r="J46"/>
-      <c r="K46"/>
-      <c r="L46"/>
+    <row r="36" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
+      <c r="B36"/>
+      <c r="C36"/>
+      <c r="D36"/>
+      <c r="E36"/>
+      <c r="F36"/>
+      <c r="G36"/>
+      <c r="H36"/>
+      <c r="I36"/>
+      <c r="J36"/>
+      <c r="K36"/>
+      <c r="L36"/>
     </row>
     <row r="47" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
       <c r="B47"/>
@@ -5983,6 +5999,19 @@
       <c r="K54"/>
       <c r="L54"/>
     </row>
+    <row r="55" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
+      <c r="B55"/>
+      <c r="C55"/>
+      <c r="D55"/>
+      <c r="E55"/>
+      <c r="F55"/>
+      <c r="G55"/>
+      <c r="H55"/>
+      <c r="I55"/>
+      <c r="J55"/>
+      <c r="K55"/>
+      <c r="L55"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="350">
   <si>
     <t>_id</t>
   </si>
@@ -479,88 +479,91 @@
     <t>麒麟神器自选</t>
   </si>
   <si>
-    <t>神器自选</t>
+    <t>61000033,61000034,61000035,61000036,61000037,61000038,61000039,61000040</t>
+  </si>
+  <si>
+    <t>全神器自选</t>
+  </si>
+  <si>
+    <t>4,4,4,4,4</t>
+  </si>
+  <si>
+    <t>35,37,38,39,40</t>
+  </si>
+  <si>
+    <t>12阶技能自选</t>
+  </si>
+  <si>
+    <t>1012,2012,3012</t>
+  </si>
+  <si>
+    <t>12技能三选一</t>
+  </si>
+  <si>
+    <t>生肖自选</t>
+  </si>
+  <si>
+    <t>22,22,22,22,22,22,22,22,22,22,22,22</t>
+  </si>
+  <si>
+    <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
+  </si>
+  <si>
+    <t>1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1</t>
+  </si>
+  <si>
+    <t>极戒自选</t>
+  </si>
+  <si>
+    <t>190007,190008,190009,190010,190011,190012</t>
+  </si>
+  <si>
+    <t>暗金专属自选</t>
+  </si>
+  <si>
+    <t>4,4,4,4,4,4,4,4,4,4,4</t>
+  </si>
+  <si>
+    <t>1101,1102,1103,1104,1105,1106,1107,1108,1109,1110,1111</t>
+  </si>
+  <si>
+    <t>高级暗金专属</t>
+  </si>
+  <si>
+    <t>1107,1108,1109,1110,1111</t>
+  </si>
+  <si>
+    <t>金色专属自选</t>
+  </si>
+  <si>
+    <t>4,4,4,4,4,4</t>
+  </si>
+  <si>
+    <t>1001,1002,1003,1010,1011,1012</t>
+  </si>
+  <si>
+    <t>高级金色专属</t>
+  </si>
+  <si>
+    <t>1007,1008,1009,1001,1002,1003,1004,1005,1006,1013,1014</t>
+  </si>
+  <si>
+    <t>驱魔6件套</t>
+  </si>
+  <si>
+    <t>12,12,12,12,12,12,5,5</t>
+  </si>
+  <si>
+    <t>36,37,38,39,40,41,4005,4010</t>
+  </si>
+  <si>
+    <t>1,1,1,1,1,1,300,60</t>
+  </si>
+  <si>
+    <t>盾专属自选套</t>
   </si>
   <si>
     <t>4,4,4,4</t>
-  </si>
-  <si>
-    <t>35,37,38,39</t>
-  </si>
-  <si>
-    <t>12阶技能自选</t>
-  </si>
-  <si>
-    <t>1012,2012,3012</t>
-  </si>
-  <si>
-    <t>12技能三选一</t>
-  </si>
-  <si>
-    <t>生肖自选</t>
-  </si>
-  <si>
-    <t>22,22,22,22,22,22,22,22,22,22,22,22</t>
-  </si>
-  <si>
-    <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
-  </si>
-  <si>
-    <t>1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1</t>
-  </si>
-  <si>
-    <t>极戒自选</t>
-  </si>
-  <si>
-    <t>190007,190008,190009,190010,190011,190012</t>
-  </si>
-  <si>
-    <t>暗金专属自选</t>
-  </si>
-  <si>
-    <t>4,4,4,4,4,4,4,4,4,4,4</t>
-  </si>
-  <si>
-    <t>1101,1102,1103,1104,1105,1106,1107,1108,1109,1110,1111</t>
-  </si>
-  <si>
-    <t>高级暗金专属</t>
-  </si>
-  <si>
-    <t>4,4,4,4,4</t>
-  </si>
-  <si>
-    <t>1107,1108,1109,1110,1111</t>
-  </si>
-  <si>
-    <t>金色专属自选</t>
-  </si>
-  <si>
-    <t>4,4,4,4,4,4</t>
-  </si>
-  <si>
-    <t>1001,1002,1003,1010,1011,1012</t>
-  </si>
-  <si>
-    <t>高级金色专属</t>
-  </si>
-  <si>
-    <t>1007,1008,1009,1001,1002,1003,1004,1005,1006,1013,1014</t>
-  </si>
-  <si>
-    <t>驱魔6件套</t>
-  </si>
-  <si>
-    <t>12,12,12,12,12,12,5,5</t>
-  </si>
-  <si>
-    <t>36,37,38,39,40,41,4005,4010</t>
-  </si>
-  <si>
-    <t>1,1,1,1,1,1,300,60</t>
-  </si>
-  <si>
-    <t>盾专属自选套</t>
   </si>
   <si>
     <t>99,102,104</t>
@@ -3357,13 +3360,13 @@
         <v>89</v>
       </c>
       <c r="I45" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="J45" s="5" t="s">
         <v>91</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="1:11">
@@ -3371,7 +3374,7 @@
         <v>41</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E46" s="1">
         <v>1</v>
@@ -3383,16 +3386,16 @@
         <v>1</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I46" s="5" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J46" s="5" t="s">
         <v>91</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="1:11">
@@ -3400,7 +3403,7 @@
         <v>42</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E47" s="1">
         <v>1</v>
@@ -3415,13 +3418,13 @@
         <v>30</v>
       </c>
       <c r="I47" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J47" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="48" customFormat="1" customHeight="1" spans="1:11">
@@ -3431,7 +3434,7 @@
         <v>43</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E48" s="1">
         <v>1</v>
@@ -3443,16 +3446,16 @@
         <v>2</v>
       </c>
       <c r="H48" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="I48" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="J48" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="K48" s="1" t="s">
         <v>138</v>
-      </c>
-      <c r="I48" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="J48" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="K48" s="1" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="49" s="1" customFormat="1" customHeight="1" spans="1:11">
@@ -3460,7 +3463,7 @@
         <v>44</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E49" s="1">
         <v>1</v>
@@ -3475,13 +3478,13 @@
         <v>77</v>
       </c>
       <c r="I49" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J49" s="5" t="s">
         <v>40</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="50" customFormat="1" customHeight="1" spans="1:11">
@@ -3504,7 +3507,7 @@
         <v>90</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E51" s="1">
         <v>1</v>
@@ -3516,16 +3519,16 @@
         <v>2</v>
       </c>
       <c r="H51" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="I51" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="J51" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="K51" s="1" t="s">
         <v>144</v>
-      </c>
-      <c r="I51" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="J51" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="K51" s="1" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="52" customFormat="1" customHeight="1" spans="1:11">
@@ -3535,7 +3538,7 @@
         <v>91</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E52" s="1">
         <v>1</v>
@@ -3547,7 +3550,7 @@
         <v>2</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="I52" s="5" t="s">
         <v>148</v>
@@ -3556,7 +3559,7 @@
         <v>16</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="53" customFormat="1" customHeight="1" spans="1:11">
@@ -3609,7 +3612,7 @@
         <v>2</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I54" s="5" t="s">
         <v>153</v>
@@ -3667,10 +3670,10 @@
         <v>2</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="I56" s="5" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J56" s="5" t="s">
         <v>32</v>
@@ -3684,7 +3687,7 @@
         <v>98</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E57" s="1">
         <v>1</v>
@@ -3696,16 +3699,16 @@
         <v>2</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I57" s="5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J57" s="5" t="s">
         <v>91</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="1:11">
@@ -3713,7 +3716,7 @@
         <v>99</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E58" s="1">
         <v>0</v>
@@ -3725,16 +3728,16 @@
         <v>2</v>
       </c>
       <c r="H58" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="I58" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="J58" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="K58" s="1" t="s">
         <v>164</v>
-      </c>
-      <c r="I58" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="J58" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="K58" s="1" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="1:11">
@@ -3742,7 +3745,7 @@
         <v>100</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E59" s="1">
         <v>0</v>
@@ -3757,13 +3760,13 @@
         <v>155</v>
       </c>
       <c r="I59" s="5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J59" s="5" t="s">
         <v>157</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="1:11">
@@ -3771,7 +3774,7 @@
         <v>101</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E60" s="1">
         <v>0</v>
@@ -3786,13 +3789,13 @@
         <v>155</v>
       </c>
       <c r="I60" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J60" s="5" t="s">
         <v>157</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="1:11">
@@ -3800,7 +3803,7 @@
         <v>102</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E61" s="1">
         <v>0</v>
@@ -3812,16 +3815,16 @@
         <v>2</v>
       </c>
       <c r="H61" s="5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I61" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="J61" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="K61" s="1" t="s">
         <v>172</v>
-      </c>
-      <c r="J61" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="K61" s="1" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="1:11">
@@ -3829,7 +3832,7 @@
         <v>103</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E62" s="1">
         <v>0</v>
@@ -3841,16 +3844,16 @@
         <v>2</v>
       </c>
       <c r="H62" s="5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I62" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="J62" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="K62" s="1" t="s">
         <v>174</v>
-      </c>
-      <c r="J62" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="K62" s="1" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="1:11">
@@ -3858,7 +3861,7 @@
         <v>104</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E63" s="1">
         <v>0</v>
@@ -3870,16 +3873,16 @@
         <v>2</v>
       </c>
       <c r="H63" s="5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I63" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="J63" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="K63" s="1" t="s">
         <v>176</v>
-      </c>
-      <c r="J63" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="K63" s="1" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="1:11">
@@ -3887,7 +3890,7 @@
         <v>105</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E64" s="1">
         <v>0</v>
@@ -3899,16 +3902,16 @@
         <v>2</v>
       </c>
       <c r="H64" s="5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I64" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="J64" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="K64" s="1" t="s">
         <v>178</v>
-      </c>
-      <c r="J64" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="K64" s="1" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="1:11">
@@ -3916,7 +3919,7 @@
         <v>106</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E66" s="1">
         <v>1</v>
@@ -3928,16 +3931,16 @@
         <v>1</v>
       </c>
       <c r="H66" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I66" s="5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J66" s="5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="1:11">
@@ -3945,7 +3948,7 @@
         <v>107</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E67" s="1">
         <v>1</v>
@@ -3960,7 +3963,7 @@
         <v>64</v>
       </c>
       <c r="I67" s="5" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J67" s="5" t="s">
         <v>40</v>
@@ -3974,7 +3977,7 @@
         <v>108</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E68" s="1">
         <v>1</v>
@@ -3989,13 +3992,13 @@
         <v>64</v>
       </c>
       <c r="I68" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J68" s="5" t="s">
         <v>40</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="1:11">
@@ -4003,7 +4006,7 @@
         <v>109</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E70" s="1">
         <v>1</v>
@@ -4015,16 +4018,16 @@
         <v>2</v>
       </c>
       <c r="H70" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I70" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J70" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="1:11">
@@ -4032,7 +4035,7 @@
         <v>110</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E71" s="1">
         <v>1</v>
@@ -4044,16 +4047,16 @@
         <v>2</v>
       </c>
       <c r="H71" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I71" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J71" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="1:11">
@@ -4061,7 +4064,7 @@
         <v>111</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E72" s="1">
         <v>1</v>
@@ -4073,16 +4076,16 @@
         <v>2</v>
       </c>
       <c r="H72" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I72" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J72" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="1:11">
@@ -4090,7 +4093,7 @@
         <v>112</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E73" s="1">
         <v>1</v>
@@ -4102,16 +4105,16 @@
         <v>2</v>
       </c>
       <c r="H73" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I73" s="5" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="J73" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="1:11">
@@ -4119,7 +4122,7 @@
         <v>113</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E74" s="1">
         <v>1</v>
@@ -4131,16 +4134,16 @@
         <v>2</v>
       </c>
       <c r="H74" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I74" s="5" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="J74" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="1:11">
@@ -4148,7 +4151,7 @@
         <v>114</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E75" s="1">
         <v>1</v>
@@ -4160,16 +4163,16 @@
         <v>2</v>
       </c>
       <c r="H75" s="5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I75" s="5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="J75" s="5" t="s">
         <v>91</v>
       </c>
       <c r="K75" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="1:11">
@@ -4177,7 +4180,7 @@
         <v>115</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E76" s="1">
         <v>1</v>
@@ -4192,27 +4195,27 @@
         <v>150</v>
       </c>
       <c r="I76" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J76" s="5" t="s">
         <v>40</v>
       </c>
       <c r="K76" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="1:11">
       <c r="A78" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C78" s="1">
         <v>118</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E78" s="1">
         <v>1</v>
@@ -4224,30 +4227,30 @@
         <v>2</v>
       </c>
       <c r="H78" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I78" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J78" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K78" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="1:11">
       <c r="A79" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C79" s="1">
         <v>119</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E79" s="1">
         <v>1</v>
@@ -4259,30 +4262,30 @@
         <v>2</v>
       </c>
       <c r="H79" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I79" s="5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J79" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="1:11">
       <c r="A80" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C80" s="1">
         <v>120</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E80" s="1">
         <v>1</v>
@@ -4294,30 +4297,30 @@
         <v>2</v>
       </c>
       <c r="H80" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I80" s="5" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="J80" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K80" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="1:11">
       <c r="A81" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C81" s="1">
         <v>121</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E81" s="1">
         <v>1</v>
@@ -4329,30 +4332,30 @@
         <v>2</v>
       </c>
       <c r="H81" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I81" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J81" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K81" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="1:11">
       <c r="A82" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C82" s="1">
         <v>122</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E82" s="1">
         <v>1</v>
@@ -4364,30 +4367,30 @@
         <v>2</v>
       </c>
       <c r="H82" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I82" s="5" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="J82" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K82" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="1:11">
       <c r="A83" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C83" s="1">
         <v>123</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E83" s="1">
         <v>1</v>
@@ -4399,30 +4402,30 @@
         <v>2</v>
       </c>
       <c r="H83" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I83" s="5" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J83" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K83" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="84" customHeight="1" spans="1:11">
       <c r="A84" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C84" s="1">
         <v>124</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E84" s="1">
         <v>1</v>
@@ -4434,30 +4437,30 @@
         <v>2</v>
       </c>
       <c r="H84" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I84" s="5" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="J84" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K84" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="85" customHeight="1" spans="1:11">
       <c r="A85" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C85" s="1">
         <v>125</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E85" s="1">
         <v>1</v>
@@ -4469,30 +4472,30 @@
         <v>2</v>
       </c>
       <c r="H85" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I85" s="5" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="J85" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K85" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="1:11">
       <c r="A86" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C86" s="1">
         <v>126</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E86" s="1">
         <v>1</v>
@@ -4504,30 +4507,30 @@
         <v>2</v>
       </c>
       <c r="H86" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I86" s="5" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="J86" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K86" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="87" customHeight="1" spans="1:11">
       <c r="A87" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C87" s="1">
         <v>127</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E87" s="1">
         <v>1</v>
@@ -4539,30 +4542,30 @@
         <v>2</v>
       </c>
       <c r="H87" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I87" s="5" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="J87" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K87" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="88" customHeight="1" spans="1:11">
       <c r="A88" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C88" s="1">
         <v>128</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E88" s="1">
         <v>1</v>
@@ -4574,30 +4577,30 @@
         <v>2</v>
       </c>
       <c r="H88" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I88" s="5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="J88" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K88" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="90" customHeight="1" spans="1:11">
       <c r="A90" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C90" s="1">
         <v>137</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E90" s="1">
         <v>1</v>
@@ -4612,27 +4615,27 @@
         <v>150</v>
       </c>
       <c r="I90" s="5" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="J90" s="5" t="s">
         <v>40</v>
       </c>
       <c r="K90" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="1:11">
       <c r="A91" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C91" s="1">
         <v>138</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E91" s="1">
         <v>1</v>
@@ -4644,51 +4647,51 @@
         <v>2</v>
       </c>
       <c r="H91" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="I91" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="J91" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="K91" s="1" t="s">
         <v>237</v>
-      </c>
-      <c r="I91" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="J91" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="K91" s="1" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="92" customHeight="1" spans="1:11">
       <c r="A92" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C92" s="1">
         <v>139</v>
       </c>
       <c r="D92" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="E92" s="1">
+        <v>1</v>
+      </c>
+      <c r="F92" s="3">
+        <v>0</v>
+      </c>
+      <c r="G92" s="3">
+        <v>2</v>
+      </c>
+      <c r="H92" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="I92" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="J92" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="E92" s="1">
-        <v>1</v>
-      </c>
-      <c r="F92" s="3">
-        <v>0</v>
-      </c>
-      <c r="G92" s="3">
-        <v>2</v>
-      </c>
-      <c r="H92" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="I92" s="5" t="s">
+      <c r="K92" s="1" t="s">
         <v>241</v>
-      </c>
-      <c r="J92" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="K92" s="1" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="102" customHeight="1" spans="3:11">
@@ -4696,7 +4699,7 @@
         <v>201</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E102" s="1">
         <v>1</v>
@@ -4708,16 +4711,16 @@
         <v>2</v>
       </c>
       <c r="H102" s="5" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I102" s="5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="J102" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K102" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="103" customHeight="1" spans="3:11">
@@ -4725,7 +4728,7 @@
         <v>202</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E103" s="1">
         <v>1</v>
@@ -4737,16 +4740,16 @@
         <v>2</v>
       </c>
       <c r="H103" s="5" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I103" s="5" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="J103" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K103" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="104" customHeight="1" spans="3:11">
@@ -4754,7 +4757,7 @@
         <v>203</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E104" s="1">
         <v>1</v>
@@ -4766,16 +4769,16 @@
         <v>2</v>
       </c>
       <c r="H104" s="5" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I104" s="5" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="J104" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K104" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="105" customHeight="1" spans="3:11">
@@ -4783,7 +4786,7 @@
         <v>204</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E105" s="1">
         <v>1</v>
@@ -4795,16 +4798,16 @@
         <v>2</v>
       </c>
       <c r="H105" s="5" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I105" s="5" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J105" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K105" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="106" customHeight="1" spans="3:11">
@@ -4812,7 +4815,7 @@
         <v>205</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E106" s="1">
         <v>1</v>
@@ -4824,16 +4827,16 @@
         <v>2</v>
       </c>
       <c r="H106" s="5" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I106" s="5" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J106" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K106" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="107" customHeight="1" spans="3:11">
@@ -4841,7 +4844,7 @@
         <v>206</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E107" s="1">
         <v>1</v>
@@ -4853,16 +4856,16 @@
         <v>2</v>
       </c>
       <c r="H107" s="5" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I107" s="5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="J107" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K107" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="108" customHeight="1" spans="3:11">
@@ -4870,7 +4873,7 @@
         <v>207</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E108" s="1">
         <v>1</v>
@@ -4882,16 +4885,16 @@
         <v>2</v>
       </c>
       <c r="H108" s="5" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="I108" s="5" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="J108" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K108" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="109" customHeight="1" spans="3:11">
@@ -4899,7 +4902,7 @@
         <v>208</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E109" s="1">
         <v>1</v>
@@ -4911,16 +4914,16 @@
         <v>2</v>
       </c>
       <c r="H109" s="5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I109" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="J109" s="5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K109" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="110" customHeight="1" spans="3:11">
@@ -4928,7 +4931,7 @@
         <v>209</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E110" s="1">
         <v>1</v>
@@ -4940,16 +4943,16 @@
         <v>2</v>
       </c>
       <c r="H110" s="5" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="I110" s="5" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="J110" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K110" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="111" customHeight="1" spans="3:11">
@@ -4957,33 +4960,33 @@
         <v>210</v>
       </c>
       <c r="D111" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="E111" s="1">
+        <v>1</v>
+      </c>
+      <c r="F111" s="3">
+        <v>0</v>
+      </c>
+      <c r="G111" s="3">
+        <v>2</v>
+      </c>
+      <c r="H111" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="I111" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="J111" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="K111" s="1" t="s">
         <v>273</v>
-      </c>
-      <c r="E111" s="1">
-        <v>1</v>
-      </c>
-      <c r="F111" s="3">
-        <v>0</v>
-      </c>
-      <c r="G111" s="3">
-        <v>2</v>
-      </c>
-      <c r="H111" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="I111" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="J111" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="K111" s="1" t="s">
-        <v>272</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="H3:K5 C3:E5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:E5 H3:K5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="F3:G5" errorStyle="warning">
@@ -5106,7 +5109,7 @@
         <v>1001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -5121,13 +5124,13 @@
         <v>14</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J6" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5135,7 +5138,7 @@
         <v>1002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -5150,13 +5153,13 @@
         <v>14</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J7" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5164,7 +5167,7 @@
         <v>1003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -5179,13 +5182,13 @@
         <v>14</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J8" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5193,7 +5196,7 @@
         <v>1004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
@@ -5208,13 +5211,13 @@
         <v>14</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="J9" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5222,7 +5225,7 @@
         <v>1005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -5237,13 +5240,13 @@
         <v>14</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J10" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5251,7 +5254,7 @@
         <v>1006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -5266,13 +5269,13 @@
         <v>14</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="J11" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5280,7 +5283,7 @@
         <v>1007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
@@ -5295,13 +5298,13 @@
         <v>14</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="J12" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5309,7 +5312,7 @@
         <v>1008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
@@ -5324,13 +5327,13 @@
         <v>14</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="J13" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5338,7 +5341,7 @@
         <v>1009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
@@ -5353,13 +5356,13 @@
         <v>14</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J14" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5367,7 +5370,7 @@
         <v>1010</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
@@ -5382,13 +5385,13 @@
         <v>14</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="J15" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5396,7 +5399,7 @@
         <v>1011</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E16" s="1">
         <v>1</v>
@@ -5411,13 +5414,13 @@
         <v>14</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="J16" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5425,7 +5428,7 @@
         <v>1012</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E17" s="1">
         <v>1</v>
@@ -5440,13 +5443,13 @@
         <v>14</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="J17" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5454,7 +5457,7 @@
         <v>1013</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E18" s="1">
         <v>1</v>
@@ -5469,13 +5472,13 @@
         <v>14</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J18" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5483,7 +5486,7 @@
         <v>1014</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E19" s="1">
         <v>1</v>
@@ -5498,13 +5501,13 @@
         <v>14</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="J19" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" ht="18" customHeight="1"/>
@@ -5513,7 +5516,7 @@
         <v>1101</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
@@ -5528,13 +5531,13 @@
         <v>14</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J21" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5542,7 +5545,7 @@
         <v>1102</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
@@ -5557,13 +5560,13 @@
         <v>14</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="J22" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5571,7 +5574,7 @@
         <v>1103</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
@@ -5586,13 +5589,13 @@
         <v>14</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J23" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5600,7 +5603,7 @@
         <v>1104</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
@@ -5615,13 +5618,13 @@
         <v>14</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="J24" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5629,7 +5632,7 @@
         <v>1105</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E25" s="1">
         <v>1</v>
@@ -5644,13 +5647,13 @@
         <v>14</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="J25" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5658,7 +5661,7 @@
         <v>1106</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
@@ -5673,13 +5676,13 @@
         <v>14</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="J26" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5687,7 +5690,7 @@
         <v>1107</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E27" s="1">
         <v>1</v>
@@ -5702,13 +5705,13 @@
         <v>14</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="J27" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5716,7 +5719,7 @@
         <v>1108</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E28" s="1">
         <v>1</v>
@@ -5731,13 +5734,13 @@
         <v>14</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="J28" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5745,7 +5748,7 @@
         <v>1109</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
@@ -5760,13 +5763,13 @@
         <v>14</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="J29" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5774,7 +5777,7 @@
         <v>1110</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
@@ -5789,13 +5792,13 @@
         <v>14</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="J30" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5803,7 +5806,7 @@
         <v>1111</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
@@ -5818,13 +5821,13 @@
         <v>14</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="J31" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5832,7 +5835,7 @@
         <v>1112</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E32" s="1">
         <v>1</v>
@@ -5847,13 +5850,13 @@
         <v>14</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="J32" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="354">
   <si>
     <t>_id</t>
   </si>
@@ -915,6 +915,18 @@
   </si>
   <si>
     <t>43,44,45,46,47,48</t>
+  </si>
+  <si>
+    <t>50粉宠自选</t>
+  </si>
+  <si>
+    <t>201,202,203</t>
+  </si>
+  <si>
+    <t>70粉宠自选</t>
+  </si>
+  <si>
+    <t>211,212,213</t>
   </si>
   <si>
     <t>金色刺杀自选</t>
@@ -2106,7 +2118,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:K111"/>
+  <dimension ref="A3:K113"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -4982,6 +4994,64 @@
       </c>
       <c r="K111" s="1" t="s">
         <v>273</v>
+      </c>
+    </row>
+    <row r="112" customHeight="1" spans="3:11">
+      <c r="C112" s="1">
+        <v>211</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="E112" s="1">
+        <v>1</v>
+      </c>
+      <c r="F112" s="3">
+        <v>0</v>
+      </c>
+      <c r="G112" s="3">
+        <v>2</v>
+      </c>
+      <c r="H112" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="I112" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="J112" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="K112" s="1" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="113" customHeight="1" spans="3:11">
+      <c r="C113" s="1">
+        <v>212</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="E113" s="1">
+        <v>1</v>
+      </c>
+      <c r="F113" s="3">
+        <v>0</v>
+      </c>
+      <c r="G113" s="3">
+        <v>2</v>
+      </c>
+      <c r="H113" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="I113" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="J113" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="K113" s="1" t="s">
+        <v>279</v>
       </c>
     </row>
   </sheetData>
@@ -5109,7 +5179,7 @@
         <v>1001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -5124,13 +5194,13 @@
         <v>14</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="J6" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5138,7 +5208,7 @@
         <v>1002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -5153,13 +5223,13 @@
         <v>14</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="J7" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5167,7 +5237,7 @@
         <v>1003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -5182,13 +5252,13 @@
         <v>14</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="J8" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5196,7 +5266,7 @@
         <v>1004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
@@ -5211,13 +5281,13 @@
         <v>14</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="J9" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5225,7 +5295,7 @@
         <v>1005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -5240,13 +5310,13 @@
         <v>14</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="J10" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5254,7 +5324,7 @@
         <v>1006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -5269,13 +5339,13 @@
         <v>14</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="J11" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5283,7 +5353,7 @@
         <v>1007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
@@ -5298,13 +5368,13 @@
         <v>14</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="J12" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5312,7 +5382,7 @@
         <v>1008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
@@ -5327,13 +5397,13 @@
         <v>14</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="J13" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5341,7 +5411,7 @@
         <v>1009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
@@ -5356,13 +5426,13 @@
         <v>14</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="J14" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5370,7 +5440,7 @@
         <v>1010</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
@@ -5385,13 +5455,13 @@
         <v>14</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="J15" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5399,7 +5469,7 @@
         <v>1011</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="E16" s="1">
         <v>1</v>
@@ -5414,13 +5484,13 @@
         <v>14</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="J16" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5428,7 +5498,7 @@
         <v>1012</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="E17" s="1">
         <v>1</v>
@@ -5443,13 +5513,13 @@
         <v>14</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="J17" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5457,7 +5527,7 @@
         <v>1013</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="E18" s="1">
         <v>1</v>
@@ -5472,13 +5542,13 @@
         <v>14</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="J18" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5486,7 +5556,7 @@
         <v>1014</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="E19" s="1">
         <v>1</v>
@@ -5501,13 +5571,13 @@
         <v>14</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="J19" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" ht="18" customHeight="1"/>
@@ -5516,7 +5586,7 @@
         <v>1101</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
@@ -5531,13 +5601,13 @@
         <v>14</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="J21" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5545,7 +5615,7 @@
         <v>1102</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
@@ -5560,13 +5630,13 @@
         <v>14</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="J22" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5574,7 +5644,7 @@
         <v>1103</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
@@ -5589,13 +5659,13 @@
         <v>14</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="J23" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5603,7 +5673,7 @@
         <v>1104</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
@@ -5618,13 +5688,13 @@
         <v>14</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="J24" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5632,7 +5702,7 @@
         <v>1105</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="E25" s="1">
         <v>1</v>
@@ -5647,13 +5717,13 @@
         <v>14</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="J25" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5661,7 +5731,7 @@
         <v>1106</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
@@ -5676,13 +5746,13 @@
         <v>14</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="J26" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5690,7 +5760,7 @@
         <v>1107</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="E27" s="1">
         <v>1</v>
@@ -5705,13 +5775,13 @@
         <v>14</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="J27" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5719,7 +5789,7 @@
         <v>1108</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="E28" s="1">
         <v>1</v>
@@ -5734,13 +5804,13 @@
         <v>14</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="J28" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5748,7 +5818,7 @@
         <v>1109</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
@@ -5763,13 +5833,13 @@
         <v>14</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="J29" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5777,7 +5847,7 @@
         <v>1110</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
@@ -5792,13 +5862,13 @@
         <v>14</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="J30" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5806,7 +5876,7 @@
         <v>1111</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
@@ -5821,13 +5891,13 @@
         <v>14</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="J31" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5835,7 +5905,7 @@
         <v>1112</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="E32" s="1">
         <v>1</v>
@@ -5850,13 +5920,13 @@
         <v>14</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="J32" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -911,10 +911,10 @@
     <t>50金宠自选1</t>
   </si>
   <si>
-    <t>21,21,21,21,21,21</t>
-  </si>
-  <si>
-    <t>43,44,45,46,47,48</t>
+    <t>21,21,21,21,21,21,21,21,21</t>
+  </si>
+  <si>
+    <t>43,44,45,46,47,48,49,50,51</t>
   </si>
   <si>
     <t>50粉宠自选</t>
@@ -1324,12 +1324,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="350">
   <si>
     <t>_id</t>
   </si>
@@ -854,22 +854,10 @@
     <t>40资质红宠自选</t>
   </si>
   <si>
-    <t>45红宠自选</t>
+    <t>30金宠自选</t>
   </si>
   <si>
     <t>13,14,15</t>
-  </si>
-  <si>
-    <t>45资质红宠自选</t>
-  </si>
-  <si>
-    <t>50红宠自选</t>
-  </si>
-  <si>
-    <t>16,17,18</t>
-  </si>
-  <si>
-    <t>50资质红宠自选</t>
   </si>
   <si>
     <t>40金宠自选</t>
@@ -1324,12 +1312,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2118,7 +2106,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:K113"/>
+  <dimension ref="A3:K114"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -3515,42 +3503,24 @@
     <row r="51" customFormat="1" customHeight="1" spans="1:11">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
-      <c r="C51" s="1">
-        <v>90</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="E51" s="1">
-        <v>1</v>
-      </c>
-      <c r="F51" s="3">
-        <v>0</v>
-      </c>
-      <c r="G51" s="1">
-        <v>2</v>
-      </c>
-      <c r="H51" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="I51" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="J51" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="K51" s="1" t="s">
-        <v>144</v>
-      </c>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="1"/>
+      <c r="F51" s="3"/>
+      <c r="G51" s="3"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
+      <c r="J51" s="1"/>
+      <c r="K51" s="1"/>
     </row>
     <row r="52" customFormat="1" customHeight="1" spans="1:11">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E52" s="1">
         <v>1</v>
@@ -3562,13 +3532,13 @@
         <v>2</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="I52" s="5" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J52" s="5" t="s">
-        <v>16</v>
+        <v>141</v>
       </c>
       <c r="K52" s="1" t="s">
         <v>144</v>
@@ -3578,10 +3548,10 @@
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E53" s="1">
         <v>1</v>
@@ -3593,87 +3563,89 @@
         <v>2</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="I53" s="5" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="J53" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="54" customFormat="1" customHeight="1" spans="1:11">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1">
+        <v>94</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E54" s="1">
+        <v>1</v>
+      </c>
+      <c r="F54" s="3">
+        <v>0</v>
+      </c>
+      <c r="G54" s="1">
+        <v>2</v>
+      </c>
+      <c r="H54" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="I54" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="J54" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="55" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A55" s="1"/>
+      <c r="B55" s="1"/>
+      <c r="C55" s="1">
         <v>95</v>
       </c>
-      <c r="D54" s="1" t="s">
+      <c r="D55" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="E54" s="1">
-        <v>1</v>
-      </c>
-      <c r="F54" s="3">
-        <v>0</v>
-      </c>
-      <c r="G54" s="1">
-        <v>2</v>
-      </c>
-      <c r="H54" s="5" t="s">
+      <c r="E55" s="1">
+        <v>1</v>
+      </c>
+      <c r="F55" s="3">
+        <v>0</v>
+      </c>
+      <c r="G55" s="1">
+        <v>2</v>
+      </c>
+      <c r="H55" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="I54" s="5" t="s">
+      <c r="I55" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="J54" s="5" t="s">
+      <c r="J55" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="K54" s="1" t="s">
+      <c r="K55" s="1" t="s">
         <v>152</v>
-      </c>
-    </row>
-    <row r="55" customHeight="1" spans="1:11">
-      <c r="C55" s="1">
-        <v>96</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="E55" s="1">
-        <v>0</v>
-      </c>
-      <c r="F55" s="3">
-        <v>0</v>
-      </c>
-      <c r="G55" s="1">
-        <v>2</v>
-      </c>
-      <c r="H55" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="I55" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="J55" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="K55" s="1" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="1:11">
       <c r="C56" s="1">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="E56" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F56" s="3">
         <v>0</v>
@@ -3682,24 +3654,24 @@
         <v>2</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="I56" s="5" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="J56" s="5" t="s">
-        <v>32</v>
+        <v>157</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="1:11">
       <c r="C57" s="1">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E57" s="1">
         <v>1</v>
@@ -3711,27 +3683,27 @@
         <v>2</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I57" s="5" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="J57" s="5" t="s">
-        <v>91</v>
+        <v>32</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="1:11">
       <c r="C58" s="1">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E58" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F58" s="3">
         <v>0</v>
@@ -3740,24 +3712,24 @@
         <v>2</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="I58" s="5" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="J58" s="5" t="s">
-        <v>167</v>
+        <v>91</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="1:11">
       <c r="C59" s="1">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E59" s="1">
         <v>0</v>
@@ -3769,24 +3741,24 @@
         <v>2</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="I59" s="5" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="J59" s="5" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="1:11">
       <c r="C60" s="1">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E60" s="1">
         <v>0</v>
@@ -3801,21 +3773,21 @@
         <v>155</v>
       </c>
       <c r="I60" s="5" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="J60" s="5" t="s">
         <v>157</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="1:11">
       <c r="C61" s="1">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E61" s="1">
         <v>0</v>
@@ -3827,24 +3799,24 @@
         <v>2</v>
       </c>
       <c r="H61" s="5" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="I61" s="5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J61" s="5" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="1:11">
       <c r="C62" s="1">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E62" s="1">
         <v>0</v>
@@ -3859,21 +3831,21 @@
         <v>165</v>
       </c>
       <c r="I62" s="5" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="J62" s="5" t="s">
         <v>167</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="1:11">
       <c r="C63" s="1">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E63" s="1">
         <v>0</v>
@@ -3888,21 +3860,21 @@
         <v>165</v>
       </c>
       <c r="I63" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="J63" s="5" t="s">
         <v>167</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="1:11">
       <c r="C64" s="1">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E64" s="1">
         <v>0</v>
@@ -3917,50 +3889,50 @@
         <v>165</v>
       </c>
       <c r="I64" s="5" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="J64" s="5" t="s">
         <v>167</v>
       </c>
       <c r="K64" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="65" customHeight="1" spans="1:11">
+      <c r="C65" s="1">
+        <v>105</v>
+      </c>
+      <c r="D65" s="1" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="66" customHeight="1" spans="1:11">
-      <c r="C66" s="1">
-        <v>106</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="E66" s="1">
-        <v>1</v>
-      </c>
-      <c r="F66" s="3">
-        <v>0</v>
-      </c>
-      <c r="G66" s="1">
-        <v>1</v>
-      </c>
-      <c r="H66" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="I66" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="J66" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="K66" s="1" t="s">
-        <v>184</v>
+      <c r="E65" s="1">
+        <v>0</v>
+      </c>
+      <c r="F65" s="3">
+        <v>0</v>
+      </c>
+      <c r="G65" s="1">
+        <v>2</v>
+      </c>
+      <c r="H65" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="I65" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="J65" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="K65" s="1" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="1:11">
       <c r="C67" s="1">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="E67" s="1">
         <v>1</v>
@@ -3969,27 +3941,27 @@
         <v>0</v>
       </c>
       <c r="G67" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H67" s="5" t="s">
-        <v>64</v>
+        <v>181</v>
       </c>
       <c r="I67" s="5" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="J67" s="5" t="s">
-        <v>40</v>
+        <v>183</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>83</v>
+        <v>184</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="1:11">
       <c r="C68" s="1">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E68" s="1">
         <v>1</v>
@@ -4004,50 +3976,50 @@
         <v>64</v>
       </c>
       <c r="I68" s="5" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="J68" s="5" t="s">
         <v>40</v>
       </c>
       <c r="K68" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="69" customHeight="1" spans="1:11">
+      <c r="C69" s="1">
+        <v>108</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E69" s="1">
+        <v>1</v>
+      </c>
+      <c r="F69" s="3">
+        <v>0</v>
+      </c>
+      <c r="G69" s="1">
+        <v>2</v>
+      </c>
+      <c r="H69" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="I69" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="J69" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K69" s="1" t="s">
         <v>189</v>
-      </c>
-    </row>
-    <row r="70" customHeight="1" spans="1:11">
-      <c r="C70" s="1">
-        <v>109</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="E70" s="1">
-        <v>1</v>
-      </c>
-      <c r="F70" s="3">
-        <v>0</v>
-      </c>
-      <c r="G70" s="3">
-        <v>2</v>
-      </c>
-      <c r="H70" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="I70" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="J70" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="K70" s="1" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="1:11">
       <c r="C71" s="1">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="E71" s="1">
         <v>1</v>
@@ -4062,21 +4034,21 @@
         <v>191</v>
       </c>
       <c r="I71" s="5" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="J71" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="1:11">
       <c r="C72" s="1">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E72" s="1">
         <v>1</v>
@@ -4091,21 +4063,21 @@
         <v>191</v>
       </c>
       <c r="I72" s="5" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="J72" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="1:11">
       <c r="C73" s="1">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="E73" s="1">
         <v>1</v>
@@ -4120,21 +4092,21 @@
         <v>191</v>
       </c>
       <c r="I73" s="5" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="J73" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="1:11">
       <c r="C74" s="1">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E74" s="1">
         <v>1</v>
@@ -4149,21 +4121,21 @@
         <v>191</v>
       </c>
       <c r="I74" s="5" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="J74" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="1:11">
       <c r="C75" s="1">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E75" s="1">
         <v>1</v>
@@ -4175,80 +4147,74 @@
         <v>2</v>
       </c>
       <c r="H75" s="5" t="s">
-        <v>207</v>
+        <v>191</v>
       </c>
       <c r="I75" s="5" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="J75" s="5" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="K75" s="1" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="1:11">
       <c r="C76" s="1">
+        <v>114</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="E76" s="1">
+        <v>1</v>
+      </c>
+      <c r="F76" s="3">
+        <v>0</v>
+      </c>
+      <c r="G76" s="3">
+        <v>2</v>
+      </c>
+      <c r="H76" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="I76" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="J76" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="K76" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="77" customHeight="1" spans="1:11">
+      <c r="C77" s="1">
         <v>115</v>
       </c>
-      <c r="D76" s="1" t="s">
+      <c r="D77" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="E76" s="1">
-        <v>1</v>
-      </c>
-      <c r="F76" s="3">
-        <v>0</v>
-      </c>
-      <c r="G76" s="3">
-        <v>2</v>
-      </c>
-      <c r="H76" s="5" t="s">
+      <c r="E77" s="1">
+        <v>1</v>
+      </c>
+      <c r="F77" s="3">
+        <v>0</v>
+      </c>
+      <c r="G77" s="3">
+        <v>2</v>
+      </c>
+      <c r="H77" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="I76" s="5" t="s">
+      <c r="I77" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="J76" s="5" t="s">
+      <c r="J77" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="K76" s="1" t="s">
+      <c r="K77" s="1" t="s">
         <v>210</v>
-      </c>
-    </row>
-    <row r="78" customHeight="1" spans="1:11">
-      <c r="A78" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="C78" s="1">
-        <v>118</v>
-      </c>
-      <c r="D78" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="E78" s="1">
-        <v>1</v>
-      </c>
-      <c r="F78" s="3">
-        <v>0</v>
-      </c>
-      <c r="G78" s="3">
-        <v>2</v>
-      </c>
-      <c r="H78" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="I78" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="J78" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="K78" s="3" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="1:11">
@@ -4259,10 +4225,10 @@
         <v>212</v>
       </c>
       <c r="C79" s="1">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E79" s="1">
         <v>1</v>
@@ -4277,13 +4243,13 @@
         <v>191</v>
       </c>
       <c r="I79" s="5" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="J79" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="1:11">
@@ -4294,10 +4260,10 @@
         <v>212</v>
       </c>
       <c r="C80" s="1">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E80" s="1">
         <v>1</v>
@@ -4312,13 +4278,13 @@
         <v>191</v>
       </c>
       <c r="I80" s="5" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="J80" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K80" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="1:11">
@@ -4329,10 +4295,10 @@
         <v>212</v>
       </c>
       <c r="C81" s="1">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E81" s="1">
         <v>1</v>
@@ -4347,13 +4313,13 @@
         <v>191</v>
       </c>
       <c r="I81" s="5" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="J81" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K81" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="1:11">
@@ -4364,10 +4330,10 @@
         <v>212</v>
       </c>
       <c r="C82" s="1">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E82" s="1">
         <v>1</v>
@@ -4382,13 +4348,13 @@
         <v>191</v>
       </c>
       <c r="I82" s="5" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J82" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K82" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="1:11">
@@ -4399,10 +4365,10 @@
         <v>212</v>
       </c>
       <c r="C83" s="1">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E83" s="1">
         <v>1</v>
@@ -4417,13 +4383,13 @@
         <v>191</v>
       </c>
       <c r="I83" s="5" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="J83" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K83" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="84" customHeight="1" spans="1:11">
@@ -4434,10 +4400,10 @@
         <v>212</v>
       </c>
       <c r="C84" s="1">
-        <v>124</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>225</v>
+        <v>123</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>223</v>
       </c>
       <c r="E84" s="1">
         <v>1</v>
@@ -4452,13 +4418,13 @@
         <v>191</v>
       </c>
       <c r="I84" s="5" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="J84" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="K84" s="1" t="s">
-        <v>225</v>
+      <c r="K84" s="3" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="85" customHeight="1" spans="1:11">
@@ -4469,10 +4435,10 @@
         <v>212</v>
       </c>
       <c r="C85" s="1">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E85" s="1">
         <v>1</v>
@@ -4487,13 +4453,13 @@
         <v>191</v>
       </c>
       <c r="I85" s="5" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="J85" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K85" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="1:11">
@@ -4504,10 +4470,10 @@
         <v>212</v>
       </c>
       <c r="C86" s="1">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E86" s="1">
         <v>1</v>
@@ -4522,13 +4488,13 @@
         <v>191</v>
       </c>
       <c r="I86" s="5" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="J86" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K86" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="87" customHeight="1" spans="1:11">
@@ -4539,10 +4505,10 @@
         <v>212</v>
       </c>
       <c r="C87" s="1">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E87" s="1">
         <v>1</v>
@@ -4557,13 +4523,13 @@
         <v>191</v>
       </c>
       <c r="I87" s="5" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="J87" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K87" s="1" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="88" customHeight="1" spans="1:11">
@@ -4574,10 +4540,10 @@
         <v>212</v>
       </c>
       <c r="C88" s="1">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E88" s="1">
         <v>1</v>
@@ -4592,48 +4558,48 @@
         <v>191</v>
       </c>
       <c r="I88" s="5" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="J88" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K88" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="89" customHeight="1" spans="1:11">
+      <c r="A89" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C89" s="1">
+        <v>128</v>
+      </c>
+      <c r="D89" s="1" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="90" customHeight="1" spans="1:11">
-      <c r="A90" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="C90" s="1">
-        <v>137</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="E90" s="1">
-        <v>1</v>
-      </c>
-      <c r="F90" s="3">
-        <v>0</v>
-      </c>
-      <c r="G90" s="3">
-        <v>2</v>
-      </c>
-      <c r="H90" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="I90" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="J90" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="K90" s="1" t="s">
-        <v>235</v>
+      <c r="E89" s="1">
+        <v>1</v>
+      </c>
+      <c r="F89" s="3">
+        <v>0</v>
+      </c>
+      <c r="G89" s="3">
+        <v>2</v>
+      </c>
+      <c r="H89" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="I89" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="J89" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K89" s="1" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="1:11">
@@ -4644,10 +4610,10 @@
         <v>212</v>
       </c>
       <c r="C91" s="1">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E91" s="1">
         <v>1</v>
@@ -4659,16 +4625,16 @@
         <v>2</v>
       </c>
       <c r="H91" s="5" t="s">
-        <v>238</v>
+        <v>150</v>
       </c>
       <c r="I91" s="5" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="J91" s="5" t="s">
-        <v>240</v>
+        <v>40</v>
       </c>
       <c r="K91" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="92" customHeight="1" spans="1:11">
@@ -4679,10 +4645,10 @@
         <v>212</v>
       </c>
       <c r="C92" s="1">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="E92" s="1">
         <v>1</v>
@@ -4697,50 +4663,56 @@
         <v>238</v>
       </c>
       <c r="I92" s="5" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="J92" s="5" t="s">
         <v>240</v>
       </c>
       <c r="K92" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="93" customHeight="1" spans="1:11">
+      <c r="A93" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C93" s="1">
+        <v>139</v>
+      </c>
+      <c r="D93" s="1" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="102" customHeight="1" spans="3:11">
-      <c r="C102" s="1">
-        <v>201</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="E102" s="1">
-        <v>1</v>
-      </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
-      <c r="G102" s="3">
-        <v>2</v>
-      </c>
-      <c r="H102" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="I102" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="J102" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K102" s="1" t="s">
-        <v>246</v>
+      <c r="E93" s="1">
+        <v>1</v>
+      </c>
+      <c r="F93" s="3">
+        <v>0</v>
+      </c>
+      <c r="G93" s="3">
+        <v>2</v>
+      </c>
+      <c r="H93" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="I93" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="J93" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="K93" s="1" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="103" customHeight="1" spans="3:11">
       <c r="C103" s="1">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="E103" s="1">
         <v>1</v>
@@ -4755,21 +4727,21 @@
         <v>244</v>
       </c>
       <c r="I103" s="5" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J103" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K103" s="1" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="104" customHeight="1" spans="3:11">
       <c r="C104" s="1">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="E104" s="1">
         <v>1</v>
@@ -4784,21 +4756,21 @@
         <v>244</v>
       </c>
       <c r="I104" s="5" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="J104" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K104" s="1" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="105" customHeight="1" spans="3:11">
       <c r="C105" s="1">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="E105" s="1">
         <v>1</v>
@@ -4813,21 +4785,21 @@
         <v>244</v>
       </c>
       <c r="I105" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="J105" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K105" s="1" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
     </row>
     <row r="106" customHeight="1" spans="3:11">
       <c r="C106" s="1">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="E106" s="1">
         <v>1</v>
@@ -4842,21 +4814,21 @@
         <v>244</v>
       </c>
       <c r="I106" s="5" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="J106" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K106" s="1" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
     </row>
     <row r="107" customHeight="1" spans="3:11">
       <c r="C107" s="1">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="E107" s="1">
         <v>1</v>
@@ -4871,50 +4843,21 @@
         <v>244</v>
       </c>
       <c r="I107" s="5" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="J107" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K107" s="1" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="108" customHeight="1" spans="3:11">
-      <c r="C108" s="1">
-        <v>207</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="E108" s="1">
-        <v>1</v>
-      </c>
-      <c r="F108" s="3">
-        <v>0</v>
-      </c>
-      <c r="G108" s="3">
-        <v>2</v>
-      </c>
-      <c r="H108" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="I108" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="J108" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="K108" s="1" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
     </row>
     <row r="109" customHeight="1" spans="3:11">
       <c r="C109" s="1">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="E109" s="1">
         <v>1</v>
@@ -4926,24 +4869,24 @@
         <v>2</v>
       </c>
       <c r="H109" s="5" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="I109" s="5" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="J109" s="5" t="s">
-        <v>141</v>
+        <v>261</v>
       </c>
       <c r="K109" s="1" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
     </row>
     <row r="110" customHeight="1" spans="3:11">
       <c r="C110" s="1">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="E110" s="1">
         <v>1</v>
@@ -4955,24 +4898,24 @@
         <v>2</v>
       </c>
       <c r="H110" s="5" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="I110" s="5" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="J110" s="5" t="s">
-        <v>265</v>
+        <v>141</v>
       </c>
       <c r="K110" s="1" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
     </row>
     <row r="111" customHeight="1" spans="3:11">
       <c r="C111" s="1">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="E111" s="1">
         <v>1</v>
@@ -4984,24 +4927,24 @@
         <v>2</v>
       </c>
       <c r="H111" s="5" t="s">
-        <v>275</v>
+        <v>259</v>
       </c>
       <c r="I111" s="5" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="J111" s="5" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K111" s="1" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
     </row>
     <row r="112" customHeight="1" spans="3:11">
       <c r="C112" s="1">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="E112" s="1">
         <v>1</v>
@@ -5013,24 +4956,24 @@
         <v>2</v>
       </c>
       <c r="H112" s="5" t="s">
-        <v>244</v>
+        <v>271</v>
       </c>
       <c r="I112" s="5" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="J112" s="5" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K112" s="1" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
     </row>
     <row r="113" customHeight="1" spans="3:11">
       <c r="C113" s="1">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="E113" s="1">
         <v>1</v>
@@ -5045,13 +4988,42 @@
         <v>244</v>
       </c>
       <c r="I113" s="5" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="J113" s="5" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K113" s="1" t="s">
-        <v>279</v>
+        <v>273</v>
+      </c>
+    </row>
+    <row r="114" customHeight="1" spans="3:11">
+      <c r="C114" s="1">
+        <v>212</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="E114" s="1">
+        <v>1</v>
+      </c>
+      <c r="F114" s="3">
+        <v>0</v>
+      </c>
+      <c r="G114" s="3">
+        <v>2</v>
+      </c>
+      <c r="H114" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="I114" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="J114" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="K114" s="1" t="s">
+        <v>275</v>
       </c>
     </row>
   </sheetData>
@@ -5179,7 +5151,7 @@
         <v>1001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -5194,13 +5166,13 @@
         <v>14</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="J6" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5208,7 +5180,7 @@
         <v>1002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -5223,13 +5195,13 @@
         <v>14</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="J7" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5237,7 +5209,7 @@
         <v>1003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -5252,13 +5224,13 @@
         <v>14</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="J8" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5266,7 +5238,7 @@
         <v>1004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
@@ -5281,13 +5253,13 @@
         <v>14</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="J9" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5295,7 +5267,7 @@
         <v>1005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -5310,13 +5282,13 @@
         <v>14</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="J10" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5324,7 +5296,7 @@
         <v>1006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -5339,13 +5311,13 @@
         <v>14</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="J11" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5353,7 +5325,7 @@
         <v>1007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
@@ -5368,13 +5340,13 @@
         <v>14</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="J12" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5382,7 +5354,7 @@
         <v>1008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
@@ -5397,13 +5369,13 @@
         <v>14</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="J13" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5411,7 +5383,7 @@
         <v>1009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
@@ -5426,13 +5398,13 @@
         <v>14</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="J14" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5440,7 +5412,7 @@
         <v>1010</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
@@ -5455,13 +5427,13 @@
         <v>14</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="J15" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5469,7 +5441,7 @@
         <v>1011</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="E16" s="1">
         <v>1</v>
@@ -5484,13 +5456,13 @@
         <v>14</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="J16" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5498,7 +5470,7 @@
         <v>1012</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="E17" s="1">
         <v>1</v>
@@ -5513,13 +5485,13 @@
         <v>14</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="J17" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5527,7 +5499,7 @@
         <v>1013</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="E18" s="1">
         <v>1</v>
@@ -5542,13 +5514,13 @@
         <v>14</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="J18" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5556,7 +5528,7 @@
         <v>1014</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="E19" s="1">
         <v>1</v>
@@ -5571,13 +5543,13 @@
         <v>14</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="J19" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" ht="18" customHeight="1"/>
@@ -5586,7 +5558,7 @@
         <v>1101</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
@@ -5601,13 +5573,13 @@
         <v>14</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="J21" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5615,7 +5587,7 @@
         <v>1102</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
@@ -5630,13 +5602,13 @@
         <v>14</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="J22" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5644,7 +5616,7 @@
         <v>1103</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
@@ -5659,13 +5631,13 @@
         <v>14</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="J23" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5673,7 +5645,7 @@
         <v>1104</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
@@ -5688,13 +5660,13 @@
         <v>14</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="J24" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5702,7 +5674,7 @@
         <v>1105</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="E25" s="1">
         <v>1</v>
@@ -5717,13 +5689,13 @@
         <v>14</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="J25" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5731,7 +5703,7 @@
         <v>1106</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
@@ -5746,13 +5718,13 @@
         <v>14</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="J26" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5760,7 +5732,7 @@
         <v>1107</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="E27" s="1">
         <v>1</v>
@@ -5775,13 +5747,13 @@
         <v>14</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="J27" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5789,7 +5761,7 @@
         <v>1108</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="E28" s="1">
         <v>1</v>
@@ -5804,13 +5776,13 @@
         <v>14</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="J28" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5818,7 +5790,7 @@
         <v>1109</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
@@ -5833,13 +5805,13 @@
         <v>14</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="J29" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5847,7 +5819,7 @@
         <v>1110</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
@@ -5862,13 +5834,13 @@
         <v>14</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="J30" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5876,7 +5848,7 @@
         <v>1111</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
@@ -5891,13 +5863,13 @@
         <v>14</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="J31" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5905,7 +5877,7 @@
         <v>1112</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="E32" s="1">
         <v>1</v>
@@ -5920,13 +5892,13 @@
         <v>14</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="J32" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="368">
   <si>
     <t>_id</t>
   </si>
@@ -518,6 +518,15 @@
     <t>190007,190008,190009,190010,190011,190012</t>
   </si>
   <si>
+    <t>粉色专属自选</t>
+  </si>
+  <si>
+    <t>4,4,4,4,4,4</t>
+  </si>
+  <si>
+    <t>1201,1202,1203,1204,1205,1206</t>
+  </si>
+  <si>
     <t>暗金专属自选</t>
   </si>
   <si>
@@ -536,9 +545,6 @@
     <t>金色专属自选</t>
   </si>
   <si>
-    <t>4,4,4,4,4,4</t>
-  </si>
-  <si>
     <t>1001,1002,1003,1010,1011,1012</t>
   </si>
   <si>
@@ -836,7 +842,7 @@
     <t>45资质橙宠自选</t>
   </si>
   <si>
-    <t>50橙宠自选</t>
+    <t>50红宠自选</t>
   </si>
   <si>
     <t>7,8,9</t>
@@ -1134,6 +1140,54 @@
   </si>
   <si>
     <t>暗金12阶技能专属</t>
+  </si>
+  <si>
+    <t>战士8阶以下</t>
+  </si>
+  <si>
+    <t>12,12,12,12,12</t>
+  </si>
+  <si>
+    <t>2001,2002,2003,2004,2005</t>
+  </si>
+  <si>
+    <t>战士8阶以下技能对应的词条</t>
+  </si>
+  <si>
+    <t>战士8阶以上</t>
+  </si>
+  <si>
+    <t>12,12,12,12,12,12,12</t>
+  </si>
+  <si>
+    <t>2006,2007,2008,2009,2010,2011,2012</t>
+  </si>
+  <si>
+    <t>1,1,1,1,1,1,1</t>
+  </si>
+  <si>
+    <t>法师8阶以下</t>
+  </si>
+  <si>
+    <t>12,12,12,12,12,12,12,12</t>
+  </si>
+  <si>
+    <t>2013,2014,2015,2016,2017,2018,2019,2020</t>
+  </si>
+  <si>
+    <t>2021,2022,2023,2024,2025</t>
+  </si>
+  <si>
+    <t>道士8阶以下</t>
+  </si>
+  <si>
+    <t>2026,2027,2028,2029,2030,2031</t>
+  </si>
+  <si>
+    <t>12,12,12,12</t>
+  </si>
+  <si>
+    <t>2032,2033,2034,2034</t>
   </si>
 </sst>
 </file>
@@ -3503,15 +3557,33 @@
     <row r="51" customFormat="1" customHeight="1" spans="1:11">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
-      <c r="C51" s="1"/>
-      <c r="D51" s="1"/>
-      <c r="E51" s="1"/>
-      <c r="F51" s="3"/>
-      <c r="G51" s="3"/>
-      <c r="H51" s="1"/>
-      <c r="I51" s="1"/>
-      <c r="J51" s="1"/>
-      <c r="K51" s="1"/>
+      <c r="C51" s="1">
+        <v>89</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E51" s="1">
+        <v>1</v>
+      </c>
+      <c r="F51" s="3">
+        <v>0</v>
+      </c>
+      <c r="G51" s="1">
+        <v>2</v>
+      </c>
+      <c r="H51" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="I51" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="J51" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="K51" s="1" t="s">
+        <v>147</v>
+      </c>
     </row>
     <row r="52" customFormat="1" customHeight="1" spans="1:11">
       <c r="A52" s="1"/>
@@ -3520,7 +3592,7 @@
         <v>90</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E52" s="1">
         <v>1</v>
@@ -3532,16 +3604,16 @@
         <v>2</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I52" s="5" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="J52" s="5" t="s">
         <v>141</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="53" customFormat="1" customHeight="1" spans="1:11">
@@ -3551,7 +3623,7 @@
         <v>91</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E53" s="1">
         <v>1</v>
@@ -3566,13 +3638,13 @@
         <v>133</v>
       </c>
       <c r="I53" s="5" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="J53" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="54" customFormat="1" customHeight="1" spans="1:11">
@@ -3582,7 +3654,7 @@
         <v>94</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E54" s="1">
         <v>1</v>
@@ -3594,16 +3666,16 @@
         <v>2</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="I54" s="5" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="J54" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="55" customFormat="1" customHeight="1" spans="1:11">
@@ -3613,7 +3685,7 @@
         <v>95</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E55" s="1">
         <v>1</v>
@@ -3625,16 +3697,16 @@
         <v>2</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I55" s="5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="J55" s="5" t="s">
         <v>91</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="1:11">
@@ -3642,7 +3714,7 @@
         <v>96</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E56" s="1">
         <v>0</v>
@@ -3654,16 +3726,16 @@
         <v>2</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="I56" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="J56" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="K56" s="1" t="s">
         <v>156</v>
-      </c>
-      <c r="J56" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="K56" s="1" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="1:11">
@@ -3671,7 +3743,7 @@
         <v>97</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E57" s="1">
         <v>1</v>
@@ -3683,16 +3755,16 @@
         <v>2</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="I57" s="5" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="J57" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="1:11">
@@ -3700,7 +3772,7 @@
         <v>98</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E58" s="1">
         <v>1</v>
@@ -3712,16 +3784,16 @@
         <v>2</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I58" s="5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J58" s="5" t="s">
         <v>91</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="1:11">
@@ -3729,7 +3801,7 @@
         <v>99</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E59" s="1">
         <v>0</v>
@@ -3741,16 +3813,16 @@
         <v>2</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="I59" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="J59" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="K59" s="1" t="s">
         <v>166</v>
-      </c>
-      <c r="J59" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="K59" s="1" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="1:11">
@@ -3758,7 +3830,7 @@
         <v>100</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E60" s="1">
         <v>0</v>
@@ -3770,16 +3842,16 @@
         <v>2</v>
       </c>
       <c r="H60" s="5" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="I60" s="5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="J60" s="5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="1:11">
@@ -3787,7 +3859,7 @@
         <v>101</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E61" s="1">
         <v>0</v>
@@ -3799,16 +3871,16 @@
         <v>2</v>
       </c>
       <c r="H61" s="5" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="I61" s="5" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J61" s="5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="1:11">
@@ -3816,7 +3888,7 @@
         <v>102</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E62" s="1">
         <v>0</v>
@@ -3828,16 +3900,16 @@
         <v>2</v>
       </c>
       <c r="H62" s="5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="I62" s="5" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="J62" s="5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="1:11">
@@ -3845,7 +3917,7 @@
         <v>103</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E63" s="1">
         <v>0</v>
@@ -3857,16 +3929,16 @@
         <v>2</v>
       </c>
       <c r="H63" s="5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="I63" s="5" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="J63" s="5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="1:11">
@@ -3874,7 +3946,7 @@
         <v>104</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E64" s="1">
         <v>0</v>
@@ -3886,16 +3958,16 @@
         <v>2</v>
       </c>
       <c r="H64" s="5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="I64" s="5" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="J64" s="5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="K64" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="1:11">
@@ -3903,7 +3975,7 @@
         <v>105</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E65" s="1">
         <v>0</v>
@@ -3915,16 +3987,16 @@
         <v>2</v>
       </c>
       <c r="H65" s="5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="I65" s="5" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="J65" s="5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="K65" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="1:11">
@@ -3932,7 +4004,7 @@
         <v>106</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E67" s="1">
         <v>1</v>
@@ -3944,16 +4016,16 @@
         <v>1</v>
       </c>
       <c r="H67" s="5" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="I67" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="J67" s="5" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="1:11">
@@ -3961,7 +4033,7 @@
         <v>107</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E68" s="1">
         <v>1</v>
@@ -3976,7 +4048,7 @@
         <v>64</v>
       </c>
       <c r="I68" s="5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="J68" s="5" t="s">
         <v>40</v>
@@ -3990,7 +4062,7 @@
         <v>108</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E69" s="1">
         <v>1</v>
@@ -4005,13 +4077,13 @@
         <v>64</v>
       </c>
       <c r="I69" s="5" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="J69" s="5" t="s">
         <v>40</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="1:11">
@@ -4019,7 +4091,7 @@
         <v>109</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E71" s="1">
         <v>1</v>
@@ -4031,16 +4103,16 @@
         <v>2</v>
       </c>
       <c r="H71" s="5" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I71" s="5" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="J71" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="1:11">
@@ -4048,7 +4120,7 @@
         <v>110</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E72" s="1">
         <v>1</v>
@@ -4060,16 +4132,16 @@
         <v>2</v>
       </c>
       <c r="H72" s="5" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I72" s="5" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="J72" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="1:11">
@@ -4077,7 +4149,7 @@
         <v>111</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E73" s="1">
         <v>1</v>
@@ -4089,16 +4161,16 @@
         <v>2</v>
       </c>
       <c r="H73" s="5" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I73" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="J73" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="1:11">
@@ -4106,7 +4178,7 @@
         <v>112</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E74" s="1">
         <v>1</v>
@@ -4118,16 +4190,16 @@
         <v>2</v>
       </c>
       <c r="H74" s="5" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I74" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="J74" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="1:11">
@@ -4135,7 +4207,7 @@
         <v>113</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E75" s="1">
         <v>1</v>
@@ -4147,16 +4219,16 @@
         <v>2</v>
       </c>
       <c r="H75" s="5" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I75" s="5" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="J75" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K75" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="1:11">
@@ -4164,7 +4236,7 @@
         <v>114</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E76" s="1">
         <v>1</v>
@@ -4176,16 +4248,16 @@
         <v>2</v>
       </c>
       <c r="H76" s="5" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I76" s="5" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="J76" s="5" t="s">
         <v>91</v>
       </c>
       <c r="K76" s="1" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="1:11">
@@ -4193,7 +4265,7 @@
         <v>115</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E77" s="1">
         <v>1</v>
@@ -4205,30 +4277,30 @@
         <v>2</v>
       </c>
       <c r="H77" s="5" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="I77" s="5" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="J77" s="5" t="s">
         <v>40</v>
       </c>
       <c r="K77" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="1:11">
       <c r="A79" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C79" s="1">
         <v>118</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E79" s="1">
         <v>1</v>
@@ -4240,30 +4312,30 @@
         <v>2</v>
       </c>
       <c r="H79" s="5" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I79" s="5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="J79" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="1:11">
       <c r="A80" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C80" s="1">
         <v>119</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E80" s="1">
         <v>1</v>
@@ -4275,30 +4347,30 @@
         <v>2</v>
       </c>
       <c r="H80" s="5" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I80" s="5" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="J80" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K80" s="3" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="1:11">
       <c r="A81" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C81" s="1">
         <v>120</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E81" s="1">
         <v>1</v>
@@ -4310,30 +4382,30 @@
         <v>2</v>
       </c>
       <c r="H81" s="5" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I81" s="5" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="J81" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K81" s="3" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="1:11">
       <c r="A82" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C82" s="1">
         <v>121</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E82" s="1">
         <v>1</v>
@@ -4345,30 +4417,30 @@
         <v>2</v>
       </c>
       <c r="H82" s="5" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I82" s="5" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="J82" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K82" s="3" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="1:11">
       <c r="A83" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C83" s="1">
         <v>122</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E83" s="1">
         <v>1</v>
@@ -4380,30 +4452,30 @@
         <v>2</v>
       </c>
       <c r="H83" s="5" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I83" s="5" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="J83" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K83" s="3" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="84" customHeight="1" spans="1:11">
       <c r="A84" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C84" s="1">
         <v>123</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E84" s="1">
         <v>1</v>
@@ -4415,30 +4487,30 @@
         <v>2</v>
       </c>
       <c r="H84" s="5" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I84" s="5" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="J84" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K84" s="3" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="85" customHeight="1" spans="1:11">
       <c r="A85" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C85" s="1">
         <v>124</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E85" s="1">
         <v>1</v>
@@ -4450,30 +4522,30 @@
         <v>2</v>
       </c>
       <c r="H85" s="5" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I85" s="5" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="J85" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K85" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="1:11">
       <c r="A86" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C86" s="1">
         <v>125</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E86" s="1">
         <v>1</v>
@@ -4485,30 +4557,30 @@
         <v>2</v>
       </c>
       <c r="H86" s="5" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I86" s="5" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="J86" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K86" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="87" customHeight="1" spans="1:11">
       <c r="A87" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C87" s="1">
         <v>126</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E87" s="1">
         <v>1</v>
@@ -4520,30 +4592,30 @@
         <v>2</v>
       </c>
       <c r="H87" s="5" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I87" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="J87" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K87" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="88" customHeight="1" spans="1:11">
       <c r="A88" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C88" s="1">
         <v>127</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E88" s="1">
         <v>1</v>
@@ -4555,30 +4627,30 @@
         <v>2</v>
       </c>
       <c r="H88" s="5" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I88" s="5" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="J88" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K88" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="89" customHeight="1" spans="1:11">
       <c r="A89" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C89" s="1">
         <v>128</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E89" s="1">
         <v>1</v>
@@ -4590,30 +4662,30 @@
         <v>2</v>
       </c>
       <c r="H89" s="5" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I89" s="5" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="J89" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K89" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="1:11">
       <c r="A91" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C91" s="1">
         <v>137</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E91" s="1">
         <v>1</v>
@@ -4625,30 +4697,30 @@
         <v>2</v>
       </c>
       <c r="H91" s="5" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="I91" s="5" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="J91" s="5" t="s">
         <v>40</v>
       </c>
       <c r="K91" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="92" customHeight="1" spans="1:11">
       <c r="A92" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C92" s="1">
         <v>138</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E92" s="1">
         <v>1</v>
@@ -4660,30 +4732,30 @@
         <v>2</v>
       </c>
       <c r="H92" s="5" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="I92" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="J92" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="K92" s="1" t="s">
         <v>239</v>
-      </c>
-      <c r="J92" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="K92" s="1" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="93" customHeight="1" spans="1:11">
       <c r="A93" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C93" s="1">
         <v>139</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E93" s="1">
         <v>1</v>
@@ -4695,16 +4767,16 @@
         <v>2</v>
       </c>
       <c r="H93" s="5" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="I93" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="J93" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="J93" s="5" t="s">
-        <v>240</v>
-      </c>
       <c r="K93" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="103" customHeight="1" spans="3:11">
@@ -4712,7 +4784,7 @@
         <v>201</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E103" s="1">
         <v>1</v>
@@ -4724,16 +4796,16 @@
         <v>2</v>
       </c>
       <c r="H103" s="5" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="I103" s="5" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="J103" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K103" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="104" customHeight="1" spans="3:11">
@@ -4741,7 +4813,7 @@
         <v>202</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E104" s="1">
         <v>1</v>
@@ -4753,16 +4825,16 @@
         <v>2</v>
       </c>
       <c r="H104" s="5" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="I104" s="5" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="J104" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K104" s="1" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="105" customHeight="1" spans="3:11">
@@ -4770,7 +4842,7 @@
         <v>203</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E105" s="1">
         <v>1</v>
@@ -4782,16 +4854,16 @@
         <v>2</v>
       </c>
       <c r="H105" s="5" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="I105" s="5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="J105" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K105" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="106" customHeight="1" spans="3:11">
@@ -4799,7 +4871,7 @@
         <v>204</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E106" s="1">
         <v>1</v>
@@ -4811,16 +4883,16 @@
         <v>2</v>
       </c>
       <c r="H106" s="5" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="I106" s="5" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="J106" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K106" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="107" customHeight="1" spans="3:11">
@@ -4828,7 +4900,7 @@
         <v>205</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E107" s="1">
         <v>1</v>
@@ -4840,16 +4912,16 @@
         <v>2</v>
       </c>
       <c r="H107" s="5" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="I107" s="5" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="J107" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K107" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="109" customHeight="1" spans="3:11">
@@ -4857,7 +4929,7 @@
         <v>207</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E109" s="1">
         <v>1</v>
@@ -4869,16 +4941,16 @@
         <v>2</v>
       </c>
       <c r="H109" s="5" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="I109" s="5" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="J109" s="5" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="K109" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="110" customHeight="1" spans="3:11">
@@ -4886,7 +4958,7 @@
         <v>208</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E110" s="1">
         <v>1</v>
@@ -4898,16 +4970,16 @@
         <v>2</v>
       </c>
       <c r="H110" s="5" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="I110" s="5" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="J110" s="5" t="s">
         <v>141</v>
       </c>
       <c r="K110" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="111" customHeight="1" spans="3:11">
@@ -4915,7 +4987,7 @@
         <v>209</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E111" s="1">
         <v>1</v>
@@ -4927,16 +4999,16 @@
         <v>2</v>
       </c>
       <c r="H111" s="5" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="I111" s="5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="J111" s="5" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="K111" s="1" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="112" customHeight="1" spans="3:11">
@@ -4944,7 +5016,7 @@
         <v>210</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E112" s="1">
         <v>1</v>
@@ -4956,16 +5028,16 @@
         <v>2</v>
       </c>
       <c r="H112" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="I112" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="J112" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="K112" s="1" t="s">
         <v>271</v>
-      </c>
-      <c r="I112" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="J112" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="K112" s="1" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="113" customHeight="1" spans="3:11">
@@ -4973,7 +5045,7 @@
         <v>211</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E113" s="1">
         <v>1</v>
@@ -4985,16 +5057,16 @@
         <v>2</v>
       </c>
       <c r="H113" s="5" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="I113" s="5" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="J113" s="5" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="K113" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="114" customHeight="1" spans="3:11">
@@ -5002,7 +5074,7 @@
         <v>212</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E114" s="1">
         <v>1</v>
@@ -5014,16 +5086,16 @@
         <v>2</v>
       </c>
       <c r="H114" s="5" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="I114" s="5" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="J114" s="5" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="K114" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
   </sheetData>
@@ -5151,7 +5223,7 @@
         <v>1001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -5166,13 +5238,13 @@
         <v>14</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J6" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5180,7 +5252,7 @@
         <v>1002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -5195,13 +5267,13 @@
         <v>14</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="J7" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5209,7 +5281,7 @@
         <v>1003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -5224,13 +5296,13 @@
         <v>14</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="J8" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5238,7 +5310,7 @@
         <v>1004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
@@ -5253,13 +5325,13 @@
         <v>14</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="J9" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5267,7 +5339,7 @@
         <v>1005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -5282,13 +5354,13 @@
         <v>14</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="J10" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5296,7 +5368,7 @@
         <v>1006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -5311,13 +5383,13 @@
         <v>14</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="J11" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5325,7 +5397,7 @@
         <v>1007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
@@ -5340,13 +5412,13 @@
         <v>14</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="J12" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5354,7 +5426,7 @@
         <v>1008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
@@ -5369,13 +5441,13 @@
         <v>14</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="J13" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5383,7 +5455,7 @@
         <v>1009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
@@ -5398,13 +5470,13 @@
         <v>14</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="J14" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5412,7 +5484,7 @@
         <v>1010</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
@@ -5427,13 +5499,13 @@
         <v>14</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="J15" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5441,7 +5513,7 @@
         <v>1011</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E16" s="1">
         <v>1</v>
@@ -5456,13 +5528,13 @@
         <v>14</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="J16" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5470,7 +5542,7 @@
         <v>1012</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E17" s="1">
         <v>1</v>
@@ -5485,13 +5557,13 @@
         <v>14</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="J17" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5499,7 +5571,7 @@
         <v>1013</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E18" s="1">
         <v>1</v>
@@ -5514,13 +5586,13 @@
         <v>14</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="J18" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5528,7 +5600,7 @@
         <v>1014</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="E19" s="1">
         <v>1</v>
@@ -5543,13 +5615,13 @@
         <v>14</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="J19" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" ht="18" customHeight="1"/>
@@ -5558,7 +5630,7 @@
         <v>1101</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
@@ -5573,13 +5645,13 @@
         <v>14</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="J21" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5587,7 +5659,7 @@
         <v>1102</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
@@ -5602,13 +5674,13 @@
         <v>14</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="J22" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5616,7 +5688,7 @@
         <v>1103</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
@@ -5631,13 +5703,13 @@
         <v>14</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="J23" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5645,7 +5717,7 @@
         <v>1104</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
@@ -5660,13 +5732,13 @@
         <v>14</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="J24" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5674,7 +5746,7 @@
         <v>1105</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E25" s="1">
         <v>1</v>
@@ -5689,13 +5761,13 @@
         <v>14</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="J25" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5703,7 +5775,7 @@
         <v>1106</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
@@ -5718,13 +5790,13 @@
         <v>14</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="J26" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5732,7 +5804,7 @@
         <v>1107</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="E27" s="1">
         <v>1</v>
@@ -5747,13 +5819,13 @@
         <v>14</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="J27" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5761,7 +5833,7 @@
         <v>1108</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E28" s="1">
         <v>1</v>
@@ -5776,13 +5848,13 @@
         <v>14</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="J28" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5790,7 +5862,7 @@
         <v>1109</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
@@ -5805,13 +5877,13 @@
         <v>14</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="J29" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5819,7 +5891,7 @@
         <v>1110</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
@@ -5834,13 +5906,13 @@
         <v>14</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="J30" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5848,7 +5920,7 @@
         <v>1111</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
@@ -5863,13 +5935,13 @@
         <v>14</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="J31" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5877,7 +5949,7 @@
         <v>1112</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E32" s="1">
         <v>1</v>
@@ -5892,13 +5964,13 @@
         <v>14</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="J32" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
@@ -5914,31 +5986,183 @@
       <c r="K33"/>
       <c r="L33"/>
     </row>
+    <row r="34" spans="2:12">
+      <c r="C34" s="1">
+        <v>1201</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="E34" s="1">
+        <v>1</v>
+      </c>
+      <c r="F34" s="3">
+        <v>0</v>
+      </c>
+      <c r="G34" s="1">
+        <v>2</v>
+      </c>
+      <c r="H34" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="J34" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>355</v>
+      </c>
+    </row>
     <row r="35" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
       <c r="B35"/>
-      <c r="C35"/>
-      <c r="D35"/>
-      <c r="E35"/>
-      <c r="F35"/>
-      <c r="G35"/>
-      <c r="H35"/>
-      <c r="I35"/>
-      <c r="J35"/>
-      <c r="K35"/>
+      <c r="C35" s="1">
+        <v>1202</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="E35" s="1">
+        <v>1</v>
+      </c>
+      <c r="F35" s="3">
+        <v>0</v>
+      </c>
+      <c r="G35" s="1">
+        <v>2</v>
+      </c>
+      <c r="H35" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="I35" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="J35" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>356</v>
+      </c>
       <c r="L35"/>
     </row>
     <row r="36" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
       <c r="B36"/>
-      <c r="C36"/>
-      <c r="D36"/>
-      <c r="E36"/>
-      <c r="F36"/>
-      <c r="G36"/>
-      <c r="H36"/>
-      <c r="I36"/>
-      <c r="J36"/>
-      <c r="K36"/>
+      <c r="C36" s="1">
+        <v>1203</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="E36" s="1">
+        <v>1</v>
+      </c>
+      <c r="F36" s="3">
+        <v>0</v>
+      </c>
+      <c r="G36" s="1">
+        <v>2</v>
+      </c>
+      <c r="H36" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="I36" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="J36" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>360</v>
+      </c>
       <c r="L36"/>
+    </row>
+    <row r="37" spans="2:12">
+      <c r="C37" s="1">
+        <v>1204</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="E37" s="1">
+        <v>1</v>
+      </c>
+      <c r="F37" s="3">
+        <v>0</v>
+      </c>
+      <c r="G37" s="1">
+        <v>2</v>
+      </c>
+      <c r="H37" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="I37" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="J37" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="38" spans="2:12">
+      <c r="C38" s="1">
+        <v>1205</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="E38" s="1">
+        <v>1</v>
+      </c>
+      <c r="F38" s="3">
+        <v>0</v>
+      </c>
+      <c r="G38" s="1">
+        <v>2</v>
+      </c>
+      <c r="H38" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I38" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="J38" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="39" spans="2:12">
+      <c r="C39" s="1">
+        <v>1206</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="E39" s="1">
+        <v>1</v>
+      </c>
+      <c r="F39" s="3">
+        <v>0</v>
+      </c>
+      <c r="G39" s="1">
+        <v>2</v>
+      </c>
+      <c r="H39" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="I39" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="J39" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>364</v>
+      </c>
     </row>
     <row r="47" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
       <c r="B47"/>

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="375">
   <si>
     <t>_id</t>
   </si>
@@ -1166,6 +1166,9 @@
     <t>1,1,1,1,1,1,1</t>
   </si>
   <si>
+    <t>战士8阶以上技能对应的词条</t>
+  </si>
+  <si>
     <t>法师8阶以下</t>
   </si>
   <si>
@@ -1175,19 +1178,37 @@
     <t>2013,2014,2015,2016,2017,2018,2019,2020</t>
   </si>
   <si>
+    <t>法师8阶以下技能对应的词条</t>
+  </si>
+  <si>
+    <t>法师8阶以上</t>
+  </si>
+  <si>
     <t>2021,2022,2023,2024,2025</t>
   </si>
   <si>
+    <t>法师8阶以上技能对应的词条</t>
+  </si>
+  <si>
     <t>道士8阶以下</t>
   </si>
   <si>
     <t>2026,2027,2028,2029,2030,2031</t>
   </si>
   <si>
+    <t>道士8阶以下技能对应的词条</t>
+  </si>
+  <si>
+    <t>道士8阶以上</t>
+  </si>
+  <si>
     <t>12,12,12,12</t>
   </si>
   <si>
     <t>2032,2033,2034,2034</t>
+  </si>
+  <si>
+    <t>道士8阶以上技能对应的词条</t>
   </si>
 </sst>
 </file>
@@ -6042,7 +6063,7 @@
         <v>359</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="L35"/>
     </row>
@@ -6052,7 +6073,7 @@
         <v>1203</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E36" s="1">
         <v>1</v>
@@ -6064,16 +6085,16 @@
         <v>2</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="J36" s="5" t="s">
         <v>40</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="L36"/>
     </row>
@@ -6082,7 +6103,7 @@
         <v>1204</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="E37" s="1">
         <v>1</v>
@@ -6097,13 +6118,13 @@
         <v>353</v>
       </c>
       <c r="I37" s="5" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="J37" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
     </row>
     <row r="38" spans="2:12">
@@ -6111,7 +6132,7 @@
         <v>1205</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="E38" s="1">
         <v>1</v>
@@ -6126,13 +6147,13 @@
         <v>14</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="J38" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
     </row>
     <row r="39" spans="2:12">
@@ -6140,7 +6161,7 @@
         <v>1206</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="E39" s="1">
         <v>1</v>
@@ -6152,16 +6173,16 @@
         <v>2</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="I39" s="5" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="J39" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -1151,7 +1151,7 @@
     <t>2001,2002,2003,2004,2005</t>
   </si>
   <si>
-    <t>战士8阶以下技能对应的词条</t>
+    <t>流光，武神盾，武力精通，战吼 对应的词条</t>
   </si>
   <si>
     <t>战士8阶以上</t>
@@ -1166,7 +1166,7 @@
     <t>1,1,1,1,1,1,1</t>
   </si>
   <si>
-    <t>战士8阶以上技能对应的词条</t>
+    <t>裂地斩，战士之魂，剑二十三 对应的词条</t>
   </si>
   <si>
     <t>法师8阶以下</t>
@@ -1178,7 +1178,7 @@
     <t>2013,2014,2015,2016,2017,2018,2019,2020</t>
   </si>
   <si>
-    <t>法师8阶以下技能对应的词条</t>
+    <t>落雷术，法力盾，法术精通，冰爆术，心灵传送 对应的词条</t>
   </si>
   <si>
     <t>法师8阶以上</t>
@@ -1187,7 +1187,7 @@
     <t>2021,2022,2023,2024,2025</t>
   </si>
   <si>
-    <t>法师8阶以上技能对应的词条</t>
+    <t>分身术，法师之魂，魔尊附体 对应的词条</t>
   </si>
   <si>
     <t>道士8阶以下</t>
@@ -1196,7 +1196,7 @@
     <t>2026,2027,2028,2029,2030,2031</t>
   </si>
   <si>
-    <t>道士8阶以下技能对应的词条</t>
+    <t>驱魔符，道力盾，道力精通，隐身道法 对应的词条</t>
   </si>
   <si>
     <t>道士8阶以上</t>
@@ -1208,7 +1208,7 @@
     <t>2032,2033,2034,2034</t>
   </si>
   <si>
-    <t>道士8阶以上技能对应的词条</t>
+    <t>无极道体，道士之魂，召唤白虎 对应的词条</t>
   </si>
 </sst>
 </file>
@@ -1221,7 +1221,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1234,6 +1234,13 @@
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -1722,16 +1729,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1740,122 +1744,126 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -2187,7 +2195,7 @@
     <col min="1" max="3" width="9" style="1"/>
     <col min="4" max="4" width="16.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="14.1666666666667" style="1" customWidth="1"/>
-    <col min="6" max="7" width="13.0833333333333" style="3" customWidth="1"/>
+    <col min="6" max="7" width="13.0833333333333" style="4" customWidth="1"/>
     <col min="8" max="8" width="31.25" style="1" customWidth="1"/>
     <col min="9" max="9" width="72.0166666666667" style="1" customWidth="1"/>
     <col min="10" max="10" width="26.875" style="1" customWidth="1"/>
@@ -2196,89 +2204,89 @@
   </cols>
   <sheetData>
     <row r="3" customHeight="1" spans="3:11">
-      <c r="C3" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="2" t="s">
+      <c r="C3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="3:11">
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="2" t="s">
+      <c r="D4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K4" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="3:11">
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="I5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="J5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="K5" s="3" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2298,13 +2306,13 @@
       <c r="G6" s="1">
         <v>2</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="I6" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="J6" s="5" t="s">
+      <c r="J6" s="6" t="s">
         <v>16</v>
       </c>
       <c r="K6" s="1" t="s">
@@ -2327,13 +2335,13 @@
       <c r="G7" s="1">
         <v>2</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="H7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="I7" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="J7" s="5" t="s">
+      <c r="J7" s="6" t="s">
         <v>16</v>
       </c>
       <c r="K7" s="1" t="s">
@@ -2356,13 +2364,13 @@
       <c r="G8" s="1">
         <v>2</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="H8" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="I8" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="J8" s="5" t="s">
+      <c r="J8" s="6" t="s">
         <v>16</v>
       </c>
       <c r="K8" s="1" t="s">
@@ -2385,13 +2393,13 @@
       <c r="G9" s="1">
         <v>2</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="H9" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="I9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="J9" s="5" t="s">
+      <c r="J9" s="6" t="s">
         <v>16</v>
       </c>
       <c r="K9" s="1" t="s">
@@ -2414,13 +2422,13 @@
       <c r="G10" s="1">
         <v>2</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="H10" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I10" s="5" t="s">
+      <c r="I10" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="J10" s="5" t="s">
+      <c r="J10" s="6" t="s">
         <v>16</v>
       </c>
       <c r="K10" s="1" t="s">
@@ -2443,13 +2451,13 @@
       <c r="G11" s="1">
         <v>2</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="H11" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I11" s="5" t="s">
+      <c r="I11" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J11" s="5" t="s">
+      <c r="J11" s="6" t="s">
         <v>16</v>
       </c>
       <c r="K11" s="1" t="s">
@@ -2472,13 +2480,13 @@
       <c r="G12" s="1">
         <v>2</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="H12" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I12" s="5" t="s">
+      <c r="I12" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="J12" s="5" t="s">
+      <c r="J12" s="6" t="s">
         <v>16</v>
       </c>
       <c r="K12" s="1" t="s">
@@ -2495,19 +2503,19 @@
       <c r="E13" s="1">
         <v>1</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="4">
         <v>0</v>
       </c>
       <c r="G13" s="1">
         <v>2</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="H13" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="I13" s="5" t="s">
+      <c r="I13" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="J13" s="5" t="s">
+      <c r="J13" s="6" t="s">
         <v>32</v>
       </c>
       <c r="K13" s="1" t="s">
@@ -2524,19 +2532,19 @@
       <c r="E14" s="1">
         <v>1</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="4">
         <v>0</v>
       </c>
       <c r="G14" s="1">
         <v>2</v>
       </c>
-      <c r="H14" s="5" t="s">
+      <c r="H14" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="I14" s="5" t="s">
+      <c r="I14" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="J14" s="5" t="s">
+      <c r="J14" s="6" t="s">
         <v>32</v>
       </c>
       <c r="K14" s="1" t="s">
@@ -2553,19 +2561,19 @@
       <c r="E15" s="1">
         <v>0</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="4">
         <v>0</v>
       </c>
       <c r="G15" s="1">
         <v>1</v>
       </c>
-      <c r="H15" s="5" t="s">
+      <c r="H15" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="I15" s="5" t="s">
+      <c r="I15" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="J15" s="5" t="s">
+      <c r="J15" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K15" s="1" t="s">
@@ -2582,19 +2590,19 @@
       <c r="E16" s="1">
         <v>0</v>
       </c>
-      <c r="F16" s="3">
+      <c r="F16" s="4">
         <v>0</v>
       </c>
       <c r="G16" s="1">
         <v>1</v>
       </c>
-      <c r="H16" s="5" t="s">
+      <c r="H16" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="I16" s="5" t="s">
+      <c r="I16" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="J16" s="5" t="s">
+      <c r="J16" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K16" s="1" t="s">
@@ -2611,19 +2619,19 @@
       <c r="E17" s="1">
         <v>0</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="4">
         <v>0</v>
       </c>
       <c r="G17" s="1">
         <v>1</v>
       </c>
-      <c r="H17" s="5" t="s">
+      <c r="H17" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="I17" s="5" t="s">
+      <c r="I17" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="J17" s="5" t="s">
+      <c r="J17" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K17" s="1" t="s">
@@ -2646,13 +2654,13 @@
       <c r="G18" s="1">
         <v>2</v>
       </c>
-      <c r="H18" s="5" t="s">
+      <c r="H18" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I18" s="5" t="s">
+      <c r="I18" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="J18" s="5" t="s">
+      <c r="J18" s="6" t="s">
         <v>16</v>
       </c>
       <c r="K18" s="1" t="s">
@@ -2669,19 +2677,19 @@
       <c r="E19" s="1">
         <v>1</v>
       </c>
-      <c r="F19" s="3">
+      <c r="F19" s="4">
         <v>0</v>
       </c>
       <c r="G19" s="1">
         <v>2</v>
       </c>
-      <c r="H19" s="5" t="s">
+      <c r="H19" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I19" s="5" t="s">
+      <c r="I19" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="J19" s="5" t="s">
+      <c r="J19" s="6" t="s">
         <v>16</v>
       </c>
       <c r="K19" s="1" t="s">
@@ -2698,19 +2706,19 @@
       <c r="E20" s="1">
         <v>0</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="4">
         <v>0</v>
       </c>
       <c r="G20" s="1">
         <v>1</v>
       </c>
-      <c r="H20" s="5" t="s">
+      <c r="H20" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="I20" s="5" t="s">
+      <c r="I20" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="J20" s="5" t="s">
+      <c r="J20" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K20" s="1" t="s">
@@ -2727,19 +2735,19 @@
       <c r="E21" s="1">
         <v>0</v>
       </c>
-      <c r="F21" s="3">
+      <c r="F21" s="4">
         <v>0</v>
       </c>
       <c r="G21" s="1">
         <v>1</v>
       </c>
-      <c r="H21" s="5" t="s">
+      <c r="H21" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="I21" s="5" t="s">
+      <c r="I21" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="J21" s="5" t="s">
+      <c r="J21" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K21" s="1" t="s">
@@ -2756,19 +2764,19 @@
       <c r="E22" s="1">
         <v>0</v>
       </c>
-      <c r="F22" s="3">
+      <c r="F22" s="4">
         <v>0</v>
       </c>
       <c r="G22" s="1">
         <v>1</v>
       </c>
-      <c r="H22" s="5" t="s">
+      <c r="H22" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="I22" s="5" t="s">
+      <c r="I22" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="J22" s="5" t="s">
+      <c r="J22" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K22" s="1" t="s">
@@ -2785,19 +2793,19 @@
       <c r="E23" s="1">
         <v>1</v>
       </c>
-      <c r="F23" s="3">
+      <c r="F23" s="4">
         <v>0</v>
       </c>
       <c r="G23" s="1">
         <v>2</v>
       </c>
-      <c r="H23" s="5" t="s">
+      <c r="H23" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="I23" s="5" t="s">
+      <c r="I23" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="J23" s="5" t="s">
+      <c r="J23" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K23" s="1" t="s">
@@ -2814,19 +2822,19 @@
       <c r="E24" s="1">
         <v>1</v>
       </c>
-      <c r="F24" s="3">
+      <c r="F24" s="4">
         <v>0</v>
       </c>
       <c r="G24" s="1">
         <v>2</v>
       </c>
-      <c r="H24" s="5" t="s">
+      <c r="H24" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="I24" s="5" t="s">
+      <c r="I24" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="J24" s="5" t="s">
+      <c r="J24" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K24" s="1" t="s">
@@ -2843,19 +2851,19 @@
       <c r="E25" s="1">
         <v>1</v>
       </c>
-      <c r="F25" s="3">
+      <c r="F25" s="4">
         <v>0</v>
       </c>
       <c r="G25" s="1">
         <v>2</v>
       </c>
-      <c r="H25" s="5" t="s">
+      <c r="H25" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="I25" s="5" t="s">
+      <c r="I25" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="J25" s="5" t="s">
+      <c r="J25" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K25" s="1" t="s">
@@ -2878,13 +2886,13 @@
       <c r="G26" s="1">
         <v>2</v>
       </c>
-      <c r="H26" s="5" t="s">
+      <c r="H26" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="I26" s="5" t="s">
+      <c r="I26" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J26" s="5" t="s">
+      <c r="J26" s="6" t="s">
         <v>32</v>
       </c>
       <c r="K26" s="1" t="s">
@@ -2907,13 +2915,13 @@
       <c r="G27" s="1">
         <v>2</v>
       </c>
-      <c r="H27" s="5" t="s">
+      <c r="H27" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="I27" s="5" t="s">
+      <c r="I27" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="J27" s="5" t="s">
+      <c r="J27" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K27" s="1" t="s">
@@ -2936,13 +2944,13 @@
       <c r="G28" s="1">
         <v>2</v>
       </c>
-      <c r="H28" s="5" t="s">
+      <c r="H28" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="I28" s="5" t="s">
+      <c r="I28" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="J28" s="5" t="s">
+      <c r="J28" s="6" t="s">
         <v>82</v>
       </c>
       <c r="K28" s="1" t="s">
@@ -2959,19 +2967,19 @@
       <c r="E29" s="1">
         <v>1</v>
       </c>
-      <c r="F29" s="3">
+      <c r="F29" s="4">
         <v>0</v>
       </c>
       <c r="G29" s="1">
         <v>2</v>
       </c>
-      <c r="H29" s="5" t="s">
+      <c r="H29" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="I29" s="5" t="s">
+      <c r="I29" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="J29" s="5" t="s">
+      <c r="J29" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K29" s="1" t="s">
@@ -2988,19 +2996,19 @@
       <c r="E30" s="1">
         <v>1</v>
       </c>
-      <c r="F30" s="3">
+      <c r="F30" s="4">
         <v>0</v>
       </c>
       <c r="G30" s="1">
         <v>2</v>
       </c>
-      <c r="H30" s="5" t="s">
+      <c r="H30" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="I30" s="5" t="s">
+      <c r="I30" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="J30" s="5" t="s">
+      <c r="J30" s="6" t="s">
         <v>87</v>
       </c>
       <c r="K30" s="1" t="s">
@@ -3017,19 +3025,19 @@
       <c r="E31" s="1">
         <v>1</v>
       </c>
-      <c r="F31" s="3">
+      <c r="F31" s="4">
         <v>0</v>
       </c>
       <c r="G31" s="1">
         <v>2</v>
       </c>
-      <c r="H31" s="5" t="s">
+      <c r="H31" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="I31" s="5" t="s">
+      <c r="I31" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="J31" s="5" t="s">
+      <c r="J31" s="6" t="s">
         <v>91</v>
       </c>
       <c r="K31" s="1" t="s">
@@ -3046,19 +3054,19 @@
       <c r="E32" s="1">
         <v>1</v>
       </c>
-      <c r="F32" s="3">
+      <c r="F32" s="4">
         <v>0</v>
       </c>
       <c r="G32" s="1">
         <v>2</v>
       </c>
-      <c r="H32" s="5" t="s">
+      <c r="H32" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="I32" s="5" t="s">
+      <c r="I32" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="J32" s="5" t="s">
+      <c r="J32" s="6" t="s">
         <v>32</v>
       </c>
       <c r="K32" s="1" t="s">
@@ -3075,19 +3083,19 @@
       <c r="E33" s="1">
         <v>1</v>
       </c>
-      <c r="F33" s="3">
+      <c r="F33" s="4">
         <v>0</v>
       </c>
       <c r="G33" s="1">
         <v>2</v>
       </c>
-      <c r="H33" s="5" t="s">
+      <c r="H33" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="I33" s="6" t="s">
+      <c r="I33" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="J33" s="5" t="s">
+      <c r="J33" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K33" s="1" t="s">
@@ -3104,19 +3112,19 @@
       <c r="E34" s="1">
         <v>1</v>
       </c>
-      <c r="F34" s="3">
+      <c r="F34" s="4">
         <v>0</v>
       </c>
       <c r="G34" s="1">
         <v>2</v>
       </c>
-      <c r="H34" s="5" t="s">
+      <c r="H34" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="I34" s="5" t="s">
+      <c r="I34" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J34" s="5" t="s">
+      <c r="J34" s="6" t="s">
         <v>32</v>
       </c>
       <c r="K34" s="1" t="s">
@@ -3133,19 +3141,19 @@
       <c r="E35" s="1">
         <v>1</v>
       </c>
-      <c r="F35" s="3">
+      <c r="F35" s="4">
         <v>0</v>
       </c>
       <c r="G35" s="1">
         <v>2</v>
       </c>
-      <c r="H35" s="5" t="s">
+      <c r="H35" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="I35" s="5" t="s">
+      <c r="I35" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="J35" s="5" t="s">
+      <c r="J35" s="6" t="s">
         <v>104</v>
       </c>
       <c r="K35" s="1" t="s">
@@ -3162,19 +3170,19 @@
       <c r="E36" s="1">
         <v>1</v>
       </c>
-      <c r="F36" s="3">
+      <c r="F36" s="4">
         <v>0</v>
       </c>
       <c r="G36" s="1">
         <v>2</v>
       </c>
-      <c r="H36" s="5" t="s">
+      <c r="H36" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="I36" s="5" t="s">
+      <c r="I36" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="J36" s="5" t="s">
+      <c r="J36" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K36" s="1" t="s">
@@ -3191,19 +3199,19 @@
       <c r="E37" s="1">
         <v>0</v>
       </c>
-      <c r="F37" s="3">
+      <c r="F37" s="4">
         <v>0</v>
       </c>
       <c r="G37" s="1">
         <v>2</v>
       </c>
-      <c r="H37" s="5" t="s">
+      <c r="H37" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="I37" s="5" t="s">
+      <c r="I37" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="J37" s="5" t="s">
+      <c r="J37" s="6" t="s">
         <v>110</v>
       </c>
       <c r="K37" s="1" t="s">
@@ -3220,19 +3228,19 @@
       <c r="E38" s="1">
         <v>0</v>
       </c>
-      <c r="F38" s="3">
+      <c r="F38" s="4">
         <v>0</v>
       </c>
       <c r="G38" s="1">
         <v>2</v>
       </c>
-      <c r="H38" s="5" t="s">
+      <c r="H38" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="I38" s="5" t="s">
+      <c r="I38" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="J38" s="5" t="s">
+      <c r="J38" s="6" t="s">
         <v>114</v>
       </c>
       <c r="K38" s="1" t="s">
@@ -3251,19 +3259,19 @@
       <c r="E39" s="1">
         <v>1</v>
       </c>
-      <c r="F39" s="3">
+      <c r="F39" s="4">
         <v>0</v>
       </c>
       <c r="G39">
         <v>2</v>
       </c>
-      <c r="H39" s="5" t="s">
+      <c r="H39" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="I39" s="5" t="s">
+      <c r="I39" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="J39" s="5" t="s">
+      <c r="J39" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K39" s="1" t="s">
@@ -3280,19 +3288,19 @@
       <c r="E40" s="1">
         <v>1</v>
       </c>
-      <c r="F40" s="3">
+      <c r="F40" s="4">
         <v>0</v>
       </c>
       <c r="G40" s="1">
         <v>1</v>
       </c>
-      <c r="H40" s="5" t="s">
+      <c r="H40" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="I40" s="5" t="s">
+      <c r="I40" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="J40" s="5" t="s">
+      <c r="J40" s="6" t="s">
         <v>91</v>
       </c>
       <c r="K40" s="1" t="s">
@@ -3309,19 +3317,19 @@
       <c r="E41" s="1">
         <v>0</v>
       </c>
-      <c r="F41" s="3">
-        <v>0</v>
-      </c>
-      <c r="G41" s="3">
-        <v>1</v>
-      </c>
-      <c r="H41" s="5" t="s">
+      <c r="F41" s="4">
+        <v>0</v>
+      </c>
+      <c r="G41" s="4">
+        <v>1</v>
+      </c>
+      <c r="H41" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="I41" s="5" t="s">
+      <c r="I41" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="J41" s="5" t="s">
+      <c r="J41" s="6" t="s">
         <v>123</v>
       </c>
       <c r="K41" s="1" t="s">
@@ -3338,19 +3346,19 @@
       <c r="E42" s="1">
         <v>1</v>
       </c>
-      <c r="F42" s="3">
+      <c r="F42" s="4">
         <v>0</v>
       </c>
       <c r="G42" s="1">
         <v>1</v>
       </c>
-      <c r="H42" s="5" t="s">
+      <c r="H42" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="I42" s="5" t="s">
+      <c r="I42" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="J42" s="5" t="s">
+      <c r="J42" s="6" t="s">
         <v>91</v>
       </c>
       <c r="K42" s="1" t="s">
@@ -3367,19 +3375,19 @@
       <c r="E43" s="1">
         <v>1</v>
       </c>
-      <c r="F43" s="3">
+      <c r="F43" s="4">
         <v>0</v>
       </c>
       <c r="G43" s="1">
         <v>1</v>
       </c>
-      <c r="H43" s="5" t="s">
+      <c r="H43" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="I43" s="5" t="s">
+      <c r="I43" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="J43" s="5" t="s">
+      <c r="J43" s="6" t="s">
         <v>91</v>
       </c>
       <c r="K43" s="1" t="s">
@@ -3396,19 +3404,19 @@
       <c r="E44" s="1">
         <v>1</v>
       </c>
-      <c r="F44" s="3">
+      <c r="F44" s="4">
         <v>0</v>
       </c>
       <c r="G44" s="1">
         <v>1</v>
       </c>
-      <c r="H44" s="5" t="s">
+      <c r="H44" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="I44" s="5" t="s">
+      <c r="I44" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="J44" s="5" t="s">
+      <c r="J44" s="6" t="s">
         <v>91</v>
       </c>
       <c r="K44" s="1" t="s">
@@ -3425,19 +3433,19 @@
       <c r="E45" s="1">
         <v>1</v>
       </c>
-      <c r="F45" s="3">
+      <c r="F45" s="4">
         <v>0</v>
       </c>
       <c r="G45" s="1">
         <v>1</v>
       </c>
-      <c r="H45" s="5" t="s">
+      <c r="H45" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="I45" s="5" t="s">
+      <c r="I45" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="J45" s="5" t="s">
+      <c r="J45" s="6" t="s">
         <v>91</v>
       </c>
       <c r="K45" s="1" t="s">
@@ -3454,19 +3462,19 @@
       <c r="E46" s="1">
         <v>1</v>
       </c>
-      <c r="F46" s="3">
+      <c r="F46" s="4">
         <v>0</v>
       </c>
       <c r="G46" s="1">
         <v>1</v>
       </c>
-      <c r="H46" s="5" t="s">
+      <c r="H46" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="I46" s="5" t="s">
+      <c r="I46" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="J46" s="5" t="s">
+      <c r="J46" s="6" t="s">
         <v>91</v>
       </c>
       <c r="K46" s="1" t="s">
@@ -3483,19 +3491,19 @@
       <c r="E47" s="1">
         <v>1</v>
       </c>
-      <c r="F47" s="3">
+      <c r="F47" s="4">
         <v>0</v>
       </c>
       <c r="G47" s="1">
         <v>2</v>
       </c>
-      <c r="H47" s="5" t="s">
+      <c r="H47" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="I47" s="5" t="s">
+      <c r="I47" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="J47" s="5" t="s">
+      <c r="J47" s="6" t="s">
         <v>32</v>
       </c>
       <c r="K47" s="1" t="s">
@@ -3514,19 +3522,19 @@
       <c r="E48" s="1">
         <v>1</v>
       </c>
-      <c r="F48" s="3">
-        <v>0</v>
-      </c>
-      <c r="G48" s="3">
-        <v>2</v>
-      </c>
-      <c r="H48" s="5" t="s">
+      <c r="F48" s="4">
+        <v>0</v>
+      </c>
+      <c r="G48" s="4">
+        <v>2</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="I48" s="5" t="s">
+      <c r="I48" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="J48" s="5" t="s">
+      <c r="J48" s="6" t="s">
         <v>141</v>
       </c>
       <c r="K48" s="1" t="s">
@@ -3549,13 +3557,13 @@
       <c r="G49" s="1">
         <v>2</v>
       </c>
-      <c r="H49" s="5" t="s">
+      <c r="H49" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="I49" s="5" t="s">
+      <c r="I49" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="J49" s="5" t="s">
+      <c r="J49" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K49" s="1" t="s">
@@ -3568,8 +3576,8 @@
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
-      <c r="F50" s="3"/>
-      <c r="G50" s="3"/>
+      <c r="F50" s="4"/>
+      <c r="G50" s="4"/>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
@@ -3587,19 +3595,19 @@
       <c r="E51" s="1">
         <v>1</v>
       </c>
-      <c r="F51" s="3">
+      <c r="F51" s="4">
         <v>0</v>
       </c>
       <c r="G51" s="1">
         <v>2</v>
       </c>
-      <c r="H51" s="5" t="s">
+      <c r="H51" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="I51" s="5" t="s">
+      <c r="I51" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J51" s="5" t="s">
+      <c r="J51" s="6" t="s">
         <v>141</v>
       </c>
       <c r="K51" s="1" t="s">
@@ -3618,19 +3626,19 @@
       <c r="E52" s="1">
         <v>1</v>
       </c>
-      <c r="F52" s="3">
+      <c r="F52" s="4">
         <v>0</v>
       </c>
       <c r="G52" s="1">
         <v>2</v>
       </c>
-      <c r="H52" s="5" t="s">
+      <c r="H52" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="I52" s="5" t="s">
+      <c r="I52" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="J52" s="5" t="s">
+      <c r="J52" s="6" t="s">
         <v>141</v>
       </c>
       <c r="K52" s="1" t="s">
@@ -3649,19 +3657,19 @@
       <c r="E53" s="1">
         <v>1</v>
       </c>
-      <c r="F53" s="3">
+      <c r="F53" s="4">
         <v>0</v>
       </c>
       <c r="G53" s="1">
         <v>2</v>
       </c>
-      <c r="H53" s="5" t="s">
+      <c r="H53" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="I53" s="5" t="s">
+      <c r="I53" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="J53" s="5" t="s">
+      <c r="J53" s="6" t="s">
         <v>16</v>
       </c>
       <c r="K53" s="1" t="s">
@@ -3680,19 +3688,19 @@
       <c r="E54" s="1">
         <v>1</v>
       </c>
-      <c r="F54" s="3">
+      <c r="F54" s="4">
         <v>0</v>
       </c>
       <c r="G54" s="1">
         <v>2</v>
       </c>
-      <c r="H54" s="5" t="s">
+      <c r="H54" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="I54" s="5" t="s">
+      <c r="I54" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="J54" s="5" t="s">
+      <c r="J54" s="6" t="s">
         <v>16</v>
       </c>
       <c r="K54" s="1" t="s">
@@ -3711,19 +3719,19 @@
       <c r="E55" s="1">
         <v>1</v>
       </c>
-      <c r="F55" s="3">
+      <c r="F55" s="4">
         <v>0</v>
       </c>
       <c r="G55" s="1">
         <v>2</v>
       </c>
-      <c r="H55" s="5" t="s">
+      <c r="H55" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="I55" s="5" t="s">
+      <c r="I55" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="J55" s="5" t="s">
+      <c r="J55" s="6" t="s">
         <v>91</v>
       </c>
       <c r="K55" s="1" t="s">
@@ -3740,19 +3748,19 @@
       <c r="E56" s="1">
         <v>0</v>
       </c>
-      <c r="F56" s="3">
+      <c r="F56" s="4">
         <v>0</v>
       </c>
       <c r="G56" s="1">
         <v>2</v>
       </c>
-      <c r="H56" s="5" t="s">
+      <c r="H56" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="I56" s="5" t="s">
+      <c r="I56" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="J56" s="5" t="s">
+      <c r="J56" s="6" t="s">
         <v>159</v>
       </c>
       <c r="K56" s="1" t="s">
@@ -3769,19 +3777,19 @@
       <c r="E57" s="1">
         <v>1</v>
       </c>
-      <c r="F57" s="3">
+      <c r="F57" s="4">
         <v>0</v>
       </c>
       <c r="G57" s="1">
         <v>2</v>
       </c>
-      <c r="H57" s="5" t="s">
+      <c r="H57" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="I57" s="5" t="s">
+      <c r="I57" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="J57" s="5" t="s">
+      <c r="J57" s="6" t="s">
         <v>32</v>
       </c>
       <c r="K57" s="1" t="s">
@@ -3798,19 +3806,19 @@
       <c r="E58" s="1">
         <v>1</v>
       </c>
-      <c r="F58" s="3">
+      <c r="F58" s="4">
         <v>0</v>
       </c>
       <c r="G58" s="1">
         <v>2</v>
       </c>
-      <c r="H58" s="5" t="s">
+      <c r="H58" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="I58" s="5" t="s">
+      <c r="I58" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="J58" s="5" t="s">
+      <c r="J58" s="6" t="s">
         <v>91</v>
       </c>
       <c r="K58" s="1" t="s">
@@ -3827,19 +3835,19 @@
       <c r="E59" s="1">
         <v>0</v>
       </c>
-      <c r="F59" s="3">
+      <c r="F59" s="4">
         <v>0</v>
       </c>
       <c r="G59" s="1">
         <v>2</v>
       </c>
-      <c r="H59" s="5" t="s">
+      <c r="H59" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="I59" s="5" t="s">
+      <c r="I59" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="J59" s="5" t="s">
+      <c r="J59" s="6" t="s">
         <v>169</v>
       </c>
       <c r="K59" s="1" t="s">
@@ -3856,19 +3864,19 @@
       <c r="E60" s="1">
         <v>0</v>
       </c>
-      <c r="F60" s="3">
+      <c r="F60" s="4">
         <v>0</v>
       </c>
       <c r="G60" s="1">
         <v>2</v>
       </c>
-      <c r="H60" s="5" t="s">
+      <c r="H60" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="I60" s="5" t="s">
+      <c r="I60" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="J60" s="5" t="s">
+      <c r="J60" s="6" t="s">
         <v>159</v>
       </c>
       <c r="K60" s="1" t="s">
@@ -3885,19 +3893,19 @@
       <c r="E61" s="1">
         <v>0</v>
       </c>
-      <c r="F61" s="3">
+      <c r="F61" s="4">
         <v>0</v>
       </c>
       <c r="G61" s="1">
         <v>2</v>
       </c>
-      <c r="H61" s="5" t="s">
+      <c r="H61" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="I61" s="5" t="s">
+      <c r="I61" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="J61" s="5" t="s">
+      <c r="J61" s="6" t="s">
         <v>159</v>
       </c>
       <c r="K61" s="1" t="s">
@@ -3914,19 +3922,19 @@
       <c r="E62" s="1">
         <v>0</v>
       </c>
-      <c r="F62" s="3">
+      <c r="F62" s="4">
         <v>0</v>
       </c>
       <c r="G62" s="1">
         <v>2</v>
       </c>
-      <c r="H62" s="5" t="s">
+      <c r="H62" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="I62" s="5" t="s">
+      <c r="I62" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="J62" s="5" t="s">
+      <c r="J62" s="6" t="s">
         <v>169</v>
       </c>
       <c r="K62" s="1" t="s">
@@ -3943,19 +3951,19 @@
       <c r="E63" s="1">
         <v>0</v>
       </c>
-      <c r="F63" s="3">
+      <c r="F63" s="4">
         <v>0</v>
       </c>
       <c r="G63" s="1">
         <v>2</v>
       </c>
-      <c r="H63" s="5" t="s">
+      <c r="H63" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="I63" s="5" t="s">
+      <c r="I63" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="J63" s="5" t="s">
+      <c r="J63" s="6" t="s">
         <v>169</v>
       </c>
       <c r="K63" s="1" t="s">
@@ -3972,19 +3980,19 @@
       <c r="E64" s="1">
         <v>0</v>
       </c>
-      <c r="F64" s="3">
+      <c r="F64" s="4">
         <v>0</v>
       </c>
       <c r="G64" s="1">
         <v>2</v>
       </c>
-      <c r="H64" s="5" t="s">
+      <c r="H64" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="I64" s="5" t="s">
+      <c r="I64" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="J64" s="5" t="s">
+      <c r="J64" s="6" t="s">
         <v>169</v>
       </c>
       <c r="K64" s="1" t="s">
@@ -4001,19 +4009,19 @@
       <c r="E65" s="1">
         <v>0</v>
       </c>
-      <c r="F65" s="3">
+      <c r="F65" s="4">
         <v>0</v>
       </c>
       <c r="G65" s="1">
         <v>2</v>
       </c>
-      <c r="H65" s="5" t="s">
+      <c r="H65" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="I65" s="5" t="s">
+      <c r="I65" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="J65" s="5" t="s">
+      <c r="J65" s="6" t="s">
         <v>169</v>
       </c>
       <c r="K65" s="1" t="s">
@@ -4030,19 +4038,19 @@
       <c r="E67" s="1">
         <v>1</v>
       </c>
-      <c r="F67" s="3">
+      <c r="F67" s="4">
         <v>0</v>
       </c>
       <c r="G67" s="1">
         <v>1</v>
       </c>
-      <c r="H67" s="5" t="s">
+      <c r="H67" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="I67" s="5" t="s">
+      <c r="I67" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="J67" s="5" t="s">
+      <c r="J67" s="6" t="s">
         <v>185</v>
       </c>
       <c r="K67" s="1" t="s">
@@ -4059,19 +4067,19 @@
       <c r="E68" s="1">
         <v>1</v>
       </c>
-      <c r="F68" s="3">
+      <c r="F68" s="4">
         <v>0</v>
       </c>
       <c r="G68" s="1">
         <v>2</v>
       </c>
-      <c r="H68" s="5" t="s">
+      <c r="H68" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="I68" s="5" t="s">
+      <c r="I68" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="J68" s="5" t="s">
+      <c r="J68" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K68" s="1" t="s">
@@ -4088,19 +4096,19 @@
       <c r="E69" s="1">
         <v>1</v>
       </c>
-      <c r="F69" s="3">
+      <c r="F69" s="4">
         <v>0</v>
       </c>
       <c r="G69" s="1">
         <v>2</v>
       </c>
-      <c r="H69" s="5" t="s">
+      <c r="H69" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="I69" s="5" t="s">
+      <c r="I69" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="J69" s="5" t="s">
+      <c r="J69" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K69" s="1" t="s">
@@ -4117,19 +4125,19 @@
       <c r="E71" s="1">
         <v>1</v>
       </c>
-      <c r="F71" s="3">
-        <v>0</v>
-      </c>
-      <c r="G71" s="3">
-        <v>2</v>
-      </c>
-      <c r="H71" s="5" t="s">
+      <c r="F71" s="4">
+        <v>0</v>
+      </c>
+      <c r="G71" s="4">
+        <v>2</v>
+      </c>
+      <c r="H71" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="I71" s="5" t="s">
+      <c r="I71" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="J71" s="5" t="s">
+      <c r="J71" s="6" t="s">
         <v>87</v>
       </c>
       <c r="K71" s="1" t="s">
@@ -4146,19 +4154,19 @@
       <c r="E72" s="1">
         <v>1</v>
       </c>
-      <c r="F72" s="3">
-        <v>0</v>
-      </c>
-      <c r="G72" s="3">
-        <v>2</v>
-      </c>
-      <c r="H72" s="5" t="s">
+      <c r="F72" s="4">
+        <v>0</v>
+      </c>
+      <c r="G72" s="4">
+        <v>2</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="I72" s="5" t="s">
+      <c r="I72" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="J72" s="5" t="s">
+      <c r="J72" s="6" t="s">
         <v>87</v>
       </c>
       <c r="K72" s="1" t="s">
@@ -4175,19 +4183,19 @@
       <c r="E73" s="1">
         <v>1</v>
       </c>
-      <c r="F73" s="3">
-        <v>0</v>
-      </c>
-      <c r="G73" s="3">
-        <v>2</v>
-      </c>
-      <c r="H73" s="5" t="s">
+      <c r="F73" s="4">
+        <v>0</v>
+      </c>
+      <c r="G73" s="4">
+        <v>2</v>
+      </c>
+      <c r="H73" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="I73" s="5" t="s">
+      <c r="I73" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="J73" s="5" t="s">
+      <c r="J73" s="6" t="s">
         <v>87</v>
       </c>
       <c r="K73" s="1" t="s">
@@ -4204,19 +4212,19 @@
       <c r="E74" s="1">
         <v>1</v>
       </c>
-      <c r="F74" s="3">
-        <v>0</v>
-      </c>
-      <c r="G74" s="3">
-        <v>2</v>
-      </c>
-      <c r="H74" s="5" t="s">
+      <c r="F74" s="4">
+        <v>0</v>
+      </c>
+      <c r="G74" s="4">
+        <v>2</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="I74" s="5" t="s">
+      <c r="I74" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="J74" s="5" t="s">
+      <c r="J74" s="6" t="s">
         <v>87</v>
       </c>
       <c r="K74" s="1" t="s">
@@ -4233,19 +4241,19 @@
       <c r="E75" s="1">
         <v>1</v>
       </c>
-      <c r="F75" s="3">
-        <v>0</v>
-      </c>
-      <c r="G75" s="3">
-        <v>2</v>
-      </c>
-      <c r="H75" s="5" t="s">
+      <c r="F75" s="4">
+        <v>0</v>
+      </c>
+      <c r="G75" s="4">
+        <v>2</v>
+      </c>
+      <c r="H75" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="I75" s="5" t="s">
+      <c r="I75" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="J75" s="5" t="s">
+      <c r="J75" s="6" t="s">
         <v>87</v>
       </c>
       <c r="K75" s="1" t="s">
@@ -4262,19 +4270,19 @@
       <c r="E76" s="1">
         <v>1</v>
       </c>
-      <c r="F76" s="3">
-        <v>0</v>
-      </c>
-      <c r="G76" s="3">
-        <v>2</v>
-      </c>
-      <c r="H76" s="5" t="s">
+      <c r="F76" s="4">
+        <v>0</v>
+      </c>
+      <c r="G76" s="4">
+        <v>2</v>
+      </c>
+      <c r="H76" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="I76" s="5" t="s">
+      <c r="I76" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="J76" s="5" t="s">
+      <c r="J76" s="6" t="s">
         <v>91</v>
       </c>
       <c r="K76" s="1" t="s">
@@ -4291,19 +4299,19 @@
       <c r="E77" s="1">
         <v>1</v>
       </c>
-      <c r="F77" s="3">
-        <v>0</v>
-      </c>
-      <c r="G77" s="3">
-        <v>2</v>
-      </c>
-      <c r="H77" s="5" t="s">
+      <c r="F77" s="4">
+        <v>0</v>
+      </c>
+      <c r="G77" s="4">
+        <v>2</v>
+      </c>
+      <c r="H77" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="I77" s="5" t="s">
+      <c r="I77" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="J77" s="5" t="s">
+      <c r="J77" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K77" s="1" t="s">
@@ -4320,28 +4328,28 @@
       <c r="C79" s="1">
         <v>118</v>
       </c>
-      <c r="D79" s="3" t="s">
+      <c r="D79" s="4" t="s">
         <v>215</v>
       </c>
       <c r="E79" s="1">
         <v>1</v>
       </c>
-      <c r="F79" s="3">
-        <v>0</v>
-      </c>
-      <c r="G79" s="3">
-        <v>2</v>
-      </c>
-      <c r="H79" s="5" t="s">
+      <c r="F79" s="4">
+        <v>0</v>
+      </c>
+      <c r="G79" s="4">
+        <v>2</v>
+      </c>
+      <c r="H79" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="I79" s="5" t="s">
+      <c r="I79" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="J79" s="5" t="s">
+      <c r="J79" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="K79" s="3" t="s">
+      <c r="K79" s="4" t="s">
         <v>215</v>
       </c>
     </row>
@@ -4355,28 +4363,28 @@
       <c r="C80" s="1">
         <v>119</v>
       </c>
-      <c r="D80" s="3" t="s">
+      <c r="D80" s="4" t="s">
         <v>217</v>
       </c>
       <c r="E80" s="1">
         <v>1</v>
       </c>
-      <c r="F80" s="3">
-        <v>0</v>
-      </c>
-      <c r="G80" s="3">
-        <v>2</v>
-      </c>
-      <c r="H80" s="5" t="s">
+      <c r="F80" s="4">
+        <v>0</v>
+      </c>
+      <c r="G80" s="4">
+        <v>2</v>
+      </c>
+      <c r="H80" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="I80" s="5" t="s">
+      <c r="I80" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="J80" s="5" t="s">
+      <c r="J80" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="K80" s="3" t="s">
+      <c r="K80" s="4" t="s">
         <v>217</v>
       </c>
     </row>
@@ -4390,28 +4398,28 @@
       <c r="C81" s="1">
         <v>120</v>
       </c>
-      <c r="D81" s="3" t="s">
+      <c r="D81" s="4" t="s">
         <v>219</v>
       </c>
       <c r="E81" s="1">
         <v>1</v>
       </c>
-      <c r="F81" s="3">
-        <v>0</v>
-      </c>
-      <c r="G81" s="3">
-        <v>2</v>
-      </c>
-      <c r="H81" s="5" t="s">
+      <c r="F81" s="4">
+        <v>0</v>
+      </c>
+      <c r="G81" s="4">
+        <v>2</v>
+      </c>
+      <c r="H81" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="I81" s="5" t="s">
+      <c r="I81" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="J81" s="5" t="s">
+      <c r="J81" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="K81" s="3" t="s">
+      <c r="K81" s="4" t="s">
         <v>219</v>
       </c>
     </row>
@@ -4425,28 +4433,28 @@
       <c r="C82" s="1">
         <v>121</v>
       </c>
-      <c r="D82" s="3" t="s">
+      <c r="D82" s="4" t="s">
         <v>221</v>
       </c>
       <c r="E82" s="1">
         <v>1</v>
       </c>
-      <c r="F82" s="3">
-        <v>0</v>
-      </c>
-      <c r="G82" s="3">
-        <v>2</v>
-      </c>
-      <c r="H82" s="5" t="s">
+      <c r="F82" s="4">
+        <v>0</v>
+      </c>
+      <c r="G82" s="4">
+        <v>2</v>
+      </c>
+      <c r="H82" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="I82" s="5" t="s">
+      <c r="I82" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="J82" s="5" t="s">
+      <c r="J82" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="K82" s="3" t="s">
+      <c r="K82" s="4" t="s">
         <v>221</v>
       </c>
     </row>
@@ -4460,28 +4468,28 @@
       <c r="C83" s="1">
         <v>122</v>
       </c>
-      <c r="D83" s="3" t="s">
+      <c r="D83" s="4" t="s">
         <v>223</v>
       </c>
       <c r="E83" s="1">
         <v>1</v>
       </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>2</v>
-      </c>
-      <c r="H83" s="5" t="s">
+      <c r="F83" s="4">
+        <v>0</v>
+      </c>
+      <c r="G83" s="4">
+        <v>2</v>
+      </c>
+      <c r="H83" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="I83" s="5" t="s">
+      <c r="I83" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="J83" s="5" t="s">
+      <c r="J83" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="K83" s="3" t="s">
+      <c r="K83" s="4" t="s">
         <v>223</v>
       </c>
     </row>
@@ -4495,28 +4503,28 @@
       <c r="C84" s="1">
         <v>123</v>
       </c>
-      <c r="D84" s="3" t="s">
+      <c r="D84" s="4" t="s">
         <v>225</v>
       </c>
       <c r="E84" s="1">
         <v>1</v>
       </c>
-      <c r="F84" s="3">
-        <v>0</v>
-      </c>
-      <c r="G84" s="3">
-        <v>2</v>
-      </c>
-      <c r="H84" s="5" t="s">
+      <c r="F84" s="4">
+        <v>0</v>
+      </c>
+      <c r="G84" s="4">
+        <v>2</v>
+      </c>
+      <c r="H84" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="I84" s="5" t="s">
+      <c r="I84" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="J84" s="5" t="s">
+      <c r="J84" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="K84" s="3" t="s">
+      <c r="K84" s="4" t="s">
         <v>225</v>
       </c>
     </row>
@@ -4536,19 +4544,19 @@
       <c r="E85" s="1">
         <v>1</v>
       </c>
-      <c r="F85" s="3">
-        <v>0</v>
-      </c>
-      <c r="G85" s="3">
-        <v>2</v>
-      </c>
-      <c r="H85" s="5" t="s">
+      <c r="F85" s="4">
+        <v>0</v>
+      </c>
+      <c r="G85" s="4">
+        <v>2</v>
+      </c>
+      <c r="H85" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="I85" s="5" t="s">
+      <c r="I85" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="J85" s="5" t="s">
+      <c r="J85" s="6" t="s">
         <v>87</v>
       </c>
       <c r="K85" s="1" t="s">
@@ -4571,19 +4579,19 @@
       <c r="E86" s="1">
         <v>1</v>
       </c>
-      <c r="F86" s="3">
-        <v>0</v>
-      </c>
-      <c r="G86" s="3">
-        <v>2</v>
-      </c>
-      <c r="H86" s="5" t="s">
+      <c r="F86" s="4">
+        <v>0</v>
+      </c>
+      <c r="G86" s="4">
+        <v>2</v>
+      </c>
+      <c r="H86" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="I86" s="5" t="s">
+      <c r="I86" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="J86" s="5" t="s">
+      <c r="J86" s="6" t="s">
         <v>87</v>
       </c>
       <c r="K86" s="1" t="s">
@@ -4606,19 +4614,19 @@
       <c r="E87" s="1">
         <v>1</v>
       </c>
-      <c r="F87" s="3">
-        <v>0</v>
-      </c>
-      <c r="G87" s="3">
-        <v>2</v>
-      </c>
-      <c r="H87" s="5" t="s">
+      <c r="F87" s="4">
+        <v>0</v>
+      </c>
+      <c r="G87" s="4">
+        <v>2</v>
+      </c>
+      <c r="H87" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="I87" s="5" t="s">
+      <c r="I87" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="J87" s="5" t="s">
+      <c r="J87" s="6" t="s">
         <v>87</v>
       </c>
       <c r="K87" s="1" t="s">
@@ -4641,19 +4649,19 @@
       <c r="E88" s="1">
         <v>1</v>
       </c>
-      <c r="F88" s="3">
-        <v>0</v>
-      </c>
-      <c r="G88" s="3">
-        <v>2</v>
-      </c>
-      <c r="H88" s="5" t="s">
+      <c r="F88" s="4">
+        <v>0</v>
+      </c>
+      <c r="G88" s="4">
+        <v>2</v>
+      </c>
+      <c r="H88" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="I88" s="5" t="s">
+      <c r="I88" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="J88" s="5" t="s">
+      <c r="J88" s="6" t="s">
         <v>87</v>
       </c>
       <c r="K88" s="1" t="s">
@@ -4676,19 +4684,19 @@
       <c r="E89" s="1">
         <v>1</v>
       </c>
-      <c r="F89" s="3">
-        <v>0</v>
-      </c>
-      <c r="G89" s="3">
-        <v>2</v>
-      </c>
-      <c r="H89" s="5" t="s">
+      <c r="F89" s="4">
+        <v>0</v>
+      </c>
+      <c r="G89" s="4">
+        <v>2</v>
+      </c>
+      <c r="H89" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="I89" s="5" t="s">
+      <c r="I89" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="J89" s="5" t="s">
+      <c r="J89" s="6" t="s">
         <v>87</v>
       </c>
       <c r="K89" s="1" t="s">
@@ -4711,19 +4719,19 @@
       <c r="E91" s="1">
         <v>1</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>2</v>
-      </c>
-      <c r="H91" s="5" t="s">
+      <c r="F91" s="4">
+        <v>0</v>
+      </c>
+      <c r="G91" s="4">
+        <v>2</v>
+      </c>
+      <c r="H91" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="I91" s="5" t="s">
+      <c r="I91" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="J91" s="5" t="s">
+      <c r="J91" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K91" s="1" t="s">
@@ -4746,19 +4754,19 @@
       <c r="E92" s="1">
         <v>1</v>
       </c>
-      <c r="F92" s="3">
-        <v>0</v>
-      </c>
-      <c r="G92" s="3">
-        <v>2</v>
-      </c>
-      <c r="H92" s="5" t="s">
+      <c r="F92" s="4">
+        <v>0</v>
+      </c>
+      <c r="G92" s="4">
+        <v>2</v>
+      </c>
+      <c r="H92" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="I92" s="5" t="s">
+      <c r="I92" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="J92" s="5" t="s">
+      <c r="J92" s="6" t="s">
         <v>242</v>
       </c>
       <c r="K92" s="1" t="s">
@@ -4781,19 +4789,19 @@
       <c r="E93" s="1">
         <v>1</v>
       </c>
-      <c r="F93" s="3">
-        <v>0</v>
-      </c>
-      <c r="G93" s="3">
-        <v>2</v>
-      </c>
-      <c r="H93" s="5" t="s">
+      <c r="F93" s="4">
+        <v>0</v>
+      </c>
+      <c r="G93" s="4">
+        <v>2</v>
+      </c>
+      <c r="H93" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="I93" s="5" t="s">
+      <c r="I93" s="6" t="s">
         <v>244</v>
       </c>
-      <c r="J93" s="5" t="s">
+      <c r="J93" s="6" t="s">
         <v>242</v>
       </c>
       <c r="K93" s="1" t="s">
@@ -4810,19 +4818,19 @@
       <c r="E103" s="1">
         <v>1</v>
       </c>
-      <c r="F103" s="3">
-        <v>0</v>
-      </c>
-      <c r="G103" s="3">
-        <v>2</v>
-      </c>
-      <c r="H103" s="5" t="s">
+      <c r="F103" s="4">
+        <v>0</v>
+      </c>
+      <c r="G103" s="4">
+        <v>2</v>
+      </c>
+      <c r="H103" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="I103" s="5" t="s">
+      <c r="I103" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="J103" s="5" t="s">
+      <c r="J103" s="6" t="s">
         <v>32</v>
       </c>
       <c r="K103" s="1" t="s">
@@ -4839,19 +4847,19 @@
       <c r="E104" s="1">
         <v>1</v>
       </c>
-      <c r="F104" s="3">
-        <v>0</v>
-      </c>
-      <c r="G104" s="3">
-        <v>2</v>
-      </c>
-      <c r="H104" s="5" t="s">
+      <c r="F104" s="4">
+        <v>0</v>
+      </c>
+      <c r="G104" s="4">
+        <v>2</v>
+      </c>
+      <c r="H104" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="I104" s="5" t="s">
+      <c r="I104" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="J104" s="5" t="s">
+      <c r="J104" s="6" t="s">
         <v>32</v>
       </c>
       <c r="K104" s="1" t="s">
@@ -4868,19 +4876,19 @@
       <c r="E105" s="1">
         <v>1</v>
       </c>
-      <c r="F105" s="3">
-        <v>0</v>
-      </c>
-      <c r="G105" s="3">
-        <v>2</v>
-      </c>
-      <c r="H105" s="5" t="s">
+      <c r="F105" s="4">
+        <v>0</v>
+      </c>
+      <c r="G105" s="4">
+        <v>2</v>
+      </c>
+      <c r="H105" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="I105" s="5" t="s">
+      <c r="I105" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="J105" s="5" t="s">
+      <c r="J105" s="6" t="s">
         <v>32</v>
       </c>
       <c r="K105" s="1" t="s">
@@ -4897,19 +4905,19 @@
       <c r="E106" s="1">
         <v>1</v>
       </c>
-      <c r="F106" s="3">
-        <v>0</v>
-      </c>
-      <c r="G106" s="3">
-        <v>2</v>
-      </c>
-      <c r="H106" s="5" t="s">
+      <c r="F106" s="4">
+        <v>0</v>
+      </c>
+      <c r="G106" s="4">
+        <v>2</v>
+      </c>
+      <c r="H106" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="I106" s="5" t="s">
+      <c r="I106" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="J106" s="5" t="s">
+      <c r="J106" s="6" t="s">
         <v>32</v>
       </c>
       <c r="K106" s="1" t="s">
@@ -4926,19 +4934,19 @@
       <c r="E107" s="1">
         <v>1</v>
       </c>
-      <c r="F107" s="3">
-        <v>0</v>
-      </c>
-      <c r="G107" s="3">
-        <v>2</v>
-      </c>
-      <c r="H107" s="5" t="s">
+      <c r="F107" s="4">
+        <v>0</v>
+      </c>
+      <c r="G107" s="4">
+        <v>2</v>
+      </c>
+      <c r="H107" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="I107" s="5" t="s">
+      <c r="I107" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="J107" s="5" t="s">
+      <c r="J107" s="6" t="s">
         <v>32</v>
       </c>
       <c r="K107" s="1" t="s">
@@ -4955,19 +4963,19 @@
       <c r="E109" s="1">
         <v>1</v>
       </c>
-      <c r="F109" s="3">
-        <v>0</v>
-      </c>
-      <c r="G109" s="3">
-        <v>2</v>
-      </c>
-      <c r="H109" s="5" t="s">
+      <c r="F109" s="4">
+        <v>0</v>
+      </c>
+      <c r="G109" s="4">
+        <v>2</v>
+      </c>
+      <c r="H109" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="I109" s="5" t="s">
+      <c r="I109" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="J109" s="5" t="s">
+      <c r="J109" s="6" t="s">
         <v>263</v>
       </c>
       <c r="K109" s="1" t="s">
@@ -4984,19 +4992,19 @@
       <c r="E110" s="1">
         <v>1</v>
       </c>
-      <c r="F110" s="3">
-        <v>0</v>
-      </c>
-      <c r="G110" s="3">
-        <v>2</v>
-      </c>
-      <c r="H110" s="5" t="s">
+      <c r="F110" s="4">
+        <v>0</v>
+      </c>
+      <c r="G110" s="4">
+        <v>2</v>
+      </c>
+      <c r="H110" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="I110" s="5" t="s">
+      <c r="I110" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="J110" s="5" t="s">
+      <c r="J110" s="6" t="s">
         <v>141</v>
       </c>
       <c r="K110" s="1" t="s">
@@ -5013,19 +5021,19 @@
       <c r="E111" s="1">
         <v>1</v>
       </c>
-      <c r="F111" s="3">
-        <v>0</v>
-      </c>
-      <c r="G111" s="3">
-        <v>2</v>
-      </c>
-      <c r="H111" s="5" t="s">
+      <c r="F111" s="4">
+        <v>0</v>
+      </c>
+      <c r="G111" s="4">
+        <v>2</v>
+      </c>
+      <c r="H111" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="I111" s="5" t="s">
+      <c r="I111" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="J111" s="5" t="s">
+      <c r="J111" s="6" t="s">
         <v>263</v>
       </c>
       <c r="K111" s="1" t="s">
@@ -5042,19 +5050,19 @@
       <c r="E112" s="1">
         <v>1</v>
       </c>
-      <c r="F112" s="3">
-        <v>0</v>
-      </c>
-      <c r="G112" s="3">
-        <v>2</v>
-      </c>
-      <c r="H112" s="5" t="s">
+      <c r="F112" s="4">
+        <v>0</v>
+      </c>
+      <c r="G112" s="4">
+        <v>2</v>
+      </c>
+      <c r="H112" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="I112" s="5" t="s">
+      <c r="I112" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="J112" s="5" t="s">
+      <c r="J112" s="6" t="s">
         <v>263</v>
       </c>
       <c r="K112" s="1" t="s">
@@ -5071,19 +5079,19 @@
       <c r="E113" s="1">
         <v>1</v>
       </c>
-      <c r="F113" s="3">
-        <v>0</v>
-      </c>
-      <c r="G113" s="3">
-        <v>2</v>
-      </c>
-      <c r="H113" s="5" t="s">
+      <c r="F113" s="4">
+        <v>0</v>
+      </c>
+      <c r="G113" s="4">
+        <v>2</v>
+      </c>
+      <c r="H113" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="I113" s="5" t="s">
+      <c r="I113" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="J113" s="5" t="s">
+      <c r="J113" s="6" t="s">
         <v>263</v>
       </c>
       <c r="K113" s="1" t="s">
@@ -5100,19 +5108,19 @@
       <c r="E114" s="1">
         <v>1</v>
       </c>
-      <c r="F114" s="3">
-        <v>0</v>
-      </c>
-      <c r="G114" s="3">
-        <v>2</v>
-      </c>
-      <c r="H114" s="5" t="s">
+      <c r="F114" s="4">
+        <v>0</v>
+      </c>
+      <c r="G114" s="4">
+        <v>2</v>
+      </c>
+      <c r="H114" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="I114" s="5" t="s">
+      <c r="I114" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="J114" s="5" t="s">
+      <c r="J114" s="6" t="s">
         <v>263</v>
       </c>
       <c r="K114" s="1" t="s">
@@ -5138,108 +5146,108 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="B3:L55"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="3" width="9"/>
-    <col min="4" max="4" width="16.625" customWidth="1"/>
-    <col min="5" max="5" width="12.1666666666667" customWidth="1"/>
-    <col min="6" max="6" width="10.5" customWidth="1"/>
-    <col min="7" max="7" width="10.25" customWidth="1"/>
-    <col min="8" max="8" width="30.4166666666667" customWidth="1"/>
-    <col min="9" max="9" width="72.0166666666667" customWidth="1"/>
-    <col min="10" max="10" width="26.875" customWidth="1"/>
-    <col min="11" max="11" width="42.25" customWidth="1"/>
-    <col min="12" max="16384" width="9"/>
+    <col min="1" max="3" width="9" style="2"/>
+    <col min="4" max="4" width="16.625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="12.1666666666667" style="2" customWidth="1"/>
+    <col min="6" max="6" width="10.5" style="2" customWidth="1"/>
+    <col min="7" max="7" width="10.25" style="2" customWidth="1"/>
+    <col min="8" max="8" width="30.4166666666667" style="2" customWidth="1"/>
+    <col min="9" max="9" width="72.0166666666667" style="2" customWidth="1"/>
+    <col min="10" max="10" width="26.875" style="2" customWidth="1"/>
+    <col min="11" max="11" width="42.25" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
-      <c r="C3" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="2" t="s">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
-      <c r="C4" s="2" t="s">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="2" t="s">
+      <c r="D4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K4" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
-      <c r="C5" s="2" t="s">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="I5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="J5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="K5" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C6" s="1">
         <v>1001</v>
       </c>
@@ -5249,26 +5257,26 @@
       <c r="E6" s="1">
         <v>1</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="4">
         <v>0</v>
       </c>
       <c r="G6" s="1">
         <v>2</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="I6" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="J6" s="5" t="s">
+      <c r="J6" s="6" t="s">
         <v>16</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C7" s="1">
         <v>1002</v>
       </c>
@@ -5278,26 +5286,26 @@
       <c r="E7" s="1">
         <v>1</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="4">
         <v>0</v>
       </c>
       <c r="G7" s="1">
         <v>2</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="H7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="I7" s="6" t="s">
         <v>283</v>
       </c>
-      <c r="J7" s="5" t="s">
+      <c r="J7" s="6" t="s">
         <v>16</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C8" s="1">
         <v>1003</v>
       </c>
@@ -5307,26 +5315,26 @@
       <c r="E8" s="1">
         <v>1</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="4">
         <v>0</v>
       </c>
       <c r="G8" s="1">
         <v>2</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="H8" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="I8" s="6" t="s">
         <v>286</v>
       </c>
-      <c r="J8" s="5" t="s">
+      <c r="J8" s="6" t="s">
         <v>16</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C9" s="1">
         <v>1004</v>
       </c>
@@ -5336,26 +5344,26 @@
       <c r="E9" s="1">
         <v>1</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="4">
         <v>0</v>
       </c>
       <c r="G9" s="1">
         <v>2</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="H9" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="I9" s="6" t="s">
         <v>289</v>
       </c>
-      <c r="J9" s="5" t="s">
+      <c r="J9" s="6" t="s">
         <v>16</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C10" s="1">
         <v>1005</v>
       </c>
@@ -5365,26 +5373,26 @@
       <c r="E10" s="1">
         <v>1</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="4">
         <v>0</v>
       </c>
       <c r="G10" s="1">
         <v>2</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="H10" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I10" s="5" t="s">
+      <c r="I10" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="J10" s="5" t="s">
+      <c r="J10" s="6" t="s">
         <v>16</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C11" s="1">
         <v>1006</v>
       </c>
@@ -5394,26 +5402,26 @@
       <c r="E11" s="1">
         <v>1</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="4">
         <v>0</v>
       </c>
       <c r="G11" s="1">
         <v>2</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="H11" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I11" s="5" t="s">
+      <c r="I11" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="J11" s="5" t="s">
+      <c r="J11" s="6" t="s">
         <v>16</v>
       </c>
       <c r="K11" s="1" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C12" s="1">
         <v>1007</v>
       </c>
@@ -5423,26 +5431,26 @@
       <c r="E12" s="1">
         <v>1</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="4">
         <v>0</v>
       </c>
       <c r="G12" s="1">
         <v>2</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="H12" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I12" s="5" t="s">
+      <c r="I12" s="6" t="s">
         <v>298</v>
       </c>
-      <c r="J12" s="5" t="s">
+      <c r="J12" s="6" t="s">
         <v>16</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C13" s="1">
         <v>1008</v>
       </c>
@@ -5452,26 +5460,26 @@
       <c r="E13" s="1">
         <v>1</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="4">
         <v>0</v>
       </c>
       <c r="G13" s="1">
         <v>2</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="H13" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I13" s="5" t="s">
+      <c r="I13" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="J13" s="5" t="s">
+      <c r="J13" s="6" t="s">
         <v>16</v>
       </c>
       <c r="K13" s="1" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C14" s="1">
         <v>1009</v>
       </c>
@@ -5481,26 +5489,26 @@
       <c r="E14" s="1">
         <v>1</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="4">
         <v>0</v>
       </c>
       <c r="G14" s="1">
         <v>2</v>
       </c>
-      <c r="H14" s="5" t="s">
+      <c r="H14" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I14" s="5" t="s">
+      <c r="I14" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="J14" s="5" t="s">
+      <c r="J14" s="6" t="s">
         <v>16</v>
       </c>
       <c r="K14" s="1" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C15" s="1">
         <v>1010</v>
       </c>
@@ -5510,26 +5518,26 @@
       <c r="E15" s="1">
         <v>1</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="4">
         <v>0</v>
       </c>
       <c r="G15" s="1">
         <v>2</v>
       </c>
-      <c r="H15" s="5" t="s">
+      <c r="H15" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I15" s="5" t="s">
+      <c r="I15" s="6" t="s">
         <v>307</v>
       </c>
-      <c r="J15" s="5" t="s">
+      <c r="J15" s="6" t="s">
         <v>16</v>
       </c>
       <c r="K15" s="1" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C16" s="1">
         <v>1011</v>
       </c>
@@ -5539,26 +5547,26 @@
       <c r="E16" s="1">
         <v>1</v>
       </c>
-      <c r="F16" s="3">
+      <c r="F16" s="4">
         <v>0</v>
       </c>
       <c r="G16" s="1">
         <v>2</v>
       </c>
-      <c r="H16" s="5" t="s">
+      <c r="H16" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I16" s="5" t="s">
+      <c r="I16" s="6" t="s">
         <v>309</v>
       </c>
-      <c r="J16" s="5" t="s">
+      <c r="J16" s="6" t="s">
         <v>16</v>
       </c>
       <c r="K16" s="1" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C17" s="1">
         <v>1012</v>
       </c>
@@ -5568,26 +5576,26 @@
       <c r="E17" s="1">
         <v>1</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="4">
         <v>0</v>
       </c>
       <c r="G17" s="1">
         <v>2</v>
       </c>
-      <c r="H17" s="5" t="s">
+      <c r="H17" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I17" s="5" t="s">
+      <c r="I17" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="J17" s="5" t="s">
+      <c r="J17" s="6" t="s">
         <v>16</v>
       </c>
       <c r="K17" s="1" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C18" s="1">
         <v>1013</v>
       </c>
@@ -5597,26 +5605,26 @@
       <c r="E18" s="1">
         <v>1</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="4">
         <v>0</v>
       </c>
       <c r="G18" s="1">
         <v>2</v>
       </c>
-      <c r="H18" s="5" t="s">
+      <c r="H18" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I18" s="5" t="s">
+      <c r="I18" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="J18" s="5" t="s">
+      <c r="J18" s="6" t="s">
         <v>16</v>
       </c>
       <c r="K18" s="1" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C19" s="1">
         <v>1014</v>
       </c>
@@ -5626,27 +5634,27 @@
       <c r="E19" s="1">
         <v>1</v>
       </c>
-      <c r="F19" s="3">
+      <c r="F19" s="4">
         <v>0</v>
       </c>
       <c r="G19" s="1">
         <v>2</v>
       </c>
-      <c r="H19" s="5" t="s">
+      <c r="H19" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I19" s="5" t="s">
+      <c r="I19" s="6" t="s">
         <v>315</v>
       </c>
-      <c r="J19" s="5" t="s">
+      <c r="J19" s="6" t="s">
         <v>16</v>
       </c>
       <c r="K19" s="1" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" ht="18" customHeight="1"/>
-    <row r="21" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+    <row r="20" s="1" customFormat="1" customHeight="1"/>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C21" s="1">
         <v>1101</v>
       </c>
@@ -5656,26 +5664,26 @@
       <c r="E21" s="1">
         <v>1</v>
       </c>
-      <c r="F21" s="3">
+      <c r="F21" s="4">
         <v>0</v>
       </c>
       <c r="G21" s="1">
         <v>2</v>
       </c>
-      <c r="H21" s="5" t="s">
+      <c r="H21" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I21" s="5" t="s">
+      <c r="I21" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="J21" s="5" t="s">
+      <c r="J21" s="6" t="s">
         <v>16</v>
       </c>
       <c r="K21" s="1" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C22" s="1">
         <v>1102</v>
       </c>
@@ -5685,26 +5693,26 @@
       <c r="E22" s="1">
         <v>1</v>
       </c>
-      <c r="F22" s="3">
+      <c r="F22" s="4">
         <v>0</v>
       </c>
       <c r="G22" s="1">
         <v>2</v>
       </c>
-      <c r="H22" s="5" t="s">
+      <c r="H22" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I22" s="5" t="s">
+      <c r="I22" s="6" t="s">
         <v>320</v>
       </c>
-      <c r="J22" s="5" t="s">
+      <c r="J22" s="6" t="s">
         <v>16</v>
       </c>
       <c r="K22" s="1" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C23" s="1">
         <v>1103</v>
       </c>
@@ -5714,26 +5722,26 @@
       <c r="E23" s="1">
         <v>1</v>
       </c>
-      <c r="F23" s="3">
+      <c r="F23" s="4">
         <v>0</v>
       </c>
       <c r="G23" s="1">
         <v>2</v>
       </c>
-      <c r="H23" s="5" t="s">
+      <c r="H23" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I23" s="5" t="s">
+      <c r="I23" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="J23" s="5" t="s">
+      <c r="J23" s="6" t="s">
         <v>16</v>
       </c>
       <c r="K23" s="1" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C24" s="1">
         <v>1104</v>
       </c>
@@ -5743,26 +5751,26 @@
       <c r="E24" s="1">
         <v>1</v>
       </c>
-      <c r="F24" s="3">
+      <c r="F24" s="4">
         <v>0</v>
       </c>
       <c r="G24" s="1">
         <v>2</v>
       </c>
-      <c r="H24" s="5" t="s">
+      <c r="H24" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I24" s="5" t="s">
+      <c r="I24" s="6" t="s">
         <v>326</v>
       </c>
-      <c r="J24" s="5" t="s">
+      <c r="J24" s="6" t="s">
         <v>16</v>
       </c>
       <c r="K24" s="1" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C25" s="1">
         <v>1105</v>
       </c>
@@ -5772,26 +5780,26 @@
       <c r="E25" s="1">
         <v>1</v>
       </c>
-      <c r="F25" s="3">
+      <c r="F25" s="4">
         <v>0</v>
       </c>
       <c r="G25" s="1">
         <v>2</v>
       </c>
-      <c r="H25" s="5" t="s">
+      <c r="H25" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I25" s="5" t="s">
+      <c r="I25" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="J25" s="5" t="s">
+      <c r="J25" s="6" t="s">
         <v>16</v>
       </c>
       <c r="K25" s="1" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C26" s="1">
         <v>1106</v>
       </c>
@@ -5801,26 +5809,26 @@
       <c r="E26" s="1">
         <v>1</v>
       </c>
-      <c r="F26" s="3">
+      <c r="F26" s="4">
         <v>0</v>
       </c>
       <c r="G26" s="1">
         <v>2</v>
       </c>
-      <c r="H26" s="5" t="s">
+      <c r="H26" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I26" s="5" t="s">
+      <c r="I26" s="6" t="s">
         <v>332</v>
       </c>
-      <c r="J26" s="5" t="s">
+      <c r="J26" s="6" t="s">
         <v>16</v>
       </c>
       <c r="K26" s="1" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C27" s="1">
         <v>1107</v>
       </c>
@@ -5830,26 +5838,26 @@
       <c r="E27" s="1">
         <v>1</v>
       </c>
-      <c r="F27" s="3">
+      <c r="F27" s="4">
         <v>0</v>
       </c>
       <c r="G27" s="1">
         <v>2</v>
       </c>
-      <c r="H27" s="5" t="s">
+      <c r="H27" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I27" s="5" t="s">
+      <c r="I27" s="6" t="s">
         <v>335</v>
       </c>
-      <c r="J27" s="5" t="s">
+      <c r="J27" s="6" t="s">
         <v>16</v>
       </c>
       <c r="K27" s="1" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="28" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C28" s="1">
         <v>1108</v>
       </c>
@@ -5859,26 +5867,26 @@
       <c r="E28" s="1">
         <v>1</v>
       </c>
-      <c r="F28" s="3">
+      <c r="F28" s="4">
         <v>0</v>
       </c>
       <c r="G28" s="1">
         <v>2</v>
       </c>
-      <c r="H28" s="5" t="s">
+      <c r="H28" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I28" s="5" t="s">
+      <c r="I28" s="6" t="s">
         <v>338</v>
       </c>
-      <c r="J28" s="5" t="s">
+      <c r="J28" s="6" t="s">
         <v>16</v>
       </c>
       <c r="K28" s="1" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="29" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C29" s="1">
         <v>1109</v>
       </c>
@@ -5888,26 +5896,26 @@
       <c r="E29" s="1">
         <v>1</v>
       </c>
-      <c r="F29" s="3">
+      <c r="F29" s="4">
         <v>0</v>
       </c>
       <c r="G29" s="1">
         <v>2</v>
       </c>
-      <c r="H29" s="5" t="s">
+      <c r="H29" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I29" s="5" t="s">
+      <c r="I29" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="J29" s="5" t="s">
+      <c r="J29" s="6" t="s">
         <v>16</v>
       </c>
       <c r="K29" s="1" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="30" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C30" s="1">
         <v>1110</v>
       </c>
@@ -5917,26 +5925,26 @@
       <c r="E30" s="1">
         <v>1</v>
       </c>
-      <c r="F30" s="3">
+      <c r="F30" s="4">
         <v>0</v>
       </c>
       <c r="G30" s="1">
         <v>2</v>
       </c>
-      <c r="H30" s="5" t="s">
+      <c r="H30" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I30" s="5" t="s">
+      <c r="I30" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="J30" s="5" t="s">
+      <c r="J30" s="6" t="s">
         <v>16</v>
       </c>
       <c r="K30" s="1" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="31" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C31" s="1">
         <v>1111</v>
       </c>
@@ -5946,26 +5954,26 @@
       <c r="E31" s="1">
         <v>1</v>
       </c>
-      <c r="F31" s="3">
+      <c r="F31" s="4">
         <v>0</v>
       </c>
       <c r="G31" s="1">
         <v>2</v>
       </c>
-      <c r="H31" s="5" t="s">
+      <c r="H31" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I31" s="5" t="s">
+      <c r="I31" s="6" t="s">
         <v>347</v>
       </c>
-      <c r="J31" s="5" t="s">
+      <c r="J31" s="6" t="s">
         <v>16</v>
       </c>
       <c r="K31" s="1" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="32" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C32" s="1">
         <v>1112</v>
       </c>
@@ -5975,39 +5983,39 @@
       <c r="E32" s="1">
         <v>1</v>
       </c>
-      <c r="F32" s="3">
+      <c r="F32" s="4">
         <v>0</v>
       </c>
       <c r="G32" s="1">
         <v>2</v>
       </c>
-      <c r="H32" s="5" t="s">
+      <c r="H32" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I32" s="5" t="s">
+      <c r="I32" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="J32" s="5" t="s">
+      <c r="J32" s="6" t="s">
         <v>16</v>
       </c>
       <c r="K32" s="1" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="33" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
-      <c r="B33"/>
-      <c r="C33"/>
-      <c r="D33"/>
-      <c r="E33"/>
-      <c r="F33"/>
-      <c r="G33"/>
-      <c r="H33"/>
-      <c r="I33"/>
-      <c r="J33"/>
-      <c r="K33"/>
-      <c r="L33"/>
-    </row>
-    <row r="34" spans="2:12">
+    <row r="33" s="1" customFormat="1" customHeight="1" spans="2:12">
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2"/>
+      <c r="L33" s="2"/>
+    </row>
+    <row r="34" customHeight="1" spans="2:12">
       <c r="C34" s="1">
         <v>1201</v>
       </c>
@@ -6017,27 +6025,27 @@
       <c r="E34" s="1">
         <v>1</v>
       </c>
-      <c r="F34" s="3">
+      <c r="F34" s="4">
         <v>0</v>
       </c>
       <c r="G34" s="1">
         <v>2</v>
       </c>
-      <c r="H34" s="5" t="s">
+      <c r="H34" s="6" t="s">
         <v>353</v>
       </c>
-      <c r="I34" s="5" t="s">
+      <c r="I34" s="6" t="s">
         <v>354</v>
       </c>
-      <c r="J34" s="5" t="s">
+      <c r="J34" s="6" t="s">
         <v>16</v>
       </c>
       <c r="K34" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="35" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
-      <c r="B35"/>
+    <row r="35" s="1" customFormat="1" customHeight="1" spans="2:12">
+      <c r="B35" s="2"/>
       <c r="C35" s="1">
         <v>1202</v>
       </c>
@@ -6047,28 +6055,28 @@
       <c r="E35" s="1">
         <v>1</v>
       </c>
-      <c r="F35" s="3">
+      <c r="F35" s="4">
         <v>0</v>
       </c>
       <c r="G35" s="1">
         <v>2</v>
       </c>
-      <c r="H35" s="5" t="s">
+      <c r="H35" s="6" t="s">
         <v>357</v>
       </c>
-      <c r="I35" s="5" t="s">
+      <c r="I35" s="6" t="s">
         <v>358</v>
       </c>
-      <c r="J35" s="5" t="s">
+      <c r="J35" s="6" t="s">
         <v>359</v>
       </c>
       <c r="K35" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="L35"/>
-    </row>
-    <row r="36" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
-      <c r="B36"/>
+      <c r="L35" s="2"/>
+    </row>
+    <row r="36" s="1" customFormat="1" customHeight="1" spans="2:12">
+      <c r="B36" s="2"/>
       <c r="C36" s="1">
         <v>1203</v>
       </c>
@@ -6078,27 +6086,27 @@
       <c r="E36" s="1">
         <v>1</v>
       </c>
-      <c r="F36" s="3">
+      <c r="F36" s="4">
         <v>0</v>
       </c>
       <c r="G36" s="1">
         <v>2</v>
       </c>
-      <c r="H36" s="5" t="s">
+      <c r="H36" s="6" t="s">
         <v>362</v>
       </c>
-      <c r="I36" s="5" t="s">
+      <c r="I36" s="6" t="s">
         <v>363</v>
       </c>
-      <c r="J36" s="5" t="s">
+      <c r="J36" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K36" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="L36"/>
-    </row>
-    <row r="37" spans="2:12">
+      <c r="L36" s="2"/>
+    </row>
+    <row r="37" customHeight="1" spans="2:12">
       <c r="C37" s="1">
         <v>1204</v>
       </c>
@@ -6108,26 +6116,26 @@
       <c r="E37" s="1">
         <v>1</v>
       </c>
-      <c r="F37" s="3">
+      <c r="F37" s="4">
         <v>0</v>
       </c>
       <c r="G37" s="1">
         <v>2</v>
       </c>
-      <c r="H37" s="5" t="s">
+      <c r="H37" s="6" t="s">
         <v>353</v>
       </c>
-      <c r="I37" s="5" t="s">
+      <c r="I37" s="6" t="s">
         <v>366</v>
       </c>
-      <c r="J37" s="5" t="s">
+      <c r="J37" s="6" t="s">
         <v>16</v>
       </c>
       <c r="K37" s="1" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="38" spans="2:12">
+    <row r="38" customHeight="1" spans="2:12">
       <c r="C38" s="1">
         <v>1205</v>
       </c>
@@ -6137,26 +6145,26 @@
       <c r="E38" s="1">
         <v>1</v>
       </c>
-      <c r="F38" s="3">
+      <c r="F38" s="4">
         <v>0</v>
       </c>
       <c r="G38" s="1">
         <v>2</v>
       </c>
-      <c r="H38" s="5" t="s">
+      <c r="H38" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I38" s="5" t="s">
+      <c r="I38" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="J38" s="5" t="s">
+      <c r="J38" s="6" t="s">
         <v>16</v>
       </c>
       <c r="K38" s="1" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="39" spans="2:12">
+    <row r="39" customHeight="1" spans="2:12">
       <c r="C39" s="1">
         <v>1206</v>
       </c>
@@ -6166,141 +6174,141 @@
       <c r="E39" s="1">
         <v>1</v>
       </c>
-      <c r="F39" s="3">
+      <c r="F39" s="4">
         <v>0</v>
       </c>
       <c r="G39" s="1">
         <v>2</v>
       </c>
-      <c r="H39" s="5" t="s">
+      <c r="H39" s="6" t="s">
         <v>372</v>
       </c>
-      <c r="I39" s="5" t="s">
+      <c r="I39" s="6" t="s">
         <v>373</v>
       </c>
-      <c r="J39" s="5" t="s">
+      <c r="J39" s="6" t="s">
         <v>16</v>
       </c>
       <c r="K39" s="1" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="47" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
-      <c r="B47"/>
-      <c r="C47"/>
-      <c r="D47"/>
-      <c r="E47"/>
-      <c r="F47"/>
-      <c r="G47"/>
-      <c r="H47"/>
-      <c r="I47"/>
-      <c r="J47"/>
-      <c r="K47"/>
-      <c r="L47"/>
-    </row>
-    <row r="48" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
-      <c r="B48"/>
-      <c r="C48"/>
-      <c r="D48"/>
-      <c r="E48"/>
-      <c r="F48"/>
-      <c r="G48"/>
-      <c r="H48"/>
-      <c r="I48"/>
-      <c r="J48"/>
-      <c r="K48"/>
-      <c r="L48"/>
-    </row>
-    <row r="49" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
-      <c r="B49"/>
-      <c r="C49"/>
-      <c r="D49"/>
-      <c r="E49"/>
-      <c r="F49"/>
-      <c r="G49"/>
-      <c r="H49"/>
-      <c r="I49"/>
-      <c r="J49"/>
-      <c r="K49"/>
-      <c r="L49"/>
-    </row>
-    <row r="50" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
-      <c r="B50"/>
-      <c r="C50"/>
-      <c r="D50"/>
-      <c r="E50"/>
-      <c r="F50"/>
-      <c r="G50"/>
-      <c r="H50"/>
-      <c r="I50"/>
-      <c r="J50"/>
-      <c r="K50"/>
-      <c r="L50"/>
-    </row>
-    <row r="51" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
-      <c r="B51"/>
-      <c r="C51"/>
-      <c r="D51"/>
-      <c r="E51"/>
-      <c r="F51"/>
-      <c r="G51"/>
-      <c r="H51"/>
-      <c r="I51"/>
-      <c r="J51"/>
-      <c r="K51"/>
-      <c r="L51"/>
-    </row>
-    <row r="52" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
-      <c r="B52"/>
-      <c r="C52"/>
-      <c r="D52"/>
-      <c r="E52"/>
-      <c r="F52"/>
-      <c r="G52"/>
-      <c r="H52"/>
-      <c r="I52"/>
-      <c r="J52"/>
-      <c r="K52"/>
-      <c r="L52"/>
-    </row>
-    <row r="53" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
-      <c r="B53"/>
-      <c r="C53"/>
-      <c r="D53"/>
-      <c r="E53"/>
-      <c r="F53"/>
-      <c r="G53"/>
-      <c r="H53"/>
-      <c r="I53"/>
-      <c r="J53"/>
-      <c r="K53"/>
-      <c r="L53"/>
-    </row>
-    <row r="54" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
-      <c r="B54"/>
-      <c r="C54"/>
-      <c r="D54"/>
-      <c r="E54"/>
-      <c r="F54"/>
-      <c r="G54"/>
-      <c r="H54"/>
-      <c r="I54"/>
-      <c r="J54"/>
-      <c r="K54"/>
-      <c r="L54"/>
-    </row>
-    <row r="55" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
-      <c r="B55"/>
-      <c r="C55"/>
-      <c r="D55"/>
-      <c r="E55"/>
-      <c r="F55"/>
-      <c r="G55"/>
-      <c r="H55"/>
-      <c r="I55"/>
-      <c r="J55"/>
-      <c r="K55"/>
-      <c r="L55"/>
+    <row r="47" s="1" customFormat="1" customHeight="1" spans="2:12">
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+      <c r="J47" s="2"/>
+      <c r="K47" s="2"/>
+      <c r="L47" s="2"/>
+    </row>
+    <row r="48" s="1" customFormat="1" customHeight="1" spans="2:12">
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+      <c r="J48" s="2"/>
+      <c r="K48" s="2"/>
+      <c r="L48" s="2"/>
+    </row>
+    <row r="49" s="1" customFormat="1" customHeight="1" spans="2:12">
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="2"/>
+      <c r="K49" s="2"/>
+      <c r="L49" s="2"/>
+    </row>
+    <row r="50" s="1" customFormat="1" customHeight="1" spans="2:12">
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
+      <c r="F50" s="2"/>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+      <c r="J50" s="2"/>
+      <c r="K50" s="2"/>
+      <c r="L50" s="2"/>
+    </row>
+    <row r="51" s="1" customFormat="1" customHeight="1" spans="2:12">
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="2"/>
+      <c r="K51" s="2"/>
+      <c r="L51" s="2"/>
+    </row>
+    <row r="52" s="1" customFormat="1" customHeight="1" spans="2:12">
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="2"/>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="2"/>
+      <c r="K52" s="2"/>
+      <c r="L52" s="2"/>
+    </row>
+    <row r="53" s="1" customFormat="1" customHeight="1" spans="2:12">
+      <c r="B53" s="2"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="2"/>
+      <c r="F53" s="2"/>
+      <c r="G53" s="2"/>
+      <c r="H53" s="2"/>
+      <c r="I53" s="2"/>
+      <c r="J53" s="2"/>
+      <c r="K53" s="2"/>
+      <c r="L53" s="2"/>
+    </row>
+    <row r="54" s="1" customFormat="1" customHeight="1" spans="2:12">
+      <c r="B54" s="2"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
+      <c r="E54" s="2"/>
+      <c r="F54" s="2"/>
+      <c r="G54" s="2"/>
+      <c r="H54" s="2"/>
+      <c r="I54" s="2"/>
+      <c r="J54" s="2"/>
+      <c r="K54" s="2"/>
+      <c r="L54" s="2"/>
+    </row>
+    <row r="55" s="1" customFormat="1" customHeight="1" spans="2:12">
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2"/>
+      <c r="F55" s="2"/>
+      <c r="G55" s="2"/>
+      <c r="H55" s="2"/>
+      <c r="I55" s="2"/>
+      <c r="J55" s="2"/>
+      <c r="K55" s="2"/>
+      <c r="L55" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="887" uniqueCount="444">
   <si>
     <t>_id</t>
   </si>
@@ -1145,9 +1145,6 @@
     <t>战士8阶以下</t>
   </si>
   <si>
-    <t>12,12,12,12,12</t>
-  </si>
-  <si>
     <t>2001,2002,2003,2004,2005</t>
   </si>
   <si>
@@ -1157,58 +1154,268 @@
     <t>战士8阶以上</t>
   </si>
   <si>
+    <t>4,4,4,4,4,4,4</t>
+  </si>
+  <si>
+    <t>2006,2007,2008,2009,2010,2011,2012</t>
+  </si>
+  <si>
+    <t>1,1,1,1,1,1,1</t>
+  </si>
+  <si>
+    <t>裂地斩，战士之魂，剑二十三 对应的词条</t>
+  </si>
+  <si>
+    <t>法师8阶以下</t>
+  </si>
+  <si>
+    <t>4,4,4,4,4,4,4,4</t>
+  </si>
+  <si>
+    <t>2013,2014,2015,2016,2017,2018,2019,2020</t>
+  </si>
+  <si>
+    <t>落雷术，法力盾，法术精通，冰爆术，心灵传送 对应的词条</t>
+  </si>
+  <si>
+    <t>法师8阶以上</t>
+  </si>
+  <si>
+    <t>2021,2022,2023,2024,2025</t>
+  </si>
+  <si>
+    <t>分身术，法师之魂，魔尊附体 对应的词条</t>
+  </si>
+  <si>
+    <t>道士8阶以下</t>
+  </si>
+  <si>
+    <t>2026,2027,2028,2029,2030,2031</t>
+  </si>
+  <si>
+    <t>驱魔符，道力盾，道力精通，隐身道法 对应的词条</t>
+  </si>
+  <si>
+    <t>道士8阶以上</t>
+  </si>
+  <si>
+    <t>2032,2033,2034,2034</t>
+  </si>
+  <si>
+    <t>无极道体，道士之魂，召唤白虎 对应的词条</t>
+  </si>
+  <si>
+    <t>流光剑法·通神</t>
+  </si>
+  <si>
     <t>12,12,12,12,12,12,12</t>
   </si>
   <si>
-    <t>2006,2007,2008,2009,2010,2011,2012</t>
-  </si>
-  <si>
-    <t>1,1,1,1,1,1,1</t>
-  </si>
-  <si>
-    <t>裂地斩，战士之魂，剑二十三 对应的词条</t>
-  </si>
-  <si>
-    <t>法师8阶以下</t>
-  </si>
-  <si>
-    <t>12,12,12,12,12,12,12,12</t>
-  </si>
-  <si>
-    <t>2013,2014,2015,2016,2017,2018,2019,2020</t>
-  </si>
-  <si>
-    <t>落雷术，法力盾，法术精通，冰爆术，心灵传送 对应的词条</t>
-  </si>
-  <si>
-    <t>法师8阶以上</t>
-  </si>
-  <si>
-    <t>2021,2022,2023,2024,2025</t>
-  </si>
-  <si>
-    <t>分身术，法师之魂，魔尊附体 对应的词条</t>
-  </si>
-  <si>
-    <t>道士8阶以下</t>
-  </si>
-  <si>
-    <t>2026,2027,2028,2029,2030,2031</t>
-  </si>
-  <si>
-    <t>驱魔符，道力盾，道力精通，隐身道法 对应的词条</t>
-  </si>
-  <si>
-    <t>道士8阶以上</t>
-  </si>
-  <si>
-    <t>12,12,12,12</t>
-  </si>
-  <si>
-    <t>2032,2033,2034,2034</t>
-  </si>
-  <si>
-    <t>无极道体，道士之魂，召唤白虎 对应的词条</t>
+    <t>2001,2002,2003,2004,2005,2006</t>
+  </si>
+  <si>
+    <t>武神盾·通神</t>
+  </si>
+  <si>
+    <t>2007,2008,2009,2010,2011,2012</t>
+  </si>
+  <si>
+    <t>武力精通·通神</t>
+  </si>
+  <si>
+    <t>2013,2014,2015,2016,2017,2018</t>
+  </si>
+  <si>
+    <t>战吼·通神</t>
+  </si>
+  <si>
+    <t>2019,2020,2021,2022,2023,2024</t>
+  </si>
+  <si>
+    <t>战吼·破限</t>
+  </si>
+  <si>
+    <t>2025,2026,2027,2028,2029,2030</t>
+  </si>
+  <si>
+    <t>裂地斩·通神</t>
+  </si>
+  <si>
+    <t>2031,2032,2033,2034,2035,2036</t>
+  </si>
+  <si>
+    <t>裂地斩·天目</t>
+  </si>
+  <si>
+    <t>2037,2038,2039,2040,2041,2042</t>
+  </si>
+  <si>
+    <t>战士之魂·通神</t>
+  </si>
+  <si>
+    <t>2043,2044,2045,2046,2047,2048</t>
+  </si>
+  <si>
+    <t>剑二十三·通神</t>
+  </si>
+  <si>
+    <t>2049,2050,2051,2052,2053,2054</t>
+  </si>
+  <si>
+    <t>剑二十三·吸血</t>
+  </si>
+  <si>
+    <t>2055,2056,2057,2058,2059,2060</t>
+  </si>
+  <si>
+    <t>剑二十三·祝福</t>
+  </si>
+  <si>
+    <t>2061,2062,2063,2064,2065,2066</t>
+  </si>
+  <si>
+    <t>剑二十三·致命</t>
+  </si>
+  <si>
+    <t>2067,2068,2069,2070,2071,2072</t>
+  </si>
+  <si>
+    <t>落雷术·通神</t>
+  </si>
+  <si>
+    <t>2073,2074,2075,2076,2077,2078</t>
+  </si>
+  <si>
+    <t>落雷术·吸血</t>
+  </si>
+  <si>
+    <t>2079,2080,2081,2082,2083,2084</t>
+  </si>
+  <si>
+    <t>落雷术·神术</t>
+  </si>
+  <si>
+    <t>2085,2086,2087,2088,2089,2090</t>
+  </si>
+  <si>
+    <t>法力盾·通神</t>
+  </si>
+  <si>
+    <t>2091,2092,2093,2094,2095,2096</t>
+  </si>
+  <si>
+    <t>法术精通·通神</t>
+  </si>
+  <si>
+    <t>2097,2098,2099,2100,2101,2102</t>
+  </si>
+  <si>
+    <t>冰爆术·哀霜Ⅱ</t>
+  </si>
+  <si>
+    <t>2103,2104,2105,2106,2107,2108</t>
+  </si>
+  <si>
+    <t>心灵传送·通神</t>
+  </si>
+  <si>
+    <t>2109,2110,2111,2112,2113,2114</t>
+  </si>
+  <si>
+    <t>心灵传送·破限</t>
+  </si>
+  <si>
+    <t>2115,2116,2117,2118,2119,2120</t>
+  </si>
+  <si>
+    <t>分身术·通神</t>
+  </si>
+  <si>
+    <t>2121,2122,2123,2124,2125,2126</t>
+  </si>
+  <si>
+    <t>分身术·超持久</t>
+  </si>
+  <si>
+    <t>2127,2128,2129,2130,2131,2132</t>
+  </si>
+  <si>
+    <t>法师之魂·通神</t>
+  </si>
+  <si>
+    <t>2133,2134,2135,2136,2137,2138</t>
+  </si>
+  <si>
+    <t>魔尊附体·通神</t>
+  </si>
+  <si>
+    <t>2139,2140,2141,2142,2143,2144</t>
+  </si>
+  <si>
+    <t>魔尊附体·双倍</t>
+  </si>
+  <si>
+    <t>2145,2146,2147,2148,2149,2150</t>
+  </si>
+  <si>
+    <t>驱魔符·通神</t>
+  </si>
+  <si>
+    <t>2151,2152,2153,2154,2155,2156</t>
+  </si>
+  <si>
+    <t>道力盾·通神</t>
+  </si>
+  <si>
+    <t>2157,2158,2159,2160,2161,2162</t>
+  </si>
+  <si>
+    <t>道力精通·通神</t>
+  </si>
+  <si>
+    <t>2163,2164,2165,2166,2167,2168</t>
+  </si>
+  <si>
+    <t>隐身道法·通神</t>
+  </si>
+  <si>
+    <t>2169,2170,2171,2172,2173,2174</t>
+  </si>
+  <si>
+    <t>隐身道法·神术</t>
+  </si>
+  <si>
+    <t>2175,2176,2177,2178,2179,2180</t>
+  </si>
+  <si>
+    <t>隐身道法·破限</t>
+  </si>
+  <si>
+    <t>2181,2182,2183,2184,2185,2186</t>
+  </si>
+  <si>
+    <t>无极道体·通神</t>
+  </si>
+  <si>
+    <t>2187,2188,2189,2190,2191,2192</t>
+  </si>
+  <si>
+    <t>道士之魂·通神</t>
+  </si>
+  <si>
+    <t>2193,2194,2195,2196,2197,2198</t>
+  </si>
+  <si>
+    <t>召唤白虎·通神</t>
+  </si>
+  <si>
+    <t>2199,2200,2201,2202,2203,2204</t>
+  </si>
+  <si>
+    <t>召唤白虎·复制</t>
+  </si>
+  <si>
+    <t>2205,2206,2207,2208,2209,2210</t>
   </si>
 </sst>
 </file>
@@ -1221,7 +1428,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1247,6 +1454,12 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1729,16 +1942,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1747,119 +1957,122 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1867,6 +2080,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1"/>
@@ -2306,13 +2521,13 @@
       <c r="G6" s="1">
         <v>2</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="H6" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I6" s="6" t="s">
+      <c r="I6" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="J6" s="6" t="s">
+      <c r="J6" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K6" s="1" t="s">
@@ -2335,13 +2550,13 @@
       <c r="G7" s="1">
         <v>2</v>
       </c>
-      <c r="H7" s="6" t="s">
+      <c r="H7" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I7" s="6" t="s">
+      <c r="I7" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="J7" s="6" t="s">
+      <c r="J7" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K7" s="1" t="s">
@@ -2364,13 +2579,13 @@
       <c r="G8" s="1">
         <v>2</v>
       </c>
-      <c r="H8" s="6" t="s">
+      <c r="H8" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I8" s="6" t="s">
+      <c r="I8" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="J8" s="6" t="s">
+      <c r="J8" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K8" s="1" t="s">
@@ -2393,13 +2608,13 @@
       <c r="G9" s="1">
         <v>2</v>
       </c>
-      <c r="H9" s="6" t="s">
+      <c r="H9" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I9" s="6" t="s">
+      <c r="I9" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="J9" s="6" t="s">
+      <c r="J9" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K9" s="1" t="s">
@@ -2422,13 +2637,13 @@
       <c r="G10" s="1">
         <v>2</v>
       </c>
-      <c r="H10" s="6" t="s">
+      <c r="H10" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I10" s="6" t="s">
+      <c r="I10" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="J10" s="6" t="s">
+      <c r="J10" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K10" s="1" t="s">
@@ -2451,13 +2666,13 @@
       <c r="G11" s="1">
         <v>2</v>
       </c>
-      <c r="H11" s="6" t="s">
+      <c r="H11" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I11" s="6" t="s">
+      <c r="I11" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="J11" s="6" t="s">
+      <c r="J11" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K11" s="1" t="s">
@@ -2480,13 +2695,13 @@
       <c r="G12" s="1">
         <v>2</v>
       </c>
-      <c r="H12" s="6" t="s">
+      <c r="H12" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I12" s="6" t="s">
+      <c r="I12" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="J12" s="6" t="s">
+      <c r="J12" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K12" s="1" t="s">
@@ -2509,13 +2724,13 @@
       <c r="G13" s="1">
         <v>2</v>
       </c>
-      <c r="H13" s="6" t="s">
+      <c r="H13" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="I13" s="6" t="s">
+      <c r="I13" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="J13" s="6" t="s">
+      <c r="J13" s="8" t="s">
         <v>32</v>
       </c>
       <c r="K13" s="1" t="s">
@@ -2538,13 +2753,13 @@
       <c r="G14" s="1">
         <v>2</v>
       </c>
-      <c r="H14" s="6" t="s">
+      <c r="H14" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="I14" s="6" t="s">
+      <c r="I14" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="J14" s="6" t="s">
+      <c r="J14" s="8" t="s">
         <v>32</v>
       </c>
       <c r="K14" s="1" t="s">
@@ -2567,13 +2782,13 @@
       <c r="G15" s="1">
         <v>1</v>
       </c>
-      <c r="H15" s="6" t="s">
+      <c r="H15" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="I15" s="6" t="s">
+      <c r="I15" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="J15" s="6" t="s">
+      <c r="J15" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K15" s="1" t="s">
@@ -2596,13 +2811,13 @@
       <c r="G16" s="1">
         <v>1</v>
       </c>
-      <c r="H16" s="6" t="s">
+      <c r="H16" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="I16" s="6" t="s">
+      <c r="I16" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="J16" s="6" t="s">
+      <c r="J16" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K16" s="1" t="s">
@@ -2625,13 +2840,13 @@
       <c r="G17" s="1">
         <v>1</v>
       </c>
-      <c r="H17" s="6" t="s">
+      <c r="H17" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="I17" s="6" t="s">
+      <c r="I17" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="J17" s="6" t="s">
+      <c r="J17" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K17" s="1" t="s">
@@ -2654,13 +2869,13 @@
       <c r="G18" s="1">
         <v>2</v>
       </c>
-      <c r="H18" s="6" t="s">
+      <c r="H18" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I18" s="6" t="s">
+      <c r="I18" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="J18" s="6" t="s">
+      <c r="J18" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K18" s="1" t="s">
@@ -2683,13 +2898,13 @@
       <c r="G19" s="1">
         <v>2</v>
       </c>
-      <c r="H19" s="6" t="s">
+      <c r="H19" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I19" s="6" t="s">
+      <c r="I19" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="J19" s="6" t="s">
+      <c r="J19" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K19" s="1" t="s">
@@ -2712,13 +2927,13 @@
       <c r="G20" s="1">
         <v>1</v>
       </c>
-      <c r="H20" s="6" t="s">
+      <c r="H20" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="I20" s="6" t="s">
+      <c r="I20" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="J20" s="6" t="s">
+      <c r="J20" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K20" s="1" t="s">
@@ -2741,13 +2956,13 @@
       <c r="G21" s="1">
         <v>1</v>
       </c>
-      <c r="H21" s="6" t="s">
+      <c r="H21" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="I21" s="6" t="s">
+      <c r="I21" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="J21" s="6" t="s">
+      <c r="J21" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K21" s="1" t="s">
@@ -2770,13 +2985,13 @@
       <c r="G22" s="1">
         <v>1</v>
       </c>
-      <c r="H22" s="6" t="s">
+      <c r="H22" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="I22" s="6" t="s">
+      <c r="I22" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="J22" s="6" t="s">
+      <c r="J22" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K22" s="1" t="s">
@@ -2799,13 +3014,13 @@
       <c r="G23" s="1">
         <v>2</v>
       </c>
-      <c r="H23" s="6" t="s">
+      <c r="H23" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="I23" s="6" t="s">
+      <c r="I23" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="J23" s="6" t="s">
+      <c r="J23" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K23" s="1" t="s">
@@ -2828,13 +3043,13 @@
       <c r="G24" s="1">
         <v>2</v>
       </c>
-      <c r="H24" s="6" t="s">
+      <c r="H24" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="I24" s="6" t="s">
+      <c r="I24" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="J24" s="6" t="s">
+      <c r="J24" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K24" s="1" t="s">
@@ -2857,13 +3072,13 @@
       <c r="G25" s="1">
         <v>2</v>
       </c>
-      <c r="H25" s="6" t="s">
+      <c r="H25" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="I25" s="6" t="s">
+      <c r="I25" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="J25" s="6" t="s">
+      <c r="J25" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K25" s="1" t="s">
@@ -2886,13 +3101,13 @@
       <c r="G26" s="1">
         <v>2</v>
       </c>
-      <c r="H26" s="6" t="s">
+      <c r="H26" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="I26" s="6" t="s">
+      <c r="I26" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="J26" s="6" t="s">
+      <c r="J26" s="8" t="s">
         <v>32</v>
       </c>
       <c r="K26" s="1" t="s">
@@ -2915,13 +3130,13 @@
       <c r="G27" s="1">
         <v>2</v>
       </c>
-      <c r="H27" s="6" t="s">
+      <c r="H27" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="I27" s="6" t="s">
+      <c r="I27" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="J27" s="6" t="s">
+      <c r="J27" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K27" s="1" t="s">
@@ -2944,13 +3159,13 @@
       <c r="G28" s="1">
         <v>2</v>
       </c>
-      <c r="H28" s="6" t="s">
+      <c r="H28" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="I28" s="6" t="s">
+      <c r="I28" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="J28" s="6" t="s">
+      <c r="J28" s="8" t="s">
         <v>82</v>
       </c>
       <c r="K28" s="1" t="s">
@@ -2973,13 +3188,13 @@
       <c r="G29" s="1">
         <v>2</v>
       </c>
-      <c r="H29" s="6" t="s">
+      <c r="H29" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="I29" s="6" t="s">
+      <c r="I29" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="J29" s="6" t="s">
+      <c r="J29" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K29" s="1" t="s">
@@ -3002,13 +3217,13 @@
       <c r="G30" s="1">
         <v>2</v>
       </c>
-      <c r="H30" s="6" t="s">
+      <c r="H30" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="I30" s="6" t="s">
+      <c r="I30" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="J30" s="6" t="s">
+      <c r="J30" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K30" s="1" t="s">
@@ -3031,13 +3246,13 @@
       <c r="G31" s="1">
         <v>2</v>
       </c>
-      <c r="H31" s="6" t="s">
+      <c r="H31" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="I31" s="6" t="s">
+      <c r="I31" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="J31" s="6" t="s">
+      <c r="J31" s="8" t="s">
         <v>91</v>
       </c>
       <c r="K31" s="1" t="s">
@@ -3060,13 +3275,13 @@
       <c r="G32" s="1">
         <v>2</v>
       </c>
-      <c r="H32" s="6" t="s">
+      <c r="H32" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="I32" s="6" t="s">
+      <c r="I32" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="J32" s="6" t="s">
+      <c r="J32" s="8" t="s">
         <v>32</v>
       </c>
       <c r="K32" s="1" t="s">
@@ -3089,13 +3304,13 @@
       <c r="G33" s="1">
         <v>2</v>
       </c>
-      <c r="H33" s="6" t="s">
+      <c r="H33" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="I33" s="7" t="s">
+      <c r="I33" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="J33" s="6" t="s">
+      <c r="J33" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K33" s="1" t="s">
@@ -3118,13 +3333,13 @@
       <c r="G34" s="1">
         <v>2</v>
       </c>
-      <c r="H34" s="6" t="s">
+      <c r="H34" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="I34" s="6" t="s">
+      <c r="I34" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="J34" s="6" t="s">
+      <c r="J34" s="8" t="s">
         <v>32</v>
       </c>
       <c r="K34" s="1" t="s">
@@ -3147,13 +3362,13 @@
       <c r="G35" s="1">
         <v>2</v>
       </c>
-      <c r="H35" s="6" t="s">
+      <c r="H35" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="I35" s="6" t="s">
+      <c r="I35" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="J35" s="6" t="s">
+      <c r="J35" s="8" t="s">
         <v>104</v>
       </c>
       <c r="K35" s="1" t="s">
@@ -3176,13 +3391,13 @@
       <c r="G36" s="1">
         <v>2</v>
       </c>
-      <c r="H36" s="6" t="s">
+      <c r="H36" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="I36" s="6" t="s">
+      <c r="I36" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="J36" s="6" t="s">
+      <c r="J36" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K36" s="1" t="s">
@@ -3205,13 +3420,13 @@
       <c r="G37" s="1">
         <v>2</v>
       </c>
-      <c r="H37" s="6" t="s">
+      <c r="H37" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="I37" s="6" t="s">
+      <c r="I37" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="J37" s="6" t="s">
+      <c r="J37" s="8" t="s">
         <v>110</v>
       </c>
       <c r="K37" s="1" t="s">
@@ -3234,13 +3449,13 @@
       <c r="G38" s="1">
         <v>2</v>
       </c>
-      <c r="H38" s="6" t="s">
+      <c r="H38" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="I38" s="6" t="s">
+      <c r="I38" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="J38" s="6" t="s">
+      <c r="J38" s="8" t="s">
         <v>114</v>
       </c>
       <c r="K38" s="1" t="s">
@@ -3265,13 +3480,13 @@
       <c r="G39">
         <v>2</v>
       </c>
-      <c r="H39" s="6" t="s">
+      <c r="H39" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="I39" s="6" t="s">
+      <c r="I39" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="J39" s="6" t="s">
+      <c r="J39" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K39" s="1" t="s">
@@ -3294,13 +3509,13 @@
       <c r="G40" s="1">
         <v>1</v>
       </c>
-      <c r="H40" s="6" t="s">
+      <c r="H40" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="I40" s="6" t="s">
+      <c r="I40" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="J40" s="6" t="s">
+      <c r="J40" s="8" t="s">
         <v>91</v>
       </c>
       <c r="K40" s="1" t="s">
@@ -3323,13 +3538,13 @@
       <c r="G41" s="4">
         <v>1</v>
       </c>
-      <c r="H41" s="6" t="s">
+      <c r="H41" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="I41" s="6" t="s">
+      <c r="I41" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="J41" s="6" t="s">
+      <c r="J41" s="8" t="s">
         <v>123</v>
       </c>
       <c r="K41" s="1" t="s">
@@ -3352,13 +3567,13 @@
       <c r="G42" s="1">
         <v>1</v>
       </c>
-      <c r="H42" s="6" t="s">
+      <c r="H42" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="I42" s="6" t="s">
+      <c r="I42" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="J42" s="6" t="s">
+      <c r="J42" s="8" t="s">
         <v>91</v>
       </c>
       <c r="K42" s="1" t="s">
@@ -3381,13 +3596,13 @@
       <c r="G43" s="1">
         <v>1</v>
       </c>
-      <c r="H43" s="6" t="s">
+      <c r="H43" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="I43" s="6" t="s">
+      <c r="I43" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="J43" s="6" t="s">
+      <c r="J43" s="8" t="s">
         <v>91</v>
       </c>
       <c r="K43" s="1" t="s">
@@ -3410,13 +3625,13 @@
       <c r="G44" s="1">
         <v>1</v>
       </c>
-      <c r="H44" s="6" t="s">
+      <c r="H44" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="I44" s="6" t="s">
+      <c r="I44" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="J44" s="6" t="s">
+      <c r="J44" s="8" t="s">
         <v>91</v>
       </c>
       <c r="K44" s="1" t="s">
@@ -3439,13 +3654,13 @@
       <c r="G45" s="1">
         <v>1</v>
       </c>
-      <c r="H45" s="6" t="s">
+      <c r="H45" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="I45" s="6" t="s">
+      <c r="I45" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="J45" s="6" t="s">
+      <c r="J45" s="8" t="s">
         <v>91</v>
       </c>
       <c r="K45" s="1" t="s">
@@ -3468,13 +3683,13 @@
       <c r="G46" s="1">
         <v>1</v>
       </c>
-      <c r="H46" s="6" t="s">
+      <c r="H46" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="I46" s="6" t="s">
+      <c r="I46" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="J46" s="6" t="s">
+      <c r="J46" s="8" t="s">
         <v>91</v>
       </c>
       <c r="K46" s="1" t="s">
@@ -3497,13 +3712,13 @@
       <c r="G47" s="1">
         <v>2</v>
       </c>
-      <c r="H47" s="6" t="s">
+      <c r="H47" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="I47" s="6" t="s">
+      <c r="I47" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="J47" s="6" t="s">
+      <c r="J47" s="8" t="s">
         <v>32</v>
       </c>
       <c r="K47" s="1" t="s">
@@ -3528,13 +3743,13 @@
       <c r="G48" s="4">
         <v>2</v>
       </c>
-      <c r="H48" s="6" t="s">
+      <c r="H48" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="I48" s="6" t="s">
+      <c r="I48" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="J48" s="6" t="s">
+      <c r="J48" s="8" t="s">
         <v>141</v>
       </c>
       <c r="K48" s="1" t="s">
@@ -3557,13 +3772,13 @@
       <c r="G49" s="1">
         <v>2</v>
       </c>
-      <c r="H49" s="6" t="s">
+      <c r="H49" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="I49" s="6" t="s">
+      <c r="I49" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="J49" s="6" t="s">
+      <c r="J49" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K49" s="1" t="s">
@@ -3601,13 +3816,13 @@
       <c r="G51" s="1">
         <v>2</v>
       </c>
-      <c r="H51" s="6" t="s">
+      <c r="H51" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="I51" s="6" t="s">
+      <c r="I51" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="J51" s="6" t="s">
+      <c r="J51" s="8" t="s">
         <v>141</v>
       </c>
       <c r="K51" s="1" t="s">
@@ -3632,13 +3847,13 @@
       <c r="G52" s="1">
         <v>2</v>
       </c>
-      <c r="H52" s="6" t="s">
+      <c r="H52" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="I52" s="6" t="s">
+      <c r="I52" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="J52" s="6" t="s">
+      <c r="J52" s="8" t="s">
         <v>141</v>
       </c>
       <c r="K52" s="1" t="s">
@@ -3663,13 +3878,13 @@
       <c r="G53" s="1">
         <v>2</v>
       </c>
-      <c r="H53" s="6" t="s">
+      <c r="H53" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="I53" s="6" t="s">
+      <c r="I53" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="J53" s="6" t="s">
+      <c r="J53" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K53" s="1" t="s">
@@ -3694,13 +3909,13 @@
       <c r="G54" s="1">
         <v>2</v>
       </c>
-      <c r="H54" s="6" t="s">
+      <c r="H54" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="I54" s="6" t="s">
+      <c r="I54" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="J54" s="6" t="s">
+      <c r="J54" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K54" s="1" t="s">
@@ -3725,13 +3940,13 @@
       <c r="G55" s="1">
         <v>2</v>
       </c>
-      <c r="H55" s="6" t="s">
+      <c r="H55" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="I55" s="6" t="s">
+      <c r="I55" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="J55" s="6" t="s">
+      <c r="J55" s="8" t="s">
         <v>91</v>
       </c>
       <c r="K55" s="1" t="s">
@@ -3754,13 +3969,13 @@
       <c r="G56" s="1">
         <v>2</v>
       </c>
-      <c r="H56" s="6" t="s">
+      <c r="H56" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="I56" s="6" t="s">
+      <c r="I56" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="J56" s="6" t="s">
+      <c r="J56" s="8" t="s">
         <v>159</v>
       </c>
       <c r="K56" s="1" t="s">
@@ -3783,13 +3998,13 @@
       <c r="G57" s="1">
         <v>2</v>
       </c>
-      <c r="H57" s="6" t="s">
+      <c r="H57" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="I57" s="6" t="s">
+      <c r="I57" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="J57" s="6" t="s">
+      <c r="J57" s="8" t="s">
         <v>32</v>
       </c>
       <c r="K57" s="1" t="s">
@@ -3812,13 +4027,13 @@
       <c r="G58" s="1">
         <v>2</v>
       </c>
-      <c r="H58" s="6" t="s">
+      <c r="H58" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="I58" s="6" t="s">
+      <c r="I58" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="J58" s="6" t="s">
+      <c r="J58" s="8" t="s">
         <v>91</v>
       </c>
       <c r="K58" s="1" t="s">
@@ -3841,13 +4056,13 @@
       <c r="G59" s="1">
         <v>2</v>
       </c>
-      <c r="H59" s="6" t="s">
+      <c r="H59" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="I59" s="6" t="s">
+      <c r="I59" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="J59" s="6" t="s">
+      <c r="J59" s="8" t="s">
         <v>169</v>
       </c>
       <c r="K59" s="1" t="s">
@@ -3870,13 +4085,13 @@
       <c r="G60" s="1">
         <v>2</v>
       </c>
-      <c r="H60" s="6" t="s">
+      <c r="H60" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="I60" s="6" t="s">
+      <c r="I60" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="J60" s="6" t="s">
+      <c r="J60" s="8" t="s">
         <v>159</v>
       </c>
       <c r="K60" s="1" t="s">
@@ -3899,13 +4114,13 @@
       <c r="G61" s="1">
         <v>2</v>
       </c>
-      <c r="H61" s="6" t="s">
+      <c r="H61" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="I61" s="6" t="s">
+      <c r="I61" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="J61" s="6" t="s">
+      <c r="J61" s="8" t="s">
         <v>159</v>
       </c>
       <c r="K61" s="1" t="s">
@@ -3928,13 +4143,13 @@
       <c r="G62" s="1">
         <v>2</v>
       </c>
-      <c r="H62" s="6" t="s">
+      <c r="H62" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="I62" s="6" t="s">
+      <c r="I62" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="J62" s="6" t="s">
+      <c r="J62" s="8" t="s">
         <v>169</v>
       </c>
       <c r="K62" s="1" t="s">
@@ -3957,13 +4172,13 @@
       <c r="G63" s="1">
         <v>2</v>
       </c>
-      <c r="H63" s="6" t="s">
+      <c r="H63" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="I63" s="6" t="s">
+      <c r="I63" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="J63" s="6" t="s">
+      <c r="J63" s="8" t="s">
         <v>169</v>
       </c>
       <c r="K63" s="1" t="s">
@@ -3986,13 +4201,13 @@
       <c r="G64" s="1">
         <v>2</v>
       </c>
-      <c r="H64" s="6" t="s">
+      <c r="H64" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="I64" s="6" t="s">
+      <c r="I64" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="J64" s="6" t="s">
+      <c r="J64" s="8" t="s">
         <v>169</v>
       </c>
       <c r="K64" s="1" t="s">
@@ -4015,13 +4230,13 @@
       <c r="G65" s="1">
         <v>2</v>
       </c>
-      <c r="H65" s="6" t="s">
+      <c r="H65" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="I65" s="6" t="s">
+      <c r="I65" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="J65" s="6" t="s">
+      <c r="J65" s="8" t="s">
         <v>169</v>
       </c>
       <c r="K65" s="1" t="s">
@@ -4044,13 +4259,13 @@
       <c r="G67" s="1">
         <v>1</v>
       </c>
-      <c r="H67" s="6" t="s">
+      <c r="H67" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="I67" s="6" t="s">
+      <c r="I67" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="J67" s="6" t="s">
+      <c r="J67" s="8" t="s">
         <v>185</v>
       </c>
       <c r="K67" s="1" t="s">
@@ -4073,13 +4288,13 @@
       <c r="G68" s="1">
         <v>2</v>
       </c>
-      <c r="H68" s="6" t="s">
+      <c r="H68" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="I68" s="6" t="s">
+      <c r="I68" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="J68" s="6" t="s">
+      <c r="J68" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K68" s="1" t="s">
@@ -4102,13 +4317,13 @@
       <c r="G69" s="1">
         <v>2</v>
       </c>
-      <c r="H69" s="6" t="s">
+      <c r="H69" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="I69" s="6" t="s">
+      <c r="I69" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="J69" s="6" t="s">
+      <c r="J69" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K69" s="1" t="s">
@@ -4131,13 +4346,13 @@
       <c r="G71" s="4">
         <v>2</v>
       </c>
-      <c r="H71" s="6" t="s">
+      <c r="H71" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="I71" s="6" t="s">
+      <c r="I71" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="J71" s="6" t="s">
+      <c r="J71" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K71" s="1" t="s">
@@ -4160,13 +4375,13 @@
       <c r="G72" s="4">
         <v>2</v>
       </c>
-      <c r="H72" s="6" t="s">
+      <c r="H72" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="I72" s="6" t="s">
+      <c r="I72" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="J72" s="6" t="s">
+      <c r="J72" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K72" s="1" t="s">
@@ -4189,13 +4404,13 @@
       <c r="G73" s="4">
         <v>2</v>
       </c>
-      <c r="H73" s="6" t="s">
+      <c r="H73" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="I73" s="6" t="s">
+      <c r="I73" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="J73" s="6" t="s">
+      <c r="J73" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K73" s="1" t="s">
@@ -4218,13 +4433,13 @@
       <c r="G74" s="4">
         <v>2</v>
       </c>
-      <c r="H74" s="6" t="s">
+      <c r="H74" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="I74" s="6" t="s">
+      <c r="I74" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="J74" s="6" t="s">
+      <c r="J74" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K74" s="1" t="s">
@@ -4247,13 +4462,13 @@
       <c r="G75" s="4">
         <v>2</v>
       </c>
-      <c r="H75" s="6" t="s">
+      <c r="H75" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="I75" s="6" t="s">
+      <c r="I75" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="J75" s="6" t="s">
+      <c r="J75" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K75" s="1" t="s">
@@ -4276,13 +4491,13 @@
       <c r="G76" s="4">
         <v>2</v>
       </c>
-      <c r="H76" s="6" t="s">
+      <c r="H76" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="I76" s="6" t="s">
+      <c r="I76" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J76" s="6" t="s">
+      <c r="J76" s="8" t="s">
         <v>91</v>
       </c>
       <c r="K76" s="1" t="s">
@@ -4305,13 +4520,13 @@
       <c r="G77" s="4">
         <v>2</v>
       </c>
-      <c r="H77" s="6" t="s">
+      <c r="H77" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="I77" s="6" t="s">
+      <c r="I77" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="J77" s="6" t="s">
+      <c r="J77" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K77" s="1" t="s">
@@ -4340,13 +4555,13 @@
       <c r="G79" s="4">
         <v>2</v>
       </c>
-      <c r="H79" s="6" t="s">
+      <c r="H79" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="I79" s="6" t="s">
+      <c r="I79" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="J79" s="6" t="s">
+      <c r="J79" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K79" s="4" t="s">
@@ -4375,13 +4590,13 @@
       <c r="G80" s="4">
         <v>2</v>
       </c>
-      <c r="H80" s="6" t="s">
+      <c r="H80" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="I80" s="6" t="s">
+      <c r="I80" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="J80" s="6" t="s">
+      <c r="J80" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K80" s="4" t="s">
@@ -4410,13 +4625,13 @@
       <c r="G81" s="4">
         <v>2</v>
       </c>
-      <c r="H81" s="6" t="s">
+      <c r="H81" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="I81" s="6" t="s">
+      <c r="I81" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="J81" s="6" t="s">
+      <c r="J81" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K81" s="4" t="s">
@@ -4445,13 +4660,13 @@
       <c r="G82" s="4">
         <v>2</v>
       </c>
-      <c r="H82" s="6" t="s">
+      <c r="H82" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="I82" s="6" t="s">
+      <c r="I82" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="J82" s="6" t="s">
+      <c r="J82" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K82" s="4" t="s">
@@ -4480,13 +4695,13 @@
       <c r="G83" s="4">
         <v>2</v>
       </c>
-      <c r="H83" s="6" t="s">
+      <c r="H83" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="I83" s="6" t="s">
+      <c r="I83" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="J83" s="6" t="s">
+      <c r="J83" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K83" s="4" t="s">
@@ -4515,13 +4730,13 @@
       <c r="G84" s="4">
         <v>2</v>
       </c>
-      <c r="H84" s="6" t="s">
+      <c r="H84" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="I84" s="6" t="s">
+      <c r="I84" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="J84" s="6" t="s">
+      <c r="J84" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K84" s="4" t="s">
@@ -4550,13 +4765,13 @@
       <c r="G85" s="4">
         <v>2</v>
       </c>
-      <c r="H85" s="6" t="s">
+      <c r="H85" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="I85" s="6" t="s">
+      <c r="I85" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="J85" s="6" t="s">
+      <c r="J85" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K85" s="1" t="s">
@@ -4585,13 +4800,13 @@
       <c r="G86" s="4">
         <v>2</v>
       </c>
-      <c r="H86" s="6" t="s">
+      <c r="H86" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="I86" s="6" t="s">
+      <c r="I86" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="J86" s="6" t="s">
+      <c r="J86" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K86" s="1" t="s">
@@ -4620,13 +4835,13 @@
       <c r="G87" s="4">
         <v>2</v>
       </c>
-      <c r="H87" s="6" t="s">
+      <c r="H87" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="I87" s="6" t="s">
+      <c r="I87" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="J87" s="6" t="s">
+      <c r="J87" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K87" s="1" t="s">
@@ -4655,13 +4870,13 @@
       <c r="G88" s="4">
         <v>2</v>
       </c>
-      <c r="H88" s="6" t="s">
+      <c r="H88" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="I88" s="6" t="s">
+      <c r="I88" s="8" t="s">
         <v>234</v>
       </c>
-      <c r="J88" s="6" t="s">
+      <c r="J88" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K88" s="1" t="s">
@@ -4690,13 +4905,13 @@
       <c r="G89" s="4">
         <v>2</v>
       </c>
-      <c r="H89" s="6" t="s">
+      <c r="H89" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="I89" s="6" t="s">
+      <c r="I89" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="J89" s="6" t="s">
+      <c r="J89" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K89" s="1" t="s">
@@ -4725,13 +4940,13 @@
       <c r="G91" s="4">
         <v>2</v>
       </c>
-      <c r="H91" s="6" t="s">
+      <c r="H91" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="I91" s="6" t="s">
+      <c r="I91" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="J91" s="6" t="s">
+      <c r="J91" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K91" s="1" t="s">
@@ -4760,13 +4975,13 @@
       <c r="G92" s="4">
         <v>2</v>
       </c>
-      <c r="H92" s="6" t="s">
+      <c r="H92" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="I92" s="6" t="s">
+      <c r="I92" s="8" t="s">
         <v>241</v>
       </c>
-      <c r="J92" s="6" t="s">
+      <c r="J92" s="8" t="s">
         <v>242</v>
       </c>
       <c r="K92" s="1" t="s">
@@ -4795,13 +5010,13 @@
       <c r="G93" s="4">
         <v>2</v>
       </c>
-      <c r="H93" s="6" t="s">
+      <c r="H93" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="I93" s="6" t="s">
+      <c r="I93" s="8" t="s">
         <v>244</v>
       </c>
-      <c r="J93" s="6" t="s">
+      <c r="J93" s="8" t="s">
         <v>242</v>
       </c>
       <c r="K93" s="1" t="s">
@@ -4824,13 +5039,13 @@
       <c r="G103" s="4">
         <v>2</v>
       </c>
-      <c r="H103" s="6" t="s">
+      <c r="H103" s="8" t="s">
         <v>246</v>
       </c>
-      <c r="I103" s="6" t="s">
+      <c r="I103" s="8" t="s">
         <v>247</v>
       </c>
-      <c r="J103" s="6" t="s">
+      <c r="J103" s="8" t="s">
         <v>32</v>
       </c>
       <c r="K103" s="1" t="s">
@@ -4853,13 +5068,13 @@
       <c r="G104" s="4">
         <v>2</v>
       </c>
-      <c r="H104" s="6" t="s">
+      <c r="H104" s="8" t="s">
         <v>246</v>
       </c>
-      <c r="I104" s="6" t="s">
+      <c r="I104" s="8" t="s">
         <v>250</v>
       </c>
-      <c r="J104" s="6" t="s">
+      <c r="J104" s="8" t="s">
         <v>32</v>
       </c>
       <c r="K104" s="1" t="s">
@@ -4882,13 +5097,13 @@
       <c r="G105" s="4">
         <v>2</v>
       </c>
-      <c r="H105" s="6" t="s">
+      <c r="H105" s="8" t="s">
         <v>246</v>
       </c>
-      <c r="I105" s="6" t="s">
+      <c r="I105" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="J105" s="6" t="s">
+      <c r="J105" s="8" t="s">
         <v>32</v>
       </c>
       <c r="K105" s="1" t="s">
@@ -4911,13 +5126,13 @@
       <c r="G106" s="4">
         <v>2</v>
       </c>
-      <c r="H106" s="6" t="s">
+      <c r="H106" s="8" t="s">
         <v>246</v>
       </c>
-      <c r="I106" s="6" t="s">
+      <c r="I106" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="J106" s="6" t="s">
+      <c r="J106" s="8" t="s">
         <v>32</v>
       </c>
       <c r="K106" s="1" t="s">
@@ -4940,13 +5155,13 @@
       <c r="G107" s="4">
         <v>2</v>
       </c>
-      <c r="H107" s="6" t="s">
+      <c r="H107" s="8" t="s">
         <v>246</v>
       </c>
-      <c r="I107" s="6" t="s">
+      <c r="I107" s="8" t="s">
         <v>259</v>
       </c>
-      <c r="J107" s="6" t="s">
+      <c r="J107" s="8" t="s">
         <v>32</v>
       </c>
       <c r="K107" s="1" t="s">
@@ -4969,13 +5184,13 @@
       <c r="G109" s="4">
         <v>2</v>
       </c>
-      <c r="H109" s="6" t="s">
+      <c r="H109" s="8" t="s">
         <v>261</v>
       </c>
-      <c r="I109" s="6" t="s">
+      <c r="I109" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="J109" s="6" t="s">
+      <c r="J109" s="8" t="s">
         <v>263</v>
       </c>
       <c r="K109" s="1" t="s">
@@ -4998,13 +5213,13 @@
       <c r="G110" s="4">
         <v>2</v>
       </c>
-      <c r="H110" s="6" t="s">
+      <c r="H110" s="8" t="s">
         <v>266</v>
       </c>
-      <c r="I110" s="6" t="s">
+      <c r="I110" s="8" t="s">
         <v>267</v>
       </c>
-      <c r="J110" s="6" t="s">
+      <c r="J110" s="8" t="s">
         <v>141</v>
       </c>
       <c r="K110" s="1" t="s">
@@ -5027,13 +5242,13 @@
       <c r="G111" s="4">
         <v>2</v>
       </c>
-      <c r="H111" s="6" t="s">
+      <c r="H111" s="8" t="s">
         <v>261</v>
       </c>
-      <c r="I111" s="6" t="s">
+      <c r="I111" s="8" t="s">
         <v>270</v>
       </c>
-      <c r="J111" s="6" t="s">
+      <c r="J111" s="8" t="s">
         <v>263</v>
       </c>
       <c r="K111" s="1" t="s">
@@ -5056,13 +5271,13 @@
       <c r="G112" s="4">
         <v>2</v>
       </c>
-      <c r="H112" s="6" t="s">
+      <c r="H112" s="8" t="s">
         <v>273</v>
       </c>
-      <c r="I112" s="6" t="s">
+      <c r="I112" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="J112" s="6" t="s">
+      <c r="J112" s="8" t="s">
         <v>263</v>
       </c>
       <c r="K112" s="1" t="s">
@@ -5085,13 +5300,13 @@
       <c r="G113" s="4">
         <v>2</v>
       </c>
-      <c r="H113" s="6" t="s">
+      <c r="H113" s="8" t="s">
         <v>246</v>
       </c>
-      <c r="I113" s="6" t="s">
+      <c r="I113" s="8" t="s">
         <v>276</v>
       </c>
-      <c r="J113" s="6" t="s">
+      <c r="J113" s="8" t="s">
         <v>263</v>
       </c>
       <c r="K113" s="1" t="s">
@@ -5114,13 +5329,13 @@
       <c r="G114" s="4">
         <v>2</v>
       </c>
-      <c r="H114" s="6" t="s">
+      <c r="H114" s="8" t="s">
         <v>246</v>
       </c>
-      <c r="I114" s="6" t="s">
+      <c r="I114" s="8" t="s">
         <v>278</v>
       </c>
-      <c r="J114" s="6" t="s">
+      <c r="J114" s="8" t="s">
         <v>263</v>
       </c>
       <c r="K114" s="1" t="s">
@@ -5129,7 +5344,7 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:E5 H3:K5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="H3:K5 C3:E5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="F3:G5" errorStyle="warning">
@@ -5145,7 +5360,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B3:L55"/>
+  <dimension ref="B3:L77"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="2"/>
@@ -5263,13 +5478,13 @@
       <c r="G6" s="1">
         <v>2</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="H6" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I6" s="6" t="s">
+      <c r="I6" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="J6" s="6" t="s">
+      <c r="J6" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K6" s="1" t="s">
@@ -5292,13 +5507,13 @@
       <c r="G7" s="1">
         <v>2</v>
       </c>
-      <c r="H7" s="6" t="s">
+      <c r="H7" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I7" s="6" t="s">
+      <c r="I7" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="J7" s="6" t="s">
+      <c r="J7" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K7" s="1" t="s">
@@ -5321,13 +5536,13 @@
       <c r="G8" s="1">
         <v>2</v>
       </c>
-      <c r="H8" s="6" t="s">
+      <c r="H8" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I8" s="6" t="s">
+      <c r="I8" s="8" t="s">
         <v>286</v>
       </c>
-      <c r="J8" s="6" t="s">
+      <c r="J8" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K8" s="1" t="s">
@@ -5350,13 +5565,13 @@
       <c r="G9" s="1">
         <v>2</v>
       </c>
-      <c r="H9" s="6" t="s">
+      <c r="H9" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I9" s="6" t="s">
+      <c r="I9" s="8" t="s">
         <v>289</v>
       </c>
-      <c r="J9" s="6" t="s">
+      <c r="J9" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K9" s="1" t="s">
@@ -5379,13 +5594,13 @@
       <c r="G10" s="1">
         <v>2</v>
       </c>
-      <c r="H10" s="6" t="s">
+      <c r="H10" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I10" s="6" t="s">
+      <c r="I10" s="8" t="s">
         <v>292</v>
       </c>
-      <c r="J10" s="6" t="s">
+      <c r="J10" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K10" s="1" t="s">
@@ -5408,13 +5623,13 @@
       <c r="G11" s="1">
         <v>2</v>
       </c>
-      <c r="H11" s="6" t="s">
+      <c r="H11" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I11" s="6" t="s">
+      <c r="I11" s="8" t="s">
         <v>295</v>
       </c>
-      <c r="J11" s="6" t="s">
+      <c r="J11" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K11" s="1" t="s">
@@ -5437,13 +5652,13 @@
       <c r="G12" s="1">
         <v>2</v>
       </c>
-      <c r="H12" s="6" t="s">
+      <c r="H12" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I12" s="6" t="s">
+      <c r="I12" s="8" t="s">
         <v>298</v>
       </c>
-      <c r="J12" s="6" t="s">
+      <c r="J12" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K12" s="1" t="s">
@@ -5466,13 +5681,13 @@
       <c r="G13" s="1">
         <v>2</v>
       </c>
-      <c r="H13" s="6" t="s">
+      <c r="H13" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I13" s="6" t="s">
+      <c r="I13" s="8" t="s">
         <v>301</v>
       </c>
-      <c r="J13" s="6" t="s">
+      <c r="J13" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K13" s="1" t="s">
@@ -5495,13 +5710,13 @@
       <c r="G14" s="1">
         <v>2</v>
       </c>
-      <c r="H14" s="6" t="s">
+      <c r="H14" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I14" s="6" t="s">
+      <c r="I14" s="8" t="s">
         <v>304</v>
       </c>
-      <c r="J14" s="6" t="s">
+      <c r="J14" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K14" s="1" t="s">
@@ -5524,13 +5739,13 @@
       <c r="G15" s="1">
         <v>2</v>
       </c>
-      <c r="H15" s="6" t="s">
+      <c r="H15" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I15" s="6" t="s">
+      <c r="I15" s="8" t="s">
         <v>307</v>
       </c>
-      <c r="J15" s="6" t="s">
+      <c r="J15" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K15" s="1" t="s">
@@ -5553,13 +5768,13 @@
       <c r="G16" s="1">
         <v>2</v>
       </c>
-      <c r="H16" s="6" t="s">
+      <c r="H16" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I16" s="6" t="s">
+      <c r="I16" s="8" t="s">
         <v>309</v>
       </c>
-      <c r="J16" s="6" t="s">
+      <c r="J16" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K16" s="1" t="s">
@@ -5582,13 +5797,13 @@
       <c r="G17" s="1">
         <v>2</v>
       </c>
-      <c r="H17" s="6" t="s">
+      <c r="H17" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I17" s="6" t="s">
+      <c r="I17" s="8" t="s">
         <v>311</v>
       </c>
-      <c r="J17" s="6" t="s">
+      <c r="J17" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K17" s="1" t="s">
@@ -5611,13 +5826,13 @@
       <c r="G18" s="1">
         <v>2</v>
       </c>
-      <c r="H18" s="6" t="s">
+      <c r="H18" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I18" s="6" t="s">
+      <c r="I18" s="8" t="s">
         <v>313</v>
       </c>
-      <c r="J18" s="6" t="s">
+      <c r="J18" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K18" s="1" t="s">
@@ -5640,13 +5855,13 @@
       <c r="G19" s="1">
         <v>2</v>
       </c>
-      <c r="H19" s="6" t="s">
+      <c r="H19" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I19" s="6" t="s">
+      <c r="I19" s="8" t="s">
         <v>315</v>
       </c>
-      <c r="J19" s="6" t="s">
+      <c r="J19" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K19" s="1" t="s">
@@ -5670,13 +5885,13 @@
       <c r="G21" s="1">
         <v>2</v>
       </c>
-      <c r="H21" s="6" t="s">
+      <c r="H21" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I21" s="6" t="s">
+      <c r="I21" s="8" t="s">
         <v>317</v>
       </c>
-      <c r="J21" s="6" t="s">
+      <c r="J21" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K21" s="1" t="s">
@@ -5699,13 +5914,13 @@
       <c r="G22" s="1">
         <v>2</v>
       </c>
-      <c r="H22" s="6" t="s">
+      <c r="H22" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I22" s="6" t="s">
+      <c r="I22" s="8" t="s">
         <v>320</v>
       </c>
-      <c r="J22" s="6" t="s">
+      <c r="J22" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K22" s="1" t="s">
@@ -5728,13 +5943,13 @@
       <c r="G23" s="1">
         <v>2</v>
       </c>
-      <c r="H23" s="6" t="s">
+      <c r="H23" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I23" s="6" t="s">
+      <c r="I23" s="8" t="s">
         <v>323</v>
       </c>
-      <c r="J23" s="6" t="s">
+      <c r="J23" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K23" s="1" t="s">
@@ -5757,13 +5972,13 @@
       <c r="G24" s="1">
         <v>2</v>
       </c>
-      <c r="H24" s="6" t="s">
+      <c r="H24" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I24" s="6" t="s">
+      <c r="I24" s="8" t="s">
         <v>326</v>
       </c>
-      <c r="J24" s="6" t="s">
+      <c r="J24" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K24" s="1" t="s">
@@ -5786,13 +6001,13 @@
       <c r="G25" s="1">
         <v>2</v>
       </c>
-      <c r="H25" s="6" t="s">
+      <c r="H25" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I25" s="6" t="s">
+      <c r="I25" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="J25" s="6" t="s">
+      <c r="J25" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K25" s="1" t="s">
@@ -5815,13 +6030,13 @@
       <c r="G26" s="1">
         <v>2</v>
       </c>
-      <c r="H26" s="6" t="s">
+      <c r="H26" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I26" s="6" t="s">
+      <c r="I26" s="8" t="s">
         <v>332</v>
       </c>
-      <c r="J26" s="6" t="s">
+      <c r="J26" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K26" s="1" t="s">
@@ -5844,13 +6059,13 @@
       <c r="G27" s="1">
         <v>2</v>
       </c>
-      <c r="H27" s="6" t="s">
+      <c r="H27" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I27" s="6" t="s">
+      <c r="I27" s="8" t="s">
         <v>335</v>
       </c>
-      <c r="J27" s="6" t="s">
+      <c r="J27" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K27" s="1" t="s">
@@ -5873,13 +6088,13 @@
       <c r="G28" s="1">
         <v>2</v>
       </c>
-      <c r="H28" s="6" t="s">
+      <c r="H28" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I28" s="6" t="s">
+      <c r="I28" s="8" t="s">
         <v>338</v>
       </c>
-      <c r="J28" s="6" t="s">
+      <c r="J28" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K28" s="1" t="s">
@@ -5902,13 +6117,13 @@
       <c r="G29" s="1">
         <v>2</v>
       </c>
-      <c r="H29" s="6" t="s">
+      <c r="H29" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I29" s="6" t="s">
+      <c r="I29" s="8" t="s">
         <v>341</v>
       </c>
-      <c r="J29" s="6" t="s">
+      <c r="J29" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K29" s="1" t="s">
@@ -5931,13 +6146,13 @@
       <c r="G30" s="1">
         <v>2</v>
       </c>
-      <c r="H30" s="6" t="s">
+      <c r="H30" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I30" s="6" t="s">
+      <c r="I30" s="8" t="s">
         <v>344</v>
       </c>
-      <c r="J30" s="6" t="s">
+      <c r="J30" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K30" s="1" t="s">
@@ -5960,13 +6175,13 @@
       <c r="G31" s="1">
         <v>2</v>
       </c>
-      <c r="H31" s="6" t="s">
+      <c r="H31" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I31" s="6" t="s">
+      <c r="I31" s="8" t="s">
         <v>347</v>
       </c>
-      <c r="J31" s="6" t="s">
+      <c r="J31" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K31" s="1" t="s">
@@ -5989,13 +6204,13 @@
       <c r="G32" s="1">
         <v>2</v>
       </c>
-      <c r="H32" s="6" t="s">
+      <c r="H32" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I32" s="6" t="s">
+      <c r="I32" s="8" t="s">
         <v>350</v>
       </c>
-      <c r="J32" s="6" t="s">
+      <c r="J32" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K32" s="1" t="s">
@@ -6031,17 +6246,17 @@
       <c r="G34" s="1">
         <v>2</v>
       </c>
-      <c r="H34" s="6" t="s">
+      <c r="H34" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="I34" s="8" t="s">
         <v>353</v>
       </c>
-      <c r="I34" s="6" t="s">
+      <c r="J34" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="K34" s="1" t="s">
         <v>354</v>
-      </c>
-      <c r="J34" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="K34" s="1" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="2:12">
@@ -6050,28 +6265,28 @@
         <v>1202</v>
       </c>
       <c r="D35" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="E35" s="1">
+        <v>1</v>
+      </c>
+      <c r="F35" s="4">
+        <v>0</v>
+      </c>
+      <c r="G35" s="1">
+        <v>2</v>
+      </c>
+      <c r="H35" s="8" t="s">
         <v>356</v>
       </c>
-      <c r="E35" s="1">
-        <v>1</v>
-      </c>
-      <c r="F35" s="4">
-        <v>0</v>
-      </c>
-      <c r="G35" s="1">
-        <v>2</v>
-      </c>
-      <c r="H35" s="6" t="s">
+      <c r="I35" s="8" t="s">
         <v>357</v>
       </c>
-      <c r="I35" s="6" t="s">
+      <c r="J35" s="8" t="s">
         <v>358</v>
       </c>
-      <c r="J35" s="6" t="s">
+      <c r="K35" s="1" t="s">
         <v>359</v>
-      </c>
-      <c r="K35" s="1" t="s">
-        <v>360</v>
       </c>
       <c r="L35" s="2"/>
     </row>
@@ -6081,28 +6296,28 @@
         <v>1203</v>
       </c>
       <c r="D36" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="E36" s="1">
+        <v>1</v>
+      </c>
+      <c r="F36" s="4">
+        <v>0</v>
+      </c>
+      <c r="G36" s="1">
+        <v>2</v>
+      </c>
+      <c r="H36" s="8" t="s">
         <v>361</v>
       </c>
-      <c r="E36" s="1">
-        <v>1</v>
-      </c>
-      <c r="F36" s="4">
-        <v>0</v>
-      </c>
-      <c r="G36" s="1">
-        <v>2</v>
-      </c>
-      <c r="H36" s="6" t="s">
+      <c r="I36" s="8" t="s">
         <v>362</v>
       </c>
-      <c r="I36" s="6" t="s">
+      <c r="J36" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="K36" s="1" t="s">
         <v>363</v>
-      </c>
-      <c r="J36" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="K36" s="1" t="s">
-        <v>364</v>
       </c>
       <c r="L36" s="2"/>
     </row>
@@ -6111,28 +6326,28 @@
         <v>1204</v>
       </c>
       <c r="D37" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="E37" s="1">
+        <v>1</v>
+      </c>
+      <c r="F37" s="4">
+        <v>0</v>
+      </c>
+      <c r="G37" s="1">
+        <v>2</v>
+      </c>
+      <c r="H37" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="I37" s="8" t="s">
         <v>365</v>
       </c>
-      <c r="E37" s="1">
-        <v>1</v>
-      </c>
-      <c r="F37" s="4">
-        <v>0</v>
-      </c>
-      <c r="G37" s="1">
-        <v>2</v>
-      </c>
-      <c r="H37" s="6" t="s">
-        <v>353</v>
-      </c>
-      <c r="I37" s="6" t="s">
+      <c r="J37" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="K37" s="1" t="s">
         <v>366</v>
-      </c>
-      <c r="J37" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="K37" s="1" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="2:12">
@@ -6140,28 +6355,28 @@
         <v>1205</v>
       </c>
       <c r="D38" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="E38" s="1">
+        <v>1</v>
+      </c>
+      <c r="F38" s="4">
+        <v>0</v>
+      </c>
+      <c r="G38" s="1">
+        <v>2</v>
+      </c>
+      <c r="H38" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="I38" s="8" t="s">
         <v>368</v>
       </c>
-      <c r="E38" s="1">
-        <v>1</v>
-      </c>
-      <c r="F38" s="4">
-        <v>0</v>
-      </c>
-      <c r="G38" s="1">
-        <v>2</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I38" s="6" t="s">
+      <c r="J38" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="K38" s="1" t="s">
         <v>369</v>
-      </c>
-      <c r="J38" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="K38" s="1" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="2:12">
@@ -6169,146 +6384,1082 @@
         <v>1206</v>
       </c>
       <c r="D39" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="E39" s="1">
+        <v>1</v>
+      </c>
+      <c r="F39" s="4">
+        <v>0</v>
+      </c>
+      <c r="G39" s="1">
+        <v>2</v>
+      </c>
+      <c r="H39" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="I39" s="8" t="s">
         <v>371</v>
       </c>
-      <c r="E39" s="1">
-        <v>1</v>
-      </c>
-      <c r="F39" s="4">
-        <v>0</v>
-      </c>
-      <c r="G39" s="1">
-        <v>2</v>
-      </c>
-      <c r="H39" s="6" t="s">
+      <c r="J39" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="K39" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="I39" s="6" t="s">
+    </row>
+    <row r="41" customHeight="1" spans="2:12">
+      <c r="C41" s="1">
+        <v>2001</v>
+      </c>
+      <c r="D41" s="5" t="s">
         <v>373</v>
       </c>
-      <c r="J39" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="K39" s="1" t="s">
+      <c r="E41" s="1">
+        <v>1</v>
+      </c>
+      <c r="F41" s="4">
+        <v>0</v>
+      </c>
+      <c r="G41" s="1">
+        <v>2</v>
+      </c>
+      <c r="H41" s="8" t="s">
         <v>374</v>
+      </c>
+      <c r="I41" s="8" t="s">
+        <v>375</v>
+      </c>
+      <c r="J41" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="K41" s="5" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="2:12">
+      <c r="C42" s="1">
+        <v>2002</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="E42" s="1">
+        <v>1</v>
+      </c>
+      <c r="F42" s="4">
+        <v>0</v>
+      </c>
+      <c r="G42" s="1">
+        <v>2</v>
+      </c>
+      <c r="H42" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="I42" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="J42" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="K42" s="5" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="2:12">
+      <c r="C43" s="1">
+        <v>2003</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="E43" s="1">
+        <v>1</v>
+      </c>
+      <c r="F43" s="4">
+        <v>0</v>
+      </c>
+      <c r="G43" s="1">
+        <v>2</v>
+      </c>
+      <c r="H43" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="I43" s="8" t="s">
+        <v>379</v>
+      </c>
+      <c r="J43" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="K43" s="5" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="2:12">
+      <c r="C44" s="1">
+        <v>2004</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="E44" s="1">
+        <v>1</v>
+      </c>
+      <c r="F44" s="4">
+        <v>0</v>
+      </c>
+      <c r="G44" s="1">
+        <v>2</v>
+      </c>
+      <c r="H44" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="I44" s="8" t="s">
+        <v>381</v>
+      </c>
+      <c r="J44" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="K44" s="5" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="2:12">
+      <c r="C45" s="1">
+        <v>2005</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="E45" s="1">
+        <v>1</v>
+      </c>
+      <c r="F45" s="4">
+        <v>0</v>
+      </c>
+      <c r="G45" s="1">
+        <v>2</v>
+      </c>
+      <c r="H45" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="I45" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="J45" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="K45" s="5" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="2:12">
+      <c r="C46" s="1">
+        <v>2006</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="E46" s="1">
+        <v>1</v>
+      </c>
+      <c r="F46" s="4">
+        <v>0</v>
+      </c>
+      <c r="G46" s="1">
+        <v>2</v>
+      </c>
+      <c r="H46" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="I46" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="J46" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="K46" s="5" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" customHeight="1" spans="2:12">
       <c r="B47" s="2"/>
-      <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
-      <c r="E47" s="2"/>
-      <c r="F47" s="2"/>
-      <c r="G47" s="2"/>
-      <c r="H47" s="2"/>
-      <c r="I47" s="2"/>
-      <c r="J47" s="2"/>
-      <c r="K47" s="2"/>
+      <c r="C47" s="1">
+        <v>2007</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="E47" s="1">
+        <v>1</v>
+      </c>
+      <c r="F47" s="4">
+        <v>0</v>
+      </c>
+      <c r="G47" s="1">
+        <v>2</v>
+      </c>
+      <c r="H47" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="I47" s="8" t="s">
+        <v>387</v>
+      </c>
+      <c r="J47" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="K47" s="5" t="s">
+        <v>386</v>
+      </c>
       <c r="L47" s="2"/>
     </row>
     <row r="48" s="1" customFormat="1" customHeight="1" spans="2:12">
       <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
-      <c r="E48" s="2"/>
-      <c r="F48" s="2"/>
-      <c r="G48" s="2"/>
-      <c r="H48" s="2"/>
-      <c r="I48" s="2"/>
-      <c r="J48" s="2"/>
-      <c r="K48" s="2"/>
+      <c r="C48" s="1">
+        <v>2008</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="E48" s="1">
+        <v>1</v>
+      </c>
+      <c r="F48" s="4">
+        <v>0</v>
+      </c>
+      <c r="G48" s="1">
+        <v>2</v>
+      </c>
+      <c r="H48" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="I48" s="8" t="s">
+        <v>389</v>
+      </c>
+      <c r="J48" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="K48" s="5" t="s">
+        <v>388</v>
+      </c>
       <c r="L48" s="2"/>
     </row>
     <row r="49" s="1" customFormat="1" customHeight="1" spans="2:12">
       <c r="B49" s="2"/>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
-      <c r="F49" s="2"/>
-      <c r="G49" s="2"/>
-      <c r="H49" s="2"/>
-      <c r="I49" s="2"/>
-      <c r="J49" s="2"/>
-      <c r="K49" s="2"/>
+      <c r="C49" s="1">
+        <v>2009</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="E49" s="1">
+        <v>1</v>
+      </c>
+      <c r="F49" s="4">
+        <v>0</v>
+      </c>
+      <c r="G49" s="1">
+        <v>2</v>
+      </c>
+      <c r="H49" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="I49" s="8" t="s">
+        <v>391</v>
+      </c>
+      <c r="J49" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="K49" s="5" t="s">
+        <v>390</v>
+      </c>
       <c r="L49" s="2"/>
     </row>
     <row r="50" s="1" customFormat="1" customHeight="1" spans="2:12">
       <c r="B50" s="2"/>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
-      <c r="E50" s="2"/>
-      <c r="F50" s="2"/>
-      <c r="G50" s="2"/>
-      <c r="H50" s="2"/>
-      <c r="I50" s="2"/>
-      <c r="J50" s="2"/>
-      <c r="K50" s="2"/>
+      <c r="C50" s="1">
+        <v>2010</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="E50" s="1">
+        <v>1</v>
+      </c>
+      <c r="F50" s="4">
+        <v>0</v>
+      </c>
+      <c r="G50" s="1">
+        <v>2</v>
+      </c>
+      <c r="H50" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="I50" s="8" t="s">
+        <v>393</v>
+      </c>
+      <c r="J50" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="K50" s="5" t="s">
+        <v>392</v>
+      </c>
       <c r="L50" s="2"/>
     </row>
     <row r="51" s="1" customFormat="1" customHeight="1" spans="2:12">
       <c r="B51" s="2"/>
-      <c r="C51" s="2"/>
-      <c r="D51" s="2"/>
-      <c r="E51" s="2"/>
-      <c r="F51" s="2"/>
-      <c r="G51" s="2"/>
-      <c r="H51" s="2"/>
-      <c r="I51" s="2"/>
-      <c r="J51" s="2"/>
-      <c r="K51" s="2"/>
+      <c r="C51" s="1">
+        <v>2011</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="E51" s="1">
+        <v>1</v>
+      </c>
+      <c r="F51" s="4">
+        <v>0</v>
+      </c>
+      <c r="G51" s="1">
+        <v>2</v>
+      </c>
+      <c r="H51" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="I51" s="8" t="s">
+        <v>395</v>
+      </c>
+      <c r="J51" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="K51" s="5" t="s">
+        <v>394</v>
+      </c>
       <c r="L51" s="2"/>
     </row>
     <row r="52" s="1" customFormat="1" customHeight="1" spans="2:12">
       <c r="B52" s="2"/>
-      <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
-      <c r="E52" s="2"/>
-      <c r="F52" s="2"/>
-      <c r="G52" s="2"/>
-      <c r="H52" s="2"/>
-      <c r="I52" s="2"/>
-      <c r="J52" s="2"/>
-      <c r="K52" s="2"/>
+      <c r="C52" s="1">
+        <v>2012</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="E52" s="1">
+        <v>1</v>
+      </c>
+      <c r="F52" s="4">
+        <v>0</v>
+      </c>
+      <c r="G52" s="1">
+        <v>2</v>
+      </c>
+      <c r="H52" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="I52" s="8" t="s">
+        <v>397</v>
+      </c>
+      <c r="J52" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="K52" s="5" t="s">
+        <v>396</v>
+      </c>
       <c r="L52" s="2"/>
     </row>
     <row r="53" s="1" customFormat="1" customHeight="1" spans="2:12">
       <c r="B53" s="2"/>
-      <c r="C53" s="2"/>
-      <c r="D53" s="2"/>
-      <c r="E53" s="2"/>
-      <c r="F53" s="2"/>
-      <c r="G53" s="2"/>
-      <c r="H53" s="2"/>
-      <c r="I53" s="2"/>
-      <c r="J53" s="2"/>
-      <c r="K53" s="2"/>
+      <c r="C53" s="1"/>
+      <c r="D53" s="1"/>
+      <c r="E53" s="1"/>
+      <c r="F53" s="1"/>
+      <c r="G53" s="1"/>
+      <c r="H53" s="1"/>
+      <c r="I53" s="1"/>
+      <c r="K53" s="5"/>
       <c r="L53" s="2"/>
     </row>
     <row r="54" s="1" customFormat="1" customHeight="1" spans="2:12">
       <c r="B54" s="2"/>
-      <c r="C54" s="2"/>
-      <c r="D54" s="2"/>
-      <c r="E54" s="2"/>
-      <c r="F54" s="2"/>
-      <c r="G54" s="2"/>
-      <c r="H54" s="2"/>
-      <c r="I54" s="2"/>
-      <c r="J54" s="2"/>
-      <c r="K54" s="2"/>
+      <c r="C54" s="1">
+        <v>2013</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>398</v>
+      </c>
+      <c r="E54" s="1">
+        <v>1</v>
+      </c>
+      <c r="F54" s="4">
+        <v>0</v>
+      </c>
+      <c r="G54" s="1">
+        <v>2</v>
+      </c>
+      <c r="H54" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="I54" s="8" t="s">
+        <v>399</v>
+      </c>
+      <c r="J54" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="K54" s="6" t="s">
+        <v>398</v>
+      </c>
       <c r="L54" s="2"/>
     </row>
     <row r="55" s="1" customFormat="1" customHeight="1" spans="2:12">
       <c r="B55" s="2"/>
-      <c r="C55" s="2"/>
-      <c r="D55" s="2"/>
-      <c r="E55" s="2"/>
-      <c r="F55" s="2"/>
-      <c r="G55" s="2"/>
-      <c r="H55" s="2"/>
-      <c r="I55" s="2"/>
-      <c r="J55" s="2"/>
-      <c r="K55" s="2"/>
+      <c r="C55" s="1">
+        <v>2014</v>
+      </c>
+      <c r="D55" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="E55" s="1">
+        <v>1</v>
+      </c>
+      <c r="F55" s="4">
+        <v>0</v>
+      </c>
+      <c r="G55" s="1">
+        <v>2</v>
+      </c>
+      <c r="H55" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="I55" s="8" t="s">
+        <v>401</v>
+      </c>
+      <c r="J55" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="K55" s="6" t="s">
+        <v>400</v>
+      </c>
       <c r="L55" s="2"/>
+    </row>
+    <row r="56" customHeight="1" spans="2:12">
+      <c r="C56" s="1">
+        <v>2015</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="E56" s="1">
+        <v>1</v>
+      </c>
+      <c r="F56" s="4">
+        <v>0</v>
+      </c>
+      <c r="G56" s="1">
+        <v>2</v>
+      </c>
+      <c r="H56" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="I56" s="8" t="s">
+        <v>403</v>
+      </c>
+      <c r="J56" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="K56" s="6" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="2:12">
+      <c r="C57" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="E57" s="1">
+        <v>1</v>
+      </c>
+      <c r="F57" s="4">
+        <v>0</v>
+      </c>
+      <c r="G57" s="1">
+        <v>2</v>
+      </c>
+      <c r="H57" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="I57" s="8" t="s">
+        <v>405</v>
+      </c>
+      <c r="J57" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="K57" s="6" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="2:12">
+      <c r="C58" s="1">
+        <v>2017</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="E58" s="1">
+        <v>1</v>
+      </c>
+      <c r="F58" s="4">
+        <v>0</v>
+      </c>
+      <c r="G58" s="1">
+        <v>2</v>
+      </c>
+      <c r="H58" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="I58" s="8" t="s">
+        <v>407</v>
+      </c>
+      <c r="J58" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="K58" s="6" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="59" customHeight="1" spans="2:12">
+      <c r="C59" s="1">
+        <v>2018</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="E59" s="1">
+        <v>1</v>
+      </c>
+      <c r="F59" s="4">
+        <v>0</v>
+      </c>
+      <c r="G59" s="1">
+        <v>2</v>
+      </c>
+      <c r="H59" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="I59" s="8" t="s">
+        <v>409</v>
+      </c>
+      <c r="J59" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="K59" s="6" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="60" customHeight="1" spans="2:12">
+      <c r="C60" s="1">
+        <v>2019</v>
+      </c>
+      <c r="D60" s="6" t="s">
+        <v>410</v>
+      </c>
+      <c r="E60" s="1">
+        <v>1</v>
+      </c>
+      <c r="F60" s="4">
+        <v>0</v>
+      </c>
+      <c r="G60" s="1">
+        <v>2</v>
+      </c>
+      <c r="H60" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="I60" s="8" t="s">
+        <v>411</v>
+      </c>
+      <c r="J60" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="K60" s="6" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="61" customHeight="1" spans="2:12">
+      <c r="C61" s="1">
+        <v>2020</v>
+      </c>
+      <c r="D61" s="6" t="s">
+        <v>412</v>
+      </c>
+      <c r="E61" s="1">
+        <v>1</v>
+      </c>
+      <c r="F61" s="4">
+        <v>0</v>
+      </c>
+      <c r="G61" s="1">
+        <v>2</v>
+      </c>
+      <c r="H61" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="I61" s="8" t="s">
+        <v>413</v>
+      </c>
+      <c r="J61" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="K61" s="6" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="62" customHeight="1" spans="2:12">
+      <c r="C62" s="1">
+        <v>2021</v>
+      </c>
+      <c r="D62" s="6" t="s">
+        <v>414</v>
+      </c>
+      <c r="E62" s="1">
+        <v>1</v>
+      </c>
+      <c r="F62" s="4">
+        <v>0</v>
+      </c>
+      <c r="G62" s="1">
+        <v>2</v>
+      </c>
+      <c r="H62" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="I62" s="8" t="s">
+        <v>415</v>
+      </c>
+      <c r="J62" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="K62" s="6" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="63" customHeight="1" spans="2:12">
+      <c r="C63" s="1">
+        <v>2022</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="E63" s="1">
+        <v>1</v>
+      </c>
+      <c r="F63" s="4">
+        <v>0</v>
+      </c>
+      <c r="G63" s="1">
+        <v>2</v>
+      </c>
+      <c r="H63" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="I63" s="8" t="s">
+        <v>417</v>
+      </c>
+      <c r="J63" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="K63" s="6" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="64" customHeight="1" spans="2:12">
+      <c r="C64" s="1">
+        <v>2023</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="E64" s="1">
+        <v>1</v>
+      </c>
+      <c r="F64" s="4">
+        <v>0</v>
+      </c>
+      <c r="G64" s="1">
+        <v>2</v>
+      </c>
+      <c r="H64" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="I64" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="J64" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="K64" s="6" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="65" customHeight="1" spans="3:11">
+      <c r="C65" s="1">
+        <v>2024</v>
+      </c>
+      <c r="D65" s="6" t="s">
+        <v>420</v>
+      </c>
+      <c r="E65" s="1">
+        <v>1</v>
+      </c>
+      <c r="F65" s="4">
+        <v>0</v>
+      </c>
+      <c r="G65" s="1">
+        <v>2</v>
+      </c>
+      <c r="H65" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="I65" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="J65" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="K65" s="6" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="66" customHeight="1" spans="3:11">
+      <c r="C66" s="1">
+        <v>2025</v>
+      </c>
+      <c r="D66" s="6" t="s">
+        <v>422</v>
+      </c>
+      <c r="E66" s="1">
+        <v>1</v>
+      </c>
+      <c r="F66" s="4">
+        <v>0</v>
+      </c>
+      <c r="G66" s="1">
+        <v>2</v>
+      </c>
+      <c r="H66" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="I66" s="8" t="s">
+        <v>423</v>
+      </c>
+      <c r="J66" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="K66" s="6" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="67" customHeight="1" spans="3:11">
+      <c r="C67" s="1"/>
+      <c r="D67" s="6"/>
+      <c r="E67" s="1"/>
+      <c r="F67" s="1"/>
+      <c r="G67" s="1"/>
+      <c r="H67" s="1"/>
+      <c r="I67" s="1"/>
+      <c r="K67" s="6"/>
+    </row>
+    <row r="68" customHeight="1" spans="3:11">
+      <c r="C68" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D68" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="E68" s="1">
+        <v>1</v>
+      </c>
+      <c r="F68" s="4">
+        <v>0</v>
+      </c>
+      <c r="G68" s="1">
+        <v>2</v>
+      </c>
+      <c r="H68" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="I68" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="J68" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="K68" s="6" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="69" customHeight="1" spans="3:11">
+      <c r="C69" s="1">
+        <v>2027</v>
+      </c>
+      <c r="D69" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="E69" s="1">
+        <v>1</v>
+      </c>
+      <c r="F69" s="4">
+        <v>0</v>
+      </c>
+      <c r="G69" s="1">
+        <v>2</v>
+      </c>
+      <c r="H69" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="I69" s="8" t="s">
+        <v>427</v>
+      </c>
+      <c r="J69" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="K69" s="6" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="70" customHeight="1" spans="3:11">
+      <c r="C70" s="1">
+        <v>2028</v>
+      </c>
+      <c r="D70" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="E70" s="1">
+        <v>1</v>
+      </c>
+      <c r="F70" s="4">
+        <v>0</v>
+      </c>
+      <c r="G70" s="1">
+        <v>2</v>
+      </c>
+      <c r="H70" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="I70" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="J70" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="K70" s="6" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="71" customHeight="1" spans="3:11">
+      <c r="C71" s="1">
+        <v>2029</v>
+      </c>
+      <c r="D71" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="E71" s="1">
+        <v>1</v>
+      </c>
+      <c r="F71" s="4">
+        <v>0</v>
+      </c>
+      <c r="G71" s="1">
+        <v>2</v>
+      </c>
+      <c r="H71" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="I71" s="8" t="s">
+        <v>431</v>
+      </c>
+      <c r="J71" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="K71" s="6" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="72" customHeight="1" spans="3:11">
+      <c r="C72" s="1">
+        <v>2030</v>
+      </c>
+      <c r="D72" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="E72" s="1">
+        <v>1</v>
+      </c>
+      <c r="F72" s="4">
+        <v>0</v>
+      </c>
+      <c r="G72" s="1">
+        <v>2</v>
+      </c>
+      <c r="H72" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="I72" s="8" t="s">
+        <v>433</v>
+      </c>
+      <c r="J72" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="K72" s="6" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="73" customHeight="1" spans="3:11">
+      <c r="C73" s="1">
+        <v>2031</v>
+      </c>
+      <c r="D73" s="6" t="s">
+        <v>434</v>
+      </c>
+      <c r="E73" s="1">
+        <v>1</v>
+      </c>
+      <c r="F73" s="4">
+        <v>0</v>
+      </c>
+      <c r="G73" s="1">
+        <v>2</v>
+      </c>
+      <c r="H73" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="I73" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="J73" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="K73" s="6" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="74" customHeight="1" spans="3:11">
+      <c r="C74" s="1">
+        <v>2032</v>
+      </c>
+      <c r="D74" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="E74" s="1">
+        <v>1</v>
+      </c>
+      <c r="F74" s="4">
+        <v>0</v>
+      </c>
+      <c r="G74" s="1">
+        <v>2</v>
+      </c>
+      <c r="H74" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="I74" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="J74" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="K74" s="6" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="75" customHeight="1" spans="3:11">
+      <c r="C75" s="1">
+        <v>2033</v>
+      </c>
+      <c r="D75" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="E75" s="1">
+        <v>1</v>
+      </c>
+      <c r="F75" s="4">
+        <v>0</v>
+      </c>
+      <c r="G75" s="1">
+        <v>2</v>
+      </c>
+      <c r="H75" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="I75" s="8" t="s">
+        <v>439</v>
+      </c>
+      <c r="J75" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="K75" s="6" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="76" customHeight="1" spans="3:11">
+      <c r="C76" s="1">
+        <v>2034</v>
+      </c>
+      <c r="D76" s="6" t="s">
+        <v>440</v>
+      </c>
+      <c r="E76" s="1">
+        <v>1</v>
+      </c>
+      <c r="F76" s="4">
+        <v>0</v>
+      </c>
+      <c r="G76" s="1">
+        <v>2</v>
+      </c>
+      <c r="H76" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="I76" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="J76" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="K76" s="6" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="77" customHeight="1" spans="3:11">
+      <c r="C77" s="1">
+        <v>2035</v>
+      </c>
+      <c r="D77" s="6" t="s">
+        <v>442</v>
+      </c>
+      <c r="E77" s="1">
+        <v>1</v>
+      </c>
+      <c r="F77" s="4">
+        <v>0</v>
+      </c>
+      <c r="G77" s="1">
+        <v>2</v>
+      </c>
+      <c r="H77" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="I77" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="J77" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="K77" s="6" t="s">
+        <v>442</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -1199,7 +1199,7 @@
     <t>道士8阶以上</t>
   </si>
   <si>
-    <t>2032,2033,2034,2034</t>
+    <t>2032,2033,2034,2035</t>
   </si>
   <si>
     <t>无极道体，道士之魂，召唤白虎 对应的词条</t>
@@ -5344,7 +5344,7 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="H3:K5 C3:E5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:E5 H3:K5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="F3:G5" errorStyle="warning">

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="887" uniqueCount="444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="446">
   <si>
     <t>_id</t>
   </si>
@@ -140,7 +140,7 @@
     <t>破魂专属自选</t>
   </si>
   <si>
-    <t>201,202,203,204,205,206</t>
+    <t>231,232,233,234,235,236</t>
   </si>
   <si>
     <t>血刃专属自选</t>
@@ -179,7 +179,7 @@
     <t>3,3,3</t>
   </si>
   <si>
-    <t>1008,2008,3008</t>
+    <t>1008,2308,3008</t>
   </si>
   <si>
     <t>1,1,1</t>
@@ -191,7 +191,7 @@
     <t>9介技能自选</t>
   </si>
   <si>
-    <t>1009,2009,3009</t>
+    <t>1009,2309,3009</t>
   </si>
   <si>
     <t>开天，流星，月灵 三选一</t>
@@ -224,7 +224,7 @@
     <t>幽冥时装包</t>
   </si>
   <si>
-    <t>3000017,3000018,3000019,3000020,3000021,3000022,3000023,3000024</t>
+    <t>3000017,3000021,3000022,3000023,3000021,3000022,3000023,3000024</t>
   </si>
   <si>
     <t>幽冥时装一套</t>
@@ -239,13 +239,13 @@
     <t>节日冰咆哮专属自选包</t>
   </si>
   <si>
-    <t>2024春节盖楼专属</t>
+    <t>2324春节盖楼专属</t>
   </si>
   <si>
     <t>801,802,803,804,805,806</t>
   </si>
   <si>
-    <t>2024春节盖楼专属自选包</t>
+    <t>2324春节盖楼专属自选包</t>
   </si>
   <si>
     <t>战魂时装包</t>
@@ -278,10 +278,10 @@
     <t>法宝自选</t>
   </si>
   <si>
-    <t>18,18,18,18,18,18</t>
-  </si>
-  <si>
-    <t>180007,180009,180001,180002,180004,180005</t>
+    <t>21,21,21,21,21,21</t>
+  </si>
+  <si>
+    <t>210007,210009,210001,210002,210004,210005</t>
   </si>
   <si>
     <t>特殊法宝自选</t>
@@ -317,10 +317,10 @@
     <t>特戒自选</t>
   </si>
   <si>
-    <t>19,19,19,19,19,19,19</t>
-  </si>
-  <si>
-    <t>190001,190002,190003,190004,190005,190006</t>
+    <t>22,22,22,22,22,22,22</t>
+  </si>
+  <si>
+    <t>223001,223002,223003,223004,223005,223006</t>
   </si>
   <si>
     <t>升级自选</t>
@@ -329,7 +329,7 @@
     <t>12,12,12,12,12,12,12,12,12,12,12,12</t>
   </si>
   <si>
-    <t>807,808,813,816,809,810,814,817,811,812,815,818</t>
+    <t>807,808,813,816,809,810,814,817,811,812,815,821</t>
   </si>
   <si>
     <t>1,1,1,1,1,1,1,1,1,1,1,1,1,1</t>
@@ -338,13 +338,13 @@
     <t>初级法宝自选</t>
   </si>
   <si>
-    <t>180006,180011,180012,180013,180020,180021</t>
-  </si>
-  <si>
-    <t>18,18,18,18,18,18,18,18,18</t>
-  </si>
-  <si>
-    <t>180001,180002,180004,180005,180007,180008,180009,180018,180019</t>
+    <t>210006,210011,210012,210013,210023,210021</t>
+  </si>
+  <si>
+    <t>21,21,21,21,21,21,21,21,21</t>
+  </si>
+  <si>
+    <t>210001,210002,210004,210005,210007,210008,210009,210021,210022</t>
   </si>
   <si>
     <t>1,1,1,1,1,1,1,1,1</t>
@@ -365,7 +365,7 @@
     <t>10阶技能自选</t>
   </si>
   <si>
-    <t>1010,2010,3010</t>
+    <t>1010,2310,3010</t>
   </si>
   <si>
     <t>地钉，分身，无极 三选一</t>
@@ -383,7 +383,7 @@
     <t>11阶技能自选</t>
   </si>
   <si>
-    <t>1011,2011,3011</t>
+    <t>1011,2311,3011</t>
   </si>
   <si>
     <t>战魂，法魂，道魂 三选一</t>
@@ -392,10 +392,10 @@
     <t>极矿工礼包</t>
   </si>
   <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>180030</t>
+    <t>21</t>
+  </si>
+  <si>
+    <t>210030</t>
   </si>
   <si>
     <t>1</t>
@@ -404,7 +404,7 @@
     <t>极法宝自选</t>
   </si>
   <si>
-    <t>180032,180034,180035,180036,180038,180039</t>
+    <t>210032,210034,210035,210036,210038,210039</t>
   </si>
   <si>
     <t>普通金宠包</t>
@@ -413,7 +413,7 @@
     <t>4,5</t>
   </si>
   <si>
-    <t>207,4022</t>
+    <t>237,4022</t>
   </si>
   <si>
     <t>2,100000</t>
@@ -425,10 +425,10 @@
     <t>满资质金宠包</t>
   </si>
   <si>
-    <t>209,4022</t>
-  </si>
-  <si>
-    <t>2,200000</t>
+    <t>239,4022</t>
+  </si>
+  <si>
+    <t>2,230000</t>
   </si>
   <si>
     <t>2个50资质金宠+5w口粮</t>
@@ -437,7 +437,7 @@
     <t>新手法宝自选</t>
   </si>
   <si>
-    <t>180006,180008,180010,180018,180020,180021</t>
+    <t>210006,210008,210010,210021,210023,210021</t>
   </si>
   <si>
     <t>青龙神器自选</t>
@@ -467,7 +467,7 @@
     <t>朱雀神器自选</t>
   </si>
   <si>
-    <t>61000017,61000018,61000019,61000020,61000021,61000022,61000023,61000024</t>
+    <t>61000017,61000021,61000022,61000023,61000021,61000022,61000023,61000024</t>
   </si>
   <si>
     <t>玄武神器自选</t>
@@ -494,7 +494,7 @@
     <t>12阶技能自选</t>
   </si>
   <si>
-    <t>1012,2012,3012</t>
+    <t>1012,2312,3012</t>
   </si>
   <si>
     <t>12技能三选一</t>
@@ -515,7 +515,7 @@
     <t>极戒自选</t>
   </si>
   <si>
-    <t>190007,190008,190009,190010,190011,190012</t>
+    <t>223007,223008,223009,223010,223011,223012</t>
   </si>
   <si>
     <t>粉色专属自选</t>
@@ -524,7 +524,7 @@
     <t>4,4,4,4,4,4</t>
   </si>
   <si>
-    <t>1201,1202,1203,1204,1205,1206</t>
+    <t>1231,1232,1233,1234,1235,1236</t>
   </si>
   <si>
     <t>暗金专属自选</t>
@@ -623,7 +623,7 @@
     <t>道力盾4件套</t>
   </si>
   <si>
-    <t>18,19,20,21,4005,4010</t>
+    <t>21,22,23,21,4005,4010</t>
   </si>
   <si>
     <t>月神4件套</t>
@@ -641,22 +641,22 @@
     <t>4014,4012,4001,4011,4102,4010</t>
   </si>
   <si>
-    <t>500,2000,10000000,20,200,50</t>
-  </si>
-  <si>
-    <t>经验丹0.5K,传世精华2k,魂环碎片1KW,红装精华3,高级书页200个,专属之心50个</t>
+    <t>500,2300,10000000,23,230,50</t>
+  </si>
+  <si>
+    <t>经验丹0.5K,传世精华2k,魂环碎片1KW,红装精华3,高级书页230个,专属之心50个</t>
   </si>
   <si>
     <t>黄金礼包</t>
   </si>
   <si>
-    <t>180005,180006,180018,180002,180004,180008</t>
+    <t>210005,210006,210021,210002,210004,210008</t>
   </si>
   <si>
     <t>钻石礼包</t>
   </si>
   <si>
-    <t>180007,180009,180001,180002,180004,180019</t>
+    <t>210007,210009,210001,210002,210004,210022</t>
   </si>
   <si>
     <t>高级法宝自选</t>
@@ -665,7 +665,7 @@
     <t>战士经验红装</t>
   </si>
   <si>
-    <t>20,20,20,20,20,20,20,20</t>
+    <t>23,23,23,23,23,23,23,23</t>
   </si>
   <si>
     <t>1,2,3,4,5,6,7,8</t>
@@ -686,7 +686,7 @@
     <t>道士经验红装</t>
   </si>
   <si>
-    <t>17,18,19,20,21,22,23,24</t>
+    <t>17,21,22,23,21,22,23,24</t>
   </si>
   <si>
     <t>道士满经验红装自选</t>
@@ -713,7 +713,7 @@
     <t>道士输出红装</t>
   </si>
   <si>
-    <t>20,20,20,20,20,20,20,20,20,20</t>
+    <t>23,23,23,23,23,23,23,23,23,23</t>
   </si>
   <si>
     <t>41,42,43,44,45,46,47,48,49,50</t>
@@ -764,7 +764,7 @@
     <t>道士平衡金装</t>
   </si>
   <si>
-    <t>117,118,119,120,121,122,123,124</t>
+    <t>117,121,122,123,121,122,123,124</t>
   </si>
   <si>
     <t>战士防御金装</t>
@@ -782,19 +782,28 @@
     <t>粉色战士</t>
   </si>
   <si>
-    <t>181,182,183,184,185,186,187,188</t>
+    <t>211,212,213,214,215,216,217,218</t>
   </si>
   <si>
     <t>粉色法师</t>
   </si>
   <si>
-    <t>191,192,193,194,195,196,197,198</t>
+    <t>221,222,223,224,225,226,227,228</t>
   </si>
   <si>
     <t>粉色道士</t>
   </si>
   <si>
-    <t>201,202,203,204,205,206,207,208</t>
+    <t>231,232,233,234,235,236,237,238</t>
+  </si>
+  <si>
+    <t>青色战士</t>
+  </si>
+  <si>
+    <t>青色法师</t>
+  </si>
+  <si>
+    <t>青色道士</t>
   </si>
   <si>
     <t>金装自选</t>
@@ -809,7 +818,7 @@
     <t>4,4,4</t>
   </si>
   <si>
-    <t>118,119,120</t>
+    <t>121,122,123</t>
   </si>
   <si>
     <t>1,1,1,</t>
@@ -872,7 +881,7 @@
     <t>21,21,21,21,21,21,21,21,21,21,21,21</t>
   </si>
   <si>
-    <t>19,20,21,22,23,24,25,26,27,28,29,30</t>
+    <t>22,23,21,22,23,24,25,26,27,28,29,30</t>
   </si>
   <si>
     <t>1,1,1,1,1,1,1,1,1,1,1,1</t>
@@ -887,7 +896,7 @@
     <t>21,21,21,21,21,21,21,21,21,21,21,21,21,21,21</t>
   </si>
   <si>
-    <t>16,17,18,101,102,103,104,105,106,107,108,109</t>
+    <t>16,17,21,101,102,103,104,105,106,107,108,109</t>
   </si>
   <si>
     <t>40资质金宠自选1</t>
@@ -905,16 +914,13 @@
     <t>50金宠自选1</t>
   </si>
   <si>
-    <t>21,21,21,21,21,21,21,21,21</t>
-  </si>
-  <si>
     <t>43,44,45,46,47,48,49,50,51</t>
   </si>
   <si>
     <t>50粉宠自选</t>
   </si>
   <si>
-    <t>201,202,203</t>
+    <t>231,232,233</t>
   </si>
   <si>
     <t>70粉宠自选</t>
@@ -2404,7 +2410,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:K114"/>
+  <dimension ref="A3:K117"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -4541,7 +4547,7 @@
         <v>214</v>
       </c>
       <c r="C79" s="1">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D79" s="4" t="s">
         <v>215</v>
@@ -4576,7 +4582,7 @@
         <v>214</v>
       </c>
       <c r="C80" s="1">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D80" s="4" t="s">
         <v>217</v>
@@ -4611,7 +4617,7 @@
         <v>214</v>
       </c>
       <c r="C81" s="1">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D81" s="4" t="s">
         <v>219</v>
@@ -4918,18 +4924,41 @@
         <v>235</v>
       </c>
     </row>
+    <row r="90" customHeight="1" spans="1:11">
+      <c r="C90" s="1">
+        <v>129</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="E90" s="1">
+        <v>1</v>
+      </c>
+      <c r="F90" s="4">
+        <v>0</v>
+      </c>
+      <c r="G90" s="4">
+        <v>2</v>
+      </c>
+      <c r="H90" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="I90" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="J90" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="K90" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
     <row r="91" customHeight="1" spans="1:11">
-      <c r="A91" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>214</v>
-      </c>
       <c r="C91" s="1">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E91" s="1">
         <v>1</v>
@@ -4941,27 +4970,21 @@
         <v>2</v>
       </c>
       <c r="H91" s="8" t="s">
-        <v>145</v>
+        <v>193</v>
       </c>
       <c r="I91" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="J91" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="K91" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="J91" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="K91" s="1" t="s">
-        <v>237</v>
-      </c>
     </row>
     <row r="92" customHeight="1" spans="1:11">
-      <c r="A92" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>214</v>
-      </c>
       <c r="C92" s="1">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>239</v>
@@ -4976,146 +4999,129 @@
         <v>2</v>
       </c>
       <c r="H92" s="8" t="s">
-        <v>240</v>
+        <v>193</v>
       </c>
       <c r="I92" s="8" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="J92" s="8" t="s">
-        <v>242</v>
+        <v>87</v>
       </c>
       <c r="K92" s="1" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="93" customHeight="1" spans="1:11">
-      <c r="A93" s="1" t="s">
+    <row r="94" customHeight="1" spans="1:11">
+      <c r="A94" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="B93" s="1" t="s">
+      <c r="B94" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="C93" s="1">
+      <c r="C94" s="1">
+        <v>137</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="E94" s="1">
+        <v>1</v>
+      </c>
+      <c r="F94" s="4">
+        <v>0</v>
+      </c>
+      <c r="G94" s="4">
+        <v>2</v>
+      </c>
+      <c r="H94" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="I94" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="J94" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="K94" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="95" customHeight="1" spans="1:11">
+      <c r="A95" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C95" s="1">
+        <v>138</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="E95" s="1">
+        <v>1</v>
+      </c>
+      <c r="F95" s="4">
+        <v>0</v>
+      </c>
+      <c r="G95" s="4">
+        <v>2</v>
+      </c>
+      <c r="H95" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="I95" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="J95" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="K95" s="1" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="96" customHeight="1" spans="1:11">
+      <c r="A96" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C96" s="1">
         <v>139</v>
       </c>
-      <c r="D93" s="1" t="s">
+      <c r="D96" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="E96" s="1">
+        <v>1</v>
+      </c>
+      <c r="F96" s="4">
+        <v>0</v>
+      </c>
+      <c r="G96" s="4">
+        <v>2</v>
+      </c>
+      <c r="H96" s="8" t="s">
         <v>243</v>
       </c>
-      <c r="E93" s="1">
-        <v>1</v>
-      </c>
-      <c r="F93" s="4">
-        <v>0</v>
-      </c>
-      <c r="G93" s="4">
-        <v>2</v>
-      </c>
-      <c r="H93" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="I93" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="J93" s="8" t="s">
-        <v>242</v>
-      </c>
-      <c r="K93" s="1" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="103" customHeight="1" spans="3:11">
-      <c r="C103" s="1">
-        <v>201</v>
-      </c>
-      <c r="D103" s="1" t="s">
+      <c r="I96" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="J96" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="E103" s="1">
-        <v>1</v>
-      </c>
-      <c r="F103" s="4">
-        <v>0</v>
-      </c>
-      <c r="G103" s="4">
-        <v>2</v>
-      </c>
-      <c r="H103" s="8" t="s">
+      <c r="K96" s="1" t="s">
         <v>246</v>
-      </c>
-      <c r="I103" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="J103" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="K103" s="1" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="104" customHeight="1" spans="3:11">
-      <c r="C104" s="1">
-        <v>202</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="E104" s="1">
-        <v>1</v>
-      </c>
-      <c r="F104" s="4">
-        <v>0</v>
-      </c>
-      <c r="G104" s="4">
-        <v>2</v>
-      </c>
-      <c r="H104" s="8" t="s">
-        <v>246</v>
-      </c>
-      <c r="I104" s="8" t="s">
-        <v>250</v>
-      </c>
-      <c r="J104" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="K104" s="1" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="105" customHeight="1" spans="3:11">
-      <c r="C105" s="1">
-        <v>203</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="E105" s="1">
-        <v>1</v>
-      </c>
-      <c r="F105" s="4">
-        <v>0</v>
-      </c>
-      <c r="G105" s="4">
-        <v>2</v>
-      </c>
-      <c r="H105" s="8" t="s">
-        <v>246</v>
-      </c>
-      <c r="I105" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="J105" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="K105" s="1" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="106" customHeight="1" spans="3:11">
       <c r="C106" s="1">
-        <v>204</v>
+        <v>231</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="E106" s="1">
         <v>1</v>
@@ -5127,24 +5133,24 @@
         <v>2</v>
       </c>
       <c r="H106" s="8" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="I106" s="8" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="J106" s="8" t="s">
         <v>32</v>
       </c>
       <c r="K106" s="1" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
     </row>
     <row r="107" customHeight="1" spans="3:11">
       <c r="C107" s="1">
-        <v>205</v>
+        <v>232</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="E107" s="1">
         <v>1</v>
@@ -5156,53 +5162,82 @@
         <v>2</v>
       </c>
       <c r="H107" s="8" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="I107" s="8" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="J107" s="8" t="s">
         <v>32</v>
       </c>
       <c r="K107" s="1" t="s">
-        <v>258</v>
+        <v>254</v>
+      </c>
+    </row>
+    <row r="108" customHeight="1" spans="3:11">
+      <c r="C108" s="1">
+        <v>233</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="E108" s="1">
+        <v>1</v>
+      </c>
+      <c r="F108" s="4">
+        <v>0</v>
+      </c>
+      <c r="G108" s="4">
+        <v>2</v>
+      </c>
+      <c r="H108" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="I108" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="J108" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="K108" s="1" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="109" customHeight="1" spans="3:11">
       <c r="C109" s="1">
-        <v>207</v>
+        <v>234</v>
       </c>
       <c r="D109" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="E109" s="1">
+        <v>1</v>
+      </c>
+      <c r="F109" s="4">
+        <v>0</v>
+      </c>
+      <c r="G109" s="4">
+        <v>2</v>
+      </c>
+      <c r="H109" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="I109" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="J109" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="K109" s="1" t="s">
         <v>260</v>
-      </c>
-      <c r="E109" s="1">
-        <v>1</v>
-      </c>
-      <c r="F109" s="4">
-        <v>0</v>
-      </c>
-      <c r="G109" s="4">
-        <v>2</v>
-      </c>
-      <c r="H109" s="8" t="s">
-        <v>261</v>
-      </c>
-      <c r="I109" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="J109" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="K109" s="1" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="110" customHeight="1" spans="3:11">
       <c r="C110" s="1">
-        <v>208</v>
+        <v>235</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="E110" s="1">
         <v>1</v>
@@ -5214,53 +5249,24 @@
         <v>2</v>
       </c>
       <c r="H110" s="8" t="s">
-        <v>266</v>
+        <v>249</v>
       </c>
       <c r="I110" s="8" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="J110" s="8" t="s">
-        <v>141</v>
+        <v>32</v>
       </c>
       <c r="K110" s="1" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="111" customHeight="1" spans="3:11">
-      <c r="C111" s="1">
-        <v>209</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="E111" s="1">
-        <v>1</v>
-      </c>
-      <c r="F111" s="4">
-        <v>0</v>
-      </c>
-      <c r="G111" s="4">
-        <v>2</v>
-      </c>
-      <c r="H111" s="8" t="s">
         <v>261</v>
-      </c>
-      <c r="I111" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="J111" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="K111" s="1" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="112" customHeight="1" spans="3:11">
       <c r="C112" s="1">
-        <v>210</v>
+        <v>237</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="E112" s="1">
         <v>1</v>
@@ -5272,24 +5278,24 @@
         <v>2</v>
       </c>
       <c r="H112" s="8" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="I112" s="8" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="J112" s="8" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="K112" s="1" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
     </row>
     <row r="113" customHeight="1" spans="3:11">
       <c r="C113" s="1">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="E113" s="1">
         <v>1</v>
@@ -5301,45 +5307,132 @@
         <v>2</v>
       </c>
       <c r="H113" s="8" t="s">
-        <v>246</v>
+        <v>269</v>
       </c>
       <c r="I113" s="8" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="J113" s="8" t="s">
-        <v>263</v>
+        <v>141</v>
       </c>
       <c r="K113" s="1" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
     </row>
     <row r="114" customHeight="1" spans="3:11">
       <c r="C114" s="1">
+        <v>239</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="E114" s="1">
+        <v>1</v>
+      </c>
+      <c r="F114" s="4">
+        <v>0</v>
+      </c>
+      <c r="G114" s="4">
+        <v>2</v>
+      </c>
+      <c r="H114" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="I114" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="J114" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="K114" s="1" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="115" customHeight="1" spans="3:11">
+      <c r="C115" s="1">
+        <v>210</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="E115" s="1">
+        <v>1</v>
+      </c>
+      <c r="F115" s="4">
+        <v>0</v>
+      </c>
+      <c r="G115" s="4">
+        <v>2</v>
+      </c>
+      <c r="H115" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="I115" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="J115" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="K115" s="1" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="116" customHeight="1" spans="3:11">
+      <c r="C116" s="1">
+        <v>211</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="E116" s="1">
+        <v>1</v>
+      </c>
+      <c r="F116" s="4">
+        <v>0</v>
+      </c>
+      <c r="G116" s="4">
+        <v>2</v>
+      </c>
+      <c r="H116" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="I116" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="J116" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="K116" s="1" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="117" customHeight="1" spans="3:11">
+      <c r="C117" s="1">
         <v>212</v>
       </c>
-      <c r="D114" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="E114" s="1">
-        <v>1</v>
-      </c>
-      <c r="F114" s="4">
-        <v>0</v>
-      </c>
-      <c r="G114" s="4">
-        <v>2</v>
-      </c>
-      <c r="H114" s="8" t="s">
-        <v>246</v>
-      </c>
-      <c r="I114" s="8" t="s">
-        <v>278</v>
-      </c>
-      <c r="J114" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="K114" s="1" t="s">
-        <v>277</v>
+      <c r="D117" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="E117" s="1">
+        <v>1</v>
+      </c>
+      <c r="F117" s="4">
+        <v>0</v>
+      </c>
+      <c r="G117" s="4">
+        <v>2</v>
+      </c>
+      <c r="H117" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="I117" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="J117" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="K117" s="1" t="s">
+        <v>279</v>
       </c>
     </row>
   </sheetData>
@@ -5467,7 +5560,7 @@
         <v>1001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -5482,13 +5575,13 @@
         <v>14</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J6" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5496,7 +5589,7 @@
         <v>1002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -5511,13 +5604,13 @@
         <v>14</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="J7" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5525,7 +5618,7 @@
         <v>1003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -5540,13 +5633,13 @@
         <v>14</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="J8" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5554,7 +5647,7 @@
         <v>1004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
@@ -5569,13 +5662,13 @@
         <v>14</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="J9" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5583,7 +5676,7 @@
         <v>1005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -5598,13 +5691,13 @@
         <v>14</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="J10" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5612,7 +5705,7 @@
         <v>1006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -5627,13 +5720,13 @@
         <v>14</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="J11" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5641,7 +5734,7 @@
         <v>1007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
@@ -5656,13 +5749,13 @@
         <v>14</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J12" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5670,7 +5763,7 @@
         <v>1008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
@@ -5685,13 +5778,13 @@
         <v>14</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="J13" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5699,7 +5792,7 @@
         <v>1009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
@@ -5714,13 +5807,13 @@
         <v>14</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="J14" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5728,7 +5821,7 @@
         <v>1010</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
@@ -5743,13 +5836,13 @@
         <v>14</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="J15" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5757,7 +5850,7 @@
         <v>1011</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E16" s="1">
         <v>1</v>
@@ -5772,13 +5865,13 @@
         <v>14</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="J16" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5786,7 +5879,7 @@
         <v>1012</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E17" s="1">
         <v>1</v>
@@ -5801,13 +5894,13 @@
         <v>14</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="J17" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5815,7 +5908,7 @@
         <v>1013</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="E18" s="1">
         <v>1</v>
@@ -5830,13 +5923,13 @@
         <v>14</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="J18" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5844,7 +5937,7 @@
         <v>1014</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E19" s="1">
         <v>1</v>
@@ -5859,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="J19" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1"/>
@@ -5874,7 +5967,7 @@
         <v>1101</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
@@ -5889,13 +5982,13 @@
         <v>14</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="J21" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5903,7 +5996,7 @@
         <v>1102</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
@@ -5918,13 +6011,13 @@
         <v>14</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="J22" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5932,7 +6025,7 @@
         <v>1103</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
@@ -5947,13 +6040,13 @@
         <v>14</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="J23" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5961,7 +6054,7 @@
         <v>1104</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
@@ -5976,13 +6069,13 @@
         <v>14</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="J24" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5990,7 +6083,7 @@
         <v>1105</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="E25" s="1">
         <v>1</v>
@@ -6005,13 +6098,13 @@
         <v>14</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="J25" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6019,7 +6112,7 @@
         <v>1106</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
@@ -6034,13 +6127,13 @@
         <v>14</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="J26" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6048,7 +6141,7 @@
         <v>1107</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E27" s="1">
         <v>1</v>
@@ -6063,13 +6156,13 @@
         <v>14</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J27" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6077,7 +6170,7 @@
         <v>1108</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E28" s="1">
         <v>1</v>
@@ -6092,13 +6185,13 @@
         <v>14</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="J28" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6106,7 +6199,7 @@
         <v>1109</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
@@ -6121,13 +6214,13 @@
         <v>14</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="J29" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6135,7 +6228,7 @@
         <v>1110</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
@@ -6150,13 +6243,13 @@
         <v>14</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="J30" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6164,7 +6257,7 @@
         <v>1111</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
@@ -6179,13 +6272,13 @@
         <v>14</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="J31" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6193,7 +6286,7 @@
         <v>1112</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E32" s="1">
         <v>1</v>
@@ -6208,13 +6301,13 @@
         <v>14</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="J32" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="2:12">
@@ -6235,7 +6328,7 @@
         <v>1201</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E34" s="1">
         <v>1</v>
@@ -6250,13 +6343,13 @@
         <v>133</v>
       </c>
       <c r="I34" s="8" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="J34" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="2:12">
@@ -6265,7 +6358,7 @@
         <v>1202</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E35" s="1">
         <v>1</v>
@@ -6277,16 +6370,16 @@
         <v>2</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="J35" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L35" s="2"/>
     </row>
@@ -6296,7 +6389,7 @@
         <v>1203</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E36" s="1">
         <v>1</v>
@@ -6308,16 +6401,16 @@
         <v>2</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="I36" s="8" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="J36" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="L36" s="2"/>
     </row>
@@ -6326,7 +6419,7 @@
         <v>1204</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E37" s="1">
         <v>1</v>
@@ -6341,13 +6434,13 @@
         <v>133</v>
       </c>
       <c r="I37" s="8" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="J37" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="2:12">
@@ -6355,7 +6448,7 @@
         <v>1205</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E38" s="1">
         <v>1</v>
@@ -6370,13 +6463,13 @@
         <v>145</v>
       </c>
       <c r="I38" s="8" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="J38" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="2:12">
@@ -6384,7 +6477,7 @@
         <v>1206</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E39" s="1">
         <v>1</v>
@@ -6399,13 +6492,13 @@
         <v>161</v>
       </c>
       <c r="I39" s="8" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="J39" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="2:12">
@@ -6413,7 +6506,7 @@
         <v>2001</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E41" s="1">
         <v>1</v>
@@ -6425,16 +6518,16 @@
         <v>2</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I41" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="J41" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="K41" s="5" t="s">
         <v>375</v>
-      </c>
-      <c r="J41" s="8" t="s">
-        <v>358</v>
-      </c>
-      <c r="K41" s="5" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="2:12">
@@ -6442,28 +6535,28 @@
         <v>2002</v>
       </c>
       <c r="D42" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="E42" s="1">
+        <v>1</v>
+      </c>
+      <c r="F42" s="4">
+        <v>0</v>
+      </c>
+      <c r="G42" s="1">
+        <v>2</v>
+      </c>
+      <c r="H42" s="8" t="s">
         <v>376</v>
       </c>
-      <c r="E42" s="1">
-        <v>1</v>
-      </c>
-      <c r="F42" s="4">
-        <v>0</v>
-      </c>
-      <c r="G42" s="1">
-        <v>2</v>
-      </c>
-      <c r="H42" s="8" t="s">
-        <v>374</v>
-      </c>
       <c r="I42" s="8" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="J42" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K42" s="5" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="2:12">
@@ -6471,7 +6564,7 @@
         <v>2003</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E43" s="1">
         <v>1</v>
@@ -6483,16 +6576,16 @@
         <v>2</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I43" s="8" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="J43" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K43" s="5" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="2:12">
@@ -6500,7 +6593,7 @@
         <v>2004</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E44" s="1">
         <v>1</v>
@@ -6512,16 +6605,16 @@
         <v>2</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I44" s="8" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="J44" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K44" s="5" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="2:12">
@@ -6529,7 +6622,7 @@
         <v>2005</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E45" s="1">
         <v>1</v>
@@ -6541,16 +6634,16 @@
         <v>2</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I45" s="8" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="J45" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K45" s="5" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="2:12">
@@ -6558,7 +6651,7 @@
         <v>2006</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E46" s="1">
         <v>1</v>
@@ -6570,16 +6663,16 @@
         <v>2</v>
       </c>
       <c r="H46" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I46" s="8" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="J46" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" customHeight="1" spans="2:12">
@@ -6588,7 +6681,7 @@
         <v>2007</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E47" s="1">
         <v>1</v>
@@ -6600,16 +6693,16 @@
         <v>2</v>
       </c>
       <c r="H47" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I47" s="8" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="J47" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K47" s="5" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="L47" s="2"/>
     </row>
@@ -6619,7 +6712,7 @@
         <v>2008</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E48" s="1">
         <v>1</v>
@@ -6631,16 +6724,16 @@
         <v>2</v>
       </c>
       <c r="H48" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I48" s="8" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="J48" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K48" s="5" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L48" s="2"/>
     </row>
@@ -6650,7 +6743,7 @@
         <v>2009</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E49" s="1">
         <v>1</v>
@@ -6662,16 +6755,16 @@
         <v>2</v>
       </c>
       <c r="H49" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I49" s="8" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="J49" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K49" s="5" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="L49" s="2"/>
     </row>
@@ -6681,7 +6774,7 @@
         <v>2010</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E50" s="1">
         <v>1</v>
@@ -6693,16 +6786,16 @@
         <v>2</v>
       </c>
       <c r="H50" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I50" s="8" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="J50" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K50" s="5" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="L50" s="2"/>
     </row>
@@ -6712,7 +6805,7 @@
         <v>2011</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E51" s="1">
         <v>1</v>
@@ -6724,16 +6817,16 @@
         <v>2</v>
       </c>
       <c r="H51" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I51" s="8" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="J51" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K51" s="5" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="L51" s="2"/>
     </row>
@@ -6743,7 +6836,7 @@
         <v>2012</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E52" s="1">
         <v>1</v>
@@ -6755,16 +6848,16 @@
         <v>2</v>
       </c>
       <c r="H52" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I52" s="8" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="J52" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K52" s="5" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="L52" s="2"/>
     </row>
@@ -6786,7 +6879,7 @@
         <v>2013</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E54" s="1">
         <v>1</v>
@@ -6798,16 +6891,16 @@
         <v>2</v>
       </c>
       <c r="H54" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I54" s="8" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="J54" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K54" s="6" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="L54" s="2"/>
     </row>
@@ -6817,7 +6910,7 @@
         <v>2014</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E55" s="1">
         <v>1</v>
@@ -6829,16 +6922,16 @@
         <v>2</v>
       </c>
       <c r="H55" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I55" s="8" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="J55" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K55" s="6" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="L55" s="2"/>
     </row>
@@ -6847,7 +6940,7 @@
         <v>2015</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E56" s="1">
         <v>1</v>
@@ -6859,16 +6952,16 @@
         <v>2</v>
       </c>
       <c r="H56" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I56" s="8" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="J56" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K56" s="6" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="2:12">
@@ -6876,7 +6969,7 @@
         <v>2016</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E57" s="1">
         <v>1</v>
@@ -6888,16 +6981,16 @@
         <v>2</v>
       </c>
       <c r="H57" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I57" s="8" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="J57" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K57" s="6" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="2:12">
@@ -6905,7 +6998,7 @@
         <v>2017</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E58" s="1">
         <v>1</v>
@@ -6917,16 +7010,16 @@
         <v>2</v>
       </c>
       <c r="H58" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I58" s="8" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="J58" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K58" s="6" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="2:12">
@@ -6934,7 +7027,7 @@
         <v>2018</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E59" s="1">
         <v>1</v>
@@ -6946,16 +7039,16 @@
         <v>2</v>
       </c>
       <c r="H59" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I59" s="8" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="J59" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K59" s="6" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="2:12">
@@ -6963,7 +7056,7 @@
         <v>2019</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E60" s="1">
         <v>1</v>
@@ -6975,16 +7068,16 @@
         <v>2</v>
       </c>
       <c r="H60" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I60" s="8" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="J60" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K60" s="6" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="2:12">
@@ -6992,7 +7085,7 @@
         <v>2020</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E61" s="1">
         <v>1</v>
@@ -7004,16 +7097,16 @@
         <v>2</v>
       </c>
       <c r="H61" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I61" s="8" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="J61" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K61" s="6" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="2:12">
@@ -7021,7 +7114,7 @@
         <v>2021</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E62" s="1">
         <v>1</v>
@@ -7033,16 +7126,16 @@
         <v>2</v>
       </c>
       <c r="H62" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I62" s="8" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="J62" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K62" s="6" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="2:12">
@@ -7050,7 +7143,7 @@
         <v>2022</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E63" s="1">
         <v>1</v>
@@ -7062,16 +7155,16 @@
         <v>2</v>
       </c>
       <c r="H63" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I63" s="8" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="J63" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K63" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="2:12">
@@ -7079,7 +7172,7 @@
         <v>2023</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E64" s="1">
         <v>1</v>
@@ -7091,16 +7184,16 @@
         <v>2</v>
       </c>
       <c r="H64" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I64" s="8" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="J64" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K64" s="6" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:11">
@@ -7108,7 +7201,7 @@
         <v>2024</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E65" s="1">
         <v>1</v>
@@ -7120,16 +7213,16 @@
         <v>2</v>
       </c>
       <c r="H65" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I65" s="8" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="J65" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K65" s="6" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="3:11">
@@ -7137,7 +7230,7 @@
         <v>2025</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E66" s="1">
         <v>1</v>
@@ -7149,16 +7242,16 @@
         <v>2</v>
       </c>
       <c r="H66" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I66" s="8" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="J66" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K66" s="6" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:11">
@@ -7176,7 +7269,7 @@
         <v>2026</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E68" s="1">
         <v>1</v>
@@ -7188,16 +7281,16 @@
         <v>2</v>
       </c>
       <c r="H68" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I68" s="8" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="J68" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K68" s="6" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:11">
@@ -7205,7 +7298,7 @@
         <v>2027</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E69" s="1">
         <v>1</v>
@@ -7217,16 +7310,16 @@
         <v>2</v>
       </c>
       <c r="H69" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I69" s="8" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="J69" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K69" s="6" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:11">
@@ -7234,7 +7327,7 @@
         <v>2028</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E70" s="1">
         <v>1</v>
@@ -7246,16 +7339,16 @@
         <v>2</v>
       </c>
       <c r="H70" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I70" s="8" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="J70" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K70" s="6" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:11">
@@ -7263,7 +7356,7 @@
         <v>2029</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="E71" s="1">
         <v>1</v>
@@ -7275,16 +7368,16 @@
         <v>2</v>
       </c>
       <c r="H71" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I71" s="8" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="J71" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K71" s="6" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:11">
@@ -7292,7 +7385,7 @@
         <v>2030</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="E72" s="1">
         <v>1</v>
@@ -7304,16 +7397,16 @@
         <v>2</v>
       </c>
       <c r="H72" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I72" s="8" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="J72" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K72" s="6" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:11">
@@ -7321,7 +7414,7 @@
         <v>2031</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E73" s="1">
         <v>1</v>
@@ -7333,16 +7426,16 @@
         <v>2</v>
       </c>
       <c r="H73" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I73" s="8" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="J73" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K73" s="6" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:11">
@@ -7350,7 +7443,7 @@
         <v>2032</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="E74" s="1">
         <v>1</v>
@@ -7362,16 +7455,16 @@
         <v>2</v>
       </c>
       <c r="H74" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I74" s="8" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="J74" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K74" s="6" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:11">
@@ -7379,7 +7472,7 @@
         <v>2033</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E75" s="1">
         <v>1</v>
@@ -7391,16 +7484,16 @@
         <v>2</v>
       </c>
       <c r="H75" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I75" s="8" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="J75" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K75" s="6" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:11">
@@ -7408,7 +7501,7 @@
         <v>2034</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="E76" s="1">
         <v>1</v>
@@ -7420,16 +7513,16 @@
         <v>2</v>
       </c>
       <c r="H76" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I76" s="8" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="J76" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K76" s="6" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:11">
@@ -7437,7 +7530,7 @@
         <v>2035</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E77" s="1">
         <v>1</v>
@@ -7449,16 +7542,16 @@
         <v>2</v>
       </c>
       <c r="H77" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I77" s="8" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="J77" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K77" s="6" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="887" uniqueCount="444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="446">
   <si>
     <t>_id</t>
   </si>
@@ -516,6 +516,12 @@
   </si>
   <si>
     <t>190007,190008,190009,190010,190011,190012</t>
+  </si>
+  <si>
+    <t>星座自选</t>
+  </si>
+  <si>
+    <t>13,14,15,16,17,18,19,20,21,22,23,24</t>
   </si>
   <si>
     <t>粉色专属自选</t>
@@ -2404,7 +2410,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K121"/>
+  <dimension ref="A1:K122"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="4" max="4" width="16.625" customWidth="1"/>
@@ -3788,114 +3794,114 @@
     <row r="50" customFormat="1" customHeight="1" spans="1:11">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
-      <c r="C50" s="1"/>
-      <c r="D50" s="1"/>
-      <c r="E50" s="1"/>
-      <c r="F50" s="4"/>
-      <c r="G50" s="4"/>
-      <c r="H50" s="1"/>
-      <c r="I50" s="1"/>
-      <c r="J50" s="1"/>
-      <c r="K50" s="1"/>
+      <c r="C50" s="1">
+        <v>46</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E50" s="1">
+        <v>1</v>
+      </c>
+      <c r="F50" s="4">
+        <v>0</v>
+      </c>
+      <c r="G50" s="4">
+        <v>2</v>
+      </c>
+      <c r="H50" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="I50" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="J50" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="K50" s="1" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="51" customFormat="1" customHeight="1" spans="1:11">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
-      <c r="C51" s="1">
-        <v>89</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="E51" s="1">
-        <v>1</v>
-      </c>
-      <c r="F51" s="4">
-        <v>0</v>
-      </c>
-      <c r="G51" s="1">
-        <v>2</v>
-      </c>
-      <c r="H51" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="I51" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="J51" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="K51" s="1" t="s">
-        <v>147</v>
-      </c>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="1"/>
+      <c r="F51" s="4"/>
+      <c r="G51" s="4"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
+      <c r="J51" s="1"/>
+      <c r="K51" s="1"/>
     </row>
     <row r="52" customFormat="1" customHeight="1" spans="1:11">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D52" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E52" s="1">
+        <v>1</v>
+      </c>
+      <c r="F52" s="4">
+        <v>0</v>
+      </c>
+      <c r="G52" s="1">
+        <v>2</v>
+      </c>
+      <c r="H52" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="E52" s="1">
-        <v>1</v>
-      </c>
-      <c r="F52" s="4">
-        <v>0</v>
-      </c>
-      <c r="G52" s="1">
-        <v>2</v>
-      </c>
-      <c r="H52" s="8" t="s">
+      <c r="I52" s="8" t="s">
         <v>148</v>
-      </c>
-      <c r="I52" s="8" t="s">
-        <v>149</v>
       </c>
       <c r="J52" s="8" t="s">
         <v>141</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="53" customFormat="1" customHeight="1" spans="1:11">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D53" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E53" s="1">
+        <v>1</v>
+      </c>
+      <c r="F53" s="4">
+        <v>0</v>
+      </c>
+      <c r="G53" s="1">
+        <v>2</v>
+      </c>
+      <c r="H53" s="8" t="s">
         <v>150</v>
-      </c>
-      <c r="E53" s="1">
-        <v>1</v>
-      </c>
-      <c r="F53" s="4">
-        <v>0</v>
-      </c>
-      <c r="G53" s="1">
-        <v>2</v>
-      </c>
-      <c r="H53" s="8" t="s">
-        <v>133</v>
       </c>
       <c r="I53" s="8" t="s">
         <v>151</v>
       </c>
       <c r="J53" s="8" t="s">
-        <v>16</v>
+        <v>141</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="54" customFormat="1" customHeight="1" spans="1:11">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>152</v>
@@ -3910,7 +3916,7 @@
         <v>2</v>
       </c>
       <c r="H54" s="8" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="I54" s="8" t="s">
         <v>153</v>
@@ -3919,14 +3925,14 @@
         <v>16</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="55" customFormat="1" customHeight="1" spans="1:11">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>154</v>
@@ -3941,27 +3947,29 @@
         <v>2</v>
       </c>
       <c r="H55" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I55" s="8" t="s">
         <v>155</v>
       </c>
       <c r="J55" s="8" t="s">
-        <v>91</v>
+        <v>16</v>
       </c>
       <c r="K55" s="1" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="56" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A56" s="1"/>
+      <c r="B56" s="1"/>
       <c r="C56" s="1">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>156</v>
       </c>
       <c r="E56" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" s="4">
         <v>0</v>
@@ -3970,13 +3978,13 @@
         <v>2</v>
       </c>
       <c r="H56" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="I56" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="I56" s="8" t="s">
-        <v>158</v>
-      </c>
       <c r="J56" s="8" t="s">
-        <v>159</v>
+        <v>91</v>
       </c>
       <c r="K56" s="1" t="s">
         <v>156</v>
@@ -3984,123 +3992,123 @@
     </row>
     <row r="57" customFormat="1" customHeight="1" spans="1:11">
       <c r="C57" s="1">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D57" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E57" s="1">
+        <v>0</v>
+      </c>
+      <c r="F57" s="4">
+        <v>0</v>
+      </c>
+      <c r="G57" s="1">
+        <v>2</v>
+      </c>
+      <c r="H57" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="I57" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="E57" s="1">
-        <v>1</v>
-      </c>
-      <c r="F57" s="4">
-        <v>0</v>
-      </c>
-      <c r="G57" s="1">
-        <v>2</v>
-      </c>
-      <c r="H57" s="8" t="s">
+      <c r="J57" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="I57" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="J57" s="8" t="s">
-        <v>32</v>
-      </c>
       <c r="K57" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="58" customFormat="1" customHeight="1" spans="1:11">
       <c r="C58" s="1">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D58" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E58" s="1">
+        <v>1</v>
+      </c>
+      <c r="F58" s="4">
+        <v>0</v>
+      </c>
+      <c r="G58" s="1">
+        <v>2</v>
+      </c>
+      <c r="H58" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="E58" s="1">
-        <v>1</v>
-      </c>
-      <c r="F58" s="4">
-        <v>0</v>
-      </c>
-      <c r="G58" s="1">
-        <v>2</v>
-      </c>
-      <c r="H58" s="8" t="s">
+      <c r="I58" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="I58" s="8" t="s">
-        <v>165</v>
-      </c>
       <c r="J58" s="8" t="s">
-        <v>91</v>
+        <v>32</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="59" customFormat="1" customHeight="1" spans="1:11">
       <c r="C59" s="1">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D59" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E59" s="1">
+        <v>1</v>
+      </c>
+      <c r="F59" s="4">
+        <v>0</v>
+      </c>
+      <c r="G59" s="1">
+        <v>2</v>
+      </c>
+      <c r="H59" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="E59" s="1">
-        <v>0</v>
-      </c>
-      <c r="F59" s="4">
-        <v>0</v>
-      </c>
-      <c r="G59" s="1">
-        <v>2</v>
-      </c>
-      <c r="H59" s="8" t="s">
+      <c r="I59" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="I59" s="8" t="s">
-        <v>168</v>
-      </c>
       <c r="J59" s="8" t="s">
-        <v>169</v>
+        <v>91</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="60" customFormat="1" customHeight="1" spans="1:11">
       <c r="C60" s="1">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D60" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E60" s="1">
+        <v>0</v>
+      </c>
+      <c r="F60" s="4">
+        <v>0</v>
+      </c>
+      <c r="G60" s="1">
+        <v>2</v>
+      </c>
+      <c r="H60" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="I60" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="E60" s="1">
-        <v>0</v>
-      </c>
-      <c r="F60" s="4">
-        <v>0</v>
-      </c>
-      <c r="G60" s="1">
-        <v>2</v>
-      </c>
-      <c r="H60" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="I60" s="8" t="s">
+      <c r="J60" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="J60" s="8" t="s">
-        <v>159</v>
-      </c>
       <c r="K60" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="61" customFormat="1" customHeight="1" spans="1:11">
       <c r="C61" s="1">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>172</v>
@@ -4115,13 +4123,13 @@
         <v>2</v>
       </c>
       <c r="H61" s="8" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I61" s="8" t="s">
         <v>173</v>
       </c>
       <c r="J61" s="8" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="K61" s="1" t="s">
         <v>172</v>
@@ -4129,7 +4137,7 @@
     </row>
     <row r="62" customFormat="1" customHeight="1" spans="1:11">
       <c r="C62" s="1">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>174</v>
@@ -4144,13 +4152,13 @@
         <v>2</v>
       </c>
       <c r="H62" s="8" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="I62" s="8" t="s">
         <v>175</v>
       </c>
       <c r="J62" s="8" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="K62" s="1" t="s">
         <v>174</v>
@@ -4158,7 +4166,7 @@
     </row>
     <row r="63" customFormat="1" customHeight="1" spans="1:11">
       <c r="C63" s="1">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>176</v>
@@ -4173,13 +4181,13 @@
         <v>2</v>
       </c>
       <c r="H63" s="8" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="I63" s="8" t="s">
         <v>177</v>
       </c>
       <c r="J63" s="8" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="K63" s="1" t="s">
         <v>176</v>
@@ -4187,7 +4195,7 @@
     </row>
     <row r="64" customFormat="1" customHeight="1" spans="1:11">
       <c r="C64" s="1">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>178</v>
@@ -4202,13 +4210,13 @@
         <v>2</v>
       </c>
       <c r="H64" s="8" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="I64" s="8" t="s">
         <v>179</v>
       </c>
       <c r="J64" s="8" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="K64" s="1" t="s">
         <v>178</v>
@@ -4216,7 +4224,7 @@
     </row>
     <row r="65" customFormat="1" customHeight="1" spans="1:11">
       <c r="C65" s="1">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>180</v>
@@ -4231,80 +4239,80 @@
         <v>2</v>
       </c>
       <c r="H65" s="8" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="I65" s="8" t="s">
         <v>181</v>
       </c>
       <c r="J65" s="8" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="K65" s="1" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="66" ht="14"/>
-    <row r="67" customFormat="1" customHeight="1" spans="1:11">
-      <c r="C67" s="1">
-        <v>106</v>
-      </c>
-      <c r="D67" s="1" t="s">
+    <row r="66" customFormat="1" customHeight="1" spans="1:11">
+      <c r="C66" s="1">
+        <v>105</v>
+      </c>
+      <c r="D66" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="E67" s="1">
-        <v>1</v>
-      </c>
-      <c r="F67" s="4">
-        <v>0</v>
-      </c>
-      <c r="G67" s="1">
-        <v>1</v>
-      </c>
-      <c r="H67" s="8" t="s">
+      <c r="E66" s="1">
+        <v>0</v>
+      </c>
+      <c r="F66" s="4">
+        <v>0</v>
+      </c>
+      <c r="G66" s="1">
+        <v>2</v>
+      </c>
+      <c r="H66" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="I66" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="I67" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="J67" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="K67" s="1" t="s">
-        <v>186</v>
-      </c>
-    </row>
+      <c r="J66" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="K66" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="67" ht="14"/>
     <row r="68" customFormat="1" customHeight="1" spans="1:11">
       <c r="C68" s="1">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D68" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="E68" s="1">
+        <v>1</v>
+      </c>
+      <c r="F68" s="4">
+        <v>0</v>
+      </c>
+      <c r="G68" s="1">
+        <v>1</v>
+      </c>
+      <c r="H68" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="I68" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="J68" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="E68" s="1">
-        <v>1</v>
-      </c>
-      <c r="F68" s="4">
-        <v>0</v>
-      </c>
-      <c r="G68" s="1">
-        <v>2</v>
-      </c>
-      <c r="H68" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="I68" s="8" t="s">
+      <c r="K68" s="1" t="s">
         <v>188</v>
-      </c>
-      <c r="J68" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="K68" s="1" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="69" customFormat="1" customHeight="1" spans="1:11">
       <c r="C69" s="1">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>189</v>
@@ -4328,258 +4336,252 @@
         <v>40</v>
       </c>
       <c r="K69" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="70" customFormat="1" customHeight="1" spans="1:11">
+      <c r="C70" s="1">
+        <v>108</v>
+      </c>
+      <c r="D70" s="1" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="70" ht="14"/>
-    <row r="71" customFormat="1" customHeight="1" spans="1:11">
-      <c r="C71" s="1">
-        <v>109</v>
-      </c>
-      <c r="D71" s="1" t="s">
+      <c r="E70" s="1">
+        <v>1</v>
+      </c>
+      <c r="F70" s="4">
+        <v>0</v>
+      </c>
+      <c r="G70" s="1">
+        <v>2</v>
+      </c>
+      <c r="H70" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="I70" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="E71" s="1">
-        <v>1</v>
-      </c>
-      <c r="F71" s="4">
-        <v>0</v>
-      </c>
-      <c r="G71" s="4">
-        <v>2</v>
-      </c>
-      <c r="H71" s="8" t="s">
+      <c r="J70" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="K70" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="I71" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="J71" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="K71" s="1" t="s">
-        <v>195</v>
-      </c>
-    </row>
+    </row>
+    <row r="71" ht="14"/>
     <row r="72" customFormat="1" customHeight="1" spans="1:11">
       <c r="C72" s="1">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D72" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E72" s="1">
+        <v>1</v>
+      </c>
+      <c r="F72" s="4">
+        <v>0</v>
+      </c>
+      <c r="G72" s="4">
+        <v>2</v>
+      </c>
+      <c r="H72" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="I72" s="8" t="s">
         <v>196</v>
-      </c>
-      <c r="E72" s="1">
-        <v>1</v>
-      </c>
-      <c r="F72" s="4">
-        <v>0</v>
-      </c>
-      <c r="G72" s="4">
-        <v>2</v>
-      </c>
-      <c r="H72" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="I72" s="8" t="s">
-        <v>197</v>
       </c>
       <c r="J72" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="73" customFormat="1" customHeight="1" spans="1:11">
       <c r="C73" s="1">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D73" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E73" s="1">
+        <v>1</v>
+      </c>
+      <c r="F73" s="4">
+        <v>0</v>
+      </c>
+      <c r="G73" s="4">
+        <v>2</v>
+      </c>
+      <c r="H73" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="I73" s="8" t="s">
         <v>199</v>
-      </c>
-      <c r="E73" s="1">
-        <v>1</v>
-      </c>
-      <c r="F73" s="4">
-        <v>0</v>
-      </c>
-      <c r="G73" s="4">
-        <v>2</v>
-      </c>
-      <c r="H73" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="I73" s="8" t="s">
-        <v>200</v>
       </c>
       <c r="J73" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="74" customFormat="1" customHeight="1" spans="1:11">
       <c r="C74" s="1">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D74" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="E74" s="1">
+        <v>1</v>
+      </c>
+      <c r="F74" s="4">
+        <v>0</v>
+      </c>
+      <c r="G74" s="4">
+        <v>2</v>
+      </c>
+      <c r="H74" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="I74" s="8" t="s">
         <v>202</v>
-      </c>
-      <c r="E74" s="1">
-        <v>1</v>
-      </c>
-      <c r="F74" s="4">
-        <v>0</v>
-      </c>
-      <c r="G74" s="4">
-        <v>2</v>
-      </c>
-      <c r="H74" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="I74" s="8" t="s">
-        <v>203</v>
       </c>
       <c r="J74" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="75" customFormat="1" customHeight="1" spans="1:11">
       <c r="C75" s="1">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D75" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="E75" s="1">
+        <v>1</v>
+      </c>
+      <c r="F75" s="4">
+        <v>0</v>
+      </c>
+      <c r="G75" s="4">
+        <v>2</v>
+      </c>
+      <c r="H75" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="I75" s="8" t="s">
         <v>205</v>
-      </c>
-      <c r="E75" s="1">
-        <v>1</v>
-      </c>
-      <c r="F75" s="4">
-        <v>0</v>
-      </c>
-      <c r="G75" s="4">
-        <v>2</v>
-      </c>
-      <c r="H75" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="I75" s="8" t="s">
-        <v>206</v>
       </c>
       <c r="J75" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K75" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="76" customFormat="1" customHeight="1" spans="1:11">
       <c r="C76" s="1">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D76" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E76" s="1">
+        <v>1</v>
+      </c>
+      <c r="F76" s="4">
+        <v>0</v>
+      </c>
+      <c r="G76" s="4">
+        <v>2</v>
+      </c>
+      <c r="H76" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="I76" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="E76" s="1">
-        <v>1</v>
-      </c>
-      <c r="F76" s="4">
-        <v>0</v>
-      </c>
-      <c r="G76" s="4">
-        <v>2</v>
-      </c>
-      <c r="H76" s="8" t="s">
+      <c r="J76" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="K76" s="1" t="s">
         <v>209</v>
-      </c>
-      <c r="I76" s="8" t="s">
-        <v>210</v>
-      </c>
-      <c r="J76" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="K76" s="1" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="77" customFormat="1" customHeight="1" spans="1:11">
       <c r="C77" s="1">
+        <v>114</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E77" s="1">
+        <v>1</v>
+      </c>
+      <c r="F77" s="4">
+        <v>0</v>
+      </c>
+      <c r="G77" s="4">
+        <v>2</v>
+      </c>
+      <c r="H77" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="I77" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="J77" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K77" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="78" customFormat="1" customHeight="1" spans="1:11">
+      <c r="C78" s="1">
         <v>115</v>
       </c>
-      <c r="D77" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="E77" s="1">
-        <v>1</v>
-      </c>
-      <c r="F77" s="4">
-        <v>0</v>
-      </c>
-      <c r="G77" s="4">
-        <v>2</v>
-      </c>
-      <c r="H77" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="I77" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="J77" s="8" t="s">
+      <c r="D78" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="E78" s="1">
+        <v>1</v>
+      </c>
+      <c r="F78" s="4">
+        <v>0</v>
+      </c>
+      <c r="G78" s="4">
+        <v>2</v>
+      </c>
+      <c r="H78" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="I78" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="J78" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="K77" s="1" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="78" ht="14"/>
-    <row r="79" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A79" s="1" t="s">
+      <c r="K78" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="B79" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="C79" s="1">
-        <v>118</v>
-      </c>
-      <c r="D79" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="E79" s="1">
-        <v>1</v>
-      </c>
-      <c r="F79" s="4">
-        <v>0</v>
-      </c>
-      <c r="G79" s="4">
-        <v>2</v>
-      </c>
-      <c r="H79" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="I79" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="J79" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="K79" s="4" t="s">
-        <v>215</v>
-      </c>
-    </row>
+    </row>
+    <row r="79" ht="14"/>
     <row r="80" customFormat="1" customHeight="1" spans="1:11">
       <c r="A80" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C80" s="1">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D80" s="4" t="s">
         <v>217</v>
@@ -4594,7 +4596,7 @@
         <v>2</v>
       </c>
       <c r="H80" s="8" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="I80" s="8" t="s">
         <v>218</v>
@@ -4608,13 +4610,13 @@
     </row>
     <row r="81" customFormat="1" customHeight="1" spans="1:11">
       <c r="A81" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C81" s="1">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D81" s="4" t="s">
         <v>219</v>
@@ -4629,7 +4631,7 @@
         <v>2</v>
       </c>
       <c r="H81" s="8" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="I81" s="8" t="s">
         <v>220</v>
@@ -4643,13 +4645,13 @@
     </row>
     <row r="82" customFormat="1" customHeight="1" spans="1:11">
       <c r="A82" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C82" s="1">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D82" s="4" t="s">
         <v>221</v>
@@ -4664,7 +4666,7 @@
         <v>2</v>
       </c>
       <c r="H82" s="8" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="I82" s="8" t="s">
         <v>222</v>
@@ -4678,13 +4680,13 @@
     </row>
     <row r="83" customFormat="1" customHeight="1" spans="1:11">
       <c r="A83" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C83" s="1">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D83" s="4" t="s">
         <v>223</v>
@@ -4699,7 +4701,7 @@
         <v>2</v>
       </c>
       <c r="H83" s="8" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="I83" s="8" t="s">
         <v>224</v>
@@ -4713,13 +4715,13 @@
     </row>
     <row r="84" customFormat="1" customHeight="1" spans="1:11">
       <c r="A84" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C84" s="1">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D84" s="4" t="s">
         <v>225</v>
@@ -4734,7 +4736,7 @@
         <v>2</v>
       </c>
       <c r="H84" s="8" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="I84" s="8" t="s">
         <v>226</v>
@@ -4748,15 +4750,15 @@
     </row>
     <row r="85" customFormat="1" customHeight="1" spans="1:11">
       <c r="A85" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C85" s="1">
-        <v>124</v>
-      </c>
-      <c r="D85" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D85" s="4" t="s">
         <v>227</v>
       </c>
       <c r="E85" s="1">
@@ -4769,7 +4771,7 @@
         <v>2</v>
       </c>
       <c r="H85" s="8" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="I85" s="8" t="s">
         <v>228</v>
@@ -4777,19 +4779,19 @@
       <c r="J85" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="K85" s="1" t="s">
+      <c r="K85" s="4" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="86" customFormat="1" customHeight="1" spans="1:11">
       <c r="A86" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C86" s="1">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>229</v>
@@ -4804,7 +4806,7 @@
         <v>2</v>
       </c>
       <c r="H86" s="8" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="I86" s="8" t="s">
         <v>230</v>
@@ -4818,13 +4820,13 @@
     </row>
     <row r="87" customFormat="1" customHeight="1" spans="1:11">
       <c r="A87" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C87" s="1">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>231</v>
@@ -4839,7 +4841,7 @@
         <v>2</v>
       </c>
       <c r="H87" s="8" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="I87" s="8" t="s">
         <v>232</v>
@@ -4853,13 +4855,13 @@
     </row>
     <row r="88" customFormat="1" customHeight="1" spans="1:11">
       <c r="A88" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C88" s="1">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>233</v>
@@ -4874,7 +4876,7 @@
         <v>2</v>
       </c>
       <c r="H88" s="8" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="I88" s="8" t="s">
         <v>234</v>
@@ -4888,13 +4890,13 @@
     </row>
     <row r="89" customFormat="1" customHeight="1" spans="1:11">
       <c r="A89" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C89" s="1">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>235</v>
@@ -4909,7 +4911,7 @@
         <v>2</v>
       </c>
       <c r="H89" s="8" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="I89" s="8" t="s">
         <v>236</v>
@@ -4921,51 +4923,51 @@
         <v>235</v>
       </c>
     </row>
-    <row r="90" ht="14"/>
-    <row r="91" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A91" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="C91" s="1">
-        <v>137</v>
-      </c>
-      <c r="D91" s="1" t="s">
+    <row r="90" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A90" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C90" s="1">
+        <v>128</v>
+      </c>
+      <c r="D90" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="E91" s="1">
-        <v>1</v>
-      </c>
-      <c r="F91" s="4">
-        <v>0</v>
-      </c>
-      <c r="G91" s="4">
-        <v>2</v>
-      </c>
-      <c r="H91" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="I91" s="8" t="s">
+      <c r="E90" s="1">
+        <v>1</v>
+      </c>
+      <c r="F90" s="4">
+        <v>0</v>
+      </c>
+      <c r="G90" s="4">
+        <v>2</v>
+      </c>
+      <c r="H90" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="I90" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="J91" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="K91" s="1" t="s">
+      <c r="J90" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="K90" s="1" t="s">
         <v>237</v>
       </c>
     </row>
+    <row r="91" ht="14"/>
     <row r="92" customFormat="1" customHeight="1" spans="1:11">
       <c r="A92" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C92" s="1">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>239</v>
@@ -4980,13 +4982,13 @@
         <v>2</v>
       </c>
       <c r="H92" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="I92" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="I92" s="8" t="s">
-        <v>241</v>
-      </c>
       <c r="J92" s="8" t="s">
-        <v>242</v>
+        <v>40</v>
       </c>
       <c r="K92" s="1" t="s">
         <v>239</v>
@@ -4994,40 +4996,74 @@
     </row>
     <row r="93" customFormat="1" customHeight="1" spans="1:11">
       <c r="A93" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C93" s="1">
+        <v>138</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="E93" s="1">
+        <v>1</v>
+      </c>
+      <c r="F93" s="4">
+        <v>0</v>
+      </c>
+      <c r="G93" s="4">
+        <v>2</v>
+      </c>
+      <c r="H93" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="I93" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="J93" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="K93" s="1" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="94" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A94" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C94" s="1">
         <v>139</v>
       </c>
-      <c r="D93" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="E93" s="1">
-        <v>1</v>
-      </c>
-      <c r="F93" s="4">
-        <v>0</v>
-      </c>
-      <c r="G93" s="4">
-        <v>2</v>
-      </c>
-      <c r="H93" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="I93" s="8" t="s">
+      <c r="D94" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="E94" s="1">
+        <v>1</v>
+      </c>
+      <c r="F94" s="4">
+        <v>0</v>
+      </c>
+      <c r="G94" s="4">
+        <v>2</v>
+      </c>
+      <c r="H94" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="I94" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="J94" s="8" t="s">
         <v>244</v>
       </c>
-      <c r="J93" s="8" t="s">
-        <v>242</v>
-      </c>
-      <c r="K93" s="1" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="94" ht="14"/>
+      <c r="K94" s="1" t="s">
+        <v>245</v>
+      </c>
+    </row>
     <row r="95" ht="14"/>
     <row r="96" ht="14"/>
     <row r="97" ht="14"/>
@@ -5036,300 +5072,272 @@
     <row r="100" ht="14"/>
     <row r="101" ht="14"/>
     <row r="102" ht="14"/>
-    <row r="103" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C103" s="1">
-        <v>201</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="E103" s="1">
-        <v>1</v>
-      </c>
-      <c r="F103" s="4">
-        <v>0</v>
-      </c>
-      <c r="G103" s="4">
-        <v>2</v>
-      </c>
-      <c r="H103" s="8" t="s">
-        <v>246</v>
-      </c>
-      <c r="I103" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="J103" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="K103" s="1" t="s">
-        <v>248</v>
-      </c>
-    </row>
+    <row r="103" ht="14"/>
     <row r="104" customFormat="1" customHeight="1" spans="3:11">
       <c r="C104" s="1">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D104" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="E104" s="1">
+        <v>1</v>
+      </c>
+      <c r="F104" s="4">
+        <v>0</v>
+      </c>
+      <c r="G104" s="4">
+        <v>2</v>
+      </c>
+      <c r="H104" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="I104" s="8" t="s">
         <v>249</v>
-      </c>
-      <c r="E104" s="1">
-        <v>1</v>
-      </c>
-      <c r="F104" s="4">
-        <v>0</v>
-      </c>
-      <c r="G104" s="4">
-        <v>2</v>
-      </c>
-      <c r="H104" s="8" t="s">
-        <v>246</v>
-      </c>
-      <c r="I104" s="8" t="s">
-        <v>250</v>
       </c>
       <c r="J104" s="8" t="s">
         <v>32</v>
       </c>
       <c r="K104" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="105" customFormat="1" customHeight="1" spans="3:11">
       <c r="C105" s="1">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D105" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="E105" s="1">
+        <v>1</v>
+      </c>
+      <c r="F105" s="4">
+        <v>0</v>
+      </c>
+      <c r="G105" s="4">
+        <v>2</v>
+      </c>
+      <c r="H105" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="I105" s="8" t="s">
         <v>252</v>
-      </c>
-      <c r="E105" s="1">
-        <v>1</v>
-      </c>
-      <c r="F105" s="4">
-        <v>0</v>
-      </c>
-      <c r="G105" s="4">
-        <v>2</v>
-      </c>
-      <c r="H105" s="8" t="s">
-        <v>246</v>
-      </c>
-      <c r="I105" s="8" t="s">
-        <v>253</v>
       </c>
       <c r="J105" s="8" t="s">
         <v>32</v>
       </c>
       <c r="K105" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="106" customFormat="1" customHeight="1" spans="3:11">
       <c r="C106" s="1">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D106" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="E106" s="1">
+        <v>1</v>
+      </c>
+      <c r="F106" s="4">
+        <v>0</v>
+      </c>
+      <c r="G106" s="4">
+        <v>2</v>
+      </c>
+      <c r="H106" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="I106" s="8" t="s">
         <v>255</v>
-      </c>
-      <c r="E106" s="1">
-        <v>1</v>
-      </c>
-      <c r="F106" s="4">
-        <v>0</v>
-      </c>
-      <c r="G106" s="4">
-        <v>2</v>
-      </c>
-      <c r="H106" s="8" t="s">
-        <v>246</v>
-      </c>
-      <c r="I106" s="8" t="s">
-        <v>256</v>
       </c>
       <c r="J106" s="8" t="s">
         <v>32</v>
       </c>
       <c r="K106" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="107" customFormat="1" customHeight="1" spans="3:11">
       <c r="C107" s="1">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D107" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="E107" s="1">
+        <v>1</v>
+      </c>
+      <c r="F107" s="4">
+        <v>0</v>
+      </c>
+      <c r="G107" s="4">
+        <v>2</v>
+      </c>
+      <c r="H107" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="I107" s="8" t="s">
         <v>258</v>
-      </c>
-      <c r="E107" s="1">
-        <v>1</v>
-      </c>
-      <c r="F107" s="4">
-        <v>0</v>
-      </c>
-      <c r="G107" s="4">
-        <v>2</v>
-      </c>
-      <c r="H107" s="8" t="s">
-        <v>246</v>
-      </c>
-      <c r="I107" s="8" t="s">
-        <v>259</v>
       </c>
       <c r="J107" s="8" t="s">
         <v>32</v>
       </c>
       <c r="K107" s="1" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="108" ht="14"/>
-    <row r="109" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C109" s="1">
-        <v>207</v>
-      </c>
-      <c r="D109" s="1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="108" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C108" s="1">
+        <v>205</v>
+      </c>
+      <c r="D108" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="E109" s="1">
-        <v>1</v>
-      </c>
-      <c r="F109" s="4">
-        <v>0</v>
-      </c>
-      <c r="G109" s="4">
-        <v>2</v>
-      </c>
-      <c r="H109" s="8" t="s">
+      <c r="E108" s="1">
+        <v>1</v>
+      </c>
+      <c r="F108" s="4">
+        <v>0</v>
+      </c>
+      <c r="G108" s="4">
+        <v>2</v>
+      </c>
+      <c r="H108" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="I108" s="8" t="s">
         <v>261</v>
       </c>
-      <c r="I109" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="J109" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="K109" s="1" t="s">
-        <v>264</v>
-      </c>
-    </row>
+      <c r="J108" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="K108" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="109" ht="14"/>
     <row r="110" customFormat="1" customHeight="1" spans="3:11">
       <c r="C110" s="1">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D110" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="E110" s="1">
+        <v>1</v>
+      </c>
+      <c r="F110" s="4">
+        <v>0</v>
+      </c>
+      <c r="G110" s="4">
+        <v>2</v>
+      </c>
+      <c r="H110" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="I110" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="J110" s="8" t="s">
         <v>265</v>
       </c>
-      <c r="E110" s="1">
-        <v>1</v>
-      </c>
-      <c r="F110" s="4">
-        <v>0</v>
-      </c>
-      <c r="G110" s="4">
-        <v>2</v>
-      </c>
-      <c r="H110" s="8" t="s">
+      <c r="K110" s="1" t="s">
         <v>266</v>
-      </c>
-      <c r="I110" s="8" t="s">
-        <v>267</v>
-      </c>
-      <c r="J110" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="K110" s="1" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="111" customFormat="1" customHeight="1" spans="3:11">
       <c r="C111" s="1">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D111" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="E111" s="1">
+        <v>1</v>
+      </c>
+      <c r="F111" s="4">
+        <v>0</v>
+      </c>
+      <c r="G111" s="4">
+        <v>2</v>
+      </c>
+      <c r="H111" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="I111" s="8" t="s">
         <v>269</v>
       </c>
-      <c r="E111" s="1">
-        <v>1</v>
-      </c>
-      <c r="F111" s="4">
-        <v>0</v>
-      </c>
-      <c r="G111" s="4">
-        <v>2</v>
-      </c>
-      <c r="H111" s="8" t="s">
-        <v>261</v>
-      </c>
-      <c r="I111" s="8" t="s">
+      <c r="J111" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="K111" s="1" t="s">
         <v>270</v>
-      </c>
-      <c r="J111" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="K111" s="1" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="112" customFormat="1" customHeight="1" spans="3:11">
       <c r="C112" s="1">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D112" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="E112" s="1">
+        <v>1</v>
+      </c>
+      <c r="F112" s="4">
+        <v>0</v>
+      </c>
+      <c r="G112" s="4">
+        <v>2</v>
+      </c>
+      <c r="H112" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="I112" s="8" t="s">
         <v>272</v>
       </c>
-      <c r="E112" s="1">
-        <v>1</v>
-      </c>
-      <c r="F112" s="4">
-        <v>0</v>
-      </c>
-      <c r="G112" s="4">
-        <v>2</v>
-      </c>
-      <c r="H112" s="8" t="s">
+      <c r="J112" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="K112" s="1" t="s">
         <v>273</v>
-      </c>
-      <c r="I112" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="J112" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="K112" s="1" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="113" customFormat="1" customHeight="1" spans="3:11">
       <c r="C113" s="1">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D113" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="E113" s="1">
+        <v>1</v>
+      </c>
+      <c r="F113" s="4">
+        <v>0</v>
+      </c>
+      <c r="G113" s="4">
+        <v>2</v>
+      </c>
+      <c r="H113" s="8" t="s">
         <v>275</v>
-      </c>
-      <c r="E113" s="1">
-        <v>1</v>
-      </c>
-      <c r="F113" s="4">
-        <v>0</v>
-      </c>
-      <c r="G113" s="4">
-        <v>2</v>
-      </c>
-      <c r="H113" s="8" t="s">
-        <v>246</v>
       </c>
       <c r="I113" s="8" t="s">
         <v>276</v>
       </c>
       <c r="J113" s="8" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="K113" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="114" customFormat="1" customHeight="1" spans="3:11">
       <c r="C114" s="1">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D114" s="1" t="s">
         <v>277</v>
@@ -5344,25 +5352,54 @@
         <v>2</v>
       </c>
       <c r="H114" s="8" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="I114" s="8" t="s">
         <v>278</v>
       </c>
       <c r="J114" s="8" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="K114" s="1" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="115" ht="14"/>
+    <row r="115" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C115" s="1">
+        <v>212</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="E115" s="1">
+        <v>1</v>
+      </c>
+      <c r="F115" s="4">
+        <v>0</v>
+      </c>
+      <c r="G115" s="4">
+        <v>2</v>
+      </c>
+      <c r="H115" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="I115" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="J115" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="K115" s="1" t="s">
+        <v>279</v>
+      </c>
+    </row>
     <row r="116" ht="14"/>
     <row r="117" ht="14"/>
     <row r="118" ht="14"/>
     <row r="119" ht="14"/>
     <row r="120" ht="14"/>
-    <row r="121"/>
+    <row r="121" ht="14"/>
+    <row r="122" ht="14"/>
   </sheetData>
   <dataValidations count="2">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:E5 H3:K5" errorStyle="warning">
@@ -5488,7 +5525,7 @@
         <v>1001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -5503,13 +5540,13 @@
         <v>14</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J6" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5517,7 +5554,7 @@
         <v>1002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -5532,13 +5569,13 @@
         <v>14</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="J7" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5546,7 +5583,7 @@
         <v>1003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -5561,13 +5598,13 @@
         <v>14</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="J8" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5575,7 +5612,7 @@
         <v>1004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
@@ -5590,13 +5627,13 @@
         <v>14</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="J9" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5604,7 +5641,7 @@
         <v>1005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -5619,13 +5656,13 @@
         <v>14</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="J10" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5633,7 +5670,7 @@
         <v>1006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -5648,13 +5685,13 @@
         <v>14</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="J11" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5662,7 +5699,7 @@
         <v>1007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
@@ -5677,13 +5714,13 @@
         <v>14</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J12" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5691,7 +5728,7 @@
         <v>1008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
@@ -5706,13 +5743,13 @@
         <v>14</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="J13" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5720,7 +5757,7 @@
         <v>1009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
@@ -5735,13 +5772,13 @@
         <v>14</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="J14" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5749,7 +5786,7 @@
         <v>1010</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
@@ -5764,13 +5801,13 @@
         <v>14</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="J15" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5778,7 +5815,7 @@
         <v>1011</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E16" s="1">
         <v>1</v>
@@ -5793,13 +5830,13 @@
         <v>14</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="J16" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5807,7 +5844,7 @@
         <v>1012</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E17" s="1">
         <v>1</v>
@@ -5822,13 +5859,13 @@
         <v>14</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="J17" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5836,7 +5873,7 @@
         <v>1013</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="E18" s="1">
         <v>1</v>
@@ -5851,13 +5888,13 @@
         <v>14</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="J18" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5865,7 +5902,7 @@
         <v>1014</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E19" s="1">
         <v>1</v>
@@ -5880,13 +5917,13 @@
         <v>14</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="J19" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1"/>
@@ -5895,7 +5932,7 @@
         <v>1101</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
@@ -5910,13 +5947,13 @@
         <v>14</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="J21" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5924,7 +5961,7 @@
         <v>1102</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
@@ -5939,13 +5976,13 @@
         <v>14</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="J22" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5953,7 +5990,7 @@
         <v>1103</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
@@ -5968,13 +6005,13 @@
         <v>14</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="J23" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5982,7 +6019,7 @@
         <v>1104</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
@@ -5997,13 +6034,13 @@
         <v>14</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="J24" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6011,7 +6048,7 @@
         <v>1105</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="E25" s="1">
         <v>1</v>
@@ -6026,13 +6063,13 @@
         <v>14</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="J25" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6040,7 +6077,7 @@
         <v>1106</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
@@ -6055,13 +6092,13 @@
         <v>14</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="J26" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6069,7 +6106,7 @@
         <v>1107</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E27" s="1">
         <v>1</v>
@@ -6084,13 +6121,13 @@
         <v>14</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J27" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6098,7 +6135,7 @@
         <v>1108</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E28" s="1">
         <v>1</v>
@@ -6113,13 +6150,13 @@
         <v>14</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="J28" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6127,7 +6164,7 @@
         <v>1109</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
@@ -6142,13 +6179,13 @@
         <v>14</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="J29" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6156,7 +6193,7 @@
         <v>1110</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
@@ -6171,13 +6208,13 @@
         <v>14</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="J30" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6185,7 +6222,7 @@
         <v>1111</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
@@ -6200,13 +6237,13 @@
         <v>14</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="J31" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6214,7 +6251,7 @@
         <v>1112</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E32" s="1">
         <v>1</v>
@@ -6229,13 +6266,13 @@
         <v>14</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="J32" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="2:12">
@@ -6256,7 +6293,7 @@
         <v>1201</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E34" s="1">
         <v>1</v>
@@ -6271,13 +6308,13 @@
         <v>133</v>
       </c>
       <c r="I34" s="8" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="J34" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="2:12">
@@ -6286,7 +6323,7 @@
         <v>1202</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E35" s="1">
         <v>1</v>
@@ -6298,16 +6335,16 @@
         <v>2</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="J35" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L35" s="2"/>
     </row>
@@ -6317,7 +6354,7 @@
         <v>1203</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E36" s="1">
         <v>1</v>
@@ -6329,16 +6366,16 @@
         <v>2</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="I36" s="8" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="J36" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="L36" s="2"/>
     </row>
@@ -6347,7 +6384,7 @@
         <v>1204</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E37" s="1">
         <v>1</v>
@@ -6362,13 +6399,13 @@
         <v>133</v>
       </c>
       <c r="I37" s="8" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="J37" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="2:12">
@@ -6376,7 +6413,7 @@
         <v>1205</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E38" s="1">
         <v>1</v>
@@ -6388,16 +6425,16 @@
         <v>2</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I38" s="8" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="J38" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="2:12">
@@ -6405,7 +6442,7 @@
         <v>1206</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E39" s="1">
         <v>1</v>
@@ -6417,16 +6454,16 @@
         <v>2</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="I39" s="8" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="J39" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="2:12">
@@ -6434,7 +6471,7 @@
         <v>2001</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E41" s="1">
         <v>1</v>
@@ -6446,16 +6483,16 @@
         <v>2</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I41" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="J41" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="K41" s="5" t="s">
         <v>375</v>
-      </c>
-      <c r="J41" s="8" t="s">
-        <v>358</v>
-      </c>
-      <c r="K41" s="5" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="2:12">
@@ -6463,28 +6500,28 @@
         <v>2002</v>
       </c>
       <c r="D42" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="E42" s="1">
+        <v>1</v>
+      </c>
+      <c r="F42" s="4">
+        <v>0</v>
+      </c>
+      <c r="G42" s="1">
+        <v>2</v>
+      </c>
+      <c r="H42" s="8" t="s">
         <v>376</v>
       </c>
-      <c r="E42" s="1">
-        <v>1</v>
-      </c>
-      <c r="F42" s="4">
-        <v>0</v>
-      </c>
-      <c r="G42" s="1">
-        <v>2</v>
-      </c>
-      <c r="H42" s="8" t="s">
-        <v>374</v>
-      </c>
       <c r="I42" s="8" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="J42" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K42" s="5" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="2:12">
@@ -6492,7 +6529,7 @@
         <v>2003</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E43" s="1">
         <v>1</v>
@@ -6504,16 +6541,16 @@
         <v>2</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I43" s="8" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="J43" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K43" s="5" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="2:12">
@@ -6521,7 +6558,7 @@
         <v>2004</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E44" s="1">
         <v>1</v>
@@ -6533,16 +6570,16 @@
         <v>2</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I44" s="8" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="J44" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K44" s="5" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="2:12">
@@ -6550,7 +6587,7 @@
         <v>2005</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E45" s="1">
         <v>1</v>
@@ -6562,16 +6599,16 @@
         <v>2</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I45" s="8" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="J45" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K45" s="5" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="2:12">
@@ -6579,7 +6616,7 @@
         <v>2006</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E46" s="1">
         <v>1</v>
@@ -6591,16 +6628,16 @@
         <v>2</v>
       </c>
       <c r="H46" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I46" s="8" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="J46" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" customHeight="1" spans="2:12">
@@ -6609,7 +6646,7 @@
         <v>2007</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E47" s="1">
         <v>1</v>
@@ -6621,16 +6658,16 @@
         <v>2</v>
       </c>
       <c r="H47" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I47" s="8" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="J47" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K47" s="5" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="L47" s="2"/>
     </row>
@@ -6640,7 +6677,7 @@
         <v>2008</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E48" s="1">
         <v>1</v>
@@ -6652,16 +6689,16 @@
         <v>2</v>
       </c>
       <c r="H48" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I48" s="8" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="J48" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K48" s="5" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L48" s="2"/>
     </row>
@@ -6671,7 +6708,7 @@
         <v>2009</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E49" s="1">
         <v>1</v>
@@ -6683,16 +6720,16 @@
         <v>2</v>
       </c>
       <c r="H49" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I49" s="8" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="J49" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K49" s="5" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="L49" s="2"/>
     </row>
@@ -6702,7 +6739,7 @@
         <v>2010</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E50" s="1">
         <v>1</v>
@@ -6714,16 +6751,16 @@
         <v>2</v>
       </c>
       <c r="H50" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I50" s="8" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="J50" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K50" s="5" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="L50" s="2"/>
     </row>
@@ -6733,7 +6770,7 @@
         <v>2011</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E51" s="1">
         <v>1</v>
@@ -6745,16 +6782,16 @@
         <v>2</v>
       </c>
       <c r="H51" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I51" s="8" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="J51" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K51" s="5" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="L51" s="2"/>
     </row>
@@ -6764,7 +6801,7 @@
         <v>2012</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E52" s="1">
         <v>1</v>
@@ -6776,16 +6813,16 @@
         <v>2</v>
       </c>
       <c r="H52" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I52" s="8" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="J52" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K52" s="5" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="L52" s="2"/>
     </row>
@@ -6807,7 +6844,7 @@
         <v>2013</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E54" s="1">
         <v>1</v>
@@ -6819,16 +6856,16 @@
         <v>2</v>
       </c>
       <c r="H54" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I54" s="8" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="J54" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K54" s="6" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="L54" s="2"/>
     </row>
@@ -6838,7 +6875,7 @@
         <v>2014</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E55" s="1">
         <v>1</v>
@@ -6850,16 +6887,16 @@
         <v>2</v>
       </c>
       <c r="H55" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I55" s="8" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="J55" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K55" s="6" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="L55" s="2"/>
     </row>
@@ -6868,7 +6905,7 @@
         <v>2015</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E56" s="1">
         <v>1</v>
@@ -6880,16 +6917,16 @@
         <v>2</v>
       </c>
       <c r="H56" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I56" s="8" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="J56" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K56" s="6" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="2:12">
@@ -6897,7 +6934,7 @@
         <v>2016</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E57" s="1">
         <v>1</v>
@@ -6909,16 +6946,16 @@
         <v>2</v>
       </c>
       <c r="H57" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I57" s="8" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="J57" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K57" s="6" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="2:12">
@@ -6926,7 +6963,7 @@
         <v>2017</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E58" s="1">
         <v>1</v>
@@ -6938,16 +6975,16 @@
         <v>2</v>
       </c>
       <c r="H58" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I58" s="8" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="J58" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K58" s="6" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="2:12">
@@ -6955,7 +6992,7 @@
         <v>2018</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E59" s="1">
         <v>1</v>
@@ -6967,16 +7004,16 @@
         <v>2</v>
       </c>
       <c r="H59" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I59" s="8" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="J59" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K59" s="6" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="2:12">
@@ -6984,7 +7021,7 @@
         <v>2019</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E60" s="1">
         <v>1</v>
@@ -6996,16 +7033,16 @@
         <v>2</v>
       </c>
       <c r="H60" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I60" s="8" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="J60" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K60" s="6" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="2:12">
@@ -7013,7 +7050,7 @@
         <v>2020</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E61" s="1">
         <v>1</v>
@@ -7025,16 +7062,16 @@
         <v>2</v>
       </c>
       <c r="H61" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I61" s="8" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="J61" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K61" s="6" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="2:12">
@@ -7042,7 +7079,7 @@
         <v>2021</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E62" s="1">
         <v>1</v>
@@ -7054,16 +7091,16 @@
         <v>2</v>
       </c>
       <c r="H62" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I62" s="8" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="J62" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K62" s="6" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="2:12">
@@ -7071,7 +7108,7 @@
         <v>2022</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E63" s="1">
         <v>1</v>
@@ -7083,16 +7120,16 @@
         <v>2</v>
       </c>
       <c r="H63" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I63" s="8" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="J63" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K63" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="2:12">
@@ -7100,7 +7137,7 @@
         <v>2023</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E64" s="1">
         <v>1</v>
@@ -7112,16 +7149,16 @@
         <v>2</v>
       </c>
       <c r="H64" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I64" s="8" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="J64" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K64" s="6" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:11">
@@ -7129,7 +7166,7 @@
         <v>2024</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E65" s="1">
         <v>1</v>
@@ -7141,16 +7178,16 @@
         <v>2</v>
       </c>
       <c r="H65" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I65" s="8" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="J65" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K65" s="6" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="3:11">
@@ -7158,7 +7195,7 @@
         <v>2025</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E66" s="1">
         <v>1</v>
@@ -7170,16 +7207,16 @@
         <v>2</v>
       </c>
       <c r="H66" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I66" s="8" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="J66" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K66" s="6" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:11">
@@ -7197,7 +7234,7 @@
         <v>2026</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E68" s="1">
         <v>1</v>
@@ -7209,16 +7246,16 @@
         <v>2</v>
       </c>
       <c r="H68" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I68" s="8" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="J68" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K68" s="6" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:11">
@@ -7226,7 +7263,7 @@
         <v>2027</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E69" s="1">
         <v>1</v>
@@ -7238,16 +7275,16 @@
         <v>2</v>
       </c>
       <c r="H69" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I69" s="8" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="J69" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K69" s="6" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:11">
@@ -7255,7 +7292,7 @@
         <v>2028</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E70" s="1">
         <v>1</v>
@@ -7267,16 +7304,16 @@
         <v>2</v>
       </c>
       <c r="H70" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I70" s="8" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="J70" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K70" s="6" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:11">
@@ -7284,7 +7321,7 @@
         <v>2029</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="E71" s="1">
         <v>1</v>
@@ -7296,16 +7333,16 @@
         <v>2</v>
       </c>
       <c r="H71" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I71" s="8" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="J71" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K71" s="6" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:11">
@@ -7313,7 +7350,7 @@
         <v>2030</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="E72" s="1">
         <v>1</v>
@@ -7325,16 +7362,16 @@
         <v>2</v>
       </c>
       <c r="H72" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I72" s="8" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="J72" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K72" s="6" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:11">
@@ -7342,7 +7379,7 @@
         <v>2031</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E73" s="1">
         <v>1</v>
@@ -7354,16 +7391,16 @@
         <v>2</v>
       </c>
       <c r="H73" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I73" s="8" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="J73" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K73" s="6" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:11">
@@ -7371,7 +7408,7 @@
         <v>2032</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="E74" s="1">
         <v>1</v>
@@ -7383,16 +7420,16 @@
         <v>2</v>
       </c>
       <c r="H74" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I74" s="8" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="J74" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K74" s="6" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:11">
@@ -7400,7 +7437,7 @@
         <v>2033</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E75" s="1">
         <v>1</v>
@@ -7412,16 +7449,16 @@
         <v>2</v>
       </c>
       <c r="H75" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I75" s="8" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="J75" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K75" s="6" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:11">
@@ -7429,7 +7466,7 @@
         <v>2034</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="E76" s="1">
         <v>1</v>
@@ -7441,16 +7478,16 @@
         <v>2</v>
       </c>
       <c r="H76" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I76" s="8" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="J76" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K76" s="6" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:11">
@@ -7458,7 +7495,7 @@
         <v>2035</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E77" s="1">
         <v>1</v>
@@ -7470,16 +7507,16 @@
         <v>2</v>
       </c>
       <c r="H77" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I77" s="8" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="J77" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K77" s="6" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="452">
   <si>
     <t>_id</t>
   </si>
@@ -801,6 +801,24 @@
   </si>
   <si>
     <t>201,202,203,204,205,206,207,208</t>
+  </si>
+  <si>
+    <t>虚无战士</t>
+  </si>
+  <si>
+    <t>211,212,213,214,215,216,217,218</t>
+  </si>
+  <si>
+    <t>虚无法师</t>
+  </si>
+  <si>
+    <t>221,222,223,224,225,226,227,228</t>
+  </si>
+  <si>
+    <t>虚无道士</t>
+  </si>
+  <si>
+    <t>231,232,233,234,235,236,237,238</t>
   </si>
   <si>
     <t>金装自选</t>
@@ -1613,12 +1631,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2410,7 +2428,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K122"/>
+  <dimension ref="A1:K125"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="4" max="4" width="16.625" customWidth="1"/>
@@ -4958,7 +4976,41 @@
         <v>237</v>
       </c>
     </row>
-    <row r="91" ht="14"/>
+    <row r="91" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A91" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C91" s="1">
+        <v>129</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="E91" s="1">
+        <v>1</v>
+      </c>
+      <c r="F91" s="4">
+        <v>0</v>
+      </c>
+      <c r="G91" s="4">
+        <v>2</v>
+      </c>
+      <c r="H91" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="I91" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="J91" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="K91" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
     <row r="92" customFormat="1" customHeight="1" spans="1:11">
       <c r="A92" s="1" t="s">
         <v>216</v>
@@ -4967,10 +5019,10 @@
         <v>216</v>
       </c>
       <c r="C92" s="1">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E92" s="1">
         <v>1</v>
@@ -4982,16 +5034,16 @@
         <v>2</v>
       </c>
       <c r="H92" s="8" t="s">
-        <v>147</v>
+        <v>195</v>
       </c>
       <c r="I92" s="8" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="J92" s="8" t="s">
-        <v>40</v>
+        <v>87</v>
       </c>
       <c r="K92" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="93" customFormat="1" customHeight="1" spans="1:11">
@@ -5002,199 +5054,183 @@
         <v>216</v>
       </c>
       <c r="C93" s="1">
+        <v>131</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="E93" s="1">
+        <v>1</v>
+      </c>
+      <c r="F93" s="4">
+        <v>0</v>
+      </c>
+      <c r="G93" s="4">
+        <v>2</v>
+      </c>
+      <c r="H93" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="I93" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="J93" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="K93" s="1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="94" ht="14"/>
+    <row r="95" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A95" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C95" s="1">
+        <v>137</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="E95" s="1">
+        <v>1</v>
+      </c>
+      <c r="F95" s="4">
+        <v>0</v>
+      </c>
+      <c r="G95" s="4">
+        <v>2</v>
+      </c>
+      <c r="H95" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="I95" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="J95" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="K95" s="1" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="96" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A96" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C96" s="1">
         <v>138</v>
       </c>
-      <c r="D93" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="E93" s="1">
-        <v>1</v>
-      </c>
-      <c r="F93" s="4">
-        <v>0</v>
-      </c>
-      <c r="G93" s="4">
-        <v>2</v>
-      </c>
-      <c r="H93" s="8" t="s">
-        <v>242</v>
-      </c>
-      <c r="I93" s="8" t="s">
-        <v>243</v>
-      </c>
-      <c r="J93" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="K93" s="1" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="94" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A94" s="1" t="s">
+      <c r="D96" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="E96" s="1">
+        <v>1</v>
+      </c>
+      <c r="F96" s="4">
+        <v>0</v>
+      </c>
+      <c r="G96" s="4">
+        <v>2</v>
+      </c>
+      <c r="H96" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="I96" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="J96" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="K96" s="1" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="97" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A97" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="B94" s="1" t="s">
+      <c r="B97" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="C94" s="1">
+      <c r="C97" s="1">
         <v>139</v>
       </c>
-      <c r="D94" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="E94" s="1">
-        <v>1</v>
-      </c>
-      <c r="F94" s="4">
-        <v>0</v>
-      </c>
-      <c r="G94" s="4">
-        <v>2</v>
-      </c>
-      <c r="H94" s="8" t="s">
-        <v>242</v>
-      </c>
-      <c r="I94" s="8" t="s">
-        <v>246</v>
-      </c>
-      <c r="J94" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="K94" s="1" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="95" ht="14"/>
-    <row r="96" ht="14"/>
-    <row r="97" ht="14"/>
+      <c r="D97" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="E97" s="1">
+        <v>1</v>
+      </c>
+      <c r="F97" s="4">
+        <v>0</v>
+      </c>
+      <c r="G97" s="4">
+        <v>2</v>
+      </c>
+      <c r="H97" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="I97" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="J97" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="K97" s="1" t="s">
+        <v>251</v>
+      </c>
+    </row>
     <row r="98" ht="14"/>
     <row r="99" ht="14"/>
     <row r="100" ht="14"/>
     <row r="101" ht="14"/>
     <row r="102" ht="14"/>
     <row r="103" ht="14"/>
-    <row r="104" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C104" s="1">
+    <row r="104" ht="14"/>
+    <row r="105" ht="14"/>
+    <row r="106" ht="14"/>
+    <row r="107" customFormat="1" customHeight="1" spans="1:11">
+      <c r="C107" s="1">
         <v>201</v>
       </c>
-      <c r="D104" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="E104" s="1">
-        <v>1</v>
-      </c>
-      <c r="F104" s="4">
-        <v>0</v>
-      </c>
-      <c r="G104" s="4">
-        <v>2</v>
-      </c>
-      <c r="H104" s="8" t="s">
-        <v>248</v>
-      </c>
-      <c r="I104" s="8" t="s">
-        <v>249</v>
-      </c>
-      <c r="J104" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="K104" s="1" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="105" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C105" s="1">
-        <v>202</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="E105" s="1">
-        <v>1</v>
-      </c>
-      <c r="F105" s="4">
-        <v>0</v>
-      </c>
-      <c r="G105" s="4">
-        <v>2</v>
-      </c>
-      <c r="H105" s="8" t="s">
-        <v>248</v>
-      </c>
-      <c r="I105" s="8" t="s">
-        <v>252</v>
-      </c>
-      <c r="J105" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="K105" s="1" t="s">
+      <c r="D107" s="1" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="106" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C106" s="1">
-        <v>203</v>
-      </c>
-      <c r="D106" s="1" t="s">
+      <c r="E107" s="1">
+        <v>1</v>
+      </c>
+      <c r="F107" s="4">
+        <v>0</v>
+      </c>
+      <c r="G107" s="4">
+        <v>2</v>
+      </c>
+      <c r="H107" s="8" t="s">
         <v>254</v>
       </c>
-      <c r="E106" s="1">
-        <v>1</v>
-      </c>
-      <c r="F106" s="4">
-        <v>0</v>
-      </c>
-      <c r="G106" s="4">
-        <v>2</v>
-      </c>
-      <c r="H106" s="8" t="s">
-        <v>248</v>
-      </c>
-      <c r="I106" s="8" t="s">
+      <c r="I107" s="8" t="s">
         <v>255</v>
-      </c>
-      <c r="J106" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="K106" s="1" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="107" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C107" s="1">
-        <v>204</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="E107" s="1">
-        <v>1</v>
-      </c>
-      <c r="F107" s="4">
-        <v>0</v>
-      </c>
-      <c r="G107" s="4">
-        <v>2</v>
-      </c>
-      <c r="H107" s="8" t="s">
-        <v>248</v>
-      </c>
-      <c r="I107" s="8" t="s">
-        <v>258</v>
       </c>
       <c r="J107" s="8" t="s">
         <v>32</v>
       </c>
       <c r="K107" s="1" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="108" customFormat="1" customHeight="1" spans="3:11">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="108" customFormat="1" customHeight="1" spans="1:11">
       <c r="C108" s="1">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="E108" s="1">
         <v>1</v>
@@ -5206,25 +5242,53 @@
         <v>2</v>
       </c>
       <c r="H108" s="8" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="I108" s="8" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="J108" s="8" t="s">
         <v>32</v>
       </c>
       <c r="K108" s="1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="109" customFormat="1" customHeight="1" spans="1:11">
+      <c r="C109" s="1">
+        <v>203</v>
+      </c>
+      <c r="D109" s="1" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="109" ht="14"/>
-    <row r="110" customFormat="1" customHeight="1" spans="3:11">
+      <c r="E109" s="1">
+        <v>1</v>
+      </c>
+      <c r="F109" s="4">
+        <v>0</v>
+      </c>
+      <c r="G109" s="4">
+        <v>2</v>
+      </c>
+      <c r="H109" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="I109" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="J109" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="K109" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="110" customFormat="1" customHeight="1" spans="1:11">
       <c r="C110" s="1">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E110" s="1">
         <v>1</v>
@@ -5236,82 +5300,54 @@
         <v>2</v>
       </c>
       <c r="H110" s="8" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="I110" s="8" t="s">
         <v>264</v>
       </c>
       <c r="J110" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="K110" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="K110" s="1" t="s">
+    </row>
+    <row r="111" customFormat="1" customHeight="1" spans="1:11">
+      <c r="C111" s="1">
+        <v>205</v>
+      </c>
+      <c r="D111" s="1" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="111" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C111" s="1">
-        <v>208</v>
-      </c>
-      <c r="D111" s="1" t="s">
+      <c r="E111" s="1">
+        <v>1</v>
+      </c>
+      <c r="F111" s="4">
+        <v>0</v>
+      </c>
+      <c r="G111" s="4">
+        <v>2</v>
+      </c>
+      <c r="H111" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="I111" s="8" t="s">
         <v>267</v>
       </c>
-      <c r="E111" s="1">
-        <v>1</v>
-      </c>
-      <c r="F111" s="4">
-        <v>0</v>
-      </c>
-      <c r="G111" s="4">
-        <v>2</v>
-      </c>
-      <c r="H111" s="8" t="s">
-        <v>268</v>
-      </c>
-      <c r="I111" s="8" t="s">
-        <v>269</v>
-      </c>
       <c r="J111" s="8" t="s">
-        <v>141</v>
+        <v>32</v>
       </c>
       <c r="K111" s="1" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="112" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C112" s="1">
-        <v>209</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="E112" s="1">
-        <v>1</v>
-      </c>
-      <c r="F112" s="4">
-        <v>0</v>
-      </c>
-      <c r="G112" s="4">
-        <v>2</v>
-      </c>
-      <c r="H112" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="I112" s="8" t="s">
-        <v>272</v>
-      </c>
-      <c r="J112" s="8" t="s">
-        <v>265</v>
-      </c>
-      <c r="K112" s="1" t="s">
-        <v>273</v>
-      </c>
-    </row>
+        <v>266</v>
+      </c>
+    </row>
+    <row r="112" ht="14"/>
     <row r="113" customFormat="1" customHeight="1" spans="3:11">
       <c r="C113" s="1">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="E113" s="1">
         <v>1</v>
@@ -5323,24 +5359,24 @@
         <v>2</v>
       </c>
       <c r="H113" s="8" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="I113" s="8" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="J113" s="8" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="K113" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="114" customFormat="1" customHeight="1" spans="3:11">
       <c r="C114" s="1">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="E114" s="1">
         <v>1</v>
@@ -5352,24 +5388,24 @@
         <v>2</v>
       </c>
       <c r="H114" s="8" t="s">
-        <v>248</v>
+        <v>274</v>
       </c>
       <c r="I114" s="8" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="J114" s="8" t="s">
-        <v>265</v>
+        <v>141</v>
       </c>
       <c r="K114" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="115" customFormat="1" customHeight="1" spans="3:11">
       <c r="C115" s="1">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E115" s="1">
         <v>1</v>
@@ -5381,25 +5417,112 @@
         <v>2</v>
       </c>
       <c r="H115" s="8" t="s">
-        <v>248</v>
+        <v>269</v>
       </c>
       <c r="I115" s="8" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="J115" s="8" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="K115" s="1" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="116" ht="14"/>
-    <row r="117" ht="14"/>
-    <row r="118" ht="14"/>
+    <row r="116" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C116" s="1">
+        <v>210</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="E116" s="1">
+        <v>1</v>
+      </c>
+      <c r="F116" s="4">
+        <v>0</v>
+      </c>
+      <c r="G116" s="4">
+        <v>2</v>
+      </c>
+      <c r="H116" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="I116" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="J116" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="K116" s="1" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="117" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C117" s="1">
+        <v>211</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="E117" s="1">
+        <v>1</v>
+      </c>
+      <c r="F117" s="4">
+        <v>0</v>
+      </c>
+      <c r="G117" s="4">
+        <v>2</v>
+      </c>
+      <c r="H117" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="I117" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="J117" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="K117" s="1" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="118" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C118" s="1">
+        <v>212</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="E118" s="1">
+        <v>1</v>
+      </c>
+      <c r="F118" s="4">
+        <v>0</v>
+      </c>
+      <c r="G118" s="4">
+        <v>2</v>
+      </c>
+      <c r="H118" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="I118" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="J118" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="K118" s="1" t="s">
+        <v>285</v>
+      </c>
+    </row>
     <row r="119" ht="14"/>
     <row r="120" ht="14"/>
     <row r="121" ht="14"/>
     <row r="122" ht="14"/>
+    <row r="123" ht="14"/>
+    <row r="124" ht="14"/>
+    <row r="125" ht="14"/>
   </sheetData>
   <dataValidations count="2">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:E5 H3:K5" errorStyle="warning">
@@ -5525,7 +5648,7 @@
         <v>1001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -5540,13 +5663,13 @@
         <v>14</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="J6" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5554,7 +5677,7 @@
         <v>1002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -5569,13 +5692,13 @@
         <v>14</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="J7" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5583,7 +5706,7 @@
         <v>1003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -5598,13 +5721,13 @@
         <v>14</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="J8" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5612,7 +5735,7 @@
         <v>1004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
@@ -5627,13 +5750,13 @@
         <v>14</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="J9" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5641,7 +5764,7 @@
         <v>1005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -5656,13 +5779,13 @@
         <v>14</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="J10" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5670,7 +5793,7 @@
         <v>1006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -5685,13 +5808,13 @@
         <v>14</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="J11" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5699,7 +5822,7 @@
         <v>1007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
@@ -5714,13 +5837,13 @@
         <v>14</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="J12" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5728,7 +5851,7 @@
         <v>1008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
@@ -5743,13 +5866,13 @@
         <v>14</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="J13" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5757,7 +5880,7 @@
         <v>1009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
@@ -5772,13 +5895,13 @@
         <v>14</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="J14" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5786,7 +5909,7 @@
         <v>1010</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
@@ -5801,13 +5924,13 @@
         <v>14</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="J15" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5815,7 +5938,7 @@
         <v>1011</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="E16" s="1">
         <v>1</v>
@@ -5830,13 +5953,13 @@
         <v>14</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="J16" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5844,7 +5967,7 @@
         <v>1012</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="E17" s="1">
         <v>1</v>
@@ -5859,13 +5982,13 @@
         <v>14</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="J17" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5873,7 +5996,7 @@
         <v>1013</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="E18" s="1">
         <v>1</v>
@@ -5888,13 +6011,13 @@
         <v>14</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="J18" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5902,7 +6025,7 @@
         <v>1014</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="E19" s="1">
         <v>1</v>
@@ -5917,13 +6040,13 @@
         <v>14</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="J19" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1"/>
@@ -5932,7 +6055,7 @@
         <v>1101</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
@@ -5947,13 +6070,13 @@
         <v>14</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="J21" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5961,7 +6084,7 @@
         <v>1102</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
@@ -5976,13 +6099,13 @@
         <v>14</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="J22" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5990,7 +6113,7 @@
         <v>1103</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
@@ -6005,13 +6128,13 @@
         <v>14</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="J23" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6019,7 +6142,7 @@
         <v>1104</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
@@ -6034,13 +6157,13 @@
         <v>14</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="J24" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6048,7 +6171,7 @@
         <v>1105</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="E25" s="1">
         <v>1</v>
@@ -6063,13 +6186,13 @@
         <v>14</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="J25" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6077,7 +6200,7 @@
         <v>1106</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
@@ -6092,13 +6215,13 @@
         <v>14</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="J26" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6106,7 +6229,7 @@
         <v>1107</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="E27" s="1">
         <v>1</v>
@@ -6121,13 +6244,13 @@
         <v>14</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="J27" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6135,7 +6258,7 @@
         <v>1108</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="E28" s="1">
         <v>1</v>
@@ -6150,13 +6273,13 @@
         <v>14</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="J28" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6164,7 +6287,7 @@
         <v>1109</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
@@ -6179,13 +6302,13 @@
         <v>14</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="J29" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6193,7 +6316,7 @@
         <v>1110</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
@@ -6208,13 +6331,13 @@
         <v>14</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="J30" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6222,7 +6345,7 @@
         <v>1111</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
@@ -6237,13 +6360,13 @@
         <v>14</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="J31" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6251,7 +6374,7 @@
         <v>1112</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="E32" s="1">
         <v>1</v>
@@ -6266,13 +6389,13 @@
         <v>14</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="J32" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="2:12">
@@ -6293,7 +6416,7 @@
         <v>1201</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="E34" s="1">
         <v>1</v>
@@ -6308,13 +6431,13 @@
         <v>133</v>
       </c>
       <c r="I34" s="8" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="J34" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="2:12">
@@ -6323,7 +6446,7 @@
         <v>1202</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="E35" s="1">
         <v>1</v>
@@ -6335,16 +6458,16 @@
         <v>2</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="J35" s="8" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="L35" s="2"/>
     </row>
@@ -6354,7 +6477,7 @@
         <v>1203</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="E36" s="1">
         <v>1</v>
@@ -6366,16 +6489,16 @@
         <v>2</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="I36" s="8" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="J36" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="L36" s="2"/>
     </row>
@@ -6384,7 +6507,7 @@
         <v>1204</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="E37" s="1">
         <v>1</v>
@@ -6399,13 +6522,13 @@
         <v>133</v>
       </c>
       <c r="I37" s="8" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="J37" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="2:12">
@@ -6413,7 +6536,7 @@
         <v>1205</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="E38" s="1">
         <v>1</v>
@@ -6428,13 +6551,13 @@
         <v>147</v>
       </c>
       <c r="I38" s="8" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="J38" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="2:12">
@@ -6442,7 +6565,7 @@
         <v>1206</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="E39" s="1">
         <v>1</v>
@@ -6457,13 +6580,13 @@
         <v>163</v>
       </c>
       <c r="I39" s="8" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="J39" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="2:12">
@@ -6471,7 +6594,7 @@
         <v>2001</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="E41" s="1">
         <v>1</v>
@@ -6483,16 +6606,16 @@
         <v>2</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="I41" s="8" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="J41" s="8" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="K41" s="5" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="2:12">
@@ -6500,7 +6623,7 @@
         <v>2002</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="E42" s="1">
         <v>1</v>
@@ -6512,16 +6635,16 @@
         <v>2</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="I42" s="8" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="J42" s="8" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="K42" s="5" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="2:12">
@@ -6529,7 +6652,7 @@
         <v>2003</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="E43" s="1">
         <v>1</v>
@@ -6541,16 +6664,16 @@
         <v>2</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="I43" s="8" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="J43" s="8" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="K43" s="5" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="2:12">
@@ -6558,28 +6681,28 @@
         <v>2004</v>
       </c>
       <c r="D44" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="E44" s="1">
+        <v>1</v>
+      </c>
+      <c r="F44" s="4">
+        <v>0</v>
+      </c>
+      <c r="G44" s="1">
+        <v>2</v>
+      </c>
+      <c r="H44" s="8" t="s">
         <v>382</v>
       </c>
-      <c r="E44" s="1">
-        <v>1</v>
-      </c>
-      <c r="F44" s="4">
-        <v>0</v>
-      </c>
-      <c r="G44" s="1">
-        <v>2</v>
-      </c>
-      <c r="H44" s="8" t="s">
-        <v>376</v>
-      </c>
       <c r="I44" s="8" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="J44" s="8" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="K44" s="5" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="2:12">
@@ -6587,7 +6710,7 @@
         <v>2005</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="E45" s="1">
         <v>1</v>
@@ -6599,16 +6722,16 @@
         <v>2</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="I45" s="8" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="J45" s="8" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="K45" s="5" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="2:12">
@@ -6616,7 +6739,7 @@
         <v>2006</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="E46" s="1">
         <v>1</v>
@@ -6628,16 +6751,16 @@
         <v>2</v>
       </c>
       <c r="H46" s="8" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="I46" s="8" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="J46" s="8" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" customHeight="1" spans="2:12">
@@ -6646,7 +6769,7 @@
         <v>2007</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="E47" s="1">
         <v>1</v>
@@ -6658,16 +6781,16 @@
         <v>2</v>
       </c>
       <c r="H47" s="8" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="I47" s="8" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="J47" s="8" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="K47" s="5" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="L47" s="2"/>
     </row>
@@ -6677,7 +6800,7 @@
         <v>2008</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="E48" s="1">
         <v>1</v>
@@ -6689,16 +6812,16 @@
         <v>2</v>
       </c>
       <c r="H48" s="8" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="I48" s="8" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="J48" s="8" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="K48" s="5" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="L48" s="2"/>
     </row>
@@ -6708,7 +6831,7 @@
         <v>2009</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="E49" s="1">
         <v>1</v>
@@ -6720,16 +6843,16 @@
         <v>2</v>
       </c>
       <c r="H49" s="8" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="I49" s="8" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="J49" s="8" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="K49" s="5" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="L49" s="2"/>
     </row>
@@ -6739,7 +6862,7 @@
         <v>2010</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="E50" s="1">
         <v>1</v>
@@ -6751,16 +6874,16 @@
         <v>2</v>
       </c>
       <c r="H50" s="8" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="I50" s="8" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="J50" s="8" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="K50" s="5" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="L50" s="2"/>
     </row>
@@ -6770,7 +6893,7 @@
         <v>2011</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="E51" s="1">
         <v>1</v>
@@ -6782,16 +6905,16 @@
         <v>2</v>
       </c>
       <c r="H51" s="8" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="I51" s="8" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="J51" s="8" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="K51" s="5" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="L51" s="2"/>
     </row>
@@ -6801,7 +6924,7 @@
         <v>2012</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="E52" s="1">
         <v>1</v>
@@ -6813,16 +6936,16 @@
         <v>2</v>
       </c>
       <c r="H52" s="8" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="I52" s="8" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="J52" s="8" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="K52" s="5" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="L52" s="2"/>
     </row>
@@ -6844,7 +6967,7 @@
         <v>2013</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="E54" s="1">
         <v>1</v>
@@ -6856,16 +6979,16 @@
         <v>2</v>
       </c>
       <c r="H54" s="8" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="I54" s="8" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="J54" s="8" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="K54" s="6" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="L54" s="2"/>
     </row>
@@ -6875,7 +6998,7 @@
         <v>2014</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="E55" s="1">
         <v>1</v>
@@ -6887,16 +7010,16 @@
         <v>2</v>
       </c>
       <c r="H55" s="8" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="I55" s="8" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="J55" s="8" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="K55" s="6" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="L55" s="2"/>
     </row>
@@ -6905,7 +7028,7 @@
         <v>2015</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="E56" s="1">
         <v>1</v>
@@ -6917,16 +7040,16 @@
         <v>2</v>
       </c>
       <c r="H56" s="8" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="I56" s="8" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="J56" s="8" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="K56" s="6" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="2:12">
@@ -6934,7 +7057,7 @@
         <v>2016</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="E57" s="1">
         <v>1</v>
@@ -6946,16 +7069,16 @@
         <v>2</v>
       </c>
       <c r="H57" s="8" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="I57" s="8" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="J57" s="8" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="K57" s="6" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="2:12">
@@ -6963,7 +7086,7 @@
         <v>2017</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="E58" s="1">
         <v>1</v>
@@ -6975,16 +7098,16 @@
         <v>2</v>
       </c>
       <c r="H58" s="8" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="I58" s="8" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="J58" s="8" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="K58" s="6" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="2:12">
@@ -6992,7 +7115,7 @@
         <v>2018</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="E59" s="1">
         <v>1</v>
@@ -7004,16 +7127,16 @@
         <v>2</v>
       </c>
       <c r="H59" s="8" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="I59" s="8" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="J59" s="8" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="K59" s="6" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="2:12">
@@ -7021,7 +7144,7 @@
         <v>2019</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="E60" s="1">
         <v>1</v>
@@ -7033,16 +7156,16 @@
         <v>2</v>
       </c>
       <c r="H60" s="8" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="I60" s="8" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="J60" s="8" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="K60" s="6" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="2:12">
@@ -7050,7 +7173,7 @@
         <v>2020</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="E61" s="1">
         <v>1</v>
@@ -7062,16 +7185,16 @@
         <v>2</v>
       </c>
       <c r="H61" s="8" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="I61" s="8" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="J61" s="8" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="K61" s="6" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="2:12">
@@ -7079,7 +7202,7 @@
         <v>2021</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="E62" s="1">
         <v>1</v>
@@ -7091,16 +7214,16 @@
         <v>2</v>
       </c>
       <c r="H62" s="8" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="I62" s="8" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="J62" s="8" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="K62" s="6" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="2:12">
@@ -7108,7 +7231,7 @@
         <v>2022</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="E63" s="1">
         <v>1</v>
@@ -7120,16 +7243,16 @@
         <v>2</v>
       </c>
       <c r="H63" s="8" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="I63" s="8" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="J63" s="8" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="K63" s="6" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="2:12">
@@ -7137,7 +7260,7 @@
         <v>2023</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="E64" s="1">
         <v>1</v>
@@ -7149,16 +7272,16 @@
         <v>2</v>
       </c>
       <c r="H64" s="8" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="I64" s="8" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="J64" s="8" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="K64" s="6" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:11">
@@ -7166,7 +7289,7 @@
         <v>2024</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="E65" s="1">
         <v>1</v>
@@ -7178,16 +7301,16 @@
         <v>2</v>
       </c>
       <c r="H65" s="8" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="I65" s="8" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="J65" s="8" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="K65" s="6" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="3:11">
@@ -7195,7 +7318,7 @@
         <v>2025</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="E66" s="1">
         <v>1</v>
@@ -7207,16 +7330,16 @@
         <v>2</v>
       </c>
       <c r="H66" s="8" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="I66" s="8" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="J66" s="8" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="K66" s="6" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:11">
@@ -7234,7 +7357,7 @@
         <v>2026</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="E68" s="1">
         <v>1</v>
@@ -7246,16 +7369,16 @@
         <v>2</v>
       </c>
       <c r="H68" s="8" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="I68" s="8" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="J68" s="8" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="K68" s="6" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:11">
@@ -7263,7 +7386,7 @@
         <v>2027</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="E69" s="1">
         <v>1</v>
@@ -7275,16 +7398,16 @@
         <v>2</v>
       </c>
       <c r="H69" s="8" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="I69" s="8" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="J69" s="8" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="K69" s="6" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:11">
@@ -7292,7 +7415,7 @@
         <v>2028</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="E70" s="1">
         <v>1</v>
@@ -7304,16 +7427,16 @@
         <v>2</v>
       </c>
       <c r="H70" s="8" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="I70" s="8" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="J70" s="8" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="K70" s="6" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:11">
@@ -7321,7 +7444,7 @@
         <v>2029</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="E71" s="1">
         <v>1</v>
@@ -7333,16 +7456,16 @@
         <v>2</v>
       </c>
       <c r="H71" s="8" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="I71" s="8" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="J71" s="8" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="K71" s="6" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:11">
@@ -7350,7 +7473,7 @@
         <v>2030</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="E72" s="1">
         <v>1</v>
@@ -7362,16 +7485,16 @@
         <v>2</v>
       </c>
       <c r="H72" s="8" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="I72" s="8" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="J72" s="8" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="K72" s="6" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:11">
@@ -7379,7 +7502,7 @@
         <v>2031</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="E73" s="1">
         <v>1</v>
@@ -7391,16 +7514,16 @@
         <v>2</v>
       </c>
       <c r="H73" s="8" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="I73" s="8" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="J73" s="8" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="K73" s="6" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:11">
@@ -7408,7 +7531,7 @@
         <v>2032</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="E74" s="1">
         <v>1</v>
@@ -7420,16 +7543,16 @@
         <v>2</v>
       </c>
       <c r="H74" s="8" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="I74" s="8" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="J74" s="8" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="K74" s="6" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:11">
@@ -7437,7 +7560,7 @@
         <v>2033</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="E75" s="1">
         <v>1</v>
@@ -7449,16 +7572,16 @@
         <v>2</v>
       </c>
       <c r="H75" s="8" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="I75" s="8" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="J75" s="8" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="K75" s="6" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:11">
@@ -7466,7 +7589,7 @@
         <v>2034</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="E76" s="1">
         <v>1</v>
@@ -7478,16 +7601,16 @@
         <v>2</v>
       </c>
       <c r="H76" s="8" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="I76" s="8" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="J76" s="8" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="K76" s="6" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:11">
@@ -7495,7 +7618,7 @@
         <v>2035</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="E77" s="1">
         <v>1</v>
@@ -7507,16 +7630,16 @@
         <v>2</v>
       </c>
       <c r="H77" s="8" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="I77" s="8" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="J77" s="8" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="K77" s="6" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="923" uniqueCount="457">
   <si>
     <t>_id</t>
   </si>
@@ -945,6 +945,21 @@
   </si>
   <si>
     <t>211,212,213</t>
+  </si>
+  <si>
+    <t>50暗金坐骑自选</t>
+  </si>
+  <si>
+    <t>23,23,23</t>
+  </si>
+  <si>
+    <t>901,902,903</t>
+  </si>
+  <si>
+    <t>70暗金坐骑自选</t>
+  </si>
+  <si>
+    <t>911,912,913</t>
   </si>
   <si>
     <t>金色刺杀自选</t>
@@ -5518,8 +5533,64 @@
     </row>
     <row r="119" ht="14"/>
     <row r="120" ht="14"/>
-    <row r="121" ht="14"/>
-    <row r="122" ht="14"/>
+    <row r="121" ht="14" spans="3:11">
+      <c r="C121" s="1">
+        <v>301</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E121" s="1">
+        <v>1</v>
+      </c>
+      <c r="F121" s="4">
+        <v>0</v>
+      </c>
+      <c r="G121" s="4">
+        <v>2</v>
+      </c>
+      <c r="H121" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="I121" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="J121" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="K121" s="1" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="122" ht="14" spans="3:11">
+      <c r="C122" s="1">
+        <v>302</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="E122" s="1">
+        <v>1</v>
+      </c>
+      <c r="F122" s="4">
+        <v>0</v>
+      </c>
+      <c r="G122" s="4">
+        <v>2</v>
+      </c>
+      <c r="H122" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="I122" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="J122" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="K122" s="1" t="s">
+        <v>290</v>
+      </c>
+    </row>
     <row r="123" ht="14"/>
     <row r="124" ht="14"/>
     <row r="125" ht="14"/>
@@ -5648,7 +5719,7 @@
         <v>1001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -5663,13 +5734,13 @@
         <v>14</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="J6" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5677,7 +5748,7 @@
         <v>1002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -5692,13 +5763,13 @@
         <v>14</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="J7" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5706,7 +5777,7 @@
         <v>1003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -5721,13 +5792,13 @@
         <v>14</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="J8" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5735,7 +5806,7 @@
         <v>1004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
@@ -5750,13 +5821,13 @@
         <v>14</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="J9" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5764,7 +5835,7 @@
         <v>1005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -5779,13 +5850,13 @@
         <v>14</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="J10" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5793,7 +5864,7 @@
         <v>1006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -5808,13 +5879,13 @@
         <v>14</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="J11" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5822,7 +5893,7 @@
         <v>1007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
@@ -5837,13 +5908,13 @@
         <v>14</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="J12" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5851,7 +5922,7 @@
         <v>1008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
@@ -5866,13 +5937,13 @@
         <v>14</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="J13" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5880,7 +5951,7 @@
         <v>1009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
@@ -5895,13 +5966,13 @@
         <v>14</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="J14" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5909,7 +5980,7 @@
         <v>1010</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
@@ -5924,13 +5995,13 @@
         <v>14</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="J15" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5938,7 +6009,7 @@
         <v>1011</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="E16" s="1">
         <v>1</v>
@@ -5953,13 +6024,13 @@
         <v>14</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="J16" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5967,7 +6038,7 @@
         <v>1012</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="E17" s="1">
         <v>1</v>
@@ -5982,13 +6053,13 @@
         <v>14</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="J17" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5996,7 +6067,7 @@
         <v>1013</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="E18" s="1">
         <v>1</v>
@@ -6011,13 +6082,13 @@
         <v>14</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="J18" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6025,7 +6096,7 @@
         <v>1014</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="E19" s="1">
         <v>1</v>
@@ -6040,13 +6111,13 @@
         <v>14</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="J19" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1"/>
@@ -6055,7 +6126,7 @@
         <v>1101</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
@@ -6070,13 +6141,13 @@
         <v>14</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="J21" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6084,7 +6155,7 @@
         <v>1102</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
@@ -6099,13 +6170,13 @@
         <v>14</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="J22" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6113,7 +6184,7 @@
         <v>1103</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
@@ -6128,13 +6199,13 @@
         <v>14</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="J23" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6142,7 +6213,7 @@
         <v>1104</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
@@ -6157,13 +6228,13 @@
         <v>14</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="J24" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6171,7 +6242,7 @@
         <v>1105</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="E25" s="1">
         <v>1</v>
@@ -6186,13 +6257,13 @@
         <v>14</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="J25" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6200,7 +6271,7 @@
         <v>1106</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
@@ -6215,13 +6286,13 @@
         <v>14</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="J26" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6229,7 +6300,7 @@
         <v>1107</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="E27" s="1">
         <v>1</v>
@@ -6244,13 +6315,13 @@
         <v>14</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="J27" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6258,7 +6329,7 @@
         <v>1108</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="E28" s="1">
         <v>1</v>
@@ -6273,13 +6344,13 @@
         <v>14</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="J28" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6287,7 +6358,7 @@
         <v>1109</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
@@ -6302,13 +6373,13 @@
         <v>14</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="J29" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6316,7 +6387,7 @@
         <v>1110</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
@@ -6331,13 +6402,13 @@
         <v>14</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="J30" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6345,7 +6416,7 @@
         <v>1111</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
@@ -6360,13 +6431,13 @@
         <v>14</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="J31" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6374,7 +6445,7 @@
         <v>1112</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="E32" s="1">
         <v>1</v>
@@ -6389,13 +6460,13 @@
         <v>14</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="J32" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="2:12">
@@ -6416,7 +6487,7 @@
         <v>1201</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="E34" s="1">
         <v>1</v>
@@ -6431,13 +6502,13 @@
         <v>133</v>
       </c>
       <c r="I34" s="8" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="J34" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="2:12">
@@ -6446,7 +6517,7 @@
         <v>1202</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="E35" s="1">
         <v>1</v>
@@ -6458,16 +6529,16 @@
         <v>2</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="J35" s="8" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="L35" s="2"/>
     </row>
@@ -6477,7 +6548,7 @@
         <v>1203</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="E36" s="1">
         <v>1</v>
@@ -6489,16 +6560,16 @@
         <v>2</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I36" s="8" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="J36" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="L36" s="2"/>
     </row>
@@ -6507,7 +6578,7 @@
         <v>1204</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="E37" s="1">
         <v>1</v>
@@ -6522,13 +6593,13 @@
         <v>133</v>
       </c>
       <c r="I37" s="8" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="J37" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="2:12">
@@ -6536,7 +6607,7 @@
         <v>1205</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="E38" s="1">
         <v>1</v>
@@ -6551,13 +6622,13 @@
         <v>147</v>
       </c>
       <c r="I38" s="8" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="J38" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="2:12">
@@ -6565,7 +6636,7 @@
         <v>1206</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="E39" s="1">
         <v>1</v>
@@ -6580,13 +6651,13 @@
         <v>163</v>
       </c>
       <c r="I39" s="8" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="J39" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="2:12">
@@ -6594,7 +6665,7 @@
         <v>2001</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="E41" s="1">
         <v>1</v>
@@ -6606,16 +6677,16 @@
         <v>2</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="I41" s="8" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="J41" s="8" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="K41" s="5" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="2:12">
@@ -6623,7 +6694,7 @@
         <v>2002</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="E42" s="1">
         <v>1</v>
@@ -6635,16 +6706,16 @@
         <v>2</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="I42" s="8" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="J42" s="8" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="K42" s="5" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="2:12">
@@ -6652,7 +6723,7 @@
         <v>2003</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="E43" s="1">
         <v>1</v>
@@ -6664,16 +6735,16 @@
         <v>2</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="I43" s="8" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="J43" s="8" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="K43" s="5" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="2:12">
@@ -6681,7 +6752,7 @@
         <v>2004</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="E44" s="1">
         <v>1</v>
@@ -6693,16 +6764,16 @@
         <v>2</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="I44" s="8" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="J44" s="8" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="K44" s="5" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="2:12">
@@ -6710,7 +6781,7 @@
         <v>2005</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="E45" s="1">
         <v>1</v>
@@ -6722,16 +6793,16 @@
         <v>2</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="I45" s="8" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="J45" s="8" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="K45" s="5" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="2:12">
@@ -6739,7 +6810,7 @@
         <v>2006</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="E46" s="1">
         <v>1</v>
@@ -6751,16 +6822,16 @@
         <v>2</v>
       </c>
       <c r="H46" s="8" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="I46" s="8" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="J46" s="8" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" customHeight="1" spans="2:12">
@@ -6769,7 +6840,7 @@
         <v>2007</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="E47" s="1">
         <v>1</v>
@@ -6781,16 +6852,16 @@
         <v>2</v>
       </c>
       <c r="H47" s="8" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="I47" s="8" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="J47" s="8" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="K47" s="5" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="L47" s="2"/>
     </row>
@@ -6800,7 +6871,7 @@
         <v>2008</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="E48" s="1">
         <v>1</v>
@@ -6812,16 +6883,16 @@
         <v>2</v>
       </c>
       <c r="H48" s="8" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="I48" s="8" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="J48" s="8" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="K48" s="5" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="L48" s="2"/>
     </row>
@@ -6831,7 +6902,7 @@
         <v>2009</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E49" s="1">
         <v>1</v>
@@ -6843,16 +6914,16 @@
         <v>2</v>
       </c>
       <c r="H49" s="8" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="I49" s="8" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="J49" s="8" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="K49" s="5" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="L49" s="2"/>
     </row>
@@ -6862,7 +6933,7 @@
         <v>2010</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="E50" s="1">
         <v>1</v>
@@ -6874,16 +6945,16 @@
         <v>2</v>
       </c>
       <c r="H50" s="8" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="I50" s="8" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="J50" s="8" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="K50" s="5" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="L50" s="2"/>
     </row>
@@ -6893,7 +6964,7 @@
         <v>2011</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="E51" s="1">
         <v>1</v>
@@ -6905,16 +6976,16 @@
         <v>2</v>
       </c>
       <c r="H51" s="8" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="I51" s="8" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="J51" s="8" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="K51" s="5" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="L51" s="2"/>
     </row>
@@ -6924,7 +6995,7 @@
         <v>2012</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="E52" s="1">
         <v>1</v>
@@ -6936,16 +7007,16 @@
         <v>2</v>
       </c>
       <c r="H52" s="8" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="I52" s="8" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="J52" s="8" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="K52" s="5" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="L52" s="2"/>
     </row>
@@ -6967,7 +7038,7 @@
         <v>2013</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="E54" s="1">
         <v>1</v>
@@ -6979,16 +7050,16 @@
         <v>2</v>
       </c>
       <c r="H54" s="8" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="I54" s="8" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="J54" s="8" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="K54" s="6" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="L54" s="2"/>
     </row>
@@ -6998,7 +7069,7 @@
         <v>2014</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="E55" s="1">
         <v>1</v>
@@ -7010,16 +7081,16 @@
         <v>2</v>
       </c>
       <c r="H55" s="8" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="I55" s="8" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="J55" s="8" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="K55" s="6" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="L55" s="2"/>
     </row>
@@ -7028,7 +7099,7 @@
         <v>2015</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="E56" s="1">
         <v>1</v>
@@ -7040,16 +7111,16 @@
         <v>2</v>
       </c>
       <c r="H56" s="8" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="I56" s="8" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="J56" s="8" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="K56" s="6" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="2:12">
@@ -7057,7 +7128,7 @@
         <v>2016</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="E57" s="1">
         <v>1</v>
@@ -7069,16 +7140,16 @@
         <v>2</v>
       </c>
       <c r="H57" s="8" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="I57" s="8" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="J57" s="8" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="K57" s="6" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="2:12">
@@ -7086,7 +7157,7 @@
         <v>2017</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="E58" s="1">
         <v>1</v>
@@ -7098,16 +7169,16 @@
         <v>2</v>
       </c>
       <c r="H58" s="8" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="I58" s="8" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="J58" s="8" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="K58" s="6" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="2:12">
@@ -7115,7 +7186,7 @@
         <v>2018</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="E59" s="1">
         <v>1</v>
@@ -7127,16 +7198,16 @@
         <v>2</v>
       </c>
       <c r="H59" s="8" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="I59" s="8" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="J59" s="8" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="K59" s="6" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="2:12">
@@ -7144,7 +7215,7 @@
         <v>2019</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="E60" s="1">
         <v>1</v>
@@ -7156,16 +7227,16 @@
         <v>2</v>
       </c>
       <c r="H60" s="8" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="I60" s="8" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="J60" s="8" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="K60" s="6" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="2:12">
@@ -7173,7 +7244,7 @@
         <v>2020</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="E61" s="1">
         <v>1</v>
@@ -7185,16 +7256,16 @@
         <v>2</v>
       </c>
       <c r="H61" s="8" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="I61" s="8" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="J61" s="8" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="K61" s="6" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="2:12">
@@ -7202,7 +7273,7 @@
         <v>2021</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="E62" s="1">
         <v>1</v>
@@ -7214,16 +7285,16 @@
         <v>2</v>
       </c>
       <c r="H62" s="8" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="I62" s="8" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="J62" s="8" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="K62" s="6" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="2:12">
@@ -7231,7 +7302,7 @@
         <v>2022</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="E63" s="1">
         <v>1</v>
@@ -7243,16 +7314,16 @@
         <v>2</v>
       </c>
       <c r="H63" s="8" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="I63" s="8" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="J63" s="8" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="K63" s="6" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="2:12">
@@ -7260,7 +7331,7 @@
         <v>2023</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="E64" s="1">
         <v>1</v>
@@ -7272,16 +7343,16 @@
         <v>2</v>
       </c>
       <c r="H64" s="8" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="I64" s="8" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="J64" s="8" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="K64" s="6" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:11">
@@ -7289,7 +7360,7 @@
         <v>2024</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="E65" s="1">
         <v>1</v>
@@ -7301,16 +7372,16 @@
         <v>2</v>
       </c>
       <c r="H65" s="8" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="I65" s="8" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="J65" s="8" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="K65" s="6" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="3:11">
@@ -7318,7 +7389,7 @@
         <v>2025</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="E66" s="1">
         <v>1</v>
@@ -7330,16 +7401,16 @@
         <v>2</v>
       </c>
       <c r="H66" s="8" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="I66" s="8" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="J66" s="8" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="K66" s="6" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:11">
@@ -7357,7 +7428,7 @@
         <v>2026</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="E68" s="1">
         <v>1</v>
@@ -7369,16 +7440,16 @@
         <v>2</v>
       </c>
       <c r="H68" s="8" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="I68" s="8" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="J68" s="8" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="K68" s="6" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:11">
@@ -7386,7 +7457,7 @@
         <v>2027</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="E69" s="1">
         <v>1</v>
@@ -7398,16 +7469,16 @@
         <v>2</v>
       </c>
       <c r="H69" s="8" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="I69" s="8" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="J69" s="8" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="K69" s="6" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:11">
@@ -7415,7 +7486,7 @@
         <v>2028</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="E70" s="1">
         <v>1</v>
@@ -7427,16 +7498,16 @@
         <v>2</v>
       </c>
       <c r="H70" s="8" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="I70" s="8" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="J70" s="8" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="K70" s="6" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:11">
@@ -7444,7 +7515,7 @@
         <v>2029</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="E71" s="1">
         <v>1</v>
@@ -7456,16 +7527,16 @@
         <v>2</v>
       </c>
       <c r="H71" s="8" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="I71" s="8" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="J71" s="8" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="K71" s="6" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:11">
@@ -7473,7 +7544,7 @@
         <v>2030</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="E72" s="1">
         <v>1</v>
@@ -7485,16 +7556,16 @@
         <v>2</v>
       </c>
       <c r="H72" s="8" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="I72" s="8" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="J72" s="8" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="K72" s="6" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:11">
@@ -7502,7 +7573,7 @@
         <v>2031</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="E73" s="1">
         <v>1</v>
@@ -7514,16 +7585,16 @@
         <v>2</v>
       </c>
       <c r="H73" s="8" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="I73" s="8" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="J73" s="8" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="K73" s="6" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:11">
@@ -7531,7 +7602,7 @@
         <v>2032</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="E74" s="1">
         <v>1</v>
@@ -7543,16 +7614,16 @@
         <v>2</v>
       </c>
       <c r="H74" s="8" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="I74" s="8" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="J74" s="8" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="K74" s="6" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:11">
@@ -7560,7 +7631,7 @@
         <v>2033</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="E75" s="1">
         <v>1</v>
@@ -7572,16 +7643,16 @@
         <v>2</v>
       </c>
       <c r="H75" s="8" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="I75" s="8" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="J75" s="8" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="K75" s="6" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:11">
@@ -7589,7 +7660,7 @@
         <v>2034</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="E76" s="1">
         <v>1</v>
@@ -7601,16 +7672,16 @@
         <v>2</v>
       </c>
       <c r="H76" s="8" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="I76" s="8" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="J76" s="8" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="K76" s="6" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:11">
@@ -7618,7 +7689,7 @@
         <v>2035</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="E77" s="1">
         <v>1</v>
@@ -7630,16 +7701,16 @@
         <v>2</v>
       </c>
       <c r="H77" s="8" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="I77" s="8" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="J77" s="8" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="K77" s="6" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="923" uniqueCount="457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="929" uniqueCount="460">
   <si>
     <t>_id</t>
   </si>
@@ -947,19 +947,28 @@
     <t>211,212,213</t>
   </si>
   <si>
+    <t>40金色坐骑自选</t>
+  </si>
+  <si>
+    <t>23,23,23</t>
+  </si>
+  <si>
+    <t>901,902,903</t>
+  </si>
+  <si>
+    <t>50金色坐骑自选</t>
+  </si>
+  <si>
     <t>50暗金坐骑自选</t>
   </si>
   <si>
-    <t>23,23,23</t>
-  </si>
-  <si>
-    <t>901,902,903</t>
+    <t>911,912,913</t>
   </si>
   <si>
     <t>70暗金坐骑自选</t>
   </si>
   <si>
-    <t>911,912,913</t>
+    <t>914,915,916</t>
   </si>
   <si>
     <t>金色刺杀自选</t>
@@ -2443,7 +2452,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K125"/>
+  <dimension ref="A1:K126"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="4" max="4" width="16.625" customWidth="1"/>
@@ -5569,31 +5578,74 @@
       <c r="D122" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="E122" s="1">
-        <v>1</v>
-      </c>
-      <c r="F122" s="4">
-        <v>0</v>
-      </c>
-      <c r="G122" s="4">
-        <v>2</v>
-      </c>
-      <c r="H122" s="8" t="s">
+      <c r="E122" s="1"/>
+      <c r="F122" s="4"/>
+      <c r="G122" s="4"/>
+      <c r="H122" s="1"/>
+      <c r="I122" s="1"/>
+      <c r="J122" s="1"/>
+      <c r="K122" s="1"/>
+    </row>
+    <row r="123" ht="14" spans="3:11">
+      <c r="C123" s="1">
+        <v>303</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="E123" s="1">
+        <v>1</v>
+      </c>
+      <c r="F123" s="4">
+        <v>0</v>
+      </c>
+      <c r="G123" s="4">
+        <v>2</v>
+      </c>
+      <c r="H123" s="8" t="s">
         <v>288</v>
       </c>
-      <c r="I122" s="8" t="s">
+      <c r="I123" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="J123" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="K123" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="J122" s="8" t="s">
+    </row>
+    <row r="124" customFormat="1" ht="14" spans="3:11">
+      <c r="C124" s="1">
+        <v>304</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="E124" s="1">
+        <v>1</v>
+      </c>
+      <c r="F124" s="4">
+        <v>0</v>
+      </c>
+      <c r="G124" s="4">
+        <v>2</v>
+      </c>
+      <c r="H124" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="I124" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="J124" s="8" t="s">
         <v>271</v>
       </c>
-      <c r="K122" s="1" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="123" ht="14"/>
-    <row r="124" ht="14"/>
-    <row r="125" ht="14"/>
+      <c r="K124" s="1" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="125"/>
+    <row r="126" ht="14"/>
   </sheetData>
   <dataValidations count="2">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:E5 H3:K5" errorStyle="warning">
@@ -5719,7 +5771,7 @@
         <v>1001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -5734,13 +5786,13 @@
         <v>14</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="J6" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5748,7 +5800,7 @@
         <v>1002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -5763,13 +5815,13 @@
         <v>14</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="J7" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5777,7 +5829,7 @@
         <v>1003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -5792,13 +5844,13 @@
         <v>14</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="J8" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5806,7 +5858,7 @@
         <v>1004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
@@ -5821,13 +5873,13 @@
         <v>14</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="J9" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5835,7 +5887,7 @@
         <v>1005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -5850,13 +5902,13 @@
         <v>14</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="J10" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5864,7 +5916,7 @@
         <v>1006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -5879,13 +5931,13 @@
         <v>14</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="J11" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5893,7 +5945,7 @@
         <v>1007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
@@ -5908,13 +5960,13 @@
         <v>14</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="J12" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5922,7 +5974,7 @@
         <v>1008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
@@ -5937,13 +5989,13 @@
         <v>14</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="J13" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5951,7 +6003,7 @@
         <v>1009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
@@ -5966,13 +6018,13 @@
         <v>14</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="J14" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5980,7 +6032,7 @@
         <v>1010</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
@@ -5995,13 +6047,13 @@
         <v>14</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="J15" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6009,7 +6061,7 @@
         <v>1011</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="E16" s="1">
         <v>1</v>
@@ -6024,13 +6076,13 @@
         <v>14</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="J16" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6038,7 +6090,7 @@
         <v>1012</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="E17" s="1">
         <v>1</v>
@@ -6053,13 +6105,13 @@
         <v>14</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="J17" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6067,7 +6119,7 @@
         <v>1013</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="E18" s="1">
         <v>1</v>
@@ -6082,13 +6134,13 @@
         <v>14</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="J18" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6096,7 +6148,7 @@
         <v>1014</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="E19" s="1">
         <v>1</v>
@@ -6111,13 +6163,13 @@
         <v>14</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="J19" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1"/>
@@ -6126,7 +6178,7 @@
         <v>1101</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
@@ -6141,13 +6193,13 @@
         <v>14</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="J21" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6155,7 +6207,7 @@
         <v>1102</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
@@ -6170,13 +6222,13 @@
         <v>14</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="J22" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6184,7 +6236,7 @@
         <v>1103</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
@@ -6199,13 +6251,13 @@
         <v>14</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="J23" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6213,7 +6265,7 @@
         <v>1104</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
@@ -6228,13 +6280,13 @@
         <v>14</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="J24" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6242,7 +6294,7 @@
         <v>1105</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="E25" s="1">
         <v>1</v>
@@ -6257,13 +6309,13 @@
         <v>14</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="J25" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6271,7 +6323,7 @@
         <v>1106</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
@@ -6286,13 +6338,13 @@
         <v>14</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="J26" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6300,7 +6352,7 @@
         <v>1107</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="E27" s="1">
         <v>1</v>
@@ -6315,13 +6367,13 @@
         <v>14</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="J27" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6329,7 +6381,7 @@
         <v>1108</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="E28" s="1">
         <v>1</v>
@@ -6344,13 +6396,13 @@
         <v>14</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="J28" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6358,7 +6410,7 @@
         <v>1109</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
@@ -6373,13 +6425,13 @@
         <v>14</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="J29" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6387,7 +6439,7 @@
         <v>1110</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
@@ -6402,13 +6454,13 @@
         <v>14</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="J30" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6416,7 +6468,7 @@
         <v>1111</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
@@ -6431,13 +6483,13 @@
         <v>14</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="J31" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6445,7 +6497,7 @@
         <v>1112</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="E32" s="1">
         <v>1</v>
@@ -6460,13 +6512,13 @@
         <v>14</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="J32" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="2:12">
@@ -6487,7 +6539,7 @@
         <v>1201</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="E34" s="1">
         <v>1</v>
@@ -6502,13 +6554,13 @@
         <v>133</v>
       </c>
       <c r="I34" s="8" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="J34" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="2:12">
@@ -6517,7 +6569,7 @@
         <v>1202</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="E35" s="1">
         <v>1</v>
@@ -6529,16 +6581,16 @@
         <v>2</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="J35" s="8" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="L35" s="2"/>
     </row>
@@ -6548,7 +6600,7 @@
         <v>1203</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="E36" s="1">
         <v>1</v>
@@ -6560,16 +6612,16 @@
         <v>2</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="I36" s="8" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="J36" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="L36" s="2"/>
     </row>
@@ -6578,7 +6630,7 @@
         <v>1204</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="E37" s="1">
         <v>1</v>
@@ -6593,13 +6645,13 @@
         <v>133</v>
       </c>
       <c r="I37" s="8" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="J37" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="2:12">
@@ -6607,7 +6659,7 @@
         <v>1205</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="E38" s="1">
         <v>1</v>
@@ -6622,13 +6674,13 @@
         <v>147</v>
       </c>
       <c r="I38" s="8" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="J38" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="2:12">
@@ -6636,7 +6688,7 @@
         <v>1206</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="E39" s="1">
         <v>1</v>
@@ -6651,13 +6703,13 @@
         <v>163</v>
       </c>
       <c r="I39" s="8" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="J39" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="2:12">
@@ -6665,7 +6717,7 @@
         <v>2001</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="E41" s="1">
         <v>1</v>
@@ -6677,16 +6729,16 @@
         <v>2</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="I41" s="8" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="J41" s="8" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="K41" s="5" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="2:12">
@@ -6694,7 +6746,7 @@
         <v>2002</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="E42" s="1">
         <v>1</v>
@@ -6706,16 +6758,16 @@
         <v>2</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="I42" s="8" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="J42" s="8" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="K42" s="5" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="2:12">
@@ -6723,7 +6775,7 @@
         <v>2003</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="E43" s="1">
         <v>1</v>
@@ -6735,16 +6787,16 @@
         <v>2</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="I43" s="8" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="J43" s="8" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="K43" s="5" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="2:12">
@@ -6752,7 +6804,7 @@
         <v>2004</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="E44" s="1">
         <v>1</v>
@@ -6764,16 +6816,16 @@
         <v>2</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="I44" s="8" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="J44" s="8" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="K44" s="5" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="2:12">
@@ -6781,7 +6833,7 @@
         <v>2005</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="E45" s="1">
         <v>1</v>
@@ -6793,16 +6845,16 @@
         <v>2</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="I45" s="8" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="J45" s="8" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="K45" s="5" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="2:12">
@@ -6810,7 +6862,7 @@
         <v>2006</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="E46" s="1">
         <v>1</v>
@@ -6822,16 +6874,16 @@
         <v>2</v>
       </c>
       <c r="H46" s="8" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="I46" s="8" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="J46" s="8" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" customHeight="1" spans="2:12">
@@ -6840,7 +6892,7 @@
         <v>2007</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="E47" s="1">
         <v>1</v>
@@ -6852,16 +6904,16 @@
         <v>2</v>
       </c>
       <c r="H47" s="8" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="I47" s="8" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="J47" s="8" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="K47" s="5" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="L47" s="2"/>
     </row>
@@ -6871,7 +6923,7 @@
         <v>2008</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="E48" s="1">
         <v>1</v>
@@ -6883,16 +6935,16 @@
         <v>2</v>
       </c>
       <c r="H48" s="8" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="I48" s="8" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="J48" s="8" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="K48" s="5" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="L48" s="2"/>
     </row>
@@ -6902,7 +6954,7 @@
         <v>2009</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="E49" s="1">
         <v>1</v>
@@ -6914,16 +6966,16 @@
         <v>2</v>
       </c>
       <c r="H49" s="8" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="I49" s="8" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="J49" s="8" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="K49" s="5" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="L49" s="2"/>
     </row>
@@ -6933,7 +6985,7 @@
         <v>2010</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="E50" s="1">
         <v>1</v>
@@ -6945,16 +6997,16 @@
         <v>2</v>
       </c>
       <c r="H50" s="8" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="I50" s="8" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="J50" s="8" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="K50" s="5" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="L50" s="2"/>
     </row>
@@ -6964,7 +7016,7 @@
         <v>2011</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="E51" s="1">
         <v>1</v>
@@ -6976,16 +7028,16 @@
         <v>2</v>
       </c>
       <c r="H51" s="8" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="I51" s="8" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="J51" s="8" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="K51" s="5" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="L51" s="2"/>
     </row>
@@ -6995,7 +7047,7 @@
         <v>2012</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="E52" s="1">
         <v>1</v>
@@ -7007,16 +7059,16 @@
         <v>2</v>
       </c>
       <c r="H52" s="8" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="I52" s="8" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="J52" s="8" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="K52" s="5" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="L52" s="2"/>
     </row>
@@ -7038,7 +7090,7 @@
         <v>2013</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="E54" s="1">
         <v>1</v>
@@ -7050,16 +7102,16 @@
         <v>2</v>
       </c>
       <c r="H54" s="8" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="I54" s="8" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="J54" s="8" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="K54" s="6" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="L54" s="2"/>
     </row>
@@ -7069,7 +7121,7 @@
         <v>2014</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="E55" s="1">
         <v>1</v>
@@ -7081,16 +7133,16 @@
         <v>2</v>
       </c>
       <c r="H55" s="8" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="I55" s="8" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J55" s="8" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="K55" s="6" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="L55" s="2"/>
     </row>
@@ -7099,7 +7151,7 @@
         <v>2015</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E56" s="1">
         <v>1</v>
@@ -7111,16 +7163,16 @@
         <v>2</v>
       </c>
       <c r="H56" s="8" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="I56" s="8" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J56" s="8" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="K56" s="6" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="2:12">
@@ -7128,7 +7180,7 @@
         <v>2016</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="E57" s="1">
         <v>1</v>
@@ -7140,16 +7192,16 @@
         <v>2</v>
       </c>
       <c r="H57" s="8" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="I57" s="8" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="J57" s="8" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="K57" s="6" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="2:12">
@@ -7157,7 +7209,7 @@
         <v>2017</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="E58" s="1">
         <v>1</v>
@@ -7169,16 +7221,16 @@
         <v>2</v>
       </c>
       <c r="H58" s="8" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="I58" s="8" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="J58" s="8" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="K58" s="6" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="2:12">
@@ -7186,7 +7238,7 @@
         <v>2018</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="E59" s="1">
         <v>1</v>
@@ -7198,16 +7250,16 @@
         <v>2</v>
       </c>
       <c r="H59" s="8" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="I59" s="8" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="J59" s="8" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="K59" s="6" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="2:12">
@@ -7215,7 +7267,7 @@
         <v>2019</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="E60" s="1">
         <v>1</v>
@@ -7227,16 +7279,16 @@
         <v>2</v>
       </c>
       <c r="H60" s="8" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="I60" s="8" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="J60" s="8" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="K60" s="6" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="2:12">
@@ -7244,7 +7296,7 @@
         <v>2020</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="E61" s="1">
         <v>1</v>
@@ -7256,16 +7308,16 @@
         <v>2</v>
       </c>
       <c r="H61" s="8" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="I61" s="8" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="J61" s="8" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="K61" s="6" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="2:12">
@@ -7273,7 +7325,7 @@
         <v>2021</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="E62" s="1">
         <v>1</v>
@@ -7285,16 +7337,16 @@
         <v>2</v>
       </c>
       <c r="H62" s="8" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="I62" s="8" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="J62" s="8" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="K62" s="6" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="2:12">
@@ -7302,7 +7354,7 @@
         <v>2022</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="E63" s="1">
         <v>1</v>
@@ -7314,16 +7366,16 @@
         <v>2</v>
       </c>
       <c r="H63" s="8" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="I63" s="8" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="J63" s="8" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="K63" s="6" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="2:12">
@@ -7331,7 +7383,7 @@
         <v>2023</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="E64" s="1">
         <v>1</v>
@@ -7343,16 +7395,16 @@
         <v>2</v>
       </c>
       <c r="H64" s="8" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="I64" s="8" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="J64" s="8" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="K64" s="6" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:11">
@@ -7360,7 +7412,7 @@
         <v>2024</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="E65" s="1">
         <v>1</v>
@@ -7372,16 +7424,16 @@
         <v>2</v>
       </c>
       <c r="H65" s="8" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="I65" s="8" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="J65" s="8" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="K65" s="6" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="3:11">
@@ -7389,7 +7441,7 @@
         <v>2025</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="E66" s="1">
         <v>1</v>
@@ -7401,16 +7453,16 @@
         <v>2</v>
       </c>
       <c r="H66" s="8" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="I66" s="8" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="J66" s="8" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="K66" s="6" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:11">
@@ -7428,7 +7480,7 @@
         <v>2026</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="E68" s="1">
         <v>1</v>
@@ -7440,16 +7492,16 @@
         <v>2</v>
       </c>
       <c r="H68" s="8" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="I68" s="8" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="J68" s="8" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="K68" s="6" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:11">
@@ -7457,7 +7509,7 @@
         <v>2027</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="E69" s="1">
         <v>1</v>
@@ -7469,16 +7521,16 @@
         <v>2</v>
       </c>
       <c r="H69" s="8" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="I69" s="8" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="J69" s="8" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="K69" s="6" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:11">
@@ -7486,7 +7538,7 @@
         <v>2028</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="E70" s="1">
         <v>1</v>
@@ -7498,16 +7550,16 @@
         <v>2</v>
       </c>
       <c r="H70" s="8" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="I70" s="8" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="J70" s="8" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="K70" s="6" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:11">
@@ -7515,7 +7567,7 @@
         <v>2029</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E71" s="1">
         <v>1</v>
@@ -7527,16 +7579,16 @@
         <v>2</v>
       </c>
       <c r="H71" s="8" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="I71" s="8" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="J71" s="8" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="K71" s="6" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:11">
@@ -7544,7 +7596,7 @@
         <v>2030</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="E72" s="1">
         <v>1</v>
@@ -7556,16 +7608,16 @@
         <v>2</v>
       </c>
       <c r="H72" s="8" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="I72" s="8" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="J72" s="8" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="K72" s="6" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:11">
@@ -7573,7 +7625,7 @@
         <v>2031</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="E73" s="1">
         <v>1</v>
@@ -7585,16 +7637,16 @@
         <v>2</v>
       </c>
       <c r="H73" s="8" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="I73" s="8" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="J73" s="8" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="K73" s="6" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:11">
@@ -7602,7 +7654,7 @@
         <v>2032</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="E74" s="1">
         <v>1</v>
@@ -7614,16 +7666,16 @@
         <v>2</v>
       </c>
       <c r="H74" s="8" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="I74" s="8" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="J74" s="8" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="K74" s="6" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:11">
@@ -7631,7 +7683,7 @@
         <v>2033</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="E75" s="1">
         <v>1</v>
@@ -7643,16 +7695,16 @@
         <v>2</v>
       </c>
       <c r="H75" s="8" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="I75" s="8" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="J75" s="8" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="K75" s="6" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:11">
@@ -7660,7 +7712,7 @@
         <v>2034</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="E76" s="1">
         <v>1</v>
@@ -7672,16 +7724,16 @@
         <v>2</v>
       </c>
       <c r="H76" s="8" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="I76" s="8" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="J76" s="8" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="K76" s="6" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:11">
@@ -7689,7 +7741,7 @@
         <v>2035</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="E77" s="1">
         <v>1</v>
@@ -7701,16 +7753,16 @@
         <v>2</v>
       </c>
       <c r="H77" s="8" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="I77" s="8" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="J77" s="8" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="K77" s="6" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="929" uniqueCount="460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="959" uniqueCount="472">
   <si>
     <t>_id</t>
   </si>
@@ -522,6 +522,42 @@
   </si>
   <si>
     <t>13,14,15,16,17,18,19,20,21,22,23,24</t>
+  </si>
+  <si>
+    <t>极龙神器自选</t>
+  </si>
+  <si>
+    <t>61000041,61000042,61000043,61000044,61000045,61000046,61000047,61000048</t>
+  </si>
+  <si>
+    <t>极虎神器自选</t>
+  </si>
+  <si>
+    <t>61000049,61000050,61000051,61000052,61000053,61000054,61000055,61000056</t>
+  </si>
+  <si>
+    <t>极雀神器自选</t>
+  </si>
+  <si>
+    <t>61000057,61000058,61000059,61000060,61000061,61000062,61000063,61000064</t>
+  </si>
+  <si>
+    <t>极玄神器自选</t>
+  </si>
+  <si>
+    <t>61000065,61000066,61000067,61000068,61000069,61000070,61000071,61000072</t>
+  </si>
+  <si>
+    <t>极麟神器自选</t>
+  </si>
+  <si>
+    <t>61000073,61000074,61000075,61000076,61000077,61000078,61000079,61000080</t>
+  </si>
+  <si>
+    <t>极神器自选</t>
+  </si>
+  <si>
+    <t>47</t>
   </si>
   <si>
     <t>粉色专属自选</t>
@@ -2452,7 +2488,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K126"/>
+  <dimension ref="A1:K132"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="4" max="4" width="16.625" customWidth="1"/>
@@ -3865,57 +3901,73 @@
       </c>
     </row>
     <row r="51" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A51" s="1"/>
-      <c r="B51" s="1"/>
-      <c r="C51" s="1"/>
-      <c r="D51" s="1"/>
-      <c r="E51" s="1"/>
-      <c r="F51" s="4"/>
-      <c r="G51" s="4"/>
-      <c r="H51" s="1"/>
-      <c r="I51" s="1"/>
-      <c r="J51" s="1"/>
-      <c r="K51" s="1"/>
+      <c r="C51" s="1">
+        <v>47</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E51" s="1">
+        <v>1</v>
+      </c>
+      <c r="F51" s="4">
+        <v>0</v>
+      </c>
+      <c r="G51" s="1">
+        <v>1</v>
+      </c>
+      <c r="H51" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="I51" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="J51" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K51" s="1" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="52" customFormat="1" customHeight="1" spans="1:11">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1">
+        <v>48</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E52" s="1">
+        <v>1</v>
+      </c>
+      <c r="F52" s="4">
+        <v>0</v>
+      </c>
+      <c r="G52" s="1">
+        <v>1</v>
+      </c>
+      <c r="H52" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="D52" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="E52" s="1">
-        <v>1</v>
-      </c>
-      <c r="F52" s="4">
-        <v>0</v>
-      </c>
-      <c r="G52" s="1">
-        <v>2</v>
-      </c>
-      <c r="H52" s="8" t="s">
-        <v>147</v>
-      </c>
       <c r="I52" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="J52" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K52" s="1" t="s">
         <v>148</v>
-      </c>
-      <c r="J52" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="K52" s="1" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="53" customFormat="1" customHeight="1" spans="1:11">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1">
-        <v>90</v>
+        <v>49</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E53" s="1">
         <v>1</v>
@@ -3924,26 +3976,26 @@
         <v>0</v>
       </c>
       <c r="G53" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H53" s="8" t="s">
-        <v>150</v>
+        <v>89</v>
       </c>
       <c r="I53" s="8" t="s">
         <v>151</v>
       </c>
       <c r="J53" s="8" t="s">
-        <v>141</v>
+        <v>91</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="54" customFormat="1" customHeight="1" spans="1:11">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1">
-        <v>91</v>
+        <v>50</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>152</v>
@@ -3955,26 +4007,26 @@
         <v>0</v>
       </c>
       <c r="G54" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H54" s="8" t="s">
-        <v>133</v>
+        <v>89</v>
       </c>
       <c r="I54" s="8" t="s">
         <v>153</v>
       </c>
       <c r="J54" s="8" t="s">
-        <v>16</v>
+        <v>91</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="55" customFormat="1" customHeight="1" spans="1:11">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1">
-        <v>94</v>
+        <v>51</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>154</v>
@@ -3986,26 +4038,24 @@
         <v>0</v>
       </c>
       <c r="G55" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H55" s="8" t="s">
-        <v>147</v>
+        <v>89</v>
       </c>
       <c r="I55" s="8" t="s">
         <v>155</v>
       </c>
       <c r="J55" s="8" t="s">
-        <v>16</v>
+        <v>91</v>
       </c>
       <c r="K55" s="1" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="56" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A56" s="1"/>
-      <c r="B56" s="1"/>
       <c r="C56" s="1">
-        <v>95</v>
+        <v>52</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>156</v>
@@ -4017,10 +4067,10 @@
         <v>0</v>
       </c>
       <c r="G56" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H56" s="8" t="s">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="I56" s="8" t="s">
         <v>157</v>
@@ -4029,134 +4079,126 @@
         <v>91</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>156</v>
+        <v>132</v>
       </c>
     </row>
     <row r="57" customFormat="1" customHeight="1" spans="1:11">
-      <c r="C57" s="1">
-        <v>96</v>
-      </c>
-      <c r="D57" s="1" t="s">
+      <c r="A57" s="1"/>
+      <c r="B57" s="1"/>
+      <c r="C57" s="1"/>
+      <c r="D57" s="1"/>
+      <c r="E57" s="1"/>
+      <c r="F57" s="4"/>
+      <c r="G57" s="4"/>
+      <c r="H57" s="1"/>
+      <c r="I57" s="1"/>
+      <c r="J57" s="1"/>
+      <c r="K57" s="1"/>
+    </row>
+    <row r="58" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A58" s="1"/>
+      <c r="B58" s="1"/>
+      <c r="C58" s="1">
+        <v>89</v>
+      </c>
+      <c r="D58" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="E57" s="1">
-        <v>0</v>
-      </c>
-      <c r="F57" s="4">
-        <v>0</v>
-      </c>
-      <c r="G57" s="1">
-        <v>2</v>
-      </c>
-      <c r="H57" s="8" t="s">
+      <c r="E58" s="1">
+        <v>1</v>
+      </c>
+      <c r="F58" s="4">
+        <v>0</v>
+      </c>
+      <c r="G58" s="1">
+        <v>2</v>
+      </c>
+      <c r="H58" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="I57" s="8" t="s">
+      <c r="I58" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="J57" s="8" t="s">
+      <c r="J58" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="K58" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="K57" s="1" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="58" customFormat="1" customHeight="1" spans="1:11">
-      <c r="C58" s="1">
-        <v>97</v>
-      </c>
-      <c r="D58" s="1" t="s">
+    </row>
+    <row r="59" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A59" s="1"/>
+      <c r="B59" s="1"/>
+      <c r="C59" s="1">
+        <v>90</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E59" s="1">
+        <v>1</v>
+      </c>
+      <c r="F59" s="4">
+        <v>0</v>
+      </c>
+      <c r="G59" s="1">
+        <v>2</v>
+      </c>
+      <c r="H59" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="E58" s="1">
-        <v>1</v>
-      </c>
-      <c r="F58" s="4">
-        <v>0</v>
-      </c>
-      <c r="G58" s="1">
-        <v>2</v>
-      </c>
-      <c r="H58" s="8" t="s">
+      <c r="I59" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="I58" s="8" t="s">
+      <c r="J59" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="K59" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="60" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A60" s="1"/>
+      <c r="B60" s="1"/>
+      <c r="C60" s="1">
+        <v>91</v>
+      </c>
+      <c r="D60" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="J58" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="K58" s="1" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="59" customFormat="1" customHeight="1" spans="1:11">
-      <c r="C59" s="1">
-        <v>98</v>
-      </c>
-      <c r="D59" s="1" t="s">
+      <c r="E60" s="1">
+        <v>1</v>
+      </c>
+      <c r="F60" s="4">
+        <v>0</v>
+      </c>
+      <c r="G60" s="1">
+        <v>2</v>
+      </c>
+      <c r="H60" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="I60" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="E59" s="1">
-        <v>1</v>
-      </c>
-      <c r="F59" s="4">
-        <v>0</v>
-      </c>
-      <c r="G59" s="1">
-        <v>2</v>
-      </c>
-      <c r="H59" s="8" t="s">
+      <c r="J60" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="K60" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="61" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A61" s="1"/>
+      <c r="B61" s="1"/>
+      <c r="C61" s="1">
+        <v>94</v>
+      </c>
+      <c r="D61" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="I59" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="J59" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="K59" s="1" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="60" customFormat="1" customHeight="1" spans="1:11">
-      <c r="C60" s="1">
-        <v>99</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="E60" s="1">
-        <v>0</v>
-      </c>
-      <c r="F60" s="4">
-        <v>0</v>
-      </c>
-      <c r="G60" s="1">
-        <v>2</v>
-      </c>
-      <c r="H60" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="I60" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="J60" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="K60" s="1" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="61" customFormat="1" customHeight="1" spans="1:11">
-      <c r="C61" s="1">
-        <v>100</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>172</v>
-      </c>
       <c r="E61" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F61" s="4">
         <v>0</v>
@@ -4168,24 +4210,26 @@
         <v>159</v>
       </c>
       <c r="I61" s="8" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="J61" s="8" t="s">
-        <v>161</v>
+        <v>16</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
     </row>
     <row r="62" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A62" s="1"/>
+      <c r="B62" s="1"/>
       <c r="C62" s="1">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="E62" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F62" s="4">
         <v>0</v>
@@ -4194,24 +4238,24 @@
         <v>2</v>
       </c>
       <c r="H62" s="8" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="I62" s="8" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="J62" s="8" t="s">
-        <v>161</v>
+        <v>91</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="63" customFormat="1" customHeight="1" spans="1:11">
       <c r="C63" s="1">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="E63" s="1">
         <v>0</v>
@@ -4223,481 +4267,491 @@
         <v>2</v>
       </c>
       <c r="H63" s="8" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="I63" s="8" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="J63" s="8" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="64" customFormat="1" customHeight="1" spans="1:11">
       <c r="C64" s="1">
+        <v>97</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E64" s="1">
+        <v>1</v>
+      </c>
+      <c r="F64" s="4">
+        <v>0</v>
+      </c>
+      <c r="G64" s="1">
+        <v>2</v>
+      </c>
+      <c r="H64" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="I64" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="J64" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="K64" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="65" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C65" s="1">
+        <v>98</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E65" s="1">
+        <v>1</v>
+      </c>
+      <c r="F65" s="4">
+        <v>0</v>
+      </c>
+      <c r="G65" s="1">
+        <v>2</v>
+      </c>
+      <c r="H65" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="I65" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="J65" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K65" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="66" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C66" s="1">
+        <v>99</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E66" s="1">
+        <v>0</v>
+      </c>
+      <c r="F66" s="4">
+        <v>0</v>
+      </c>
+      <c r="G66" s="1">
+        <v>2</v>
+      </c>
+      <c r="H66" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="I66" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="J66" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="K66" s="1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="67" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C67" s="1">
+        <v>100</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="E67" s="1">
+        <v>0</v>
+      </c>
+      <c r="F67" s="4">
+        <v>0</v>
+      </c>
+      <c r="G67" s="1">
+        <v>2</v>
+      </c>
+      <c r="H67" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="I67" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="J67" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="K67" s="1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="68" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C68" s="1">
+        <v>101</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="E68" s="1">
+        <v>0</v>
+      </c>
+      <c r="F68" s="4">
+        <v>0</v>
+      </c>
+      <c r="G68" s="1">
+        <v>2</v>
+      </c>
+      <c r="H68" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="I68" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="J68" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="K68" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="69" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C69" s="1">
+        <v>102</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="E69" s="1">
+        <v>0</v>
+      </c>
+      <c r="F69" s="4">
+        <v>0</v>
+      </c>
+      <c r="G69" s="1">
+        <v>2</v>
+      </c>
+      <c r="H69" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="I69" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="J69" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="K69" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="70" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C70" s="1">
         <v>103</v>
       </c>
-      <c r="D64" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="E64" s="1">
-        <v>0</v>
-      </c>
-      <c r="F64" s="4">
-        <v>0</v>
-      </c>
-      <c r="G64" s="1">
-        <v>2</v>
-      </c>
-      <c r="H64" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="I64" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="J64" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="K64" s="1" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="65" customFormat="1" customHeight="1" spans="1:11">
-      <c r="C65" s="1">
+      <c r="D70" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E70" s="1">
+        <v>0</v>
+      </c>
+      <c r="F70" s="4">
+        <v>0</v>
+      </c>
+      <c r="G70" s="1">
+        <v>2</v>
+      </c>
+      <c r="H70" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="I70" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="J70" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="K70" s="1" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="71" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C71" s="1">
         <v>104</v>
       </c>
-      <c r="D65" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="E65" s="1">
-        <v>0</v>
-      </c>
-      <c r="F65" s="4">
-        <v>0</v>
-      </c>
-      <c r="G65" s="1">
-        <v>2</v>
-      </c>
-      <c r="H65" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="I65" s="8" t="s">
+      <c r="D71" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="E71" s="1">
+        <v>0</v>
+      </c>
+      <c r="F71" s="4">
+        <v>0</v>
+      </c>
+      <c r="G71" s="1">
+        <v>2</v>
+      </c>
+      <c r="H71" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="J65" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="K65" s="1" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="66" customFormat="1" customHeight="1" spans="1:11">
-      <c r="C66" s="1">
+      <c r="I71" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="J71" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="K71" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="72" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C72" s="1">
         <v>105</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="E66" s="1">
-        <v>0</v>
-      </c>
-      <c r="F66" s="4">
-        <v>0</v>
-      </c>
-      <c r="G66" s="1">
-        <v>2</v>
-      </c>
-      <c r="H66" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="I66" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="J66" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="K66" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="67" ht="14"/>
-    <row r="68" customFormat="1" customHeight="1" spans="1:11">
-      <c r="C68" s="1">
-        <v>106</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="E68" s="1">
-        <v>1</v>
-      </c>
-      <c r="F68" s="4">
-        <v>0</v>
-      </c>
-      <c r="G68" s="1">
-        <v>1</v>
-      </c>
-      <c r="H68" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="I68" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="J68" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="K68" s="1" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="69" customFormat="1" customHeight="1" spans="1:11">
-      <c r="C69" s="1">
-        <v>107</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="E69" s="1">
-        <v>1</v>
-      </c>
-      <c r="F69" s="4">
-        <v>0</v>
-      </c>
-      <c r="G69" s="1">
-        <v>2</v>
-      </c>
-      <c r="H69" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="I69" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="J69" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="K69" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="70" customFormat="1" customHeight="1" spans="1:11">
-      <c r="C70" s="1">
-        <v>108</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="E70" s="1">
-        <v>1</v>
-      </c>
-      <c r="F70" s="4">
-        <v>0</v>
-      </c>
-      <c r="G70" s="1">
-        <v>2</v>
-      </c>
-      <c r="H70" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="I70" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="J70" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="K70" s="1" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="71" ht="14"/>
-    <row r="72" customFormat="1" customHeight="1" spans="1:11">
-      <c r="C72" s="1">
-        <v>109</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>194</v>
       </c>
       <c r="E72" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F72" s="4">
         <v>0</v>
       </c>
-      <c r="G72" s="4">
+      <c r="G72" s="1">
         <v>2</v>
       </c>
       <c r="H72" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="I72" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="I72" s="8" t="s">
+      <c r="J72" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="K72" s="1" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="73" ht="14"/>
+    <row r="74" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C74" s="1">
+        <v>106</v>
+      </c>
+      <c r="D74" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="J72" s="8" t="s">
+      <c r="E74" s="1">
+        <v>1</v>
+      </c>
+      <c r="F74" s="4">
+        <v>0</v>
+      </c>
+      <c r="G74" s="1">
+        <v>1</v>
+      </c>
+      <c r="H74" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="I74" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="J74" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="K74" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="75" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C75" s="1">
+        <v>107</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="E75" s="1">
+        <v>1</v>
+      </c>
+      <c r="F75" s="4">
+        <v>0</v>
+      </c>
+      <c r="G75" s="1">
+        <v>2</v>
+      </c>
+      <c r="H75" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="I75" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="J75" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="K75" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="76" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C76" s="1">
+        <v>108</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="E76" s="1">
+        <v>1</v>
+      </c>
+      <c r="F76" s="4">
+        <v>0</v>
+      </c>
+      <c r="G76" s="1">
+        <v>2</v>
+      </c>
+      <c r="H76" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="I76" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="J76" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="K76" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="77" ht="14"/>
+    <row r="78" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C78" s="1">
+        <v>109</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="E78" s="1">
+        <v>1</v>
+      </c>
+      <c r="F78" s="4">
+        <v>0</v>
+      </c>
+      <c r="G78" s="4">
+        <v>2</v>
+      </c>
+      <c r="H78" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="I78" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J78" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="K72" s="1" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="73" customFormat="1" customHeight="1" spans="1:11">
-      <c r="C73" s="1">
+      <c r="K78" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="79" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C79" s="1">
         <v>110</v>
       </c>
-      <c r="D73" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="E73" s="1">
-        <v>1</v>
-      </c>
-      <c r="F73" s="4">
-        <v>0</v>
-      </c>
-      <c r="G73" s="4">
-        <v>2</v>
-      </c>
-      <c r="H73" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="I73" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="J73" s="8" t="s">
+      <c r="D79" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E79" s="1">
+        <v>1</v>
+      </c>
+      <c r="F79" s="4">
+        <v>0</v>
+      </c>
+      <c r="G79" s="4">
+        <v>2</v>
+      </c>
+      <c r="H79" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="I79" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="J79" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="K73" s="1" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="74" customFormat="1" customHeight="1" spans="1:11">
-      <c r="C74" s="1">
+      <c r="K79" s="1" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="80" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C80" s="1">
         <v>111</v>
       </c>
-      <c r="D74" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="E74" s="1">
-        <v>1</v>
-      </c>
-      <c r="F74" s="4">
-        <v>0</v>
-      </c>
-      <c r="G74" s="4">
-        <v>2</v>
-      </c>
-      <c r="H74" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="I74" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="J74" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="K74" s="1" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="75" customFormat="1" customHeight="1" spans="1:11">
-      <c r="C75" s="1">
-        <v>112</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="E75" s="1">
-        <v>1</v>
-      </c>
-      <c r="F75" s="4">
-        <v>0</v>
-      </c>
-      <c r="G75" s="4">
-        <v>2</v>
-      </c>
-      <c r="H75" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="I75" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="J75" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="K75" s="1" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="76" customFormat="1" customHeight="1" spans="1:11">
-      <c r="C76" s="1">
-        <v>113</v>
-      </c>
-      <c r="D76" s="1" t="s">
+      <c r="D80" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="E80" s="1">
+        <v>1</v>
+      </c>
+      <c r="F80" s="4">
+        <v>0</v>
+      </c>
+      <c r="G80" s="4">
+        <v>2</v>
+      </c>
+      <c r="H80" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="E76" s="1">
-        <v>1</v>
-      </c>
-      <c r="F76" s="4">
-        <v>0</v>
-      </c>
-      <c r="G76" s="4">
-        <v>2</v>
-      </c>
-      <c r="H76" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="I76" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="J76" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="K76" s="1" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="77" customFormat="1" customHeight="1" spans="1:11">
-      <c r="C77" s="1">
-        <v>114</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="E77" s="1">
-        <v>1</v>
-      </c>
-      <c r="F77" s="4">
-        <v>0</v>
-      </c>
-      <c r="G77" s="4">
-        <v>2</v>
-      </c>
-      <c r="H77" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="I77" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="J77" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="K77" s="1" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="78" customFormat="1" customHeight="1" spans="1:11">
-      <c r="C78" s="1">
-        <v>115</v>
-      </c>
-      <c r="D78" s="1" t="s">
+      <c r="I80" s="8" t="s">
         <v>214</v>
-      </c>
-      <c r="E78" s="1">
-        <v>1</v>
-      </c>
-      <c r="F78" s="4">
-        <v>0</v>
-      </c>
-      <c r="G78" s="4">
-        <v>2</v>
-      </c>
-      <c r="H78" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="I78" s="8" t="s">
-        <v>215</v>
-      </c>
-      <c r="J78" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="K78" s="1" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="79" ht="14"/>
-    <row r="80" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A80" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C80" s="1">
-        <v>118</v>
-      </c>
-      <c r="D80" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="E80" s="1">
-        <v>1</v>
-      </c>
-      <c r="F80" s="4">
-        <v>0</v>
-      </c>
-      <c r="G80" s="4">
-        <v>2</v>
-      </c>
-      <c r="H80" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="I80" s="8" t="s">
-        <v>218</v>
       </c>
       <c r="J80" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="K80" s="4" t="s">
+      <c r="K80" s="1" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="81" customFormat="1" customHeight="1" spans="1:11">
+      <c r="C81" s="1">
+        <v>112</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="E81" s="1">
+        <v>1</v>
+      </c>
+      <c r="F81" s="4">
+        <v>0</v>
+      </c>
+      <c r="G81" s="4">
+        <v>2</v>
+      </c>
+      <c r="H81" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="I81" s="8" t="s">
         <v>217</v>
-      </c>
-    </row>
-    <row r="81" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A81" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C81" s="1">
-        <v>119</v>
-      </c>
-      <c r="D81" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="E81" s="1">
-        <v>1</v>
-      </c>
-      <c r="F81" s="4">
-        <v>0</v>
-      </c>
-      <c r="G81" s="4">
-        <v>2</v>
-      </c>
-      <c r="H81" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="I81" s="8" t="s">
-        <v>220</v>
       </c>
       <c r="J81" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="K81" s="4" t="s">
+      <c r="K81" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="82" customFormat="1" customHeight="1" spans="1:11">
+      <c r="C82" s="1">
+        <v>113</v>
+      </c>
+      <c r="D82" s="1" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="82" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A82" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C82" s="1">
-        <v>120</v>
-      </c>
-      <c r="D82" s="4" t="s">
-        <v>221</v>
-      </c>
       <c r="E82" s="1">
         <v>1</v>
       </c>
@@ -4708,65 +4762,53 @@
         <v>2</v>
       </c>
       <c r="H82" s="8" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="I82" s="8" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J82" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="K82" s="4" t="s">
+      <c r="K82" s="1" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="83" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A83" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="C83" s="1">
-        <v>121</v>
-      </c>
-      <c r="D83" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E83" s="1">
+        <v>1</v>
+      </c>
+      <c r="F83" s="4">
+        <v>0</v>
+      </c>
+      <c r="G83" s="4">
+        <v>2</v>
+      </c>
+      <c r="H83" s="8" t="s">
         <v>223</v>
-      </c>
-      <c r="E83" s="1">
-        <v>1</v>
-      </c>
-      <c r="F83" s="4">
-        <v>0</v>
-      </c>
-      <c r="G83" s="4">
-        <v>2</v>
-      </c>
-      <c r="H83" s="8" t="s">
-        <v>195</v>
       </c>
       <c r="I83" s="8" t="s">
         <v>224</v>
       </c>
       <c r="J83" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="K83" s="4" t="s">
-        <v>223</v>
+        <v>91</v>
+      </c>
+      <c r="K83" s="1" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="84" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A84" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="C84" s="1">
-        <v>122</v>
-      </c>
-      <c r="D84" s="4" t="s">
-        <v>225</v>
+        <v>115</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>226</v>
       </c>
       <c r="E84" s="1">
         <v>1</v>
@@ -4778,64 +4820,30 @@
         <v>2</v>
       </c>
       <c r="H84" s="8" t="s">
-        <v>195</v>
+        <v>159</v>
       </c>
       <c r="I84" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="J84" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="K84" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="J84" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="K84" s="4" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="85" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A85" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C85" s="1">
-        <v>123</v>
-      </c>
-      <c r="D85" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="E85" s="1">
-        <v>1</v>
-      </c>
-      <c r="F85" s="4">
-        <v>0</v>
-      </c>
-      <c r="G85" s="4">
-        <v>2</v>
-      </c>
-      <c r="H85" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="I85" s="8" t="s">
-        <v>228</v>
-      </c>
-      <c r="J85" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="K85" s="4" t="s">
-        <v>227</v>
-      </c>
-    </row>
+    </row>
+    <row r="85" ht="14"/>
     <row r="86" customFormat="1" customHeight="1" spans="1:11">
       <c r="A86" s="1" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="C86" s="1">
-        <v>124</v>
-      </c>
-      <c r="D86" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D86" s="4" t="s">
         <v>229</v>
       </c>
       <c r="E86" s="1">
@@ -4848,7 +4856,7 @@
         <v>2</v>
       </c>
       <c r="H86" s="8" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="I86" s="8" t="s">
         <v>230</v>
@@ -4856,21 +4864,21 @@
       <c r="J86" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="K86" s="1" t="s">
+      <c r="K86" s="4" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="87" customFormat="1" customHeight="1" spans="1:11">
       <c r="A87" s="1" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="C87" s="1">
-        <v>125</v>
-      </c>
-      <c r="D87" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D87" s="4" t="s">
         <v>231</v>
       </c>
       <c r="E87" s="1">
@@ -4883,7 +4891,7 @@
         <v>2</v>
       </c>
       <c r="H87" s="8" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="I87" s="8" t="s">
         <v>232</v>
@@ -4891,21 +4899,21 @@
       <c r="J87" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="K87" s="1" t="s">
+      <c r="K87" s="4" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="88" customFormat="1" customHeight="1" spans="1:11">
       <c r="A88" s="1" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="C88" s="1">
-        <v>126</v>
-      </c>
-      <c r="D88" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D88" s="4" t="s">
         <v>233</v>
       </c>
       <c r="E88" s="1">
@@ -4918,7 +4926,7 @@
         <v>2</v>
       </c>
       <c r="H88" s="8" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="I88" s="8" t="s">
         <v>234</v>
@@ -4926,21 +4934,21 @@
       <c r="J88" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="K88" s="1" t="s">
+      <c r="K88" s="4" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="89" customFormat="1" customHeight="1" spans="1:11">
       <c r="A89" s="1" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="C89" s="1">
-        <v>127</v>
-      </c>
-      <c r="D89" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="D89" s="4" t="s">
         <v>235</v>
       </c>
       <c r="E89" s="1">
@@ -4953,7 +4961,7 @@
         <v>2</v>
       </c>
       <c r="H89" s="8" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="I89" s="8" t="s">
         <v>236</v>
@@ -4961,21 +4969,21 @@
       <c r="J89" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="K89" s="1" t="s">
+      <c r="K89" s="4" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="90" customFormat="1" customHeight="1" spans="1:11">
       <c r="A90" s="1" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="C90" s="1">
-        <v>128</v>
-      </c>
-      <c r="D90" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D90" s="4" t="s">
         <v>237</v>
       </c>
       <c r="E90" s="1">
@@ -4988,7 +4996,7 @@
         <v>2</v>
       </c>
       <c r="H90" s="8" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="I90" s="8" t="s">
         <v>238</v>
@@ -4996,21 +5004,21 @@
       <c r="J90" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="K90" s="1" t="s">
+      <c r="K90" s="4" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="91" customFormat="1" customHeight="1" spans="1:11">
       <c r="A91" s="1" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="C91" s="1">
-        <v>129</v>
-      </c>
-      <c r="D91" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D91" s="4" t="s">
         <v>239</v>
       </c>
       <c r="E91" s="1">
@@ -5023,7 +5031,7 @@
         <v>2</v>
       </c>
       <c r="H91" s="8" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="I91" s="8" t="s">
         <v>240</v>
@@ -5031,19 +5039,19 @@
       <c r="J91" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="K91" s="1" t="s">
+      <c r="K91" s="4" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="92" customFormat="1" customHeight="1" spans="1:11">
       <c r="A92" s="1" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="C92" s="1">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>241</v>
@@ -5058,7 +5066,7 @@
         <v>2</v>
       </c>
       <c r="H92" s="8" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="I92" s="8" t="s">
         <v>242</v>
@@ -5072,13 +5080,13 @@
     </row>
     <row r="93" customFormat="1" customHeight="1" spans="1:11">
       <c r="A93" s="1" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="C93" s="1">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>243</v>
@@ -5093,7 +5101,7 @@
         <v>2</v>
       </c>
       <c r="H93" s="8" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="I93" s="8" t="s">
         <v>244</v>
@@ -5105,19 +5113,53 @@
         <v>243</v>
       </c>
     </row>
-    <row r="94" ht="14"/>
+    <row r="94" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A94" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C94" s="1">
+        <v>126</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="E94" s="1">
+        <v>1</v>
+      </c>
+      <c r="F94" s="4">
+        <v>0</v>
+      </c>
+      <c r="G94" s="4">
+        <v>2</v>
+      </c>
+      <c r="H94" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="I94" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="J94" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="K94" s="1" t="s">
+        <v>245</v>
+      </c>
+    </row>
     <row r="95" customFormat="1" customHeight="1" spans="1:11">
       <c r="A95" s="1" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="C95" s="1">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E95" s="1">
         <v>1</v>
@@ -5129,30 +5171,30 @@
         <v>2</v>
       </c>
       <c r="H95" s="8" t="s">
-        <v>147</v>
+        <v>207</v>
       </c>
       <c r="I95" s="8" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="J95" s="8" t="s">
-        <v>40</v>
+        <v>87</v>
       </c>
       <c r="K95" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="96" customFormat="1" customHeight="1" spans="1:11">
       <c r="A96" s="1" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="C96" s="1">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E96" s="1">
         <v>1</v>
@@ -5164,27 +5206,27 @@
         <v>2</v>
       </c>
       <c r="H96" s="8" t="s">
-        <v>248</v>
+        <v>207</v>
       </c>
       <c r="I96" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="J96" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="K96" s="1" t="s">
         <v>249</v>
-      </c>
-      <c r="J96" s="8" t="s">
-        <v>250</v>
-      </c>
-      <c r="K96" s="1" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="97" customFormat="1" customHeight="1" spans="1:11">
       <c r="A97" s="1" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="C97" s="1">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>251</v>
@@ -5199,208 +5241,238 @@
         <v>2</v>
       </c>
       <c r="H97" s="8" t="s">
-        <v>248</v>
+        <v>207</v>
       </c>
       <c r="I97" s="8" t="s">
         <v>252</v>
       </c>
       <c r="J97" s="8" t="s">
-        <v>250</v>
+        <v>87</v>
       </c>
       <c r="K97" s="1" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="98" ht="14"/>
-    <row r="99" ht="14"/>
+    <row r="98" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A98" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C98" s="1">
+        <v>130</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="E98" s="1">
+        <v>1</v>
+      </c>
+      <c r="F98" s="4">
+        <v>0</v>
+      </c>
+      <c r="G98" s="4">
+        <v>2</v>
+      </c>
+      <c r="H98" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="I98" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="J98" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="K98" s="1" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="99" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A99" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C99" s="1">
+        <v>131</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="E99" s="1">
+        <v>1</v>
+      </c>
+      <c r="F99" s="4">
+        <v>0</v>
+      </c>
+      <c r="G99" s="4">
+        <v>2</v>
+      </c>
+      <c r="H99" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="I99" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="J99" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="K99" s="1" t="s">
+        <v>255</v>
+      </c>
+    </row>
     <row r="100" ht="14"/>
-    <row r="101" ht="14"/>
-    <row r="102" ht="14"/>
-    <row r="103" ht="14"/>
+    <row r="101" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A101" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C101" s="1">
+        <v>137</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="E101" s="1">
+        <v>1</v>
+      </c>
+      <c r="F101" s="4">
+        <v>0</v>
+      </c>
+      <c r="G101" s="4">
+        <v>2</v>
+      </c>
+      <c r="H101" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="I101" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="J101" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="K101" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="102" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A102" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C102" s="1">
+        <v>138</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="E102" s="1">
+        <v>1</v>
+      </c>
+      <c r="F102" s="4">
+        <v>0</v>
+      </c>
+      <c r="G102" s="4">
+        <v>2</v>
+      </c>
+      <c r="H102" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="I102" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="J102" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="K102" s="1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="103" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A103" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C103" s="1">
+        <v>139</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="E103" s="1">
+        <v>1</v>
+      </c>
+      <c r="F103" s="4">
+        <v>0</v>
+      </c>
+      <c r="G103" s="4">
+        <v>2</v>
+      </c>
+      <c r="H103" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="I103" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="J103" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="K103" s="1" t="s">
+        <v>263</v>
+      </c>
+    </row>
     <row r="104" ht="14"/>
     <row r="105" ht="14"/>
     <row r="106" ht="14"/>
-    <row r="107" customFormat="1" customHeight="1" spans="1:11">
-      <c r="C107" s="1">
-        <v>201</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="E107" s="1">
-        <v>1</v>
-      </c>
-      <c r="F107" s="4">
-        <v>0</v>
-      </c>
-      <c r="G107" s="4">
-        <v>2</v>
-      </c>
-      <c r="H107" s="8" t="s">
-        <v>254</v>
-      </c>
-      <c r="I107" s="8" t="s">
-        <v>255</v>
-      </c>
-      <c r="J107" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="K107" s="1" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="108" customFormat="1" customHeight="1" spans="1:11">
-      <c r="C108" s="1">
-        <v>202</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="E108" s="1">
-        <v>1</v>
-      </c>
-      <c r="F108" s="4">
-        <v>0</v>
-      </c>
-      <c r="G108" s="4">
-        <v>2</v>
-      </c>
-      <c r="H108" s="8" t="s">
-        <v>254</v>
-      </c>
-      <c r="I108" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="J108" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="K108" s="1" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="109" customFormat="1" customHeight="1" spans="1:11">
-      <c r="C109" s="1">
-        <v>203</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="E109" s="1">
-        <v>1</v>
-      </c>
-      <c r="F109" s="4">
-        <v>0</v>
-      </c>
-      <c r="G109" s="4">
-        <v>2</v>
-      </c>
-      <c r="H109" s="8" t="s">
-        <v>254</v>
-      </c>
-      <c r="I109" s="8" t="s">
-        <v>261</v>
-      </c>
-      <c r="J109" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="K109" s="1" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="110" customFormat="1" customHeight="1" spans="1:11">
-      <c r="C110" s="1">
-        <v>204</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="E110" s="1">
-        <v>1</v>
-      </c>
-      <c r="F110" s="4">
-        <v>0</v>
-      </c>
-      <c r="G110" s="4">
-        <v>2</v>
-      </c>
-      <c r="H110" s="8" t="s">
-        <v>254</v>
-      </c>
-      <c r="I110" s="8" t="s">
-        <v>264</v>
-      </c>
-      <c r="J110" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="K110" s="1" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="111" customFormat="1" customHeight="1" spans="1:11">
-      <c r="C111" s="1">
-        <v>205</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="E111" s="1">
-        <v>1</v>
-      </c>
-      <c r="F111" s="4">
-        <v>0</v>
-      </c>
-      <c r="G111" s="4">
-        <v>2</v>
-      </c>
-      <c r="H111" s="8" t="s">
-        <v>254</v>
-      </c>
-      <c r="I111" s="8" t="s">
-        <v>267</v>
-      </c>
-      <c r="J111" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="K111" s="1" t="s">
-        <v>266</v>
-      </c>
-    </row>
+    <row r="107" ht="14"/>
+    <row r="108" ht="14"/>
+    <row r="109" ht="14"/>
+    <row r="110" ht="14"/>
+    <row r="111" ht="14"/>
     <row r="112" ht="14"/>
     <row r="113" customFormat="1" customHeight="1" spans="3:11">
       <c r="C113" s="1">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="D113" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="E113" s="1">
+        <v>1</v>
+      </c>
+      <c r="F113" s="4">
+        <v>0</v>
+      </c>
+      <c r="G113" s="4">
+        <v>2</v>
+      </c>
+      <c r="H113" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="I113" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="J113" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="K113" s="1" t="s">
         <v>268</v>
-      </c>
-      <c r="E113" s="1">
-        <v>1</v>
-      </c>
-      <c r="F113" s="4">
-        <v>0</v>
-      </c>
-      <c r="G113" s="4">
-        <v>2</v>
-      </c>
-      <c r="H113" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="I113" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="J113" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="K113" s="1" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="114" customFormat="1" customHeight="1" spans="3:11">
       <c r="C114" s="1">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="E114" s="1">
         <v>1</v>
@@ -5412,24 +5484,24 @@
         <v>2</v>
       </c>
       <c r="H114" s="8" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="I114" s="8" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="J114" s="8" t="s">
-        <v>141</v>
+        <v>32</v>
       </c>
       <c r="K114" s="1" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
     </row>
     <row r="115" customFormat="1" customHeight="1" spans="3:11">
       <c r="C115" s="1">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="E115" s="1">
         <v>1</v>
@@ -5441,24 +5513,24 @@
         <v>2</v>
       </c>
       <c r="H115" s="8" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="I115" s="8" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="J115" s="8" t="s">
-        <v>271</v>
+        <v>32</v>
       </c>
       <c r="K115" s="1" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
     </row>
     <row r="116" customFormat="1" customHeight="1" spans="3:11">
       <c r="C116" s="1">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="E116" s="1">
         <v>1</v>
@@ -5470,182 +5542,328 @@
         <v>2</v>
       </c>
       <c r="H116" s="8" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="I116" s="8" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="J116" s="8" t="s">
-        <v>271</v>
+        <v>32</v>
       </c>
       <c r="K116" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="117" customFormat="1" customHeight="1" spans="3:11">
       <c r="C117" s="1">
+        <v>205</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E117" s="1">
+        <v>1</v>
+      </c>
+      <c r="F117" s="4">
+        <v>0</v>
+      </c>
+      <c r="G117" s="4">
+        <v>2</v>
+      </c>
+      <c r="H117" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="I117" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="J117" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="K117" s="1" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="118" ht="14"/>
+    <row r="119" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C119" s="1">
+        <v>207</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="E119" s="1">
+        <v>1</v>
+      </c>
+      <c r="F119" s="4">
+        <v>0</v>
+      </c>
+      <c r="G119" s="4">
+        <v>2</v>
+      </c>
+      <c r="H119" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="I119" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="J119" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="K119" s="1" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="120" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C120" s="1">
+        <v>208</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="E120" s="1">
+        <v>1</v>
+      </c>
+      <c r="F120" s="4">
+        <v>0</v>
+      </c>
+      <c r="G120" s="4">
+        <v>2</v>
+      </c>
+      <c r="H120" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="I120" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="J120" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="K120" s="1" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="121" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C121" s="1">
+        <v>209</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="E121" s="1">
+        <v>1</v>
+      </c>
+      <c r="F121" s="4">
+        <v>0</v>
+      </c>
+      <c r="G121" s="4">
+        <v>2</v>
+      </c>
+      <c r="H121" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="I121" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="J121" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="K121" s="1" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="122" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C122" s="1">
+        <v>210</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="E122" s="1">
+        <v>1</v>
+      </c>
+      <c r="F122" s="4">
+        <v>0</v>
+      </c>
+      <c r="G122" s="4">
+        <v>2</v>
+      </c>
+      <c r="H122" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="I122" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="J122" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="K122" s="1" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="123" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C123" s="1">
         <v>211</v>
       </c>
-      <c r="D117" s="1" t="s">
+      <c r="D123" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="E123" s="1">
+        <v>1</v>
+      </c>
+      <c r="F123" s="4">
+        <v>0</v>
+      </c>
+      <c r="G123" s="4">
+        <v>2</v>
+      </c>
+      <c r="H123" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="I123" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="J123" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="E117" s="1">
-        <v>1</v>
-      </c>
-      <c r="F117" s="4">
-        <v>0</v>
-      </c>
-      <c r="G117" s="4">
-        <v>2</v>
-      </c>
-      <c r="H117" s="8" t="s">
-        <v>254</v>
-      </c>
-      <c r="I117" s="8" t="s">
-        <v>284</v>
-      </c>
-      <c r="J117" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="K117" s="1" t="s">
+      <c r="K123" s="1" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="124" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C124" s="1">
+        <v>212</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="E124" s="1">
+        <v>1</v>
+      </c>
+      <c r="F124" s="4">
+        <v>0</v>
+      </c>
+      <c r="G124" s="4">
+        <v>2</v>
+      </c>
+      <c r="H124" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="I124" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="J124" s="8" t="s">
         <v>283</v>
       </c>
-    </row>
-    <row r="118" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C118" s="1">
-        <v>212</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="E118" s="1">
-        <v>1</v>
-      </c>
-      <c r="F118" s="4">
-        <v>0</v>
-      </c>
-      <c r="G118" s="4">
-        <v>2</v>
-      </c>
-      <c r="H118" s="8" t="s">
-        <v>254</v>
-      </c>
-      <c r="I118" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="J118" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="K118" s="1" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="119" ht="14"/>
-    <row r="120" ht="14"/>
-    <row r="121" ht="14" spans="3:11">
-      <c r="C121" s="1">
+      <c r="K124" s="1" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="125" ht="14"/>
+    <row r="126" ht="14"/>
+    <row r="127" ht="14" spans="3:11">
+      <c r="C127" s="1">
         <v>301</v>
       </c>
-      <c r="D121" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="E121" s="1">
-        <v>1</v>
-      </c>
-      <c r="F121" s="4">
-        <v>0</v>
-      </c>
-      <c r="G121" s="4">
-        <v>2</v>
-      </c>
-      <c r="H121" s="8" t="s">
-        <v>288</v>
-      </c>
-      <c r="I121" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="J121" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="K121" s="1" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="122" ht="14" spans="3:11">
-      <c r="C122" s="1">
+      <c r="D127" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="E127" s="1">
+        <v>1</v>
+      </c>
+      <c r="F127" s="4">
+        <v>0</v>
+      </c>
+      <c r="G127" s="4">
+        <v>2</v>
+      </c>
+      <c r="H127" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="I127" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="J127" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="K127" s="1" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="128" ht="14" spans="3:11">
+      <c r="C128" s="1">
         <v>302</v>
       </c>
-      <c r="D122" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="E122" s="1"/>
-      <c r="F122" s="4"/>
-      <c r="G122" s="4"/>
-      <c r="H122" s="1"/>
-      <c r="I122" s="1"/>
-      <c r="J122" s="1"/>
-      <c r="K122" s="1"/>
-    </row>
-    <row r="123" ht="14" spans="3:11">
-      <c r="C123" s="1">
+      <c r="D128" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="E128" s="1"/>
+      <c r="F128" s="4"/>
+      <c r="G128" s="4"/>
+      <c r="H128" s="1"/>
+      <c r="I128" s="1"/>
+      <c r="J128" s="1"/>
+      <c r="K128" s="1"/>
+    </row>
+    <row r="129" ht="14" spans="3:11">
+      <c r="C129" s="1">
         <v>303</v>
       </c>
-      <c r="D123" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="E123" s="1">
-        <v>1</v>
-      </c>
-      <c r="F123" s="4">
-        <v>0</v>
-      </c>
-      <c r="G123" s="4">
-        <v>2</v>
-      </c>
-      <c r="H123" s="8" t="s">
-        <v>288</v>
-      </c>
-      <c r="I123" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="J123" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="K123" s="1" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="124" customFormat="1" ht="14" spans="3:11">
-      <c r="C124" s="1">
+      <c r="D129" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="E129" s="1">
+        <v>1</v>
+      </c>
+      <c r="F129" s="4">
+        <v>0</v>
+      </c>
+      <c r="G129" s="4">
+        <v>2</v>
+      </c>
+      <c r="H129" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="I129" s="8" t="s">
         <v>304</v>
       </c>
-      <c r="D124" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="E124" s="1">
-        <v>1</v>
-      </c>
-      <c r="F124" s="4">
-        <v>0</v>
-      </c>
-      <c r="G124" s="4">
-        <v>2</v>
-      </c>
-      <c r="H124" s="8" t="s">
-        <v>288</v>
-      </c>
-      <c r="I124" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="J124" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="K124" s="1" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="125"/>
-    <row r="126" ht="14"/>
+      <c r="J129" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="K129" s="1" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="130" customFormat="1" ht="14" spans="3:11">
+      <c r="C130" s="1">
+        <v>304</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="E130" s="1">
+        <v>1</v>
+      </c>
+      <c r="F130" s="4">
+        <v>0</v>
+      </c>
+      <c r="G130" s="4">
+        <v>2</v>
+      </c>
+      <c r="H130" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="I130" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="J130" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="K130" s="1" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="131" ht="14"/>
+    <row r="132" ht="14"/>
   </sheetData>
   <dataValidations count="2">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:E5 H3:K5" errorStyle="warning">
@@ -5771,7 +5989,7 @@
         <v>1001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -5786,13 +6004,13 @@
         <v>14</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="J6" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5800,7 +6018,7 @@
         <v>1002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -5815,13 +6033,13 @@
         <v>14</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="J7" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>300</v>
+        <v>312</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5829,7 +6047,7 @@
         <v>1003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -5844,13 +6062,13 @@
         <v>14</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="J8" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5858,7 +6076,7 @@
         <v>1004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
@@ -5873,13 +6091,13 @@
         <v>14</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="J9" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5887,7 +6105,7 @@
         <v>1005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -5902,13 +6120,13 @@
         <v>14</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="J10" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5916,7 +6134,7 @@
         <v>1006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -5931,13 +6149,13 @@
         <v>14</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="J11" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5945,7 +6163,7 @@
         <v>1007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
@@ -5960,13 +6178,13 @@
         <v>14</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="J12" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -5974,7 +6192,7 @@
         <v>1008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
@@ -5989,13 +6207,13 @@
         <v>14</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="J13" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6003,7 +6221,7 @@
         <v>1009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
@@ -6018,13 +6236,13 @@
         <v>14</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="J14" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6032,7 +6250,7 @@
         <v>1010</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
@@ -6047,13 +6265,13 @@
         <v>14</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="J15" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6061,7 +6279,7 @@
         <v>1011</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="E16" s="1">
         <v>1</v>
@@ -6076,13 +6294,13 @@
         <v>14</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="J16" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6090,7 +6308,7 @@
         <v>1012</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="E17" s="1">
         <v>1</v>
@@ -6105,13 +6323,13 @@
         <v>14</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="J17" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>326</v>
+        <v>338</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6119,7 +6337,7 @@
         <v>1013</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="E18" s="1">
         <v>1</v>
@@ -6134,13 +6352,13 @@
         <v>14</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="J18" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6148,7 +6366,7 @@
         <v>1014</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="E19" s="1">
         <v>1</v>
@@ -6163,13 +6381,13 @@
         <v>14</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="J19" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1"/>
@@ -6178,7 +6396,7 @@
         <v>1101</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
@@ -6193,13 +6411,13 @@
         <v>14</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="J21" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>334</v>
+        <v>346</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6207,7 +6425,7 @@
         <v>1102</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
@@ -6222,13 +6440,13 @@
         <v>14</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="J22" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>337</v>
+        <v>349</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6236,7 +6454,7 @@
         <v>1103</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
@@ -6251,13 +6469,13 @@
         <v>14</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="J23" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6265,7 +6483,7 @@
         <v>1104</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
@@ -6280,13 +6498,13 @@
         <v>14</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>342</v>
+        <v>354</v>
       </c>
       <c r="J24" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>343</v>
+        <v>355</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6294,7 +6512,7 @@
         <v>1105</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="E25" s="1">
         <v>1</v>
@@ -6309,13 +6527,13 @@
         <v>14</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="J25" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>346</v>
+        <v>358</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6323,7 +6541,7 @@
         <v>1106</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
@@ -6338,13 +6556,13 @@
         <v>14</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="J26" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>349</v>
+        <v>361</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6352,7 +6570,7 @@
         <v>1107</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="E27" s="1">
         <v>1</v>
@@ -6367,13 +6585,13 @@
         <v>14</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="J27" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>352</v>
+        <v>364</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6381,7 +6599,7 @@
         <v>1108</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="E28" s="1">
         <v>1</v>
@@ -6396,13 +6614,13 @@
         <v>14</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="J28" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6410,7 +6628,7 @@
         <v>1109</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>356</v>
+        <v>368</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
@@ -6425,13 +6643,13 @@
         <v>14</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="J29" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>358</v>
+        <v>370</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6439,7 +6657,7 @@
         <v>1110</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
@@ -6454,13 +6672,13 @@
         <v>14</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>360</v>
+        <v>372</v>
       </c>
       <c r="J30" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>361</v>
+        <v>373</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6468,7 +6686,7 @@
         <v>1111</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
@@ -6483,13 +6701,13 @@
         <v>14</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="J31" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>364</v>
+        <v>376</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6497,7 +6715,7 @@
         <v>1112</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="E32" s="1">
         <v>1</v>
@@ -6512,13 +6730,13 @@
         <v>14</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="J32" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="2:12">
@@ -6539,7 +6757,7 @@
         <v>1201</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="E34" s="1">
         <v>1</v>
@@ -6554,13 +6772,13 @@
         <v>133</v>
       </c>
       <c r="I34" s="8" t="s">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="J34" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>370</v>
+        <v>382</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="2:12">
@@ -6569,7 +6787,7 @@
         <v>1202</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="E35" s="1">
         <v>1</v>
@@ -6581,16 +6799,16 @@
         <v>2</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="J35" s="8" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="L35" s="2"/>
     </row>
@@ -6600,7 +6818,7 @@
         <v>1203</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="E36" s="1">
         <v>1</v>
@@ -6612,16 +6830,16 @@
         <v>2</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>377</v>
+        <v>389</v>
       </c>
       <c r="I36" s="8" t="s">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="J36" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="L36" s="2"/>
     </row>
@@ -6630,7 +6848,7 @@
         <v>1204</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="E37" s="1">
         <v>1</v>
@@ -6645,13 +6863,13 @@
         <v>133</v>
       </c>
       <c r="I37" s="8" t="s">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="J37" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>382</v>
+        <v>394</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="2:12">
@@ -6659,7 +6877,7 @@
         <v>1205</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="E38" s="1">
         <v>1</v>
@@ -6671,16 +6889,16 @@
         <v>2</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="I38" s="8" t="s">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="J38" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>385</v>
+        <v>397</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="2:12">
@@ -6688,7 +6906,7 @@
         <v>1206</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c r="E39" s="1">
         <v>1</v>
@@ -6700,16 +6918,16 @@
         <v>2</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="I39" s="8" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="J39" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>388</v>
+        <v>400</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="2:12">
@@ -6717,7 +6935,7 @@
         <v>2001</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="E41" s="1">
         <v>1</v>
@@ -6729,16 +6947,16 @@
         <v>2</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="I41" s="8" t="s">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c r="J41" s="8" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="K41" s="5" t="s">
-        <v>389</v>
+        <v>401</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="2:12">
@@ -6746,7 +6964,7 @@
         <v>2002</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="E42" s="1">
         <v>1</v>
@@ -6758,16 +6976,16 @@
         <v>2</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="I42" s="8" t="s">
-        <v>393</v>
+        <v>405</v>
       </c>
       <c r="J42" s="8" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="K42" s="5" t="s">
-        <v>392</v>
+        <v>404</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="2:12">
@@ -6775,7 +6993,7 @@
         <v>2003</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="E43" s="1">
         <v>1</v>
@@ -6787,16 +7005,16 @@
         <v>2</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="I43" s="8" t="s">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="J43" s="8" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="K43" s="5" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="2:12">
@@ -6804,7 +7022,7 @@
         <v>2004</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="E44" s="1">
         <v>1</v>
@@ -6816,16 +7034,16 @@
         <v>2</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="I44" s="8" t="s">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="J44" s="8" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="K44" s="5" t="s">
-        <v>396</v>
+        <v>408</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="2:12">
@@ -6833,7 +7051,7 @@
         <v>2005</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>398</v>
+        <v>410</v>
       </c>
       <c r="E45" s="1">
         <v>1</v>
@@ -6845,16 +7063,16 @@
         <v>2</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="I45" s="8" t="s">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="J45" s="8" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="K45" s="5" t="s">
-        <v>398</v>
+        <v>410</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="2:12">
@@ -6862,7 +7080,7 @@
         <v>2006</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="E46" s="1">
         <v>1</v>
@@ -6874,16 +7092,16 @@
         <v>2</v>
       </c>
       <c r="H46" s="8" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="I46" s="8" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="J46" s="8" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" customHeight="1" spans="2:12">
@@ -6892,28 +7110,28 @@
         <v>2007</v>
       </c>
       <c r="D47" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="E47" s="1">
+        <v>1</v>
+      </c>
+      <c r="F47" s="4">
+        <v>0</v>
+      </c>
+      <c r="G47" s="1">
+        <v>2</v>
+      </c>
+      <c r="H47" s="8" t="s">
         <v>402</v>
       </c>
-      <c r="E47" s="1">
-        <v>1</v>
-      </c>
-      <c r="F47" s="4">
-        <v>0</v>
-      </c>
-      <c r="G47" s="1">
-        <v>2</v>
-      </c>
-      <c r="H47" s="8" t="s">
-        <v>390</v>
-      </c>
       <c r="I47" s="8" t="s">
-        <v>403</v>
+        <v>415</v>
       </c>
       <c r="J47" s="8" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="K47" s="5" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c r="L47" s="2"/>
     </row>
@@ -6923,7 +7141,7 @@
         <v>2008</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="E48" s="1">
         <v>1</v>
@@ -6935,16 +7153,16 @@
         <v>2</v>
       </c>
       <c r="H48" s="8" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="I48" s="8" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="J48" s="8" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="K48" s="5" t="s">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="L48" s="2"/>
     </row>
@@ -6954,7 +7172,7 @@
         <v>2009</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
       <c r="E49" s="1">
         <v>1</v>
@@ -6966,16 +7184,16 @@
         <v>2</v>
       </c>
       <c r="H49" s="8" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="I49" s="8" t="s">
-        <v>407</v>
+        <v>419</v>
       </c>
       <c r="J49" s="8" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="K49" s="5" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
       <c r="L49" s="2"/>
     </row>
@@ -6985,7 +7203,7 @@
         <v>2010</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="E50" s="1">
         <v>1</v>
@@ -6997,16 +7215,16 @@
         <v>2</v>
       </c>
       <c r="H50" s="8" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="I50" s="8" t="s">
-        <v>409</v>
+        <v>421</v>
       </c>
       <c r="J50" s="8" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="K50" s="5" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="L50" s="2"/>
     </row>
@@ -7016,7 +7234,7 @@
         <v>2011</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="E51" s="1">
         <v>1</v>
@@ -7028,16 +7246,16 @@
         <v>2</v>
       </c>
       <c r="H51" s="8" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="I51" s="8" t="s">
-        <v>411</v>
+        <v>423</v>
       </c>
       <c r="J51" s="8" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="K51" s="5" t="s">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="L51" s="2"/>
     </row>
@@ -7047,7 +7265,7 @@
         <v>2012</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>412</v>
+        <v>424</v>
       </c>
       <c r="E52" s="1">
         <v>1</v>
@@ -7059,16 +7277,16 @@
         <v>2</v>
       </c>
       <c r="H52" s="8" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="I52" s="8" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
       <c r="J52" s="8" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="K52" s="5" t="s">
-        <v>412</v>
+        <v>424</v>
       </c>
       <c r="L52" s="2"/>
     </row>
@@ -7090,7 +7308,7 @@
         <v>2013</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>414</v>
+        <v>426</v>
       </c>
       <c r="E54" s="1">
         <v>1</v>
@@ -7102,16 +7320,16 @@
         <v>2</v>
       </c>
       <c r="H54" s="8" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="I54" s="8" t="s">
-        <v>415</v>
+        <v>427</v>
       </c>
       <c r="J54" s="8" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="K54" s="6" t="s">
-        <v>414</v>
+        <v>426</v>
       </c>
       <c r="L54" s="2"/>
     </row>
@@ -7121,7 +7339,7 @@
         <v>2014</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="E55" s="1">
         <v>1</v>
@@ -7133,16 +7351,16 @@
         <v>2</v>
       </c>
       <c r="H55" s="8" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="I55" s="8" t="s">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="J55" s="8" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="K55" s="6" t="s">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="L55" s="2"/>
     </row>
@@ -7151,7 +7369,7 @@
         <v>2015</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>418</v>
+        <v>430</v>
       </c>
       <c r="E56" s="1">
         <v>1</v>
@@ -7163,16 +7381,16 @@
         <v>2</v>
       </c>
       <c r="H56" s="8" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="I56" s="8" t="s">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="J56" s="8" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="K56" s="6" t="s">
-        <v>418</v>
+        <v>430</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="2:12">
@@ -7180,7 +7398,7 @@
         <v>2016</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="E57" s="1">
         <v>1</v>
@@ -7192,16 +7410,16 @@
         <v>2</v>
       </c>
       <c r="H57" s="8" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="I57" s="8" t="s">
-        <v>421</v>
+        <v>433</v>
       </c>
       <c r="J57" s="8" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="K57" s="6" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="2:12">
@@ -7209,7 +7427,7 @@
         <v>2017</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>422</v>
+        <v>434</v>
       </c>
       <c r="E58" s="1">
         <v>1</v>
@@ -7221,16 +7439,16 @@
         <v>2</v>
       </c>
       <c r="H58" s="8" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="I58" s="8" t="s">
-        <v>423</v>
+        <v>435</v>
       </c>
       <c r="J58" s="8" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="K58" s="6" t="s">
-        <v>422</v>
+        <v>434</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="2:12">
@@ -7238,7 +7456,7 @@
         <v>2018</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>424</v>
+        <v>436</v>
       </c>
       <c r="E59" s="1">
         <v>1</v>
@@ -7250,16 +7468,16 @@
         <v>2</v>
       </c>
       <c r="H59" s="8" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="I59" s="8" t="s">
-        <v>425</v>
+        <v>437</v>
       </c>
       <c r="J59" s="8" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="K59" s="6" t="s">
-        <v>424</v>
+        <v>436</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="2:12">
@@ -7267,7 +7485,7 @@
         <v>2019</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>426</v>
+        <v>438</v>
       </c>
       <c r="E60" s="1">
         <v>1</v>
@@ -7279,16 +7497,16 @@
         <v>2</v>
       </c>
       <c r="H60" s="8" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="I60" s="8" t="s">
-        <v>427</v>
+        <v>439</v>
       </c>
       <c r="J60" s="8" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="K60" s="6" t="s">
-        <v>426</v>
+        <v>438</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="2:12">
@@ -7296,7 +7514,7 @@
         <v>2020</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>428</v>
+        <v>440</v>
       </c>
       <c r="E61" s="1">
         <v>1</v>
@@ -7308,16 +7526,16 @@
         <v>2</v>
       </c>
       <c r="H61" s="8" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="I61" s="8" t="s">
-        <v>429</v>
+        <v>441</v>
       </c>
       <c r="J61" s="8" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="K61" s="6" t="s">
-        <v>428</v>
+        <v>440</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="2:12">
@@ -7325,7 +7543,7 @@
         <v>2021</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="E62" s="1">
         <v>1</v>
@@ -7337,16 +7555,16 @@
         <v>2</v>
       </c>
       <c r="H62" s="8" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="I62" s="8" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="J62" s="8" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="K62" s="6" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="2:12">
@@ -7354,7 +7572,7 @@
         <v>2022</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>432</v>
+        <v>444</v>
       </c>
       <c r="E63" s="1">
         <v>1</v>
@@ -7366,16 +7584,16 @@
         <v>2</v>
       </c>
       <c r="H63" s="8" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="I63" s="8" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="J63" s="8" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="K63" s="6" t="s">
-        <v>432</v>
+        <v>444</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="2:12">
@@ -7383,7 +7601,7 @@
         <v>2023</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="E64" s="1">
         <v>1</v>
@@ -7395,16 +7613,16 @@
         <v>2</v>
       </c>
       <c r="H64" s="8" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="I64" s="8" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="J64" s="8" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="K64" s="6" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:11">
@@ -7412,7 +7630,7 @@
         <v>2024</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="E65" s="1">
         <v>1</v>
@@ -7424,16 +7642,16 @@
         <v>2</v>
       </c>
       <c r="H65" s="8" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="I65" s="8" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="J65" s="8" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="K65" s="6" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="3:11">
@@ -7441,7 +7659,7 @@
         <v>2025</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>438</v>
+        <v>450</v>
       </c>
       <c r="E66" s="1">
         <v>1</v>
@@ -7453,16 +7671,16 @@
         <v>2</v>
       </c>
       <c r="H66" s="8" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="I66" s="8" t="s">
-        <v>439</v>
+        <v>451</v>
       </c>
       <c r="J66" s="8" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="K66" s="6" t="s">
-        <v>438</v>
+        <v>450</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:11">
@@ -7480,7 +7698,7 @@
         <v>2026</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c r="E68" s="1">
         <v>1</v>
@@ -7492,16 +7710,16 @@
         <v>2</v>
       </c>
       <c r="H68" s="8" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="I68" s="8" t="s">
-        <v>441</v>
+        <v>453</v>
       </c>
       <c r="J68" s="8" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="K68" s="6" t="s">
-        <v>440</v>
+        <v>452</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:11">
@@ -7509,7 +7727,7 @@
         <v>2027</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="E69" s="1">
         <v>1</v>
@@ -7521,16 +7739,16 @@
         <v>2</v>
       </c>
       <c r="H69" s="8" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="I69" s="8" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="J69" s="8" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="K69" s="6" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:11">
@@ -7538,7 +7756,7 @@
         <v>2028</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="E70" s="1">
         <v>1</v>
@@ -7550,16 +7768,16 @@
         <v>2</v>
       </c>
       <c r="H70" s="8" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="I70" s="8" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="J70" s="8" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="K70" s="6" t="s">
-        <v>444</v>
+        <v>456</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:11">
@@ -7567,7 +7785,7 @@
         <v>2029</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>446</v>
+        <v>458</v>
       </c>
       <c r="E71" s="1">
         <v>1</v>
@@ -7579,16 +7797,16 @@
         <v>2</v>
       </c>
       <c r="H71" s="8" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="I71" s="8" t="s">
-        <v>447</v>
+        <v>459</v>
       </c>
       <c r="J71" s="8" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="K71" s="6" t="s">
-        <v>446</v>
+        <v>458</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:11">
@@ -7596,7 +7814,7 @@
         <v>2030</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="E72" s="1">
         <v>1</v>
@@ -7608,16 +7826,16 @@
         <v>2</v>
       </c>
       <c r="H72" s="8" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="I72" s="8" t="s">
-        <v>449</v>
+        <v>461</v>
       </c>
       <c r="J72" s="8" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="K72" s="6" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:11">
@@ -7625,7 +7843,7 @@
         <v>2031</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="E73" s="1">
         <v>1</v>
@@ -7637,16 +7855,16 @@
         <v>2</v>
       </c>
       <c r="H73" s="8" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="I73" s="8" t="s">
-        <v>451</v>
+        <v>463</v>
       </c>
       <c r="J73" s="8" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="K73" s="6" t="s">
-        <v>450</v>
+        <v>462</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:11">
@@ -7654,7 +7872,7 @@
         <v>2032</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c r="E74" s="1">
         <v>1</v>
@@ -7666,16 +7884,16 @@
         <v>2</v>
       </c>
       <c r="H74" s="8" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="I74" s="8" t="s">
-        <v>453</v>
+        <v>465</v>
       </c>
       <c r="J74" s="8" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="K74" s="6" t="s">
-        <v>452</v>
+        <v>464</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:11">
@@ -7683,7 +7901,7 @@
         <v>2033</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>454</v>
+        <v>466</v>
       </c>
       <c r="E75" s="1">
         <v>1</v>
@@ -7695,16 +7913,16 @@
         <v>2</v>
       </c>
       <c r="H75" s="8" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="I75" s="8" t="s">
-        <v>455</v>
+        <v>467</v>
       </c>
       <c r="J75" s="8" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="K75" s="6" t="s">
-        <v>454</v>
+        <v>466</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:11">
@@ -7712,7 +7930,7 @@
         <v>2034</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>456</v>
+        <v>468</v>
       </c>
       <c r="E76" s="1">
         <v>1</v>
@@ -7724,16 +7942,16 @@
         <v>2</v>
       </c>
       <c r="H76" s="8" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="I76" s="8" t="s">
-        <v>457</v>
+        <v>469</v>
       </c>
       <c r="J76" s="8" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="K76" s="6" t="s">
-        <v>456</v>
+        <v>468</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:11">
@@ -7741,7 +7959,7 @@
         <v>2035</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>458</v>
+        <v>470</v>
       </c>
       <c r="E77" s="1">
         <v>1</v>
@@ -7753,16 +7971,16 @@
         <v>2</v>
       </c>
       <c r="H77" s="8" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="I77" s="8" t="s">
-        <v>459</v>
+        <v>471</v>
       </c>
       <c r="J77" s="8" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="K77" s="6" t="s">
-        <v>458</v>
+        <v>470</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -3854,7 +3854,7 @@
         <v>0</v>
       </c>
       <c r="G49" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H49" s="8" t="s">
         <v>77</v>

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="959" uniqueCount="472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="964" uniqueCount="474">
   <si>
     <t>_id</t>
   </si>
@@ -558,6 +558,12 @@
   </si>
   <si>
     <t>47</t>
+  </si>
+  <si>
+    <t>道戒自选</t>
+  </si>
+  <si>
+    <t>190013,190014,190015,190016,190017,190018</t>
   </si>
   <si>
     <t>粉色专属自选</t>
@@ -2488,7 +2494,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K132"/>
+  <dimension ref="A1:K133"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="4" max="4" width="16.625" customWidth="1"/>
@@ -4082,117 +4088,115 @@
         <v>132</v>
       </c>
     </row>
-    <row r="57" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A57" s="1"/>
-      <c r="B57" s="1"/>
-      <c r="C57" s="1"/>
-      <c r="D57" s="1"/>
-      <c r="E57" s="1"/>
-      <c r="F57" s="4"/>
-      <c r="G57" s="4"/>
-      <c r="H57" s="1"/>
-      <c r="I57" s="1"/>
-      <c r="J57" s="1"/>
-      <c r="K57" s="1"/>
+    <row r="57" s="1" customFormat="1" customHeight="1" spans="1:11">
+      <c r="C57" s="1">
+        <v>53</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E57" s="1">
+        <v>1</v>
+      </c>
+      <c r="F57" s="1">
+        <v>0</v>
+      </c>
+      <c r="G57" s="1">
+        <v>1</v>
+      </c>
+      <c r="H57" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="I57" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="J57" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="K57" s="1" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="58" customFormat="1" customHeight="1" spans="1:11">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
-      <c r="C58" s="1">
-        <v>89</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="E58" s="1">
-        <v>1</v>
-      </c>
-      <c r="F58" s="4">
-        <v>0</v>
-      </c>
-      <c r="G58" s="1">
-        <v>2</v>
-      </c>
-      <c r="H58" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="I58" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="J58" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="K58" s="1" t="s">
-        <v>161</v>
-      </c>
+      <c r="C58" s="1"/>
+      <c r="D58" s="1"/>
+      <c r="E58" s="1"/>
+      <c r="F58" s="4"/>
+      <c r="G58" s="4"/>
+      <c r="H58" s="1"/>
+      <c r="I58" s="1"/>
+      <c r="J58" s="1"/>
+      <c r="K58" s="1"/>
     </row>
     <row r="59" customFormat="1" customHeight="1" spans="1:11">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D59" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E59" s="1">
+        <v>1</v>
+      </c>
+      <c r="F59" s="4">
+        <v>0</v>
+      </c>
+      <c r="G59" s="1">
+        <v>2</v>
+      </c>
+      <c r="H59" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="E59" s="1">
-        <v>1</v>
-      </c>
-      <c r="F59" s="4">
-        <v>0</v>
-      </c>
-      <c r="G59" s="1">
-        <v>2</v>
-      </c>
-      <c r="H59" s="8" t="s">
+      <c r="I59" s="8" t="s">
         <v>162</v>
-      </c>
-      <c r="I59" s="8" t="s">
-        <v>163</v>
       </c>
       <c r="J59" s="8" t="s">
         <v>141</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="60" customFormat="1" customHeight="1" spans="1:11">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D60" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E60" s="1">
+        <v>1</v>
+      </c>
+      <c r="F60" s="4">
+        <v>0</v>
+      </c>
+      <c r="G60" s="1">
+        <v>2</v>
+      </c>
+      <c r="H60" s="8" t="s">
         <v>164</v>
-      </c>
-      <c r="E60" s="1">
-        <v>1</v>
-      </c>
-      <c r="F60" s="4">
-        <v>0</v>
-      </c>
-      <c r="G60" s="1">
-        <v>2</v>
-      </c>
-      <c r="H60" s="8" t="s">
-        <v>133</v>
       </c>
       <c r="I60" s="8" t="s">
         <v>165</v>
       </c>
       <c r="J60" s="8" t="s">
-        <v>16</v>
+        <v>141</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="61" customFormat="1" customHeight="1" spans="1:11">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>166</v>
@@ -4207,7 +4211,7 @@
         <v>2</v>
       </c>
       <c r="H61" s="8" t="s">
-        <v>159</v>
+        <v>133</v>
       </c>
       <c r="I61" s="8" t="s">
         <v>167</v>
@@ -4216,14 +4220,14 @@
         <v>16</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="62" customFormat="1" customHeight="1" spans="1:11">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>168</v>
@@ -4238,27 +4242,29 @@
         <v>2</v>
       </c>
       <c r="H62" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I62" s="8" t="s">
         <v>169</v>
       </c>
       <c r="J62" s="8" t="s">
-        <v>91</v>
+        <v>16</v>
       </c>
       <c r="K62" s="1" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="63" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A63" s="1"/>
+      <c r="B63" s="1"/>
       <c r="C63" s="1">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>170</v>
       </c>
       <c r="E63" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F63" s="4">
         <v>0</v>
@@ -4267,13 +4273,13 @@
         <v>2</v>
       </c>
       <c r="H63" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="I63" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="I63" s="8" t="s">
-        <v>172</v>
-      </c>
       <c r="J63" s="8" t="s">
-        <v>173</v>
+        <v>91</v>
       </c>
       <c r="K63" s="1" t="s">
         <v>170</v>
@@ -4281,123 +4287,123 @@
     </row>
     <row r="64" customFormat="1" customHeight="1" spans="1:11">
       <c r="C64" s="1">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D64" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E64" s="1">
+        <v>0</v>
+      </c>
+      <c r="F64" s="4">
+        <v>0</v>
+      </c>
+      <c r="G64" s="1">
+        <v>2</v>
+      </c>
+      <c r="H64" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="I64" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="E64" s="1">
-        <v>1</v>
-      </c>
-      <c r="F64" s="4">
-        <v>0</v>
-      </c>
-      <c r="G64" s="1">
-        <v>2</v>
-      </c>
-      <c r="H64" s="8" t="s">
+      <c r="J64" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="I64" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="J64" s="8" t="s">
-        <v>32</v>
-      </c>
       <c r="K64" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="65" customFormat="1" customHeight="1" spans="3:11">
       <c r="C65" s="1">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D65" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="E65" s="1">
+        <v>1</v>
+      </c>
+      <c r="F65" s="4">
+        <v>0</v>
+      </c>
+      <c r="G65" s="1">
+        <v>2</v>
+      </c>
+      <c r="H65" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="E65" s="1">
-        <v>1</v>
-      </c>
-      <c r="F65" s="4">
-        <v>0</v>
-      </c>
-      <c r="G65" s="1">
-        <v>2</v>
-      </c>
-      <c r="H65" s="8" t="s">
+      <c r="I65" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="I65" s="8" t="s">
-        <v>179</v>
-      </c>
       <c r="J65" s="8" t="s">
-        <v>91</v>
+        <v>32</v>
       </c>
       <c r="K65" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="66" customFormat="1" customHeight="1" spans="3:11">
       <c r="C66" s="1">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D66" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="E66" s="1">
+        <v>1</v>
+      </c>
+      <c r="F66" s="4">
+        <v>0</v>
+      </c>
+      <c r="G66" s="1">
+        <v>2</v>
+      </c>
+      <c r="H66" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="E66" s="1">
-        <v>0</v>
-      </c>
-      <c r="F66" s="4">
-        <v>0</v>
-      </c>
-      <c r="G66" s="1">
-        <v>2</v>
-      </c>
-      <c r="H66" s="8" t="s">
+      <c r="I66" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="I66" s="8" t="s">
-        <v>182</v>
-      </c>
       <c r="J66" s="8" t="s">
-        <v>183</v>
+        <v>91</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="67" customFormat="1" customHeight="1" spans="3:11">
       <c r="C67" s="1">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D67" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="E67" s="1">
+        <v>0</v>
+      </c>
+      <c r="F67" s="4">
+        <v>0</v>
+      </c>
+      <c r="G67" s="1">
+        <v>2</v>
+      </c>
+      <c r="H67" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="I67" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="E67" s="1">
-        <v>0</v>
-      </c>
-      <c r="F67" s="4">
-        <v>0</v>
-      </c>
-      <c r="G67" s="1">
-        <v>2</v>
-      </c>
-      <c r="H67" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="I67" s="8" t="s">
+      <c r="J67" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="J67" s="8" t="s">
-        <v>173</v>
-      </c>
       <c r="K67" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="68" customFormat="1" customHeight="1" spans="3:11">
       <c r="C68" s="1">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>186</v>
@@ -4412,13 +4418,13 @@
         <v>2</v>
       </c>
       <c r="H68" s="8" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I68" s="8" t="s">
         <v>187</v>
       </c>
       <c r="J68" s="8" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="K68" s="1" t="s">
         <v>186</v>
@@ -4426,7 +4432,7 @@
     </row>
     <row r="69" customFormat="1" customHeight="1" spans="3:11">
       <c r="C69" s="1">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>188</v>
@@ -4441,13 +4447,13 @@
         <v>2</v>
       </c>
       <c r="H69" s="8" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="I69" s="8" t="s">
         <v>189</v>
       </c>
       <c r="J69" s="8" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="K69" s="1" t="s">
         <v>188</v>
@@ -4455,7 +4461,7 @@
     </row>
     <row r="70" customFormat="1" customHeight="1" spans="3:11">
       <c r="C70" s="1">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>190</v>
@@ -4470,13 +4476,13 @@
         <v>2</v>
       </c>
       <c r="H70" s="8" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="I70" s="8" t="s">
         <v>191</v>
       </c>
       <c r="J70" s="8" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="K70" s="1" t="s">
         <v>190</v>
@@ -4484,7 +4490,7 @@
     </row>
     <row r="71" customFormat="1" customHeight="1" spans="3:11">
       <c r="C71" s="1">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>192</v>
@@ -4499,13 +4505,13 @@
         <v>2</v>
       </c>
       <c r="H71" s="8" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="I71" s="8" t="s">
         <v>193</v>
       </c>
       <c r="J71" s="8" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="K71" s="1" t="s">
         <v>192</v>
@@ -4513,7 +4519,7 @@
     </row>
     <row r="72" customFormat="1" customHeight="1" spans="3:11">
       <c r="C72" s="1">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>194</v>
@@ -4528,80 +4534,80 @@
         <v>2</v>
       </c>
       <c r="H72" s="8" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="I72" s="8" t="s">
         <v>195</v>
       </c>
       <c r="J72" s="8" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="K72" s="1" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="73" ht="14"/>
-    <row r="74" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C74" s="1">
-        <v>106</v>
-      </c>
-      <c r="D74" s="1" t="s">
+    <row r="73" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C73" s="1">
+        <v>105</v>
+      </c>
+      <c r="D73" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="E74" s="1">
-        <v>1</v>
-      </c>
-      <c r="F74" s="4">
-        <v>0</v>
-      </c>
-      <c r="G74" s="1">
-        <v>1</v>
-      </c>
-      <c r="H74" s="8" t="s">
+      <c r="E73" s="1">
+        <v>0</v>
+      </c>
+      <c r="F73" s="4">
+        <v>0</v>
+      </c>
+      <c r="G73" s="1">
+        <v>2</v>
+      </c>
+      <c r="H73" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="I73" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="I74" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="J74" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="K74" s="1" t="s">
-        <v>200</v>
-      </c>
-    </row>
+      <c r="J73" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="K73" s="1" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="74" ht="14"/>
     <row r="75" customFormat="1" customHeight="1" spans="3:11">
       <c r="C75" s="1">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D75" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E75" s="1">
+        <v>1</v>
+      </c>
+      <c r="F75" s="4">
+        <v>0</v>
+      </c>
+      <c r="G75" s="1">
+        <v>1</v>
+      </c>
+      <c r="H75" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="I75" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="J75" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="E75" s="1">
-        <v>1</v>
-      </c>
-      <c r="F75" s="4">
-        <v>0</v>
-      </c>
-      <c r="G75" s="1">
-        <v>2</v>
-      </c>
-      <c r="H75" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="I75" s="8" t="s">
+      <c r="K75" s="1" t="s">
         <v>202</v>
-      </c>
-      <c r="J75" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="K75" s="1" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="76" customFormat="1" customHeight="1" spans="3:11">
       <c r="C76" s="1">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>203</v>
@@ -4625,258 +4631,252 @@
         <v>40</v>
       </c>
       <c r="K76" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="77" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C77" s="1">
+        <v>108</v>
+      </c>
+      <c r="D77" s="1" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="77" ht="14"/>
-    <row r="78" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C78" s="1">
-        <v>109</v>
-      </c>
-      <c r="D78" s="1" t="s">
+      <c r="E77" s="1">
+        <v>1</v>
+      </c>
+      <c r="F77" s="4">
+        <v>0</v>
+      </c>
+      <c r="G77" s="1">
+        <v>2</v>
+      </c>
+      <c r="H77" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="I77" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="E78" s="1">
-        <v>1</v>
-      </c>
-      <c r="F78" s="4">
-        <v>0</v>
-      </c>
-      <c r="G78" s="4">
-        <v>2</v>
-      </c>
-      <c r="H78" s="8" t="s">
+      <c r="J77" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="K77" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="I78" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="J78" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="K78" s="1" t="s">
-        <v>209</v>
-      </c>
-    </row>
+    </row>
+    <row r="78" ht="14"/>
     <row r="79" customFormat="1" customHeight="1" spans="3:11">
       <c r="C79" s="1">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D79" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="E79" s="1">
+        <v>1</v>
+      </c>
+      <c r="F79" s="4">
+        <v>0</v>
+      </c>
+      <c r="G79" s="4">
+        <v>2</v>
+      </c>
+      <c r="H79" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="I79" s="8" t="s">
         <v>210</v>
-      </c>
-      <c r="E79" s="1">
-        <v>1</v>
-      </c>
-      <c r="F79" s="4">
-        <v>0</v>
-      </c>
-      <c r="G79" s="4">
-        <v>2</v>
-      </c>
-      <c r="H79" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="I79" s="8" t="s">
-        <v>211</v>
       </c>
       <c r="J79" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K79" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="80" customFormat="1" customHeight="1" spans="3:11">
       <c r="C80" s="1">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D80" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="E80" s="1">
+        <v>1</v>
+      </c>
+      <c r="F80" s="4">
+        <v>0</v>
+      </c>
+      <c r="G80" s="4">
+        <v>2</v>
+      </c>
+      <c r="H80" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="I80" s="8" t="s">
         <v>213</v>
-      </c>
-      <c r="E80" s="1">
-        <v>1</v>
-      </c>
-      <c r="F80" s="4">
-        <v>0</v>
-      </c>
-      <c r="G80" s="4">
-        <v>2</v>
-      </c>
-      <c r="H80" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="I80" s="8" t="s">
-        <v>214</v>
       </c>
       <c r="J80" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K80" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="81" customFormat="1" customHeight="1" spans="1:11">
       <c r="C81" s="1">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D81" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E81" s="1">
+        <v>1</v>
+      </c>
+      <c r="F81" s="4">
+        <v>0</v>
+      </c>
+      <c r="G81" s="4">
+        <v>2</v>
+      </c>
+      <c r="H81" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="I81" s="8" t="s">
         <v>216</v>
-      </c>
-      <c r="E81" s="1">
-        <v>1</v>
-      </c>
-      <c r="F81" s="4">
-        <v>0</v>
-      </c>
-      <c r="G81" s="4">
-        <v>2</v>
-      </c>
-      <c r="H81" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="I81" s="8" t="s">
-        <v>217</v>
       </c>
       <c r="J81" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K81" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="82" customFormat="1" customHeight="1" spans="1:11">
       <c r="C82" s="1">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D82" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="E82" s="1">
+        <v>1</v>
+      </c>
+      <c r="F82" s="4">
+        <v>0</v>
+      </c>
+      <c r="G82" s="4">
+        <v>2</v>
+      </c>
+      <c r="H82" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="I82" s="8" t="s">
         <v>219</v>
-      </c>
-      <c r="E82" s="1">
-        <v>1</v>
-      </c>
-      <c r="F82" s="4">
-        <v>0</v>
-      </c>
-      <c r="G82" s="4">
-        <v>2</v>
-      </c>
-      <c r="H82" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="I82" s="8" t="s">
-        <v>220</v>
       </c>
       <c r="J82" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K82" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="83" customFormat="1" customHeight="1" spans="1:11">
       <c r="C83" s="1">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D83" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="E83" s="1">
+        <v>1</v>
+      </c>
+      <c r="F83" s="4">
+        <v>0</v>
+      </c>
+      <c r="G83" s="4">
+        <v>2</v>
+      </c>
+      <c r="H83" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="I83" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="E83" s="1">
-        <v>1</v>
-      </c>
-      <c r="F83" s="4">
-        <v>0</v>
-      </c>
-      <c r="G83" s="4">
-        <v>2</v>
-      </c>
-      <c r="H83" s="8" t="s">
+      <c r="J83" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="K83" s="1" t="s">
         <v>223</v>
-      </c>
-      <c r="I83" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="J83" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="K83" s="1" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="84" customFormat="1" customHeight="1" spans="1:11">
       <c r="C84" s="1">
+        <v>114</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="E84" s="1">
+        <v>1</v>
+      </c>
+      <c r="F84" s="4">
+        <v>0</v>
+      </c>
+      <c r="G84" s="4">
+        <v>2</v>
+      </c>
+      <c r="H84" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="I84" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="J84" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K84" s="1" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="85" customFormat="1" customHeight="1" spans="1:11">
+      <c r="C85" s="1">
         <v>115</v>
       </c>
-      <c r="D84" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="E84" s="1">
-        <v>1</v>
-      </c>
-      <c r="F84" s="4">
-        <v>0</v>
-      </c>
-      <c r="G84" s="4">
-        <v>2</v>
-      </c>
-      <c r="H84" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="I84" s="8" t="s">
-        <v>227</v>
-      </c>
-      <c r="J84" s="8" t="s">
+      <c r="D85" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E85" s="1">
+        <v>1</v>
+      </c>
+      <c r="F85" s="4">
+        <v>0</v>
+      </c>
+      <c r="G85" s="4">
+        <v>2</v>
+      </c>
+      <c r="H85" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="I85" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="J85" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="K84" s="1" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="85" ht="14"/>
-    <row r="86" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A86" s="1" t="s">
+      <c r="K85" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="B86" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="C86" s="1">
-        <v>118</v>
-      </c>
-      <c r="D86" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="E86" s="1">
-        <v>1</v>
-      </c>
-      <c r="F86" s="4">
-        <v>0</v>
-      </c>
-      <c r="G86" s="4">
-        <v>2</v>
-      </c>
-      <c r="H86" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="I86" s="8" t="s">
-        <v>230</v>
-      </c>
-      <c r="J86" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="K86" s="4" t="s">
-        <v>229</v>
-      </c>
-    </row>
+    </row>
+    <row r="86" ht="14"/>
     <row r="87" customFormat="1" customHeight="1" spans="1:11">
       <c r="A87" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C87" s="1">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D87" s="4" t="s">
         <v>231</v>
@@ -4891,7 +4891,7 @@
         <v>2</v>
       </c>
       <c r="H87" s="8" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I87" s="8" t="s">
         <v>232</v>
@@ -4905,13 +4905,13 @@
     </row>
     <row r="88" customFormat="1" customHeight="1" spans="1:11">
       <c r="A88" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C88" s="1">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D88" s="4" t="s">
         <v>233</v>
@@ -4926,7 +4926,7 @@
         <v>2</v>
       </c>
       <c r="H88" s="8" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I88" s="8" t="s">
         <v>234</v>
@@ -4940,13 +4940,13 @@
     </row>
     <row r="89" customFormat="1" customHeight="1" spans="1:11">
       <c r="A89" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C89" s="1">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D89" s="4" t="s">
         <v>235</v>
@@ -4961,7 +4961,7 @@
         <v>2</v>
       </c>
       <c r="H89" s="8" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I89" s="8" t="s">
         <v>236</v>
@@ -4975,13 +4975,13 @@
     </row>
     <row r="90" customFormat="1" customHeight="1" spans="1:11">
       <c r="A90" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C90" s="1">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D90" s="4" t="s">
         <v>237</v>
@@ -4996,7 +4996,7 @@
         <v>2</v>
       </c>
       <c r="H90" s="8" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I90" s="8" t="s">
         <v>238</v>
@@ -5010,13 +5010,13 @@
     </row>
     <row r="91" customFormat="1" customHeight="1" spans="1:11">
       <c r="A91" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C91" s="1">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D91" s="4" t="s">
         <v>239</v>
@@ -5031,7 +5031,7 @@
         <v>2</v>
       </c>
       <c r="H91" s="8" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I91" s="8" t="s">
         <v>240</v>
@@ -5045,15 +5045,15 @@
     </row>
     <row r="92" customFormat="1" customHeight="1" spans="1:11">
       <c r="A92" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C92" s="1">
-        <v>124</v>
-      </c>
-      <c r="D92" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D92" s="4" t="s">
         <v>241</v>
       </c>
       <c r="E92" s="1">
@@ -5066,7 +5066,7 @@
         <v>2</v>
       </c>
       <c r="H92" s="8" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I92" s="8" t="s">
         <v>242</v>
@@ -5074,19 +5074,19 @@
       <c r="J92" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="K92" s="1" t="s">
+      <c r="K92" s="4" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="93" customFormat="1" customHeight="1" spans="1:11">
       <c r="A93" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C93" s="1">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>243</v>
@@ -5101,7 +5101,7 @@
         <v>2</v>
       </c>
       <c r="H93" s="8" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I93" s="8" t="s">
         <v>244</v>
@@ -5115,13 +5115,13 @@
     </row>
     <row r="94" customFormat="1" customHeight="1" spans="1:11">
       <c r="A94" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C94" s="1">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>245</v>
@@ -5136,7 +5136,7 @@
         <v>2</v>
       </c>
       <c r="H94" s="8" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I94" s="8" t="s">
         <v>246</v>
@@ -5150,13 +5150,13 @@
     </row>
     <row r="95" customFormat="1" customHeight="1" spans="1:11">
       <c r="A95" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C95" s="1">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>247</v>
@@ -5171,7 +5171,7 @@
         <v>2</v>
       </c>
       <c r="H95" s="8" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I95" s="8" t="s">
         <v>248</v>
@@ -5185,13 +5185,13 @@
     </row>
     <row r="96" customFormat="1" customHeight="1" spans="1:11">
       <c r="A96" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C96" s="1">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>249</v>
@@ -5206,7 +5206,7 @@
         <v>2</v>
       </c>
       <c r="H96" s="8" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I96" s="8" t="s">
         <v>250</v>
@@ -5220,13 +5220,13 @@
     </row>
     <row r="97" customFormat="1" customHeight="1" spans="1:11">
       <c r="A97" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C97" s="1">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>251</v>
@@ -5241,7 +5241,7 @@
         <v>2</v>
       </c>
       <c r="H97" s="8" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I97" s="8" t="s">
         <v>252</v>
@@ -5255,13 +5255,13 @@
     </row>
     <row r="98" customFormat="1" customHeight="1" spans="1:11">
       <c r="A98" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C98" s="1">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D98" s="1" t="s">
         <v>253</v>
@@ -5276,7 +5276,7 @@
         <v>2</v>
       </c>
       <c r="H98" s="8" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I98" s="8" t="s">
         <v>254</v>
@@ -5290,13 +5290,13 @@
     </row>
     <row r="99" customFormat="1" customHeight="1" spans="1:11">
       <c r="A99" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C99" s="1">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D99" s="1" t="s">
         <v>255</v>
@@ -5311,7 +5311,7 @@
         <v>2</v>
       </c>
       <c r="H99" s="8" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I99" s="8" t="s">
         <v>256</v>
@@ -5323,51 +5323,51 @@
         <v>255</v>
       </c>
     </row>
-    <row r="100" ht="14"/>
-    <row r="101" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A101" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="C101" s="1">
-        <v>137</v>
-      </c>
-      <c r="D101" s="1" t="s">
+    <row r="100" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A100" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C100" s="1">
+        <v>131</v>
+      </c>
+      <c r="D100" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="E101" s="1">
-        <v>1</v>
-      </c>
-      <c r="F101" s="4">
-        <v>0</v>
-      </c>
-      <c r="G101" s="4">
-        <v>2</v>
-      </c>
-      <c r="H101" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="I101" s="8" t="s">
+      <c r="E100" s="1">
+        <v>1</v>
+      </c>
+      <c r="F100" s="4">
+        <v>0</v>
+      </c>
+      <c r="G100" s="4">
+        <v>2</v>
+      </c>
+      <c r="H100" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="I100" s="8" t="s">
         <v>258</v>
       </c>
-      <c r="J101" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="K101" s="1" t="s">
+      <c r="J100" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="K100" s="1" t="s">
         <v>257</v>
       </c>
     </row>
+    <row r="101" ht="14"/>
     <row r="102" customFormat="1" customHeight="1" spans="1:11">
       <c r="A102" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C102" s="1">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D102" s="1" t="s">
         <v>259</v>
@@ -5382,13 +5382,13 @@
         <v>2</v>
       </c>
       <c r="H102" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="I102" s="8" t="s">
         <v>260</v>
       </c>
-      <c r="I102" s="8" t="s">
-        <v>261</v>
-      </c>
       <c r="J102" s="8" t="s">
-        <v>262</v>
+        <v>40</v>
       </c>
       <c r="K102" s="1" t="s">
         <v>259</v>
@@ -5396,40 +5396,74 @@
     </row>
     <row r="103" customFormat="1" customHeight="1" spans="1:11">
       <c r="A103" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C103" s="1">
+        <v>138</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="E103" s="1">
+        <v>1</v>
+      </c>
+      <c r="F103" s="4">
+        <v>0</v>
+      </c>
+      <c r="G103" s="4">
+        <v>2</v>
+      </c>
+      <c r="H103" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="I103" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="J103" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="K103" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="104" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A104" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C104" s="1">
         <v>139</v>
       </c>
-      <c r="D103" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="E103" s="1">
-        <v>1</v>
-      </c>
-      <c r="F103" s="4">
-        <v>0</v>
-      </c>
-      <c r="G103" s="4">
-        <v>2</v>
-      </c>
-      <c r="H103" s="8" t="s">
-        <v>260</v>
-      </c>
-      <c r="I103" s="8" t="s">
+      <c r="D104" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="E104" s="1">
+        <v>1</v>
+      </c>
+      <c r="F104" s="4">
+        <v>0</v>
+      </c>
+      <c r="G104" s="4">
+        <v>2</v>
+      </c>
+      <c r="H104" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="I104" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="J104" s="8" t="s">
         <v>264</v>
       </c>
-      <c r="J103" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="K103" s="1" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="104" ht="14"/>
+      <c r="K104" s="1" t="s">
+        <v>265</v>
+      </c>
+    </row>
     <row r="105" ht="14"/>
     <row r="106" ht="14"/>
     <row r="107" ht="14"/>
@@ -5438,300 +5472,272 @@
     <row r="110" ht="14"/>
     <row r="111" ht="14"/>
     <row r="112" ht="14"/>
-    <row r="113" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C113" s="1">
-        <v>201</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="E113" s="1">
-        <v>1</v>
-      </c>
-      <c r="F113" s="4">
-        <v>0</v>
-      </c>
-      <c r="G113" s="4">
-        <v>2</v>
-      </c>
-      <c r="H113" s="8" t="s">
-        <v>266</v>
-      </c>
-      <c r="I113" s="8" t="s">
-        <v>267</v>
-      </c>
-      <c r="J113" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="K113" s="1" t="s">
-        <v>268</v>
-      </c>
-    </row>
+    <row r="113" ht="14"/>
     <row r="114" customFormat="1" customHeight="1" spans="3:11">
       <c r="C114" s="1">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D114" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="E114" s="1">
+        <v>1</v>
+      </c>
+      <c r="F114" s="4">
+        <v>0</v>
+      </c>
+      <c r="G114" s="4">
+        <v>2</v>
+      </c>
+      <c r="H114" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="I114" s="8" t="s">
         <v>269</v>
-      </c>
-      <c r="E114" s="1">
-        <v>1</v>
-      </c>
-      <c r="F114" s="4">
-        <v>0</v>
-      </c>
-      <c r="G114" s="4">
-        <v>2</v>
-      </c>
-      <c r="H114" s="8" t="s">
-        <v>266</v>
-      </c>
-      <c r="I114" s="8" t="s">
-        <v>270</v>
       </c>
       <c r="J114" s="8" t="s">
         <v>32</v>
       </c>
       <c r="K114" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="115" customFormat="1" customHeight="1" spans="3:11">
       <c r="C115" s="1">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D115" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="E115" s="1">
+        <v>1</v>
+      </c>
+      <c r="F115" s="4">
+        <v>0</v>
+      </c>
+      <c r="G115" s="4">
+        <v>2</v>
+      </c>
+      <c r="H115" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="I115" s="8" t="s">
         <v>272</v>
-      </c>
-      <c r="E115" s="1">
-        <v>1</v>
-      </c>
-      <c r="F115" s="4">
-        <v>0</v>
-      </c>
-      <c r="G115" s="4">
-        <v>2</v>
-      </c>
-      <c r="H115" s="8" t="s">
-        <v>266</v>
-      </c>
-      <c r="I115" s="8" t="s">
-        <v>273</v>
       </c>
       <c r="J115" s="8" t="s">
         <v>32</v>
       </c>
       <c r="K115" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="116" customFormat="1" customHeight="1" spans="3:11">
       <c r="C116" s="1">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D116" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="E116" s="1">
+        <v>1</v>
+      </c>
+      <c r="F116" s="4">
+        <v>0</v>
+      </c>
+      <c r="G116" s="4">
+        <v>2</v>
+      </c>
+      <c r="H116" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="I116" s="8" t="s">
         <v>275</v>
-      </c>
-      <c r="E116" s="1">
-        <v>1</v>
-      </c>
-      <c r="F116" s="4">
-        <v>0</v>
-      </c>
-      <c r="G116" s="4">
-        <v>2</v>
-      </c>
-      <c r="H116" s="8" t="s">
-        <v>266</v>
-      </c>
-      <c r="I116" s="8" t="s">
-        <v>276</v>
       </c>
       <c r="J116" s="8" t="s">
         <v>32</v>
       </c>
       <c r="K116" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="117" customFormat="1" customHeight="1" spans="3:11">
       <c r="C117" s="1">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D117" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="E117" s="1">
+        <v>1</v>
+      </c>
+      <c r="F117" s="4">
+        <v>0</v>
+      </c>
+      <c r="G117" s="4">
+        <v>2</v>
+      </c>
+      <c r="H117" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="I117" s="8" t="s">
         <v>278</v>
-      </c>
-      <c r="E117" s="1">
-        <v>1</v>
-      </c>
-      <c r="F117" s="4">
-        <v>0</v>
-      </c>
-      <c r="G117" s="4">
-        <v>2</v>
-      </c>
-      <c r="H117" s="8" t="s">
-        <v>266</v>
-      </c>
-      <c r="I117" s="8" t="s">
-        <v>279</v>
       </c>
       <c r="J117" s="8" t="s">
         <v>32</v>
       </c>
       <c r="K117" s="1" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="118" ht="14"/>
-    <row r="119" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C119" s="1">
-        <v>207</v>
-      </c>
-      <c r="D119" s="1" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="118" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C118" s="1">
+        <v>205</v>
+      </c>
+      <c r="D118" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="E119" s="1">
-        <v>1</v>
-      </c>
-      <c r="F119" s="4">
-        <v>0</v>
-      </c>
-      <c r="G119" s="4">
-        <v>2</v>
-      </c>
-      <c r="H119" s="8" t="s">
+      <c r="E118" s="1">
+        <v>1</v>
+      </c>
+      <c r="F118" s="4">
+        <v>0</v>
+      </c>
+      <c r="G118" s="4">
+        <v>2</v>
+      </c>
+      <c r="H118" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="I118" s="8" t="s">
         <v>281</v>
       </c>
-      <c r="I119" s="8" t="s">
-        <v>282</v>
-      </c>
-      <c r="J119" s="8" t="s">
-        <v>283</v>
-      </c>
-      <c r="K119" s="1" t="s">
-        <v>284</v>
-      </c>
-    </row>
+      <c r="J118" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="K118" s="1" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="119" ht="14"/>
     <row r="120" customFormat="1" customHeight="1" spans="3:11">
       <c r="C120" s="1">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D120" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="E120" s="1">
+        <v>1</v>
+      </c>
+      <c r="F120" s="4">
+        <v>0</v>
+      </c>
+      <c r="G120" s="4">
+        <v>2</v>
+      </c>
+      <c r="H120" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="I120" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="J120" s="8" t="s">
         <v>285</v>
       </c>
-      <c r="E120" s="1">
-        <v>1</v>
-      </c>
-      <c r="F120" s="4">
-        <v>0</v>
-      </c>
-      <c r="G120" s="4">
-        <v>2</v>
-      </c>
-      <c r="H120" s="8" t="s">
+      <c r="K120" s="1" t="s">
         <v>286</v>
-      </c>
-      <c r="I120" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="J120" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="K120" s="1" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="121" customFormat="1" customHeight="1" spans="3:11">
       <c r="C121" s="1">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D121" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E121" s="1">
+        <v>1</v>
+      </c>
+      <c r="F121" s="4">
+        <v>0</v>
+      </c>
+      <c r="G121" s="4">
+        <v>2</v>
+      </c>
+      <c r="H121" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="I121" s="8" t="s">
         <v>289</v>
       </c>
-      <c r="E121" s="1">
-        <v>1</v>
-      </c>
-      <c r="F121" s="4">
-        <v>0</v>
-      </c>
-      <c r="G121" s="4">
-        <v>2</v>
-      </c>
-      <c r="H121" s="8" t="s">
-        <v>281</v>
-      </c>
-      <c r="I121" s="8" t="s">
+      <c r="J121" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="K121" s="1" t="s">
         <v>290</v>
-      </c>
-      <c r="J121" s="8" t="s">
-        <v>283</v>
-      </c>
-      <c r="K121" s="1" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="122" customFormat="1" customHeight="1" spans="3:11">
       <c r="C122" s="1">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D122" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="E122" s="1">
+        <v>1</v>
+      </c>
+      <c r="F122" s="4">
+        <v>0</v>
+      </c>
+      <c r="G122" s="4">
+        <v>2</v>
+      </c>
+      <c r="H122" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="I122" s="8" t="s">
         <v>292</v>
       </c>
-      <c r="E122" s="1">
-        <v>1</v>
-      </c>
-      <c r="F122" s="4">
-        <v>0</v>
-      </c>
-      <c r="G122" s="4">
-        <v>2</v>
-      </c>
-      <c r="H122" s="8" t="s">
+      <c r="J122" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="K122" s="1" t="s">
         <v>293</v>
-      </c>
-      <c r="I122" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="J122" s="8" t="s">
-        <v>283</v>
-      </c>
-      <c r="K122" s="1" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="123" customFormat="1" customHeight="1" spans="3:11">
       <c r="C123" s="1">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D123" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="E123" s="1">
+        <v>1</v>
+      </c>
+      <c r="F123" s="4">
+        <v>0</v>
+      </c>
+      <c r="G123" s="4">
+        <v>2</v>
+      </c>
+      <c r="H123" s="8" t="s">
         <v>295</v>
-      </c>
-      <c r="E123" s="1">
-        <v>1</v>
-      </c>
-      <c r="F123" s="4">
-        <v>0</v>
-      </c>
-      <c r="G123" s="4">
-        <v>2</v>
-      </c>
-      <c r="H123" s="8" t="s">
-        <v>266</v>
       </c>
       <c r="I123" s="8" t="s">
         <v>296</v>
       </c>
       <c r="J123" s="8" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="K123" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="124" customFormat="1" customHeight="1" spans="3:11">
       <c r="C124" s="1">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D124" s="1" t="s">
         <v>297</v>
@@ -5746,96 +5752,96 @@
         <v>2</v>
       </c>
       <c r="H124" s="8" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="I124" s="8" t="s">
         <v>298</v>
       </c>
       <c r="J124" s="8" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="K124" s="1" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="125" ht="14"/>
+    <row r="125" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C125" s="1">
+        <v>212</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="E125" s="1">
+        <v>1</v>
+      </c>
+      <c r="F125" s="4">
+        <v>0</v>
+      </c>
+      <c r="G125" s="4">
+        <v>2</v>
+      </c>
+      <c r="H125" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="I125" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="J125" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="K125" s="1" t="s">
+        <v>299</v>
+      </c>
+    </row>
     <row r="126" ht="14"/>
-    <row r="127" ht="14" spans="3:11">
-      <c r="C127" s="1">
-        <v>301</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="E127" s="1">
-        <v>1</v>
-      </c>
-      <c r="F127" s="4">
-        <v>0</v>
-      </c>
-      <c r="G127" s="4">
-        <v>2</v>
-      </c>
-      <c r="H127" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="I127" s="8" t="s">
-        <v>301</v>
-      </c>
-      <c r="J127" s="8" t="s">
-        <v>283</v>
-      </c>
-      <c r="K127" s="1" t="s">
-        <v>299</v>
-      </c>
-    </row>
+    <row r="127" ht="14"/>
     <row r="128" ht="14" spans="3:11">
       <c r="C128" s="1">
+        <v>301</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="E128" s="1">
+        <v>1</v>
+      </c>
+      <c r="F128" s="4">
+        <v>0</v>
+      </c>
+      <c r="G128" s="4">
+        <v>2</v>
+      </c>
+      <c r="H128" s="8" t="s">
         <v>302</v>
       </c>
-      <c r="D128" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="E128" s="1"/>
-      <c r="F128" s="4"/>
-      <c r="G128" s="4"/>
-      <c r="H128" s="1"/>
-      <c r="I128" s="1"/>
-      <c r="J128" s="1"/>
-      <c r="K128" s="1"/>
+      <c r="I128" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="J128" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="K128" s="1" t="s">
+        <v>301</v>
+      </c>
     </row>
     <row r="129